--- a/data/articles.xlsx
+++ b/data/articles.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="457">
   <si>
     <t>Competitor</t>
   </si>
@@ -13110,6 +13110,84 @@
   "IMPORTANT_DATES": {"NOTIFICATION_DATE": "", "EXAM_DATE": "", "ADMIT_CARD_DATE": "", "RESULT_DATE": "", "INTERVIEW_DATE": "", "FINAL_RESULT_DATE": "", "JOINING_DATE": ""},
   "IMPORTANT_LINKS": {"OFFICIAL_NOTIFICATION_PDF": "", "APPLY_ONLINE_LINK": "", "OFFICIAL_WEBSITE": "https://rectt.crpf.gov.in", "ADMIT_CARD_LINK": "", "RESULT_LINK": "", "SYLLABUS_LINK": "", "PREVIOUS_PAPER_LINK": ""},
   "ADDITIONAL_INFO": {"PROBATION_PERIOD": "2 years", "SERVICE_BOND": "", "CAREER_GROWTH": "", "TRANSFER_POLICY": "", "RESERVATION_DETAILS": "", "CONTACT_HELPLINE": "", "IMP_INSTRUCTIONS": [], "OFFICIAL_LANGUAGE": "", "DOMICILE_REQUIREMENTS": ""}
+}</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "AAI Junior Assistant Exam 2026",
+    "RECRUITMENT_NAME": "AAI Junior Assistant Recruitment 2026",
+    "POST_NAME": "Junior Assistant",
+    "CONDUCTING_BODY": "Airports Authority of India (AAI)",
+    "EXAM_TYPE": "Recruitment Exam",
+    "CATEGORY": "Government Job"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026-01-01",
+    "RESULT_TYPE": "Final Result",
+    "DIRECT_RESULT_LINK": "https://www.aai.aero/en/careers/recruitment",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website aai.aero",
+      "Click on 'Careers' section",
+      "Find and click on 'AAI Junior Assistant Result 2026' link",
+      "Enter your registration number and date of birth",
+      "Submit and view/print your result"
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Direct link provided on freejobalert.com"
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026-01-01",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "https://www.aai.aero/en/careers/recruitment",
+    "OFFICIAL_WEBSITE": "https://www.aai.aero",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
 }</t>
   </si>
 </sst>
@@ -15970,6 +16048,29 @@
         <v>455</v>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>52</v>
+      </c>
+      <c r="B112" t="s">
+        <v>266</v>
+      </c>
+      <c r="C112" t="s">
+        <v>267</v>
+      </c>
+      <c r="D112" t="s">
+        <v>268</v>
+      </c>
+      <c r="E112" t="s">
+        <v>29</v>
+      </c>
+      <c r="F112" t="s">
+        <v>266</v>
+      </c>
+      <c r="G112" t="s">
+        <v>456</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/data/articles.xlsx
+++ b/data/articles.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="754">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="1003">
   <si>
     <t>Competitor</t>
   </si>
@@ -22127,6 +22127,7422 @@
   },
   "APPLICATION_PROCESS": {
     "APPLICATION_MODE": "ऑफलाइन",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>SSC CGL Online Form 2026 (12,256 Posts) – Start</t>
+  </si>
+  <si>
+    <t>https://sarkariresult.com.cm/ssc-cgl-2026/</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 09:46:42 +0000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Combined Graduate Level Examination 2026",
+    "JOB_TYPE": "Group B and C",
+    "JOB_CATEGORY": "Government",
+    "DEPARTMENT": "Various Ministries/Departments",
+    "MINISTRY": "Ministry of Personnel, Public Grievances and Pensions",
+    "RECRUITING_AGENCY": "Staff Selection Commission (SSC)",
+    "ADVT_NO": "To be announced",
+    "TOTAL_VACANCIES": 12256,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Assistant Audit Officer",
+        "VACANCIES": null,
+        "CATEGORY": "Group B",
+        "PAY_LEVEL": "Level 8",
+        "CLASSIFICATION": "Gazetted"
+      },
+      {
+        "POST_NAME": "Assistant Accounts Officer",
+        "VACANCIES": null,
+        "CATEGORY": "Group B",
+        "PAY_LEVEL": "Level 8",
+        "CLASSIFICATION": "Gazetted"
+      },
+      {
+        "POST_NAME": "Assistant Section Officer",
+        "VACANCIES": null,
+        "CATEGORY": "Group B",
+        "PAY_LEVEL": "Level 7",
+        "CLASSIFICATION": "Non-Gazetted"
+      },
+      {
+        "POST_NAME": "Inspector of Income Tax",
+        "VACANCIES": null,
+        "CATEGORY": "Group B",
+        "PAY_LEVEL": "Level 7",
+        "CLASSIFICATION": "Gazetted"
+      },
+      {
+        "POST_NAME": "Inspector (Central Excise/ Preventative Officer/ Examiner)",
+        "VACANCIES": null,
+        "CATEGORY": "Group B",
+        "PAY_LEVEL": "Level 7",
+        "CLASSIFICATION": "Gazetted"
+      },
+      {
+        "POST_NAME": "Inspector of Central Tax",
+        "VACANCIES": null,
+        "CATEGORY": "Group B",
+        "PAY_LEVEL": "Level 7",
+        "CLASSIFICATION": "Gazetted"
+      },
+      {
+        "POST_NAME": "Inspector of Posts",
+        "VACANCIES": null,
+        "CATEGORY": "Group B",
+        "PAY_LEVEL": "Level 7",
+        "CLASSIFICATION": "Gazetted"
+      },
+      {
+        "POST_NAME": "Sub Inspector (CBI)",
+        "VACANCIES": null,
+        "CATEGORY": "Group B",
+        "PAY_LEVEL": "Level 7",
+        "CLASSIFICATION": "Gazetted"
+      },
+      {
+        "POST_NAME": "Sub Inspector (NIA)",
+        "VACANCIES": null,
+        "CATEGORY": "Group B",
+        "PAY_LEVEL": "Level 7",
+        "CLASSIFICATION": "Gazetted"
+      },
+      {
+        "POST_NAME": "Divisional Accountant",
+        "VACANCIES": null,
+        "CATEGORY": "Group B",
+        "PAY_LEVEL": "Level 6",
+        "CLASSIFICATION": "Non-Gazetted"
+      },
+      {
+        "POST_NAME": "Statistical Investigator",
+        "VACANCIES": null,
+        "CATEGORY": "Group B",
+        "PAY_LEVEL": "Level 6",
+        "CLASSIFICATION": "Non-Gazetted"
+      },
+      {
+        "POST_NAME": "Auditor",
+        "VACANCIES": null,
+        "CATEGORY": "Group C",
+        "PAY_LEVEL": "Level 5",
+        "CLASSIFICATION": "Non-Gazetted"
+      },
+      {
+        "POST_NAME": "Accountant",
+        "VACANCIES": null,
+        "CATEGORY": "Group C",
+        "PAY_LEVEL": "Level 5",
+        "CLASSIFICATION": "Non-Gazetted"
+      },
+      {
+        "POST_NAME": "Senior Secretariat Assistant (Upper Division Clerk)",
+        "VACANCIES": null,
+        "CATEGORY": "Group C",
+        "PAY_LEVEL": "Level 4",
+        "CLASSIFICATION": "Non-Gazetted"
+      },
+      {
+        "POST_NAME": "Tax Assistant",
+        "VACANCIES": null,
+        "CATEGORY": "Group C",
+        "PAY_LEVEL": "Level 4",
+        "CLASSIFICATION": "Non-Gazetted"
+      },
+      {
+        "POST_NAME": "Sub Inspector (Central Bureau of Narcotics)",
+        "VACANCIES": null,
+        "CATEGORY": "Group B",
+        "PAY_LEVEL": "Level 7",
+        "CLASSIFICATION": "Gazetted"
+      },
+      {
+        "POST_NAME": "Assistant (Intelligence Bureau)",
+        "VACANCIES": null,
+        "CATEGORY": "Group C",
+        "PAY_LEVEL": "Level 4",
+        "CLASSIFICATION": "Non-Gazetted"
+      }
+    ],
+    "JOB_LOCATION": "All India",
+    "GROUP": "B and C"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "Level 4 to Level 8",
+    "PAY_SCALE": "As per 7th CPC",
+    "MINIMUM_SALARY": 25500,
+    "MAXIMUM_SALARY": 151100,
+    "ALLOWANCES": ["Dearness Allowance", "House Rent Allowance", "Travel Allowance"],
+    "PERKS": ["Medical Facilities", "Leave Travel Concession", "Central Government Health Scheme"]
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Bachelor's Degree from a recognized university",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "Not required",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 18,
+      "MAXIMUM_AGE": 32,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "10 years",
+        "EX_SERVICEMEN": "As per rules",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": "To be announced"
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "To be announced",
+    "APPLICATION_LAST_DATE": "To be announced",
+    "LAST_DATE_FOR_FEE": "To be announced",
+    "FORM_CORRECTION_DATE": "To be announced",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 100,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [
+        {
+          "CATEGORY": "Women",
+          "FEE": 0
+        }
+      ],
+      "PAYMENT_MODE": "Online (SBI net banking, Visa/Mastercard, etc.)"
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "Visit SSC official website (ssc.nic.in)",
+      "Click on 'Apply' for CGL 2026",
+      "Register and fill application form",
+      "Upload scanned photo and signature",
+      "Pay fee online",
+      "Submit and print confirmation"
+    ],
+    "REQUIRED_DOCUMENTS": ["Scanned photograph (passport size)", "Scanned signature", "Category certificate (if applicable)", "ID proof (Aadhar, Voter ID, etc.)"],
+    "PHOTO_SPECIFICATIONS": "Passport size, jpg format, 20-50 KB, 4.5 cm x 3.5 cm",
+    "SIGNATURE_SPECIFICATIONS": "Black ink on white paper, jpg format, 10-20 KB, 6 cm x 2 cm"
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Tier I (Computer Based Test)", "Tier II (Computer Based Test)", "Tier III (Descriptive Paper)", "Tier IV (Skill Test/ Document Verification)"],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 200,
+        "DURATION": "60 minutes",
+        "SUBJECTS": ["General Intelligence and Reasoning", "General Awareness", "Quantitative Aptitude", "English Comprehension"],
+        "NEGATIVE_MARKING": "0.50 marks for each wrong answer"
+</t>
+  </si>
+  <si>
+    <t>UP Police SI DV &amp; PST Date 2026 – Out</t>
+  </si>
+  <si>
+    <t>https://sarkariresult.com.cm/up-police-si-2025/</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 09:30:13 +0000</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "UP Police Sub Inspector (SI)",
+    "JOB_TYPE": "Direct Recruitment",
+    "JOB_CATEGORY": "State Government",
+    "DEPARTMENT": "Uttar Pradesh Police",
+    "MINISTRY": "Home Department, Government of Uttar Pradesh",
+    "RECRUITING_AGENCY": "Uttar Pradesh Police Recruitment and Promotion Board (UPPRPB)",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [],
+    "JOB_LOCATION": "Uttar Pradesh",
+    "GROUP": "Group B"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": false
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://sarkariresult.com.cm",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>RPSC RAS Pre Online Form 2026</t>
+  </si>
+  <si>
+    <t>https://sarkariresult.com.cm/rpsc-ras-2026/</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 09:28:26 +0000</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "RAS (Rajasthan Administrative Service) Pre",
+    "JOB_TYPE": "ग्रुप A (राजपत्रित)",
+    "JOB_CATEGORY": "सीधी भर्ती",
+    "DEPARTMENT": "राजस्थान प्रशासनिक सेवा",
+    "MINISTRY": "राजस्थान सरकार, कार्मिक विभाग",
+    "RECRUITING_AGENCY": "RPSC (Rajasthan Public Service Commission)",
+    "ADVT_NO": "जारी नहीं",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [],
+    "JOB_LOCATION": "राजस्थान",
+    "GROUP": "A"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "लेवल 12-15 (7वें वेतन आयोग)",
+    "PAY_SCALE": "56100-177500 रुपये",
+    "MINIMUM_SALARY": 56100,
+    "MAXIMUM_SALARY": 177500,
+    "ALLOWANCES": ["महंगाई भत्ता", "यात्रा भत्ता", "आवास भत्ता"],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "किसी मान्यता प्राप्त विश्वविद्यालय से स्नातक",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 21,
+      "MAXIMUM_AGE": 40,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 वर्ष",
+        "OBC": "3 वर्ष",
+        "PWD": "10 वर्ष",
+        "EX_SERVICEMEN": "जितनी सेवा अवधि + 3 वर्ष",
+        "WOMEN": "राजस्थान की महिलाओं को 5 वर्ष",
+        "OTHER": []
+      },
+      "AGE_AS_ON": "1 जनवरी 2026"
+    },
+    "PHYSICAL_STANDARDS": null,
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "ऑनलाइन",
+    "APPLICATION_START_DATE": "अभी घोषित नहीं",
+    "APPLICATION_LAST_DATE": "अभी घोषित नहीं",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 600,
+      "SC_ST_PWD_WOMEN": 400,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": "ऑनलाइन (डेबिट/क्रेडिट कार्ड, नेट बैंकिंग)"
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["प्रारंभिक परीक्षा", "मुख्य परीक्षा", "साक्षात्कार"],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 200,
+        "DURATION": "3 घंटे",
+        "SUBJECTS": ["सामान्य ज्ञान एवं सामान्य विज्ञान"],
+        "NEGATIVE_MARKING": "गलत उत्तर पर 1/3 अंक काटा जाएगा"
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 800,
+        "DURATION": "3 घंटे प्रति पेपर",
+        "SUBJECTS": ["सामान्य अध्ययन I, II, III, IV", "हिंदी", "अंग्रेजी", "निबंध"],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 100,
+        "DURATION": ""
+      },
+      "SKILL_TEST": null,
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "जारी नहीं",
+    "EXAM_DATE": "जारी नहीं",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "https://sso.rajasthan.gov.in",
+    "OFFICIAL_WEBSITE": "https://rpsc.rajasthan.gov.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "2 वर्ष",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "राजस्थान सरकार के नियमानुसार आरक्षण",
+    "CONTACT_HELPLINE": "0141-2717702",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "हिंदी एवं अंग्रेजी",
+    "DOMICILE_REQUIREMENTS": "राजस्थान का मूल निवासी प्रमाण पत्र आवश्यक (कुछ पदों के लिए)"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Railway RRB ALP Online Form 2026 (11,127 Posts) – Start</t>
+  </si>
+  <si>
+    <t>https://sarkariresult.com.cm/rrb-alp-2026/</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 09:27:55 +0000</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Assistant Loco Pilot",
+    "JOB_TYPE": "Regular",
+    "JOB_CATEGORY": "Technical",
+    "DEPARTMENT": "Railway",
+    "MINISTRY": "Ministry of Railways",
+    "RECRUITING_AGENCY": "Railway Recruitment Board (RRB)",
+    "ADVT_NO": "CEN 01/2026",
+    "TOTAL_VACANCIES": 11127,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Assistant Loco Pilot",
+        "VACANCIES": 11127,
+        "CATEGORY": "Group C (Non-Gazetted)",
+        "PAY_LEVEL": "Pay Level 2",
+        "CLASSIFICATION": "Technical"
+      }
+    ],
+    "JOB_LOCATION": "All India",
+    "GROUP": "C"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "Pay Level 2",
+    "PAY_SCALE": "₹ 19,900 - ₹ 63,200",
+    "MINIMUM_SALARY": 19900,
+    "MAXIMUM_SALARY": 63200,
+    "ALLOWANCES": ["Dearness Allowance", "House Rent Allowance", "Transport Allowance", "Medical Allowance"],
+    "PERKS": ["Free Railway Pass", "Uniform Allowance", "Pension"]
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Full time ITI (Fitter, Electrician, Electronics Mechanic, Instrument Mechanic, Millwright/Maintenance Mechanic, Mechanic Motor Vehicle, Wireman, Turner, Machinist, Refrigeration and Air Conditioning Mechanic, Diesel Mechanic (Road Transport)) OR Full time Diploma in Engineering (Mechanical, Electrical, Electronics, Automobile, Production) OR Full time B.Sc. (Physics and Mathematics / Computer Science / IT / Chemistry / Electronics) from recognized university OR Full time graduate degree (BA, B.Com, B.Sc) or its equivalent.",
+    "EDUCATION_DETAILS": [
+      "ITI in relevant trades",
+      "Diploma in Engineering (relevant branches)",
+      "B.Sc. with Physics and Mathematics or equivalent",
+      "Graduate degree (any discipline)"
+    ],
+    "MINIMUM_PERCENTAGE": "Not specified",
+    "EXPERIENCE_REQUIRED": "Freshers allowed",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 18,
+      "MAXIMUM_AGE": 30,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "10 years",
+        "EX_SERVICEMEN": "As per rules",
+        "WOMEN": "Not specified",
+        "OTHER": ["Relaxation for Jammu &amp; Kashmir domicile - 5 years", "Relaxation for Railway employees - up to 45 years"]
+      },
+      "AGE_AS_ON": "01-01-2026"
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "Visual Acuity Unaided: 6/6, 6/6 without glasses; Distant vision: 6/9,6/9 after correction; Near vision: Snellen 0.8, 0.8 after correction; Color vision: CP III / Must pass Lantern Test",
+      "OTHER": ["Medical fitness as per Railway norms"]
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": ["Must be a citizen of India", "Must possess valid domicile of India"]
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "January 2026 (Tentative)",
+    "APPLICATION_LAST_DATE": "February 2026 (Tentative)",
+    "LAST_DATE_FOR_FEE": "Same as application last date",
+    "FORM_CORRECTION_DATE": "Within 15 days after last date",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 500,
+      "SC_ST_PWD_WOMEN": 250,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": "Online (Debit Card, Credit Card, Net Banking, UPI)"
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "Visit official website of RRB (respective region)",
+      "Click on 'Apply Online' for CEN 01/2026",
+      "Register with email and mobile",
+      "Fill application form with personal, educational, and address details",
+      "Upload scanned photo, signature, and documents",
+      "Pay application fee online",
+      "Submit and take printout"
+    ],
+    "REQUIRED_DOCUMENTS": [
+      "Photograph (recent passport size)",
+      "Signature",
+      "Educational certificates (ITI/Diploma/Degree mark sheets)",
+      "Age proof (10th certificate)",
+      "Caste certificate (if applicable)",
+      "Disability certificate (if applicable)",
+      "PWD certificate (if applicable)",
+      "Identity proof (Aadhaar/Voter ID)"
+    ],
+    "PHOTO_SPECIFICATIONS": "4.5 cm x 3.5 cm, white background, JPEG, 20-50 KB",
+    "SIGNATURE_SPECIFICATIONS": "In black ink on white paper, JPEG, 10-20 KB"
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Computer Based Test (CBT) Stage 1", "Computer Based Test (CBT) Stage 2", "Skill Test / Aptitude Test", "Document Verification", "Medical Examination"],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 100,
+        "DURATION": "90 minutes",
+        "SUBJECTS": ["Mathematics", "General Intelligence &amp; Reasoning", "General Science", "Current Affairs and General Awareness"],
+        "NEGATIVE_MARKING": "1/3rd mark deduction for each wrong answer"
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 175,
+        "DURATION": "90 minutes",
+        "SUBJECTS": ["Part A: Mathematics", "General Intelligence &amp; Reasoning", "General Science", "General Awareness}, Part B: Qualifying – general awareness, drawing, etc."],
+        "NEGATIVE_MARKING": "1/3rd mark deduction for each wrong answer"
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "Psychometric / Aptitude Test",
+        "TOTAL_MARKS": 0,
+        "DURATION": "60 minutes"
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": ["Mathematics (Algebra, Arithmetic, Geometry, Mensuration, Statistics)", "General Intelligence (Analogies, Coding-Decoding, Puzzles, etc.)", "General Science (Physics, Chemistry, Biology up to 10th level)", "Current Affairs (National &amp; International)", "General Awareness on Indian Railway", "Trade-specific topics for ALP"],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [
+        {"YEAR": "2024", "CATEGORY": "General", "MARKS": 78.25, "POST": "ALP"},
+        {"YEAR": "2024", "CATEGORY": "OBC", "MARKS": 73.50},
+        {"YEAR": "2024", "CATEGORY": "SC", "MARKS": 65.00},
+        {"YEAR": "2024", "CATEGORY": "ST", "MARKS": 60.25}
+      ],
+      "EXPECTED": "Expected cut-off will be released after exam"
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "January 2026 (Tentative)",
+    "EXAM_DATE": "CBT Stage 1: March-April 2026; CBT Stage 2: June-July 2026",
+    "ADMIT_CARD_DATE": "4 weeks before CBT Stage 1",
+    "RESULT_DATE": "Stage 1 result after 1 month of exam",
+    "INTERVIEW_DATE": "Not applicable (no interview)",
+    "FINAL_RESULT_DATE": "After Document Verification and Medical",
+    "JOINING_DATE": "Within 6 months from final result"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "https://www.rrbapply.gov.in/</t>
+  </si>
+  <si>
+    <t>RSSB Computer Instructor Online Form 2026 (3951 Posts) – Start</t>
+  </si>
+  <si>
+    <t>https://sarkariresult.com.cm/rssb-computer-instructor-2026/</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 09:27:37 +0000</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Computer Instructor",
+    "JOB_TYPE": "Teaching",
+    "JOB_CATEGORY": "Government",
+    "DEPARTMENT": "Rajasthan Staff Selection Board",
+    "MINISTRY": "Government of Rajasthan",
+    "RECRUITING_AGENCY": "Rajasthan Staff Selection Board (RSSB)",
+    "ADVT_NO": "Not specified",
+    "TOTAL_VACANCIES": 3951,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Computer Instructor",
+        "VACANCIES": 3951,
+        "CATEGORY": "Not specified",
+        "PAY_LEVEL": "Not specified",
+        "CLASSIFICATION": "Not specified"
+      }
+    ],
+    "JOB_LOCATION": "Rajasthan",
+    "GROUP": "Not specified"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "Not specified",
+    "PAY_SCALE": "Not specified",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Bachelor's Degree in Computer Science/IT/Computer Application or equivalent with at least 50% marks; must have computer proficiency (PG Diploma in Computer Science/Computer Application or B.E./B.Tech in Computer Science/IT or M.Sc. in Computer Science/IT or equivalent). Also, must have studied Hindi as a subject in school or passed Hindi language exam at secondary level. Additional: Possess Hindi typing speed of 30 wpm (English: 40 wpm).",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "50% in graduation (relaxation as per norms)",
+    "EXPERIENCE_REQUIRED": "Not required",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 18,
+      "MAXIMUM_AGE": 40,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "10 years (gen.), 13 years (OBC), 15 years (SC/ST)",
+        "EX_SERVICEMEN": "As per rules",
+        "WOMEN": "Not specified",
+        "OTHER": []
+      },
+      "AGE_AS_ON": "Not specified"
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "Not yet announced (expected 2026)",
+    "APPLICATION_LAST_DATE": "Not yet announced",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 600,
+      "SC_ST_PWD_WOMEN": 400,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": "Online"
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Written Exam", "Skill Test (Typing) - qualifying", "Document Verification"],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 200,
+        "DURATION": "3 hours",
+        "SUBJECTS": ["Subject Concerned (Computer) - 150 marks", "Rajasthan GK - 25 marks", "Hindi - 25 marks"],
+        "NEGATIVE_MARKING": "1/3 marks deduction for each wrong answer"
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "Typing Test (Hindi/English) - qualifying",
+        "TOTAL_MARKS": 0,
+        "DURATION": "Not specified"
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "To be announced (expected 2026)",
+    "EXAM_DATE": "Not yet announced",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "Not available yet (expected when released)",
+    "APPLY_ONLINE_LINK": "Not available yet (will be on rssb.rajasthan.gov.in)",
+    "OFFICIAL_WEBSITE": "https://rssb.rajasthan.gov.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "As per Rajasthan government norms",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "Hindi &amp; English",
+    "DOMICILE_REQUIREMENTS": "Rajasthan Domicile (as per norms)"
+  }
+}</t>
+  </si>
+  <si>
+    <t>BSNL Junior Telecom Officer JTO Online Form 2026</t>
+  </si>
+  <si>
+    <t>https://sarkariresult.com.cm/bsnl-junior-telecom-officer-jto-2026/</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 09:23:29 +0000</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "जूनियर टेलीकॉम ऑफिसर (JTO)",
+    "JOB_TYPE": "सरकारी नौकरी",
+    "JOB_CATEGORY": "तकनीकी",
+    "DEPARTMENT": "टेलीकॉम",
+    "MINISTRY": "दूरसंचार विभाग",
+    "RECRUITING_AGENCY": "BSNL",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "JTO",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "देशभर",
+    "GROUP": "ग्रुप B"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "BE/B.Tech या समकक्ष",
+    "EDUCATION_DETAILS": [
+      "BE/B.Tech (इलेक्ट्रॉनिक्स/कम्युनिकेशन/कंप्यूटर/इंफॉर्मेशन टेक्नोलॉजी)"
+    ],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 18,
+      "MAXIMUM_AGE": 30,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 वर्ष",
+        "OBC": "3 वर्ष",
+        "PWD": "10 वर्ष",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": "अधिसूचना अनुसार"
+    },
+    "PHYSICAL_STANDARDS": {},
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "ऑनलाइन",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "BSNL की आधिकारिक वेबसाइट पर जाएं",
+      "ऑनलाइन आवेदन फॉर्म भरें",
+      "आवश्यक दस्तावेज अपलोड करें",
+      "शुल्क का भुगतान करें"
+    ],
+    "REQUIRED_DOCUMENTS": [
+      "शैक्षिक प्रमाणपत्र",
+      "आयु प्रमाण",
+      "जाति प्रमाणपत्र",
+      "फोटो",
+      "हस्ताक्षर"
+    ],
+    "PHOTO_SPECIFICATIONS": "पासपोर्ट साइज",
+    "SIGNATURE_SPECIFICATIONS": "स्कैन की गई हस्ताक्षर"
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["लिखित परीक्षा", "साक्षात्कार"],
+    "EXAM_PATTERN": {
+      "PRELIMS": {},
+      "MAINS": {
+        "TOTAL_MARKS": 500,
+        "DURATION": "3 घंटे",
+        "SUBJECTS": ["टेलीकॉम/इलेक्ट्रॉनिक्स", "जनरल अवेयरनेस", "अंग्रेजी"],
+        "NEGATIVE_MARKING": "गलत उत्तर पर 1/3 अंक काटे जाएंगे"
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 100,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {},
+      "PHYSICAL_EFFICIENCY_TEST": {},
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": ["इलेक्ट्रॉनिक्स", "डिजिटल सर्किट", "नेटवर्किंग", "कंप्यूटर", "जनरल नॉलेज"],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.bsnl.co.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "सरकारी नियमानुसार",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "हिंदी/अंग्रेजी",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>UPSC IAS / IFS Pre Answer Key 2026 – Out</t>
+  </si>
+  <si>
+    <t>https://sarkariresult.com.cm/upsc-civil-services-ias-ifs-2026/</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 08:58:03 +0000</t>
+  </si>
+  <si>
+    <t>{
+  "ANSWER_KEY_IDENTIFICATION": {
+    "EXAM_NAME": "Civil Services (Preliminary) Examination",
+    "RECRUITMENT_NAME": "UPSC IAS/IFS Recruitment",
+    "POST_NAME": "IAS/IFS",
+    "CONDUCTING_BODY": "Union Public Service Commission (UPSC)",
+    "EXAM_TYPE": "Preliminary",
+    "CATEGORY": "Central Government",
+    "SET_CODE": ""
+  },
+  "ANSWER_KEY_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "2026-06-01",
+    "ANSWER_KEY_TYPE": "Provisional",
+    "DIRECT_DOWNLOAD_LINK": "https://sarkariresult.com.cm/upsc-civil-services-ias-ifs-2026/answer-key",
+    "STATUS_CHECK_LINK": "https://sarkariresult.com.cm/upsc-civil-services-ias-ifs-2026/"
+  },
+  "HOW_TO_DOWNLOAD_OR_CHECK": {
+    "STEPS": [
+      "Visit the official UPSC website or the provided link.",
+      "Click on the 'Answer Key' link for Civil Services (Prelim) 2026.",
+      "Select your set code (A/B/C/D) if applicable.",
+      "Download the PDF file."
+    ],
+    "REQUIRED_DETAILS": ["Set code", "Roll number (optional)"],
+    "ALTERNATE_METHOD": ""
+  },
+  "ANSWER_KEY_DETAILS": {
+    "SUBJECT_WISE_KEYS": [
+      {
+        "SUBJECT": "General Studies Paper I",
+        "SET_CODE": "",
+        "DOWNLOAD_LINK": "https://sarkariresult.com.cm/upsc-civil-services-ias-ifs-2026/answer-key-gs1"
+      },
+      {
+        "SUBJECT": "CSAT Paper II",
+        "SET_CODE": "",
+        "DOWNLOAD_LINK": "https://sarkariresult.com.cm/upsc-civil-services-ias-ifs-2026/answer-key-csat"
+      }
+    ],
+    "QUESTION_WISE_ANSWER": [],
+    "MASTER_QUESTION_PAPER_LINK": "",
+    "SHIFT_WISE": []
+  },
+  "OBJECTION_PROCESS": {
+    "OBJECTION_WINDOW_START": "2026-06-02",
+    "OBJECTION_WINDOW_END": "2026-06-08",
+    "OBJECTION_FEE_PER_QUESTION": 200,
+    "HOW_TO_RAISE_OBJECTION": [
+      "Log in to the UPSC objection portal using credentials.",
+      "Select the question and provide evidence.",
+      "Pay the fee online."
+    ],
+    "REVISED_KEY_DATE": "2026-07-01"
+  },
+  "IMPORTANT_DATES": {
+    "ANSWER_KEY_AVAILABLE_FROM": "2026-06-01",
+    "ANSWER_KEY_AVAILABLE_UNTIL": "",
+    "OBJECTION_WINDOW": "2026-06-02 to 2026-06-08",
+    "FINAL_KEY_DATE": "2026-07-01",
+    "RESULT_DATE": "2026-07-15"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://sarkariresult.com.cm/upsc-civil-services-ias-ifs-2026/notification",
+    "DIRECT_DOWNLOAD": "https://sarkariresult.com.cm/upsc-civil-services-ias-ifs-2026/answer-key",
+    "OFFICIAL_WEBSITE": "https://upsc.gov.in",
+    "HELPLINE_NUMBER": "1800-111-555"
+  },
+  "ADDITIONAL_INFO": {
+    "GENERAL_INSTRUCTIONS": [
+      "Answer key is provisional; challenge if needed.",
+      "Keep roll number ready for objection."
+    ],
+    "DISPUTE_RESOLUTION": "Objections are reviewed within 2 weeks.",
+    "REVALUATION_PROCESS": "Not applicable for prelims.",
+    "CONTACT_DETAILS": "upsc@nic.in"
+  }
+}</t>
+  </si>
+  <si>
+    <t>JMI Guest Teacher Recruitment  2026 - Apply Offline for 34 PGT &amp; TGT Posts</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/jmi-guest-teacher-recruitment-2026-apply-offline-for-34-pgt-tgt-posts-3051329</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 10:47:08 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Guest Teacher",
+    "JOB_TYPE": "Teaching",
+    "JOB_CATEGORY": "Guest Faculty",
+    "DEPARTMENT": "School Education",
+    "MINISTRY": "Ministry of Education",
+    "RECRUITING_AGENCY": "Jamia Millia Islamia (JMI)",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 34,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "PGT",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": "Teaching"
+      },
+      {
+        "POST_NAME": "TGT",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": "Teaching"
+      }
+    ],
+    "JOB_LOCATION": "New Delhi",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Offline",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.jmi.ac.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Calicut University Time Table 2026 OUT - Download UG Supplementary &amp; Improvement Exam PDF at uoc.ac.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/calicut-university-time-table-2026-out-download-ug-supplementary-and-improvement-exam-pdf-3051327</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 10:45:22 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "SYLLABUS_IDENTIFICATION": {
+    "EXAM_NAME": "UG Supplementary &amp; Improvement Exam",
+    "RECRUITMENT_NAME": "",
+    "CONDUCTING_BODY": "Calicut University",
+    "EXAM_TYPE": "Supplementary &amp; Improvement",
+    "CATEGORY": "University Exam",
+    "ACADEMIC_YEAR": "2026",
+    "CLASS_OR_LEVEL": "UG"
+  },
+  "SYLLABUS_STATUS": {
+    "RELEASED": false,
+    "RELEASE_DATE": "",
+    "SYLLABUS_VERSION": "",
+    "OFFICIAL_SYLLABUS_LINK": ""
+  },
+  "EXAM_PATTERN_OVERVIEW": {
+    "TOTAL_MARKS": 0,
+    "TOTAL_QUESTIONS": 0,
+    "DURATION": "",
+    "MEDIUM": "",
+    "MODE": "",
+    "NEGATIVE_MARKING": "",
+    "SECTIONS_COUNT": 0
+  },
+  "SUBJECTS": [],
+  "SECTIONAL_DETAILS": [],
+  "RECOMMENDED_RESOURCES": {
+    "BOOKS": [],
+    "ONLINE_RESOURCES": [],
+    "PREVIOUS_YEAR_PAPERS_LINK": ""
+  },
+  "PREPARATION_TIPS": {
+    "STRATEGY": "",
+    "IMPORTANT_TOPICS": [],
+    "TIME_MANAGEMENT_TIPS": ""
+  },
+  "IMPORTANT_DATES": {
+    "SYLLABUS_RELEASE_DATE": "",
+    "LAST_UPDATED": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "SYLLABUS_PDF": "",
+    "OFFICIAL_WEBSITE": "https://www.uoc.ac.in"
+  },
+  "ADDITIONAL_INFO": {
+    "FREQUENTLY_ASKED_QUESTIONS": [],
+    "LATEST_CHANGES": "",
+    "CONTACT_HELPLINE": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>RRB NTPC UG Final Cut Off Marks 2025-26 OUT: Download PDF, Zone Wise Marks and More</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/rrb-ntpc-ug-final-cut-off-2026-3051325</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 10:43:16 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "RRB NTPC UG",
+    "RECRUITMENT_NAME": "RRB NTPC Undergraduate Recruitment",
+    "POST_NAME": "Various Under Graduate Posts",
+    "CONDUCTING_BODY": "Railway Recruitment Board (RRB)",
+    "EXAM_TYPE": "Recruitment Exam",
+    "CATEGORY": "Government"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2025-2026",
+    "RESULT_TYPE": "Final Cut Off Marks",
+    "DIRECT_RESULT_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [],
+    "REQUIRED_DETAILS": [],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "https://www.freejobalert.com/articles/rrb-ntpc-ug-final-cut-off-2026-3051325",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "https://www.freejobalert.com/articles/rrb-ntpc-ug-final-cut-off-2026-3051325",
+    "OFFICIAL_WEBSITE": "",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>BEL Senior Assistant Engineer Recruitment 2026 - Apply Offline</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/bel-senior-assistant-engineer-recruitment-2026-apply-offline-3051324</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 10:42:23 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Senior Assistant Engineer",
+    "JOB_TYPE": "Engineering",
+    "JOB_CATEGORY": "Technical",
+    "DEPARTMENT": "Engineering",
+    "MINISTRY": "Ministry of Defence",
+    "RECRUITING_AGENCY": "Bharat Electronics Limited (BEL)",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Senior Assistant Engineer",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "Various",
+    "GROUP": "A"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "₹40,000 - ₹1,40,000",
+    "MINIMUM_SALARY": 40000,
+    "MAXIMUM_SALARY": 140000,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "B.E./B.Tech in relevant engineering discipline",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "2 years of relevant experience",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 32,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "10 years",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Offline",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 500,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": "Demand Draft"
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.bel-india.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "1 year",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "As per Govt. norms",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Vikram University Time Table 2026 OUT - Download Revised UG &amp; PG Exam Schedule PDF at vikramuniv.ac.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/vikram-university-time-table-2026-out-download-revised-ug-pg-exam-schedule-pdf-3051322</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 10:38:36 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "SYLLABUS_IDENTIFICATION": {
+    "EXAM_NAME": "Vikram University UG/PG Exams",
+    "RECRUITMENT_NAME": "",
+    "CONDUCTING_BODY": "Vikram University",
+    "EXAM_TYPE": "University Semester/Annual Examinations",
+    "CATEGORY": "University",
+    "ACADEMIC_YEAR": "2026",
+    "CLASS_OR_LEVEL": "UG and PG"
+  },
+  "SYLLABUS_STATUS": {
+    "RELEASED": false,
+    "RELEASE_DATE": "",
+    "SYLLABUS_VERSION": "",
+    "OFFICIAL_SYLLABUS_LINK": ""
+  },
+  "EXAM_PATTERN_OVERVIEW": {
+    "TOTAL_MARKS": 0,
+    "TOTAL_QUESTIONS": 0,
+    "DURATION": "",
+    "MEDIUM": "",
+    "MODE": "Offline",
+    "NEGATIVE_MARKING": "",
+    "SECTIONS_COUNT": 0
+  },
+  "SUBJECTS": [],
+  "SECTIONAL_DETAILS": [],
+  "RECOMMENDED_RESOURCES": {
+    "BOOKS": [],
+    "ONLINE_RESOURCES": [],
+    "PREVIOUS_YEAR_PAPERS_LINK": ""
+  },
+  "PREPARATION_TIPS": {
+    "STRATEGY": "",
+    "IMPORTANT_TOPICS": [],
+    "TIME_MANAGEMENT_TIPS": ""
+  },
+  "IMPORTANT_DATES": {
+    "SYLLABUS_RELEASE_DATE": "",
+    "LAST_UPDATED": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "SYLLABUS_PDF": "",
+    "OFFICIAL_WEBSITE": "https://vikramuniv.ac.in"
+  },
+  "ADDITIONAL_INFO": {
+    "FREQUENTLY_ASKED_QUESTIONS": [],
+    "LATEST_CHANGES": "Revised UG &amp; PG Exam Schedule released",
+    "CONTACT_HELPLINE": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>BBMB ITI Apprentices 2026-27: Apply Online for 45 Posts at Dehar Power House Circle, Slapper</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/bbmb-iti-apprentices-recruitment-2026-apply-online-for-45-posts-3051321</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 10:37:09 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "ITI Apprentices",
+    "JOB_TYPE": "Apprenticeship",
+    "JOB_CATEGORY": "Technical",
+    "DEPARTMENT": "Dehar Power House Circle",
+    "MINISTRY": "Ministry of Power",
+    "RECRUITING_AGENCY": "BBMB (Bhakra Beas Management Board)",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 45,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "ITI Apprentice",
+        "VACANCIES": 45,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": "Group C"
+      }
+    ],
+    "JOB_LOCATION": "Dehar Power House Circle, Slapper, Himachal Pradesh",
+    "GROUP": "C"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "As per Apprenticeship Act",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "ITI (Industrial Training Institute) in relevant trade",
+    "EDUCATION_DETAILS": [
+      "ITI in relevant trade"
+    ],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "No experience required",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 18,
+      "MAXIMUM_AGE": 35,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "10 years",
+        "EX_SERVICEMEN": "As per rules",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": null,
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": "No fee"
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "Apply online through the BBMB official website or designated portal",
+      "Fill in the required details",
+      "Upload scanned documents"
+    ],
+    "REQUIRED_DOCUMENTS": [
+      "ITI certificate",
+      "Age proof",
+      "Category certificate if applicable",
+      "Photograph and signature"
+    ],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [
+      "Merit List based on ITI marks"
+    ],
+    "EXAM_PATTERN": null,
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": null
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "No exam",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Gujarat University Research Associate Recruitment 2026 - Apply Online for 28 Posts</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/gujarat-university-research-associate-recruitment-2026-apply-online-for-28-posts-3051320</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 10:34:10 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Research Associate",
+    "JOB_TYPE": "अनुबंध",
+    "JOB_CATEGORY": "शोध",
+    "DEPARTMENT": "Research",
+    "MINISTRY": "",
+    "RECRUITING_AGENCY": "Gujarat University",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 28,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Research Associate",
+        "VACANCIES": 28,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "Gujarat",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>CMHO Korba Radiographer Result 2026 OUT (Direct Link) - Download Scorecard @korba.gov.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/cmho-korba-radiographer-result-2026-3051315</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 10:31:28 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "CMHO Korba Radiographer Exam 2025",
+    "RECRUITMENT_NAME": "CMHO Korba Radiographer Recruitment",
+    "POST_NAME": "Radiographer",
+    "CONDUCTING_BODY": "CMHO Korba, Chhattisgarh",
+    "EXAM_TYPE": "Recruitment",
+    "CATEGORY": "Health Department"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2025-04-02",
+    "RESULT_TYPE": "Written Exam Result",
+    "DIRECT_RESULT_LINK": "https://korba.gov.in/en/radiography-2025/",
+    "STATUS_CHECK_LINK": "https://korba.gov.in/"
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website korba.gov.in",
+      "Click on the 'Radiographer Result 2026' link on the homepage",
+      "Enter your registration number and date of birth",
+      "Submit to view result",
+      "Download and print the result for future reference"
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Direct link provided on FreeJobAlert."
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "https://korba.gov.in/merit-list-radiographer-2025.pdf",
+      "CUTOFF_MARKS": {
+        "GENERAL": 70,
+        "OBC": 65,
+        "SC": 60,
+        "ST": 55,
+        "EWS": 0,
+        "PWD": 50,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": "https://korba.gov.in/answer-key-radiographer-2025.pdf"
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "2025-04-30",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "2025-06-01",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2025-04-02",
+    "LAST_DATE_TO_CHECK": "2025-05-15",
+    "REVALUATION_DATE": "2025-04-10"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://korba.gov.in/notification-radiographer-2025.pdf",
+    "DIRECT_RESULT": "https://korba.gov.in/en/radiography-2025/",
+    "OFFICIAL_WEBSITE": "https://korba.gov.in",
+    "HELPLINE_NUMBER": "07759-234567"
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "In case of tie, the older candidate will be given preference.",
+    "REVALUATION_PROCESS": "Candidates can apply for revaluation within 7 days of result declaration by paying Rs. 500 per question.",
+    "CONTACT_DETAILS": "CMHO Office, Korba, Chhattisgarh - 495677",
+    "IMP_INSTRUCTIONS": [
+      "Keep a copy of the result for document verification.",
+      "Original documents must be presented during verification.",
+      "No TA/DA will be paid for attending document verification."
+    ]
+  }
+}</t>
+  </si>
+  <si>
+    <t>Rajasthan University Time Table 2026 OUT - Download Uniraj MBA &amp; LLB Exam Date Sheet PDF at uniraj.ac.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/rajasthan-university-time-table-2026-out-download-uniraj-mba-and-llb-exam-date-sheet-pdf-3051316</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 10:30:22 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "MBA &amp; LLB Examination",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "University of Rajasthan (Uniraj)",
+    "EXAM_TYPE": "University Exam",
+    "CATEGORY": "Time Table"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": false,
+    "DECLARATION_DATE": "",
+    "RESULT_TYPE": "",
+    "DIRECT_RESULT_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [],
+    "REQUIRED_DETAILS": [],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://www.freejobalert.com/articles/rajasthan-university-time-table-2026-out-download-uniraj-mba-and-llb-exam-date-sheet-pdf-3051316",
+    "DIRECT_RESULT": "",
+    "OFFICIAL_WEBSITE": "https://uniraj.ac.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>Dantewada District Assistant Veterinary Field Officer Recruitment 2026 - Apply Offline</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/dantewada-district-assistant-veterinary-field-officer-avfo-third-class-recruitment-2026-apply-offline-3051314</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 10:25:13 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Assistant Veterinary Field Officer (Third Class)",
+    "JOB_TYPE": "सरकारी",
+    "JOB_CATEGORY": "गैर-तकनीकी",
+    "DEPARTMENT": "पशुधन विकास विभाग",
+    "MINISTRY": "",
+    "RECRUITING_AGENCY": "जिला पशुधन विकास अधिकारी, दंतेवाड़ा",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Assistant Veterinary Field Officer",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": "Third Class"
+      }
+    ],
+    "JOB_LOCATION": "दंतेवाड़ा, छत्तीसगढ़",
+    "GROUP": "C"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "मान्यता प्राप्त बोर्ड से 10+2 या समकक्ष, और डेयरी/पशुपालन/वेटरनरी साइंस में डिप्लोमा",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 18,
+      "MAXIMUM_AGE": 40,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 वर्ष",
+        "OBC": "3 वर्ष",
+        "PWD": "10 वर्ष",
+        "EX_SERVICEMEN": "जैसा नियमानुसार",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "ऑफलाइन",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": "छत्तीसगढ़ के मूल निवासी को प्राथमिकता"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Jharkhand Field Worker Exam Date 2026 (Out) - Check Schedule &amp; Details</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/jharkhand-field-worker-exam-date-2026-3051312</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 10:24:41 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Field Worker",
+    "JOB_TYPE": "Government Job",
+    "JOB_CATEGORY": "Group C",
+    "DEPARTMENT": "Health Department",
+    "MINISTRY": "Ministry of Health and Family Welfare",
+    "RECRUITING_AGENCY": "Jharkhand Staff Selection Commission (JSSC)",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Field Worker",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "Jharkhand",
+    "GROUP": "C"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 18,
+      "MAXIMUM_AGE": 40,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "10 years",
+        "EX_SERVICEMEN": "3 years",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": "01-01-2026"
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Written Exam"],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "2026",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.freejobalert.com",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Mumbai University Time Table 2026 OUT - Check MA Geography Practical Exam Schedule PDF at mu.ac.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/mumbai-university-time-table-2026-out-check-ma-geography-practical-exam-schedule-pdf-3051311</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 10:23:22 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "MA Geography Practical Exam",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Mumbai University",
+    "EXAM_TYPE": "University Exam",
+    "CATEGORY": "Time Table"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": false,
+    "DECLARATION_DATE": "",
+    "RESULT_TYPE": "Time Table",
+    "DIRECT_RESULT_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": ["Visit mu.ac.in", "Navigate to Time Table section", "Download the MA Geography Practical Exam schedule PDF"],
+    "REQUIRED_DETAILS": [],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "",
+    "OFFICIAL_WEBSITE": "https://mu.ac.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>ZSS Jajpur Recruitment 2026 - Apply Offline for 13 BPM, Medical Officer and More Posts</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/zss-jajpur-recruitment-2026-apply-offline-for-13-bpm-medical-officer-and-more-posts-3051310</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 10:17:18 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "BPM, Medical Officer and Others",
+    "JOB_TYPE": "Regular",
+    "JOB_CATEGORY": "Group B and C",
+    "DEPARTMENT": "Zilla Swasthya Samiti (ZSS), Jajpur",
+    "MINISTRY": "Health and Family Welfare",
+    "RECRUITING_AGENCY": "Zilla Swasthya Samiti (ZSS), Jajpur",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 13,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Block Programme Manager (BPM)",
+        "VACANCIES": 6,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      },
+      {
+        "POST_NAME": "Medical Officer",
+        "VACANCIES": 3,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      },
+      {
+        "POST_NAME": "Other Posts",
+        "VACANCIES": 4,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "Jajpur, Odisha",
+    "GROUP": "B and C"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "As per Govt norms",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Varies by post",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 21,
+      "MAXIMUM_AGE": 45,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Offline",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "16-12-2025",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "Visit the official website or ZSS Jajpur office.",
+      "Download the application form.",
+      "Fill the form with required details.",
+      "Attach self-attested copies of documents.",
+      "Submit the application before the last date."
+    ],
+    "REQUIRED_DOCUMENTS": [
+      "Educational certificates",
+      "Age proof",
+      "Caste certificate (if applicable)",
+      "Experience certificate (if required)",
+      "Passport size photographs",
+      "ID proof"
+    ],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [
+      "Written Exam",
+      "Interview"
+    ],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>TNPSC CTS Exam Notification 2026 Out For 461 Non Interview Post - Apply Online</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/tnpsc-cts-exam-non-interview-posts-recruitment-2026-apply-online-for-461-posts-3049979</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 10:12:50 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Combined Technical Services Examination (CTS) - Non Interview Posts",
+    "JOB_TYPE": "Sarkari Naukri",
+    "JOB_CATEGORY": "Technical Services",
+    "DEPARTMENT": "Tamil Nadu Public Service Commission (TNPSC)",
+    "MINISTRY": "Government of Tamil Nadu",
+    "RECRUITING_AGENCY": "Tamil Nadu Public Service Commission (TNPSC)",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 461,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Junior Draughting Officer",
+        "VACANCIES": 461,
+        "CATEGORY": "Group B",
+        "PAY_LEVEL": "Level 20 (Rs. 35,400 - 1,12,400) as per 7th CPC",
+        "CLASSIFICATION": "Technical"
+      }
+    ],
+    "JOB_LOCATION": "Tamil Nadu",
+    "GROUP": "B"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "Level 20",
+    "PAY_SCALE": "Rs. 35,400 - 1,12,400",
+    "MINIMUM_SALARY": 35400,
+    "MAXIMUM_SALARY": 112400,
+    "ALLOWANCES": ["Dearness Allowance", "House Rent Allowance", "Medical Allowance", "Other allowances as per rules"],
+    "PERKS": ["Travel Allowance", "Dearness Allowance", "House Rent Allowance"]
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Degree in Civil Engineering / Mechanical Engineering / Electrical Engineering / Electronics and Communication Engineering / Automobile Engineering / Architecture / Town Planning / or equivalent from a recognized university",
+    "EDUCATION_DETAILS": [
+      "Bachelor's Degree in Engineering or Technology in relevant discipline"
+    ],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 18,
+      "MAXIMUM_AGE": 32,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "10 years",
+        "EX_SERVICEMEN": "As per rules",
+        "WOMEN": "",
+        "OTHER": ["MBC/DC: 3 years", "Destitute Widow: 7 years"]
+      },
+      "AGE_AS_ON": "01.07.2026"
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": ["Must have studied Tamil language as a subject in school or passed SSLC/Class 10 with Tamil as language"]
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "2026-01-02",
+    "APPLICATION_LAST_DATE": "2026-02-01",
+    "LAST_DATE_FOR_FEE": "2026-02-01",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 200,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [{"category": "Ex-Servicemen", "amount": 0}],
+      "PAYMENT_MODE": "Online (Net Banking, Credit Card, Debit Card)"
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "Visit the official TNPSC website (www.tnpsc.gov.in)",
+      "Click on the 'Apply Online' link for CTS Exam 2026",
+      "Register with email and mobile number",
+      "Fill the application form with personal and educational details",
+      "Upload scanned photograph, signature and thumb impression",
+      "Pay the application fee online",
+      "Submit the form and take a printout for future reference"
+    ],
+    "REQUIRED_DOCUMENTS": ["Scanned photograph", "Scanned signature", "Scanned thumb impression", "Educational certificates", "Age proof", "Community certificate if applicable"],
+    "PHOTO_SPECIFICATIONS": "Passport size (e.g., 3.5 cm x 4.5 cm) in JPEG format, size between 10 KB to 100 KB",
+    "SIGNATURE_SPECIFICATIONS": "White background with black ink, JPEG format, size between 10 KB to 100 KB"
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Objective Type Exam (Written)", "Document Verification"],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 300,
+        "DURATION": "3 hours",
+        "SUBJECTS": ["Subject Paper: Engineering discipline relevant (300 marks)"],
+        "NEGATIVE_MARKING": "1/3 marks deducted for each wrong answer"
+      },
+      "INTERVIEW": null,
+      "SKILL_TEST": null,
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": ["Civil Engineering", "Mechanical Engineering", "Electrical Engineering", "Electronics and Communication Engineering", "Automobile Engineering", "Architecture and Town Planning"],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "2026-01-02",
+    "EXAM_DATE": "2026-04-19",
+    "ADMIT_CARD_DATE": "10 days before exam",
+    "RESULT_DATE": "2026-06-30",
+    "INTERVIEW_DATE": null,
+    "FINAL_RESULT_DATE": "2026-07-31",
+    "JOINING_DATE": "2026-09-01"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "https://www.tnpsc.gov.in/notifications/CTS2026.pdf",
+    "APPLY_ONLINE_LINK": "https://apply.tnpsc.gov.in/",
+    "OFFICIAL_WEBSITE": "https://www.tnpsc.gov.in",
+    "ADMIT_CARD_LINK": "https://www.tnpsc.gov.in/admitcards",
+    "RESULT_LINK": "https://www.tnpsc.gov.in/results",
+    "SYLLABUS_LINK": "https://www.tnpsc.gov.in/syllabus/CTS2026.pdf",
+    "PREVIOUS_PAPER_LINK": "https://www.tnpsc.gov.in/previouspapers"
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "2 years",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "Promotion to higher grades as per departmental rules",
+    "TRANSFER_POLICY": "Transferable within Tamil Nadu",
+    "RESERVATION_DETAILS": "As per Government of Tamil Nadu reservation rules for SC/ST/OBC/MBC/EWS",
+    "CONTACT_HELPLINE": "1800-XXX-XXXX (toll free)",
+    "IMP_INSTRUCTIONS": [
+      "Candidates must bring original documents at the time of certificate verification.",
+      "Candidates must have a valid email ID and mobile number.",
+      "Applications submitted incomplete will be rejected."
+    ],
+    "OFFICIAL_LANGUAGE": "Tamil and English",
+    "DOMICILE_REQUIREMENTS": "No domicile requirement, but preference given to Tamil Nadu domicile in some cases"
+  }
+}</t>
+  </si>
+  <si>
+    <t>MMRCL Recruitment 2026 Notification Out - Apply Online for 24 Assistant, Jr Engineer and More Posts</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/mmrcl-recruitment-2026-apply-online-for-24-assistant-jr-engineer-and-more-posts-3051307</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 10:06:08 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Assistant, Jr Engineer and More Posts",
+    "JOB_TYPE": "Government Job",
+    "JOB_CATEGORY": "Technical &amp; Non-Technical",
+    "DEPARTMENT": "Maha Mumbai Metro Rail Corporation",
+    "MINISTRY": "",
+    "RECRUITING_AGENCY": "Maha Mumbai Metro Rail Corporation (MMRCL)",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 24,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Assistant",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      },
+      {
+        "POST_NAME": "Junior Engineer",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      },
+      {
+        "POST_NAME": "Other Posts",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "Mumbai, Maharashtra",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Varies by post",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": ["Visit official website", "Fill online application", "Upload documents", "Pay fee", "Submit"],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Written Exam", "Interview"],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "https://www.freejobalert.com/articles/mmrcl-recruitment-2026-apply-online-for-24-assistant-jr-engineer-and-more-posts-3051307",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>UPSC CSE Prelims Answer Key 2026 (Out) - Download PDF, Response Sheet &amp; Objection Link</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/upsc-cse-prelims-answer-key-2026-3051306</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 09:59:18 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "ANSWER_KEY_IDENTIFICATION": {
+    "EXAM_NAME": "UPSC CSE Prelims",
+    "RECRUITMENT_NAME": "Civil Services Examination",
+    "POST_NAME": "Various Civil Services Posts",
+    "CONDUCTING_BODY": "Union Public Service Commission (UPSC)",
+    "EXAM_TYPE": "Preliminary Examination",
+    "CATEGORY": "Civil Services",
+    "SET_CODE": ""
+  },
+  "ANSWER_KEY_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "2026-05-31",
+    "ANSWER_KEY_TYPE": "Provisional",
+    "DIRECT_DOWNLOAD_LINK": "https://www.freejobalert.com/upsc-cse-prelims-answer-key-2026",
+    "STATUS_CHECK_LINK": "https://upsc.gov.in/"
+  },
+  "HOW_TO_DOWNLOAD_OR_CHECK": {
+    "STEPS": [
+      "Visit the official UPSC website or the direct download link.",
+      "Click on the link for 'UPSC CSE Prelims Answer Key 2026'.",
+      "Enter your roll number and date of birth if required.",
+      "Download the PDF or view the response sheet.",
+      "Save or print the answer key for future reference."
+    ],
+    "REQUIRED_DETAILS": [
+      "Roll Number",
+      "Date of Birth",
+      "Exam Set Code (if applicable)"
+    ],
+    "ALTERNATE_METHOD": "You can also check the answer key from the FreeJobAlert portal by clicking the provided direct download link."
+  },
+  "ANSWER_KEY_DETAILS": {
+    "SUBJECT_WISE_KEYS": [],
+    "QUESTION_WISE_ANSWER": [],
+    "MASTER_QUESTION_PAPER_LINK": "",
+    "SHIFT_WISE": [
+      {
+        "SHIFT": "Morning Shift",
+        "DATE": "2026-05-26",
+        "KEY_LINK": "https://www.freejobalert.com/upsc-cse-prelims-answer-key-2026"
+      }
+    ]
+  },
+  "OBJECTION_PROCESS": {
+    "OBJECTION_WINDOW_START": "2026-06-01",
+    "OBJECTION_WINDOW_END": "2026-06-07",
+    "OBJECTION_FEE_PER_QUESTION": 100,
+    "HOW_TO_RAISE_OBJECTION": [
+      "Go to the official UPSC website.",
+      "Log in with your credentials.",
+      "Navigate to the objection section for CSE Prelims 2026.",
+      "Select the question(s) you wish to challenge.",
+      "Provide a valid reason and upload supporting documents.",
+      "Pay the objection fee per question (₹100 each).",
+      "Submit the objection."
+    ],
+    "REVISED_KEY_DATE": "2026-06-21"
+  },
+  "IMPORTANT_DATES": {
+    "ANSWER_KEY_AVAILABLE_FROM": "2026-05-31",
+    "ANSWER_KEY_AVAILABLE_UNTIL": "2026-12-31",
+    "OBJECTION_WINDOW": "2026-06-01 to 2026-06-07",
+    "FINAL_KEY_DATE": "2026-06-21",
+    "RESULT_DATE": "2026-07-15"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://upsc.gov.in/sites/default/files/notifications/CSE_2026_Prelim_Answer_Key.pdf",
+    "DIRECT_DOWNLOAD": "https://www.freejobalert.com/upsc-cse-prelims-answer-key-2026",
+    "OFFICIAL_WEBSITE": "https://upsc.gov.in/",
+    "HELPLINE_NUMBER": "1800-111-555"
+  },
+  "ADDITIONAL_INFO": {
+    "GENERAL_INSTRUCTIONS": [
+      "Candidates should verify their answers with the official answer key.",
+      "Objections must be submitted within the given window period.",
+      "No objections will be entertained after the deadline."
+    ],
+    "DISPUTE_RESOLUTION": "Any dispute regarding the answer key can be raised through the objection process.",
+    "REVALUATION_PROCESS": "Revaluation is not applicable for UPSC CSE Prelims. Only answer key objections are considered.",
+    "CONTACT_DETAILS": "For any queries, contact UPSC helpline at 1800-111-555 or email at upsc@nic.in"
+  }
+}</t>
+  </si>
+  <si>
+    <t>HSCAP Kerala Plus One Admission 2026: Chect Important Date, Steps to Apply and Eligibility</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/hscap-kerala-plus-one-admission-2026-3051305</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 09:58:42 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "MAIN_TOPIC": "HSCAP Kerala Plus One Admission 2026",
+  "SUMMARY": "HSCAP Kerala Plus One Admission 2026: आवेदन तिथियाँ, पात्रता, और आवेदन प्रक्रिया।",
+  "KEY_POINTS": [
+    "HSCAP Kerala Plus One Admission 2026 के लिए आवेदन प्रक्रिया शुरू हो गई है।",
+    "महत्वपूर्ण तिथियाँ: आवेदन की अंतिम तिथि, प्रवेश परीक्षा की तिथि आदि।",
+    "पात्रता: 10वीं पास, न्यूनतम अंक आवश्यक।",
+    "आवेदन ऑनलाइन माध्यम से करना होगा।",
+    "आधिकारिक वेबसाइट hscap.kerala.gov.in है।"
+  ]
+}</t>
+  </si>
+  <si>
+    <t>BPSC Stenographer New Exam Date 2026 Out at bpsc.bihar.gov.in - Check Schedule</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/bpsc-stenographer-new-exam-date-2026-3046144</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 09:58:39 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Stenographer",
+    "JOB_TYPE": "Government Job",
+    "JOB_CATEGORY": "Group C",
+    "DEPARTMENT": "Bihar Public Service Commission",
+    "MINISTRY": "State Government",
+    "RECRUITING_AGENCY": "Bihar Public Service Commission (BPSC)",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [],
+    "JOB_LOCATION": "Bihar",
+    "GROUP": "C"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": null,
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": null,
+      "INTERVIEW": null,
+      "SKILL_TEST": null,
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": null
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "http://bpsc.bihar.gov.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>DSEO East Garo Hills Assistant Lecturer Recruitment 2026 - Apply Offline</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/dseo-east-garo-hills-assistant-lecturer-recruitment-2026-apply-offline-for-05-posts-3051304</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 09:56:10 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Assistant Lecturer",
+    "JOB_TYPE": "Teaching",
+    "JOB_CATEGORY": "Government",
+    "DEPARTMENT": "District School Education Office (DSEO), East Garo Hills",
+    "MINISTRY": "Education Department, Meghalaya",
+    "RECRUITING_AGENCY": "District School Education Office, East Garo Hills",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 5,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Assistant Lecturer",
+        "VACANCIES": 5,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "East Garo Hills, Meghalaya",
+    "GROUP": "B"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Post Graduate in relevant subject with B.Ed from a recognized university",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Offline",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "Visit official website or DSEO office to obtain application form",
+      "Fill form with required details",
+      "Attach self-attested copies of documents",
+      "Send by post or submit in person before deadline"
+    ],
+    "REQUIRED_DOCUMENTS": [
+      "Educational certificates",
+      "Age proof",
+      "Caste certificate (if applicable)",
+      "Experience certificate (if any)",
+      "Recent passport size photographs"
+    ],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [
+      "Written Exam",
+      "Interview"
+    ],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>VNSGU Result 2026 Out - Check B.Arch 2nd 4th 5th 6th Semester Result Online at vnsgu.ac.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/vnsgu-result-2026-out-check-barch-2nd-4th-5th-6th-semester-result-online-3051302</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 09:49:39 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "B.Arch 2nd, 4th, 5th, 6th Semester Exam",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Veer Narmad South Gujarat University (VNSGU)",
+    "EXAM_TYPE": "semester",
+    "CATEGORY": "university"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026",
+    "RESULT_TYPE": "semester",
+    "DIRECT_RESULT_LINK": "https://vnsgu.ac.in/results",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": ["Visit official website vnsgu.ac.in", "Click on 'Results' section", "Find B.Arch Semester Result link", "Enter enrollment number and date of birth", "Submit and view result"],
+    "REQUIRED_DETAILS": ["Enrollment number", "Date of birth"],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://vnsgu.ac.in/results",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "https://vnsgu.ac.in/results",
+    "OFFICIAL_WEBSITE": "https://vnsgu.ac.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>SAGES Teaching Recruitment 2026 - Apply Online for 57 Teacher, Computer Teacher and More Posts</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/sages-teaching-recruitment-2026-apply-online-for-57-teacher-computer-teacher-and-more-posts-3051301</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 08:55:29 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Teacher, Computer Teacher and More",
+    "JOB_TYPE": "Teaching",
+    "JOB_CATEGORY": "State Government",
+    "DEPARTMENT": "SAGES",
+    "MINISTRY": "School Education",
+    "RECRUITING_AGENCY": "SAGES",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 57,
+    "POST_WISE_VACANCIES": [],
+    "JOB_LOCATION": "Uttarakhand",
+    "GROUP": "B"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Varies by post - typically B.Ed, Bachelor's Degree",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 21,
+      "MAXIMUM_AGE": 42,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "10 years",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": null,
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 1000,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": "Online"
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [
+      "Written Exam",
+      "Interview"
+    ],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": null,
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": null
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "Hindi",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Rajasthan RPSC RAS Recruitment 2026 Notification Out - Apply Online for 607 Posts</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/rajasthan-rpsc-ras-recruitment-2026-apply-online-for-607-posts-3051300</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 08:53:54 GMT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "राजस्थान राज्य एवं अधीनस्थ सेवाएं (RAS)",
+    "JOB_TYPE": "संयुक्त राज्य सेवा",
+    "JOB_CATEGORY": "ग्रुप A और B",
+    "DEPARTMENT": "राजस्थान लोक सेवा आयोग (RPSC)",
+    "MINISTRY": "राजस्थान सरकार",
+    "RECRUITING_AGENCY": "राजस्थान लोक सेवा आयोग (RPSC)",
+    "ADVT_NO": "अधिसूचना में दिया जाएगा",
+    "TOTAL_VACANCIES": 607,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "राजस्थान राज्य सेवा (ग्रुप A)",
+        "VACANCIES": null,
+        "CATEGORY": "राजपत्रित",
+        "PAY_LEVEL": "पे लेवल 13-15",
+        "CLASSIFICATION": "ग्रुप A"
+      },
+      {
+        "POST_NAME": "राजस्थान अधीनस्थ सेवा (ग्रुप B)",
+        "VACANCIES": null,
+        "CATEGORY": "अराजपत्रित",
+        "PAY_LEVEL": "पे लेवल 12",
+        "CLASSIFICATION": "ग्रुप B"
+      }
+    ],
+    "JOB_LOCATION": "राजस्थान",
+    "GROUP": "A और B"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "पे लेवल 12-15",
+    "PAY_SCALE": "₹56,100 - ₹2,18,200",
+    "MINIMUM_SALARY": 56100,
+    "MAXIMUM_SALARY": 218200,
+    "ALLOWANCES": ["महंगाई भत्ता", "आवास भत्ता", "यात्रा भत्ता"],
+    "PERKS": ["चिकित्सा सुविधा", "पेंशन", "अन्य भत्ते"]
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "किसी मान्यता प्राप्त विश्वविद्यालय से स्नातक की डिग्री",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "कोई न्यूनतम प्रतिशत नहीं",
+    "EXPERIENCE_REQUIRED": "अनुभव आवश्यक नहीं",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 20,
+      "MAXIMUM_AGE": 40,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 वर्ष",
+        "OBC": "5 वर्ष",
+        "PWD": "10 वर्ष",
+        "EX_SERVICEMEN": "अधिसूचना के अनुसार",
+        "WOMEN": "अधिसूचना के अनुसार",
+        "OTHER": []
+      },
+      "AGE_AS_ON": "अधिसूचना में निर्धारित तिथि"
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": ["राजस्थान का मूल निवासी होना अनिवार्य नहीं"]
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "ऑनलाइन",
+    "APPLICATION_START_DATE": "अप्रैल 2026 (अनुमानित)",
+    "APPLICATION_LAST_DATE": "मई 2026 (अनुमानित)",
+    "LAST_DATE_FOR_FEE": "आवेदन की अंतिम तिथि के समान",
+    "FORM_CORRECTION_DATE": "अधिसूचना में दिया जाएगा",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 350,
+      "SC_ST_PWD_WOMEN": 150,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": "ऑनलाइन"
+    },
+    "HOW_TO_APPLY_STEPS": ["आधिकारिक वेबसाइट rpsc.rajasthan.gov.in पर जाएं", "ऑनलाइन आवेदन लिंक पर क्लिक करें", "पंजीकरण करें और आवेदन पत्र भरें", "आवश्यक दस्तावेज अपलोड करें", "आवेदन शुल्क का भुगतान करें", "फॉर्म सबमिट करें और प्रिंट निकालें"],
+    "REQUIRED_DOCUMENTS": ["शैक्षिक प्रमाणपत्र", "आयु प्रमाण", "आधार कार्ड", "जाति प्रमाण पत्र", "फोटो व हस्ताक्षर"],
+    "PHOTO_SPECIFICATIONS": "पासपोर्ट आकार, सफेद पृष्ठभूमि, जेपीजी, 50KB तक",
+    "SIGNATURE_SPECIFICATIONS": "काली स्याही, सफेद कागज, जेपीजी, 20KB तक"
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["प्रारंभिक परीक्षा", "मुख्य परीक्षा", "साक्षात्कार"],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 200,
+        "DURATION": "3 घंटे",
+        "SUBJECTS": ["सामान्य ज्ञान और सामान्य विज्ञान"],
+        "NEGATIVE_MARKING": "गलत उत्तर पर 1/3 अंक की कटौती"
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 800,
+        "DURATION": "4 पेपर, प्रत्येक 3 घंटे",
+        "SUBJECTS": ["सामान्य अध्ययन I", "सामान्य अध्ययन II", "सामान्य अध्ययन III", "हिंदी और अंग्रेजी"],
+        "NEGATIVE_MARKING": "कोई नकारात्मक अंकन नहीं"
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 100,
+        "DURATION": "लगभग 30 मिनट"
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": ["राजस्थान का इतिहास", "अर्थव्यवस्था", "विज्ञान और प्रौद्योगिकी", "राजनीति", "भूगोल"],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [{"2023": "सामान्य: 120/200"}],
+      "EXPECTED": "2026 के लिए अभी अनुमान नहीं"
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "2026 की पहली तिमाही (अनुमानित)",
+    "EXAM_DATE": "प्रारंभिक: मध्य 2026, मुख्य: अंत 2026",
+    "ADMIT_CARD_DATE": "परीक्षा से 2 सप्ताह पहले",
+    "RESULT_DATE": "प्रारंभिक: परीक्षा के 2 महीने बाद",
+    "INTERVIEW_DATE": "मुख्य परिणाम के बाद",
+    "FINAL_RESULT_DATE": "साक्षात्कार के बाद",
+    "JOINING_DATE": "अंतिम परिणाम के 6-12 महीने बाद"
+  },
+ </t>
+  </si>
+  <si>
+    <t>Barkatullah University Time Table 2026 OUT - Download BU Bhopal May-June Exam Date Sheet PDF at bubhopal.ac.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/barkatullah-university-time-table-2026-out-download-bu-bhopal-may-june-exam-date-sheet-pdf-3051299</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 08:51:15 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "SYLLABUS_IDENTIFICATION": {
+    "EXAM_NAME": "Barkatullah University Time Table",
+    "RECRUITMENT_NAME": "",
+    "CONDUCTING_BODY": "Barkatullah University, Bhopal",
+    "EXAM_TYPE": "University Examination",
+    "CATEGORY": "Academic",
+    "ACADEMIC_YEAR": "2025-2026",
+    "CLASS_OR_LEVEL": "Various (UG/PG)"
+  },
+  "SYLLABUS_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "2026",
+    "SYLLABUS_VERSION": "",
+    "OFFICIAL_SYLLABUS_LINK": "https://www.bubhopal.ac.in"
+  },
+  "EXAM_PATTERN_OVERVIEW": {
+    "TOTAL_MARKS": 0,
+    "TOTAL_QUESTIONS": 0,
+    "DURATION": "",
+    "MEDIUM": "",
+    "MODE": "Offline",
+    "NEGATIVE_MARKING": "",
+    "SECTIONS_COUNT": 0
+  },
+  "SUBJECTS": [],
+  "SECTIONAL_DETAILS": [],
+  "RECOMMENDED_RESOURCES": {
+    "BOOKS": [],
+    "ONLINE_RESOURCES": [],
+    "PREVIOUS_YEAR_PAPERS_LINK": ""
+  },
+  "PREPARATION_TIPS": {
+    "STRATEGY": "",
+    "IMPORTANT_TOPICS": [],
+    "TIME_MANAGEMENT_TIPS": ""
+  },
+  "IMPORTANT_DATES": {
+    "SYLLABUS_RELEASE_DATE": "",
+    "LAST_UPDATED": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "SYLLABUS_PDF": "",
+    "OFFICIAL_WEBSITE": "https://www.bubhopal.ac.in"
+  },
+  "ADDITIONAL_INFO": {
+    "FREQUENTLY_ASKED_QUESTIONS": [],
+    "LATEST_CHANGES": "",
+    "CONTACT_HELPLINE": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>MCU Bhopal Date Sheet 2026 OUT -Download May-June Exam Time Table PDF at mcu.ac.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/mcu-bhopal-date-sheet-2026-out-download-may-june-exam-time-table-pdf-3051298</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 08:44:03 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "MAIN_TOPIC": "MCU Bhopal Date Sheet 2026",
+  "SUMMARY": "MCU (Makhanlal Chaturvedi National University of Journalism and Communication) Bhopal has released the date sheet for May-June 2026 exams. The time table is available for download in PDF format from the official website mcu.ac.in. The article provides details on how to download the exam schedule and important dates.",
+  "KEY_POINTS": [
+    "MCU Bhopal date sheet for May-June 2026 exams is released.",
+    "The exam time table is available in PDF format on the official website mcu.ac.in.",
+    "Students can download the date sheet directly from the article link.",
+    "The article includes step-by-step instructions for downloading the PDF."
+  ]
+}</t>
+  </si>
+  <si>
+    <t>Punjabi University Patiala Result 2026 Out - Check UG PG Sem 1st 3rd 5th Result Online at results.pupexamination.ac.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/punjabi-university-patiala-result-2026-out-check-ug-pg-sem-1st-3rd-5th-result-online-3051297</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 08:36:22 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "UG PG Semester 1st, 3rd, 5th Examination",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Punjabi University Patiala",
+    "EXAM_TYPE": "Semester Examination",
+    "CATEGORY": "University"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026",
+    "RESULT_TYPE": "Semester Result",
+    "DIRECT_RESULT_LINK": "https://results.pupexamination.ac.in",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website at results.pupexamination.ac.in",
+      "Click on the link for the respective semester result",
+      "Enter your roll number and other required details",
+      "Submit and view your result",
+      "Download and take a printout for future reference"
+    ],
+    "REQUIRED_DETAILS": ["Roll Number", "Date of Birth (if required)"],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://results.pupexamination.ac.in",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "https://results.pupexamination.ac.in",
+    "OFFICIAL_WEBSITE": "https://www.punjabiuniversity.ac.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>Hemchand Yadav Vishwavidyalaya Result 2026 Out - Direct Link to Download BBA 5th Semester Revaluation Result at durg.ucanapply.com</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/hemchand-yadav-vishwavidyalaya-result-2026-out-direct-link-to-download-bba-5th-semester-revaluation-result-3051296</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 08:29:56 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "BBA 5th Semester Revaluation Result 2026",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Hemchand Yadav Vishwavidyalaya",
+    "EXAM_TYPE": "University Semester Exam",
+    "CATEGORY": "Result"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "",
+    "RESULT_TYPE": "Revaluation Result",
+    "DIRECT_RESULT_LINK": "https://durg.ucanapply.com",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website at https://durg.ucanapply.com",
+      "Click on the result link for BBA 5th Semester Revaluation Result 2026",
+      "Enter your roll number and other required details",
+      "Submit and view your result"
+    ],
+    "REQUIRED_DETAILS": [
+      "Roll Number",
+      "Date of Birth or other credentials"
+    ],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://durg.ucanapply.com",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "https://durg.ucanapply.com",
+    "OFFICIAL_WEBSITE": "https://durg.ucanapply.com",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>DCPU Siwan Provisional Merit List 2026 OUT for Educator, Housekeeper and More (Direct Link) - Download Scorecard @siwan.nic.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/dcpu-siwan-provisional-merit-list-2026-3051295</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 08:29:38 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Educator, Housekeeper and Various Posts",
+    "JOB_TYPE": "Government",
+    "JOB_CATEGORY": "Other",
+    "DEPARTMENT": "District Child Protection Unit (DCPU)",
+    "MINISTRY": "Women and Child Development",
+    "RECRUITING_AGENCY": "District Child Protection Unit, Siwan",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Educator",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      },
+      {
+        "POST_NAME": "Housekeeper",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "Siwan",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "http://siwan.nic.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Nabarangpur Forest Division Veterinary Officer Recruitment 2026 - Apply Online</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/nabarangpur-forest-division-veterinary-officer-recruitment-2026-apply-online-3051294</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 08:28:10 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Veterinary Officer",
+    "JOB_TYPE": "Government Job",
+    "JOB_CATEGORY": "Technical",
+    "DEPARTMENT": "Forest Division",
+    "MINISTRY": "Ministry of Environment, Forest and Climate Change",
+    "RECRUITING_AGENCY": "Nabarangpur Forest Division",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [],
+    "JOB_LOCATION": "Nabarangpur, Odisha",
+    "GROUP": "Group B"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Bachelor's degree in Veterinary Science",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 21,
+      "MAXIMUM_AGE": 32,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "10 years",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": "01-01-2026"
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": ["Registration with Odisha State Veterinary Council"]
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 500,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": "Online"
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Written Exam", "Interview"],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 100,
+        "DURATION": "2 hours",
+        "SUBJECTS": ["Veterinary Science", "General Knowledge", "English"],
+        "NEGATIVE_MARKING": "Yes, 0.25 marks per wrong answer"
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 20,
+        "DURATION": "15 minutes"
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "2 years",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "As per GoI norms",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": ["Candidates must have valid registration with Odisha State Veterinary Council."],
+    "OFFICIAL_LANGUAGE": "English and Odia",
+    "DOMICILE_REQUIREMENTS": "Odisha domicile may be required"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Optical Illusion: Only Eagle Eyes Can Spot the Number 0857 Among 0357 in 7 Seconds</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/optical-illusion-only-eagle-eyes-can-spot-the-number-0857-among-0357-in-7-seconds-10244</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 08:23:42 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "MAIN_TOPIC": "Optical Illusion: Find the Hidden Number",
+  "SUMMARY": "An optical illusion challenges readers to spot the number 0857 hidden among 0357 within 7 seconds, testing visual acuity and attention to detail.",
+  "KEY_POINTS": [
+    "Goal: Find the number 0857 among a grid or sequence of 0357.",
+    "Time limit: 7 seconds.",
+    "Skill tested: Eagle eyes or sharp visual perception.",
+    "Common challenge in optical illusion puzzles."
+  ]
+}</t>
+  </si>
+  <si>
+    <t>Pondicherry University Result 2026 Out - Check DEE, DME, DMR 1st 2nd 3rd Semester Result at pondiuni.edu.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/pondicherry-university-result-2026-out-check-dee-dme-dmr-1st-2nd-3rd-semester-result-3051292</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 08:23:18 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "DEE, DME, DMR 1st 2nd 3rd Semester Examination",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Pondicherry University",
+    "EXAM_TYPE": "Semester",
+    "CATEGORY": "University"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026",
+    "RESULT_TYPE": "Semester Result",
+    "DIRECT_RESULT_LINK": "https://www.pondiuni.edu.in/result",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website pondiuni.edu.in",
+      "Click on the 'Result' section",
+      "Select your course (DEE/DME/DMR) and semester",
+      "Enter your roll number and other required details",
+      "Submit to view your result",
+      "Download and take a printout for future reference"
+    ],
+    "REQUIRED_DETAILS": ["Roll Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Check result via SMS (if available)"
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": null,
+    "TOTAL_CANDIDATES_QUALIFIED": null,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": null,
+        "OBC": null,
+        "SC": null,
+        "ST": null,
+        "EWS": null,
+        "PWD": null,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://www.pondiuni.edu.in/result",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "https://www.freejobalert.com/articles/pondicherry-university-result-2026-out-check-dee-dme-dmr-1st-2nd-3rd-semester-result-3051292",
+    "OFFICIAL_WEBSITE": "https://www.pondiuni.edu.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>EMRS Pakur Guest Teacher Recruitment 2026 - Apply Offline for 20 Posts</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/emrs-pakur-guest-teacher-recruitment-2026-apply-offline-for-20-posts-3051291</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 08:19:17 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "EMRS Pakur Guest Teacher Recruitment 2026",
+    "JOB_TYPE": "सरकारी नौकरी",
+    "JOB_CATEGORY": "शिक्षण",
+    "DEPARTMENT": "EMRS Pakur",
+    "MINISTRY": "Ministry of Tribal Affairs",
+    "RECRUITING_AGENCY": "EMRS Pakur",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 20,
+    "POST_WISE_VACANCIES": [],
+    "JOB_LOCATION": "Pakur, Jharkhand",
+    "GROUP": "B (गैर-राजपत्रित)"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "गेस्ट टीचर के लिए नियत मानदेय",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "संबंधित विषय में स्नातकोत्तर उत्तीर्ण",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "ऑफलाइन",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.freejobalert.com/articles/emrs-pakur-guest-teacher-recruitment-2026-apply-offline-for-20-posts-3051291",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Collectorate Rayagada Recruitment 2026 - Apply Offline for Launch Driver &amp; Khalasi Posts</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/collectorate-rayagada-recruitment-2026-apply-offline-for-launch-driver-khalasi-posts-3051287</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 08:10:59 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Launch Driver &amp; Khalasi",
+    "JOB_TYPE": "Government",
+    "JOB_CATEGORY": "Group C",
+    "DEPARTMENT": "Collectorate Rayagada",
+    "MINISTRY": null,
+    "RECRUITING_AGENCY": "Collectorate Rayagada",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Launch Driver",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      },
+      {
+        "POST_NAME": "Khalasi",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "Rayagada, Odisha",
+    "GROUP": "C"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Offline",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Pudukkottai District Recruitment 2026 - Apply Offline for Project Manager, Counsellor and More Posts</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/pudukkottai-district-recruitment-2026-apply-offline-for-project-manager-counsellor-and-more-posts-3051285</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 08:09:02 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Project Manager, Counsellor and More Posts",
+    "JOB_TYPE": "Government",
+    "JOB_CATEGORY": "Contractual",
+    "DEPARTMENT": "Pudukkottai District Administration",
+    "MINISTRY": "",
+    "RECRUITING_AGENCY": "Pudukkottai District Administration",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Project Manager",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      },
+      {
+        "POST_NAME": "Counsellor",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "Pudukkottai, Tamil Nadu",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Offline",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": null,
+      "INTERVIEW": null,
+      "SKILL_TEST": null,
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": false
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>IIT JAM 2026 Round 1 Seat Allotment List Out - Check Admission Status at jam.iitm.ac.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/iit-jam-2026-round-1-seat-allotment-list-check-admission-status-3050751</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 08:08:16 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "IIT JAM 2026",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "M.Sc. and other programs",
+    "CONDUCTING_BODY": "Indian Institute of Technology Madras",
+    "EXAM_TYPE": "Admission",
+    "CATEGORY": "Postgraduate"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026-04-15",
+    "RESULT_TYPE": "Seat Allotment List",
+    "DIRECT_RESULT_LINK": "https://jam.iitm.ac.in/seatallotment2026",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website jam.iitm.ac.in",
+      "Click on 'Round 1 Seat Allotment' link",
+      "Enter your JAM 2026 registration number and date of birth",
+      "View and download your seat allotment letter"
+    ],
+    "REQUIRED_DETAILS": ["JAM 2026 Registration Number", "Date of Birth"],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "https://jam.iitm.ac.in/meritlist2026.pdf",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "2026-05-01 to 2026-05-10",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "2026-06-15",
+    "JOINING_DATE": "2026-07-01",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026-04-15",
+    "LAST_DATE_TO_CHECK": "2026-04-30",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://jam.iitm.ac.in/notifications",
+    "DIRECT_RESULT": "https://jam.iitm.ac.in/seatallotment2026",
+    "OFFICIAL_WEBSITE": "https://jam.iitm.ac.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "Higher marks in JAM 2026; if still tie, older age",
+    "REVALUATION_PROCESS": "Not applicable for seat allotment",
+    "CONTACT_DETAILS": "Email: jam2026@iitm.ac.in",
+    "IMP_INSTRUCTIONS": ["Candidates must accept the allotted seat online by the deadline", "Upload required documents for verification within the specified date"]
+  }
+}</t>
+  </si>
+  <si>
+    <t>MP Police Head Constable Physical Test Admit Card 2026 (Out) - Download Here</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/mp-police-head-constable-physical-test-admit-card-2026-3051282</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 08:05:03 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "MP Police Head Constable Physical Test",
+    "RECRUITMENT_NAME": "MP Police Head Constable Recruitment",
+    "POST_NAME": "Head Constable",
+    "CONDUCTING_BODY": "Madhya Pradesh Police",
+    "EXAM_TYPE": "Physical Test",
+    "CATEGORY": "Police Recruitment"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "2026",
+    "DIRECT_DOWNLOAD_LINK": "https://www.freejobalert.com/articles/mp-police-head-constable-physical-test-admit-card-2026-3051282",
+    "STATUS_CHECK_LINK": ""
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "",
+    "EXAM_TIME": "",
+    "EXAM_SHIFT": "",
+    "EXAM_DURATION": "",
+    "EXAM_MODE": "Offline",
+    "EXAM_CENTER_CITY": "",
+    "EXAM_CENTER_NAME": "",
+    "FULL_SCHEDULE": []
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [
+      "Visit official website of MP Police",
+      "Click on the admit card link for Head Constable Physical Test",
+      "Enter required details (Registration Number, Date of Birth)",
+      "Download and print the admit card"
+    ],
+    "REQUIRED_DETAILS": [
+      "Registration Number",
+      "Date of Birth"
+    ],
+    "ALTERNATE_METHOD": "Direct download from freejobalert.com"
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": [],
+    "EXAM_DAY_GUIDELINES": [],
+    "DOCUMENTS_TO_CARRY": [],
+    "PROHIBITED_ITEMS": [],
+    "COVID_SPECIFIC": ""
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "",
+    "EXAM_DATE_LIST": [],
+    "RESULT_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_DOWNLOAD": "https://www.freejobalert.com/articles/mp-police-head-constable-physical-test-admit-card-2026-3051282",
+    "OFFICIAL_WEBSITE": "",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "Contact MP Police helpline for any discrepancies in admit card",
+    "REPRINT_OPTION": "Available on portal if initial download fails",
+    "CONTACT_DETAILS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>HARTRON Advanced Skill Centre Admission 2026-27: Apply Now for AI, Cyber Security, Digital Marketing &amp; IT Courses</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/hartron-advanced-skill-centre-courses-admission-2026-3051281</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 07:57:23 GMT</t>
+  </si>
+  <si>
+    <t>स्किल डेवलपमेंट &amp; स्वरोजगार</t>
+  </si>
+  <si>
+    <t>{
+  "SKILL_IDENTIFICATION": {
+    "PROGRAM_NAME": "HARTRON Advanced Skill Centre Admission 2026-27",
+    "PROVIDER_NAME": "Haryana State Electronics Development Corporation Ltd. (HARTRON)",
+    "PROVIDER_TYPE": "Government",
+    "PROGRAM_TYPE": "Skill Training Course",
+    "CATEGORY": "Skill Development",
+    "SKILL_CATEGORY": "IT and Digital Skills",
+    "LEVEL": "Advanced",
+    "MODE": "Offline",
+    "LANGUAGE": "English"
+  },
+  "PROGRAM_STATUS": {
+    "OPEN_FOR_APPLICATION": true,
+    "APPLICATION_START_DATE": "01-01-2026",
+    "APPLICATION_LAST_DATE": "15-03-2026",
+    "LAST_DATE_EXTENSION": ""
+  },
+  "COURSE_OR_SCHEME_DETAILS": {
+    "COURSE_NAME": "AI, Cyber Security, Digital Marketing &amp; IT Courses",
+    "DURATION": "",
+    "DURATION_UNIT": "",
+    "TOTAL_HOURS": 0,
+    "FEE": {
+      "TOTAL_FEE": 0,
+      "FEE_TYPE": "",
+      "IS_FREE": false,
+      "DISCOUNT_DETAILS": "",
+      "FEE_PAYMENT_MODE": ""
+    },
+    "MEDIUM_OF_INSTRUCTION": "English",
+    "BATCH_SIZE": "",
+    "CERTIFICATION": ""
+  },
+  "ELIGIBILITY": {
+    "MINIMUM_EDUCATION": "12th Pass",
+    "EDUCATION_DETAILS": ["12th Pass", "Graduation in relevant field preferred"],
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 18,
+      "MAXIMUM_AGE": 35
+    },
+    "GENDER": "All",
+    "RESERVATION_CATEGORY": "As per government norms",
+    "DOMICILE": "Haryana",
+    "EXPERIENCE_REQUIRED": "Not required",
+    "OTHER_REQUIREMENTS": ["Basic computer knowledge"]
+  },
+  "BENEFITS_AND_OUTCOMES": {
+    "CERTIFICATE_PROVIDED": true,
+    "CERTIFICATE_DETAILS": "HARTRON certificate upon completion",
+    "JOB_PLACEMENT_ASSISTANCE": true,
+    "PLACEMENT_DETAILS": "Placement assistance provided",
+    "AVERAGE_STIPEND": "",
+    "EXPECTED_SALARY": "",
+    "LOAN_FACILITY": false,
+    "LOAN_DETAILS": "",
+    "SUBSIDY": false,
+    "SUBSIDY_DETAILS": "",
+    "TOOLKIT_PROVIDED": false,
+    "TOOLKIT_DETAILS": "",
+    "OTHER_BENEFITS": []
+  },
+  "SELF_EMPLOYMENT_OPPORTUNITIES": {
+    "BUSINESS_IDEA": "",
+    "SECTOR": "IT Services",
+    "INITIAL_INVESTMENT": {
+      "MINIMUM": 0,
+      "MAXIMUM": 0
+    },
+    "PROFIT_MARGIN": "",
+    "GOVERNMENT_SCHEMES_LINKED": [],
+    "TRAINING_AVAILABLE": true,
+    "MARKET_DEMAND": "High"
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "ONLINE_LINK": "https://hartron.org.in",
+    "OFFLINE_VENUE": "",
+    "STEPS_TO_APPLY": ["Visit official website", "Fill online application form", "Upload required documents", "Submit application"],
+    "REQUIRED_DOCUMENTS": ["12th mark sheet", "Graduation certificate (if applicable)", "ID proof", "Domicile certificate"],
+    "APPLICATION_FEE": 0
+  },
+  "SELECTION_PROCESS": {
+    "SELECTION_METHOD": "Merit Based",
+    "INTERVIEW": false,
+    "MERIT_BASED": true,
+    "OTHER_DETAILS": "Selection based on academic marks and first-come-first-serve basis"
+  },
+  "SUCCESS_STORIES": [],
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "15-12-2025",
+    "APPLICATION_START_DATE": "01-01-2026",
+    "APPLICATION_LAST_DATE": "15-03-2026",
+    "TRAINING_START_DATE": "01-04-2026",
+    "CERTIFICATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://www.freejobalert.com/articles/hartron-advanced-skill-centre-courses-admission-2026-3051281",
+    "APPLY_LINK": "https://hartron.org.in",
+    "OFFICIAL_WEBSITE": "https://hartron.org.in",
+    "HELPLINE": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TERMS_AND_CONDITIONS": "",
+    "RENEWAL_OR_FURTHER_STEPS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>Gurugram University Clerk Recruitment 2026 - Walkin</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/gurugram-university-clerk-recruitment-2026-walkin-for-05-posts-3051280</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 07:54:29 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Clerk",
+    "JOB_TYPE": "Walkin Interview",
+    "JOB_CATEGORY": "Government",
+    "DEPARTMENT": "Gurugram University",
+    "MINISTRY": "",
+    "RECRUITING_AGENCY": "Gurugram University",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 5,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Clerk",
+        "VACANCIES": 5,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": "Group C"
+      }
+    ],
+    "JOB_LOCATION": "Gurugram",
+    "GROUP": "C"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Bachelor's Degree from a recognized university",
+    "EDUCATION_DETAILS": [
+      "Bachelor's Degree"
+    ],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Walkin",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "https://www.freejobalert.com/articles/gurugram-university-clerk-recruitment-2026-walkin-for-05-posts-3051280",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Sardar Patel University Result 2026 Out - Direct Link to Download SPU 2nd 3rd 4th 6th Semester Results at spuvvn.edu</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/sardar-patel-university-result-2026-out-direct-link-to-download-spu-2nd-3rd-4th-6th-semester-results-3051277</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 07:49:20 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "SPU 2nd, 3rd, 4th, 6th Semester Exam",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Sardar Patel University",
+    "EXAM_TYPE": "University Semester Exam",
+    "CATEGORY": "University"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026",
+    "RESULT_TYPE": "Semester Result",
+    "DIRECT_RESULT_LINK": "https://spuvvn.edu/result",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website spuvvn.edu",
+      "Click on 'Result' link",
+      "Select your semester and course",
+      "Enter your roll number and date of birth",
+      "View and download your result"
+    ],
+    "REQUIRED_DETAILS": ["Roll Number", "Date of Birth"],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://spuvvn.edu/result",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://spuvvn.edu/notification",
+    "DIRECT_RESULT": "https://spuvvn.edu/result",
+    "OFFICIAL_WEBSITE": "https://spuvvn.edu",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>BSNL JTO Recruitment 2026 Notification Out - Apply Online for 100 Junior Telecom Officer Posts</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/bsnl-jto-recruitment-2026-apply-online-for-100-junior-telecom-officer-posts-3051276</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 07:40:40 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Junior Telecom Officer",
+    "JOB_TYPE": "Regular",
+    "JOB_CATEGORY": "Technical",
+    "DEPARTMENT": "Telecom",
+    "MINISTRY": "Ministry of Communications",
+    "RECRUITING_AGENCY": "BSNL",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 100,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Junior Telecom Officer",
+        "VACANCIES": 100,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": "Group B (Gazetted)"
+      }
+    ],
+    "JOB_LOCATION": "All India",
+    "GROUP": "B"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "Rs. 24,900 - 50,500",
+    "MINIMUM_SALARY": 24900,
+    "MAXIMUM_SALARY": 50500,
+    "ALLOWANCES": ["DA", "HRA", "Medical", "Other allowances as per rules"],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "B.E/B.Tech in Electrical/Electronics/Telecommunication/Computer Science or equivalent",
+    "EDUCATION_DETAILS": [
+      {
+        "DEGREE": "B.E/B.Tech",
+        "BRANCH": "Electrical/Electronics/Telecommunication/Computer Science",
+        "MINIMUM_PERCENTAGE": "60%"
+      }
+    ],
+    "MINIMUM_PERCENTAGE": "60%",
+    "EXPERIENCE_REQUIRED": "Not required",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 18,
+      "MAXIMUM_AGE": 30,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "10 years",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": "01-01-2026"
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "To be announced",
+    "APPLICATION_LAST_DATE": "To be announced",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 1000,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": "Online"
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "Visit official website",
+      "Click on recruitment tab",
+      "Fill application form",
+      "Upload documents",
+      "Pay fee",
+      "Submit"
+    ],
+    "REQUIRED_DOCUMENTS": [
+      "Scanned photograph",
+      "Scanned signature",
+      "Educational certificates",
+      "Category certificate",
+      "ID proof"
+    ],
+    "PHOTO_SPECIFICATIONS": "Passport size, less than 50KB",
+    "SIGNATURE_SPECIFICATIONS": "Less than 20KB"
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Written Exam", "Interview", "Document Verification"],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 100,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "To be announced",
+    "EXAM_DATE": "To be announced",
+    "ADMIT_CARD_DATE": "To be announced",
+    "RESULT_DATE": "To be announced",
+    "INTERVIEW_DATE": "To be announced",
+    "FINAL_RESULT_DATE": "To be announced",
+    "JOINING_DATE": "To be announced"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "https://www.bsnl.co.in",
+    "APPLY_ONLINE_LINK": "https://www.bsnl.co.in",
+    "OFFICIAL_WEBSITE": "https://www.bsnl.co.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "2 years",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "As per BSNL rules",
+    "TRANSFER_POLICY": "All India transferable",
+    "RESERVATION_DETAILS": "As per government norms",
+    "CONTACT_HELPLINE": "1800-xxx-xxxx",
+    "IMP_INSTRUCTIONS": ["Eligibility criteria must be checked before applying", "Keep scanned documents ready"],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>IIM Ahmedabad Assistant Manager Recruitment 2026 - Apply Online</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/iim-ahmedabad-assistant-manager-recruitment-2026-apply-online-3051275</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 07:33:11 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Assistant Manager",
+    "JOB_TYPE": "Regular",
+    "JOB_CATEGORY": "Group A",
+    "DEPARTMENT": "Administration",
+    "MINISTRY": "Ministry of Education",
+    "RECRUITING_AGENCY": "IIM Ahmedabad",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [],
+    "JOB_LOCATION": "Ahmedabad, Gujarat",
+    "GROUP": "A"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "As per IIM norms",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Master's degree or equivalent",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "2-3 years",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 21,
+      "MAXIMUM_AGE": 35,
+      "AGE_RELAXATION": {
+        "SC_ST": "As per Govt rules",
+        "OBC": "As per Govt rules",
+        "PWD": "As per Govt rules",
+        "EX_SERVICEMEN": "As per Govt rules",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": null,
+      "INTERVIEW": {
+        "TOTAL_MARKS": 100,
+        "DURATION": ""
+      },
+      "SKILL_TEST": null,
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.iima.ac.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "English",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>PU CET UG Result 2026 Out - Check Panjab University Entrance Test Result Online at cetug.puchd.ac.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/pu-cet-ug-result-2026-out-check-panjab-university-entrance-test-result-online-3051273</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 07:31:56 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "PU CET UG 2026",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Panjab University",
+    "EXAM_TYPE": "University Entrance Exam",
+    "CATEGORY": "Undergraduate"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026",
+    "RESULT_TYPE": "Online",
+    "DIRECT_RESULT_LINK": "https://cetug.puchd.ac.in",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit official website cetug.puchd.ac.in",
+      "Click on result link",
+      "Enter roll number and other details",
+      "Submit and download result"
+    ],
+    "REQUIRED_DETAILS": ["Roll Number", "Date of Birth"],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://cetug.puchd.ac.in",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "https://cetug.puchd.ac.in",
+    "OFFICIAL_WEBSITE": "https://cetug.puchd.ac.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>IIT Kanpur Content Manager Recruitment 2026 - Apply Offline</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/iit-kanpur-content-manager-recruitment-2026-apply-offline-3051271</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 07:28:07 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Content Manager",
+    "JOB_TYPE": "प्रोजेक्ट",
+    "JOB_CATEGORY": "अन्य",
+    "DEPARTMENT": "Industrial and Management Engineering",
+    "MINISTRY": "",
+    "RECRUITING_AGENCY": "Indian Institute of Technology Kanpur",
+    "ADVT_NO": "IME/2025-2026/019",
+    "TOTAL_VACANCIES": 1,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Content Manager",
+        "VACANCIES": 1,
+        "CATEGORY": "UR",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": "अन्य"
+      }
+    ],
+    "JOB_LOCATION": "Kanpur, Uttar Pradesh",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "₹56,000 - ₹1,77,500 प्रति माह",
+    "MINIMUM_SALARY": 56000,
+    "MAXIMUM_SALARY": 177500,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "मास्टर डिग्री (किसी भी विषय में) या समकक्ष",
+    "EDUCATION_DETAILS": [
+      {
+        "DEGREE": "मास्टर डिग्री",
+        "SPECIALIZATION": "किसी भी विषय",
+        "MINIMUM_PERCENTAGE": ""
+      }
+    ],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "3 वर्ष प्रासंगिक अनुभव",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 45,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 वर्ष",
+        "OBC": "3 वर्ष",
+        "PWD": "10 वर्ष",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": "2026-01-30"
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Offline",
+    "APPLICATION_START_DATE": "2026-01-01",
+    "APPLICATION_LAST_DATE": "2026-01-30",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": "कोई शुल्क नहीं"
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "आवेदन पत्र IIT Kanpur की वेबसाइट से डाउनलोड करें।",
+      "पूर्ण भरे हुए आवेदन को आवश्यक दस्तावेजों के साथ संलग्न करें।",
+      "आवेदन को निर्धारित पते पर डाक या कूरियर द्वारा भेजें।"
+    ],
+    "REQUIRED_DOCUMENTS": [
+      "शैक्षणिक प्रमाणपत्र",
+      "अनुभव प्रमाणपत्र",
+      "आयु प्रमाण",
+      "जाति प्रमाणपत्र (यदि लागू हो)",
+      "पासपोर्ट साइज फोटो"
+    ],
+    "PHOTO_SPECIFICATIONS": "पासपोर्ट साइज, सफेद पृष्ठभूमि",
+    "SIGNATURE_SPECIFICATIONS": "सफेद कागज पर नीली स्याही से हस्ताक्षर"
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [
+      "स्क्रीनिंग",
+      "इंटरव्यू"
+    ],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": null,
+      "INTERVIEW": {
+        "TOTAL_MARKS": 100,
+        "DURATION": "निर्धारित नहीं"
+      },
+      "SKILL_TEST": null,
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "2026-01-01",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "निर्धारित किया जाएगा",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "https://www.iitk.ac.in/ime/advt_content_manager_2026.pdf",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.iitk.ac.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "आरक्षण सरकारी नियमानुसार",
+    "CONTACT_HELPLINE": "0512-259-XXXX",
+    "IMP_INSTRUCTIONS": [
+      "आवेदन पत्र में सभी जानकारी सही भरें।",
+      "अंतिम तिथि के बाद प्राप्त आवेदन स्वीकार नहीं होंगे।"
+    ],
+    "OFFICIAL_LANGUAGE": "अंग्रेजी और हिंदी",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>IIT Dharwad Nursing Superintendent Recruitment 2026 - Apply Online</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/iit-dharwad-nursing-superintendent-recruitment-2026-apply-online-3051268</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 07:26:46 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Nursing Superintendent",
+    "JOB_TYPE": "सरकारी नौकरी",
+    "JOB_CATEGORY": "स्वास्थ्य/चिकित्सा",
+    "DEPARTMENT": "IIT Dharwad",
+    "MINISTRY": "",
+    "RECRUITING_AGENCY": "IIT Dharwad",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [],
+    "JOB_LOCATION": "Dharwad, Karnataka",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {},
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {},
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {},
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {},
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {}
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.iitdh.ac.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>OAVs Bhadrak Support Staff Recruitment 2026 - Apply Offline for Warden, Head Cook and More Posts</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/oavs-bhadrak-support-staff-recruitment-2026-apply-offline-for-warden-head-cook-and-more-posts-3051267</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 07:25:35 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Support Staff",
+    "JOB_TYPE": "Sarkari Naukri",
+    "JOB_CATEGORY": "Group C",
+    "DEPARTMENT": "Odisha Adarsh Vidyalaya, Bhadrak",
+    "MINISTRY": "School and Mass Education Department, Odisha",
+    "RECRUITING_AGENCY": "Odisha Adarsh Vidyalaya, Bhadrak",
+    "ADVT_NO": "Not Mentioned",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Warden",
+        "VACANCIES": 0,
+        "CATEGORY": "Not Mentioned",
+        "PAY_LEVEL": "Not Mentioned",
+        "CLASSIFICATION": "Non-Technical"
+      },
+      {
+        "POST_NAME": "Head Cook",
+        "VACANCIES": 0,
+        "CATEGORY": "Not Mentioned",
+        "PAY_LEVEL": "Not Mentioned",
+        "CLASSIFICATION": "Non-Technical"
+      }
+    ],
+    "JOB_LOCATION": "Bhadrak, Odisha",
+    "GROUP": "C"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "Not Mentioned",
+    "PAY_SCALE": "Not Mentioned",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Not Mentioned",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "Not Mentioned",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Offline",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": false
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>93 Percentile in JEE Mains 2026 Means How Many Marks? Check Expected Rank, Marks &amp; College Chances 2026</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/93-percentile-in-jee-mains-means-how-many-marks-10243</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 07:23:57 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "MAIN_TOPIC": "93 Percentile in JEE Mains 2026 - Expected Marks, Rank and College Chances",
+  "SUMMARY": "This article explains that a 93 percentile in JEE Mains 2026 typically corresponds to marks around 90-100 out of 300, with an expected rank between 80,000 and 90,000. It outlines college possibilities, including lower NITs, IIITs, and GFTIs, and emphasizes that top NITs may not be reachable but decent branches in some NITs are possible.",
+  "KEY_POINTS": [
+    "93 percentile in JEE Mains 2026 translates to approximately 90-100 marks out of 300.",
+    "Expected rank for 93 percentile is between 80,000 and 90,000.",
+    "Admission chances include lower NITs, IIITs, and GFTIs; top NITs and IIITs are unlikely.",
+    "Some NITs like NIT Sikkim, NIT Mizoram, etc. may offer non-core branches at this percentile.",
+    "State-level colleges might be a better option compared to lower-ranked NITs at this percentile."
+  ]
+}</t>
+  </si>
+  <si>
+    <t>THSTI Recruitment 2026 - Apply Online for Technical Officer, System Administrator Posts</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/thsti-recruitment-2026-apply-online-for-02-technical-officer-system-administrator-posts-3051263</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 07:21:33 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Technical Officer, System Administrator",
+    "JOB_TYPE": "Government Job",
+    "JOB_CATEGORY": "Technical",
+    "DEPARTMENT": "Translational Health Science and Technology Institute (THSTI)",
+    "MINISTRY": "Ministry of Health and Family Welfare?",
+    "RECRUITING_AGENCY": "Translational Health Science and Technology Institute (THSTI)",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 2,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Technical Officer",
+        "VACANCIES": 1,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      },
+      {
+        "POST_NAME": "System Administrator",
+        "VACANCIES": 1,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "Faridabad, Haryana",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "Level 10 (Rs. 56,100 - 1,77,500) for Technical Officer?",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Technical Officer: Master's degree in Life Sciences with 3 years experience; System Administrator: B.E./B.Tech in Computer Science/IT with 5 years experience",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "Yes",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 40,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": null,
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": null,
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.thsti.res.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>IGNOU Hall Ticket June 2026 Out - Download IGNOU TEE June 2026 Admit Card at ignou.ac.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/ignou-hall-ticket-june-2026-out-download-ignou-tee-june-2026-admit-card-3049737</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 07:16:08 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "IGNOU TEE June 2026",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Indira Gandhi National Open University (IGNOU)",
+    "EXAM_TYPE": "University Exam",
+    "CATEGORY": "Term End Examination"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "",
+    "DIRECT_DOWNLOAD_LINK": "https://exam.ignou.ac.in/",
+    "STATUS_CHECK_LINK": ""
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "",
+    "EXAM_TIME": "",
+    "EXAM_SHIFT": "",
+    "EXAM_DURATION": "",
+    "EXAM_MODE": "Offline",
+    "EXAM_CENTER_CITY": "",
+    "EXAM_CENTER_NAME": "",
+    "FULL_SCHEDULE": []
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [
+      "Go to official website ignou.ac.in",
+      "Click on 'Student Zone' then 'Hall Ticket'",
+      "Enter your Enrollment Number and Programme Code",
+      "Click Submit and download admit card"
+    ],
+    "REQUIRED_DETAILS": ["Enrollment Number", "Programme Code"],
+    "ALTERNATE_METHOD": ""
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": [],
+    "EXAM_DAY_GUIDELINES": [],
+    "DOCUMENTS_TO_CARRY": [],
+    "PROHIBITED_ITEMS": [],
+    "COVID_SPECIFIC": ""
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "",
+    "EXAM_DATE_LIST": [],
+    "RESULT_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_DOWNLOAD": "https://exam.ignou.ac.in/",
+    "OFFICIAL_WEBSITE": "https://ignou.ac.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "",
+    "REPRINT_OPTION": "",
+    "CONTACT_DETAILS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>IIM Amritsar Faculty Recruitment 2026 - Apply Online for Professor, Associate Professor and More Post</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/iim-amritsar-faculty-recruitment-2026-apply-online-for-professor-associate-professor-and-more-post-3051261</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 07:10:47 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Professor, Associate Professor, Assistant Professor, and Other Faculty Positions",
+    "JOB_TYPE": "Faculty",
+    "JOB_CATEGORY": "Teaching",
+    "DEPARTMENT": "Various",
+    "MINISTRY": "Ministry of Education",
+    "RECRUITING_AGENCY": "IIM Amritsar",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [],
+    "JOB_LOCATION": "Amritsar, Punjab",
+    "GROUP": "A"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "As per UGC norms",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Ph.D. in relevant discipline with first class at preceding degree",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 1000,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": "Online"
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Shortlisting", "Interview"],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.iiamritsar.ac.in/",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>IIT (ISM) Dhanbad Junior Research Fellow Recruitment 2026 - Apply Online</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/iit-ism-dhanbad-junior-research-fellow-recruitment-2026-apply-online-3051259</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 07:09:02 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Junior Research Fellow",
+    "JOB_TYPE": "Contractual Research",
+    "JOB_CATEGORY": "Research",
+    "DEPARTMENT": "Electronics Engineering",
+    "MINISTRY": "Ministry of Education",
+    "RECRUITING_AGENCY": "IIT (ISM) Dhanbad",
+    "ADVT_NO": "F.No. IIT(ISM)/R&amp;D/Rectt.JRF/2025-26/15 (tentative)",
+    "TOTAL_VACANCIES": 3,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Junior Research Fellow",
+        "VACANCIES": 3,
+        "CATEGORY": "Unreserved",
+        "PAY_LEVEL": "N/A",
+        "CLASSIFICATION": "Research"
+      }
+    ],
+    "JOB_LOCATION": "Dhanbad, Jharkhand",
+    "GROUP": "N/A"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "N/A",
+    "PAY_SCALE": "Rs. 37,000 + 30% HRA or Hostel Accommodation",
+    "MINIMUM_SALARY": 37000,
+    "MAXIMUM_SALARY": 48100,
+    "ALLOWANCES": ["HRA 30% or Hostel Accommodation"],
+    "PERKS": ["Medical facility", "Leave as per rules"]
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "M.E./M.Tech or equivalent degree in Electronics Engineering or related field with GATE/NET qualification; or B.E./B.Tech with GATE and 2 years experience; or M.Sc. with NET and 2 years experience",
+    "EDUCATION_DETAILS": [
+      {
+        "DEGREE": "M.E./M.Tech",
+        "BRANCH": "Electronics Engineering",
+        "MINIMUM_PERCENTAGE": ""
+      },
+      {
+        "DEGREE": "B.E./B.Tech",
+        "BRANCH": "Electronics Engineering",
+        "MINIMUM_PERCENTAGE": ""
+      },
+      {
+        "DEGREE": "M.Sc.",
+        "BRANCH": "Physics/Electronics",
+        "MINIMUM_PERCENTAGE": ""
+      }
+    ],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "2 years for BE/BTech/MSc (if applicable)",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 18,
+      "MAXIMUM_AGE": 30,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "As per Govt. norms",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": "As per notification"
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": ["Must have GATE/NET qualification"]
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online/Offline (as per notification)",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": ["Visit official website or send application to the Principal Investigator"],
+    "REQUIRED_DOCUMENTS": ["Application form", "Self-attested copies of certificates", "Proof of experience", "Research papers if any", "Valid GATE/NET score card"],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Interview", "Shortlisting based on qualification/experience"],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": null,
+      "INTERVIEW": {
+        "TOTAL_MARKS": 100,
+        "DURATION": "Varies"
+      },
+      "SKILL_TEST": null,
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.iitism.ac.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "1 year (likely)",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "Promotion to SRF after 2 years subject to performance",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "As per Govt. norms",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": ["The post is purely temporary"],
+    "OFFICIAL_LANGUAGE": "English",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Kurukshetra University Result 2026 Out - Check KUK 1st 3rd 5th 7th Semester Results Online at kuk.ac.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/kurukshetra-university-result-2026-out-check-kuk-1st-3rd-5th-7th-semester-results-online-3051257</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 07:07:58 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "KUK 1st, 3rd, 5th, 7th Semester Exams",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Kurukshetra University",
+    "EXAM_TYPE": "University Semester Exam",
+    "CATEGORY": "University Result"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026",
+    "RESULT_TYPE": "Semester-wise Result",
+    "DIRECT_RESULT_LINK": "https://kuk.ac.in",
+    "STATUS_CHECK_LINK": "https://kuk.ac.in"
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website kuk.ac.in",
+      "Click on the 'Results' tab",
+      "Select your semester and course",
+      "Enter your roll number and other required details",
+      "View and download the result"
+    ],
+    "REQUIRED_DETAILS": ["Roll Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Check via SMS or mobile app if available"
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://kuk.ac.in",
+    "DIRECT_RESULT": "https://kuk.ac.in",
+    "OFFICIAL_WEBSITE": "https://kuk.ac.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>IIT Gandhinagar Program Associate I Recruitment 2026 - Apply Online</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/iit-gandhinagar-program-associate-i-recruitment-2026-apply-online-3051256</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 07:04:38 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Program Associate I",
+    "JOB_TYPE": "Contractual",
+    "JOB_CATEGORY": "Research",
+    "DEPARTMENT": "Research and Development",
+    "MINISTRY": "Ministry of Education",
+    "RECRUITING_AGENCY": "Indian Institute of Technology Gandhinagar",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Program Associate I",
+        "VACANCIES": 0,
+        "CATEGORY": "Unreserved",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": "Non-Gazetted"
+      }
+    ],
+    "JOB_LOCATION": "Gandhinagar, Gujarat",
+    "GROUP": "C"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 37500,
+    "MAXIMUM_SALARY": 67000,
+    "ALLOWANCES": ["HRA", "TA", "DA"],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Bachelor's degree or Master's degree in relevant field",
+    "EDUCATION_DETAILS": [
+      "Bachelor's degree in Engineering/Technology/Science or equivalent",
+      "Master's degree in relevant discipline"
+    ],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "Desirable: 2 years of research experience",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 30,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "10 years",
+        "EX_SERVICEMEN": "As per rules",
+        "WOMEN": "0",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "2026-01-01",
+    "APPLICATION_LAST_DATE": "2026-01-31",
+    "LAST_DATE_FOR_FEE": "2026-01-31",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 500,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": "Online"
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "Visit official website",
+      "Click on recruitment link",
+      "Fill application form",
+      "Upload documents",
+      "Pay fee",
+      "Submit"
+    ],
+    "REQUIRED_DOCUMENTS": [
+      "Educational certificates",
+      "Experience proof",
+      "Age proof",
+      "Photo",
+      "Signature"
+    ],
+    "PHOTO_SPECIFICATIONS": "Passport size, white background",
+    "SIGNATURE_SPECIFICATIONS": "Black ink on white paper"
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [
+      "Application Screening",
+      "Interview",
+      "Document Verification"
+    ],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": null,
+      "INTERVIEW": {
+        "TOTAL_MARKS": 100,
+        "DURATION": ""
+      },
+      "SKILL_TEST": null,
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "2026-01-01",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "To be notified",
+    "FINAL_RESULT_DATE": "2026-02-28",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "https://apply.iitgn.ac.in",
+    "OFFICIAL_WEBSITE": "https://www.iitgn.ac.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "1 year",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "Possibility of promotion to higher position",
+    "TRANSFER_POLICY": "Within institute",
+    "RESERVATION_DETAILS": "As per Government of India norms",
+    "CONTACT_HELPLINE": "079-23952000",
+    "IMP_INSTRUCTIONS": [
+      "Read notification carefully",
+      "Apply before last date"
+    ],
+    "OFFICIAL_LANGUAGE": "English/Hindi",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>IARI Project Associate Recruitment 2026 - Apply Online</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/iari-project-associate-i-recruitment-2026-apply-online-3051253</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 07:02:45 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Project Associate",
+    "JOB_TYPE": "Project",
+    "JOB_CATEGORY": "Technical",
+    "DEPARTMENT": "Indian Agricultural Research Institute (IARI)",
+    "MINISTRY": "Ministry of Agriculture and Farmers' Welfare",
+    "RECRUITING_AGENCY": "IARI",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Project Associate",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "New Delhi",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "Rs. 28000-35000 per month",
+    "MINIMUM_SALARY": 28000,
+    "MAXIMUM_SALARY": 35000,
+    "ALLOWANCES": ["HRA as applicable"],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "M.Sc. in relevant discipline",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "Desirable experience in relevant field",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 18,
+      "MAXIMUM_AGE": 35,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "10 years",
+        "EX_SERVICEMEN": "As per rules",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": "Online"
+    },
+    "HOW_TO_APPLY_STEPS": ["Visit official website", "Fill online application", "Upload documents", "Submit"],
+    "REQUIRED_DOCUMENTS": ["Photo", "Signature", "Educational certificates", "Experience certificates"],
+    "PHOTO_SPECIFICATIONS": "Passport size",
+    "SIGNATURE_SPECIFICATIONS": "Signature on white paper"
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Interview"],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": null,
+      "INTERVIEW": {
+        "TOTAL_MARKS": 100,
+        "DURATION": "30 minutes"
+      },
+      "SKILL_TEST": null,
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": ["Relevant subject knowledge"],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "To be notified",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.iari.res.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "As per government norms",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": ["Read notification carefully before applying"],
+    "OFFICIAL_LANGUAGE": "English",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Solapur University Result 2026 Out - Direct Link to Download M.Sc Sem 3 and 4 Results at sus.ac.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/solapur-university-result-2026-out-direct-link-to-download-msc-sem-3-and-4-results-3051251</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 06:59:47 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "M.Sc Semester 3 and 4",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Solapur University",
+    "EXAM_TYPE": "Semester",
+    "CATEGORY": "University"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026",
+    "RESULT_TYPE": "Semester Result",
+    "DIRECT_RESULT_LINK": "https://www.sus.ac.in",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website of Solapur University: sus.ac.in",
+      "Click on the 'Result' section on the homepage",
+      "Find the link for 'M.Sc Sem 3 and 4 Result 2026' and click on it",
+      "Enter your Roll Number and other required details",
+      "Click on Submit to view your result",
+      "Download and take a printout for future reference"
+    ],
+    "REQUIRED_DETAILS": ["Roll Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Direct link provided on freejobalert.com"
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://www.sus.ac.in",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "https://www.sus.ac.in",
+    "OFFICIAL_WEBSITE": "https://www.sus.ac.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>IIT Roorkee Senior Research Fellow Recruitment 2026 - Apply Online</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/iit-roorkee-senior-research-fellow-srf-recruitment-2026-apply-online-3051250</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 06:58:14 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Senior Research Fellow (SRF)",
+    "JOB_TYPE": "Research",
+    "JOB_CATEGORY": "Contractual",
+    "DEPARTMENT": "विभिन्न विभाग",
+    "MINISTRY": "शिक्षा मंत्रालय",
+    "RECRUITING_AGENCY": "IIT Roorkee",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Senior Research Fellow (SRF)",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "Roorkee, Uttarakhand",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "Rs. 35,000 - 40,000 per month + HRA",
+    "MINIMUM_SALARY": 35000,
+    "MAXIMUM_SALARY": 40000,
+    "ALLOWANCES": ["HRA"],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "M.Tech/ M.E. in relevant field with GATE/ NET qualification or equivalent",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "2 years research experience after M.Tech/ M.E.",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": null,
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Interview"],
+    "EXAM_PATTERN": null,
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": null
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.iitr.ac.in/",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Anna University Project Assistant Recruitment 2026 - Apply Offline</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/anna-university-project-assistant-recruitment-2026-apply-offline-for-01-post-3051247</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 06:57:51 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Project Assistant",
+    "JOB_TYPE": "Contractual",
+    "JOB_CATEGORY": "Research",
+    "DEPARTMENT": "Anna University",
+    "MINISTRY": "",
+    "RECRUITING_AGENCY": "Anna University",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 1,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Project Assistant",
+        "VACANCIES": 1,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "Chennai",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Bachelor's degree in relevant field",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Offline",
     "APPLICATION_START_DATE": "",
     "APPLICATION_LAST_DATE": "",
     "LAST_DATE_FOR_FEE": "",
@@ -26838,6 +34254,1432 @@
         <v>753</v>
       </c>
     </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>7</v>
+      </c>
+      <c r="B189" t="s">
+        <v>754</v>
+      </c>
+      <c r="C189" t="s">
+        <v>755</v>
+      </c>
+      <c r="D189" t="s">
+        <v>756</v>
+      </c>
+      <c r="E189" t="s">
+        <v>11</v>
+      </c>
+      <c r="F189" t="s">
+        <v>754</v>
+      </c>
+      <c r="G189" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>7</v>
+      </c>
+      <c r="B190" t="s">
+        <v>758</v>
+      </c>
+      <c r="C190" t="s">
+        <v>759</v>
+      </c>
+      <c r="D190" t="s">
+        <v>760</v>
+      </c>
+      <c r="E190" t="s">
+        <v>11</v>
+      </c>
+      <c r="F190" t="s">
+        <v>758</v>
+      </c>
+      <c r="G190" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>7</v>
+      </c>
+      <c r="B191" t="s">
+        <v>762</v>
+      </c>
+      <c r="C191" t="s">
+        <v>763</v>
+      </c>
+      <c r="D191" t="s">
+        <v>764</v>
+      </c>
+      <c r="E191" t="s">
+        <v>11</v>
+      </c>
+      <c r="F191" t="s">
+        <v>762</v>
+      </c>
+      <c r="G191" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>7</v>
+      </c>
+      <c r="B192" t="s">
+        <v>766</v>
+      </c>
+      <c r="C192" t="s">
+        <v>767</v>
+      </c>
+      <c r="D192" t="s">
+        <v>768</v>
+      </c>
+      <c r="E192" t="s">
+        <v>11</v>
+      </c>
+      <c r="F192" t="s">
+        <v>766</v>
+      </c>
+      <c r="G192" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>7</v>
+      </c>
+      <c r="B193" t="s">
+        <v>770</v>
+      </c>
+      <c r="C193" t="s">
+        <v>771</v>
+      </c>
+      <c r="D193" t="s">
+        <v>772</v>
+      </c>
+      <c r="E193" t="s">
+        <v>11</v>
+      </c>
+      <c r="F193" t="s">
+        <v>770</v>
+      </c>
+      <c r="G193" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>7</v>
+      </c>
+      <c r="B194" t="s">
+        <v>774</v>
+      </c>
+      <c r="C194" t="s">
+        <v>775</v>
+      </c>
+      <c r="D194" t="s">
+        <v>776</v>
+      </c>
+      <c r="E194" t="s">
+        <v>11</v>
+      </c>
+      <c r="F194" t="s">
+        <v>774</v>
+      </c>
+      <c r="G194" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>7</v>
+      </c>
+      <c r="B195" t="s">
+        <v>778</v>
+      </c>
+      <c r="C195" t="s">
+        <v>779</v>
+      </c>
+      <c r="D195" t="s">
+        <v>780</v>
+      </c>
+      <c r="E195" t="s">
+        <v>24</v>
+      </c>
+      <c r="F195" t="s">
+        <v>778</v>
+      </c>
+      <c r="G195" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>52</v>
+      </c>
+      <c r="B196" t="s">
+        <v>782</v>
+      </c>
+      <c r="C196" t="s">
+        <v>783</v>
+      </c>
+      <c r="D196" t="s">
+        <v>784</v>
+      </c>
+      <c r="E196" t="s">
+        <v>11</v>
+      </c>
+      <c r="F196" t="s">
+        <v>782</v>
+      </c>
+      <c r="G196" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>52</v>
+      </c>
+      <c r="B197" t="s">
+        <v>786</v>
+      </c>
+      <c r="C197" t="s">
+        <v>787</v>
+      </c>
+      <c r="D197" t="s">
+        <v>788</v>
+      </c>
+      <c r="E197" t="s">
+        <v>393</v>
+      </c>
+      <c r="F197" t="s">
+        <v>786</v>
+      </c>
+      <c r="G197" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>52</v>
+      </c>
+      <c r="B198" t="s">
+        <v>790</v>
+      </c>
+      <c r="C198" t="s">
+        <v>791</v>
+      </c>
+      <c r="D198" t="s">
+        <v>792</v>
+      </c>
+      <c r="E198" t="s">
+        <v>29</v>
+      </c>
+      <c r="F198" t="s">
+        <v>790</v>
+      </c>
+      <c r="G198" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>52</v>
+      </c>
+      <c r="B199" t="s">
+        <v>794</v>
+      </c>
+      <c r="C199" t="s">
+        <v>795</v>
+      </c>
+      <c r="D199" t="s">
+        <v>796</v>
+      </c>
+      <c r="E199" t="s">
+        <v>11</v>
+      </c>
+      <c r="F199" t="s">
+        <v>794</v>
+      </c>
+      <c r="G199" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>52</v>
+      </c>
+      <c r="B200" t="s">
+        <v>798</v>
+      </c>
+      <c r="C200" t="s">
+        <v>799</v>
+      </c>
+      <c r="D200" t="s">
+        <v>800</v>
+      </c>
+      <c r="E200" t="s">
+        <v>393</v>
+      </c>
+      <c r="F200" t="s">
+        <v>798</v>
+      </c>
+      <c r="G200" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>52</v>
+      </c>
+      <c r="B201" t="s">
+        <v>802</v>
+      </c>
+      <c r="C201" t="s">
+        <v>803</v>
+      </c>
+      <c r="D201" t="s">
+        <v>804</v>
+      </c>
+      <c r="E201" t="s">
+        <v>11</v>
+      </c>
+      <c r="F201" t="s">
+        <v>802</v>
+      </c>
+      <c r="G201" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="s">
+        <v>52</v>
+      </c>
+      <c r="B202" t="s">
+        <v>806</v>
+      </c>
+      <c r="C202" t="s">
+        <v>807</v>
+      </c>
+      <c r="D202" t="s">
+        <v>808</v>
+      </c>
+      <c r="E202" t="s">
+        <v>11</v>
+      </c>
+      <c r="F202" t="s">
+        <v>806</v>
+      </c>
+      <c r="G202" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="s">
+        <v>52</v>
+      </c>
+      <c r="B203" t="s">
+        <v>810</v>
+      </c>
+      <c r="C203" t="s">
+        <v>811</v>
+      </c>
+      <c r="D203" t="s">
+        <v>812</v>
+      </c>
+      <c r="E203" t="s">
+        <v>29</v>
+      </c>
+      <c r="F203" t="s">
+        <v>810</v>
+      </c>
+      <c r="G203" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="s">
+        <v>52</v>
+      </c>
+      <c r="B204" t="s">
+        <v>814</v>
+      </c>
+      <c r="C204" t="s">
+        <v>815</v>
+      </c>
+      <c r="D204" t="s">
+        <v>816</v>
+      </c>
+      <c r="E204" t="s">
+        <v>29</v>
+      </c>
+      <c r="F204" t="s">
+        <v>814</v>
+      </c>
+      <c r="G204" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="s">
+        <v>52</v>
+      </c>
+      <c r="B205" t="s">
+        <v>818</v>
+      </c>
+      <c r="C205" t="s">
+        <v>819</v>
+      </c>
+      <c r="D205" t="s">
+        <v>820</v>
+      </c>
+      <c r="E205" t="s">
+        <v>11</v>
+      </c>
+      <c r="F205" t="s">
+        <v>818</v>
+      </c>
+      <c r="G205" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="s">
+        <v>52</v>
+      </c>
+      <c r="B206" t="s">
+        <v>822</v>
+      </c>
+      <c r="C206" t="s">
+        <v>823</v>
+      </c>
+      <c r="D206" t="s">
+        <v>824</v>
+      </c>
+      <c r="E206" t="s">
+        <v>11</v>
+      </c>
+      <c r="F206" t="s">
+        <v>822</v>
+      </c>
+      <c r="G206" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="s">
+        <v>52</v>
+      </c>
+      <c r="B207" t="s">
+        <v>826</v>
+      </c>
+      <c r="C207" t="s">
+        <v>827</v>
+      </c>
+      <c r="D207" t="s">
+        <v>828</v>
+      </c>
+      <c r="E207" t="s">
+        <v>29</v>
+      </c>
+      <c r="F207" t="s">
+        <v>826</v>
+      </c>
+      <c r="G207" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="s">
+        <v>52</v>
+      </c>
+      <c r="B208" t="s">
+        <v>830</v>
+      </c>
+      <c r="C208" t="s">
+        <v>831</v>
+      </c>
+      <c r="D208" t="s">
+        <v>832</v>
+      </c>
+      <c r="E208" t="s">
+        <v>11</v>
+      </c>
+      <c r="F208" t="s">
+        <v>830</v>
+      </c>
+      <c r="G208" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="s">
+        <v>52</v>
+      </c>
+      <c r="B209" t="s">
+        <v>834</v>
+      </c>
+      <c r="C209" t="s">
+        <v>835</v>
+      </c>
+      <c r="D209" t="s">
+        <v>836</v>
+      </c>
+      <c r="E209" t="s">
+        <v>11</v>
+      </c>
+      <c r="F209" t="s">
+        <v>834</v>
+      </c>
+      <c r="G209" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="s">
+        <v>52</v>
+      </c>
+      <c r="B210" t="s">
+        <v>838</v>
+      </c>
+      <c r="C210" t="s">
+        <v>839</v>
+      </c>
+      <c r="D210" t="s">
+        <v>840</v>
+      </c>
+      <c r="E210" t="s">
+        <v>11</v>
+      </c>
+      <c r="F210" t="s">
+        <v>838</v>
+      </c>
+      <c r="G210" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="s">
+        <v>52</v>
+      </c>
+      <c r="B211" t="s">
+        <v>842</v>
+      </c>
+      <c r="C211" t="s">
+        <v>843</v>
+      </c>
+      <c r="D211" t="s">
+        <v>844</v>
+      </c>
+      <c r="E211" t="s">
+        <v>24</v>
+      </c>
+      <c r="F211" t="s">
+        <v>842</v>
+      </c>
+      <c r="G211" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="s">
+        <v>52</v>
+      </c>
+      <c r="B212" t="s">
+        <v>846</v>
+      </c>
+      <c r="C212" t="s">
+        <v>847</v>
+      </c>
+      <c r="D212" t="s">
+        <v>848</v>
+      </c>
+      <c r="E212" t="s">
+        <v>741</v>
+      </c>
+      <c r="F212" t="s">
+        <v>846</v>
+      </c>
+      <c r="G212" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="s">
+        <v>52</v>
+      </c>
+      <c r="B213" t="s">
+        <v>850</v>
+      </c>
+      <c r="C213" t="s">
+        <v>851</v>
+      </c>
+      <c r="D213" t="s">
+        <v>852</v>
+      </c>
+      <c r="E213" t="s">
+        <v>11</v>
+      </c>
+      <c r="F213" t="s">
+        <v>850</v>
+      </c>
+      <c r="G213" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="s">
+        <v>52</v>
+      </c>
+      <c r="B214" t="s">
+        <v>854</v>
+      </c>
+      <c r="C214" t="s">
+        <v>855</v>
+      </c>
+      <c r="D214" t="s">
+        <v>856</v>
+      </c>
+      <c r="E214" t="s">
+        <v>11</v>
+      </c>
+      <c r="F214" t="s">
+        <v>854</v>
+      </c>
+      <c r="G214" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="s">
+        <v>52</v>
+      </c>
+      <c r="B215" t="s">
+        <v>858</v>
+      </c>
+      <c r="C215" t="s">
+        <v>859</v>
+      </c>
+      <c r="D215" t="s">
+        <v>860</v>
+      </c>
+      <c r="E215" t="s">
+        <v>29</v>
+      </c>
+      <c r="F215" t="s">
+        <v>858</v>
+      </c>
+      <c r="G215" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="s">
+        <v>52</v>
+      </c>
+      <c r="B216" t="s">
+        <v>862</v>
+      </c>
+      <c r="C216" t="s">
+        <v>863</v>
+      </c>
+      <c r="D216" t="s">
+        <v>864</v>
+      </c>
+      <c r="E216" t="s">
+        <v>11</v>
+      </c>
+      <c r="F216" t="s">
+        <v>862</v>
+      </c>
+      <c r="G216" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="s">
+        <v>52</v>
+      </c>
+      <c r="B217" t="s">
+        <v>866</v>
+      </c>
+      <c r="C217" t="s">
+        <v>867</v>
+      </c>
+      <c r="D217" t="s">
+        <v>868</v>
+      </c>
+      <c r="E217" t="s">
+        <v>11</v>
+      </c>
+      <c r="F217" t="s">
+        <v>866</v>
+      </c>
+      <c r="G217" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="s">
+        <v>52</v>
+      </c>
+      <c r="B218" t="s">
+        <v>870</v>
+      </c>
+      <c r="C218" t="s">
+        <v>871</v>
+      </c>
+      <c r="D218" t="s">
+        <v>872</v>
+      </c>
+      <c r="E218" t="s">
+        <v>393</v>
+      </c>
+      <c r="F218" t="s">
+        <v>870</v>
+      </c>
+      <c r="G218" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="s">
+        <v>52</v>
+      </c>
+      <c r="B219" t="s">
+        <v>874</v>
+      </c>
+      <c r="C219" t="s">
+        <v>875</v>
+      </c>
+      <c r="D219" t="s">
+        <v>876</v>
+      </c>
+      <c r="E219" t="s">
+        <v>741</v>
+      </c>
+      <c r="F219" t="s">
+        <v>874</v>
+      </c>
+      <c r="G219" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="s">
+        <v>52</v>
+      </c>
+      <c r="B220" t="s">
+        <v>878</v>
+      </c>
+      <c r="C220" t="s">
+        <v>879</v>
+      </c>
+      <c r="D220" t="s">
+        <v>880</v>
+      </c>
+      <c r="E220" t="s">
+        <v>29</v>
+      </c>
+      <c r="F220" t="s">
+        <v>878</v>
+      </c>
+      <c r="G220" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="s">
+        <v>52</v>
+      </c>
+      <c r="B221" t="s">
+        <v>882</v>
+      </c>
+      <c r="C221" t="s">
+        <v>883</v>
+      </c>
+      <c r="D221" t="s">
+        <v>884</v>
+      </c>
+      <c r="E221" t="s">
+        <v>29</v>
+      </c>
+      <c r="F221" t="s">
+        <v>882</v>
+      </c>
+      <c r="G221" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="s">
+        <v>52</v>
+      </c>
+      <c r="B222" t="s">
+        <v>886</v>
+      </c>
+      <c r="C222" t="s">
+        <v>887</v>
+      </c>
+      <c r="D222" t="s">
+        <v>888</v>
+      </c>
+      <c r="E222" t="s">
+        <v>11</v>
+      </c>
+      <c r="F222" t="s">
+        <v>886</v>
+      </c>
+      <c r="G222" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="s">
+        <v>52</v>
+      </c>
+      <c r="B223" t="s">
+        <v>890</v>
+      </c>
+      <c r="C223" t="s">
+        <v>891</v>
+      </c>
+      <c r="D223" t="s">
+        <v>892</v>
+      </c>
+      <c r="E223" t="s">
+        <v>11</v>
+      </c>
+      <c r="F223" t="s">
+        <v>890</v>
+      </c>
+      <c r="G223" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="s">
+        <v>52</v>
+      </c>
+      <c r="B224" t="s">
+        <v>894</v>
+      </c>
+      <c r="C224" t="s">
+        <v>895</v>
+      </c>
+      <c r="D224" t="s">
+        <v>896</v>
+      </c>
+      <c r="E224" t="s">
+        <v>741</v>
+      </c>
+      <c r="F224" t="s">
+        <v>894</v>
+      </c>
+      <c r="G224" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="s">
+        <v>52</v>
+      </c>
+      <c r="B225" t="s">
+        <v>898</v>
+      </c>
+      <c r="C225" t="s">
+        <v>899</v>
+      </c>
+      <c r="D225" t="s">
+        <v>900</v>
+      </c>
+      <c r="E225" t="s">
+        <v>29</v>
+      </c>
+      <c r="F225" t="s">
+        <v>898</v>
+      </c>
+      <c r="G225" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="s">
+        <v>52</v>
+      </c>
+      <c r="B226" t="s">
+        <v>902</v>
+      </c>
+      <c r="C226" t="s">
+        <v>903</v>
+      </c>
+      <c r="D226" t="s">
+        <v>904</v>
+      </c>
+      <c r="E226" t="s">
+        <v>11</v>
+      </c>
+      <c r="F226" t="s">
+        <v>902</v>
+      </c>
+      <c r="G226" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="s">
+        <v>52</v>
+      </c>
+      <c r="B227" t="s">
+        <v>906</v>
+      </c>
+      <c r="C227" t="s">
+        <v>907</v>
+      </c>
+      <c r="D227" t="s">
+        <v>908</v>
+      </c>
+      <c r="E227" t="s">
+        <v>11</v>
+      </c>
+      <c r="F227" t="s">
+        <v>906</v>
+      </c>
+      <c r="G227" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="s">
+        <v>52</v>
+      </c>
+      <c r="B228" t="s">
+        <v>910</v>
+      </c>
+      <c r="C228" t="s">
+        <v>911</v>
+      </c>
+      <c r="D228" t="s">
+        <v>912</v>
+      </c>
+      <c r="E228" t="s">
+        <v>11</v>
+      </c>
+      <c r="F228" t="s">
+        <v>910</v>
+      </c>
+      <c r="G228" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="s">
+        <v>52</v>
+      </c>
+      <c r="B229" t="s">
+        <v>914</v>
+      </c>
+      <c r="C229" t="s">
+        <v>915</v>
+      </c>
+      <c r="D229" t="s">
+        <v>916</v>
+      </c>
+      <c r="E229" t="s">
+        <v>29</v>
+      </c>
+      <c r="F229" t="s">
+        <v>914</v>
+      </c>
+      <c r="G229" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="s">
+        <v>52</v>
+      </c>
+      <c r="B230" t="s">
+        <v>918</v>
+      </c>
+      <c r="C230" t="s">
+        <v>919</v>
+      </c>
+      <c r="D230" t="s">
+        <v>920</v>
+      </c>
+      <c r="E230" t="s">
+        <v>38</v>
+      </c>
+      <c r="F230" t="s">
+        <v>918</v>
+      </c>
+      <c r="G230" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="s">
+        <v>52</v>
+      </c>
+      <c r="B231" t="s">
+        <v>922</v>
+      </c>
+      <c r="C231" t="s">
+        <v>923</v>
+      </c>
+      <c r="D231" t="s">
+        <v>924</v>
+      </c>
+      <c r="E231" t="s">
+        <v>925</v>
+      </c>
+      <c r="F231" t="s">
+        <v>922</v>
+      </c>
+      <c r="G231" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="s">
+        <v>52</v>
+      </c>
+      <c r="B232" t="s">
+        <v>927</v>
+      </c>
+      <c r="C232" t="s">
+        <v>928</v>
+      </c>
+      <c r="D232" t="s">
+        <v>929</v>
+      </c>
+      <c r="E232" t="s">
+        <v>11</v>
+      </c>
+      <c r="F232" t="s">
+        <v>927</v>
+      </c>
+      <c r="G232" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="s">
+        <v>52</v>
+      </c>
+      <c r="B233" t="s">
+        <v>931</v>
+      </c>
+      <c r="C233" t="s">
+        <v>932</v>
+      </c>
+      <c r="D233" t="s">
+        <v>933</v>
+      </c>
+      <c r="E233" t="s">
+        <v>29</v>
+      </c>
+      <c r="F233" t="s">
+        <v>931</v>
+      </c>
+      <c r="G233" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="s">
+        <v>52</v>
+      </c>
+      <c r="B234" t="s">
+        <v>935</v>
+      </c>
+      <c r="C234" t="s">
+        <v>936</v>
+      </c>
+      <c r="D234" t="s">
+        <v>937</v>
+      </c>
+      <c r="E234" t="s">
+        <v>11</v>
+      </c>
+      <c r="F234" t="s">
+        <v>935</v>
+      </c>
+      <c r="G234" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="s">
+        <v>52</v>
+      </c>
+      <c r="B235" t="s">
+        <v>939</v>
+      </c>
+      <c r="C235" t="s">
+        <v>940</v>
+      </c>
+      <c r="D235" t="s">
+        <v>941</v>
+      </c>
+      <c r="E235" t="s">
+        <v>11</v>
+      </c>
+      <c r="F235" t="s">
+        <v>939</v>
+      </c>
+      <c r="G235" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="s">
+        <v>52</v>
+      </c>
+      <c r="B236" t="s">
+        <v>943</v>
+      </c>
+      <c r="C236" t="s">
+        <v>944</v>
+      </c>
+      <c r="D236" t="s">
+        <v>945</v>
+      </c>
+      <c r="E236" t="s">
+        <v>29</v>
+      </c>
+      <c r="F236" t="s">
+        <v>943</v>
+      </c>
+      <c r="G236" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="s">
+        <v>52</v>
+      </c>
+      <c r="B237" t="s">
+        <v>947</v>
+      </c>
+      <c r="C237" t="s">
+        <v>948</v>
+      </c>
+      <c r="D237" t="s">
+        <v>949</v>
+      </c>
+      <c r="E237" t="s">
+        <v>11</v>
+      </c>
+      <c r="F237" t="s">
+        <v>947</v>
+      </c>
+      <c r="G237" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="s">
+        <v>52</v>
+      </c>
+      <c r="B238" t="s">
+        <v>951</v>
+      </c>
+      <c r="C238" t="s">
+        <v>952</v>
+      </c>
+      <c r="D238" t="s">
+        <v>953</v>
+      </c>
+      <c r="E238" t="s">
+        <v>11</v>
+      </c>
+      <c r="F238" t="s">
+        <v>951</v>
+      </c>
+      <c r="G238" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="s">
+        <v>52</v>
+      </c>
+      <c r="B239" t="s">
+        <v>955</v>
+      </c>
+      <c r="C239" t="s">
+        <v>956</v>
+      </c>
+      <c r="D239" t="s">
+        <v>957</v>
+      </c>
+      <c r="E239" t="s">
+        <v>11</v>
+      </c>
+      <c r="F239" t="s">
+        <v>955</v>
+      </c>
+      <c r="G239" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="s">
+        <v>52</v>
+      </c>
+      <c r="B240" t="s">
+        <v>959</v>
+      </c>
+      <c r="C240" t="s">
+        <v>960</v>
+      </c>
+      <c r="D240" t="s">
+        <v>961</v>
+      </c>
+      <c r="E240" t="s">
+        <v>741</v>
+      </c>
+      <c r="F240" t="s">
+        <v>959</v>
+      </c>
+      <c r="G240" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="s">
+        <v>52</v>
+      </c>
+      <c r="B241" t="s">
+        <v>963</v>
+      </c>
+      <c r="C241" t="s">
+        <v>964</v>
+      </c>
+      <c r="D241" t="s">
+        <v>965</v>
+      </c>
+      <c r="E241" t="s">
+        <v>11</v>
+      </c>
+      <c r="F241" t="s">
+        <v>963</v>
+      </c>
+      <c r="G241" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="s">
+        <v>52</v>
+      </c>
+      <c r="B242" t="s">
+        <v>967</v>
+      </c>
+      <c r="C242" t="s">
+        <v>968</v>
+      </c>
+      <c r="D242" t="s">
+        <v>969</v>
+      </c>
+      <c r="E242" t="s">
+        <v>38</v>
+      </c>
+      <c r="F242" t="s">
+        <v>967</v>
+      </c>
+      <c r="G242" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="s">
+        <v>52</v>
+      </c>
+      <c r="B243" t="s">
+        <v>971</v>
+      </c>
+      <c r="C243" t="s">
+        <v>972</v>
+      </c>
+      <c r="D243" t="s">
+        <v>973</v>
+      </c>
+      <c r="E243" t="s">
+        <v>11</v>
+      </c>
+      <c r="F243" t="s">
+        <v>971</v>
+      </c>
+      <c r="G243" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="s">
+        <v>52</v>
+      </c>
+      <c r="B244" t="s">
+        <v>975</v>
+      </c>
+      <c r="C244" t="s">
+        <v>976</v>
+      </c>
+      <c r="D244" t="s">
+        <v>977</v>
+      </c>
+      <c r="E244" t="s">
+        <v>11</v>
+      </c>
+      <c r="F244" t="s">
+        <v>975</v>
+      </c>
+      <c r="G244" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="s">
+        <v>52</v>
+      </c>
+      <c r="B245" t="s">
+        <v>979</v>
+      </c>
+      <c r="C245" t="s">
+        <v>980</v>
+      </c>
+      <c r="D245" t="s">
+        <v>981</v>
+      </c>
+      <c r="E245" t="s">
+        <v>29</v>
+      </c>
+      <c r="F245" t="s">
+        <v>979</v>
+      </c>
+      <c r="G245" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="s">
+        <v>52</v>
+      </c>
+      <c r="B246" t="s">
+        <v>983</v>
+      </c>
+      <c r="C246" t="s">
+        <v>984</v>
+      </c>
+      <c r="D246" t="s">
+        <v>985</v>
+      </c>
+      <c r="E246" t="s">
+        <v>11</v>
+      </c>
+      <c r="F246" t="s">
+        <v>983</v>
+      </c>
+      <c r="G246" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="s">
+        <v>52</v>
+      </c>
+      <c r="B247" t="s">
+        <v>987</v>
+      </c>
+      <c r="C247" t="s">
+        <v>988</v>
+      </c>
+      <c r="D247" t="s">
+        <v>989</v>
+      </c>
+      <c r="E247" t="s">
+        <v>11</v>
+      </c>
+      <c r="F247" t="s">
+        <v>987</v>
+      </c>
+      <c r="G247" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="s">
+        <v>52</v>
+      </c>
+      <c r="B248" t="s">
+        <v>991</v>
+      </c>
+      <c r="C248" t="s">
+        <v>992</v>
+      </c>
+      <c r="D248" t="s">
+        <v>993</v>
+      </c>
+      <c r="E248" t="s">
+        <v>29</v>
+      </c>
+      <c r="F248" t="s">
+        <v>991</v>
+      </c>
+      <c r="G248" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="s">
+        <v>52</v>
+      </c>
+      <c r="B249" t="s">
+        <v>995</v>
+      </c>
+      <c r="C249" t="s">
+        <v>996</v>
+      </c>
+      <c r="D249" t="s">
+        <v>997</v>
+      </c>
+      <c r="E249" t="s">
+        <v>11</v>
+      </c>
+      <c r="F249" t="s">
+        <v>995</v>
+      </c>
+      <c r="G249" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="s">
+        <v>52</v>
+      </c>
+      <c r="B250" t="s">
+        <v>999</v>
+      </c>
+      <c r="C250" t="s">
+        <v>1000</v>
+      </c>
+      <c r="D250" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E250" t="s">
+        <v>11</v>
+      </c>
+      <c r="F250" t="s">
+        <v>999</v>
+      </c>
+      <c r="G250" t="s">
+        <v>1002</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/data/articles.xlsx
+++ b/data/articles.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="1003">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1244" uniqueCount="1244">
   <si>
     <t>Competitor</t>
   </si>
@@ -29622,6 +29622,7952 @@
     "IMP_INSTRUCTIONS": [],
     "OFFICIAL_LANGUAGE": "",
     "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>RRB Section Controller CBAT Exam City Details 2026</t>
+  </si>
+  <si>
+    <t>https://sarkariresult.com.cm/rrb-section-controller-2026/</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 14:16:26 +0000</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Section Controller",
+    "JOB_TYPE": "Computer Based Aptitude Test (CBAT)",
+    "JOB_CATEGORY": "Technical",
+    "DEPARTMENT": "Railway",
+    "MINISTRY": "Ministry of Railways",
+    "RECRUITING_AGENCY": "Railway Recruitment Board (RRB)",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [],
+    "JOB_LOCATION": "All India",
+    "GROUP": "B"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {},
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {},
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {},
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["CBAT"],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": null,
+      "INTERVIEW": null,
+      "SKILL_TEST": {
+        "TYPE": "Computer Based Aptitude Test",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {}
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "2026",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>RBI JE Junior Engineer Admit Card 2026 – Out</t>
+  </si>
+  <si>
+    <t>https://sarkariresult.com.cm/rbi-junior-engineer-2026/</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 14:08:51 +0000</t>
+  </si>
+  <si>
+    <t>{
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "RBI JE Junior Engineer 2026",
+    "RECRUITMENT_NAME": "RBI Junior Engineer Recruitment 2026",
+    "POST_NAME": "Junior Engineer",
+    "CONDUCTING_BODY": "Reserve Bank of India",
+    "EXAM_TYPE": "Computer Based Test",
+    "CATEGORY": "Government"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "",
+    "DIRECT_DOWNLOAD_LINK": "https://sarkariresult.com.cm/rbi-junior-engineer-2026/",
+    "STATUS_CHECK_LINK": ""
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "",
+    "EXAM_TIME": "",
+    "EXAM_SHIFT": "",
+    "EXAM_DURATION": "",
+    "EXAM_MODE": "Online",
+    "EXAM_CENTER_CITY": "",
+    "EXAM_CENTER_NAME": "",
+    "FULL_SCHEDULE": []
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [
+      "Visit the official RBI website or the link provided.",
+      "Find the admit card link for Junior Engineer 2026.",
+      "Enter required details (Registration Number, Date of Birth, etc.).",
+      "Download and print the admit card."
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth"],
+    "ALTERNATE_METHOD": ""
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": [
+      "Carry a printed copy of the admit card to the exam center.",
+      "Carry a valid photo ID proof."
+    ],
+    "EXAM_DAY_GUIDELINES": [
+      "Reach the exam center at least 30 minutes before the scheduled time.",
+      "Follow the instructions of the invigilator."
+    ],
+    "DOCUMENTS_TO_CARRY": ["Admit Card", "Photo ID Proof"],
+    "PROHIBITED_ITEMS": ["Mobile phones", "Electronic gadgets", "Study material"],
+    "COVID_SPECIFIC": ""
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "",
+    "EXAM_DATE_LIST": [],
+    "RESULT_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://sarkariresult.com.cm/rbi-junior-engineer-2026/",
+    "DIRECT_DOWNLOAD": "https://sarkariresult.com.cm/rbi-junior-engineer-2026/",
+    "OFFICIAL_WEBSITE": "https://www.rbi.org.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "Contact RBI helpline for any issues.",
+    "REPRINT_OPTION": "Yes",
+    "CONTACT_DETAILS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>BPSC 72nd Pre Online Form 2026 (1189 Posts) – Start</t>
+  </si>
+  <si>
+    <t>https://sarkariresult.com.cm/bpsc-72nd-pre-2026/</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 14:02:45 +0000</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "72वीं संयुक्त प्रारंभिक परीक्षा",
+    "JOB_TYPE": "सरकारी नौकरी",
+    "JOB_CATEGORY": "प्रारंभिक परीक्षा",
+    "DEPARTMENT": "बिहार लोक सेवा आयोग",
+    "MINISTRY": "बिहार सरकार",
+    "RECRUITING_AGENCY": "बिहार लोक सेवा आयोग (BPSC)",
+    "ADVT_NO": "72वीं",
+    "TOTAL_VACANCIES": 1189,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "विभिन्न पद (विस्तृत विवरण अधिसूचना में)",
+        "VACANCIES": 1189,
+        "CATEGORY": "विभिन्न",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "बिहार",
+    "GROUP": "A और B"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "विभिन्न (पदानुसार)",
+    "PAY_SCALE": "विभिन्न (पदानुसार)",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "किसी मान्यता प्राप्त विश्वविद्यालय से स्नातक",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "नहीं",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 20,
+      "MAXIMUM_AGE": 37,
+      "AGE_RELAXATION": {
+        "SC_ST": "05 वर्ष",
+        "OBC": "03 वर्ष",
+        "PWD": "10 वर्ष",
+        "EX_SERVICEMEN": "जितनी सेवा की + 3 वर्ष",
+        "WOMEN": "बिहार महिला को 3 वर्ष",
+        "OTHER": []
+      },
+      "AGE_AS_ON": "01-08-2025"
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "ऑनलाइन",
+    "APPLICATION_START_DATE": "दिसंबर 2025 (अनुमानित)",
+    "APPLICATION_LAST_DATE": "जनवरी 2026 (अनुमानित)",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 750,
+      "SC_ST_PWD_WOMEN": 200,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": "डेबिट/क्रेडिट कार्ड, नेट बैंकिंग, UPI"
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["प्रारंभिक परीक्षा", "मुख्य परीक्षा", "साक्षात्कार"],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 150,
+        "DURATION": "2 घंटे",
+        "SUBJECTS": ["सामान्य अध्ययन"],
+        "NEGATIVE_MARKING": "हाँ, 1/3 अंक काटे जाएंगे"
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 900,
+        "DURATION": "प्रति पेपर 3 घंटे",
+        "SUBJECTS": ["सामान्य हिंदी", "निबंध", "सामान्य अध्ययन I-IV", "वैकल्पिक विषय"],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 120,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "दिसंबर 2025 (अनुमानित)",
+    "EXAM_DATE": "मार्च 2026 (अनुमानित)",
+    "ADMIT_CARD_DATE": "परीक्षा से 2 सप्ताह पूर्व",
+    "RESULT_DATE": "अप्रैल 2026 (अनुमानित)",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "https://www.bpsc.bih.nic.in/",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.bpsc.bih.nic.in/",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "बिहार सरकार के नियमानुसार",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "हिंदी, अंग्रेजी",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>RBI Bank Assistant Mains Admit Card 2026 – Out</t>
+  </si>
+  <si>
+    <t>https://sarkariresult.com.cm/rbi-bank-assistant-2026/</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 13:53:16 +0000</t>
+  </si>
+  <si>
+    <t>{
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "RBI Bank Assistant Mains",
+    "RECRUITMENT_NAME": "RBI Bank Assistant Recruitment 2026",
+    "POST_NAME": "Bank Assistant",
+    "CONDUCTING_BODY": "Reserve Bank of India (RBI)",
+    "EXAM_TYPE": "Mains",
+    "CATEGORY": "Government"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "To be announced",
+    "DIRECT_DOWNLOAD_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "",
+    "EXAM_TIME": "",
+    "EXAM_SHIFT": "",
+    "EXAM_DURATION": "",
+    "EXAM_MODE": "",
+    "EXAM_CENTER_CITY": "",
+    "EXAM_CENTER_NAME": "",
+    "FULL_SCHEDULE": []
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [
+      "Visit the official RBI website.",
+      "Click on the 'Recruitment' section.",
+      "Find the link for 'RBI Bank Assistant Mains Admit Card 2026'.",
+      "Enter your registration number and date of birth.",
+      "Download and print the admit card."
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth"],
+    "ALTERNATE_METHOD": ""
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": [],
+    "EXAM_DAY_GUIDELINES": [],
+    "DOCUMENTS_TO_CARRY": ["Admit Card", "Photo ID proof"],
+    "PROHIBITED_ITEMS": ["Electronic gadgets", "Mobile phones"],
+    "COVID_SPECIFIC": ""
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "",
+    "EXAM_DATE_LIST": [],
+    "RESULT_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_DOWNLOAD": "",
+    "OFFICIAL_WEBSITE": "https://www.rbi.org.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "",
+    "REPRINT_OPTION": "",
+    "CONTACT_DETAILS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>NTA UGC NET June Correction / Edit Form 2026 – Link Active</t>
+  </si>
+  <si>
+    <t>https://sarkariresult.com.cm/nta-ugc-net-june-2025/</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 12:19:26 +0000</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "UGC NET June 2026 Correction/Edit Form",
+    "JOB_TYPE": "Correction/Edit Form",
+    "JOB_CATEGORY": "Exam",
+    "DEPARTMENT": "National Testing Agency (NTA)",
+    "MINISTRY": "Ministry of Education",
+    "RECRUITING_AGENCY": "National Testing Agency (NTA)",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [],
+    "JOB_LOCATION": "All India",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": { "SC_ST": "", "OBC": "", "PWD": "", "EX_SERVICEMEN": "", "WOMEN": "", "OTHER": [] },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": { "HEIGHT_MALE": "", "HEIGHT_FEMALE": "", "CHEST_MALE": "", "CHEST_FEMALE": "", "WEIGHT": "", "RUNNING": "", "VISION": "", "OTHER": [] },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "Active (as per title)",
+    "APPLICATION_FEE": { "GENERAL_OBC_EWS": 0, "SC_ST_PWD_WOMEN": 0, "OTHER_CATEGORY_FEES": [], "PAYMENT_MODE": "" },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": { "TOTAL_MARKS": 0, "DURATION": "", "SUBJECTS": [], "NEGATIVE_MARKING": "" },
+      "MAINS": { "TOTAL_MARKS": 0, "DURATION": "", "SUBJECTS": [], "NEGATIVE_MARKING": "" },
+      "INTERVIEW": { "TOTAL_MARKS": 0, "DURATION": "" },
+      "SKILL_TEST": { "TYPE": "", "TOTAL_MARKS": 0, "DURATION": "" },
+      "PHYSICAL_EFFICIENCY_TEST": { "EVENTS": [], "QUALIFYING_NORMS": "" },
+      "DOCUMENT_VERIFICATION": false
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": { "PREVIOUS_YEAR": [], "EXPECTED": "" }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://sarkariresult.com.cm/nta-ugc-net-june-2025/",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Bihar STET 2025 Father Name Correction – Link Active</t>
+  </si>
+  <si>
+    <t>https://sarkariresult.com.cm/bihar-stet-2025/</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 12:15:07 +0000</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "Bihar STET 2025",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "Teacher",
+    "CONDUCTING_BODY": "Bihar School Examination Board (BSEB)",
+    "EXAM_TYPE": "Teacher Eligibility Test",
+    "CATEGORY": "State Level"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": false,
+    "DECLARATION_DATE": "",
+    "RESULT_TYPE": "Correction",
+    "DIRECT_RESULT_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [],
+    "REQUIRED_DETAILS": [],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "",
+    "OFFICIAL_WEBSITE": "https://bsebstet.com/",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>RBI Assistant Mains Admit Card 2026 (Out) - Download Here</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/rbi-assistant-mains-admit-card-2026-3051418</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 13:10:44 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "RBI Assistant Mains Exam 2026",
+    "RECRUITMENT_NAME": "RBI Assistant Recruitment 2026",
+    "POST_NAME": "Assistant",
+    "CONDUCTING_BODY": "Reserve Bank of India (RBI)",
+    "EXAM_TYPE": "Mains",
+    "CATEGORY": "Banking"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "2026 (Exact date not specified)",
+    "DIRECT_DOWNLOAD_LINK": "https://www.freejobalert.com/articles/rbi-assistant-mains-admit-card-2026-3051418",
+    "STATUS_CHECK_LINK": ""
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "To be announced",
+    "EXAM_TIME": "",
+    "EXAM_SHIFT": "",
+    "EXAM_DURATION": "",
+    "EXAM_MODE": "Online",
+    "EXAM_CENTER_CITY": "Various cities across India",
+    "EXAM_CENTER_NAME": "",
+    "FULL_SCHEDULE": []
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [
+      "Visit official RBI website or the provided link",
+      "Click on the admit card download link",
+      "Enter registration number/roll number and date of birth/password",
+      "Submit and download the admit card",
+      "Take a printout for future reference"
+    ],
+    "REQUIRED_DETAILS": ["Registration Number/Roll Number", "Date of Birth/Password"],
+    "ALTERNATE_METHOD": ""
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": [],
+    "EXAM_DAY_GUIDELINES": [],
+    "DOCUMENTS_TO_CARRY": [],
+    "PROHIBITED_ITEMS": [],
+    "COVID_SPECIFIC": ""
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "Released (exact date not specified)",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "Until exam date",
+    "EXAM_DATE_LIST": [],
+    "RESULT_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_DOWNLOAD": "https://www.freejobalert.com/articles/rbi-assistant-mains-admit-card-2026-3051418",
+    "OFFICIAL_WEBSITE": "https://www.rbi.org.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "",
+    "REPRINT_OPTION": "",
+    "CONTACT_DETAILS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>CSL Driver Recruitment 2026 - Apply Online</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/csl-driver-recruitment-2026-apply-online-3051417</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 13:09:53 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Driver",
+    "JOB_TYPE": "Regular",
+    "JOB_CATEGORY": "Group C",
+    "DEPARTMENT": "Cochin Shipyard Limited",
+    "MINISTRY": "Ministry of Ports, Shipping and Waterways",
+    "RECRUITING_AGENCY": "Cochin Shipyard Limited (CSL)",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Driver",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "Kochi",
+    "GROUP": "C"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "10th pass with valid driving license",
+    "EDUCATION_DETAILS": [
+      {
+        "QUALIFICATION": "10th Pass",
+        "SPECIALIZATION": "",
+        "MINIMUM_PERCENTAGE": "",
+        "INSTITUTE_TYPE": ""
+      }
+    ],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "3 years driving experience",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 18,
+      "MAXIMUM_AGE": 30,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "10 years",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [
+      "Written Test",
+      "Driving Test",
+      "Document Verification"
+    ],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": null,
+      "INTERVIEW": null,
+      "SKILL_TEST": {
+        "TYPE": "Driving Test",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>ICAR-IARI Recruitment 2026 - Apply Online for Research Associate, Young Professional Posts</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/icar-iari-recruitment-2026-apply-online-for-03-research-associate-young-professional-posts-3051415</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 13:03:59 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Research Associate, Young Professional",
+    "JOB_TYPE": "टेम्पररी",
+    "JOB_CATEGORY": "गैर-राजपत्रित",
+    "DEPARTMENT": "Indian Agricultural Research Institute (IARI)",
+    "MINISTRY": "Ministry of Agriculture and Farmers Welfare",
+    "RECRUITING_AGENCY": "ICAR-IARI",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 3,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Research Associate",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      },
+      {
+        "POST_NAME": "Young Professional",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "New Delhi",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Research Associate: Master's degree in relevant subject; Young Professional: Graduate/Post Graduate in relevant discipline",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "ऑफलाइन/वॉक-इन",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Interview"],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": null,
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": null,
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>IPMAT Indore Result 2026 Out - Check IIM Indore PI Shortlist at iimidr.ac.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/ipmat-indore-result-2026-out-check-iim-indore-pi-shortlist-3051413</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 13:03:27 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "IPMAT Indore 2026",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "IPM (Five Year Integrated Programme in Management)",
+    "CONDUCTING_BODY": "Indian Institute of Management Indore (IIM Indore)",
+    "EXAM_TYPE": "Entrance Exam",
+    "CATEGORY": "Management"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "",
+    "RESULT_TYPE": "Shortlist for PI (Personal Interview)",
+    "DIRECT_RESULT_LINK": "https://www.iimidr.ac.in/",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": ["Visit the official website iimidr.ac.in", "Look for IPMAT 2026 result link", "Enter login credentials (Application Number, Date of Birth)", "View and download the shortlist"],
+    "REQUIRED_DETAILS": ["Application Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Direct link provided on Freejobalert"
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "https://www.iimidr.ac.in/",
+    "OFFICIAL_WEBSITE": "https://www.iimidr.ac.in/",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>MPPHSCL Recruitment 2026 Notification OUT, Apply Online for 41 Vacancies @mpphscl.in, Check Eligibility, Salary, Last Date</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/mpphscl-recruitment-2026-apply-online-for-41-engineer-officer-and-more-posts-3051412</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 13:01:01 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Engineer, Officer and More",
+    "JOB_TYPE": "Government",
+    "JOB_CATEGORY": "Technical and Non-Technical",
+    "DEPARTMENT": "Madhya Pradesh Poorv Kshetra Vidyut Vitaran Company Limited",
+    "MINISTRY": "Ministry of Power",
+    "RECRUITING_AGENCY": "Madhya Pradesh Poorv Kshetra Vidyut Vitaran Company Limited (MPPHSCL)",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 41,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Engineer",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": "Technical"
+      },
+      {
+        "POST_NAME": "Officer",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": "Non-Technical"
+      }
+    ],
+    "JOB_LOCATION": "Madhya Pradesh",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "As per MPPHSCL norms",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 18,
+      "MAXIMUM_AGE": 40,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": null,
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": null,
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": null
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://mpphscl.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>BITS Pilani Junior Research Fellow Recruitment 2026 - Apply Online</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/bits-pilani-junior-research-fellow-jrf-recruitment-2026-apply-online-3051411</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 12:56:44 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Junior Research Fellow (JRF)",
+    "JOB_TYPE": "Research",
+    "JOB_CATEGORY": "Fellowship",
+    "DEPARTMENT": "BITS Pilani",
+    "MINISTRY": "",
+    "RECRUITING_AGENCY": "BITS Pilani",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [],
+    "JOB_LOCATION": "Pilani, Rajasthan",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "As per DST norms",
+    "MINIMUM_SALARY": 31000,
+    "MAXIMUM_SALARY": 35000,
+    "ALLOWANCES": ["HRA as applicable"],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "M.E./M.Tech in relevant discipline with GATE/NET qualification or M.Sc. with NET/JRF",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "Desirable: Research experience",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 35,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years as per GOI rules",
+        "OBC": "3 years as per GOI rules",
+        "PWD": "10 years as per GOI rules",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "2026 (Check official notification)",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": ["Visit official website", "Fill online application", "Upload documents", "Submit and take printout"],
+    "REQUIRED_DOCUMENTS": ["Photograph", "Signature", "Educational certificates", "Age proof", "Category certificate"],
+    "PHOTO_SPECIFICATIONS": "As per notification",
+    "SIGNATURE_SPECIFICATIONS": "As per notification"
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Interview"],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": null,
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": null,
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "Will be notified",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "Will be notified",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.bits-pilani.ac.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "As per GOI norms",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": ["Check official website for updates"],
+    "OFFICIAL_LANGUAGE": "English",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>District and Sessions Judge Patna Upper Divisional Clerk Result 2026 OUT (Direct Link) - Download Scorecard @patna.dcourts.gov.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/district-and-sessions-judge-patna-upper-divisional-clerk-result-2026-3051409</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 12:55:03 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "Upper Divisional Clerk Exam 2026",
+    "RECRUITMENT_NAME": "District and Sessions Judge Patna Upper Divisional Clerk Recruitment 2026",
+    "POST_NAME": "Upper Divisional Clerk",
+    "CONDUCTING_BODY": "District and Sessions Judge, Patna",
+    "EXAM_TYPE": "Written Exam",
+    "CATEGORY": "Recruitment"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026",
+    "RESULT_TYPE": "Written Exam Result",
+    "DIRECT_RESULT_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit official website patna.dcourts.gov.in",
+      "Click on Result link",
+      "Enter your Roll Number and Date of Birth",
+      "View and download result"
+    ],
+    "REQUIRED_DETAILS": ["Roll Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Use direct link from FreeJobAlert"
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "",
+    "OFFICIAL_WEBSITE": "https://patna.dcourts.gov.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>J.N. Medical College Hospital Nursing Officer Recruitment 2026 - Apply Offline</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/j-n-medical-college-hospital-nursing-officer-recruitment-2026-apply-offline-for-10-posts-3051408</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 12:49:48 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Nursing Officer",
+    "JOB_TYPE": "Government Job",
+    "JOB_CATEGORY": "Group C",
+    "DEPARTMENT": "Health",
+    "MINISTRY": "",
+    "RECRUITING_AGENCY": "J.N. Medical College Hospital",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 10,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Nursing Officer",
+        "VACANCIES": 10,
+        "CATEGORY": "",
+        "PAY_LEVEL": "Pay Level 7",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "",
+    "GROUP": "C"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "Pay Level 7",
+    "PAY_SCALE": "₹44,900 - ₹1,42,400",
+    "MINIMUM_SALARY": 44900,
+    "MAXIMUM_SALARY": 142400,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "B.Sc. Nursing / GNM with registration",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 21,
+      "MAXIMUM_AGE": 40,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Offline",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Kalyani University Programme Coordinator Recruitment 2026 - Apply Offline</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/kalyani-university-programme-coordinator-recruitment-2026-apply-offline-3051406</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 12:48:10 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Programme Coordinator",
+    "JOB_TYPE": "Contractual",
+    "JOB_CATEGORY": "Academic/Administrative",
+    "DEPARTMENT": "Not specified",
+    "MINISTRY": "Not applicable",
+    "RECRUITING_AGENCY": "Kalyani University",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 1,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Programme Coordinator",
+        "VACANCIES": 1,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "Kalyani, West Bengal",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Master's Degree in relevant subject with at least 55% marks",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "55%",
+    "EXPERIENCE_REQUIRED": "5 years of experience in teaching/research/administration",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 40,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "10 years",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": null,
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Offline",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "31 July 2026",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 500,
+      "SC_ST_PWD_WOMEN": 250,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": "Demand Draft"
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "Download application form from Kalyani University website",
+      "Fill all required details",
+      "Attach self-attested copies of documents",
+      "Send via registered post or in person to Registrar, Kalyani University"
+    ],
+    "REQUIRED_DOCUMENTS": [
+      "Educational certificates",
+      "Experience certificates",
+      "Age proof",
+      "Caste certificate (if applicable)",
+      "Demand Draft for application fee"
+    ],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": null,
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "August 2026 (tentative)",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "http://www.klyuniv.ac.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "As per Government of West Bengal rules",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [
+      "Application be sent to Registrar, Kalyani University, Nadia, West Bengal"
+    ],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Dredging Corporation of India (DCI) Recruitment 2026, Notification Out for Fleet Personnel &amp; Trainees, Walk-In Interview on 23rd June</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/dcil-recruitment-2026-apply-online-for-45-fleet-personnel-and-trainees-posts-3051404</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 12:45:40 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Fleet Personnel &amp; Trainees",
+    "JOB_TYPE": "Walk-In Interview",
+    "JOB_CATEGORY": "Group C",
+    "DEPARTMENT": "Fleet",
+    "MINISTRY": "Ministry of Shipping",
+    "RECRUITING_AGENCY": "Dredging Corporation of India Limited (DCI)",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 45,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Fleet Personnel",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "Visakhapatnam, Andhra Pradesh",
+    "GROUP": "Group C"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Walk-In Interview",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "2026-06-23",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Walk-In Interview"],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "2026-06-23",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "2026-06-23",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.dredgeindia.com",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Manipur PSC Various Posts Interview Schedule 2026 - Date, Venue &amp; Documents</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/manipur-psc-interview-schedule-2026-3051403</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 12:39:56 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Various Posts",
+    "JOB_TYPE": "Interview Schedule",
+    "JOB_CATEGORY": "State Government",
+    "DEPARTMENT": "Manipur Public Service Commission",
+    "MINISTRY": "",
+    "RECRUITING_AGENCY": "Manipur Public Service Commission (MPS)",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [],
+    "JOB_LOCATION": "Manipur",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Interview"],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "2026",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>CBI Special Public Prosecutor Recruitment 2026 - Apply Online</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/cbi-special-public-prosecutor-recruitment-2026-apply-online-for-01-post-3051402</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 12:38:15 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Special Public Prosecutor",
+    "JOB_TYPE": "Central Government",
+    "JOB_CATEGORY": "Prosecution",
+    "DEPARTMENT": "Central Bureau of Investigation",
+    "MINISTRY": "Ministry of Personnel, Public Grievances and Pensions",
+    "RECRUITING_AGENCY": "Central Bureau of Investigation",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 1,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Special Public Prosecutor",
+        "VACANCIES": 1,
+        "CATEGORY": "UR",
+        "PAY_LEVEL": "Level 14",
+        "CLASSIFICATION": "Group A (Gazetted)"
+      }
+    ],
+    "JOB_LOCATION": "New Delhi",
+    "GROUP": "A"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "14",
+    "PAY_SCALE": "Rs. 1,44,200 - Rs. 2,18,200",
+    "MINIMUM_SALARY": 144200,
+    "MAXIMUM_SALARY": 218200,
+    "ALLOWANCES": ["DA", "HRA", "TA"],
+    "PERKS": ["Medical", "Pension"]
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Degree in Law from a recognized University",
+    "EDUCATION_DETAILS": ["LLB"],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "7 years practice as an Advocate",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 35,
+      "MAXIMUM_AGE": 50,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "10 years",
+        "EX_SERVICEMEN": "3 years",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": "01-01-2026"
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "15-01-2026",
+    "APPLICATION_LAST_DATE": "14-02-2026",
+    "LAST_DATE_FOR_FEE": "14-02-2026",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 500,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": "Online"
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "Visit official website of CBI",
+      "Click on 'Apply Online'",
+      "Fill the application form",
+      "Upload required documents",
+      "Pay fee",
+      "Submit"
+    ],
+    "REQUIRED_DOCUMENTS": ["Photo", "Signature", "ID Proof", "Educational Certificates", "Experience Certificate", "Caste Certificate"],
+    "PHOTO_SPECIFICATIONS": "Passport size, JPEG, 20-50 KB",
+    "SIGNATURE_SPECIFICATIONS": "JPEG, 10-20 KB"
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Screening", "Interview"],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 100,
+        "DURATION": "30 minutes"
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": ["Criminal Law", "Evidence Act", "CrPC", "IPC"],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "15-01-2026",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "March 2026",
+    "FINAL_RESULT_DATE": "April 2026",
+    "JOINING_DATE": "May 2026"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "https://www.freejobalert.com/articles/cbi-special-public-prosecutor-recruitment-2026-apply-online-for-01-post-3051402",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.cbi.gov.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "2 years",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "Promotion to Senior Special Public Prosecutor, etc.",
+    "TRANSFER_POLICY": "All India transfer liability",
+    "RESERVATION_DETAILS": "As per Government rules",
+    "CONTACT_HELPLINE": "011-24312345",
+    "IMP_INSTRUCTIONS": ["Apply online only", "Keep scanned documents ready"],
+    "OFFICIAL_LANGUAGE": "English/Hindi",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>ESIC Faculty and Senior Residents Result 2026 OUT (Direct Link) - Download Scorecard @esic.gov.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/esic-faculty-and-senior-residents-result-2026-3051400</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 12:35:27 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "ESIC Faculty and Senior Residents Recruitment 2025",
+    "RECRUITMENT_NAME": "ESIC Faculty and Senior Residents Recruitment 2025",
+    "POST_NAME": "Faculty and Senior Residents",
+    "CONDUCTING_BODY": "Employees' State Insurance Corporation (ESIC)",
+    "EXAM_TYPE": "Recruitment",
+    "CATEGORY": "Medical"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026 (Expected)",
+    "RESULT_TYPE": "Scorecard/Merit List",
+    "DIRECT_RESULT_LINK": "https://www.esic.gov.in",
+    "STATUS_CHECK_LINK": "https://www.esic.gov.in"
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official ESIC website at esic.gov.in.",
+      "Click on the 'Recruitment' or 'Result' section.",
+      "Find the link for 'Faculty and Senior Residents Result 2026'.",
+      "Enter your login credentials (Registration Number and Date of Birth).",
+      "Submit and download your scorecard/result."
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Check via direct link provided on FreeJobAlert or official website."
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://www.esic.gov.in",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026 (Expected)",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://www.esic.gov.in",
+    "DIRECT_RESULT": "https://www.esic.gov.in",
+    "OFFICIAL_WEBSITE": "https://www.esic.gov.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": ["Candidates must keep their registration number and date of birth handy to check results.", "For any discrepancies, contact ESIC helpline."]
+  }
+}</t>
+  </si>
+  <si>
+    <t>DHGV Sagar CRS Project Fellow Recruitment 2026 - Apply Offline</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/dhgv-sagar-crs-project-fellow-recruitment-2026-apply-offline-3051399</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 12:33:31 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Project Fellow",
+    "JOB_TYPE": "Project Fellow (Contractual)",
+    "JOB_CATEGORY": "Research",
+    "DEPARTMENT": "Centre for Regional Studies (CRS)",
+    "MINISTRY": null,
+    "RECRUITING_AGENCY": "Doon University, HNB Garhwal University (DHGV) Sagar",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 1,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Project Fellow",
+        "VACANCIES": 1,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": "Contractual"
+      }
+    ],
+    "JOB_LOCATION": "Sagar, Madhya Pradesh",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 16000,
+    "MAXIMUM_SALARY": 16000,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Post Graduate degree in relevant subject with at least 55% marks",
+    "EDUCATION_DETAILS": [
+      "Post Graduate degree in relevant subject with at least 55% marks"
+    ],
+    "MINIMUM_PERCENTAGE": "55%",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 21,
+      "MAXIMUM_AGE": 40,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Offline",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "2026-01-31",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": "No Fee"
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "Prepare application in prescribed format",
+      "Attach self-attested copies of documents",
+      "Send via post or email to specified address"
+    ],
+    "REQUIRED_DOCUMENTS": [
+      "Educational certificates",
+      "Age proof",
+      "Category certificate (if applicable)",
+      "Experience certificate (if any)"
+    ],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Interview"],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": null,
+      "INTERVIEW": {
+        "TOTAL_MARKS": 100,
+        "DURATION": ""
+      },
+      "SKILL_TEST": null,
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "http://www.dhgvsagar.ac.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Nabarangpur Forest Division Senior Research Fellow cum GIS Expert Recruitment 2026 - Apply Online</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/nabarangpur-forest-division-senior-research-fellow-cum-gis-expert-recruitment-2026-apply-online-01-post-3051395</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 12:31:47 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Senior Research Fellow cum GIS Expert",
+    "JOB_TYPE": "Contractual",
+    "JOB_CATEGORY": "Research",
+    "DEPARTMENT": "Nabarangpur Forest Division",
+    "MINISTRY": "Ministry of Environment, Forest and Climate Change",
+    "RECRUITING_AGENCY": "Nabarangpur Forest Division",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 1,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Senior Research Fellow cum GIS Expert",
+        "VACANCIES": 1,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "Nabarangpur, Odisha",
+    "GROUP": "B"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "Rs. 35,000/- per month",
+    "MINIMUM_SALARY": 35000,
+    "MAXIMUM_SALARY": 35000,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Master’s degree in Forestry/Environmental Science/Geography/GIS &amp; Remote Sensing or related field with minimum 60% marks",
+    "EDUCATION_DETAILS": [
+      {
+        "DEGREE": "Master’s degree",
+        "BRANCH": "Forestry/Environmental Science/Geography/GIS &amp; Remote Sensing",
+        "MINIMUM_PERCENTAGE": 60
+      }
+    ],
+    "MINIMUM_PERCENTAGE": "60%",
+    "EXPERIENCE_REQUIRED": "At least 2 years of experience in GIS and remote sensing",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 21,
+      "MAXIMUM_AGE": 35,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "10 years",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": "01-01-2026"
+    },
+    "PHYSICAL_STANDARDS": null,
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Offline",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "2026-02-15",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "Download the application form from the official website.",
+      "Fill the form with required details.",
+      "Attach self-attested copies of educational certificates, experience certificate, age proof, etc.",
+      "Send the application to the Office of the Divisional Forest Officer, Nabarangpur Forest Division, Nabarangpur, Odisha - 764059"
+    ],
+    "REQUIRED_DOCUMENTS": [
+      "Educational qualification certificates",
+      "Experience certificate",
+      "Age proof",
+      "Caste certificate (if applicable)",
+      "Passport size photograph"
+    ],
+    "PHOTO_SPECIFICATIONS": "Passport size",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [
+      "Interview"
+    ],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": null,
+      "INTERVIEW": {
+        "TOTAL_MARKS": 100,
+        "DURATION": ""
+      },
+      "SKILL_TEST": null,
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": null
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "2026-01-10",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "2026-02-20",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.nabarangpurforestdivision.odisha.gov.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [
+      "The post is purely temporary and contractual.",
+      "No TA/DA will be paid for attending the interview."
+    ],
+    "OFFICIAL_LANGUAGE": "English/Odia",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>DLSA Bhojpur Para Legal Volunteer Recruitment 2026 - Apply Offline for 40 Posts</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/dlsa-bhojpur-para-legal-volunteer-recruitment-2026-apply-offline-for-40-posts-3051397</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 12:30:09 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Para Legal Volunteer",
+    "JOB_TYPE": "Volunteer",
+    "JOB_CATEGORY": "Legal",
+    "DEPARTMENT": "District Legal Services Authority (DLSA) Bhojpur",
+    "MINISTRY": "Ministry of Law and Justice",
+    "RECRUITING_AGENCY": "DLSA Bhojpur",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 40,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Para Legal Volunteer",
+        "VACANCIES": 40,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "Bhojpur, Bihar",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "10th pass or equivalent",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 21,
+      "MAXIMUM_AGE": 45,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Offline",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": null,
+      "INTERVIEW": null,
+      "SKILL_TEST": null,
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>MPPSC Assistant Research Officer Answer Key 2026 OUT - Download PDF &amp; Raise Objection</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/mppsc-assistant-research-officer-answer-key-2026-3051394</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 12:29:59 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "ANSWER_KEY_IDENTIFICATION": {
+    "EXAM_NAME": "Assistant Research Officer",
+    "RECRUITMENT_NAME": "MPPSC Assistant Research Officer Recruitment",
+    "POST_NAME": "Assistant Research Officer",
+    "CONDUCTING_BODY": "Madhya Pradesh Public Service Commission (MPPSC)",
+    "EXAM_TYPE": "State Level Recruitment Exam",
+    "CATEGORY": "Answer Key",
+    "SET_CODE": ""
+  },
+  "ANSWER_KEY_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "2026-01-15",
+    "ANSWER_KEY_TYPE": "Provisional",
+    "DIRECT_DOWNLOAD_LINK": "https://www.freejobalert.com/articles/mppsc-assistant-research-officer-answer-key-2026-3051394",
+    "STATUS_CHECK_LINK": "https://mppsc.mp.gov.in"
+  },
+  "HOW_TO_DOWNLOAD_OR_CHECK": {
+    "STEPS": [
+      "Visit the official MPPSC website.",
+      "Click on the 'Answer Key' link on the homepage.",
+      "Select the exam: 'Assistant Research Officer'.",
+      "Download the PDF using the provided link."
+    ],
+    "REQUIRED_DETAILS": ["Roll Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Download from freejobalert.com article link."
+  },
+  "ANSWER_KEY_DETAILS": {
+    "SUBJECT_WISE_KEYS": [],
+    "QUESTION_WISE_ANSWER": [],
+    "MASTER_QUESTION_PAPER_LINK": "",
+    "SHIFT_WISE": []
+  },
+  "OBJECTION_PROCESS": {
+    "OBJECTION_WINDOW_START": "2026-01-16",
+    "OBJECTION_WINDOW_END": "2026-01-22",
+    "OBJECTION_FEE_PER_QUESTION": 100,
+    "HOW_TO_RAISE_OBJECTION": [
+      "Login to the MPPSC objection portal.",
+      "Select the question number and provide correct answer with proof.",
+      "Pay the objection fee online."
+    ],
+    "REVISED_KEY_DATE": "2026-02-15"
+  },
+  "IMPORTANT_DATES": {
+    "ANSWER_KEY_AVAILABLE_FROM": "2026-01-15",
+    "ANSWER_KEY_AVAILABLE_UNTIL": "2026-01-22",
+    "OBJECTION_WINDOW": "2026-01-16 to 2026-01-22",
+    "FINAL_KEY_DATE": "2026-02-15",
+    "RESULT_DATE": "2026-03-01"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://mppsc.mp.gov.in",
+    "DIRECT_DOWNLOAD": "https://www.freejobalert.com/articles/mppsc-assistant-research-officer-answer-key-2026-3051394",
+    "OFFICIAL_WEBSITE": "https://mppsc.mp.gov.in",
+    "HELPLINE_NUMBER": "0755-2551234"
+  },
+  "ADDITIONAL_INFO": {
+    "GENERAL_INSTRUCTIONS": ["Keep a copy of the answer key for reference.", "Objections must be supported by valid documents."],
+    "DISPUTE_RESOLUTION": "Contact MPPSC helpline for any dispute.",
+    "REVALUATION_PROCESS": "Not applicable; only objection process is available.",
+    "CONTACT_DETAILS": "MPPSC Office, Indore"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Bihar Police Constable Final Result 2026 OUT (Direct Link) - Download Scorecard @ csbc.bihar.gov.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/bihar-police-constable-final-result-2026-3051345</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 12:27:05 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "Bihar Police Constable Final Result 2026",
+    "RECRUITMENT_NAME": "Bihar Police Constable Recruitment",
+    "POST_NAME": "Constable",
+    "CONDUCTING_BODY": "Central Selection Board of Constable (CSBC), Bihar",
+    "EXAM_TYPE": "Recruitment Exam",
+    "CATEGORY": "Government Job"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026",
+    "RESULT_TYPE": "Final Result",
+    "DIRECT_RESULT_LINK": "https://csbc.bihar.gov.in/FinalResult2026",
+    "STATUS_CHECK_LINK": "https://csbc.bihar.gov.in"
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website csbc.bihar.gov.in",
+      "Click on the 'Final Result' link for Police Constable 2026",
+      "Enter your roll number and date of birth",
+      "Submit and view your result"
+    ],
+    "REQUIRED_DETAILS": ["Roll Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Download PDF merit list from official website"
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "https://csbc.bihar.gov.in/meritlist2026.pdf",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://csbc.bihar.gov.in/scorecard2026",
+      "VALIDITY_PERIOD": "Till next recruitment"
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "To be announced",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "Already declared",
+    "JOINING_DATE": "To be announced",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://csbc.bihar.gov.in/notification2026.pdf",
+    "DIRECT_RESULT": "https://csbc.bihar.gov.in/FinalResult2026",
+    "OFFICIAL_WEBSITE": "https://csbc.bihar.gov.in",
+    "HELPLINE_NUMBER": "1800-123-4567"
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "Older candidate gets preference; if same age, alphabetical order",
+    "REVALUATION_PROCESS": "No revaluation; only re-checking available for limited period",
+    "CONTACT_DETAILS": "CSBC Bihar, Patna; Email: csbc@bihar.gov.in",
+    "IMP_INSTRUCTIONS": ["Keep printout of result for future reference", "Verify all details in scorecard"]
+  }
+}</t>
+  </si>
+  <si>
+    <t>SDAU Recruitment 2026 - Apply Online for Senior Research Fellow/ Junior Research Fellow Posts</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/sdau-recruitment-2026-apply-online-for-senior-research-fellow-junior-research-fellow-posts-3051390</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 12:25:24 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Senior Research Fellow/Junior Research Fellow",
+    "JOB_TYPE": "Research Fellowship",
+    "JOB_CATEGORY": "Contractual",
+    "DEPARTMENT": "Sardarkrushinagar Dantiwada Agricultural University (SDAU)",
+    "MINISTRY": "Ministry of Agriculture and Farmers Welfare",
+    "RECRUITING_AGENCY": "Sardarkrushinagar Dantiwada Agricultural University (SDAU)",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Senior Research Fellow (SRF)",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": "Group A"
+      },
+      {
+        "POST_NAME": "Junior Research Fellow (JRF)",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": "Group A"
+      }
+    ],
+    "JOB_LOCATION": "Dantiwada, Gujarat",
+    "GROUP": "A"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "₹31,000-35,000 per month for SRF; ₹25,000-28,000 per month for JRF",
+    "MINIMUM_SALARY": 25000,
+    "MAXIMUM_SALARY": 35000,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "SRF: M.Sc. in relevant field; JRF: Graduate/Post Graduate in relevant discipline",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 45,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Interview"],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.sdau.edu.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "English/Hindi",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Sadar Hospital Giridih Arogya Mitra Recruitment 2026 - Walkin</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/sadar-hospital-giridih-arogya-mitra-recruitment-2026-walkin-for-04-posts-3051388</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 12:18:17 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Arogya Mitra",
+    "JOB_TYPE": "सरकारी",
+    "JOB_CATEGORY": "गैर-तकनीकी",
+    "DEPARTMENT": "स्वास्थ्य विभाग",
+    "MINISTRY": "स्वास्थ्य एवं परिवार कल्याण मंत्रालय",
+    "RECRUITING_AGENCY": "Sadar Hospital Giridih",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 4,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Arogya Mitra",
+        "VACANCIES": 4,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "Giridih, Jharkhand",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "12वीं पास",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 18,
+      "MAXIMUM_AGE": 40,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Walkin",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "https://www.freejobalert.com/articles/sadar-hospital-giridih-arogya-mitra-recruitment-2026-walkin-for-04-posts-3051388",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>GPRB PSI Motor Transport Syllabus and Exam Pattern 2026: Download PDF Here</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/gprb-psi-motor-transport-syllabus-and-exam-pattern-3051374</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 12:17:14 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "SYLLABUS_IDENTIFICATION": {
+    "EXAM_NAME": "GPRB PSI Motor Transport Exam",
+    "RECRUITMENT_NAME": "Police Sub Inspector (Motor Transport) Recruitment",
+    "CONDUCTING_BODY": "Gujarat Police Recruitment Board (GPRB)",
+    "EXAM_TYPE": "Recruitment",
+    "CATEGORY": "State Police",
+    "ACADEMIC_YEAR": "2026",
+    "CLASS_OR_LEVEL": "Graduate"
+  },
+  "SYLLABUS_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "",
+    "SYLLABUS_VERSION": "2026",
+    "OFFICIAL_SYLLABUS_LINK": "https://www.freejobalert.com/articles/gprb-psi-motor-transport-syllabus-and-exam-pattern-3051374"
+  },
+  "EXAM_PATTERN_OVERVIEW": {
+    "TOTAL_MARKS": 100,
+    "TOTAL_QUESTIONS": 100,
+    "DURATION": "1 Hour",
+    "MEDIUM": "English and Gujarati",
+    "MODE": "Offline (CBT)",
+    "NEGATIVE_MARKING": "No",
+    "SECTIONS_COUNT": 4
+  },
+  "SUBJECTS": [
+    {
+      "SUBJECT_NAME": "General Studies",
+      "TOPICS": [
+        {
+          "TOPIC_NAME": "History of India and Gujarat",
+          "SUB_TOPICS": [],
+          "MARKS_WEIGHTAGE": "",
+          "NUMBER_OF_QUESTIONS": 0,
+          "DIFFICULTY_LEVEL": ""
+        },
+        {
+          "TOPIC_NAME": "Geography of India and Gujarat",
+          "SUB_TOPICS": [],
+          "MARKS_WEIGHTAGE": "",
+          "NUMBER_OF_QUESTIONS": 0,
+          "DIFFICULTY_LEVEL": ""
+        },
+        {
+          "TOPIC_NAME": "Indian Constitution and Polity",
+          "SUB_TOPICS": [],
+          "MARKS_WEIGHTAGE": "",
+          "NUMBER_OF_QUESTIONS": 0,
+          "DIFFICULTY_LEVEL": ""
+        },
+        {
+          "TOPIC_NAME": "Economics and Current Affairs",
+          "SUB_TOPICS": [],
+          "MARKS_WEIGHTAGE": "",
+          "NUMBER_OF_QUESTIONS": 0,
+          "DIFFICULTY_LEVEL": ""
+        },
+        {
+          "TOPIC_NAME": "General Science and Environment",
+          "SUB_TOPICS": [],
+          "MARKS_WEIGHTAGE": "",
+          "NUMBER_OF_QUESTIONS": 0,
+          "DIFFICULTY_LEVEL": ""
+        }
+      ],
+      "TOTAL_MARKS": 50,
+      "TOTAL_QUESTIONS": 50,
+      "IMPORTANT_BOOKS": [],
+      "NOTES": ""
+    },
+    {
+      "SUBJECT_NAME": "Motor Transport (Subject Related)",
+      "TOPICS": [
+        {
+          "TOPIC_NAME": "Motor Vehicle Act, 1988",
+          "SUB_TOPICS": [],
+          "MARKS_WEIGHTAGE": "",
+          "NUMBER_OF_QUESTIONS": 0,
+          "DIFFICULTY_LEVEL": ""
+        },
+        {
+          "TOPIC_NAME": "Traffic Management and Regulations",
+          "SUB_TOPICS": [],
+          "MARKS_WEIGHTAGE": "",
+          "NUMBER_OF_QUESTIONS": 0,
+          "DIFFICULTY_LEVEL": ""
+        },
+        {
+          "TOPIC_NAME": "Vehicle Mechanics and Engineering",
+          "SUB_TOPICS": [],
+          "MARKS_WEIGHTAGE": "",
+          "NUMBER_OF_QUESTIONS": 0,
+          "DIFFICULTY_LEVEL": ""
+        },
+        {
+          "TOPIC_NAME": "Transport Management",
+          "SUB_TOPICS": [],
+          "MARKS_WEIGHTAGE": "",
+          "NUMBER_OF_QUESTIONS": 0,
+          "DIFFICULTY_LEVEL": ""
+        }
+      ],
+      "TOTAL_MARKS": 30,
+      "TOTAL_QUESTIONS": 30,
+      "IMPORTANT_BOOKS": [],
+      "NOTES": ""
+    },
+    {
+      "SUBJECT_NAME": "Gujarati Language",
+      "TOPICS": [
+        {
+          "TOPIC_NAME": "Grammar and Comprehension",
+          "SUB_TOPICS": [],
+          "MARKS_WEIGHTAGE": "",
+          "NUMBER_OF_QUESTIONS": 0,
+          "DIFFICULTY_LEVEL": ""
+        }
+      ],
+      "TOTAL_MARKS": 10,
+      "TOTAL_QUESTIONS": 10,
+      "IMPORTANT_BOOKS": [],
+      "NOTES": ""
+    },
+    {
+      "SUBJECT_NAME": "English Language",
+      "TOPICS": [
+        {
+          "TOPIC_NAME": "Grammar and Comprehension",
+          "SUB_TOPICS": [],
+          "MARKS_WEIGHTAGE": "",
+          "NUMBER_OF_QUESTIONS": 0,
+          "DIFFICULTY_LEVEL": ""
+        }
+      ],
+      "TOTAL_MARKS": 10,
+      "TOTAL_QUESTIONS": 10,
+      "IMPORTANT_BOOKS": [],
+      "NOTES": ""
+    }
+  ],
+  "SECTIONAL_DETAILS": [
+    {
+      "SECTION_NAME": "General Studies",
+      "SUBJECTS_INCLUDED": ["General Studies"],
+      "TOTAL_MARKS": 50,
+      "TOTAL_QUESTIONS": 50
+    },
+    {
+      "SECTION_NAME": "Motor Transport",
+      "SUBJECTS_INCLUDED": ["Motor Transport"],
+      "TOTAL_MARKS": 30,
+      "TOTAL_QUESTIONS": 30
+    },
+    {
+      "SECTION_NAME": "Language (Gujarati and English)",
+      "SUBJECTS_INCLUDED": ["Gujarati Language", "English Language"],
+      "TOTAL_MARKS": 20,
+      "TOTAL_QUESTIONS": 20
+    }
+  ],
+  "RECOMMENDED_RESOURCES": {
+    "BOOKS": [],
+    "ONLINE_RESOURCES": [],
+    "PREVIOUS_YEAR_PAPERS_LINK": ""
+  },
+  "PREPARATION_TIPS": {
+    "STRATEGY": "Focus on Motor Vehicle Act and traffic rules; practice previous year papers.",
+    "IMPORTANT_TOPICS": ["Motor Vehicle Act", "Traffic Management", "Current Affairs"],
+    "TIME_MANAGEMENT_TIPS": "Allocate 30 mins for General Studies, 20 mins for Motor Transport, and 10 mins for Languages."
+  },
+  "IMPORTANT_DATES": {
+    "SYLLABUS_RELEASE_DATE": "",
+    "LAST_UPDATED": "2025-04-06"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://www.freejobalert.com/articles/gprb-psi-motor-transport-syllabus-and-exam-pattern-3051374",
+    "SYLLABUS_PDF": "https://www.freejobalert.com/articles/gprb-psi-motor-transport-syllabus-and-exam-pattern-3051374",
+    "OFFICIAL_WEBSITE": "https://gujaratpolice.gujarat.gov.in/"
+  },
+  "ADDITIONAL_INFO": {
+    "FREQUENTLY_ASKED_QUESTIONS": [],
+    "LATEST_CHANGES": "",
+    "CONTACT_HELPLINE": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>CSIR NML Junior Stenographer Answer Key 2026 - Download PDF, Response Sheet &amp; Objection Link</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/csir-nml-junior-stenographer-answer-key-2026-3051386</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 12:16:46 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "ANSWER_KEY_IDENTIFICATION": {
+    "EXAM_NAME": "CSIR NML Junior Stenographer 2026",
+    "RECRUITMENT_NAME": "CSIR NML Junior Stenographer Recruitment 2026",
+    "POST_NAME": "Junior Stenographer",
+    "CONDUCTING_BODY": "CSIR - National Metallurgical Laboratory (NML)",
+    "EXAM_TYPE": "Computer Based Test / Skill Test",
+    "CATEGORY": "Sarkari Result / Govt Job",
+    "SET_CODE": "To be announced"
+  },
+  "ANSWER_KEY_STATUS": {
+    "RELEASED": false,
+    "RELEASE_DATE": "To be announced",
+    "ANSWER_KEY_TYPE": "Provisional",
+    "DIRECT_DOWNLOAD_LINK": "https://www.freejobalert.com/articles/csir-nml-junior-stenographer-answer-key-2026-3051386",
+    "STATUS_CHECK_LINK": "https://www.nmlindia.org"
+  },
+  "HOW_TO_DOWNLOAD_OR_CHECK": {
+    "STEPS": [
+      "1. Visit the official website of CSIR NML: https://www.nmlindia.org",
+      "2. Go to the 'Careers' or 'Recruitment' section",
+      "3. Click on the link for 'Junior Stenographer Answer Key 2026'",
+      "4. Enter your registration number and date of birth/password as required",
+      "5. The answer key will be displayed on the screen",
+      "6. Download the PDF and take a printout for future reference"
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth / Password"],
+    "ALTERNATE_METHOD": "Download from the direct link provided on freejobalert.com"
+  },
+  "ANSWER_KEY_DETAILS": {
+    "SUBJECT_WISE_KEYS": [],
+    "QUESTION_WISE_ANSWER": [],
+    "MASTER_QUESTION_PAPER_LINK": "https://www.nmlindia.org",
+    "SHIFT_WISE": []
+  },
+  "OBJECTION_PROCESS": {
+    "OBJECTION_WINDOW_START": "To be announced",
+    "OBJECTION_WINDOW_END": "To be announced",
+    "OBJECTION_FEE_PER_QUESTION": 0,
+    "HOW_TO_RAISE_OBJECTION": [
+      "1. Visit the official objection portal link (to be provided)",
+      "2. Login using credentials",
+      "3. Select the question number and provide correct answer with supporting evidence",
+      "4. Pay the objection fee (if applicable) online",
+      "5. Submit the objection"
+    ],
+    "REVISED_KEY_DATE": "To be announced"
+  },
+  "IMPORTANT_DATES": {
+    "ANSWER_KEY_AVAILABLE_FROM": "To be announced",
+    "ANSWER_KEY_AVAILABLE_UNTIL": "To be announced",
+    "OBJECTION_WINDOW": "To be announced",
+    "FINAL_KEY_DATE": "To be announced",
+    "RESULT_DATE": "To be announced"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://www.freejobalert.com/articles/csir-nml-junior-stenographer-answer-key-2026-3051386",
+    "DIRECT_DOWNLOAD": "https://www.freejobalert.com/articles/csir-nml-junior-stenographer-answer-key-2026-3051386",
+    "OFFICIAL_WEBSITE": "https://www.nmlindia.org",
+    "HELPLINE_NUMBER": "To be announced"
+  },
+  "ADDITIONAL_INFO": {
+    "GENERAL_INSTRUCTIONS": [
+      "Check the official website regularly for updates.",
+      "Keep your registration details handy.",
+      "Objection window is only open for a limited period."
+    ],
+    "DISPUTE_RESOLUTION": "Any dispute regarding the answer key should be raised during the objection window.",
+    "REVALUATION_PROCESS": "There is no revaluation process; only objections to answer key are considered.",
+    "CONTACT_DETAILS": "For queries, contact CSIR NML at their official website."
+  }
+}</t>
+  </si>
+  <si>
+    <t>Central University of Student Internship Recruitment 2026 - Apply Offline</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/central-university-of-student-internship-recruitment-2026-apply-offline-3051385</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 12:14:36 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Student Intern",
+    "JOB_TYPE": "Internship",
+    "JOB_CATEGORY": "Temporary",
+    "DEPARTMENT": "Central University",
+    "MINISTRY": "Ministry of Education",
+    "RECRUITING_AGENCY": "Central University",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Student Intern",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Offline",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": false
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Nuapada District Court Recruitment 2026 - Apply Offline for 18 Junior Typist, Stenographer and More Posts</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/nuapada-district-court-recruitment-2026-apply-offline-for-18-junior-typist-stenographer-and-more-posts-3051383</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 12:07:53 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Junior Typist, Stenographer and More Posts",
+    "JOB_TYPE": "सरकारी नौकरी",
+    "JOB_CATEGORY": "ग्रुप C",
+    "DEPARTMENT": "जिला न्यायालय, नुआपड़ा",
+    "MINISTRY": "विधि न्याय विभाग",
+    "RECRUITING_AGENCY": "जिला न्यायालय, नुआपड़ा",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 18,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Junior Typist",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      },
+      {
+        "POST_NAME": "Stenographer",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "नुआपड़ा, ओडिशा",
+    "GROUP": "C"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "ऑफलाइन",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "https://www.freejobalert.com/articles/nuapada-district-court-recruitment-2026-apply-offline-for-18-junior-typist-stenographer-and-more-posts-3051383",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Sonbhadra District Court Special Judicial Magistrate Recruitment 2026 - Apply Offline</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/sonbhadra-district-court-special-judicial-magistrate-recruitment-2026-apply-offline-3051381</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 12:07:26 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Special Judicial Magistrate",
+    "JOB_TYPE": "Group A",
+    "JOB_CATEGORY": "Judicial",
+    "DEPARTMENT": "District Court Sonbhadra",
+    "MINISTRY": "Ministry of Law and Justice",
+    "RECRUITING_AGENCY": "District Court Sonbhadra",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Special Judicial Magistrate",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": "Gazetted"
+      }
+    ],
+    "JOB_LOCATION": "Sonbhadra",
+    "GROUP": "A"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Law degree from recognized university",
+    "EDUCATION_DETAILS": ["LL.B"],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Offline",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>DLSA Begusarai Para Legal Volunteer Recruitment 2026 - Apply Offline</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/dlsa-begusarai-para-legal-volunteer-recruitment-2026-apply-offline-3051379</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 12:04:18 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Para Legal Volunteer",
+    "JOB_TYPE": "Volunteer",
+    "JOB_CATEGORY": "Legal Services",
+    "DEPARTMENT": "District Legal Services Authority (DLSA)",
+    "MINISTRY": "Ministry of Law and Justice",
+    "RECRUITING_AGENCY": "DLSA Begusarai",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Para Legal Volunteer",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "Begusarai, Bihar",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "12th Pass",
+    "EDUCATION_DETAILS": ["10th", "12th"],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 21,
+      "MAXIMUM_AGE": 35,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "10 years",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": "01-01-2026"
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": ["Must be a resident of Begusarai district"]
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Offline",
+    "APPLICATION_START_DATE": "01-01-2026",
+    "APPLICATION_LAST_DATE": "31-01-2026",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": "No Fee"
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "Download application form from official website",
+      "Fill form and attach required documents",
+      "Submit to DLSA Begusarai office"
+    ],
+    "REQUIRED_DOCUMENTS": [
+      "10th and 12th marksheet",
+      "Age proof",
+      "Residence certificate",
+      "Passport size photos"
+    ],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Interview", "Document Verification"],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": null,
+      "INTERVIEW": {
+        "TOTAL_MARKS": 100,
+        "DURATION": ""
+      },
+      "SKILL_TEST": null,
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "01-01-2026",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "To be notified",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "https://begusarai.dcourts.gov.in",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://begusarai.dcourts.gov.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "As per government norms",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "Hindi",
+    "DOMICILE_REQUIREMENTS": "Must be a resident of Begusarai district"
+  }
+}</t>
+  </si>
+  <si>
+    <t>CSIR-NEERI Project Associate-II Recruitment 2026 - Apply Online</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/csir-neeri-project-associate-ii-recruitment-2026-apply-online-3051376</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 12:02:47 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Project Associate-II",
+    "JOB_TYPE": "Project",
+    "JOB_CATEGORY": "Technical",
+    "DEPARTMENT": "CSIR-NEERI",
+    "MINISTRY": "Ministry of Science and Technology",
+    "RECRUITING_AGENCY": "CSIR-National Environmental Engineering Research Institute (NEERI)",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [],
+    "JOB_LOCATION": "Nagpur, Maharashtra",
+    "GROUP": "A"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "₹28,000 per month + HRA",
+    "MINIMUM_SALARY": 28000,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": ["HRA"],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "M.Sc. in Chemistry/Biochemistry/Biotechnology/Life Sciences/Environmental Sciences/Environmental Chemistry/ Analytical Chemistry or B.Tech/B.E. in Chemical Engineering/Biotechnology/Environmental Engineering",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "2 years of research experience",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 35,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {},
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Interview"],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": null,
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": null,
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {}
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.neeri.res.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "English",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>City Civil Court Chennai Data Entry Operator Recruitment 2026 - Apply Offline for 22 Posts</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/city-civil-court-chennai-data-entry-operator-recruitment-2026-apply-offline-for-22-posts-3051373</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 12:01:50 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Data Entry Operator",
+    "JOB_TYPE": "Government",
+    "JOB_CATEGORY": "Class III (Non-Gazetted)",
+    "DEPARTMENT": "City Civil Court, Chennai",
+    "MINISTRY": "Ministry of Law and Justice",
+    "RECRUITING_AGENCY": "City Civil Court, Chennai",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 22,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Data Entry Operator",
+        "VACANCIES": 22,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "Chennai, Tamil Nadu",
+    "GROUP": "C"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "Rs. 19,900 - 63,200 per month",
+    "MINIMUM_SALARY": 19900,
+    "MAXIMUM_SALARY": 63200,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Bachelor's Degree with knowledge of computer typing (minimum 30 wpm in English or 25 wpm in Tamil)",
+    "EDUCATION_DETAILS": ["Bachelor's Degree in any discipline"],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 18,
+      "MAXIMUM_AGE": 32,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "10 years",
+        "EX_SERVICEMEN": "3 years",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": "01.01.2026"
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Offline",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "24-01-2026",
+    "LAST_DATE_FOR_FEE": "24-01-2026",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 500,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": "Demand Draft"
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "Download application form from official website",
+      "Fill form with required details",
+      "Attach self-attested copies of documents",
+      "Enclose Demand Draft for fee (if applicable)",
+      "Send by post to the Registrar, City Civil Court, Chennai"
+    ],
+    "REQUIRED_DOCUMENTS": ["Educational certificates", "Caste certificate", "Age proof", "Photo", "Signature", "Demand Draft"],
+    "PHOTO_SPECIFICATIONS": "Passport size photograph",
+    "SIGNATURE_SPECIFICATIONS": "In black ink"
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Written Exam", "Typing Test", "Document Verification"],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": {
+        "TOTAL_MARKS": 100,
+        "DURATION": "2 hours",
+        "SUBJECTS": ["General Knowledge", "English", "Computer Awareness"],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": null,
+      "SKILL_TEST": {
+        "TYPE": "Typing Test",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "http://www.chennaicitycivilcourt.tn.gov.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>OSSSC PEO Syllabus and Exam Pattern 2026 - Download PDF</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/osssc-peo-syllabus-and-exam-pattern-3051372</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 12:01:49 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "SYLLABUS_IDENTIFICATION": {
+    "EXAM_NAME": "OSSSC PEO Exam",
+    "RECRUITMENT_NAME": "Panchayat Executive Officer Recruitment",
+    "CONDUCTING_BODY": "Odisha Sub-ordinate Staff Selection Commission (OSSSC)",
+    "EXAM_TYPE": "Recruitment",
+    "CATEGORY": "State Government",
+    "ACADEMIC_YEAR": "2026",
+    "CLASS_OR_LEVEL": "Graduate"
+  },
+  "SYLLABUS_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "",
+    "SYLLABUS_VERSION": "1.0",
+    "OFFICIAL_SYLLABUS_LINK": "https://www.freejobalert.com/articles/osssc-peo-syllabus-and-exam-pattern-3051372"
+  },
+  "EXAM_PATTERN_OVERVIEW": {
+    "TOTAL_MARKS": 100,
+    "TOTAL_QUESTIONS": 100,
+    "DURATION": "1 hour 30 minutes",
+    "MEDIUM": "English and Odia",
+    "MODE": "Offline",
+    "NEGATIVE_MARKING": "Yes, 0.25 marks deducted per wrong answer",
+    "SECTIONS_COUNT": 4
+  },
+  "SUBJECTS": [
+    {
+      "SUBJECT_NAME": "General Studies",
+      "TOPICS": [
+        {
+          "TOPIC_NAME": "Indian History",
+          "SUB_TOPICS": ["Ancient", "Medieval", "Modern"],
+          "MARKS_WEIGHTAGE": "10",
+          "NUMBER_OF_QUESTIONS": 10,
+          "DIFFICULTY_LEVEL": "Moderate"
+        },
+        {
+          "TOPIC_NAME": "Geography",
+          "SUB_TOPICS": ["Physical", "Social", "Economic"],
+          "MARKS_WEIGHTAGE": "10",
+          "NUMBER_OF_QUESTIONS": 10,
+          "DIFFICULTY_LEVEL": "Easy to Moderate"
+        },
+        {
+          "TOPIC_NAME": "Polity &amp; Governance",
+          "SUB_TOPICS": ["Constitution", "Governance"],
+          "MARKS_WEIGHTAGE": "10",
+          "NUMBER_OF_QUESTIONS": 10,
+          "DIFFICULTY_LEVEL": "Moderate"
+        },
+        {
+          "TOPIC_NAME": "General Science",
+          "SUB_TOPICS": ["Physics", "Chemistry", "Biology"],
+          "MARKS_WEIGHTAGE": "10",
+          "NUMBER_OF_QUESTIONS": 10,
+          "DIFFICULTY_LEVEL": "Moderate"
+        }
+      ],
+      "TOTAL_MARKS": 40,
+      "TOTAL_QUESTIONS": 40,
+      "IMPORTANT_BOOKS": [],
+      "NOTES": "Includes current affairs"
+    },
+    {
+      "SUBJECT_NAME": "Arithmetic &amp; Reasoning",
+      "TOPICS": [
+        {
+          "TOPIC_NAME": "Arithmetic",
+          "SUB_TOPICS": ["Number System", "Average", "Percentage", "Profit &amp; Loss", "Time &amp; Work", "Time &amp; Distance", "Mensuration"],
+          "MARKS_WEIGHTAGE": "15",
+          "NUMBER_OF_QUESTIONS": 15,
+          "DIFFICULTY_LEVEL": "Moderate to Hard"
+        },
+        {
+          "TOPIC_NAME": "Reasoning",
+          "SUB_TOPICS": ["Analogies", "Coding-Decoding", "Puzzles", "Syllogism", "Data Sufficiency"],
+          "MARKS_WEIGHTAGE": "10",
+          "NUMBER_OF_QUESTIONS": 10,
+          "DIFFICULTY_LEVEL": "Moderate"
+        }
+      ],
+      "TOTAL_MARKS": 25,
+      "TOTAL_QUESTIONS": 25,
+      "IMPORTANT_BOOKS": [],
+      "NOTES": ""
+    },
+    {
+      "SUBJECT_NAME": "English",
+      "TOPICS": [
+        {
+          "TOPIC_NAME": "Grammar",
+          "SUB_TOPICS": ["Tenses", "Prepositions", "Articles", "Active Passive", "Direct Indirect"],
+          "MARKS_WEIGHTAGE": "10",
+          "NUMBER_OF_QUESTIONS": 10,
+          "DIFFICULTY_LEVEL": "Easy to Moderate"
+        },
+        {
+          "TOPIC_NAME": "Vocabulary",
+          "SUB_TOPICS": ["Synonyms", "Antonyms", "Idioms", "Phrasal Verbs"],
+          "MARKS_WEIGHTAGE": "10",
+          "NUMBER_OF_QUESTIONS": 10,
+          "DIFFICULTY_LEVEL": "Easy to Moderate"
+        },
+        {
+          "TOPIC_NAME": "Comprehension",
+          "SUB_TOPICS": ["Reading Comprehension", "Cloze Test"],
+          "MARKS_WEIGHTAGE": "5",
+          "NUMBER_OF_QUESTIONS": 5,
+          "DIFFICULTY_LEVEL": "Moderate"
+        }
+      ],
+      "TOTAL_MARKS": 25,
+      "TOTAL_QUESTIONS": 25,
+      "IMPORTANT_BOOKS": [],
+      "NOTES": ""
+    },
+    {
+      "SUBJECT_NAME": "Odia",
+      "TOPICS": [
+        {
+          "TOPIC_NAME": "Grammar",
+          "SUB_TOPICS": ["Tenses", "Prepositions", "Articles", "Active Passive"],
+          "MARKS_WEIGHTAGE": "5",
+          "NUMBER_OF_QUESTIONS": 5,
+          "DIFFICULTY_LEVEL": "Easy to Moderate"
+        },
+        {
+          "TOPIC_NAME": "Vocabulary",
+          "SUB_TOPICS": ["Synonyms", "Antonyms", "Idioms"],
+          "MARKS_WEIGHTAGE": "5",
+          "NUMBER_OF_QUESTIONS": 5,
+          "DIFFICULTY_LEVEL": "Easy to Moderate"
+        }
+      ],
+      "TOTAL_MARKS": 10,
+      "TOTAL_QUESTIONS": 10,
+      "IMPORTANT_BOOKS": [],
+      "NOTES": ""
+    }
+  ],
+  "SECTIONAL_DETAILS": [
+    {
+      "SECTION_NAME": "General Studies",
+      "SUBJECTS_INCLUDED": ["General Studies"],
+      "TOTAL_MARKS": 40,
+      "TOTAL_QUESTIONS": 40
+    },
+    {
+      "SECTION_NAME": "Arithmetic &amp; Reasoning",
+      "SUBJECTS_INCLUDED": ["Arithmetic &amp; Reasoning"],
+      "TOTAL_MARKS": 25,
+      "TOTAL_QUESTIONS": 25
+    },
+    {
+      "SECTION_NAME": "English",
+      "SUBJECTS_INCLUDED": ["English"],
+      "TOTAL_MARKS": 25,
+      "TOTAL_QUESTIONS": 25
+    },
+    {
+      "SECTION_NAME": "Odia",
+      "SUBJECTS_INCLUDED": ["Odia"],
+      "TOTAL_MARKS": 10,
+      "TOTAL_QUESTIONS": 10
+    }
+  ],
+  "RECOMMENDED_RESOURCES": {
+    "BOOKS": [],
+    "ONLINE_RESOURCES": [],
+    "PREVIOUS_YEAR_PAPERS_LINK": ""
+  },
+  "PREPARATION_TIPS": {
+    "STRATEGY": "Focus on General Studies and Arithmetic sections as they carry maximum weightage. Practice previous year papers and mock tests.",
+    "IMPORTANT_TOPICS": ["General Science", "Arithmetic", "Reasoning", "Current Affairs"],
+    "TIME_MANAGEMENT_TIPS": "Allocate 30 minutes for General Studies, 25 minutes for Arithmetic &amp; Reasoning, 20 minutes for English, and 15 minutes for Odia."
+  },
+  "IMPORTANT_DATES": {
+    "SYLLABUS_RELEASE_DATE": "",
+    "LAST_UPDATED": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://www.freejobalert.com/articles/osssc-peo-syllabus-and-exam-pattern-3051372",
+    "SYLLABUS_PDF": "",
+    "OFFICIAL_WEBSITE": "https://www.osssc.gov.in"
+  },
+  "ADDITIONAL_INFO": {
+    "FREQUENTLY_ASKED_QUESTIONS": [],
+    "LATEST_CHANGES": "",
+    "CONTACT_HELPLINE": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>District Court Jagatsinghpur Recruitment 2026 - Apply Offline for Junior Typist, Stenographer and More Posts</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/district-court-jagatsinghpur-recruitment-2026-apply-offline-for-08-junior-typist-stenographer-and-more-posts-3051370</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 11:58:06 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Junior Typist, Stenographer and More Posts",
+    "JOB_TYPE": "Regular",
+    "JOB_CATEGORY": "Group C",
+    "DEPARTMENT": "District Court Jagatsinghpur",
+    "MINISTRY": "Law and Justice",
+    "RECRUITING_AGENCY": "District Court Jagatsinghpur",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 8,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Junior Typist",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      },
+      {
+        "POST_NAME": "Stenographer",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "Jagatsinghpur, Odisha",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Pass in 10+2 and Computer Typing",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 18,
+      "MAXIMUM_AGE": 40,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Offline",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": null,
+      "INTERVIEW": null,
+      "SKILL_TEST": {
+        "TYPE": "Typing Test",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>JMI Recruitment 2026 - Apply Online for Project Research Scientist, Project Technical Support Posts</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/jmi-recruitment-2026-apply-online-for-project-research-scientist-project-technical-support-posts-3051369</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 11:57:59 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Project Research Scientist, Project Technical Support",
+    "JOB_TYPE": "Contractual",
+    "JOB_CATEGORY": "Research",
+    "DEPARTMENT": "Jamia Millia Islamia",
+    "MINISTRY": "Ministry of Education",
+    "RECRUITING_AGENCY": "Jamia Millia Islamia",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Project Research Scientist",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      },
+      {
+        "POST_NAME": "Project Technical Support",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "New Delhi",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.jmi.ac.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Balangir District Court Group C Recruitment 2026 - Apply Offline for 27 Steno, Junior Typist and More Posts</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/balangir-district-court-group-c-recruitment-2026-apply-offline-for-27-steno-junior-typist-and-more-posts-3051366</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 11:54:54 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Balangir District Court Group C Recruitment 2026",
+    "JOB_TYPE": "सरकारी नौकरी",
+    "JOB_CATEGORY": "ग्रुप सी",
+    "DEPARTMENT": "जिला न्यायालय, बालांगीर",
+    "MINISTRY": "कानून और न्याय मंत्रालय",
+    "RECRUITING_AGENCY": "जिला न्यायालय, बालांगीर",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 27,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "स्टेनोग्राफर",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": "ग्रुप सी"
+      },
+      {
+        "POST_NAME": "जूनियर टाइपिस्ट",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": "ग्रुप सी"
+      }
+    ],
+    "JOB_LOCATION": "बालांगीर, ओडिशा",
+    "GROUP": "ग्रुप सी"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 21,
+      "MAXIMUM_AGE": 32,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 वर्ष",
+        "OBC": "3 वर्ष",
+        "PWD": "10 वर्ष",
+        "EX_SERVICEMEN": "सेवा अवधि के अनुसार",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": "01-01-2026"
+    },
+    "PHYSICAL_STANDARDS": {},
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "ऑफलाइन",
+    "APPLICATION_START_DATE": "02-01-2026",
+    "APPLICATION_LAST_DATE": "31-01-2026",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 100,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": "डिमांड ड्राफ्ट"
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "आधिकारिक वेबसाइट से आवेदन पत्र डाउनलोड करें।",
+      "आवेदन पत्र को सही ढंग से भरें।",
+      "आवश्यक दस्तावेजों की स्व-प्रमाणित प्रतियां संलग्न करें।",
+      "आवेदन शुल्क का डिमांड ड्राफ्ट तैयार करें।",
+      "आवेदन पत्र को निर्धारित पते पर डाक द्वारा भेजें।"
+    ],
+    "REQUIRED_DOCUMENTS": [
+      "शैक्षिक योग्यता प्रमाण पत्र",
+      "जाति प्रमाण पत्र",
+      "आयु प्रमाण पत्र",
+      "फोटो और हस्ताक्षर",
+      "अनुभव प्रमाण पत्र (यदि लागू हो)"
+    ],
+    "PHOTO_SPECIFICATIONS": "हाल ही का पासपोर्ट साइज फोटो",
+    "SIGNATURE_SPECIFICATIONS": "सफेद कागज पर काली स्याही से हस्ताक्षर"
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["लिखित परीक्षा", "कौशल परीक्षा"],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": null,
+      "INTERVIEW": null,
+      "SKILL_TEST": {
+        "TYPE": "टाइपिंग टेस्ट / स्टेनोग्राफी टेस्ट",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": null
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "02-01-2026",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>NEHU Junior Research Fellow Recruitment 2026 - Apply Online</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/nehu-junior-research-fellow-jrf-recruitment-2026-apply-online-3051365</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 11:54:14 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Junior Research Fellow (JRF)",
+    "JOB_TYPE": "Research Fellowship",
+    "JOB_CATEGORY": "गैर-सरकारी, अनुसंधान परियोजना",
+    "DEPARTMENT": "Biochemistry",
+    "MINISTRY": "",
+    "RECRUITING_AGENCY": "North Eastern Hill University (NEHU)",
+    "ADVT_NO": "NEHU/R&amp;C/2025-26/05 dated 19.12.2025",
+    "TOTAL_VACANCIES": 1,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Junior Research Fellow",
+        "VACANCIES": 1,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": "Temporary"
+      }
+    ],
+    "JOB_LOCATION": "Shillong, Meghalaya",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "₹37,000/- per month + HRA as per rules",
+    "MINIMUM_SALARY": 37000,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": ["HRA"],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "M.Sc. in Biochemistry/Life Sciences/Biotechnology/Chemistry with minimum 55% marks (50% for SC/ST) and NET/ GATE qualification",
+    "EDUCATION_DETAILS": [
+      "M.Sc. in Biochemistry",
+      "M.Sc. in Life Sciences",
+      "M.Sc. in Biotechnology",
+      "M.Sc. in Chemistry"
+    ],
+    "MINIMUM_PERCENTAGE": "55% (50% for SC/ST)",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 28,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "10 years",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": "19.12.2025"
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": ["NET/ GATE qualified"]
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online (Email)",
+    "APPLICATION_START_DATE": "19.12.2025",
+    "APPLICATION_LAST_DATE": "17.01.2026",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "Prepare application form along with self-attested copies of all relevant documents.",
+      "Send the scanned copies via email to hodbiochemistry@nehu.ac.in with subject 'Application for JRF in DBT-Builder project'.",
+      "Also send hard copy by post to the Head, Department of Biochemistry, NEHU, Shillong-793022.",
+      "Appear for interview on 20.01.2026 at 10:30 AM in the Department of Biochemistry."
+    ],
+    "REQUIRED_DOCUMENTS": [
+      "Application form",
+      "Self-attested copies of educational certificates",
+      "Age proof",
+      "NET/GATE certificate",
+      "Experience certificate (if any)",
+      "Caste certificate (if applicable)"
+    ],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Interview"],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": null,
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": null,
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "19.12.2025",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "20.01.2026",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "https://www.nehu.ac.in/notification/advt_05_2025_26.pdf",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.nehu.ac.in/",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "Fellowship may be upgraded to SRF as per DBT norms",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "As per Govt. of India norms",
+    "CONTACT_HELPLINE": "Head, Dept. of Biochemistry, NEHU, Shillong",
+    "IMP_INSTRUCTIONS": [
+      "The position is temporary and co-terminus with the project.",
+      "No TA/DA will be paid for attending interview."
+    ],
+    "OFFICIAL_LANGUAGE": "English",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>DLSA Dhalai Recruitment 2026 - Apply Offline for Clerk, Typist Posts</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/dlsa-dhalai-recruitment-2026-apply-offline-for-02-clerk-typist-posts-3051363</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 11:47:55 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Clerk, Typist",
+    "JOB_TYPE": "सरकारी नौकरी",
+    "JOB_CATEGORY": "सचिवालय",
+    "DEPARTMENT": "District Legal Services Authority (DLSA) Dhalai",
+    "MINISTRY": "Kanoon aur Nyay Mantralaya",
+    "RECRUITING_AGENCY": "District Legal Services Authority (DLSA) Dhalai",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 2,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Clerk",
+        "VACANCIES": 1,
+        "CATEGORY": "", 
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      },
+      {
+        "POST_NAME": "Typist",
+        "VACANCIES": 1,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "Dhalai, Tripura",
+    "GROUP": "C"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Clerk: Bachelor's Degree with computer knowledge; Typist: Bachelor's Degree with 40 wpm typing speed in English or 30 wpm in Hindi",
+    "EDUCATION_DETAILS": [
+      "Clerk: Bachelor's Degree, computer knowledge",
+      "Typist: Bachelor's Degree, typing speed 40 wpm (English) or 30 wpm (Hindi)"
+    ],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 18,
+      "MAXIMUM_AGE": 40,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Offline",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "2025-05-30",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "Download application form from official website",
+      "Fill form with required details",
+      "Attach self-attested copies of documents",
+      "Send to DLSA Dhalai office by post"
+    ],
+    "REQUIRED_DOCUMENTS": [
+      "Educational certificates",
+      "Age proof",
+      "Caste certificate (if applicable)",
+      "Typing speed certificate (for Typist)",
+      "Computer knowledge certificate (for Clerk)"
+    ],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Written Exam", "Typing Test", "Interview"],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": null,
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "Typing Test",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "2025-05-01",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "http://dlsa.tripura.gov.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "English, Hindi, Bengali",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Union Bank of India Apprentice Exam Date 2026 (Out) - Check Schedule &amp; Details</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/union-bank-of-india-apprentice-exam-date-2026-3051361</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 11:44:09 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Apprentice",
+    "JOB_TYPE": "Apprenticeship",
+    "JOB_CATEGORY": "Banking",
+    "DEPARTMENT": "",
+    "MINISTRY": "",
+    "RECRUITING_AGENCY": "Indian Banks Association (IBA)",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [],
+    "JOB_LOCATION": "All India",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 15000,
+    "MAXIMUM_SALARY": 15000,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Graduate in any discipline",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 20,
+      "MAXIMUM_AGE": 28,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "10 years",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "2026",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.unionbankofindia.co.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>DLSA Motihari Para Legal Volunteers Interview Schedule 2026 - Date &amp; Documents</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/dlsa-motihari-para-legal-volunteers-interview-schedule-2026-3051358</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 11:43:39 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Para Legal Volunteer",
+    "JOB_TYPE": "Volunteer",
+    "JOB_CATEGORY": "Legal",
+    "DEPARTMENT": "District Legal Services Authority (DLSA) Motihari",
+    "MINISTRY": "Ministry of Law and Justice",
+    "RECRUITING_AGENCY": "DLSA Motihari",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Para Legal Volunteer",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "Motihari, Bihar",
+    "GROUP": "Volunteer"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Interview"],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.freejobalert.com/articles/dlsa-motihari-para-legal-volunteers-interview-schedule-2026-3051358",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Tripura University Project Associate Recruitment 2026 - Apply Online</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/tripura-university-project-associate-recruitment-2026-apply-online-3051360</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 11:43:37 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Project Associate",
+    "JOB_TYPE": "Contractual",
+    "JOB_CATEGORY": "Research",
+    "DEPARTMENT": "Various Departments",
+    "MINISTRY": "Ministry of Education",
+    "RECRUITING_AGENCY": "Tripura University",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [],
+    "JOB_LOCATION": "Tripura",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Post Graduate Degree in relevant subject",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Gujarat University Research Assistant Recruitment 2026 - Apply Offline</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/gujarat-university-research-assistant-recruitment-2026-apply-offline-3051357</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 11:38:43 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Research Assistant",
+    "JOB_TYPE": "Research",
+    "JOB_CATEGORY": "Teaching/Research",
+    "DEPARTMENT": "Gujarat University",
+    "MINISTRY": "",
+    "RECRUITING_AGENCY": "Gujarat University",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [],
+    "JOB_LOCATION": "Ahmedabad, Gujarat",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "As per norms",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Post Graduate in relevant subject",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Offline",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.gujaratuniversity.ac.in/",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>DRDO DIBT Paid Intern Recruitment 2026 - Apply Online</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/drdo-dibt-paid-intern-recruitment-2026-apply-online-3051355</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 11:38:31 GMT</t>
+  </si>
+  <si>
+    <t>इंटरनेशनल नौकरियाँ</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "DRDO DIBT Paid Intern Recruitment 2026",
+    "COMPANY_NAME": "DRDO - Defence Research and Development Organisation",
+    "COMPANY_DESCRIPTION": "Defence Research and Development Organisation (DRDO) is an agency under the Ministry of Defence, Government of India, responsible for military research and development.",
+    "INDUSTRY": "Defence &amp; Aerospace",
+    "JOB_CATEGORY": "Internship",
+    "JOB_TYPE": "Internship",
+    "EMPLOYMENT_TYPE": "Temporary",
+    "WORK_MODE": "On-site",
+    "COUNTRY": "India",
+    "CITY": "Various",
+    "JOB_LOCATION": "DRDO laboratories across India",
+    "NO_OF_OPENINGS": null,
+    "SKILL_LEVEL": "Entry Level"
+  },
+  "SALARY_AND_BENEFITS": {
+    "MINIMUM_SALARY": 18000,
+    "MAXIMUM_SALARY": 30000,
+    "SALARY_UNIT": "Monthly",
+    "SALARY_CURRENCY": "INR",
+    "SALARY_DETAILS": "Rs. 18,000 to Rs. 30,000 per month depending on educational qualification",
+    "CTC_DETAILS": null,
+    "TAX_FREE": false,
+    "OVERTIME_DETAILS": null,
+    "BENEFITS": {
+      "FREE_ACCOMMODATION": false,
+      "ACCOMMODATION_DETAILS": null,
+      "FREE_FOOD": false,
+      "FOOD_DETAILS": null,
+      "FREE_AIR_TICKET": false,
+      "AIR_TICKET_DETAILS": null,
+      "FREE_MEDICAL": false,
+      "HEALTH_INSURANCE": false,
+      "MEDICAL_DETAILS": null,
+      "FREE_TRANSPORTATION": false,
+      "TRANSPORTATION_DETAILS": null,
+      "ANNUAL_LEAVES": null,
+      "OTHER_BENEFITS": ["Certificate of internship", "Experience certificate"]
+    },
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "B.E/B.Tech, M.E/M.Tech, M.Sc, or equivalent in relevant discipline",
+    "EDUCATION_DETAILS": ["B.E/B.Tech", "M.E/M.Tech", "M.Sc"],
+    "MINIMUM_PERCENTAGE": "60% marks or equivalent CGPA",
+    "PREFERRED_DEGREE": "Engineering, Science, or Technology",
+    "EXPERIENCE_REQUIRED": {
+      "MINIMUM_YEARS": 0,
+      "MAXIMUM_YEARS": 0,
+      "EXPERIENCE_LEVEL": "Freshers"
+    },
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 18,
+      "MAXIMUM_AGE": 28
+    },
+    "SKILLS_REQUIRED": ["Research aptitude", "Analytical skills", "Technical skills as per domain"],
+    "LANGUAGE_PROFICIENCY": ["English"],
+    "CERTIFICATIONS": [],
+    "PASSPORT_REQUIREMENT": "",
+    "OTHER_ELIGIBILITY": ["Indian nationals only"]
+  },
+  "VISA_AND_WORK_PERMIT": {
+    "VISA_TYPE": "",
+    "VISA_SPONSORSHIP": "",
+    "WORK_PERMIT_DETAILS": "",
+    "VISA_PROCESSING_TIME": "",
+    "VISA_FEES": "",
+    "VISA_SPONSOR_BY_EMPLOYER": false,
+    "VISA_SPONSOR_BY_AGENCY": false
+  },
+  "JOB_DESCRIPTION": {
+    "KEY_RESPONSIBILITIES": ["Assist in research projects", "Data collection and analysis", "Report preparation"],
+    "DAILY_TASKS": ["Work under guidance of scientists", "Conduct experiments/literature review", "Document findings"],
+    "ROLE_OVERVIEW": "Paid internship for students to gain practical experience in defence research."
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_LINK": "https://www.drdo.gov.in",
+    "APPLICATION_EMAIL": null,
+    "APPLICATION_DEADLINE": "30-06-2025",
+    "WALK_IN_INTERVIEW": {
+      "DATE": "",
+      "TIME": "",
+      "VENUE": ""
+    },
+    "HOW_TO_APPLY_STEPS": ["Visit DRDO official website", "Go to Careers section", "Find DIBT internship notification", "Fill online application", "Upload documents", "Submit"],
+    "REQUIRED_DOCUMENTS": ["Resume", "Mark sheets", "ID proof", "Passport size photo"],
+    "RECRUITMENT_AGENCY": {
+      "AGENCY_NAME": "",
+      "AGENCY_LICENSE_NO": "",
+      "AGENCY_CONTACT": ""
+    }
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Application screening", "Interview"],
+    "WRITTEN_TEST": false,
+    "TECHNICAL_INTERVIEW": false,
+    "HR_INTERVIEW": true,
+    "TRADE_TEST": false,
+    "MEDICAL_EXAMINATION": false,
+    "OTHER_DETAILS": "Selection based on academic record and interview performance."
+  },
+  "IMPORTANT_DATES": {
+    "JOB_POSTED_DATE": "01-12-2025",
+    "APPLICATION_START_DATE": "01-12-2025",
+    "APPLICATION_LAST_DATE": "30-06-2025",
+    "INTERVIEW_DATE": "To be announced",
+    "JOINING_DATE": "As per project requirement",
+    "EXPECTED_TRAVEL_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_JOB_LISTING": "https://www.drdo.gov.in/careers",
+    "COMPANY_WEBSITE": "https://www.drdo.gov.in",
+    "APPLY_NOW_LINK": "https://www.drdo.gov.in/careers/dibt-internship",
+    "CONTACT_HELPLINE": "011-XXXXXXX"
+  },
+  "ADDITIONAL_INFO": {
+    "CONTRACT_DURATION": "6 months to 1 year",
+    "PROBATION_PERIOD": "",
+    "WORK_TIMINGS": "9:00 AM to 5:30 PM",
+    "WORKING_DAYS": "Monday to Friday",
+    "NOTICE_PERIOD": "",
+    "TRAINING_PROVIDED": "On-the-job training",
+    "COMPANY_CULTURE": "Research-oriented, disciplined",
+    "GROWTH_OPPORTUNITIES": "May lead to PhD sponsorship or future employment",
+    "MEDICAL_TEST_REQUIRED": false,
+    "POLICE_CLEARANCE_REQUIRED": false,
+    "EMIGRATION_CLEARANCE_REQUIRED": false,
+    "IMPORTANT_INSTRUCTIONS": ["Apply only through official website", "Keep documents ready"],
+    "FRAUD_ALERT": "No application fee required. Beware of scams."
+  }
+}</t>
+  </si>
+  <si>
+    <t>Nagaland University Junior Project Fellow Recruitment 2026 - Apply Online</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/nagaland-university-junior-project-fellow-recruitment-2026-apply-online-3051353</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 11:33:26 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Junior Project Fellow",
+    "JOB_TYPE": "Project",
+    "JOB_CATEGORY": "Research",
+    "DEPARTMENT": "Botany",
+    "MINISTRY": "Ministry of Education",
+    "RECRUITING_AGENCY": "Nagaland University",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 1,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Junior Project Fellow",
+        "VACANCIES": 1,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "Nagaland",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 20000,
+    "MAXIMUM_SALARY": 20000,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "M.Sc. in Botany or related subject with minimum 55% marks",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "55%",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "2026-01-19",
+    "APPLICATION_LAST_DATE": "2026-01-30",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": false
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "2026-01-19",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "https://nagalanduniversity.ac.in/",
+    "APPLY_ONLINE_LINK": "https://nagalanduniversity.ac.in/",
+    "OFFICIAL_WEBSITE": "https://nagalanduniversity.ac.in/",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>OPSC OCS Admit Card 2026 - Download Prelims Hall Ticket at opsc.gov.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/opsc-ocs-admit-card-2026-3051351</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 11:31:31 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "OPSC OCS Prelims",
+    "RECRUITMENT_NAME": "Odisha Civil Services (OCS)",
+    "POST_NAME": "Various",
+    "CONDUCTING_BODY": "Odisha Public Service Commission (OPSC)",
+    "EXAM_TYPE": "Preliminary Examination",
+    "CATEGORY": "Recruitment"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "Not specified",
+    "DIRECT_DOWNLOAD_LINK": "https://www.opsc.gov.in",
+    "STATUS_CHECK_LINK": ""
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "Not specified",
+    "EXAM_TIME": "",
+    "EXAM_SHIFT": "",
+    "EXAM_DURATION": "",
+    "EXAM_MODE": "Offline",
+    "EXAM_CENTER_CITY": "",
+    "EXAM_CENTER_NAME": "",
+    "FULL_SCHEDULE": []
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [
+      "Visit the official website opsc.gov.in.",
+      "Click on 'Admit Card' link.",
+      "Select 'OPSC OCS Prelims Admit Card 2026'.",
+      "Enter Registration Number and Password/Date of Birth.",
+      "Download and print the hall ticket."
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Password/Date of Birth"],
+    "ALTERNATE_METHOD": ""
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": [
+      "Carry a printed copy of the admit card.",
+      "Carry a valid photo ID proof.",
+      "Reach the exam center on time."
+    ],
+    "EXAM_DAY_GUIDELINES": [
+      "Follow all instructions given by invigilators.",
+      "Do not carry any electronic gadgets."
+    ],
+    "DOCUMENTS_TO_CARRY": ["Admit Card", "Photo ID proof"],
+    "PROHIBITED_ITEMS": ["Mobile phones", "Smartwatches", "Electronic devices"],
+    "COVID_SPECIFIC": ""
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "",
+    "EXAM_DATE_LIST": [],
+    "RESULT_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_DOWNLOAD": "https://www.opsc.gov.in",
+    "OFFICIAL_WEBSITE": "https://www.opsc.gov.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "Contact OPSC helpline if any discrepancy in admit card.",
+    "REPRINT_OPTION": "Admit card can be downloaded multiple times until exam date.",
+    "CONTACT_DETAILS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Howrah Court Sweeper Recruitment 2026 - Apply Offline</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/howrah-court-sweeper-recruitment-2026-apply-offline-for-02-posts-3051350</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 11:27:50 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Sweeper",
+    "JOB_TYPE": "Sarkari Naukri",
+    "JOB_CATEGORY": "Sweeper",
+    "DEPARTMENT": "Howrah Court",
+    "MINISTRY": "",
+    "RECRUITING_AGENCY": "Howrah Court",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 2,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Sweeper",
+        "VACANCIES": 2,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": "Group D"
+      }
+    ],
+    "JOB_LOCATION": "Howrah, West Bengal",
+    "GROUP": "D"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "Rs. 18,000 - 56,900/-",
+    "MINIMUM_SALARY": 18000,
+    "MAXIMUM_SALARY": 56900,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "8th Pass",
+    "EDUCATION_DETAILS": [
+      {
+        "QUALIFICATION": "8th Pass",
+        "SUBJECTS": null,
+        "PERCENTAGE": null
+      }
+    ],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "Not required",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 18,
+      "MAXIMUM_AGE": 40,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": "01-01-2026"
+    },
+    "PHYSICAL_STANDARDS": null,
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Offline",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": "No Fee"
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "Visit the official website of Howrah Court.",
+      "Download the application form.",
+      "Fill the form with required details.",
+      "Attach self-attested copies of documents.",
+      "Send the application via post to the court address."
+    ],
+    "REQUIRED_DOCUMENTS": [
+      "Educational certificates",
+      "Age proof",
+      "Caste certificate (if applicable)",
+      "Residence proof",
+      "Passport size photographs"
+    ],
+    "PHOTO_SPECIFICATIONS": "Recent passport size photo",
+    "SIGNATURE_SPECIFICATIONS": "Signature on white paper"
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Written Test", "Document Verification"],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": null,
+      "INTERVIEW": null,
+      "SKILL_TEST": null,
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": "West Bengal domicile may be required"
+  }
+}</t>
+  </si>
+  <si>
+    <t>BEL Project Engineer-I Recruitment 2026 - Apply Offline</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/bel-project-engineer-i-recruitment-2026-apply-offline-3051347</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 11:24:49 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Project Engineer-I",
+    "JOB_TYPE": "सरकारी",
+    "JOB_CATEGORY": "तकनीकी",
+    "DEPARTMENT": "Bharat Electronics Limited (BEL)",
+    "MINISTRY": "",
+    "RECRUITING_AGENCY": "Bharat Electronics Limited (BEL)",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Project Engineer-I",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": "अराजपत्रित"
+      }
+    ],
+    "JOB_LOCATION": "देश भर में BEL इकाइयाँ",
+    "GROUP": "ग्रुप A"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "40,000 - 1,40,000 रुपये प्रति माह",
+    "MINIMUM_SALARY": 40000,
+    "MAXIMUM_SALARY": 140000,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "B.E./B.Tech या समकक्ष",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "ऑफलाइन",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>HAL Refractionist Recruitment 2026 - Apply Offline</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/hal-refractionist-basis-recruitment-2026-apply-offline-for-01-post-3051344</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 11:19:30 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Refractionist",
+    "JOB_TYPE": "अराजपत्रित",
+    "JOB_CATEGORY": "तकनीकी",
+    "DEPARTMENT": "Medical Department",
+    "MINISTRY": "Ministry of Defence",
+    "RECRUITING_AGENCY": "Hindustan Aeronautics Limited (HAL)",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 1,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Refractionist",
+        "VACANCIES": 1,
+        "CATEGORY": "UR",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": "Group C"
+      }
+    ],
+    "JOB_LOCATION": "Koraput, Odisha",
+    "GROUP": "Group C"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "Rs. 25,000 - 55,000/- per month",
+    "MINIMUM_SALARY": 25000,
+    "MAXIMUM_SALARY": 55000,
+    "ALLOWANCES": ["DA", "HRA", "Medical"],
+    "PERKS": ["Accommodation", "CPF", "Medical facility"]
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "12th pass with Diploma in Refraction/Optometry or equivalent from a recognized institute. Preferable: 2 years experience in a hospital.",
+    "EDUCATION_DETAILS": [
+      "10+2",
+      "Diploma in Refraction/Optometry"
+    ],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "2 years in a hospital (preferred)",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 18,
+      "MAXIMUM_AGE": 35,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "10 years",
+        "EX_SERVICEMEN": "as per rules",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": "15-04-2026"
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": ["Must be medically fit."]
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Offline",
+    "APPLICATION_START_DATE": "01-04-2026",
+    "APPLICATION_LAST_DATE": "30-04-2026",
+    "LAST_DATE_FOR_FEE": "30-04-2026",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 500,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": "Demand Draft in favour of Hindustan Aeronautics Limited payable at Koraput"
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "Download the application form from the official HAL website.",
+      "Fill the form with required details.",
+      "Attach self-attested copies of documents.",
+      "Enclose a Demand Draft of application fee (if applicable).",
+      "Send the application to: The Chief Manager (HR), HR Department, HAL, Sunabeda, Koraput, Odisha - 763002."
+    ],
+    "REQUIRED_DOCUMENTS": [
+      "Educational certificates",
+      "Age proof",
+      "Experience certificate",
+      "Caste certificate (if applicable)",
+      "Disability certificate (if applicable)",
+      "Demand Draft"
+    ],
+    "PHOTO_SPECIFICATIONS": "Recent passport size photograph",
+    "SIGNATURE_SPECIFICATIONS": "Signature on application"
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Interview"],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": null,
+      "INTERVIEW": {
+        "TOTAL_MARKS": 100,
+        "DURATION": ""
+      },
+      "SKILL_TEST": null,
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "01-04-2026",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "To be notified",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "https://hal-india.co.in",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://hal-india.co.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "1 year",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "As per HAL rules",
+    "RESERVATION_DETAILS": "As per Government norms",
+    "CONTACT_HELPLINE": "06852-272000",
+    "IMP_INSTRUCTIONS": [
+      "Candidates must ensure they fulfill eligibility criteria.",
+      "Application must be sent by speed post or courier.",
+      "No TA/DA will be paid for interview."
+    ],
+    "OFFICIAL_LANGUAGE": "Hindi/English",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>District Magistrate Farrukhabad Panchayat Sahayak / Accountant cum DEO Recruitment 2026 - Apply Offline for 38 Posts</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/district-magistrate-farrukhabad-panchayat-sahayak-accountant-cum-data-entry-operator-recruitment-2026-apply-offline-for-38-posts-3051342</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 11:17:49 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Panchayat Sahayak / Accountant cum DEO",
+    "JOB_TYPE": "सरकारी नौकरी",
+    "JOB_CATEGORY": "ग्रामीण विकास",
+    "DEPARTMENT": "जिला पंचायत राज विभाग",
+    "MINISTRY": "पंचायती राज मंत्रालय",
+    "RECRUITING_AGENCY": "जिला मजिस्ट्रेट, फर्रुखाबाद",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 38,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Panchayat Sahayak",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      },
+      {
+        "POST_NAME": "Accountant cum Data Entry Operator",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "फर्रुखाबाद, उत्तर प्रदेश",
+    "GROUP": "C"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "25,000/- (निर्धारित वेतन)",
+    "MINIMUM_SALARY": 25000,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "किसी मान्यता प्राप्त विश्वविद्यालय से स्नातक; कंप्यूटर ज्ञान आवश्यक",
+    "EDUCATION_DETAILS": [
+      "स्नातक"
+    ],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 18,
+      "MAXIMUM_AGE": 40,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 वर्ष",
+        "OBC": "3 वर्ष",
+        "PWD": "10 वर्ष",
+        "EX_SERVICEMEN": "जितनी सेवा + 3 वर्ष",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": "01-01-2026"
+    },
+    "PHYSICAL_STANDARDS": null,
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Offline (डाक द्वारा)",
+    "APPLICATION_START_DATE": "15-01-2026",
+    "APPLICATION_LAST_DATE": "14-02-2026",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 500,
+      "SC_ST_PWD_WOMEN": 250,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": "डिमांड ड्राफ्ट / बैंक चालान"
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "आवेदन पत्र डाउनलोड करें",
+      "आवश्यक दस्तावेज संलग्न करें",
+      "निर्धारित पते पर डाक द्वारा भेजें"
+    ],
+    "REQUIRED_DOCUMENTS": [
+      "शैक्षणिक प्रमाणपत्र",
+      "आयु प्रमाणपत्र",
+      "जाति प्रमाणपत्र",
+      "निवास प्रमाणपत्र",
+      "पासपोर्ट साइज फोटो",
+      "हस्ताक्षर"
+    ],
+    "PHOTO_SPECIFICATIONS": "पासपोर्ट साइज, सफेद पृष्ठभूमि",
+    "SIGNATURE_SPECIFICATIONS": "काले पेन से स्कैन"
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [
+      "लिखित परीक्षा",
+      "कौशल परीक्षण",
+      "दस्तावेज़ सत्यापन"
+    ],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": {
+        "TOTAL_MARKS": 100,
+        "DURATION": "2 घंटे",
+        "SUBJECTS": [
+          "सामान्य ज्ञान",
+          "हिंदी",
+          "गणित",
+          "कंप्यूटर"
+        ],
+        "NEGATIVE_MARKING": "0.25 अंक प्रति गलत उत्तर"
+      },
+      "INTERVIEW": null,
+      "SKILL_TEST": {
+        "TYPE": "टाइपिंग टेस्ट / कंप्यूटर परीक्षण",
+        "TOTAL_MARKS": 50,
+        "DURATION": "30 मिनट"
+      },
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [
+      "सामान्य ज्ञान",
+      "हिंदी व्याकरण",
+      "गणित",
+      "कंप्यूटर बेसिक्स"
+    ],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "10-01-2026",
+    "EXAM_DATE": "मार्च 2026 (अनुमानित)",
+    "ADMIT_CARD_DATE": "परीक्षा से 2 सप्ताह पूर्व",
+    "RESULT_DATE": "अप्रैल 2026 (अनुमानित)",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "मई 2026 (अनुमानित)",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "https://farrukhabad.nic.in/",
+    "APPLY_ONLINE_LINK": "ऑफलाइन आवेदन",
+    "OFFICIAL_WEBSITE": "https://farrukhabad.nic.in/",
+    "ADMIT_CARD_LINK": "https://farrukhabad.nic.in/",
+    "RESULT_LINK": "https://farrukhabad.nic.in/",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "2 वर्ष",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "समय-समय पर पदोन्नति",
+    "TRANSFER_POLICY": "जिले के भीतर स्थानांतरण संभव",
+    "RESERVATION_DETAILS": "उत्तर प्रदेश सरकार के नियमानुसार",
+    "CONTACT_HELPLINE": "जिला मजिस्ट्रेट कार्यालय, फर्रुखाबाद",
+    "IMP_INSTRUCTIONS": [
+      "आवेदन पत्र विधिवत भरकर ही भेजें",
+      "सभी दस्तावेज स्वप्रमाणित करें"
+    ],
+    "OFFICIAL_LANGUAGE": "हिंदी / अंग्रेजी",
+    "DOMICILE_REQUIREMENTS": "उत्तर प्रदेश का मूल निवासी"
+  }
+}</t>
+  </si>
+  <si>
+    <t>District Magistrate Farrukhabad Panchayat Sahayak / Accountant cum Data Entry Operator Recruitment 2026 - Apply Offline for 38 Posts</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/district-magistrate-farrukhabad-panchayat-sahayak-accountant-cum-data-entry-operator-recruitment-2026-apply-offline-for-38-posts-3051339</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 11:14:54 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Panchayat Sahayak / Accountant cum Data Entry Operator",
+    "JOB_TYPE": "सरकारी नौकरी",
+    "JOB_CATEGORY": "गैर-राजपत्रित",
+    "DEPARTMENT": "पंचायत विभाग",
+    "MINISTRY": "उत्तर प्रदेश सरकार",
+    "RECRUITING_AGENCY": "जिला मजिस्ट्रेट, फर्रुखाबाद",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 38,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Panchayat Sahayak",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      },
+      {
+        "POST_NAME": "Accountant cum Data Entry Operator",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "फर्रुखाबाद, उत्तर प्रदेश",
+    "GROUP": "ग्रुप सी"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "किसी मान्यता प्राप्त बोर्ड या विश्वविद्यालय से 12वीं या स्नातक; डाटा एंट्री ऑपरेटर के लिए कंप्यूटर टाइपिंग और बेसिक कंप्यूटर ज्ञान",
+    "EDUCATION_DETAILS": [
+      "12वीं पास",
+      "स्नातक डिग्री",
+      "कंप्यूटर टाइपिंग"
+    ],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 18,
+      "MAXIMUM_AGE": 40,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 वर्ष",
+        "OBC": "3 वर्ष",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": null,
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "ऑफलाइन",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "आवेदन पत्र डाउनलोड करें",
+      "फॉर्म भरें",
+      "आवश्यक दस्तावेज संलग्न करें",
+      "जिला मजिस्ट्रेट कार्यालय में जमा करें"
+    ],
+    "REQUIRED_DOCUMENTS": [
+      "शैक्षणिक प्रमाणपत्र",
+      "आयु प्रमाण",
+      "जाति प्रमाण पत्र",
+      "फोटो",
+      "हस्ताक्षर"
+    ],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [
+      "लिखित परीक्षा",
+      "कौशल परीक्षा/टाइपिंग टेस्ट",
+      "दस्तावेज़ सत्यापन"
+    ],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": null,
+      "INTERVIEW": null,
+      "SKILL_TEST": {
+        "TYPE": "टाइपिंग टेस्ट",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": null
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "https://www.freejobalert.com/articles/district-magistrate-farrukhabad-panchayat-sahayak-accountant-cum-data-entry-operator-recruitment-2026-apply-offline-for-38-posts-3051339",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "हिंदी",
+    "DOMICILE_REQUIREMENTS": "उत्तर प्रदेश के मूल निवासी"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Kurukshetra University Date Sheet 2026 OUT - Direct Link to Download KUK UG, B.Tech Exam Schedule PDF at kuk.ac.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/kurukshetra-university-date-sheet-2026-out-direct-link-to-download-kuk-ug-btech-exam-schedule-pdf-3051337</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 11:13:36 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Kurukshetra University",
+    "EXAM_TYPE": "Academic Exam",
+    "CATEGORY": "Date Sheet"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": false,
+    "DECLARATION_DATE": "",
+    "RESULT_TYPE": "Date Sheet",
+    "DIRECT_RESULT_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [],
+    "REQUIRED_DETAILS": [],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://www.freejobalert.com/articles/kurukshetra-university-date-sheet-2026-out-direct-link-to-download-kuk-ug-btech-exam-schedule-pdf-3051337",
+    "DIRECT_RESULT": "",
+    "OFFICIAL_WEBSITE": "https://kuk.ac.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>UP Police Constable Exam Date 2026 (Out) - Check Official Schedule &amp; Admit Card</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/up-police-constable-exam-date-2026-3036445</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 11:13:18 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "UP Police Constable Exam 2026",
+    "RECRUITMENT_NAME": "UP Police Constable Recruitment 2026",
+    "POST_NAME": "Constable",
+    "CONDUCTING_BODY": "Uttar Pradesh Police Recruitment and Promotion Board (UPPRPB)",
+    "EXAM_TYPE": "Written Exam",
+    "CATEGORY": "Government Job"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": false,
+    "RELEASE_DATE": "",
+    "DIRECT_DOWNLOAD_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "",
+    "EXAM_TIME": "",
+    "EXAM_SHIFT": "",
+    "EXAM_DURATION": "",
+    "EXAM_MODE": "",
+    "EXAM_CENTER_CITY": "",
+    "EXAM_CENTER_NAME": "",
+    "FULL_SCHEDULE": []
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [],
+    "REQUIRED_DETAILS": [],
+    "ALTERNATE_METHOD": ""
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": [],
+    "EXAM_DAY_GUIDELINES": [],
+    "DOCUMENTS_TO_CARRY": [],
+    "PROHIBITED_ITEMS": [],
+    "COVID_SPECIFIC": ""
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "",
+    "EXAM_DATE_LIST": [],
+    "RESULT_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_DOWNLOAD": "",
+    "OFFICIAL_WEBSITE": "https://uppbpb.gov.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "",
+    "REPRINT_OPTION": "",
+    "CONTACT_DETAILS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Allahabad University Recruitment 2026 - Apply Online for Research Assistant and Field Investigator Posts</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/allahabad-university-recruitment-2026-apply-online-for-03-research-assistant-and-field-investigator-posts-3051336</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 11:08:06 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Research Assistant and Field Investigator",
+    "JOB_TYPE": "अनुबंध आधारित",
+    "JOB_CATEGORY": "अनुसंधान",
+    "DEPARTMENT": "इलाहाबाद विश्वविद्यालय",
+    "MINISTRY": "शिक्षा मंत्रालय",
+    "RECRUITING_AGENCY": "इलाहाबाद विश्वविद्यालय",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 3,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Research Assistant",
+        "VACANCIES": 2,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": "अनुबंध"
+      },
+      {
+        "POST_NAME": "Field Investigator",
+        "VACANCIES": 1,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": "अनुबंध"
+      }
+    ],
+    "JOB_LOCATION": "प्रयागराज",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "25000-30000 रुपये प्रति माह (Research Assistant), 20000-25000 रुपये प्रति माह (Field Investigator)",
+    "MINIMUM_SALARY": 20000,
+    "MAXIMUM_SALARY": 30000,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Research Assistant: पीएचडी / एम.फिल / पोस्ट ग्रेजुएट; Field Investigator: ग्रेजुएट",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 40,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "ऑनलाइन",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.allduniv.ac.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Osmania University Time Table 2026 OUT - Download Revised UG CBCS Exam Schedule PDF at ouexams.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/osmania-university-time-table-2026-out-download-revised-ug-cbcs-exam-schedule-pdf-3051334</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 11:07:06 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "UG CBCS Exam",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Osmania University",
+    "EXAM_TYPE": "University",
+    "CATEGORY": "Exam Schedule"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": false,
+    "DECLARATION_DATE": "",
+    "RESULT_TYPE": "Time Table",
+    "DIRECT_RESULT_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [],
+    "REQUIRED_DETAILS": [],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://www.freejobalert.com/articles/osmania-university-time-table-2026-out-download-revised-ug-cbcs-exam-schedule-pdf-3051334",
+    "DIRECT_RESULT": "",
+    "OFFICIAL_WEBSITE": "https://ouexams.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>GPRB PSI Technical Operator Syllabus and Exam Pattern 2026 - Download PDF Here</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/gprb-psi-technical-operator-syllabus-and-exam-pattern-3051333</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 11:05:19 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "SYLLABUS_IDENTIFICATION": {
+    "EXAM_NAME": "GPRB PSI Technical Operator",
+    "RECRUITMENT_NAME": "GPRB PSI Technical Operator Recruitment",
+    "CONDUCTING_BODY": "Gujarat Police Recruitment Board (GPRB)",
+    "EXAM_TYPE": "Police Recruitment",
+    "CATEGORY": "Government Job",
+    "ACADEMIC_YEAR": "2026",
+    "CLASS_OR_LEVEL": ""
+  },
+  "SYLLABUS_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "",
+    "SYLLABUS_VERSION": "",
+    "OFFICIAL_SYLLABUS_LINK": "https://www.freejobalert.com/articles/gprb-psi-technical-operator-syllabus-and-exam-pattern-3051333"
+  },
+  "EXAM_PATTERN_OVERVIEW": {
+    "TOTAL_MARKS": 0,
+    "TOTAL_QUESTIONS": 0,
+    "DURATION": "",
+    "MEDIUM": "",
+    "MODE": "Offline",
+    "NEGATIVE_MARKING": "",
+    "SECTIONS_COUNT": 0
+  },
+  "SUBJECTS": [
+    {
+      "SUBJECT_NAME": "General Studies",
+      "TOPICS": [
+        {
+          "TOPIC_NAME": "General Knowledge",
+          "SUB_TOPICS": [],
+          "MARKS_WEIGHTAGE": "",
+          "NUMBER_OF_QUESTIONS": 0,
+          "DIFFICULTY_LEVEL": ""
+        },
+        {
+          "TOPIC_NAME": "Current Affairs",
+          "SUB_TOPICS": [],
+          "MARKS_WEIGHTAGE": "",
+          "NUMBER_OF_QUESTIONS": 0,
+          "DIFFICULTY_LEVEL": ""
+        },
+        {
+          "TOPIC_NAME": "General Science",
+          "SUB_TOPICS": [],
+          "MARKS_WEIGHTAGE": "",
+          "NUMBER_OF_QUESTIONS": 0,
+          "DIFFICULTY_LEVEL": ""
+        },
+        {
+          "TOPIC_NAME": "Geography",
+          "SUB_TOPICS": [],
+          "MARKS_WEIGHTAGE": "",
+          "NUMBER_OF_QUESTIONS": 0,
+          "DIFFICULTY_LEVEL": ""
+        },
+        {
+          "TOPIC_NAME": "History",
+          "SUB_TOPICS": [],
+          "MARKS_WEIGHTAGE": "",
+          "NUMBER_OF_QUESTIONS": 0,
+          "DIFFICULTY_LEVEL": ""
+        }
+      ],
+      "TOTAL_MARKS": 0,
+      "TOTAL_QUESTIONS": 0,
+      "IMPORTANT_BOOKS": [],
+      "NOTES": ""
+    },
+    {
+      "SUBJECT_NAME": "Technical Subjects",
+      "TOPICS": [
+        {
+          "TOPIC_NAME": "Electronics &amp; Communication",
+          "SUB_TOPICS": [],
+          "MARKS_WEIGHTAGE": "",
+          "NUMBER_OF_QUESTIONS": 0,
+          "DIFFICULTY_LEVEL": ""
+        },
+        {
+          "TOPIC_NAME": "Computer Science",
+          "SUB_TOPICS": [],
+          "MARKS_WEIGHTAGE": "",
+          "NUMBER_OF_QUESTIONS": 0,
+          "DIFFICULTY_LEVEL": ""
+        },
+        {
+          "TOPIC_NAME": "Information Technology",
+          "SUB_TOPICS": [],
+          "MARKS_WEIGHTAGE": "",
+          "NUMBER_OF_QUESTIONS": 0,
+          "DIFFICULTY_LEVEL": ""
+        }
+      ],
+      "TOTAL_MARKS": 0,
+      "TOTAL_QUESTIONS": 0,
+      "IMPORTANT_BOOKS": [],
+      "NOTES": ""
+    },
+    {
+      "SUBJECT_NAME": "Gujarat State Knowledge",
+      "TOPICS": [
+        {
+          "TOPIC_NAME": "Gujarat History &amp; Culture",
+          "SUB_TOPICS": [],
+          "MARKS_WEIGHTAGE": "",
+          "NUMBER_OF_QUESTIONS": 0,
+          "DIFFICULTY_LEVEL": ""
+        },
+        {
+          "TOPIC_NAME": "Gujarat Geography",
+          "SUB_TOPICS": [],
+          "MARKS_WEIGHTAGE": "",
+          "NUMBER_OF_QUESTIONS": 0,
+          "DIFFICULTY_LEVEL": ""
+        },
+        {
+          "TOPIC_NAME": "Gujarat Politics &amp; Economy",
+          "SUB_TOPICS": [],
+          "MARKS_WEIGHTAGE": "",
+          "NUMBER_OF_QUESTIONS": 0,
+          "DIFFICULTY_LEVEL": ""
+        }
+      ],
+      "TOTAL_MARKS": 0,
+      "TOTAL_QUESTIONS": 0,
+      "IMPORTANT_BOOKS": [],
+      "NOTES": ""
+    },
+    {
+      "SUBJECT_NAME": "Mental Ability",
+      "TOPICS": [
+        {
+          "TOPIC_NAME": "Logical Reasoning",
+          "SUB_TOPICS": [],
+          "MARKS_WEIGHTAGE": "",
+          "NUMBER_OF_QUESTIONS": 0,
+          "DIFFICULTY_LEVEL": ""
+        },
+        {
+          "TOPIC_NAME": "Quantitative Aptitude",
+          "SUB_TOPICS": [],
+          "MARKS_WEIGHTAGE": "",
+          "NUMBER_OF_QUESTIONS": 0,
+          "DIFFICULTY_LEVEL": ""
+        },
+        {
+          "TOPIC_NAME": "Data Interpretation",
+          "SUB_TOPICS": [],
+          "MARKS_WEIGHTAGE": "",
+          "NUMBER_OF_QUESTIONS": 0,
+          "DIFFICULTY_LEVEL": ""
+        }
+      ],
+      "TOTAL_MARKS": 0,
+      "TOTAL_QUESTIONS": 0,
+      "IMPORTANT_BOOKS": [],
+      "NOTES": ""
+    }
+  ],
+  "SECTIONAL_DETAILS": [],
+  "RECOMMENDED_RESOURCES": {
+    "BOOKS": [],
+    "ONLINE_RESOURCES": [],
+    "PREVIOUS_YEAR_PAPERS_LINK": ""
+  },
+  "PREPARATION_TIPS": {
+    "STRATEGY": "",
+    "IMPORTANT_TOPICS": [],
+    "TIME_MANAGEMENT_TIPS": ""
+  },
+  "IMPORTANT_DATES": {
+    "SYLLABUS_RELEASE_DATE": "",
+    "LAST_UPDATED": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "SYLLABUS_PDF": "",
+    "OFFICIAL_WEBSITE": ""
+  },
+  "ADDITIONAL_INFO": {
+    "FREQUENTLY_ASKED_QUESTIONS": [],
+    "LATEST_CHANGES": "",
+    "CONTACT_HELPLINE": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>JMI Recruitment 2026 - Apply Offline for Primary Teacher, Nursery Teacher and More Posts</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/jmi-recruitment-2026-apply-offline-for-06-primary-teacher-nursery-teacher-and-more-posts-3051332</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 10:59:55 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Primary Teacher, Nursery Teacher and More Posts",
+    "JOB_TYPE": "Teaching",
+    "JOB_CATEGORY": "Group B",
+    "DEPARTMENT": "Jamia Millia Islamia",
+    "MINISTRY": "Ministry of Education",
+    "RECRUITING_AGENCY": "Jamia Millia Islamia (JMI)",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 6,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Primary Teacher",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      },
+      {
+        "POST_NAME": "Nursery Teacher",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      },
+      {
+        "POST_NAME": "More Posts",
+        "VACANCIES": 6,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "Delhi",
+    "GROUP": "B"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Offline",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.jmi.ac.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>DSSSB Final Answer Key 2026 Out For Assistant Editor, PGT and Other Posts – Download PDF, Response Sheet &amp; Objection Link</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/dsssb-assistant-editor-pgt-and-other-posts-final-answer-key-2026-3051331</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 10:54:38 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "ANSWER_KEY_IDENTIFICATION": {
+    "EXAM_NAME": "DSSSB Assistant Editor, PGT and Other Posts Final Answer Key",
+    "RECRUITMENT_NAME": "DSSSB Recruitment 2026",
+    "POST_NAME": "Assistant Editor, PGT and Other Posts",
+    "CONDUCTING_BODY": "Delhi Subordinate Services Selection Board (DSSSB)",
+    "EXAM_TYPE": "Recruitment Exam",
+    "CATEGORY": "Teaching &amp; Non-Teaching",
+    "SET_CODE": ""
+  },
+  "ANSWER_KEY_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "2026 (Exact date not specified)",
+    "ANSWER_KEY_TYPE": "Final Answer Key",
+    "DIRECT_DOWNLOAD_LINK": "https://dsssb.delhi.gov.in",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_DOWNLOAD_OR_CHECK": {
+    "STEPS": [
+      "Visit the official DSSSB website: https://dsssb.delhi.gov.in",
+      "Click on the 'Result/Answer Key' section",
+      "Find the link for 'Final Answer Key 2026 for Assistant Editor, PGT and Other Posts'",
+      "Click on the link and download the PDF",
+      "Check the answer key for your specific post and set"
+    ],
+    "REQUIRED_DETAILS": ["Roll Number", "Password/Date of Birth"],
+    "ALTERNATE_METHOD": "Check through the direct download link provided on FreeJobAlert"
+  },
+  "ANSWER_KEY_DETAILS": {
+    "SUBJECT_WISE_KEYS": [],
+    "QUESTION_WISE_ANSWER": [],
+    "MASTER_QUESTION_PAPER_LINK": "",
+    "SHIFT_WISE": []
+  },
+  "OBJECTION_PROCESS": {
+    "OBJECTION_WINDOW_START": "Not specified",
+    "OBJECTION_WINDOW_END": "Not specified",
+    "OBJECTION_FEE_PER_QUESTION": 100,
+    "HOW_TO_RAISE_OBJECTION": [],
+    "REVISED_KEY_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "ANSWER_KEY_AVAILABLE_FROM": "2026 (Exact date not specified)",
+    "ANSWER_KEY_AVAILABLE_UNTIL": "",
+    "OBJECTION_WINDOW": "Not specified",
+    "FINAL_KEY_DATE": "2026 (Exact date not specified)",
+    "RESULT_DATE": "To be announced"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://dsssb.delhi.gov.in",
+    "DIRECT_DOWNLOAD": "https://dsssb.delhi.gov.in",
+    "OFFICIAL_WEBSITE": "https://dsssb.delhi.gov.in",
+    "HELPLINE_NUMBER": "011-23392000"
+  },
+  "ADDITIONAL_INFO": {
+    "GENERAL_INSTRUCTIONS": [],
+    "DISPUTE_RESOLUTION": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Jiwaji University Time Table 2026 OUT: Download Revised UG &amp; PG Exam Schedule PDF at jiwaji.edu</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/jiwaji-university-time-table-2026-out-download-revised-ug-and-pg-exam-schedule-pdf-3051330</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 10:52:08 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "UG &amp; PG Exam Schedule",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Jiwaji University",
+    "EXAM_TYPE": "University Exam",
+    "CATEGORY": "Time Table"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "",
+    "RESULT_TYPE": "Revised Exam Schedule",
+    "DIRECT_RESULT_LINK": "",
+    "STATUS_CHECK_LINK": "https://www.freejobalert.com/articles/jiwaji-university-time-table-2026-out-download-revised-ug-and-pg-exam-schedule-pdf-3051330"
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website jiwaji.edu",
+      "Click on the 'Time Table' section",
+      "Download the PDF for your course"
+    ],
+    "REQUIRED_DETAILS": [],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "",
+    "OFFICIAL_WEBSITE": "http://www.jiwaji.edu",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
   }
 }</t>
   </si>
@@ -35680,6 +43626,1386 @@
         <v>1002</v>
       </c>
     </row>
+    <row r="251">
+      <c r="A251" t="s">
+        <v>7</v>
+      </c>
+      <c r="B251" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C251" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D251" t="s">
+        <v>1005</v>
+      </c>
+      <c r="E251" t="s">
+        <v>11</v>
+      </c>
+      <c r="F251" t="s">
+        <v>1003</v>
+      </c>
+      <c r="G251" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="s">
+        <v>7</v>
+      </c>
+      <c r="B252" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C252" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D252" t="s">
+        <v>1009</v>
+      </c>
+      <c r="E252" t="s">
+        <v>38</v>
+      </c>
+      <c r="F252" t="s">
+        <v>1007</v>
+      </c>
+      <c r="G252" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="s">
+        <v>7</v>
+      </c>
+      <c r="B253" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C253" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D253" t="s">
+        <v>1013</v>
+      </c>
+      <c r="E253" t="s">
+        <v>11</v>
+      </c>
+      <c r="F253" t="s">
+        <v>1011</v>
+      </c>
+      <c r="G253" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="s">
+        <v>7</v>
+      </c>
+      <c r="B254" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C254" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D254" t="s">
+        <v>1017</v>
+      </c>
+      <c r="E254" t="s">
+        <v>38</v>
+      </c>
+      <c r="F254" t="s">
+        <v>1015</v>
+      </c>
+      <c r="G254" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="s">
+        <v>7</v>
+      </c>
+      <c r="B255" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C255" t="s">
+        <v>1020</v>
+      </c>
+      <c r="D255" t="s">
+        <v>1021</v>
+      </c>
+      <c r="E255" t="s">
+        <v>11</v>
+      </c>
+      <c r="F255" t="s">
+        <v>1019</v>
+      </c>
+      <c r="G255" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="s">
+        <v>7</v>
+      </c>
+      <c r="B256" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C256" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D256" t="s">
+        <v>1025</v>
+      </c>
+      <c r="E256" t="s">
+        <v>29</v>
+      </c>
+      <c r="F256" t="s">
+        <v>1023</v>
+      </c>
+      <c r="G256" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="s">
+        <v>52</v>
+      </c>
+      <c r="B257" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C257" t="s">
+        <v>1028</v>
+      </c>
+      <c r="D257" t="s">
+        <v>1029</v>
+      </c>
+      <c r="E257" t="s">
+        <v>38</v>
+      </c>
+      <c r="F257" t="s">
+        <v>1027</v>
+      </c>
+      <c r="G257" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="s">
+        <v>52</v>
+      </c>
+      <c r="B258" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C258" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D258" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E258" t="s">
+        <v>11</v>
+      </c>
+      <c r="F258" t="s">
+        <v>1031</v>
+      </c>
+      <c r="G258" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="s">
+        <v>52</v>
+      </c>
+      <c r="B259" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C259" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D259" t="s">
+        <v>1037</v>
+      </c>
+      <c r="E259" t="s">
+        <v>11</v>
+      </c>
+      <c r="F259" t="s">
+        <v>1035</v>
+      </c>
+      <c r="G259" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="s">
+        <v>52</v>
+      </c>
+      <c r="B260" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C260" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D260" t="s">
+        <v>1041</v>
+      </c>
+      <c r="E260" t="s">
+        <v>29</v>
+      </c>
+      <c r="F260" t="s">
+        <v>1039</v>
+      </c>
+      <c r="G260" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="s">
+        <v>52</v>
+      </c>
+      <c r="B261" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C261" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D261" t="s">
+        <v>1045</v>
+      </c>
+      <c r="E261" t="s">
+        <v>11</v>
+      </c>
+      <c r="F261" t="s">
+        <v>1043</v>
+      </c>
+      <c r="G261" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="s">
+        <v>52</v>
+      </c>
+      <c r="B262" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C262" t="s">
+        <v>1048</v>
+      </c>
+      <c r="D262" t="s">
+        <v>1049</v>
+      </c>
+      <c r="E262" t="s">
+        <v>11</v>
+      </c>
+      <c r="F262" t="s">
+        <v>1047</v>
+      </c>
+      <c r="G262" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="s">
+        <v>52</v>
+      </c>
+      <c r="B263" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C263" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D263" t="s">
+        <v>1053</v>
+      </c>
+      <c r="E263" t="s">
+        <v>29</v>
+      </c>
+      <c r="F263" t="s">
+        <v>1051</v>
+      </c>
+      <c r="G263" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="s">
+        <v>52</v>
+      </c>
+      <c r="B264" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C264" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D264" t="s">
+        <v>1057</v>
+      </c>
+      <c r="E264" t="s">
+        <v>11</v>
+      </c>
+      <c r="F264" t="s">
+        <v>1055</v>
+      </c>
+      <c r="G264" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="s">
+        <v>52</v>
+      </c>
+      <c r="B265" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C265" t="s">
+        <v>1060</v>
+      </c>
+      <c r="D265" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E265" t="s">
+        <v>11</v>
+      </c>
+      <c r="F265" t="s">
+        <v>1059</v>
+      </c>
+      <c r="G265" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="s">
+        <v>52</v>
+      </c>
+      <c r="B266" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C266" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D266" t="s">
+        <v>1065</v>
+      </c>
+      <c r="E266" t="s">
+        <v>11</v>
+      </c>
+      <c r="F266" t="s">
+        <v>1063</v>
+      </c>
+      <c r="G266" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="s">
+        <v>52</v>
+      </c>
+      <c r="B267" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C267" t="s">
+        <v>1068</v>
+      </c>
+      <c r="D267" t="s">
+        <v>1069</v>
+      </c>
+      <c r="E267" t="s">
+        <v>11</v>
+      </c>
+      <c r="F267" t="s">
+        <v>1067</v>
+      </c>
+      <c r="G267" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="s">
+        <v>52</v>
+      </c>
+      <c r="B268" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C268" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D268" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E268" t="s">
+        <v>11</v>
+      </c>
+      <c r="F268" t="s">
+        <v>1071</v>
+      </c>
+      <c r="G268" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="s">
+        <v>52</v>
+      </c>
+      <c r="B269" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C269" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D269" t="s">
+        <v>1077</v>
+      </c>
+      <c r="E269" t="s">
+        <v>29</v>
+      </c>
+      <c r="F269" t="s">
+        <v>1075</v>
+      </c>
+      <c r="G269" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="s">
+        <v>52</v>
+      </c>
+      <c r="B270" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C270" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D270" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E270" t="s">
+        <v>11</v>
+      </c>
+      <c r="F270" t="s">
+        <v>1079</v>
+      </c>
+      <c r="G270" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="s">
+        <v>52</v>
+      </c>
+      <c r="B271" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C271" t="s">
+        <v>1084</v>
+      </c>
+      <c r="D271" t="s">
+        <v>1085</v>
+      </c>
+      <c r="E271" t="s">
+        <v>11</v>
+      </c>
+      <c r="F271" t="s">
+        <v>1083</v>
+      </c>
+      <c r="G271" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="s">
+        <v>52</v>
+      </c>
+      <c r="B272" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C272" t="s">
+        <v>1088</v>
+      </c>
+      <c r="D272" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E272" t="s">
+        <v>11</v>
+      </c>
+      <c r="F272" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G272" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="s">
+        <v>52</v>
+      </c>
+      <c r="B273" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C273" t="s">
+        <v>1092</v>
+      </c>
+      <c r="D273" t="s">
+        <v>1093</v>
+      </c>
+      <c r="E273" t="s">
+        <v>24</v>
+      </c>
+      <c r="F273" t="s">
+        <v>1091</v>
+      </c>
+      <c r="G273" t="s">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="s">
+        <v>52</v>
+      </c>
+      <c r="B274" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C274" t="s">
+        <v>1096</v>
+      </c>
+      <c r="D274" t="s">
+        <v>1097</v>
+      </c>
+      <c r="E274" t="s">
+        <v>29</v>
+      </c>
+      <c r="F274" t="s">
+        <v>1095</v>
+      </c>
+      <c r="G274" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="s">
+        <v>52</v>
+      </c>
+      <c r="B275" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C275" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D275" t="s">
+        <v>1101</v>
+      </c>
+      <c r="E275" t="s">
+        <v>11</v>
+      </c>
+      <c r="F275" t="s">
+        <v>1099</v>
+      </c>
+      <c r="G275" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="s">
+        <v>52</v>
+      </c>
+      <c r="B276" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C276" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D276" t="s">
+        <v>1105</v>
+      </c>
+      <c r="E276" t="s">
+        <v>11</v>
+      </c>
+      <c r="F276" t="s">
+        <v>1103</v>
+      </c>
+      <c r="G276" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="s">
+        <v>52</v>
+      </c>
+      <c r="B277" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C277" t="s">
+        <v>1108</v>
+      </c>
+      <c r="D277" t="s">
+        <v>1109</v>
+      </c>
+      <c r="E277" t="s">
+        <v>393</v>
+      </c>
+      <c r="F277" t="s">
+        <v>1107</v>
+      </c>
+      <c r="G277" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="s">
+        <v>52</v>
+      </c>
+      <c r="B278" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C278" t="s">
+        <v>1112</v>
+      </c>
+      <c r="D278" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E278" t="s">
+        <v>24</v>
+      </c>
+      <c r="F278" t="s">
+        <v>1111</v>
+      </c>
+      <c r="G278" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="s">
+        <v>52</v>
+      </c>
+      <c r="B279" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C279" t="s">
+        <v>1116</v>
+      </c>
+      <c r="D279" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E279" t="s">
+        <v>11</v>
+      </c>
+      <c r="F279" t="s">
+        <v>1115</v>
+      </c>
+      <c r="G279" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="s">
+        <v>52</v>
+      </c>
+      <c r="B280" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C280" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D280" t="s">
+        <v>1121</v>
+      </c>
+      <c r="E280" t="s">
+        <v>11</v>
+      </c>
+      <c r="F280" t="s">
+        <v>1119</v>
+      </c>
+      <c r="G280" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="s">
+        <v>52</v>
+      </c>
+      <c r="B281" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C281" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D281" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E281" t="s">
+        <v>11</v>
+      </c>
+      <c r="F281" t="s">
+        <v>1123</v>
+      </c>
+      <c r="G281" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="s">
+        <v>52</v>
+      </c>
+      <c r="B282" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C282" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D282" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E282" t="s">
+        <v>11</v>
+      </c>
+      <c r="F282" t="s">
+        <v>1127</v>
+      </c>
+      <c r="G282" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="s">
+        <v>52</v>
+      </c>
+      <c r="B283" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C283" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D283" t="s">
+        <v>1133</v>
+      </c>
+      <c r="E283" t="s">
+        <v>11</v>
+      </c>
+      <c r="F283" t="s">
+        <v>1131</v>
+      </c>
+      <c r="G283" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="s">
+        <v>52</v>
+      </c>
+      <c r="B284" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C284" t="s">
+        <v>1136</v>
+      </c>
+      <c r="D284" t="s">
+        <v>1137</v>
+      </c>
+      <c r="E284" t="s">
+        <v>11</v>
+      </c>
+      <c r="F284" t="s">
+        <v>1135</v>
+      </c>
+      <c r="G284" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="s">
+        <v>52</v>
+      </c>
+      <c r="B285" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C285" t="s">
+        <v>1140</v>
+      </c>
+      <c r="D285" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E285" t="s">
+        <v>393</v>
+      </c>
+      <c r="F285" t="s">
+        <v>1139</v>
+      </c>
+      <c r="G285" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="s">
+        <v>52</v>
+      </c>
+      <c r="B286" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C286" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D286" t="s">
+        <v>1145</v>
+      </c>
+      <c r="E286" t="s">
+        <v>11</v>
+      </c>
+      <c r="F286" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G286" t="s">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="s">
+        <v>52</v>
+      </c>
+      <c r="B287" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C287" t="s">
+        <v>1148</v>
+      </c>
+      <c r="D287" t="s">
+        <v>1149</v>
+      </c>
+      <c r="E287" t="s">
+        <v>11</v>
+      </c>
+      <c r="F287" t="s">
+        <v>1147</v>
+      </c>
+      <c r="G287" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="s">
+        <v>52</v>
+      </c>
+      <c r="B288" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C288" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D288" t="s">
+        <v>1153</v>
+      </c>
+      <c r="E288" t="s">
+        <v>11</v>
+      </c>
+      <c r="F288" t="s">
+        <v>1151</v>
+      </c>
+      <c r="G288" t="s">
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="s">
+        <v>52</v>
+      </c>
+      <c r="B289" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C289" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D289" t="s">
+        <v>1157</v>
+      </c>
+      <c r="E289" t="s">
+        <v>11</v>
+      </c>
+      <c r="F289" t="s">
+        <v>1155</v>
+      </c>
+      <c r="G289" t="s">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="s">
+        <v>52</v>
+      </c>
+      <c r="B290" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C290" t="s">
+        <v>1160</v>
+      </c>
+      <c r="D290" t="s">
+        <v>1161</v>
+      </c>
+      <c r="E290" t="s">
+        <v>11</v>
+      </c>
+      <c r="F290" t="s">
+        <v>1159</v>
+      </c>
+      <c r="G290" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="s">
+        <v>52</v>
+      </c>
+      <c r="B291" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C291" t="s">
+        <v>1164</v>
+      </c>
+      <c r="D291" t="s">
+        <v>1165</v>
+      </c>
+      <c r="E291" t="s">
+        <v>11</v>
+      </c>
+      <c r="F291" t="s">
+        <v>1163</v>
+      </c>
+      <c r="G291" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="s">
+        <v>52</v>
+      </c>
+      <c r="B292" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C292" t="s">
+        <v>1168</v>
+      </c>
+      <c r="D292" t="s">
+        <v>1169</v>
+      </c>
+      <c r="E292" t="s">
+        <v>11</v>
+      </c>
+      <c r="F292" t="s">
+        <v>1167</v>
+      </c>
+      <c r="G292" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="s">
+        <v>52</v>
+      </c>
+      <c r="B293" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C293" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D293" t="s">
+        <v>1173</v>
+      </c>
+      <c r="E293" t="s">
+        <v>11</v>
+      </c>
+      <c r="F293" t="s">
+        <v>1171</v>
+      </c>
+      <c r="G293" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="s">
+        <v>52</v>
+      </c>
+      <c r="B294" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C294" t="s">
+        <v>1176</v>
+      </c>
+      <c r="D294" t="s">
+        <v>1177</v>
+      </c>
+      <c r="E294" t="s">
+        <v>11</v>
+      </c>
+      <c r="F294" t="s">
+        <v>1175</v>
+      </c>
+      <c r="G294" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="s">
+        <v>52</v>
+      </c>
+      <c r="B295" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C295" t="s">
+        <v>1180</v>
+      </c>
+      <c r="D295" t="s">
+        <v>1181</v>
+      </c>
+      <c r="E295" t="s">
+        <v>1182</v>
+      </c>
+      <c r="F295" t="s">
+        <v>1179</v>
+      </c>
+      <c r="G295" t="s">
+        <v>1183</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="s">
+        <v>52</v>
+      </c>
+      <c r="B296" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C296" t="s">
+        <v>1185</v>
+      </c>
+      <c r="D296" t="s">
+        <v>1186</v>
+      </c>
+      <c r="E296" t="s">
+        <v>11</v>
+      </c>
+      <c r="F296" t="s">
+        <v>1184</v>
+      </c>
+      <c r="G296" t="s">
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="s">
+        <v>52</v>
+      </c>
+      <c r="B297" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C297" t="s">
+        <v>1189</v>
+      </c>
+      <c r="D297" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E297" t="s">
+        <v>38</v>
+      </c>
+      <c r="F297" t="s">
+        <v>1188</v>
+      </c>
+      <c r="G297" t="s">
+        <v>1191</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="s">
+        <v>52</v>
+      </c>
+      <c r="B298" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C298" t="s">
+        <v>1193</v>
+      </c>
+      <c r="D298" t="s">
+        <v>1194</v>
+      </c>
+      <c r="E298" t="s">
+        <v>11</v>
+      </c>
+      <c r="F298" t="s">
+        <v>1192</v>
+      </c>
+      <c r="G298" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="s">
+        <v>52</v>
+      </c>
+      <c r="B299" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C299" t="s">
+        <v>1197</v>
+      </c>
+      <c r="D299" t="s">
+        <v>1198</v>
+      </c>
+      <c r="E299" t="s">
+        <v>11</v>
+      </c>
+      <c r="F299" t="s">
+        <v>1196</v>
+      </c>
+      <c r="G299" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="s">
+        <v>52</v>
+      </c>
+      <c r="B300" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C300" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D300" t="s">
+        <v>1202</v>
+      </c>
+      <c r="E300" t="s">
+        <v>11</v>
+      </c>
+      <c r="F300" t="s">
+        <v>1200</v>
+      </c>
+      <c r="G300" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="s">
+        <v>52</v>
+      </c>
+      <c r="B301" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C301" t="s">
+        <v>1205</v>
+      </c>
+      <c r="D301" t="s">
+        <v>1206</v>
+      </c>
+      <c r="E301" t="s">
+        <v>11</v>
+      </c>
+      <c r="F301" t="s">
+        <v>1204</v>
+      </c>
+      <c r="G301" t="s">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="s">
+        <v>52</v>
+      </c>
+      <c r="B302" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C302" t="s">
+        <v>1209</v>
+      </c>
+      <c r="D302" t="s">
+        <v>1210</v>
+      </c>
+      <c r="E302" t="s">
+        <v>11</v>
+      </c>
+      <c r="F302" t="s">
+        <v>1208</v>
+      </c>
+      <c r="G302" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="s">
+        <v>52</v>
+      </c>
+      <c r="B303" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C303" t="s">
+        <v>1213</v>
+      </c>
+      <c r="D303" t="s">
+        <v>1214</v>
+      </c>
+      <c r="E303" t="s">
+        <v>29</v>
+      </c>
+      <c r="F303" t="s">
+        <v>1212</v>
+      </c>
+      <c r="G303" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="s">
+        <v>52</v>
+      </c>
+      <c r="B304" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C304" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D304" t="s">
+        <v>1218</v>
+      </c>
+      <c r="E304" t="s">
+        <v>38</v>
+      </c>
+      <c r="F304" t="s">
+        <v>1216</v>
+      </c>
+      <c r="G304" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="s">
+        <v>52</v>
+      </c>
+      <c r="B305" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C305" t="s">
+        <v>1221</v>
+      </c>
+      <c r="D305" t="s">
+        <v>1222</v>
+      </c>
+      <c r="E305" t="s">
+        <v>11</v>
+      </c>
+      <c r="F305" t="s">
+        <v>1220</v>
+      </c>
+      <c r="G305" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="s">
+        <v>52</v>
+      </c>
+      <c r="B306" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C306" t="s">
+        <v>1225</v>
+      </c>
+      <c r="D306" t="s">
+        <v>1226</v>
+      </c>
+      <c r="E306" t="s">
+        <v>29</v>
+      </c>
+      <c r="F306" t="s">
+        <v>1224</v>
+      </c>
+      <c r="G306" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="s">
+        <v>52</v>
+      </c>
+      <c r="B307" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C307" t="s">
+        <v>1229</v>
+      </c>
+      <c r="D307" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E307" t="s">
+        <v>393</v>
+      </c>
+      <c r="F307" t="s">
+        <v>1228</v>
+      </c>
+      <c r="G307" t="s">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="s">
+        <v>52</v>
+      </c>
+      <c r="B308" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C308" t="s">
+        <v>1233</v>
+      </c>
+      <c r="D308" t="s">
+        <v>1234</v>
+      </c>
+      <c r="E308" t="s">
+        <v>11</v>
+      </c>
+      <c r="F308" t="s">
+        <v>1232</v>
+      </c>
+      <c r="G308" t="s">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="s">
+        <v>52</v>
+      </c>
+      <c r="B309" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C309" t="s">
+        <v>1237</v>
+      </c>
+      <c r="D309" t="s">
+        <v>1238</v>
+      </c>
+      <c r="E309" t="s">
+        <v>24</v>
+      </c>
+      <c r="F309" t="s">
+        <v>1236</v>
+      </c>
+      <c r="G309" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="s">
+        <v>52</v>
+      </c>
+      <c r="B310" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C310" t="s">
+        <v>1241</v>
+      </c>
+      <c r="D310" t="s">
+        <v>1242</v>
+      </c>
+      <c r="E310" t="s">
+        <v>29</v>
+      </c>
+      <c r="F310" t="s">
+        <v>1240</v>
+      </c>
+      <c r="G310" t="s">
+        <v>1243</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/data/articles.xlsx
+++ b/data/articles.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1244" uniqueCount="1244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1256" uniqueCount="1256">
   <si>
     <t>Competitor</t>
   </si>
@@ -37568,6 +37568,321 @@
     "REVALUATION_PROCESS": "",
     "CONTACT_DETAILS": "",
     "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>RSSB REET Mains Upper Teacher Result 2026 – Out</t>
+  </si>
+  <si>
+    <t>https://sarkariresult.com.cm/rssb-reet-mains-upper-teacher-2026/</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 16:47:37 +0000</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "REET Mains (Upper Teacher)",
+    "RECRUITMENT_NAME": "REET Mains Upper Teacher Recruitment",
+    "POST_NAME": "Upper Teacher",
+    "CONDUCTING_BODY": "Rajasthan Staff Selection Board (RSSB)",
+    "EXAM_TYPE": "Teaching Eligibility Test",
+    "CATEGORY": "Recruitment Result"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026",
+    "RESULT_TYPE": "Mains Result",
+    "DIRECT_RESULT_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [],
+    "REQUIRED_DETAILS": [],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "",
+    "OFFICIAL_WEBSITE": "",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>RSSB REET Mains Primary Teacher Result 2026 – Out</t>
+  </si>
+  <si>
+    <t>https://sarkariresult.com.cm/rssb-reet-mains-primary-teacher-2026/</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 16:47:12 +0000</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "REET Mains",
+    "RECRUITMENT_NAME": "RSSB REET Mains Primary Teacher Recruitment 2025-26",
+    "POST_NAME": "Primary Teacher (Level 1)",
+    "CONDUCTING_BODY": "Rajasthan Staff Selection Board (RSSB)",
+    "EXAM_TYPE": "Teacher Eligibility Test (Mains)",
+    "CATEGORY": "Teaching Recruitment"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "10-12-2025",
+    "RESULT_TYPE": "Mains Result",
+    "DIRECT_RESULT_LINK": "https://sarkariresult.com.cm/rssb-reet-mains-primary-teacher-2026/",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website of RSSB or sarkariresult.com.cm",
+      "Click on the link 'RSSB REET Mains Primary Teacher Result 2026'",
+      "Enter your registration number and roll number",
+      "Click submit and view your result",
+      "Download and take a printout for future reference"
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Roll Number"],
+    "ALTERNATE_METHOD": "Check via SMS or mobile app if available"
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "10-12-2025",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "https://sarkariresult.com.cm/rssb-reet-mains-primary-teacher-2026/",
+    "OFFICIAL_WEBSITE": "https://rssb.rajasthan.gov.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>RPSC APO Online Form 2026</t>
+  </si>
+  <si>
+    <t>https://sarkariresult.com.cm/rpsc-apo-2026/</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 14:37:10 +0000</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Assistant Prosecution Officer (APO)",
+    "JOB_TYPE": "Government",
+    "JOB_CATEGORY": "Group A",
+    "DEPARTMENT": "Home Department",
+    "MINISTRY": "Government of Rajasthan",
+    "RECRUITING_AGENCY": "Rajasthan Public Service Commission (RPSC)",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [],
+    "JOB_LOCATION": "Rajasthan",
+    "GROUP": "A"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Law Graduate from a recognized university",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
   }
 }</t>
   </si>
@@ -45006,6 +45321,75 @@
         <v>1243</v>
       </c>
     </row>
+    <row r="311">
+      <c r="A311" t="s">
+        <v>7</v>
+      </c>
+      <c r="B311" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C311" t="s">
+        <v>1245</v>
+      </c>
+      <c r="D311" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E311" t="s">
+        <v>29</v>
+      </c>
+      <c r="F311" t="s">
+        <v>1244</v>
+      </c>
+      <c r="G311" t="s">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="s">
+        <v>7</v>
+      </c>
+      <c r="B312" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C312" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D312" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E312" t="s">
+        <v>29</v>
+      </c>
+      <c r="F312" t="s">
+        <v>1248</v>
+      </c>
+      <c r="G312" t="s">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="s">
+        <v>7</v>
+      </c>
+      <c r="B313" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C313" t="s">
+        <v>1253</v>
+      </c>
+      <c r="D313" t="s">
+        <v>1254</v>
+      </c>
+      <c r="E313" t="s">
+        <v>11</v>
+      </c>
+      <c r="F313" t="s">
+        <v>1252</v>
+      </c>
+      <c r="G313" t="s">
+        <v>1255</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/data/articles.xlsx
+++ b/data/articles.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1256" uniqueCount="1256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1260" uniqueCount="1260">
   <si>
     <t>Competitor</t>
   </si>
@@ -37883,6 +37883,77 @@
     "IMP_INSTRUCTIONS": [],
     "OFFICIAL_LANGUAGE": "",
     "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>MPESB Van Rakshak / Jail Prahari Admit Card 2026 – Out</t>
+  </si>
+  <si>
+    <t>https://sarkariresult.com.cm/mpesb-van-rakshak-jail-prahari-2026/</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 18:50:44 +0000</t>
+  </si>
+  <si>
+    <t>{
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "Van Rakshak / Jail Prahari Exam 2026",
+    "RECRUITMENT_NAME": "MPESB Van Rakshak / Jail Prahari Recruitment 2026",
+    "POST_NAME": "Van Rakshak, Jail Prahari",
+    "CONDUCTING_BODY": "Madhya Pradesh Employee Selection Board (MPESB)",
+    "EXAM_TYPE": "Recruitment Exam",
+    "CATEGORY": ""
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "",
+    "DIRECT_DOWNLOAD_LINK": "https://sarkariresult.com.cm/mpesb-van-rakshak-jail-prahari-2026/",
+    "STATUS_CHECK_LINK": ""
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "",
+    "EXAM_TIME": "",
+    "EXAM_SHIFT": "",
+    "EXAM_DURATION": "",
+    "EXAM_MODE": "",
+    "EXAM_CENTER_CITY": "",
+    "EXAM_CENTER_NAME": "",
+    "FULL_SCHEDULE": []
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [
+      "Visit the official website of MPESB.",
+      "Navigate to the admit card download section.",
+      "Enter your registration number and date of birth.",
+      "Download and print the admit card."
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth"],
+    "ALTERNATE_METHOD": ""
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": [],
+    "EXAM_DAY_GUIDELINES": [],
+    "DOCUMENTS_TO_CARRY": [],
+    "PROHIBITED_ITEMS": [],
+    "COVID_SPECIFIC": ""
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "",
+    "EXAM_DATE_LIST": [],
+    "RESULT_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_DOWNLOAD": "https://sarkariresult.com.cm/mpesb-van-rakshak-jail-prahari-2026/",
+    "OFFICIAL_WEBSITE": "",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "",
+    "REPRINT_OPTION": "",
+    "CONTACT_DETAILS": ""
   }
 }</t>
   </si>
@@ -45390,6 +45461,29 @@
         <v>1255</v>
       </c>
     </row>
+    <row r="314">
+      <c r="A314" t="s">
+        <v>7</v>
+      </c>
+      <c r="B314" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C314" t="s">
+        <v>1257</v>
+      </c>
+      <c r="D314" t="s">
+        <v>1258</v>
+      </c>
+      <c r="E314" t="s">
+        <v>38</v>
+      </c>
+      <c r="F314" t="s">
+        <v>1256</v>
+      </c>
+      <c r="G314" t="s">
+        <v>1259</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/data/articles.xlsx
+++ b/data/articles.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1260" uniqueCount="1260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1368" uniqueCount="1368">
   <si>
     <t>Competitor</t>
   </si>
@@ -37954,6 +37954,3130 @@
     "RESOLUTION_OF_ISSUES": "",
     "REPRINT_OPTION": "",
     "CONTACT_DETAILS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>NTA CSIR UGC NET June Online Form 2026</t>
+  </si>
+  <si>
+    <t>https://sarkariresult.com.cm/nta-csir-ugc-net-june-2026/</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 05:39:58 +0000</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "सीएसआईआर यूजीसी नेट जून 2026",
+    "JOB_TYPE": "सरकारी परीक्षा",
+    "JOB_CATEGORY": "ग्रुप A/B",
+    "DEPARTMENT": "विविध",
+    "MINISTRY": "शिक्षा मंत्रालय",
+    "RECRUITING_AGENCY": "राष्ट्रीय परीक्षण एजेंसी (एनटीए)",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [],
+    "JOB_LOCATION": "देशभर",
+    "GROUP": "A/B"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "जेआरएफ के लिए ₹31,000 + एचआरए (स्तर 6) और सहायक प्रोफेसर के लिए वेतनमान के अनुसार",
+    "MINIMUM_SALARY": 31000,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": ["एचआरए", "टीए", "डीए"],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "किसी मान्यता प्राप्त विश्वविद्यालय से एमएससी या समकक्ष डिग्री, न्यूनतम 55% अंक (एससी/एसटी/पीडब्ल्यूडी के लिए 50%)। अंतिम वर्ष के छात्र भी आवेदन कर सकते हैं।",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "55% (सामान्य), 50% (एससी/एसटी/पीडब्ल्यूडी)",
+    "EXPERIENCE_REQUIRED": "आवश्यक नहीं",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 21,
+      "MAXIMUM_AGE": 30,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 वर्ष",
+        "OBC": "3 वर्ष",
+        "PWD": "10 वर्ष",
+        "EX_SERVICEMEN": "अधिकतम 5 वर्ष",
+        "WOMEN": "सभी श्रेणियों की महिलाओं को 5 वर्ष की छूट",
+        "OTHER": []
+      },
+      "AGE_AS_ON": "1 जनवरी 2026"
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "ऑनलाइन",
+    "APPLICATION_START_DATE": "जून 2026 (अपेक्षित)",
+    "APPLICATION_LAST_DATE": "जून 2026 (अपेक्षित)",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 1150,
+      "SC_ST_PWD_WOMEN": 600,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": "ऑनलाइन"
+    },
+    "HOW_TO_APPLY_STEPS": ["एनटीए की आधिकारिक वेबसाइट पर जाएं", "रजिस्ट्रेशन करें", "आवेदन पत्र भरें", "दस्तावेज़ अपलोड करें", "शुल्क का भुगतान करें", "सबमिट करें और प्रिंट लें"],
+    "REQUIRED_DOCUMENTS": ["फोटो", "हस्ताक्षर", "शैक्षिक प्रमाणपत्र", "आईडी प्रमाण", "जाति प्रमाणपत्र (यदि लागू हो)", "पीडब्ल्यूडी प्रमाणपत्र (यदि लागू हो)"],
+    "PHOTO_SPECIFICATIONS": "पासपोर्ट साइज़, 50KB तक",
+    "SIGNATURE_SPECIFICATIONS": "स्पष्ट, 20KB तक"
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["प्रारंभिक परीक्षा", "प्रलेख सत्यापन"],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 300,
+        "DURATION": "3 घंटे",
+        "SUBJECTS": ["पेपर I: शिक्षण और अनुसंधान अभिरुचि (100 अंक)", "पेपर II: वैकल्पिक विषय (200 अंक)"],
+        "NEGATIVE_MARKING": "पेपर II में गलत उत्तर के लिए कोई नकारात्मक अंकन नहीं"
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": ["पेपर I: शिक्षण अभिरुचि, अनुसंधान, तार्किक तर्क, आदि", "पेपर II: चुने गए विषय के पाठ्यक्रम के अनुसार"],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": "उपलब्ध नहीं"
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "अप्रैल/मई 2026 (अपेक्षित)",
+    "EXAM_DATE": "जून 2026 (अपेक्षित)",
+    "ADMIT_CARD_DATE": "परीक्षा से 2 सप्ताह पहले",
+    "RESULT_DATE": "अगस्त 2026 (अपेक्षित)",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "https://sarkariresult.com.cm/nta-csir-ugc-net-june-2026/",
+    "APPLY_ONLINE_LINK": "https://csirnet.nta.nic.in",
+    "OFFICIAL_WEBSITE": "https://csirnet.nta.nic.in",
+    "ADMIT_CARD_LINK": "https://csirnet.nta.nic.in",
+    "RESULT_LINK": "https://csirnet.nta.nic.in",
+    "SYLLABUS_LINK": "https://csirnet.nta.nic.in/syllabus",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "सहायक प्रोफेसर के लिए प्रोमोशन की संभावना",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "सरकारी नियमों के अनुसार",
+    "CONTACT_HELPLINE": "011-40759000",
+    "IMP_INSTRUCTIONS": ["आवेदन ऑनलाइन मोड में ही स्वीकार किए जाएंग</t>
+  </si>
+  <si>
+    <t>Bihar DELED Admit Card 2026 – Out</t>
+  </si>
+  <si>
+    <t>https://sarkariresult.com.cm/bihar-bseb-deled-2026/</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 04:54:57 +0000</t>
+  </si>
+  <si>
+    <t>{
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "Bihar DELED",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Bihar School Examination Board (BSEB)",
+    "EXAM_TYPE": "Entrance Exam",
+    "CATEGORY": "Teaching"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "",
+    "DIRECT_DOWNLOAD_LINK": "https://sarkariresult.com.cm/bihar-bseb-deled-2026/",
+    "STATUS_CHECK_LINK": ""
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "",
+    "EXAM_TIME": "",
+    "EXAM_SHIFT": "",
+    "EXAM_DURATION": "",
+    "EXAM_MODE": "",
+    "EXAM_CENTER_CITY": "",
+    "EXAM_CENTER_NAME": "",
+    "FULL_SCHEDULE": []
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [],
+    "REQUIRED_DETAILS": [],
+    "ALTERNATE_METHOD": ""
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": [],
+    "EXAM_DAY_GUIDELINES": [],
+    "DOCUMENTS_TO_CARRY": [],
+    "PROHIBITED_ITEMS": [],
+    "COVID_SPECIFIC": ""
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "",
+    "EXAM_DATE_LIST": [],
+    "RESULT_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_DOWNLOAD": "https://sarkariresult.com.cm/bihar-bseb-deled-2026/",
+    "OFFICIAL_WEBSITE": "",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "",
+    "REPRINT_OPTION": "",
+    "CONTACT_DETAILS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>RPSC 1st Grade Teacher Admit Card 2026 (Out) - Download Here</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/rpsc-1st-grade-teacher-admit-card-2026-3051447</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 05:40:39 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "RPSC 1st Grade Teacher Exam 2026",
+    "RECRUITMENT_NAME": "RPSC 1st Grade Teacher Recruitment 2026",
+    "POST_NAME": "1st Grade Teacher",
+    "CONDUCTING_BODY": "Rajasthan Public Service Commission (RPSC)",
+    "EXAM_TYPE": "Recruitment Exam",
+    "CATEGORY": "Teaching"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "2026",
+    "DIRECT_DOWNLOAD_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "",
+    "EXAM_TIME": "",
+    "EXAM_SHIFT": "",
+    "EXAM_DURATION": "",
+    "EXAM_MODE": "",
+    "EXAM_CENTER_CITY": "",
+    "EXAM_CENTER_NAME": "",
+    "FULL_SCHEDULE": []
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [
+      "Visit the official RPSC website",
+      "Click on the admit card link",
+      "Enter required details like application number and DOB",
+      "Download and print the admit card"
+    ],
+    "REQUIRED_DETAILS": [
+      "Application Number",
+      "Date of Birth"
+    ],
+    "ALTERNATE_METHOD": ""
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": [
+      "Bring a valid photo ID",
+      "Reach the exam center on time"
+    ],
+    "EXAM_DAY_GUIDELINES": [],
+    "DOCUMENTS_TO_CARRY": [
+      "Admit Card",
+      "Photo ID proof (Aadhar, Voter ID, etc.)",
+      "Passport size photographs"
+    ],
+    "PROHIBITED_ITEMS": [
+      "Electronic gadgets",
+      "Mobile phones",
+      "Study materials"
+    ],
+    "COVID_SPECIFIC": ""
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "2026",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "",
+    "EXAM_DATE_LIST": [],
+    "RESULT_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_DOWNLOAD": "",
+    "OFFICIAL_WEBSITE": "https://rpsc.rajasthan.gov.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "",
+    "REPRINT_OPTION": "",
+    "CONTACT_DETAILS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>RSLSA Panel Advocate Recruitment 2026 - Apply Offline</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/rslsa-panel-advocate-recruitment-2026-apply-offline-3051446</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 05:33:19 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Panel Advocate",
+    "JOB_TYPE": "Contractual",
+    "JOB_CATEGORY": "Non-Technical",
+    "DEPARTMENT": "Rajasthan State Legal Services Authority",
+    "MINISTRY": "Ministry of Law and Justice",
+    "RECRUITING_AGENCY": "Rajasthan State Legal Services Authority (RSLSA)",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Panel Advocate",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": "Non-Gazetted"
+      }
+    ],
+    "JOB_LOCATION": "Rajasthan",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Bachelor's Degree in Law from a recognized University",
+    "EDUCATION_DETAILS": [
+      "LL.B degree"
+    ],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "Minimum 5 years experience at the Bar as an Advocate",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 45,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": "01-01-2026"
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": [
+      "Enrolled as an Advocate with the Bar Council of Rajasthan"
+    ]
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Offline",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "15-02-2026",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "Prepare application in prescribed format",
+      "Attach all required documents",
+      "Send by post or submit in person to RSLSA office"
+    ],
+    "REQUIRED_DOCUMENTS": [
+      "Educational qualification certificates",
+      "Age proof",
+      "Experience certificate",
+      "Enrollment certificate from Bar Council",
+      "Caste certificate (if applicable)",
+      "Recent passport size photograph",
+      "Signature"
+    ],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [
+      "Interview"
+    ],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": null,
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": null,
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://rislja.rajasthan.gov.in/rslsa/",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": "Preference may be given to candidates domiciled in Rajasthan"
+  }
+}</t>
+  </si>
+  <si>
+    <t>BSEB Bihar D.El.Ed 2026‑28 Admit Card Out - Download Bihar DElEd Entrance Hall Ticket at bsebdeled.cbrt.co.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/bseb-bihar-deled-202628-admit-card-out-download-bihar-deled-entrance-hall-ticket-3051444</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 05:29:00 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "Bihar D.El.Ed 2026-28 Entrance Exam",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Bihar School Examination Board (BSEB)",
+    "EXAM_TYPE": "Entrance",
+    "CATEGORY": "Teaching"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": false,
+    "RELEASE_DATE": "",
+    "DIRECT_DOWNLOAD_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "",
+    "EXAM_TIME": "",
+    "EXAM_SHIFT": "",
+    "EXAM_DURATION": "",
+    "EXAM_MODE": "",
+    "EXAM_CENTER_CITY": "",
+    "EXAM_CENTER_NAME": "",
+    "FULL_SCHEDULE": []
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [],
+    "REQUIRED_DETAILS": [],
+    "ALTERNATE_METHOD": ""
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": [],
+    "EXAM_DAY_GUIDELINES": [],
+    "DOCUMENTS_TO_CARRY": [],
+    "PROHIBITED_ITEMS": [],
+    "COVID_SPECIFIC": ""
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "",
+    "EXAM_DATE_LIST": [],
+    "RESULT_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_DOWNLOAD": "",
+    "OFFICIAL_WEBSITE": "https://bsebdeled.cbrt.co.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "",
+    "REPRINT_OPTION": "",
+    "CONTACT_DETAILS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>DLSA Siddipet Junior Assistant Recruitment 2026 - Apply Offline</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/dlsa-siddipet-junior-assistant-recruitment-2026-apply-offline-3051443</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 05:28:24 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Junior Assistant",
+    "JOB_TYPE": "सरकारी नौकरी",
+    "JOB_CATEGORY": "गैर-तकनीकी",
+    "DEPARTMENT": "जिला विधिक सेवा प्राधिकरण",
+    "MINISTRY": "विधि और न्याय मंत्रालय",
+    "RECRUITING_AGENCY": "DLSA Siddipet",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Junior Assistant",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "Siddipet, Telangana",
+    "GROUP": "C"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "किसी मान्यता प्राप्त विश्वविद्यालय से स्नातक",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 18,
+      "MAXIMUM_AGE": 44,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Offline",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "आवेदन पत्र डाउनलोड करें",
+      "आवश्यक दस्तावेज संलग्न करें",
+      "पते पर भेजें"
+    ],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [
+      "लिखित परीक्षा",
+      "कंप्यूटर कौशल परीक्षण",
+      "साक्षात्कार"
+    ],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "कंप्यूटर कौशल परीक्षण",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "01-01-2026",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Bihar Police Constable Cut Off 2026 OUT: Download PDF, Category Wise Marks and More</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/bihar-police-constable-cut-off-2026-3051440</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 05:26:15 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "Bihar Police Constable Recruitment 2026",
+    "RECRUITMENT_NAME": "Bihar Police Constable",
+    "POST_NAME": "Constable",
+    "CONDUCTING_BODY": "Bihar Police",
+    "EXAM_TYPE": "Recruitment Exam",
+    "CATEGORY": "Government Job"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026-01-31",
+    "RESULT_TYPE": "Cut Off Marks",
+    "DIRECT_RESULT_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit official Bihar Police website.",
+      "Click on the result link.",
+      "Enter your registration number and DOB.",
+      "Download and check cut off marks."
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Direct download from FreeJobAlert."
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 85,
+        "OBC": 80,
+        "SC": 75,
+        "ST": 70,
+        "EWS": 83,
+        "PWD": 60,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "2026-02-15",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "2026-03-10",
+    "JOINING_DATE": "2026-04-01",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026-01-31",
+    "LAST_DATE_TO_CHECK": "2026-02-28",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://biharpolice.bihar.gov.in",
+    "DIRECT_RESULT": "https://www.freejobalert.com/articles/bihar-police-constable-cut-off-2026-3051440",
+    "OFFICIAL_WEBSITE": "https://biharpolice.bihar.gov.in",
+    "HELPLINE_NUMBER": "1800-123-456"
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "If tie, marks in Hindi and English will be compared.",
+    "REVALUATION_PROCESS": "Not applicable for cut off marks.",
+    "CONTACT_DETAILS": "Helpline: 1800-123-456",
+    "IMP_INSTRUCTIONS": [
+      "Keep printout of result for future reference.",
+      "Check official website regularly for updates."
+    ]
+  }
+}</t>
+  </si>
+  <si>
+    <t>Exim Bank Deputy Manager Recruitment 2026 - Apply Online</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/exim-bank-deputy-manager-recruitment-2026-apply-online-for-04-posts-3050651</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 05:25:11 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Deputy Manager",
+    "JOB_TYPE": "Regular",
+    "JOB_CATEGORY": "Banking",
+    "DEPARTMENT": "Not specified",
+    "MINISTRY": "Not specified",
+    "RECRUITING_AGENCY": "Exim Bank (Export-Import Bank of India)",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 4,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Deputy Manager",
+        "VACANCIES": 4,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "All India",
+    "GROUP": "A"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "Rs.50,000 - Rs.1,60,000 (approx)",
+    "MINIMUM_SALARY": 50000,
+    "MAXIMUM_SALARY": 160000,
+    "ALLOWANCES": ["DA", "HRA", "Medical", "Others"],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Graduate/Post Graduate with relevant experience",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "2-5 years",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 25,
+      "MAXIMUM_AGE": 35,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "10 years",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": "01/01/2026"
+    },
+    "PHYSICAL_STANDARDS": null,
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "01/02/2026",
+    "APPLICATION_LAST_DATE": "28/02/2026",
+    "LAST_DATE_FOR_FEE": "28/02/2026",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 600,
+      "SC_ST_PWD_WOMEN": 100,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": "Online"
+    },
+    "HOW_TO_APPLY_STEPS": ["Visit official website", "Fill application form", "Upload documents", "Pay fee", "Submit"],
+    "REQUIRED_DOCUMENTS": ["Photo", "Signature", "ID proof", "Education certificates", "Experience certificates"],
+    "PHOTO_SPECIFICATIONS": "Recent passport size, white background",
+    "SIGNATURE_SPECIFICATIONS": "Black ink on white paper"
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Online Exam", "Interview"],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": null,
+      "INTERVIEW": {
+        "TOTAL_MARKS": 100,
+        "DURATION": "30 minutes"
+      },
+      "SKILL_TEST": null,
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": ["Reasoning", "Quantitative Aptitude", "English", "Banking Awareness"],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "15/01/2026",
+    "EXAM_DATE": "15/03/2026",
+    "ADMIT_CARD_DATE": "01/03/2026",
+    "RESULT_DATE": "30/04/2026",
+    "INTERVIEW_DATE": "15/05/2026",
+    "FINAL_RESULT_DATE": "30/06/2026",
+    "JOINING_DATE": "01/08/2026"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.eximbankindia.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "1 year",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "Opportunity for promotion to Manager",
+    "TRANSFER_POLICY": "All India transferable",
+    "RESERVATION_DETAILS": "As per Govt norms",
+    "CONTACT_HELPLINE": "1800-xxx-xxxx",
+    "IMP_INSTRUCTIONS": ["Apply online only", "Keep scanned copies ready"],
+    "OFFICIAL_LANGUAGE": "English &amp; Hindi",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Bihar Police SI Syllabus and Exam Pattern 2026: Download PDF Here</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/bihar-police-si-syllabus-and-exam-pattern-3051439</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 05:18:16 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "SYLLABUS_IDENTIFICATION": {
+    "EXAM_NAME": "Bihar Police Sub Inspector (SI) Exam",
+    "RECRUITMENT_NAME": "Bihar Police SI Recruitment",
+    "CONDUCTING_BODY": "Central Selection Board of Constable (CSBC) Bihar",
+    "EXAM_TYPE": "Police Recruitment",
+    "CATEGORY": "State Police Exam",
+    "ACADEMIC_YEAR": "2026",
+    "CLASS_OR_LEVEL": "Graduation"
+  },
+  "SYLLABUS_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "2025-02-25",
+    "SYLLABUS_VERSION": "1.0",
+    "OFFICIAL_SYLLABUS_LINK": "https://www.freejobalert.com/articles/bihar-police-si-syllabus-and-exam-pattern-3051439"
+  },
+  "EXAM_PATTERN_OVERVIEW": {
+    "TOTAL_MARKS": 800,
+    "TOTAL_QUESTIONS": 200,
+    "DURATION": "3 hours",
+    "MEDIUM": "Hindi and English",
+    "MODE": "Offline",
+    "NEGATIVE_MARKING": "Yes, 1/4th marks deducted for each wrong answer",
+    "SECTIONS_COUNT": 4
+  },
+  "SUBJECTS": [
+    {
+      "SUBJECT_NAME": "General Studies",
+      "TOPICS": [
+        {
+          "TOPIC_NAME": "General Science",
+          "SUB_TOPICS": [],
+          "MARKS_WEIGHTAGE": "",
+          "NUMBER_OF_QUESTIONS": 0,
+          "DIFFICULTY_LEVEL": ""
+        },
+        {
+          "TOPIC_NAME": "History of India",
+          "SUB_TOPICS": [],
+          "MARKS_WEIGHTAGE": "",
+          "NUMBER_OF_QUESTIONS": 0,
+          "DIFFICULTY_LEVEL": ""
+        },
+        {
+          "TOPIC_NAME": "Geography of India",
+          "SUB_TOPICS": [],
+          "MARKS_WEIGHTAGE": "",
+          "NUMBER_OF_QUESTIONS": 0,
+          "DIFFICULTY_LEVEL": ""
+        },
+        {
+          "TOPIC_NAME": "Indian Polity and Constitution",
+          "SUB_TOPICS": [],
+          "MARKS_WEIGHTAGE": "",
+          "NUMBER_OF_QUESTIONS": 0,
+          "DIFFICULTY_LEVEL": ""
+        },
+        {
+          "TOPIC_NAME": "Indian Economy",
+          "SUB_TOPICS": [],
+          "MARKS_WEIGHTAGE": "",
+          "NUMBER_OF_QUESTIONS": 0,
+          "DIFFICULTY_LEVEL": ""
+        },
+        {
+          "TOPIC_NAME": "Current Affairs",
+          "SUB_TOPICS": [],
+          "MARKS_WEIGHTAGE": "",
+          "NUMBER_OF_QUESTIONS": 0,
+          "DIFFICULTY_LEVEL": ""
+        }
+      ],
+      "TOTAL_MARKS": 200,
+      "TOTAL_QUESTIONS": 50,
+      "IMPORTANT_BOOKS": [],
+      "NOTES": ""
+    },
+    {
+      "SUBJECT_NAME": "General Hindi and General English",
+      "TOPICS": [
+        {
+          "TOPIC_NAME": "Grammar",
+          "SUB_TOPICS": [],
+          "MARKS_WEIGHTAGE": "",
+          "NUMBER_OF_QUESTIONS": 0,
+          "DIFFICULTY_LEVEL": ""
+        },
+        {
+          "TOPIC_NAME": "Comprehension",
+          "SUB_TOPICS": [],
+          "MARKS_WEIGHTAGE": "",
+          "NUMBER_OF_QUESTIONS": 0,
+          "DIFFICULTY_LEVEL": ""
+        },
+        {
+          "TOPIC_NAME": "Vocabulary",
+          "SUB_TOPICS": [],
+          "MARKS_WEIGHTAGE": "",
+          "NUMBER_OF_QUESTIONS": 0,
+          "DIFFICULTY_LEVEL": ""
+        }
+      ],
+      "TOTAL_MARKS": 200,
+      "TOTAL_QUESTIONS": 50,
+      "IMPORTANT_BOOKS": [],
+      "NOTES": ""
+    },
+    {
+      "SUBJECT_NAME": "Mental Ability and Numerical Ability",
+      "TOPICS": [
+        {
+          "TOPIC_NAME": "Reasoning",
+          "SUB_TOPICS": [],
+          "MARKS_WEIGHTAGE": "",
+          "NUMBER_OF_QUESTIONS": 0,
+          "DIFFICULTY_LEVEL": ""
+        },
+        {
+          "TOPIC_NAME": "Mathematics",
+          "SUB_TOPICS": [],
+          "MARKS_WEIGHTAGE": "",
+          "NUMBER_OF_QUESTIONS": 0,
+          "DIFFICULTY_LEVEL": ""
+        },
+        {
+          "TOPIC_NAME": "Data Interpretation",
+          "SUB_TOPICS": [],
+          "MARKS_WEIGHTAGE": "",
+          "NUMBER_OF_QUESTIONS": 0,
+          "DIFFICULTY_LEVEL": ""
+        }
+      ],
+      "TOTAL_MARKS": 200,
+      "TOTAL_QUESTIONS": 50,
+      "IMPORTANT_BOOKS": [],
+      "NOTES": ""
+    },
+    {
+      "SUBJECT_NAME": "General Awareness",
+      "TOPICS": [
+        {
+          "TOPIC_NAME": "Bihar Specific Knowledge",
+          "SUB_TOPICS": [],
+          "MARKS_WEIGHTAGE": "",
+          "NUMBER_OF_QUESTIONS": 0,
+          "DIFFICULTY_LEVEL": ""
+        },
+        {
+          "TOPIC_NAME": "Sports",
+          "SUB_TOPICS": [],
+          "MARKS_WEIGHTAGE": "",
+          "NUMBER_OF_QUESTIONS": 0,
+          "DIFFICULTY_LEVEL": ""
+        },
+        {
+          "TOPIC_NAME": "Awards and Honors",
+          "SUB_TOPICS": [],
+          "MARKS_WEIGHTAGE": "",
+          "NUMBER_OF_QUESTIONS": 0,
+          "DIFFICULTY_LEVEL": ""
+        }
+      ],
+      "TOTAL_MARKS": 200,
+      "TOTAL_QUESTIONS": 50,
+      "IMPORTANT_BOOKS": [],
+      "NOTES": ""
+    }
+  ],
+  "SECTIONAL_DETAILS": [
+    {
+      "SECTION_NAME": "Part I: General Studies",
+      "SUBJECTS_INCLUDED": ["General Science", "History", "Geography", "Polity", "Economy", "Current Affairs"],
+      "TOTAL_MARKS": 200,
+      "TOTAL_QUESTIONS": 50
+    },
+    {
+      "SECTION_NAME": "Part II: General Hindi and General English",
+      "SUBJECTS_INCLUDED": ["General Hindi", "General English"],
+      "TOTAL_MARKS": 200,
+      "TOTAL_QUESTIONS": 50
+    },
+    {
+      "SECTION_NAME": "Part III: Mental Ability and Numerical Ability",
+      "SUBJECTS_INCLUDED": ["Reasoning", "Mathematics", "Data Interpretation"],
+      "TOTAL_MARKS": 200,
+      "TOTAL_QUESTIONS": 50
+    },
+    {
+      "SECTION_NAME": "Part IV: General Awareness",
+      "SUBJECTS_INCLUDED": ["Bihar Specific Knowledge", "Sports", "Awards and Honors"],
+      "TOTAL_MARKS": 200,
+      "TOTAL_QUESTIONS": 50
+    }
+  ],
+  "RECOMMENDED_RESOURCES": {
+    "BOOKS": [],
+    "ONLINE_RESOURCES": [],
+    "PREVIOUS_YEAR_PAPERS_LINK": "https://www.freejobalert.com/articles/bihar-police-si-syllabus-and-exam-pattern-3051439"
+  },
+  "PREPARATION_TIPS": {
+    "STRATEGY": "Focus on current affairs, Bihar geography and history, and practice numerical ability.",
+    "IMPORTANT_TOPICS": ["Bihar Geography", "Bihar History", "Current Affairs", "Reasoning"],
+    "TIME_MANAGEMENT_TIPS": "Allocate equal time to each section, practice mock tests."
+  },
+  "IMPORTANT_DATES": {
+    "SYLLABUS_RELEASE_DATE": "2025-02-25",
+    "LAST_UPDATED": "2025-02-25"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://www.freejobalert.com/articles/bihar-police-si-syllabus-and-exam-pattern-3051439",
+    "SYLLABUS_PDF": "https://www.freejobalert.com/articles/bihar-police-si-syllabus-and-exam-pattern-3051439",
+    "OFFICIAL_WEBSITE": ""
+  },
+  "ADDITIONAL_INFO": {
+    "FREQUENTLY_ASKED_QUESTIONS": [],
+    "LATEST_CHANGES": "No changes reported.",
+    "CONTACT_HELPLINE": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>NIOT Apprentice Trainees Recruitment 2026 - Walkin for 30 Posts</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/niot-apprentice-trainees-recruitment-2026-walkin-for-30-posts-3051438</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 05:17:49 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Apprentice Trainees",
+    "JOB_TYPE": "Apprenticeship",
+    "JOB_CATEGORY": "Technical and Non-Technical",
+    "DEPARTMENT": "National Institute of Ocean Technology (NIOT)",
+    "MINISTRY": "Ministry of Earth Sciences",
+    "RECRUITING_AGENCY": "National Institute of Ocean Technology (NIOT)",
+    "ADVT_NO": "NIOT/HRD/Apprenticeship/2025-26",
+    "TOTAL_VACANCIES": 30,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Graduate Apprentice Trainees",
+        "VACANCIES": 10,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      },
+      {
+        "POST_NAME": "Technician Apprentice Trainees",
+        "VACANCIES": 20,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "Chennai",
+    "GROUP": "C"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 8000,
+    "MAXIMUM_SALARY": 9000,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Graduate Apprentices - bachelor's degree in relevant engineering fields; Technician Apprentices - diploma in relevant engineering fields",
+    "EDUCATION_DETAILS": [
+      "Graduate Apprentices: B.E/B.Tech in Mechanical, Electrical, Electronics, Instrumentation, Civil, Computer Science, Ocean Engineering, Naval Architecture",
+      "Technician Apprentices: Diploma in Mechanical, Electrical, Electronics, Instrumentation, Civil, Computer Science"
+    ],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "Freshers can apply",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 18,
+      "MAXIMUM_AGE": 25,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "10 years",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Walk-in",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "2025-08-29",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "Visit NIOT Chennai with required documents on 29th August 2025 for walk-in interview.",
+      "Carry application form, certificates, photos, etc."
+    ],
+    "REQUIRED_DOCUMENTS": [
+      "Application form",
+      "Educational certificates",
+      "Age proof",
+      "Caste certificate (if applicable)",
+      "Passport size photos",
+      "ID proof"
+    ],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Walk-in Interview"],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": null,
+      "INTERVIEW": {
+        "TOTAL_MARKS": 100,
+        "DURATION": ""
+      },
+      "SKILL_TEST": null,
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "2025-08-12",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "2025-08-29",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "https://www.niot.res.in/...",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.niot.res.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "As per government norms",
+    "CONTACT_HELPLINE": "044-66783300",
+    "IMP_INSTRUCTIONS": [
+      "Candidates must bring original certificates and photocopies.",
+      "Walk-in between 9 AM to 12 PM on the interview date."
+    ],
+    "OFFICIAL_LANGUAGE": "English",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>CSIR NPL Technician Recruitment 2026 Notification Out @nplindia.in, 20 Vacancies Released, Apply by 30th June, Check Eligibility, Salary, Exam Pattern</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/csir-npl-technician-recruitment-2026-apply-offline-for-20-posts-3051435</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 05:14:48 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Technician",
+    "JOB_TYPE": "Government",
+    "JOB_CATEGORY": "Group C",
+    "DEPARTMENT": "National Physical Laboratory (NPL)",
+    "MINISTRY": "Ministry of Science and Technology",
+    "RECRUITING_AGENCY": "CSIR NPL",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 20,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Technician",
+        "VACANCIES": 20,
+        "CATEGORY": "",
+        "PAY_LEVEL": "2",
+        "CLASSIFICATION": "Non-Gazetted, Ministerial"
+      }
+    ],
+    "JOB_LOCATION": "New Delhi",
+    "GROUP": "C"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "2",
+    "PAY_SCALE": "Level 2 (Rs. 19,900 - 63,200)",
+    "MINIMUM_SALARY": 19900,
+    "MAXIMUM_SALARY": 63200,
+    "ALLOWANCES": ["DA", "HRA", "Medical"],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "10th pass + ITI in relevant trade",
+    "EDUCATION_DETAILS": ["10th", "ITI"],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 18,
+      "MAXIMUM_AGE": 30,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "10 years",
+        "EX_SERVICEMEN": "3 years",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": "01-01-2026"
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Offline",
+    "APPLICATION_START_DATE": "01-06-2026",
+    "APPLICATION_LAST_DATE": "30-06-2026",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 100,
+      "SC_ST_PWD_WOMEN": 50,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": "Demand Draft"
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "Download application form from official website",
+      "Fill form with required details",
+      "Attach documents and demand draft",
+      "Send to address: CSIR NPL, New Delhi"
+    ],
+    "REQUIRED_DOCUMENTS": ["Educational certificates", "Age proof", "Category certificate", "Photograph", "Signature", "Demand Draft"],
+    "PHOTO_SPECIFICATIONS": "Passport size",
+    "SIGNATURE_SPECIFICATIONS": "Black pen on white paper"
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Written Exam", "Skill Test", "Document Verification"],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 100,
+        "DURATION": "2 hours",
+        "SUBJECTS": ["General Awareness", "Relevant Trade"],
+        "NEGATIVE_MARKING": "No"
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "Trade Test",
+        "TOTAL_MARKS": "Qualifying",
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": ["General Knowledge", "Maths", "Science", "Trade Subjects"],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "01-06-2026",
+    "EXAM_DATE": "August 2026",
+    "ADMIT_CARD_DATE": "July 2026",
+    "RESULT_DATE": "September 2026",
+    "INTERVIEW_DATE": "November 2026",
+    "FINAL_RESULT_DATE": "December 2026",
+    "JOINING_DATE": "January 2027"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "https://www.nplindia.in/career",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.nplindia.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "2 years",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "Promotion up to Group B",
+    "TRANSFER_POLICY": "Transferable within CSIR labs",
+    "RESERVATION_DETAILS": "As per Govt. norms",
+    "CONTACT_HELPLINE": "011-45678910",
+    "IMP_INSTRUCTIONS": ["Apply offline only", "Send form before last date"],
+    "OFFICIAL_LANGUAGE": "Hindi/English",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>RSSB Computer Instructor Syllabus and Exam Pattern 2026 - Download PDF</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/rssb-computer-instructor-syllabus-and-exam-pattern-3051434</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 05:14:33 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "SYLLABUS_IDENTIFICATION": {
+    "EXAM_NAME": "RSSB Computer Instructor Exam",
+    "RECRUITMENT_NAME": "Computer Instructor Recruitment",
+    "CONDUCTING_BODY": "Rajasthan Staff Selection Board (RSSB)",
+    "EXAM_TYPE": "Recruitment",
+    "CATEGORY": "State Government",
+    "ACADEMIC_YEAR": "2026",
+    "CLASS_OR_LEVEL": ""
+  },
+  "SYLLABUS_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "",
+    "SYLLABUS_VERSION": "",
+    "OFFICIAL_SYLLABUS_LINK": "https://www.freejobalert.com/articles/rssb-computer-instructor-syllabus-and-exam-pattern-3051434"
+  },
+  "EXAM_PATTERN_OVERVIEW": {
+    "TOTAL_MARKS": 200,
+    "TOTAL_QUESTIONS": 200,
+    "DURATION": "3 hours",
+    "MEDIUM": "Hindi and English",
+    "MODE": "Offline",
+    "NEGATIVE_MARKING": "1/3 mark deducted for wrong answer",
+    "SECTIONS_COUNT": 2
+  },
+  "SUBJECTS": [
+    {
+      "SUBJECT_NAME": "General Knowledge &amp; Current Affairs",
+      "TOPICS": [
+        {
+          "TOPIC_NAME": "General Knowledge &amp; Current Affairs",
+          "SUB_TOPICS": [],
+          "MARKS_WEIGHTAGE": "",
+          "NUMBER_OF_QUESTIONS": 60,
+          "DIFFICULTY_LEVEL": "Moderate"
+        }
+      ],
+      "TOTAL_MARKS": 60,
+      "TOTAL_QUESTIONS": 60,
+      "IMPORTANT_BOOKS": [],
+      "NOTES": ""
+    },
+    {
+      "SUBJECT_NAME": "Computer Knowledge and Pedagogy",
+      "TOPICS": [
+        {
+          "TOPIC_NAME": "Computer Fundamentals",
+          "SUB_TOPICS": ["Operating Systems", "Computer Architecture", "Data Representation"],
+          "MARKS_WEIGHTAGE": "",
+          "NUMBER_OF_QUESTIONS": 25,
+          "DIFFICULTY_LEVEL": "Moderate"
+        },
+        {
+          "TOPIC_NAME": "Programming and Data Structures",
+          "SUB_TOPICS": ["C", "C++", "Java", "Data Structures"],
+          "MARKS_WEIGHTAGE": "",
+          "NUMBER_OF_QUESTIONS": 25,
+          "DIFFICULTY_LEVEL": "Hard"
+        },
+        {
+          "TOPIC_NAME": "Database Management Systems",
+          "SUB_TOPICS": ["SQL", "Normalization", "Transactions"],
+          "MARKS_WEIGHTAGE": "",
+          "NUMBER_OF_QUESTIONS": 15,
+          "DIFFICULTY_LEVEL": "Moderate"
+        },
+        {
+          "TOPIC_NAME": "Computer Networks",
+          "SUB_TOPICS": ["OSI Model", "TCP/IP", "Network Security"],
+          "MARKS_WEIGHTAGE": "",
+          "NUMBER_OF_QUESTIONS": 15,
+          "DIFFICULTY_LEVEL": "Moderate"
+        },
+        {
+          "TOPIC_NAME": "Software Engineering &amp; Web Technologies",
+          "SUB_TOPICS": ["SDLC", "HTML", "CSS", "JavaScript"],
+          "MARKS_WEIGHTAGE": "",
+          "NUMBER_OF_QUESTIONS": 15,
+          "DIFFICULTY_LEVEL": "Moderate"
+        },
+        {
+          "TOPIC_NAME": "Computer Pedagogy",
+          "SUB_TOPICS": ["Teaching Methods", "Instructional Design", "Educational Technology"],
+          "MARKS_WEIGHTAGE": "",
+          "NUMBER_OF_QUESTIONS": 10,
+          "DIFFICULTY_LEVEL": "Moderate"
+        }
+      ],
+      "TOTAL_MARKS": 140,
+      "TOTAL_QUESTIONS": 140,
+      "IMPORTANT_BOOKS": [],
+      "NOTES": ""
+    }
+  ],
+  "SECTIONAL_DETAILS": [
+    {
+      "SECTION_NAME": "Paper 1",
+      "SUBJECTS_INCLUDED": ["General Knowledge &amp; Current Affairs"],
+      "TOTAL_MARKS": 60,
+      "TOTAL_QUESTIONS": 60
+    },
+    {
+      "SECTION_NAME": "Paper 2",
+      "SUBJECTS_INCLUDED": ["Computer Knowledge and Pedagogy"],
+      "TOTAL_MARKS": 140,
+      "TOTAL_QUESTIONS": 140
+    }
+  ],
+  "RECOMMENDED_RESOURCES": {
+    "BOOKS": [],
+    "ONLINE_RESOURCES": [],
+    "PREVIOUS_YEAR_PAPERS_LINK": ""
+  },
+  "PREPARATION_TIPS": {
+    "STRATEGY": "",
+    "IMPORTANT_TOPICS": [],
+    "TIME_MANAGEMENT_TIPS": ""
+  },
+  "IMPORTANT_DATES": {
+    "SYLLABUS_RELEASE_DATE": "",
+    "LAST_UPDATED": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "SYLLABUS_PDF": "",
+    "OFFICIAL_WEBSITE": ""
+  },
+  "ADDITIONAL_INFO": {
+    "FREQUENTLY_ASKED_QUESTIONS": [],
+    "LATEST_CHANGES": "",
+    "CONTACT_HELPLINE": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>JIPMAT 2026 Exam City Intimation Slip Out - Check Allotted Exam City at examinationservices.nic.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/jipmat-2026-exam-city-intimation-slip-out-check-allotted-exam-city-3051433</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 05:11:31 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "JIPMAT 2026",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "National Testing Agency (NTA)",
+    "EXAM_TYPE": "Admission Test",
+    "CATEGORY": "UG"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": false,
+    "RELEASE_DATE": "",
+    "DIRECT_DOWNLOAD_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "",
+    "EXAM_TIME": "",
+    "EXAM_SHIFT": "",
+    "EXAM_DURATION": "",
+    "EXAM_MODE": "Computer-Based Test (CBT)",
+    "EXAM_CENTER_CITY": "",
+    "EXAM_CENTER_NAME": "",
+    "FULL_SCHEDULE": []
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [
+      "Visit the official website examinationservices.nic.in",
+      "Click on the link for JIPMAT 2026 City Intimation Slip",
+      "Enter Application Number and Date of Birth",
+      "Login to view and download the city intimation slip"
+    ],
+    "REQUIRED_DETAILS": [
+      "Application Number",
+      "Date of Birth"
+    ],
+    "ALTERNATE_METHOD": ""
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": [],
+    "EXAM_DAY_GUIDELINES": [],
+    "DOCUMENTS_TO_CARRY": [
+      "Printout of City Intimation Slip",
+      "Valid Photo ID Proof (such as Aadhaar, Voter ID, Passport, etc.)"
+    ],
+    "PROHIBITED_ITEMS": [],
+    "COVID_SPECIFIC": ""
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "",
+    "EXAM_DATE_LIST": [],
+    "RESULT_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_DOWNLOAD": "https://examinationservices.nic.in/JIPMAT2026",
+    "OFFICIAL_WEBSITE": "https://examinationservices.nic.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "",
+    "REPRINT_OPTION": "",
+    "CONTACT_DETAILS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Rajasthan APO Syllabus And Exam Pattern 2026: Download PDF Here</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/rajasthan-apo-syllabus-and-exam-pattern-3051432</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 04:57:18 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "SYLLABUS_IDENTIFICATION": {
+    "EXAM_NAME": "Rajasthan APO (Assistant Prosecution Officer) Exam",
+    "RECRUITMENT_NAME": "Rajasthan APO Bharti 2026",
+    "CONDUCTING_BODY": "Rajasthan Public Service Commission (RPSC)",
+    "EXAM_TYPE": "State Level Recruitment",
+    "CATEGORY": "Law / Prosecution",
+    "ACADEMIC_YEAR": "2026",
+    "CLASS_OR_LEVEL": "Graduate / Professional"
+  },
+  "SYLLABUS_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "To be announced",
+    "SYLLABUS_VERSION": "Latest as per RPSC",
+    "OFFICIAL_SYLLABUS_LINK": "https://rpsc.rajasthan.gov.in"
+  },
+  "EXAM_PATTERN_OVERVIEW": {
+    "TOTAL_MARKS": 300,
+    "TOTAL_QUESTIONS": 200,
+    "DURATION": "3 hours",
+    "MEDIUM": "English &amp; Hindi",
+    "MODE": "Offline",
+    "NEGATIVE_MARKING": "Yes (1/3 mark for each wrong answer)",
+    "SECTIONS_COUNT": 2
+  },
+  "SUBJECTS": [
+    {
+      "SUBJECT_NAME": "Law",
+      "TOPICS": [
+        {
+          "TOPIC_NAME": "Indian Penal Code",
+          "SUB_TOPICS": [
+            "General Exceptions",
+            "Offences against State, Body, Property",
+            "Attempt, Abetment, Conspiracy"
+          ],
+          "MARKS_WEIGHTAGE": "40 marks",
+          "NUMBER_OF_QUESTIONS": 33,
+          "DIFFICULTY_LEVEL": "Moderate"
+        },
+        {
+          "TOPIC_NAME": "Code of Criminal Procedure",
+          "SUB_TOPICS": [
+            "Investigation, Inquiry, Trial",
+            "Bail, Arrest, Search, Seizure",
+            "Appeals, Revision, Reference"
+          ],
+          "MARKS_WEIGHTAGE": "40 marks",
+          "NUMBER_OF_QUESTIONS": 33,
+          "DIFFICULTY_LEVEL": "Moderate"
+        },
+        {
+          "TOPIC_NAME": "Indian Evidence Act",
+          "SUB_TOPICS": [
+            "Relevancy of Facts",
+            "Burden of Proof",
+            "Witnesses, Examination"
+          ],
+          "MARKS_WEIGHTAGE": "30 marks",
+          "NUMBER_OF_QUESTIONS": 25,
+          "DIFFICULTY_LEVEL": "Moderate"
+        }
+      ],
+      "TOTAL_MARKS": 150,
+      "TOTAL_QUESTIONS": 100,
+      "IMPORTANT_BOOKS": [
+        "KD Gaur - IPC",
+        "Ratanlal &amp; Dhirajlal - IPC",
+        "CK Takwani - CrPC",
+        "Bathla - Evidence Act"
+      ],
+      "NOTES": "All topics based on Rajasthan law syllabus"
+    },
+    {
+      "SUBJECT_NAME": "General Knowledge &amp; Current Affairs",
+      "TOPICS": [
+        {
+          "TOPIC_NAME": "Rajasthan History &amp; Culture",
+          "SUB_TOPICS": [
+            "Major Dynasties, Freedom Struggle",
+            "Art, Architecture, Festivals"
+          ],
+          "MARKS_WEIGHTAGE": "20 marks",
+          "NUMBER_OF_QUESTIONS": 17,
+          "DIFFICULTY_LEVEL": "Easy"
+        },
+        {
+          "TOPIC_NAME": "Polity &amp; Constitution",
+          "SUB_TOPICS": [
+            "Fundamental Rights, DPSP, Union &amp; State"
+          ],
+          "MARKS_WEIGHTAGE": "10 marks",
+          "NUMBER_OF_QUESTIONS": 8,
+          "DIFFICULTY_LEVEL": "Moderate"
+        },
+        {
+          "TOPIC_NAME": "Geography of Rajasthan",
+          "SUB_TOPICS": [
+            "Rivers, Mountains, Climate, Agriculture"
+          ],
+          "MARKS_WEIGHTAGE": "10 marks",
+          "NUMBER_OF_QUESTIONS": 8,
+          "DIFFICULTY_LEVEL": "Easy"
+        },
+        {
+          "TOPIC_NAME": "Current Affairs (National &amp; International)",
+          "SUB_TOPICS": [
+            "Last 6 months events, Schemes, Awards"
+          ],
+          "MARKS_WEIGHTAGE": "20 marks",
+          "NUMBER_OF_QUESTIONS": 17,
+          "DIFFICULTY_LEVEL": "Moderate"
+        }
+      ],
+      "TOTAL_MARKS": 150,
+      "TOTAL_QUESTIONS": 100,
+      "IMPORTANT_BOOKS": [
+        "Rajasthan GK by Mehra",
+        "Manorma Yearbook",
+        "Daily Newspaper (Dainik Bhaskar)"
+      ],
+      "NOTES": "Focus on Rajasthan specific topics"
+    }
+  ],
+  "SECTIONAL_DETAILS": [
+    {
+      "SECTION_NAME": "Paper I - Law",
+      "SUBJECTS_INCLUDED": ["Law"],
+      "TOTAL_MARKS": 150,
+      "TOTAL_QUESTIONS": 100
+    },
+    {
+      "SECTION_NAME": "Paper II - General Knowledge &amp; Current Affairs",
+      "SUBJECTS_INCLUDED": ["General Knowledge &amp; Current Affairs"],
+      "TOTAL_MARKS": 150,
+      "TOTAL_QUESTIONS": 100
+    }
+  ],
+  "RECOMMENDED_RESOURCES": {
+    "BOOKS": [
+      "KD Gaur - IPC",
+      "Ratanlal &amp; Dhirajlal - IPC",
+      "CK Takwani - CrPC",
+      "Bathla - Indian Evidence Act",
+      "Rajasthan GK by Dr. Neeraj"
+    ],
+    "ONLINE_RESOURCES": [
+      "FreeJobAlert.com",
+      "RPSC Official Website",
+      "YouTube channels (Law exams preparation)"
+    ],
+    "PREVIOUS_YEAR_PAPERS_LINK": "https://www.freejobalert.com/articles/rajasthan-apo-syllabus-and-exam-pattern-3051432"
+  },
+  "PREPARATION_TIPS": {
+    "STRATEGY": "Cover IPC, CrPC, Evidence Act thoroughly; focus on Rajasthan GK; solve previous year papers.",
+    "IMPORTANT_TOPICS": ["IPC General Exceptions", "CrPC Bail provisions", "Evidence Act Relevancy"],
+    "TIME_MANAGEMENT_TIPS": "Allocate 2 hours for Law, 1 hour for GK; practice mock tests"
+  },
+  "IMPORTANT_DATES": {
+    "SYLLABUS_RELEASE_DATE": "TBD",
+    "LAST_UPDATED": "2025-03-17"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://rpsc.rajasthan.gov.in",
+    "SYLLABUS_PDF": "https://www.freejobalert.com/articles/rajasthan-apo-syllabus-and-exam-pattern-3051432",
+    "OFFICIAL_WEBSITE": "https://rpsc.rajasthan.gov.in"
+  },
+  "ADDITIONAL_INFO": {
+    "FREQUENTLY_ASKED_QUESTIONS": [
+      "What is the eligibility for Rajasthan APO?",
+      "Is there negative marking?",
+      "Can I choose Hindi medium?"
+    ],
+    "LATEST_CHANGES": "No major changes expected from previous pattern",
+    "CONTACT_HELPLINE": "RPSC Helpline: +91-141-2227450"
+  }
+}</t>
+  </si>
+  <si>
+    <t>District &amp; Sessions Judge Yamuna Nagar Peon Recruitment 2026 - Apply Offline for 10 Posts</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/district-sessions-judge-yamuna-nagar-peon-recruitment-2026-apply-offline-for-10-posts-3051431</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 04:53:21 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Peon",
+    "JOB_TYPE": "Government",
+    "JOB_CATEGORY": "Group D",
+    "DEPARTMENT": "District &amp; Sessions Judge Yamuna Nagar",
+    "MINISTRY": "Law and Justice",
+    "RECRUITING_AGENCY": "District &amp; Sessions Judge, Yamuna Nagar",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 10,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Peon",
+        "VACANCIES": 10,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": "Group D"
+      }
+    ],
+    "JOB_LOCATION": "Yamuna Nagar, Haryana",
+    "GROUP": "D"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "₹16900 - ₹53700",
+    "MINIMUM_SALARY": 16900,
+    "MAXIMUM_SALARY": 53700,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "10th Pass",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "Not required",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 18,
+      "MAXIMUM_AGE": 42,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": "01.01.2026"
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Offline",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "15-02-2026",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Written Exam", "Interview"],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Rajasthan 3rd Grade Teacher Result 2026 Out (Direct Link) - Download Scorecard @rssb.rajasthan.gov.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/rajasthan-3rd-grade-teacher-result-2026-3051426</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 04:42:16 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "Rajasthan 3rd Grade Teacher Result 2026",
+    "RECRUITMENT_NAME": "Rajasthan 3rd Grade Teacher Recruitment 2026",
+    "POST_NAME": "3rd Grade Teacher",
+    "CONDUCTING_BODY": "Rajasthan Staff Selection Board (RSSB)",
+    "EXAM_TYPE": "Recruitment Exam",
+    "CATEGORY": "Teaching"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": false,
+    "DECLARATION_DATE": "2026",
+    "RESULT_TYPE": "Scorecard",
+    "DIRECT_RESULT_LINK": "http://rssb.rajasthan.gov.in",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website rssb.rajasthan.gov.in",
+      "Click on the result link for 3rd Grade Teacher",
+      "Enter your credentials (roll number/application number and date of birth)",
+      "View and download your scorecard"
+    ],
+    "REQUIRED_DETAILS": ["Roll Number", "Date of Birth"],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "http://rssb.rajasthan.gov.in",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "http://rssb.rajasthan.gov.in",
+    "OFFICIAL_WEBSITE": "http://rssb.rajasthan.gov.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>MHT CET 2nd Attempt Answer Key 2026 (Out) - Download PCM Response Sheet at cetcell.mahacet.org</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/mht-cet-2nd-attempt-answer-key-2026-out-download-pcm-response-sheet-3051428</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 04:40:32 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "ANSWER_KEY_IDENTIFICATION": {
+    "EXAM_NAME": "MHT CET 2nd Attempt 2026",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "State Common Entrance Test Cell, Maharashtra",
+    "EXAM_TYPE": "Engineering Entrance",
+    "CATEGORY": "Undergraduate",
+    "SET_CODE": ""
+  },
+  "ANSWER_KEY_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "",
+    "ANSWER_KEY_TYPE": "Response Sheet",
+    "DIRECT_DOWNLOAD_LINK": "https://cetcell.mahacet.org",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_DOWNLOAD_OR_CHECK": {
+    "STEPS": [
+      "Visit the official website cetcell.mahacet.org",
+      "Click on the link for MHT CET 2nd Attempt 2026 Response Sheet",
+      "Enter your login credentials (Application Number and Date of Birth/Password)",
+      "View and download the response sheet/answer key"
+    ],
+    "REQUIRED_DETAILS": ["Application Number", "Date of Birth/Password"],
+    "ALTERNATE_METHOD": ""
+  },
+  "ANSWER_KEY_DETAILS": {
+    "SUBJECT_WISE_KEYS": [
+      {
+        "SUBJECT": "Physics",
+        "SET_CODE": "",
+        "DOWNLOAD_LINK": ""
+      },
+      {
+        "SUBJECT": "Chemistry",
+        "SET_CODE": "",
+        "DOWNLOAD_LINK": ""
+      },
+      {
+        "SUBJECT": "Mathematics",
+        "SET_CODE": "",
+        "DOWNLOAD_LINK": ""
+      }
+    ],
+    "QUESTION_WISE_ANSWER": [],
+    "MASTER_QUESTION_PAPER_LINK": "",
+    "SHIFT_WISE": [
+      {
+        "SHIFT": "1",
+        "DATE": "",
+        "KEY_LINK": ""
+      },
+      {
+        "SHIFT": "2",
+        "DATE": "",
+        "KEY_LINK": ""
+      }
+    ]
+  },
+  "OBJECTION_PROCESS": {
+    "OBJECTION_WINDOW_START": "",
+    "OBJECTION_WINDOW_END": "",
+    "OBJECTION_FEE_PER_QUESTION": 0,
+    "HOW_TO_RAISE_OBJECTION": [],
+    "REVISED_KEY_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "ANSWER_KEY_AVAILABLE_FROM": "",
+    "ANSWER_KEY_AVAILABLE_UNTIL": "",
+    "OBJECTION_WINDOW": "",
+    "FINAL_KEY_DATE": "",
+    "RESULT_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_DOWNLOAD": "https://cetcell.mahacet.org",
+    "OFFICIAL_WEBSITE": "https://cetcell.mahacet.org",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "GENERAL_INSTRUCTIONS": [],
+    "DISPUTE_RESOLUTION": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>RPSC APO Recruitment 2026 Notification Out - Apply Online for 371 Posts</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/rpsc-assistant-prosecution-officer-recruitment-2026-apply-online-for-371-posts-3051420</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 04:40:25 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Assistant Prosecution Officer",
+    "JOB_TYPE": "सरकारी नौकरी",
+    "JOB_CATEGORY": "राज्य सरकार",
+    "DEPARTMENT": "गृह विभाग",
+    "MINISTRY": "राजस्थान सरकार",
+    "RECRUITING_AGENCY": "Rajasthan Public Service Commission (RPSC)",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 371,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Assistant Prosecution Officer",
+        "VACANCIES": 371,
+        "CATEGORY": "",
+        "PAY_LEVEL": "Level 7 (as per 7th CPC)",
+        "CLASSIFICATION": "ग्रुप B (राजपत्रित)"
+      }
+    ],
+    "JOB_LOCATION": "राजस्थान",
+    "GROUP": "B"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "Level 7",
+    "PAY_SCALE": "₹44,900 - ₹1,42,400",
+    "MINIMUM_SALARY": 44900,
+    "MAXIMUM_SALARY": 142400,
+    "ALLOWANCES": ["महंगाई भत्ता", "मकान किराया भत्ता", "यात्रा भत्ता", "चिकित्सा भत्ता"],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "किसी मान्यता प्राप्त विश्वविद्यालय से विधि स्नातक (LLB) की डिग्री",
+    "EDUCATION_DETAILS": [
+      {
+        "QUALIFICATION": "LLB",
+        "SPECIALIZATION": "",
+        "MINIMUM_PERCENTAGE": ""
+      }
+    ],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 21,
+      "MAXIMUM_AGE": 40,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 वर्ष",
+        "OBC": "3 वर्ष",
+        "PWD": "10 वर्ष",
+        "EX_SERVICEMEN": "3 वर्ष",
+        "WOMEN": "5 वर्ष (राजस्थान की महिलाएं)",
+        "OTHER": []
+      },
+      "AGE_AS_ON": "1 जनवरी 2026"
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "ऑनलाइन",
+    "APPLICATION_START_DATE": "जनवरी 2026 (अनुमानित)",
+    "APPLICATION_LAST_DATE": "फरवरी 2026 (अनुमानित)",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 600,
+      "SC_ST_PWD_WOMEN": 400,
+      "OTHER_CATEGORY_FEES": [
+        {
+          "CATEGORY": "OBC (क्रीमीलेयर)",
+          "FEE": 600
+        },
+        {
+          "CATEGORY": "EWS",
+          "FEE": 600
+        }
+      ],
+      "PAYMENT_MODE": "ऑनलाइन (क्रेडिट कार्ड/डेबिट कार्ड/नेट बैंकिंग)"
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "RPSC की आधिकारिक वेबसाइट पर जाएं",
+      "रजिस्ट्रेशन करें और लॉगिन करें",
+      "आवेदन पत्र भरें",
+      "आवश्यक दस्तावेज अपलोड करें",
+      "आवेदन शुल्क का भुगतान करें",
+      "फॉर्म सबमिट करें और प्रिंट लें"
+    ],
+    "REQUIRED_DOCUMENTS": [
+      "शैक्षिक प्रमाणपत्र",
+      "जाति प्रमाण पत्र",
+      "आयु प्रमाण पत्र",
+      "फोटो और हस्ताक्षर"
+    ],
+    "PHOTO_SPECIFICATIONS": "पासपोर्ट साइज फोटो (4.5 सेमी x 3.5 सेमी), सफेद पृष्ठभूमि",
+    "SIGNATURE_SPECIFICATIONS": "काले पेन से हस्ताक्षर (स्कैन किया हुआ)"
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["प्रारंभिक परीक्षा", "मुख्य परीक्षा", "साक्षात्कार"],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 200,
+        "DURATION": "2 घंटे",
+        "SUBJECTS": ["सामान्य ज्ञान और सामान्य विज्ञान", "विधि विषय"],
+        "NEGATIVE_MARKING": "गलत उत्तर पर 1/3 अंक काटे जाएंगे"
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 400,
+        "DURATION": "3 घंटे (प्रति पेपर)",
+        "SUBJECTS": ["विधि-I", "विधि-II", "सामान्य अध्ययन-I", "सामान्य अध्ययन-II"],
+        "NEGATIVE_MARKING": "गलत उत्तर पर 1/3 अंक काटे जाएंगे"
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 100,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [
+      "भारतीय संविधान",
+      "दंड प्रक्रिया संहिता",
+      "भारतीय दंड संहिता",
+      "साक्ष्य अधिनियम",
+      "अपराध विज्ञान"
+    ],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "दिसंबर 2025/जनवरी 2026",
+    "EXAM_DATE": "मार्च/अप्रैल 2026 (प्रारंभिक); मई/जून 2026 (मुख्य)",
+    "ADMIT_CARD_DATE": "परीक्षा से 2 सप्ताह पहले",
+    "RESULT_DATE": "परीक्षा के 2-3 महीने बाद",
+    "INTERVIEW_DATE": "अगस्त/सितंबर 2026",
+    "FINAL_RESULT_DATE": "अक्टूबर 2026",
+    "JOINING_DATE": "नवंबर 2026"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "https://rpsc.rajasthan.gov.in/",
+    "OFFICIAL_WEBSITE": "https://rpsc.rajasthan.gov.in/",
+    "ADMIT_CARD_LINK": "https://rpsc.rajasthan.gov.in/admit-card",
+    "RESULT_LINK": "https://rpsc.rajasthan.gov.in/result",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD":</t>
+  </si>
+  <si>
+    <t>Lucknow University Application Form 2026: Check  Important Dates, Application Fee and More</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/lucknow-university-application-form-2026-3051427</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 04:36:32 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "Lucknow University Application Form 2026",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Lucknow University",
+    "EXAM_TYPE": "University",
+    "CATEGORY": "Application Form"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": false,
+    "RELEASE_DATE": "",
+    "DIRECT_DOWNLOAD_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "",
+    "EXAM_TIME": "",
+    "EXAM_SHIFT": "",
+    "EXAM_DURATION": "",
+    "EXAM_MODE": "",
+    "EXAM_CENTER_CITY": "",
+    "EXAM_CENTER_NAME": "",
+    "FULL_SCHEDULE": []
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [],
+    "REQUIRED_DETAILS": [],
+    "ALTERNATE_METHOD": ""
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": [],
+    "EXAM_DAY_GUIDELINES": [],
+    "DOCUMENTS_TO_CARRY": [],
+    "PROHIBITED_ITEMS": [],
+    "COVID_SPECIFIC": ""
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "",
+    "EXAM_DATE_LIST": [],
+    "RESULT_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_DOWNLOAD": "",
+    "OFFICIAL_WEBSITE": "https://www.lkouniv.ac.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "",
+    "REPRINT_OPTION": "",
+    "CONTACT_DETAILS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>CUET UG 2026 New Admit Card Out - Download Updated Hall Ticket at cuet.nta.nic.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/cuet-ug-2026-new-admit-card-out-download-updated-hall-ticket-3051425</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 04:19:03 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "CUET UG 2026",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "National Testing Agency (NTA)",
+    "EXAM_TYPE": "Undergraduate Entrance Exam",
+    "CATEGORY": "University"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "",
+    "DIRECT_DOWNLOAD_LINK": "https://cuet.nta.nic.in/",
+    "STATUS_CHECK_LINK": "https://cuet.nta.nic.in/"
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "",
+    "EXAM_TIME": "",
+    "EXAM_SHIFT": "",
+    "EXAM_DURATION": "",
+    "EXAM_MODE": "Computer Based Test (CBT)",
+    "EXAM_CENTER_CITY": "",
+    "EXAM_CENTER_NAME": "",
+    "FULL_SCHEDULE": []
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [
+      "Visit the official website cuet.nta.nic.in",
+      "Click on the 'Download Admit Card' link",
+      "Enter your Application Number and Date of Birth",
+      "Click on 'Submit'",
+      "View and download the admit card",
+      "Take a printout for future reference"
+    ],
+    "REQUIRED_DETAILS": ["Application Number", "Date of Birth"],
+    "ALTERNATE_METHOD": ""
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": [],
+    "EXAM_DAY_GUIDELINES": [
+      "Reach the exam center at least 30 minutes before the reporting time",
+      "Carry a valid photo ID proof",
+      "Admit card must be printed on A4 size paper"
+    ],
+    "DOCUMENTS_TO_CARRY": ["Admit Card", "Photo ID Proof (Aadhaar, PAN, etc.)", "Passport size photograph"],
+    "PROHIBITED_ITEMS": ["Mobile phones", "Electronic gadgets", "Study material"],
+    "COVID_SPECIFIC": ""
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "",
+    "EXAM_DATE_LIST": [],
+    "RESULT_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_DOWNLOAD": "https://cuet.nta.nic.in/",
+    "OFFICIAL_WEBSITE": "https://cuet.nta.nic.in/",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "For any discrepancy, contact NTA helpline or visit the official website",
+    "REPRINT_OPTION": "Yes, download again from the website",
+    "CONTACT_DETAILS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>MP Forest Guard and Jail Prahari Admit Card 2026 (Out) - Download Here</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/mp-forest-guard-and-jail-prahari-admit-card-2026-3051424</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 04:14:59 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "MP Forest Guard and Jail Prahari Exam 2026",
+    "RECRUITMENT_NAME": "MP Forest Guard and Jail Prahari Recruitment 2026",
+    "POST_NAME": "Forest Guard, Jail Prahari",
+    "CONDUCTING_BODY": "Madhya Pradesh Professional Examination Board (MPPEB)",
+    "EXAM_TYPE": "Written Exam",
+    "CATEGORY": "Government Jobs"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "2026-03-15",
+    "DIRECT_DOWNLOAD_LINK": "https://www.freejobalert.com/articles/mp-forest-guard-and-jail-prahari-admit-card-2026-3051424",
+    "STATUS_CHECK_LINK": ""
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "2026-04-10",
+    "EXAM_TIME": "",
+    "EXAM_SHIFT": "",
+    "EXAM_DURATION": "",
+    "EXAM_MODE": "Offline",
+    "EXAM_CENTER_CITY": "",
+    "EXAM_CENTER_NAME": "",
+    "FULL_SCHEDULE": []
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [
+      "Visit the official website of MPPEB",
+      "Click on the admit card link for MP Forest Guard and Jail Prahari",
+      "Enter your registration number and date of birth",
+      "Download and print the admit card"
+    ],
+    "REQUIRED_DETAILS": [
+      "Registration Number",
+      "Date of Birth"
+    ],
+    "ALTERNATE_METHOD": "Direct download link provided on freejobalert.com"
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": [
+      "Carry a valid photo ID",
+      "Reach the exam center on time"
+    ],
+    "EXAM_DAY_GUIDELINES": [],
+    "DOCUMENTS_TO_CARRY": [
+      "Admit Card",
+      "Photo ID Proof"
+    ],
+    "PROHIBITED_ITEMS": [
+      "Mobile Phone",
+      "Electronic Devices"
+    ],
+    "COVID_SPECIFIC": ""
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "2026-03-15",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "2026-04-10",
+    "EXAM_DATE_LIST": ["2026-04-10"],
+    "RESULT_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_DOWNLOAD": "https://www.freejobalert.com/articles/mp-forest-guard-and-jail-prahari-admit-card-2026-3051424",
+    "OFFICIAL_WEBSITE": "https://peb.mponline.gov.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "Contact MPPEB helpdesk for any issues",
+    "REPRINT_OPTION": "Available on official website",
+    "CONTACT_DETAILS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Purnea University UG Admission 2026-30: Check  Important Dates, Application Fee and More</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/purnea-university-ug-admission-2026-30-3051423</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 04:09:49 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "MAIN_TOPIC": "Purnea University UG Admission 2026-30",
+  "SUMMARY": "This article provides information about undergraduate admission at Purnea University for the 2026-30 academic session, including important dates, application fee, and eligibility criteria.",
+  "KEY_POINTS": [
+    "Application start date: May 2026",
+    "Last date to apply: June 2026",
+    "Admission process through online mode",
+    "Application fee: INR 500 for general, INR 250 for reserved categories",
+    "Eligibility: 10+2 with 45% marks (general) and 40% (reserved)",
+    "Courses offered: BA, B.Sc, B.Com, etc."
+  ]
+}</t>
+  </si>
+  <si>
+    <t>RRB Section Controller CBAT City Intimation Slip 2026 Out – Download Link Here</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/rrb-section-controller-cbat-city-intimation-slip-2026-3051422</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 04:07:06 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Section Controller",
+    "JOB_TYPE": "CBAT City Intimation Slip",
+    "JOB_CATEGORY": "",
+    "DEPARTMENT": "Railway",
+    "MINISTRY": "Ministry of Railways",
+    "RECRUITING_AGENCY": "Railway Recruitment Board (RRB)",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [],
+    "JOB_LOCATION": "India",
+    "GROUP": "B"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "Level 6 (7th CPC)",
+    "MINIMUM_SALARY": 35400,
+    "MAXIMUM_SALARY": 112400,
+    "ALLOWANCES": ["DA", "HRA", "TA"],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 18,
+      "MAXIMUM_AGE": 36,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "10 years",
+        "EX_SERVICEMEN": "3 years",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": null,
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["CBAT"],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": null,
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "CBAT",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>CUET UG 2026 Re-Scheduled Exam Date Out - Check NTA Re-schedules 28 May Exam to 31 May at cuet.nta.nic.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/cuet-ug-2026-re-scheduled-exam-date-out-check-nta-re-schedules-3051421</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 04:03:12 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "CUET UG 2026",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "National Testing Agency (NTA)",
+    "EXAM_TYPE": "Entrance Exam",
+    "CATEGORY": "UG"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": false,
+    "RELEASE_DATE": "",
+    "DIRECT_DOWNLOAD_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "31 May 2026",
+    "EXAM_TIME": "",
+    "EXAM_SHIFT": "",
+    "EXAM_DURATION": "",
+    "EXAM_MODE": "",
+    "EXAM_CENTER_CITY": "",
+    "EXAM_CENTER_NAME": "",
+    "FULL_SCHEDULE": [
+      {
+        "DATE": "28 May 2026",
+        "SUBJECT": "Original Date",
+        "TIME": ""
+      },
+      {
+        "DATE": "31 May 2026",
+        "SUBJECT": "Re-scheduled Date",
+        "TIME": ""
+      }
+    ]
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [],
+    "REQUIRED_DETAILS": [],
+    "ALTERNATE_METHOD": ""
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": [],
+    "EXAM_DAY_GUIDELINES": [],
+    "DOCUMENTS_TO_CARRY": [],
+    "PROHIBITED_ITEMS": [],
+    "COVID_SPECIFIC": ""
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "",
+    "EXAM_DATE_LIST": ["28 May 2026", "31 May 2026"],
+    "RESULT_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_DOWNLOAD": "",
+    "OFFICIAL_WEBSITE": "https://cuet.nta.nic.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "",
+    "REPRINT_OPTION": "",
+    "CONTACT_DETAILS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>TS SSC Supplementary Hall Ticket 2026 Out - Download Telangana 10th ASE June Admit Card at bse.telangana.gov.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/ts-ssc-supplementary-hall-ticket-2026-out-download-telangana-10th-ase-june-admit-card-3051419</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 03:51:48 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "TS SSC Supplementary Examination / Telangana 10th ASE June",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Board of Secondary Education, Telangana (BSE Telangana)",
+    "EXAM_TYPE": "Board Exam",
+    "CATEGORY": "Supplementary"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "",
+    "DIRECT_DOWNLOAD_LINK": "https://bse.telangana.gov.in",
+    "STATUS_CHECK_LINK": ""
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "",
+    "EXAM_TIME": "",
+    "EXAM_SHIFT": "",
+    "EXAM_DURATION": "",
+    "EXAM_MODE": "Offline",
+    "EXAM_CENTER_CITY": "",
+    "EXAM_CENTER_NAME": "",
+    "FULL_SCHEDULE": []
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [
+      "Visit the official website bse.telangana.gov.in",
+      "Click on the TS SSC Supplementary Hall Ticket 2026 link",
+      "Enter the required details (Roll Number, Date of Birth, etc.)",
+      "Download and print the admit card"
+    ],
+    "REQUIRED_DETAILS": ["Roll Number", "Date of Birth"],
+    "ALTERNATE_METHOD": ""
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": [],
+    "EXAM_DAY_GUIDELINES": [],
+    "DOCUMENTS_TO_CARRY": ["Admit Card", "Valid Photo ID"],
+    "PROHIBITED_ITEMS": ["Mobile Phone", "Electronic Gadgets"],
+    "COVID_SPECIFIC": ""
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "",
+    "EXAM_DATE_LIST": [],
+    "RESULT_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_DOWNLOAD": "",
+    "OFFICIAL_WEBSITE": "https://bse.telangana.gov.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "",
+    "REPRINT_OPTION": "",
+    "CONTACT_DETAILS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Daily Current Affairs – 28 May 2026</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/daily-current-affairs-28-may-2026-10245</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 03:50:06 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "",
+    "EXAM_TYPE": "",
+    "CATEGORY": ""
+  },
+  "RESULT_STATUS": {
+    "DECLARED": false,
+    "DECLARATION_DATE": "",
+    "RESULT_TYPE": "",
+    "DIRECT_RESULT_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [],
+    "REQUIRED_DETAILS": [],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "",
+    "OFFICIAL_WEBSITE": "",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>CSIR - UGC NET 2026 June Application Form Date: Check Date, Eligibility Criteria &amp; How to Apply</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/csir-net-june-2026-application-form-date-3044339</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 03:42:29 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "CSIR UGC NET June 2026",
+    "JOB_TYPE": "Fellowship/Lectureship",
+    "JOB_CATEGORY": "National Eligibility Test",
+    "DEPARTMENT": "",
+    "MINISTRY": "",
+    "RECRUITING_AGENCY": "CSIR (Council of Scientific &amp; Industrial Research)",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [],
+    "JOB_LOCATION": "All India",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "As per UGC norms",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Master's degree in Science, Engineering/Technology, or relevant subjects with minimum 55% marks",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "55% (50% for reserved categories)",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 28,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "10 years",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": "To be announced"
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "To be announced (likely March 2026)",
+    "APPLICATION_LAST_DATE": "To be announced (likely April 2026)",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 1150,
+      "SC_ST_PWD_WOMEN": 600,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": "Online"
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Computer Based Test", "Document Verification"],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 300,
+        "DURATION": "3 hours",
+        "SUBJECTS": ["Subject Paper (200 marks)", "General Aptitude (100 marks)"],
+        "NEGATIVE_MARKING": "Yes"
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "To be announced",
+    "EXAM_DATE": "To be announced (likely June 2026)",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "https://csirnet.nta.ac.in",
+    "OFFICIAL_WEBSITE": "https://csirnet.nta.ac.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "As per government norms",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
   }
 }</t>
   </si>
@@ -45484,6 +48608,627 @@
         <v>1259</v>
       </c>
     </row>
+    <row r="315">
+      <c r="A315" t="s">
+        <v>7</v>
+      </c>
+      <c r="B315" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C315" t="s">
+        <v>1261</v>
+      </c>
+      <c r="D315" t="s">
+        <v>1262</v>
+      </c>
+      <c r="E315" t="s">
+        <v>11</v>
+      </c>
+      <c r="F315" t="s">
+        <v>1260</v>
+      </c>
+      <c r="G315" t="s">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="s">
+        <v>7</v>
+      </c>
+      <c r="B316" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C316" t="s">
+        <v>1265</v>
+      </c>
+      <c r="D316" t="s">
+        <v>1266</v>
+      </c>
+      <c r="E316" t="s">
+        <v>38</v>
+      </c>
+      <c r="F316" t="s">
+        <v>1264</v>
+      </c>
+      <c r="G316" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="s">
+        <v>52</v>
+      </c>
+      <c r="B317" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C317" t="s">
+        <v>1269</v>
+      </c>
+      <c r="D317" t="s">
+        <v>1270</v>
+      </c>
+      <c r="E317" t="s">
+        <v>38</v>
+      </c>
+      <c r="F317" t="s">
+        <v>1268</v>
+      </c>
+      <c r="G317" t="s">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="s">
+        <v>52</v>
+      </c>
+      <c r="B318" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C318" t="s">
+        <v>1273</v>
+      </c>
+      <c r="D318" t="s">
+        <v>1274</v>
+      </c>
+      <c r="E318" t="s">
+        <v>11</v>
+      </c>
+      <c r="F318" t="s">
+        <v>1272</v>
+      </c>
+      <c r="G318" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="s">
+        <v>52</v>
+      </c>
+      <c r="B319" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C319" t="s">
+        <v>1277</v>
+      </c>
+      <c r="D319" t="s">
+        <v>1278</v>
+      </c>
+      <c r="E319" t="s">
+        <v>38</v>
+      </c>
+      <c r="F319" t="s">
+        <v>1276</v>
+      </c>
+      <c r="G319" t="s">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="s">
+        <v>52</v>
+      </c>
+      <c r="B320" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C320" t="s">
+        <v>1281</v>
+      </c>
+      <c r="D320" t="s">
+        <v>1282</v>
+      </c>
+      <c r="E320" t="s">
+        <v>11</v>
+      </c>
+      <c r="F320" t="s">
+        <v>1280</v>
+      </c>
+      <c r="G320" t="s">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="s">
+        <v>52</v>
+      </c>
+      <c r="B321" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C321" t="s">
+        <v>1285</v>
+      </c>
+      <c r="D321" t="s">
+        <v>1286</v>
+      </c>
+      <c r="E321" t="s">
+        <v>29</v>
+      </c>
+      <c r="F321" t="s">
+        <v>1284</v>
+      </c>
+      <c r="G321" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="s">
+        <v>52</v>
+      </c>
+      <c r="B322" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C322" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D322" t="s">
+        <v>1290</v>
+      </c>
+      <c r="E322" t="s">
+        <v>11</v>
+      </c>
+      <c r="F322" t="s">
+        <v>1288</v>
+      </c>
+      <c r="G322" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="s">
+        <v>52</v>
+      </c>
+      <c r="B323" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C323" t="s">
+        <v>1293</v>
+      </c>
+      <c r="D323" t="s">
+        <v>1294</v>
+      </c>
+      <c r="E323" t="s">
+        <v>393</v>
+      </c>
+      <c r="F323" t="s">
+        <v>1292</v>
+      </c>
+      <c r="G323" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="s">
+        <v>52</v>
+      </c>
+      <c r="B324" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C324" t="s">
+        <v>1297</v>
+      </c>
+      <c r="D324" t="s">
+        <v>1298</v>
+      </c>
+      <c r="E324" t="s">
+        <v>11</v>
+      </c>
+      <c r="F324" t="s">
+        <v>1296</v>
+      </c>
+      <c r="G324" t="s">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="s">
+        <v>52</v>
+      </c>
+      <c r="B325" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C325" t="s">
+        <v>1301</v>
+      </c>
+      <c r="D325" t="s">
+        <v>1302</v>
+      </c>
+      <c r="E325" t="s">
+        <v>11</v>
+      </c>
+      <c r="F325" t="s">
+        <v>1300</v>
+      </c>
+      <c r="G325" t="s">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="s">
+        <v>52</v>
+      </c>
+      <c r="B326" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C326" t="s">
+        <v>1305</v>
+      </c>
+      <c r="D326" t="s">
+        <v>1306</v>
+      </c>
+      <c r="E326" t="s">
+        <v>393</v>
+      </c>
+      <c r="F326" t="s">
+        <v>1304</v>
+      </c>
+      <c r="G326" t="s">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="s">
+        <v>52</v>
+      </c>
+      <c r="B327" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C327" t="s">
+        <v>1309</v>
+      </c>
+      <c r="D327" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E327" t="s">
+        <v>38</v>
+      </c>
+      <c r="F327" t="s">
+        <v>1308</v>
+      </c>
+      <c r="G327" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="s">
+        <v>52</v>
+      </c>
+      <c r="B328" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C328" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D328" t="s">
+        <v>1314</v>
+      </c>
+      <c r="E328" t="s">
+        <v>393</v>
+      </c>
+      <c r="F328" t="s">
+        <v>1312</v>
+      </c>
+      <c r="G328" t="s">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="s">
+        <v>52</v>
+      </c>
+      <c r="B329" t="s">
+        <v>1316</v>
+      </c>
+      <c r="C329" t="s">
+        <v>1317</v>
+      </c>
+      <c r="D329" t="s">
+        <v>1318</v>
+      </c>
+      <c r="E329" t="s">
+        <v>11</v>
+      </c>
+      <c r="F329" t="s">
+        <v>1316</v>
+      </c>
+      <c r="G329" t="s">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="s">
+        <v>52</v>
+      </c>
+      <c r="B330" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C330" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D330" t="s">
+        <v>1322</v>
+      </c>
+      <c r="E330" t="s">
+        <v>29</v>
+      </c>
+      <c r="F330" t="s">
+        <v>1320</v>
+      </c>
+      <c r="G330" t="s">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="s">
+        <v>52</v>
+      </c>
+      <c r="B331" t="s">
+        <v>1324</v>
+      </c>
+      <c r="C331" t="s">
+        <v>1325</v>
+      </c>
+      <c r="D331" t="s">
+        <v>1326</v>
+      </c>
+      <c r="E331" t="s">
+        <v>24</v>
+      </c>
+      <c r="F331" t="s">
+        <v>1324</v>
+      </c>
+      <c r="G331" t="s">
+        <v>1327</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="s">
+        <v>52</v>
+      </c>
+      <c r="B332" t="s">
+        <v>1328</v>
+      </c>
+      <c r="C332" t="s">
+        <v>1329</v>
+      </c>
+      <c r="D332" t="s">
+        <v>1330</v>
+      </c>
+      <c r="E332" t="s">
+        <v>11</v>
+      </c>
+      <c r="F332" t="s">
+        <v>1328</v>
+      </c>
+      <c r="G332" t="s">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="s">
+        <v>52</v>
+      </c>
+      <c r="B333" t="s">
+        <v>1332</v>
+      </c>
+      <c r="C333" t="s">
+        <v>1333</v>
+      </c>
+      <c r="D333" t="s">
+        <v>1334</v>
+      </c>
+      <c r="E333" t="s">
+        <v>38</v>
+      </c>
+      <c r="F333" t="s">
+        <v>1332</v>
+      </c>
+      <c r="G333" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="s">
+        <v>52</v>
+      </c>
+      <c r="B334" t="s">
+        <v>1336</v>
+      </c>
+      <c r="C334" t="s">
+        <v>1337</v>
+      </c>
+      <c r="D334" t="s">
+        <v>1338</v>
+      </c>
+      <c r="E334" t="s">
+        <v>38</v>
+      </c>
+      <c r="F334" t="s">
+        <v>1336</v>
+      </c>
+      <c r="G334" t="s">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="s">
+        <v>52</v>
+      </c>
+      <c r="B335" t="s">
+        <v>1340</v>
+      </c>
+      <c r="C335" t="s">
+        <v>1341</v>
+      </c>
+      <c r="D335" t="s">
+        <v>1342</v>
+      </c>
+      <c r="E335" t="s">
+        <v>38</v>
+      </c>
+      <c r="F335" t="s">
+        <v>1340</v>
+      </c>
+      <c r="G335" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="s">
+        <v>52</v>
+      </c>
+      <c r="B336" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C336" t="s">
+        <v>1345</v>
+      </c>
+      <c r="D336" t="s">
+        <v>1346</v>
+      </c>
+      <c r="E336" t="s">
+        <v>741</v>
+      </c>
+      <c r="F336" t="s">
+        <v>1344</v>
+      </c>
+      <c r="G336" t="s">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="s">
+        <v>52</v>
+      </c>
+      <c r="B337" t="s">
+        <v>1348</v>
+      </c>
+      <c r="C337" t="s">
+        <v>1349</v>
+      </c>
+      <c r="D337" t="s">
+        <v>1350</v>
+      </c>
+      <c r="E337" t="s">
+        <v>11</v>
+      </c>
+      <c r="F337" t="s">
+        <v>1348</v>
+      </c>
+      <c r="G337" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="s">
+        <v>52</v>
+      </c>
+      <c r="B338" t="s">
+        <v>1352</v>
+      </c>
+      <c r="C338" t="s">
+        <v>1353</v>
+      </c>
+      <c r="D338" t="s">
+        <v>1354</v>
+      </c>
+      <c r="E338" t="s">
+        <v>38</v>
+      </c>
+      <c r="F338" t="s">
+        <v>1352</v>
+      </c>
+      <c r="G338" t="s">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="s">
+        <v>52</v>
+      </c>
+      <c r="B339" t="s">
+        <v>1356</v>
+      </c>
+      <c r="C339" t="s">
+        <v>1357</v>
+      </c>
+      <c r="D339" t="s">
+        <v>1358</v>
+      </c>
+      <c r="E339" t="s">
+        <v>38</v>
+      </c>
+      <c r="F339" t="s">
+        <v>1356</v>
+      </c>
+      <c r="G339" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="s">
+        <v>52</v>
+      </c>
+      <c r="B340" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C340" t="s">
+        <v>1361</v>
+      </c>
+      <c r="D340" t="s">
+        <v>1362</v>
+      </c>
+      <c r="E340" t="s">
+        <v>29</v>
+      </c>
+      <c r="F340" t="s">
+        <v>1360</v>
+      </c>
+      <c r="G340" t="s">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="s">
+        <v>52</v>
+      </c>
+      <c r="B341" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C341" t="s">
+        <v>1365</v>
+      </c>
+      <c r="D341" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E341" t="s">
+        <v>11</v>
+      </c>
+      <c r="F341" t="s">
+        <v>1364</v>
+      </c>
+      <c r="G341" t="s">
+        <v>1367</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/data/articles.xlsx
+++ b/data/articles.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1368" uniqueCount="1368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1567" uniqueCount="1567">
   <si>
     <t>Competitor</t>
   </si>
@@ -41078,6 +41078,5645 @@
     "IMP_INSTRUCTIONS": [],
     "OFFICIAL_LANGUAGE": "",
     "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Indian Navy Civilian INCET 01/2025 Answer Key</t>
+  </si>
+  <si>
+    <t>https://sarkariresult.com.cm/indian-navy-civilian-incet-01-2025/</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 07:33:29 +0000</t>
+  </si>
+  <si>
+    <t>{
+  "ANSWER_KEY_IDENTIFICATION": {
+    "EXAM_NAME": "Indian Navy Civilian INCET 01/2025",
+    "RECRUITMENT_NAME": "INCET 01/2025",
+    "POST_NAME": "Civilian Posts under Indian Navy",
+    "CONDUCTING_BODY": "Indian Navy",
+    "EXAM_TYPE": "Computer Based Test",
+    "CATEGORY": "Recruitment",
+    "SET_CODE": ""
+  },
+  "ANSWER_KEY_STATUS": {
+    "RELEASED": false,
+    "RELEASE_DATE": "",
+    "ANSWER_KEY_TYPE": "",
+    "DIRECT_DOWNLOAD_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_DOWNLOAD_OR_CHECK": {
+    "STEPS": [],
+    "REQUIRED_DETAILS": [],
+    "ALTERNATE_METHOD": ""
+  },
+  "ANSWER_KEY_DETAILS": {
+    "SUBJECT_WISE_KEYS": [],
+    "QUESTION_WISE_ANSWER": [],
+    "MASTER_QUESTION_PAPER_LINK": "",
+    "SHIFT_WISE": []
+  },
+  "OBJECTION_PROCESS": {
+    "OBJECTION_WINDOW_START": "",
+    "OBJECTION_WINDOW_END": "",
+    "OBJECTION_FEE_PER_QUESTION": 0,
+    "HOW_TO_RAISE_OBJECTION": [],
+    "REVISED_KEY_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "ANSWER_KEY_AVAILABLE_FROM": "",
+    "ANSWER_KEY_AVAILABLE_UNTIL": "",
+    "OBJECTION_WINDOW": "",
+    "FINAL_KEY_DATE": "",
+    "RESULT_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://sarkariresult.com.cm/indian-navy-civilian-incet-01-2025/",
+    "DIRECT_DOWNLOAD": "",
+    "OFFICIAL_WEBSITE": "",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "GENERAL_INSTRUCTIONS": [],
+    "DISPUTE_RESOLUTION": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Bihar Police CSBC Constable Final Result 2026 – Out</t>
+  </si>
+  <si>
+    <t>https://sarkariresult.com.cm/bihar-police-csbc-constable-2025/</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 06:43:23 +0000</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "CSBC Constable Recruitment 2025-2026",
+    "RECRUITMENT_NAME": "Bihar Police Constable Recruitment",
+    "POST_NAME": "Constable",
+    "CONDUCTING_BODY": "Central Selection Board of Constable (CSBC), Bihar",
+    "EXAM_TYPE": "Recruitment Exam",
+    "CATEGORY": "Police"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026",
+    "RESULT_TYPE": "Final Result",
+    "DIRECT_RESULT_LINK": "https://sarkariresult.com.cm/bihar-police-csbc-constable-2025/",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website or the provided result link.",
+      "Click on the result link for Bihar Police Constable Final Result 2026.",
+      "Enter your registration number and date of birth or roll number.",
+      "The result will be displayed on the screen.",
+      "Download and take a printout for future reference."
+    ],
+    "REQUIRED_DETAILS": [
+      "Registration Number",
+      "Date of Birth",
+      "Roll Number"
+    ],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "https://sarkariresult.com.cm/bihar-police-csbc-constable-2025/",
+    "OFFICIAL_WEBSITE": "",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>NTA JIPMAT Exam City Details 2026 – Out</t>
+  </si>
+  <si>
+    <t>https://sarkariresult.com.cm/nta-jipmat-admission-2026/</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 06:42:07 +0000</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "JIPMAT Joint Entrance Test for IPM",
+    "JOB_TYPE": "Education",
+    "JOB_CATEGORY": "Admission",
+    "DEPARTMENT": "NTA",
+    "MINISTRY": "Education",
+    "RECRUITING_AGENCY": "National Testing Agency",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [],
+    "JOB_LOCATION": "Multiple Cities",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": false
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>HPCET 2026 Final Answer Key OUT -  Download UG and PG Courses PDF @ himtu.ac.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/hpcet-2026-final-answer-key-out-download-ug-and-pg-courses-pdf-3051516</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 08:41:37 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "ANSWER_KEY_IDENTIFICATION": {
+    "EXAM_NAME": "HPCET 2026",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Himachal Pradesh Technical University (HPTU)",
+    "EXAM_TYPE": "University Entrance Exam",
+    "CATEGORY": "UG and PG Courses",
+    "SET_CODE": ""
+  },
+  "ANSWER_KEY_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "",
+    "ANSWER_KEY_TYPE": "Final",
+    "DIRECT_DOWNLOAD_LINK": "",
+    "STATUS_CHECK_LINK": "https://himtu.ac.in"
+  },
+  "HOW_TO_DOWNLOAD_OR_CHECK": {
+    "STEPS": [
+      "Visit official website himtu.ac.in",
+      "Click on HPCET 2026 link",
+      "Select answer key for UG or PG",
+      "Download PDF"
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth"],
+    "ALTERNATE_METHOD": ""
+  },
+  "ANSWER_KEY_DETAILS": {
+    "SUBJECT_WISE_KEYS": [],
+    "QUESTION_WISE_ANSWER": [],
+    "MASTER_QUESTION_PAPER_LINK": "",
+    "SHIFT_WISE": []
+  },
+  "OBJECTION_PROCESS": {
+    "OBJECTION_WINDOW_START": "",
+    "OBJECTION_WINDOW_END": "",
+    "OBJECTION_FEE_PER_QUESTION": 0,
+    "HOW_TO_RAISE_OBJECTION": [],
+    "REVISED_KEY_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "ANSWER_KEY_AVAILABLE_FROM": "",
+    "ANSWER_KEY_AVAILABLE_UNTIL": "",
+    "OBJECTION_WINDOW": "",
+    "FINAL_KEY_DATE": "",
+    "RESULT_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://himtu.ac.in",
+    "DIRECT_DOWNLOAD": "https://himtu.ac.in",
+    "OFFICIAL_WEBSITE": "https://himtu.ac.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "GENERAL_INSTRUCTIONS": [],
+    "DISPUTE_RESOLUTION": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>East Coast Railway Junior Engineer Recruitment 2026 - Apply Offline</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/east-coast-railway-junior-engineer-recruitment-2026-apply-offline-3051515</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 08:37:11 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Junior Engineer",
+    "JOB_TYPE": "Government",
+    "JOB_CATEGORY": "Engineering",
+    "DEPARTMENT": "East Coast Railway",
+    "MINISTRY": "Ministry of Railways",
+    "RECRUITING_AGENCY": "East Coast Railway",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Junior Engineer",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": "Technical"
+      }
+    ],
+    "JOB_LOCATION": "East Coast Railway (Odisha, Andhra Pradesh, etc.)",
+    "GROUP": "B"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Offline",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": false
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.eastcoastrailway.gov.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Rajasthan Sanskrit University Admission 2026: Check Important Dates, Eligibility Criteria and More</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/rajasthan-sanskrit-university-admission-2026-check-important-dates-eligibility-criteria-and-more-3051513</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 08:29:37 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "Rajasthan Sanskrit University Admission 2026",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Rajasthan Sanskrit University",
+    "EXAM_TYPE": "Admission",
+    "CATEGORY": "University"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": false,
+    "RELEASE_DATE": "",
+    "DIRECT_DOWNLOAD_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "",
+    "EXAM_TIME": "",
+    "EXAM_SHIFT": "",
+    "EXAM_DURATION": "",
+    "EXAM_MODE": "",
+    "EXAM_CENTER_CITY": "",
+    "EXAM_CENTER_NAME": "",
+    "FULL_SCHEDULE": []
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [],
+    "REQUIRED_DETAILS": [],
+    "ALTERNATE_METHOD": ""
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": [],
+    "EXAM_DAY_GUIDELINES": [],
+    "DOCUMENTS_TO_CARRY": [],
+    "PROHIBITED_ITEMS": [],
+    "COVID_SPECIFIC": ""
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "",
+    "EXAM_DATE_LIST": [],
+    "RESULT_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_DOWNLOAD": "",
+    "OFFICIAL_WEBSITE": "https://www.freejobalert.com/articles/rajasthan-sanskrit-university-admission-2026-check-important-dates-eligibility-criteria-and-more-3051513",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "",
+    "REPRINT_OPTION": "",
+    "CONTACT_DETAILS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Karnataka PSC Exam Schedule 2026 Out- Download Revised KPSC Time Table PDF</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/karnataka-psc-exam-schedule-2026-out-download-revised-kpsc-time-table-pdf-3051512</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 08:29:01 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "KPSC Exam 2026",
+    "JOB_TYPE": "Exam Schedule",
+    "JOB_CATEGORY": "",
+    "DEPARTMENT": "",
+    "MINISTRY": "",
+    "RECRUITING_AGENCY": "Karnataka Public Service Commission (KPSC)",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [],
+    "JOB_LOCATION": "Karnataka",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": false
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "https://www.freejobalert.com/articles/karnataka-psc-exam-schedule-2026-out-download-revised-kpsc-time-table-pdf-3051512",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Utkal Balashram Kandhamal Recruitment 2026 - Apply Online for Store Keeper-cum-Accountant, House Father Posts</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/utkal-balashram-kandhamal-recruitment-2026-apply-online-for-store-keeper-cum-accountant-house-father-posts-3051511</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 08:23:05 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Store Keeper-cum-Accountant, House Father",
+    "JOB_TYPE": "सरकारी नौकरी",
+    "JOB_CATEGORY": "गैर-तकनीकी",
+    "DEPARTMENT": "Utkal Balashram, Kandhamal",
+    "MINISTRY": "",
+    "RECRUITING_AGENCY": "Utkal Balashram, Kandhamal",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Store Keeper-cum-Accountant",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      },
+      {
+        "POST_NAME": "House Father",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "Kandhamal, Odisha",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "ऑनलाइन",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>CUJ PG Admission 2026: Check Eligibility, Apply Link and Registration Fee</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/cuj-pg-admission-2026-check-eligibility-apply-link-and-registration-fee-3051506</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 08:09:58 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "CUJ PG Admission 2026",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Central University of Jammu",
+    "EXAM_TYPE": "Admission Test",
+    "CATEGORY": "PG Admission"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": false,
+    "RELEASE_DATE": "",
+    "DIRECT_DOWNLOAD_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "",
+    "EXAM_TIME": "",
+    "EXAM_SHIFT": "",
+    "EXAM_DURATION": "",
+    "EXAM_MODE": "",
+    "EXAM_CENTER_CITY": "",
+    "EXAM_CENTER_NAME": "",
+    "FULL_SCHEDULE": []
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [],
+    "REQUIRED_DETAILS": [],
+    "ALTERNATE_METHOD": ""
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": [],
+    "EXAM_DAY_GUIDELINES": [],
+    "DOCUMENTS_TO_CARRY": [],
+    "PROHIBITED_ITEMS": [],
+    "COVID_SPECIFIC": ""
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "",
+    "EXAM_DATE_LIST": [],
+    "RESULT_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_DOWNLOAD": "",
+    "OFFICIAL_WEBSITE": "",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "",
+    "REPRINT_OPTION": "",
+    "CONTACT_DETAILS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>AWEIL Recruitment 2026 Notification Out - Apply Offline for 09 Executive, Jr. Executiveand More Posts</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/aweil-recruitment-2026-apply-offline-for-09-executive-jr-executiveand-more-posts-3051505</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 08:06:05 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Executive, Jr. Executive and More Posts",
+    "JOB_TYPE": "Government",
+    "JOB_CATEGORY": "",
+    "DEPARTMENT": "AWEIL",
+    "MINISTRY": "Ministry of Defence",
+    "RECRUITING_AGENCY": "Army Welfare Education and Research Institute (AWEIL)",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 9,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Executive",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "Level 10",
+        "CLASSIFICATION": "Group A"
+      },
+      {
+        "POST_NAME": "Jr. Executive",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "Level 8",
+        "CLASSIFICATION": "Group B"
+      },
+      {
+        "POST_NAME": "Other Posts",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "Across India",
+    "GROUP": "A, B"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "Level 10/8",
+    "PAY_SCALE": "Rs. 56,100 - 1,77,500/- (Level 10), Rs. 47,600 - 1,51,100/- (Level 8)",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": ["DA", "HRA", "Medical", "Other allowances as per rules"],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Graduate Degree in any discipline from a recognized University/Institute",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "Experience required for specific posts as per notification",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 18,
+      "MAXIMUM_AGE": 45,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "10 years",
+        "EX_SERVICEMEN": "As per rules",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": "01-01-2026"
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Offline",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 500,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": "Demand Draft"
+    },
+    "HOW_TO_APPLY_STEPS": ["Download the application form from official website", "Fill the form with required details", "Attach self-attested copies of documents", "Pay the fee via Demand Draft", "Send the application to the given address"],
+    "REQUIRED_DOCUMENTS": ["10th/12th Mark sheet", "Graduation Degree", "Caste Certificate", "Identity Proof", "Passport size photos", "Experience Certificate"],
+    "PHOTO_SPECIFICATIONS": "Recent passport size photograph",
+    "SIGNATURE_SPECIFICATIONS": "Signature in black ink"
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Written Exam", "Interview", "Document Verification"],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 100,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": ["Candidates are advised to read the official notification before applying"],
+    "OFFICIAL_LANGUAGE": "English/Hindi",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>VSSC Result 2026 OUT For Technical Assistant, Library Assistant and Other Posts (Direct Link) - Download Scorecard @ vssc.gov.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/vssc-technical-assistant-and-other-post-result-2026-3051504</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 07:52:01 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "",
+    "RECRUITMENT_NAME": "VSSC Technical Assistant, Library Assistant and Other Posts Recruitment 2026",
+    "POST_NAME": "Technical Assistant, Library Assistant and Other Posts",
+    "CONDUCTING_BODY": "Vikram Sarabhai Space Centre (VSSC)",
+    "EXAM_TYPE": "Recruitment",
+    "CATEGORY": "Government Jobs"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026",
+    "RESULT_TYPE": "Final Result",
+    "DIRECT_RESULT_LINK": "https://vssc.gov.in",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website vssc.gov.in",
+      "Click on the 'Result' or 'Recruitment' section",
+      "Find the link for 'Technical Assistant and Other Posts Result 2026'",
+      "Enter your registration number and date of birth",
+      "View and download your result/scorecard"
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Use the direct result link provided in the article."
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://vssc.gov.in",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "https://vssc.gov.in",
+    "OFFICIAL_WEBSITE": "https://vssc.gov.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/anna-university-project-assistant-recruitment-2026-apply-offline-3051503</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 07:48:39 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Project Assistant",
+    "JOB_TYPE": "Contractual",
+    "JOB_CATEGORY": "Technical",
+    "DEPARTMENT": "Anna University",
+    "MINISTRY": "Education",
+    "RECRUITING_AGENCY": "Anna University",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Project Assistant",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": "Project"
+      }
+    ],
+    "JOB_LOCATION": "Chennai, Tamil Nadu",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 15000,
+    "MAXIMUM_SALARY": 20000,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "B.E./B.Tech or equivalent",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "Desirable",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 21,
+      "MAXIMUM_AGE": 35,
+      "AGE_RELAXATION": {
+        "SC_ST": "05 years",
+        "OBC": "03 years",
+        "PWD": "10 years",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Offline",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": "No Fee"
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "Visit the official Anna University website",
+      "Download the application form",
+      "Fill the form and attach required documents",
+      "Send the application to the specified address"
+    ],
+    "REQUIRED_DOCUMENTS": [
+      "Degree certificate",
+      "Age proof",
+      "Experience certificate",
+      "ID proof"
+    ],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Interview"],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": null,
+      "INTERVIEW": {
+        "TOTAL_MARKS": 100,
+        "DURATION": ""
+      },
+      "SKILL_TEST": null,
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.annauniv.edu",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Punjabi University Patiala Date Sheet 2026 Out for BA LLB, BBA LLB &amp; B.Com LLB at pupexamination.ac.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/punjabi-university-patiala-date-sheet-2026-out-for-ba-llb-bba-llb-and-bcom-llb-3051501</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 07:46:29 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "SYLLABUS_IDENTIFICATION": {
+    "EXAM_NAME": "BA LLB, BBA LLB, B.Com LLB Semester Exams",
+    "RECRUITMENT_NAME": "",
+    "CONDUCTING_BODY": "Punjabi University Patiala",
+    "EXAM_TYPE": "Semester",
+    "CATEGORY": "University",
+    "ACADEMIC_YEAR": "2026",
+    "CLASS_OR_LEVEL": "Undergraduate"
+  },
+  "SYLLABUS_STATUS": {
+    "RELEASED": false,
+    "RELEASE_DATE": "",
+    "SYLLABUS_VERSION": "",
+    "OFFICIAL_SYLLABUS_LINK": ""
+  },
+  "EXAM_PATTERN_OVERVIEW": {
+    "TOTAL_MARKS": 0,
+    "TOTAL_QUESTIONS": 0,
+    "DURATION": "",
+    "MEDIUM": "",
+    "MODE": "",
+    "NEGATIVE_MARKING": "",
+    "SECTIONS_COUNT": 0
+  },
+  "SUBJECTS": [],
+  "SECTIONAL_DETAILS": [],
+  "RECOMMENDED_RESOURCES": {
+    "BOOKS": [],
+    "ONLINE_RESOURCES": [],
+    "PREVIOUS_YEAR_PAPERS_LINK": ""
+  },
+  "PREPARATION_TIPS": {
+    "STRATEGY": "",
+    "IMPORTANT_TOPICS": [],
+    "TIME_MANAGEMENT_TIPS": ""
+  },
+  "IMPORTANT_DATES": {
+    "SYLLABUS_RELEASE_DATE": "",
+    "LAST_UPDATED": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://pupexamination.ac.in",
+    "SYLLABUS_PDF": "",
+    "OFFICIAL_WEBSITE": "https://pupexamination.ac.in"
+  },
+  "ADDITIONAL_INFO": {
+    "FREQUENTLY_ASKED_QUESTIONS": [],
+    "LATEST_CHANGES": "",
+    "CONTACT_HELPLINE": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>ABV-IIITM Gwalior Junior Superintendent Recruitment 2026 - Apply Offline for 10 Posts</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/abv-iiitm-gwalior-junior-superintendent-recruitment-2026-apply-offline-for-10-posts-3051500</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 07:43:37 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Junior Superintendent",
+    "JOB_TYPE": "Regular",
+    "JOB_CATEGORY": "Group B",
+    "DEPARTMENT": "Administration",
+    "MINISTRY": "Ministry of Education",
+    "RECRUITING_AGENCY": "Atal Bihari Vajpayee Indian Institute of Information Technology and Management (ABV-IIITM) Gwalior",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 10,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Junior Superintendent",
+        "VACANCIES": 10,
+        "CATEGORY": "",
+        "PAY_LEVEL": "Level 6",
+        "CLASSIFICATION": "Non-Technical"
+      }
+    ],
+    "JOB_LOCATION": "Gwalior",
+    "GROUP": "B"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "Level 6",
+    "PAY_SCALE": "₹35,400 - ₹1,12,400",
+    "MINIMUM_SALARY": 35400,
+    "MAXIMUM_SALARY": 112400,
+    "ALLOWANCES": ["DA", "HRA", "TPA", "Medical"],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Bachelor's Degree from a recognized university with knowledge of computer applications.",
+    "EDUCATION_DETAILS": [
+      {
+        "DEGREE": "Bachelor's Degree",
+        "STREAM": "Any",
+        "MINIMUM_PERCENTAGE": ""
+      }
+    ],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "Not required",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 18,
+      "MAXIMUM_AGE": 30,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "10 years",
+        "EX_SERVICEMEN": "As per Govt rules",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": "01-01-2026"
+    },
+    "PHYSICAL_STANDARDS": {},
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Offline",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "Download the application form from the official website.",
+      "Fill the form with all required details.",
+      "Attach self-attested copies of documents.",
+      "Send the application to the institute by post or courier."
+    ],
+    "REQUIRED_DOCUMENTS": [
+      "Educational certificates",
+      "Age proof",
+      "Caste certificate (if applicable)",
+      "Experience certificate (if any)",
+      "Recent passport-size photograph",
+      "Signature"
+    ],
+    "PHOTO_SPECIFICATIONS": "Passport size",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Written Test", "Skill Test", "Document Verification"],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": {
+        "TOTAL_MARKS": 100,
+        "DURATION": "2 hours",
+        "SUBJECTS": ["General English", "General Knowledge", "Computer Knowledge", "Quantitative Aptitude"],
+        "NEGATIVE_MARKING": "No"
+      },
+      "INTERVIEW": null,
+      "SKILL_TEST": {
+        "TYPE": "Computer Skill Test",
+        "TOTAL_MARKS": 50,
+        "DURATION": "30 minutes"
+      },
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": ["General English", "General Knowledge", "Computer Knowledge", "Quantitative Aptitude"],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "https://www.freejobalert.com/articles/abv-iiitm-gwalior-junior-superintendent-recruitment-2026-apply-offline-for-10-posts-3051500",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.iiitm.ac.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "1 year",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "Promotion to Superintendent",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "As per Government rules",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "Hindi and English",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>MAHAVITARAN Exam Date 2026 Out for LDC, Junior Assistant and More - Important Dates and Exam Pattern</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/mahavitaran-exam-date-2026-3051498</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 07:41:54 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "LDC, Junior Assistant and More",
+    "JOB_TYPE": "Government",
+    "JOB_CATEGORY": "Clerical",
+    "DEPARTMENT": "MAHAVITARAN",
+    "MINISTRY": "",
+    "RECRUITING_AGENCY": "MAHAVITARAN",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "LDC",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      },
+      {
+        "POST_NAME": "Junior Assistant",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "Maharashtra",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Graduate",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 18,
+      "MAXIMUM_AGE": 38,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "10 years",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": null,
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Written Exam", "Skill Test"],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": null,
+      "INTERVIEW": null,
+      "SKILL_TEST": {
+        "TYPE": "Typing",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "2026",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.freejobalert.com",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": "Maharashtra"
+  }
+}</t>
+  </si>
+  <si>
+    <t>IWAI Lower Division Clerk Result 2026 OUT (Direct Link) - Download Scorecard @ iwai.nic.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/iwai-lower-division-clerk-result-2026-3051497</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 07:40:35 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "Lower Division Clerk (LDC) Result",
+    "RECRUITMENT_NAME": "IWAI Lower Division Clerk Recruitment 2025",
+    "POST_NAME": "Lower Division Clerk (LDC)",
+    "CONDUCTING_BODY": "Inland Waterways Authority of India (IWAI)",
+    "EXAM_TYPE": "Recruitment",
+    "CATEGORY": "Govt Job"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": false,
+    "DECLARATION_DATE": "2026",
+    "RESULT_TYPE": "Scorecard",
+    "DIRECT_RESULT_LINK": "https://www.freejobalert.com/articles/iwai-lower-division-clerk-result-2026-3051497",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": ["Visit the official website iwai.nic.in", "Find the 'Result' section on the homepage", "Click on 'Lower Division Clerk Result 2025'", "Enter your registration number/roll number and date of birth", "View and download your scorecard"],
+    "REQUIRED_DETAILS": ["Registration Number / Roll Number", "Date of Birth"],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://www.freejobalert.com/articles/iwai-lower-division-clerk-result-2026-3051497",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "https://www.freejobalert.com/articles/iwai-lower-division-clerk-result-2026-3051497",
+    "OFFICIAL_WEBSITE": "https://iwai.nic.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>MDU Date Sheet 2026 Out for M.Sc, MA, B.Tech &amp; B.Ed Exams at mdu.ac.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/mdu-date-sheet-2026-out-for-msc-ma-btech-and-bed-exams-3051496</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 07:39:49 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Maharshi Dayanand University (MDU)",
+    "EXAM_TYPE": "University Examination",
+    "CATEGORY": "Date Sheet"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": false,
+    "DECLARATION_DATE": "",
+    "RESULT_TYPE": "Date Sheet",
+    "DIRECT_RESULT_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [],
+    "REQUIRED_DETAILS": [],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://www.freejobalert.com/articles/mdu-date-sheet-2026-out-for-msc-ma-btech-and-bed-exams-3051496",
+    "DIRECT_RESULT": "",
+    "OFFICIAL_WEBSITE": "http://mdu.ac.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>Jiwaji University Time Table 2026 OUT for LL.M &amp; BBA Hons June Exams at jiwaji.edu</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/jiwaji-university-time-table-2026-out-for-llm-and-bba-hons-june-exams-3051495</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 07:32:39 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "SYLLABUS_IDENTIFICATION": {
+    "EXAM_NAME": "LL.M &amp; BBA Hons June Exams",
+    "RECRUITMENT_NAME": "",
+    "CONDUCTING_BODY": "Jiwaji University",
+    "EXAM_TYPE": "University Exam",
+    "CATEGORY": "University",
+    "ACADEMIC_YEAR": "2025-2026",
+    "CLASS_OR_LEVEL": "Postgraduate and Undergraduate"
+  },
+  "SYLLABUS_STATUS": {
+    "RELEASED": false,
+    "RELEASE_DATE": "",
+    "SYLLABUS_VERSION": "",
+    "OFFICIAL_SYLLABUS_LINK": ""
+  },
+  "EXAM_PATTERN_OVERVIEW": {
+    "TOTAL_MARKS": 0,
+    "TOTAL_QUESTIONS": 0,
+    "DURATION": "",
+    "MEDIUM": "",
+    "MODE": "Offline",
+    "NEGATIVE_MARKING": "",
+    "SECTIONS_COUNT": 0
+  },
+  "SUBJECTS": [],
+  "SECTIONAL_DETAILS": [],
+  "RECOMMENDED_RESOURCES": {
+    "BOOKS": [],
+    "ONLINE_RESOURCES": [],
+    "PREVIOUS_YEAR_PAPERS_LINK": ""
+  },
+  "PREPARATION_TIPS": {
+    "STRATEGY": "",
+    "IMPORTANT_TOPICS": [],
+    "TIME_MANAGEMENT_TIPS": ""
+  },
+  "IMPORTANT_DATES": {
+    "SYLLABUS_RELEASE_DATE": "",
+    "LAST_UPDATED": "2025-04-11"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://www.freejobalert.com/articles/jiwaji-university-time-table-2026-out-for-llm-and-bba-hons-june-exams-3051495",
+    "SYLLABUS_PDF": "",
+    "OFFICIAL_WEBSITE": "https://www.jiwaji.edu"
+  },
+  "ADDITIONAL_INFO": {
+    "FREQUENTLY_ASKED_QUESTIONS": [],
+    "LATEST_CHANGES": "Time table released for June 2026 exams",
+    "CONTACT_HELPLINE": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>NISER Project Fellow Recruitment 2026 - Walkin</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/niser-project-fellow-recruitment-2026-walkin-3051494</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 07:28:07 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Project Fellow",
+    "JOB_TYPE": "Contractual",
+    "JOB_CATEGORY": "Research",
+    "DEPARTMENT": "School of Biological Sciences",
+    "MINISTRY": "Department of Atomic Energy",
+    "RECRUITING_AGENCY": "National Institute of Science Education and Research (NISER)",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 1,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Project Fellow",
+        "VACANCIES": 1,
+        "CATEGORY": "Unreserved",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "Bhubaneswar, Odisha",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "Rs. 25,000/- per month + HRA",
+    "MINIMUM_SALARY": 25000,
+    "MAXIMUM_SALARY": 25000,
+    "ALLOWANCES": ["HRA"],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "M.Sc. in Life Sciences/Biochemistry/Biotechnology/Microbiology/Genetics",
+    "EDUCATION_DETAILS": [
+      {
+        "DEGREE": "M.Sc.",
+        "SPECIALIZATION": "Life Sciences/Biochemistry/Biotechnology/Microbiology/Genetics",
+        "MINIMUM_PERCENTAGE": 60
+      }
+    ],
+    "MINIMUM_PERCENTAGE": "60% in M.Sc.",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 28,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": "30-01-2026"
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Walk-in",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "30-01-2026",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "Download application form from NISER website",
+      "Fill the form and bring it to the walk-in interview",
+      "Attach self-attested copies of certificates",
+      "Report to the venue on 30 Jan 2026 at 9 AM"
+    ],
+    "REQUIRED_DOCUMENTS": [
+      "Application form",
+      "Mark sheets and certificates",
+      "Experience certificates (if any)",
+      "Photo ID proof",
+      "Age proof",
+      "Caste certificate (if applicable)"
+    ],
+    "PHOTO_SPECIFICATIONS": "2 passport size photographs",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Walk-in Interview"],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": null,
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": null,
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "30-01-2026",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "30-01-2026",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "https://www.niser.ac.in/career/",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.niser.ac.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "As per GOI norms",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": ["Candidates must bring original documents for verification", "No TA/DA will be paid"],
+    "OFFICIAL_LANGUAGE": "English",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>RRB NTPC (Graduate) Admit Card 2026 (Out) - Download Here</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/rrb-ntpc-graduate-admit-card-2026-3051491</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 07:25:32 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "RRB NTPC (Graduate)",
+    "RECRUITMENT_NAME": "Non-Technical Popular Categories (NTPC) Graduate Level",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Railway Recruitment Board (RRB)",
+    "EXAM_TYPE": "Recruitment",
+    "CATEGORY": "Graduate Level"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "",
+    "DIRECT_DOWNLOAD_LINK": "https://www.freejobalert.com/articles/rrb-ntpc-graduate-admit-card-2026-3051491",
+    "STATUS_CHECK_LINK": ""
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "",
+    "EXAM_TIME": "",
+    "EXAM_SHIFT": "",
+    "EXAM_DURATION": "",
+    "EXAM_MODE": "Computer Based Test",
+    "EXAM_CENTER_CITY": "",
+    "EXAM_CENTER_NAME": "",
+    "FULL_SCHEDULE": []
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [
+      "Visit the official RRB website.",
+      "Click on the admit card link for NTPC Graduate.",
+      "Enter your registration number and date of birth.",
+      "Download and print the admit card."
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Download from FreeJobAlert link"
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": [],
+    "EXAM_DAY_GUIDELINES": [],
+    "DOCUMENTS_TO_CARRY": [],
+    "PROHIBITED_ITEMS": [],
+    "COVID_SPECIFIC": ""
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "",
+    "EXAM_DATE_LIST": [],
+    "RESULT_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_DOWNLOAD": "https://www.freejobalert.com/articles/rrb-ntpc-graduate-admit-card-2026-3051491",
+    "OFFICIAL_WEBSITE": "https://www.rrbcdg.gov.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "",
+    "REPRINT_OPTION": "Yes, multiple prints allowed.",
+    "CONTACT_DETAILS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Panjab University B.Sc Result 2026 Out - Direct Link to Download 3rd Semester Results at puexam.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/panjab-university-bsc-result-2026-out-direct-link-to-download-3rd-semester-results-3051490</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 07:23:48 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "B.Sc 3rd Semester",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Panjab University",
+    "EXAM_TYPE": "University Semester Exam",
+    "CATEGORY": "Undergraduate"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026",
+    "RESULT_TYPE": "Semester Result",
+    "DIRECT_RESULT_LINK": "https://puexam.in",
+    "STATUS_CHECK_LINK": "https://puexam.in"
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website puexam.in",
+      "Click on the result link for B.Sc 3rd Semester",
+      "Enter your roll number and other required details",
+      "Submit to view and download the result"
+    ],
+    "REQUIRED_DETAILS": ["Roll Number", "Date of Birth"],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://puexam.in",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://puexam.in",
+    "DIRECT_RESULT": "https://puexam.in",
+    "OFFICIAL_WEBSITE": "https://puexam.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>ICAR IISWC Recruitment 2026 - Apply Offline for 16 Assistant and Lower Division Clerk Posts</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/icar-iiswc-recruitment-2026-apply-offline-for-16-assistant-and-lower-division-clerk-posts-3051489</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 07:19:04 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "ICAR IISWC Recruitment 2026",
+    "JOB_TYPE": "सरकारी नौकरी",
+    "JOB_CATEGORY": "केंद्र सरकार",
+    "DEPARTMENT": "भारतीय कृषि अनुसंधान परिषद् (ICAR)",
+    "MINISTRY": "कृषि और किसान कल्याण मंत्रालय",
+    "RECRUITING_AGENCY": "भारतीय मृदा और जल संरक्षण संस्थान (IISWC)",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 16,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Assistant",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      },
+      {
+        "POST_NAME": "Lower Division Clerk",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "",
+    "GROUP": "C"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "ऑफलाइन",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Mumbai University Result 2026 Out - Check MA 2nd Sem, MHCMER 4th Sem Results Online at mu.ac.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/mumbai-university-result-2026-out-check-ma-2nd-sem-mhcmer-4th-sem-results-online-3051487</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 07:18:01 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "MA 2nd Sem, MHCMER 4th Sem",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Mumbai University",
+    "EXAM_TYPE": "University",
+    "CATEGORY": "Result"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026",
+    "RESULT_TYPE": "Semester",
+    "DIRECT_RESULT_LINK": "https://mu.ac.in",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website at mu.ac.in",
+      "Click on the 'Results' link on the homepage",
+      "Find the link for 'MA 2nd Sem Result 2026' or 'MHCMER 4th Sem Result 2026'",
+      "Enter your PRN/Roll Number and other required details",
+      "Click 'Submit' to view your result",
+      "Download and print the result for future reference"
+    ],
+    "REQUIRED_DETAILS": ["PRN/Roll Number", "Date of Birth"],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://mu.ac.in",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "https://mu.ac.in/resultpage",
+    "OFFICIAL_WEBSITE": "https://mu.ac.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>IIM Mumbai Management Trainee Recruitment 2026 - Apply Online for 10 Posts</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/iim-mumbai-management-trainee-recruitment-2026-apply-online-for-10-posts-3051486</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 07:14:30 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Management Trainee",
+    "JOB_TYPE": "Regular",
+    "JOB_CATEGORY": "Government",
+    "DEPARTMENT": "IIM Mumbai",
+    "MINISTRY": "Ministry of Education",
+    "RECRUITING_AGENCY": "Indian Institute of Management Mumbai",
+    "ADVT_NO": "To be announced",
+    "TOTAL_VACANCIES": 10,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Management Trainee",
+        "VACANCIES": 10,
+        "CATEGORY": "To be announced",
+        "PAY_LEVEL": "To be announced",
+        "CLASSIFICATION": "Group A"
+      }
+    ],
+    "JOB_LOCATION": "Mumbai, Maharashtra",
+    "GROUP": "A"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "To be announced",
+    "PAY_SCALE": "To be announced",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "To be announced",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "Freshers can apply",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "To be announced",
+    "APPLICATION_LAST_DATE": "To be announced",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "To be announced",
+    "EXAM_DATE": "To be announced",
+    "ADMIT_CARD_DATE": "To be announced",
+    "RESULT_DATE": "To be announced",
+    "INTERVIEW_DATE": "To be announced",
+    "FINAL_RESULT_DATE": "To be announced",
+    "JOINING_DATE": "To be announced"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.iimmumbai.ac.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>JNVU Result 2026 Out - Direct Link to Download UG PG Sem 1, 3, 5, 7 Results at jnvuiums.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/jnvu-result-2026-out-direct-link-to-download-ug-pg-sem-1-3-5-7-results-3051485</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 07:11:50 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "UG PG Semester Exam (Sem 1, 3, 5, 7)",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Jai Narain Vyas University (JNVU)",
+    "EXAM_TYPE": "Semester Exam",
+    "CATEGORY": "University"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026",
+    "RESULT_TYPE": "Semester Result",
+    "DIRECT_RESULT_LINK": "https://jnvuiums.in",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website jnvuiums.in",
+      "Click on the 'Result' link on the homepage",
+      "Select your course and semester",
+      "Enter your roll number and other required details",
+      "Submit and view/download your result"
+    ],
+    "REQUIRED_DETAILS": ["Roll Number", "Date of Birth"],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://jnvuiums.in",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "https://jnvuiums.in",
+    "OFFICIAL_WEBSITE": "https://www.jnvu.ac.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>BSNL JTO Syllabus and Exam Pattern 2026  - Download PDF</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/bsnl-jto-syllabus-and-exam-pattern-3051484</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 07:07:37 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "SYLLABUS_IDENTIFICATION": {
+    "EXAM_NAME": "BSNL JTO",
+    "RECRUITMENT_NAME": "Junior Telecom Officer",
+    "CONDUCTING_BODY": "BSNL",
+    "EXAM_TYPE": "Recruitment",
+    "CATEGORY": "Engineering",
+    "ACADEMIC_YEAR": "2026",
+    "CLASS_OR_LEVEL": ""
+  },
+  "SYLLABUS_STATUS": {
+    "RELEASED": false,
+    "RELEASE_DATE": "",
+    "SYLLABUS_VERSION": "",
+    "OFFICIAL_SYLLABUS_LINK": ""
+  },
+  "EXAM_PATTERN_OVERVIEW": {
+    "TOTAL_MARKS": 0,
+    "TOTAL_QUESTIONS": 0,
+    "DURATION": "",
+    "MEDIUM": "",
+    "MODE": "",
+    "NEGATIVE_MARKING": "",
+    "SECTIONS_COUNT": 0
+  },
+  "SUBJECTS": [],
+  "SECTIONAL_DETAILS": [],
+  "RECOMMENDED_RESOURCES": {
+    "BOOKS": [],
+    "ONLINE_RESOURCES": [],
+    "PREVIOUS_YEAR_PAPERS_LINK": ""
+  },
+  "PREPARATION_TIPS": {
+    "STRATEGY": "",
+    "IMPORTANT_TOPICS": [],
+    "TIME_MANAGEMENT_TIPS": ""
+  },
+  "IMPORTANT_DATES": {
+    "SYLLABUS_RELEASE_DATE": "",
+    "LAST_UPDATED": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "SYLLABUS_PDF": "https://www.freejobalert.com/articles/bsnl-jto-syllabus-and-exam-pattern-3051484",
+    "OFFICIAL_WEBSITE": ""
+  },
+  "ADDITIONAL_INFO": {
+    "FREQUENTLY_ASKED_QUESTIONS": [],
+    "LATEST_CHANGES": "",
+    "CONTACT_HELPLINE": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>PRSU Result 2026 Out - Check UG &amp; PG Results Online at prsu.ac.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/prsu-result-2026-out-check-ug-and-pg-results-online-3051483</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 07:02:32 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "PRSU UG/PG Result 2026",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Pt. Ravishankar Shukla University (PRSU)",
+    "EXAM_TYPE": "University Exam",
+    "CATEGORY": "UG/PG"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "TBD",
+    "RESULT_TYPE": "University Result",
+    "DIRECT_RESULT_LINK": "https://prsu.ac.in",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit official website prsu.ac.in",
+      "Click on Result link",
+      "Enter your roll number and date of birth",
+      "View and download result"
+    ],
+    "REQUIRED_DETAILS": ["Roll Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Check via SMS"
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://prsu.ac.in",
+      "VALIDITY_PERIOD": "TBD"
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "TBD",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://prsu.ac.in",
+    "DIRECT_RESULT": "https://prsu.ac.in",
+    "OFFICIAL_WEBSITE": "https://prsu.ac.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>Sports Authority of India Assistant Coach Recruitment 2026 Notification Out - Apply Offline for 100 Posts</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/sports-authority-of-india-assistant-coach-recruitment-2026-apply-offline-for-100-posts-3051482</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 07:00:26 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Assistant Coach",
+    "JOB_TYPE": "Government",
+    "JOB_CATEGORY": "Sports",
+    "DEPARTMENT": "Sports Authority of India",
+    "MINISTRY": "Ministry of Youth Affairs and Sports",
+    "RECRUITING_AGENCY": "Sports Authority of India",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 100,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Assistant Coach",
+        "VACANCIES": 100,
+        "CATEGORY": "",
+        "PAY_LEVEL": "Level 7 (₹ 44,900 – 1,42,400)",
+        "CLASSIFICATION": "Group B"
+      }
+    ],
+    "JOB_LOCATION": "All India",
+    "GROUP": "B"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "Level 7",
+    "PAY_SCALE": "₹ 44,900 – 1,42,400",
+    "MINIMUM_SALARY": 44900,
+    "MAXIMUM_SALARY": 142400,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Bachelor's degree in Physical Education or equivalent",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "3 years' coaching experience in sports",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 18,
+      "MAXIMUM_AGE": 35,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "10 years",
+        "EX_SERVICEMEN": "3 years + service length",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": "01-01-2026"
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Offline",
+    "APPLICATION_START_DATE": "01-01-2026",
+    "APPLICATION_LAST_DATE": "31-01-2026",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 500,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": "Demand Draft"
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "01-01-2026",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://sportsauthorityofindia.nic.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "2 years",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "As per government norms",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "Hindi/English",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Indian Army Agniveer Selection List 2026 OUT (Direct Link) - Download Scorecard @ joinindianarmy.nic.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/indian-army-agniveer-selection-list-2026-3051481</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 06:58:23 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "Indian Army Agniveer Selection List 2026",
+    "RECRUITMENT_NAME": "Agniveer Recruitment",
+    "POST_NAME": "Agniveer",
+    "CONDUCTING_BODY": "Indian Army",
+    "EXAM_TYPE": "Recruitment",
+    "CATEGORY": "Defence"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2025-04-10",
+    "RESULT_TYPE": "Selection List",
+    "DIRECT_RESULT_LINK": "https://www.freejobalert.com/go/?id=3051481",
+    "STATUS_CHECK_LINK": "https://www.freejobalert.com/go/?id=3051481"
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website joinindianarmy.nic.in",
+      "Click on the 'Agniveer Selection List 2026' link",
+      "Enter your application number and date of birth",
+      "View and download the result/scorecard"
+    ],
+    "REQUIRED_DETAILS": ["Application Number", "Date of Birth"],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://www.freejobalert.com/go/?id=3051481",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2025-04-10",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://www.freejobalert.com/go/?id=3051481",
+    "DIRECT_RESULT": "https://www.freejobalert.com/go/?id=3051481",
+    "OFFICIAL_WEBSITE": "https://joinindianarmy.nic.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>MAHAVITARAN Result 2026 OUT for UDC, LDC &amp; Head Clerk: Download Scorecard @mahadiscom.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/mahavitaran-udc-ldc-head-clerk-result-2026-3051480</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 06:57:52 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "MAHAVITARAN UDC, LDC &amp; Head Clerk Exam 2025",
+    "RECRUITMENT_NAME": "MAHAVITARAN Recruitment 2025 for UDC, LDC &amp; Head Clerk",
+    "POST_NAME": "UDC, LDC, Head Clerk",
+    "CONDUCTING_BODY": "Maharashtra State Electricity Distribution Company Ltd. (MAHAVITARAN)",
+    "EXAM_TYPE": "Recruitment Exam",
+    "CATEGORY": "Government Jobs"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026-01-01",
+    "RESULT_TYPE": "Scorecard",
+    "DIRECT_RESULT_LINK": "https://www.mahadiscom.in/result-2026",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website mahadiscom.in",
+      "Click on the 'Result' section",
+      "Find the link for 'MAHAVITARAN UDC, LDC &amp; Head Clerk Result 2026'",
+      "Enter your registration number and date of birth",
+      "Submit and view/download your scorecard"
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Click on the direct result link provided above."
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://www.mahadiscom.in/scorecard-2026",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026-01-01",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "https://www.mahadiscom.in/result-2026",
+    "OFFICIAL_WEBSITE": "https://www.mahadiscom.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>GTU Sem 8 Result 2026 Out - Direct Link to Download BE BH BI Semester 8 Results at Check at gtu.ac.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/gtu-sem-8-result-2026-out-direct-link-to-download-be-bh-bi-semester-8-results-3051479</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 06:52:26 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "GTU Sem 8 Result 2026",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Gujarat Technological University",
+    "EXAM_TYPE": "Semester Exam",
+    "CATEGORY": "University Result"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "",
+    "RESULT_TYPE": "Semester Result",
+    "DIRECT_RESULT_LINK": "",
+    "STATUS_CHECK_LINK": "https://www.gtu.ac.in"
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website gtu.ac.in.",
+      "Click on the 'Result' link on the homepage.",
+      "Select 'Semester 8 Result' from the list.",
+      "Enter your enrollment number and select the exam.",
+      "Click 'Submit' to view your result."
+    ],
+    "REQUIRED_DETAILS": ["Enrollment Number", "Exam Type"],
+    "ALTERNATE_METHOD": "Check via the direct link provided on Freejobalert.com."
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "",
+    "OFFICIAL_WEBSITE": "https://www.gtu.ac.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>Ayush University Result 2026 Out - Direct Link to Download B.Sc Nursing 7th Semester Results Online at ddumhsaucg.ac.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/ayush-university-result-2026-out-direct-link-to-download-bsc-nursing-7th-semester-results-online-3051478</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 06:44:29 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "B.Sc Nursing 7th Semester",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Ayush University",
+    "EXAM_TYPE": "University Semester Exam",
+    "CATEGORY": "University Exam"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026",
+    "RESULT_TYPE": "Semester Result",
+    "DIRECT_RESULT_LINK": "https://ddumhsaucg.ac.in",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": ["Visit the official website ddumhsaucg.ac.in", "Click on the result link", "Enter roll number and other details", "Download result"],
+    "REQUIRED_DETAILS": ["Roll Number", "Date of Birth"],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://ddumhsaucg.ac.in",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "https://ddumhsaucg.ac.in",
+    "OFFICIAL_WEBSITE": "https://ddumhsaucg.ac.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>BDL Trade Apprentices Recruitment 2026 Notification Out - Apply Online for 33 Posts</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/bdl-trade-apprentices-recruitment-2026-apply-online-for-33-posts-3051477</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 06:40:13 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Trade Apprentice",
+    "JOB_TYPE": "Apprenticeship",
+    "JOB_CATEGORY": "Technical",
+    "DEPARTMENT": "BDL",
+    "MINISTRY": "Ministry of Defence",
+    "RECRUITING_AGENCY": "Bharat Dynamics Limited (BDL)",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 33,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Trade Apprentice",
+        "VACANCIES": 33,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": "A"
+      }
+    ],
+    "JOB_LOCATION": "",
+    "GROUP": "A"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "ITI in relevant trade",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "Freshers",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 18,
+      "MAXIMUM_AGE": 27,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Assam University Silchar Result 2026 Out - Check FYUGP Odd Semester Results Online at ausexamination.ac.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/assam-university-silchar-result-2026-out-check-fyugp-odd-semester-results-online-3051476</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 06:30:32 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "FYUGP Odd Semester Examination",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Assam University Silchar",
+    "EXAM_TYPE": "University Semester Exam",
+    "CATEGORY": "University"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026",
+    "RESULT_TYPE": "Semester Result",
+    "DIRECT_RESULT_LINK": "https://ausexamination.ac.in/",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website ausexamination.ac.in",
+      "Click on the 'Result' link on the homepage",
+      "Select your course and semester",
+      "Enter your roll number and other required details",
+      "Submit and view your result"
+    ],
+    "REQUIRED_DETAILS": ["Roll Number", "Date of Birth or Registration Number"],
+    "ALTERNATE_METHOD": "Check via SMS or mobile app if provided by the university"
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://ausexamination.ac.in/result",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "https://ausexamination.ac.in/",
+    "OFFICIAL_WEBSITE": "https://ausexamination.ac.in/",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": ["Candidates should keep their roll number and registration details handy.", "Result can be downloaded in PDF format for future reference."]
+  }
+}</t>
+  </si>
+  <si>
+    <t>NEET MDS Result 2026 - Direct Link to Download MDS Result at natboard.edu.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/neet-mds-result-2026-direct-link-to-download-mds-result-3051475</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 06:26:25 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "NEET MDS",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "MDS",
+    "CONDUCTING_BODY": "National Board of Examinations (NBE)",
+    "EXAM_TYPE": "Entrance Exam",
+    "CATEGORY": "Postgraduate Medical"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": false,
+    "DECLARATION_DATE": "To be announced",
+    "RESULT_TYPE": "Scorecard",
+    "DIRECT_RESULT_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit natboard.edu.in",
+      "Click on NEET MDS Result link",
+      "Enter application number and date of birth",
+      "View and download result"
+    ],
+    "REQUIRED_DETAILS": ["Application Number", "Date of Birth"],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": "1 year"
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "",
+    "OFFICIAL_WEBSITE": "https://natboard.edu.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>DLSA Umaria Driver Recruitment 2026 - Apply Offline</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/dlsa-umaria-driver-recruitment-2026-apply-offline-3051474</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 06:23:52 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "DLSA Umaria Driver Recruitment 2026",
+    "JOB_TYPE": "सरकारी नौकरी",
+    "JOB_CATEGORY": "ड्राइवर",
+    "DEPARTMENT": "जिला विधिक सेवा प्राधिकरण (DLSA) उमरिया",
+    "MINISTRY": "विधि न्याय मंत्रालय",
+    "RECRUITING_AGENCY": "जिला विधिक सेवा प्राधिकरण (DLSA) उमरिया",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "उमरिया, मध्य प्रदेश",
+    "GROUP": "ग्रुप C"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "ऑफलाइन",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://dlsaumaria.com/",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Spot the 5 Differences: Can You Find All 5 Differences in This Image Within 10 Seconds?</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/spot-the-5-differences-can-you-find-all-5-differences-in-this-image-within-10-seconds-10246</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 06:18:44 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "MAIN_TOPIC": "Spot the Difference Puzzle",
+  "SUMMARY": "A puzzle challenge where readers are asked to find 5 differences between two images within 10 seconds, testing observation skills.",
+  "KEY_POINTS": [
+    "Puzzle features two similar images with 5 subtle differences.",
+    "Time limit of 10 seconds increases difficulty.",
+    "Designed to test and improve observation and concentration.",
+    "Commonly found in puzzle magazines and online games.",
+    "Answers are typically provided for verification."
+  ]
+}</t>
+  </si>
+  <si>
+    <t>Solapur University Exam Result 2026 Out - Direct Link to Download UG PG Sem 1, 2, 4 Results at sus.ac.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/solapur-university-exam-result-2026-out-direct-link-to-download-ug-pg-sem-1-2-4-results-3051471</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 06:18:06 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "Solapur University UG PG Sem 1, 2, 4 Exam",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Solapur University",
+    "EXAM_TYPE": "University Semester Exam",
+    "CATEGORY": "University Result"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026",
+    "RESULT_TYPE": "Semester Result",
+    "DIRECT_RESULT_LINK": "https://www.sus.ac.in",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website of Solapur University: https://www.sus.ac.in",
+      "Click on 'Examination' tab",
+      "Click on 'Result' link",
+      "Select your course and semester",
+      "Enter your roll number and other required details",
+      "Click on 'Submit' to view your result"
+    ],
+    "REQUIRED_DETAILS": [
+      "Roll Number"
+    ],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://www.sus.ac.in",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "https://www.sus.ac.in",
+    "OFFICIAL_WEBSITE": "https://www.sus.ac.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>MH SET Notification 2026 Out: Exam Date, Eligibility &amp; Apply Online Details</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/mh-set-notification-2026-3051470</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 06:14:58 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "महाराष्ट्र राज्य पात्रता परीक्षा (MH SET) 2026",
+    "JOB_TYPE": "पात्रता परीक्षा",
+    "JOB_CATEGORY": "शैक्षणिक",
+    "DEPARTMENT": "उच्च शिक्षा विभाग",
+    "MINISTRY": "महाराष्ट्र सरकार",
+    "RECRUITING_AGENCY": "महाराष्ट्र राज्य पात्रता परीक्षा सेवा (MSETS)",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [],
+    "JOB_LOCATION": "महाराष्ट्र",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "मान्यता प्राप्त विश्वविद्यालय से न्यूनतम 50% अंकों के साथ मास्टर डिग्री (SC/ST/OBC/PWD के लिए 55% या शिथिलता के अनुसार)",
+    "EDUCATION_DETAILS": [
+      "मास्टर डिग्री (MA/MSc/MCom आदि)"
+    ],
+    "MINIMUM_PERCENTAGE": "सामान्य: 55%, SC/ST/OBC/PWD: 50%",
+    "EXPERIENCE_REQUIRED": "नहीं",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "सरकारी नियमानुसार",
+        "OBC": "सरकारी नियमानुसार",
+        "PWD": "सरकारी नियमानुसार",
+        "EX_SERVICEMEN": "सरकारी नियमानुसार",
+        "WOMEN": "सरकारी नियमानुसार",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": [
+      "उम्मीदवार महाराष्ट्र के निवासी होने चाहिए या अन्य राज्यों के लिए पात्रता शर्तें लागू हो सकती हैं"
+    ]
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "ऑनलाइन",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 800,
+      "SC_ST_PWD_WOMEN": 400,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": "ऑनलाइन"
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "आधिकारिक वेबसाइट पर जाएँ",
+      "पंजीकरण करें",
+      "आवेदन पत्र भरें",
+      "दस्तावेज़ अपलोड करें",
+      "शुल्क भुगतान करें",
+      "सबमिट करें"
+    ],
+    "REQUIRED_DOCUMENTS": [
+      "फोटो",
+      "हस्ताक्षर",
+      "शैक्षणिक प्रमाण पत्र",
+      "आधार कार्ड",
+      "जाति प्रमाण पत्र",
+      "आय प्रमाण पत्र (यदि लागू हो)"
+    ],
+    "PHOTO_SPECIFICATIONS": "पासपोर्ट साइज, सफेद पृष्ठभूमि",
+    "SIGNATURE_SPECIFICATIONS": "काले/नीले स्याही से हस्ताक्षर"
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [
+      "पेपर I",
+      "पेपर II"
+    ],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [
+      "विषय से संबंधित पाठ्यक्रम"
+    ],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "2025-12-31",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "https://www.freejobalert.com/articles/mh-set-notification-2026-3051470",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://setexam.unipune.ac.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "NET/SET उत्तीर्ण होने पर सहायक प्राध्यापक पद हेतु पात्रता",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "महाराष्ट्र सरकार के नियमानुसार",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "मराठी और अंग्रेज़ी",
+    "DOMICILE_REQUIREMENTS": "महाराष्ट्र का निवासी या राज्य द्वारा निर्धारित शर्तें पूरी करने वाले"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Hemchand Yadav Vishwavidyalaya Result 2026 Out - Check BBA 3rd Semester Revaluation Results Online durg.ucanapply.com</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/hemchand-yadav-vishwavidyalaya-result-2026-out-check-bba-3rd-semester-revaluation-results-3051469</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 06:10:06 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "BBA 3rd Semester Revaluation Result",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Hemchand Yadav Vishwavidyalaya",
+    "EXAM_TYPE": "University Exam",
+    "CATEGORY": "Revaluation"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026",
+    "RESULT_TYPE": "Revaluation",
+    "DIRECT_RESULT_LINK": "https://durg.ucanapply.com",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": ["Visit the official website durg.ucanapply.com", "Enter your roll number and other required details", "Submit to view your revaluation result"],
+    "REQUIRED_DETAILS": ["Roll Number"],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "https://durg.ucanapply.com",
+    "OFFICIAL_WEBSITE": "https://durg.ucanapply.com",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>DLSA Narsinghpur Vehicle Driver Recruitment 2026 - Apply Offline</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/dlsa-narsinghpur-vehicle-driver-recruitment-2026-apply-offline-3051468</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 06:08:53 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Vehicle Driver",
+    "JOB_TYPE": "Government",
+    "JOB_CATEGORY": "Driving",
+    "DEPARTMENT": "District Legal Services Authority (DLSA)",
+    "MINISTRY": "Law and Justice",
+    "RECRUITING_AGENCY": "DLSA Narsinghpur",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 1,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Vehicle Driver",
+        "VACANCIES": 1,
+        "CATEGORY": "",
+        "PAY_LEVEL": "Level 1",
+        "CLASSIFICATION": "Group C"
+      }
+    ],
+    "JOB_LOCATION": "Narsinghpur, Madhya Pradesh",
+    "GROUP": "C"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "Level 1",
+    "PAY_SCALE": "Rs. 19,900 - 63,200",
+    "MINIMUM_SALARY": 19900,
+    "MAXIMUM_SALARY": 63200,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "10th pass + valid driving license",
+    "EDUCATION_DETAILS": [
+      "10th pass from recognized board",
+      "Valid driving license for heavy/light vehicles"
+    ],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "3 years driving experience",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 18,
+      "MAXIMUM_AGE": 40,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "10 years",
+        "EX_SERVICEMEN": "3 years",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": "01-01-2026"
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Offline",
+    "APPLICATION_START_DATE": "2025-12-01",
+    "APPLICATION_LAST_DATE": "2026-01-15",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": "No fee"
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "Download application form from official website",
+      "Fill form with required details",
+      "Attach self-attested copies of documents",
+      "Send by post to DLSA office"
+    ],
+    "REQUIRED_DOCUMENTS": [
+      "10th mark sheet",
+      "Driving license",
+      "Experience certificate",
+      "Age proof",
+      "Category certificate (if applicable)"
+    ],
+    "PHOTO_SPECIFICATIONS": "Recent passport size",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Document verification", "Driving test", "Interview"],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": null,
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "Driving test",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": null
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "2025-12-01",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.dlsanarsinghpur.org",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "2 years",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "Promotion to senior driver",
+    "TRANSFER_POLICY": "As per DLSA rules",
+    "RESERVATION_DETAILS": "As per MP government norms",
+    "CONTACT_HELPLINE": "07792-250123",
+    "IMP_INSTRUCTIONS": ["Bring original documents at time of interview"],
+    "OFFICIAL_LANGUAGE": "Hindi",
+    "DOMICILE_REQUIREMENTS": "MP domicile"
+  }
+}</t>
+  </si>
+  <si>
+    <t>DLSA Jhabua Vehicle Driver Recruitment 2026 - Apply Offline</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/dlsa-jhabua-vehicle-driver-recruitment-2026-apply-offline-3051466</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 06:08:42 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "वाहन चालक",
+    "JOB_TYPE": "सरकारी नौकरी",
+    "JOB_CATEGORY": "ग्रुप C",
+    "DEPARTMENT": "जिला विधिक सेवा प्राधिकरण",
+    "MINISTRY": "विधि और न्याय मंत्रालय",
+    "RECRUITING_AGENCY": "जिला विधिक सेवा प्राधिकरण, झाबुआ",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 1,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "वाहन चालक",
+        "VACANCIES": 1,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": "नियमित"
+      }
+    ],
+    "JOB_LOCATION": "झाबुआ, मध्य प्रदेश",
+    "GROUP": "C"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "Rs. 1,99,00 - 2,32,000 (प्रति माह? संभवतः वार्षिक?)",
+    "MINIMUM_SALARY": 19900,
+    "MAXIMUM_SALARY": 232000,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "10वीं पास, वैध ड्राइविंग लाइसेंस",
+    "EDUCATION_DETAILS": [
+      "10वीं पास",
+      "वैध ड्राइविंग लाइसेंस"
+    ],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "प्रासंगिक अनुभव",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 18,
+      "MAXIMUM_AGE": 40,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 वर्ष",
+        "OBC": "3 वर्ष",
+        "PWD": "10 वर्ष",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Offline",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "डाउनलोड आवेदन पत्र",
+      "भरकर प्राधिकरण को भेजें"
+    ],
+    "REQUIRED_DOCUMENTS": [
+      "शैक्षणिक प्रमाणपत्र",
+      "ड्राइविंग लाइसेंस",
+      "आयु प्रमाण",
+      "अनुभव प्रमाण"
+    ],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [
+      "दस्तावेज़ सत्यापन",
+      "ड्राइविंग टेस्ट",
+      "साक्षात्कार"
+    ],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": null,
+      "INTERVIEW": null,
+      "SKILL_TEST": {
+        "TYPE": "ड्राइविंग टेस्ट",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": null
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "https://www.freejobalert.com/articles/dlsa-jhabua-vehicle-driver-recruitment-2026-apply-offline-3051466",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "हिंदी, अंग्रेजी",
+    "DOMICILE_REQUIREMENTS": "मध्य प्रदेश"
+  }
+}</t>
+  </si>
+  <si>
+    <t>DRDO DEAL Paid Internship Recruitment 2026 - Apply Offline for 45 Posts</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/drdo-deal-paid-internship-recruitment-2026-apply-offline-for-45-posts-3051462</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 06:01:45 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Paid Internship",
+    "JOB_TYPE": "Internship",
+    "JOB_CATEGORY": "Non-Gazetted",
+    "DEPARTMENT": "Defence Research and Development Organisation (DRDO)",
+    "MINISTRY": "Ministry of Defence",
+    "RECRUITING_AGENCY": "DRDO DEAL (Defence Avionics Research Establishment)",
+    "ADVT_NO": null,
+    "TOTAL_VACANCIES": 45,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Paid Internship",
+        "VACANCIES": 45,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": "Internship"
+      }
+    ],
+    "JOB_LOCATION": "Dehradun, India",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 30000,
+    "MAXIMUM_SALARY": 30000,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "B.E/B.Tech/M.Sc in relevant disciplines",
+    "EDUCATION_DETAILS": [
+      "B.E/B.Tech in relevant engineering branches",
+      "M.Sc in relevant science disciplines"
+    ],
+    "MINIMUM_PERCENTAGE": "60% or equivalent CGPA",
+    "EXPERIENCE_REQUIRED": "Not Required",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 18,
+      "MAXIMUM_AGE": 28,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": "01-01-2026"
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Offline",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "2026-01-31",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "Download application form from official website",
+      "Fill the form with required details",
+      "Attach self-attested copies of documents",
+      "Send the application to the given address by post or in person"
+    ],
+    "REQUIRED_DOCUMENTS": [
+      "Educational certificates",
+      "Age proof",
+      "Category certificate if applicable",
+      "Recent passport size photograph",
+      "Signature"
+    ],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Shortlisting", "Interview"],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.drdo.gov.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [
+      "Internship duration is 6 months",
+      "Stipend of Rs. 30,000 per month"
+    ],
+    "OFFICIAL_LANGUAGE": "English/Hindi",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>GPRB Head Constable Driver Mechanic Syllabus and Exam Pattern 2026: Download PDF Here</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/gprb-head-constable-driver-mechanic-syllabus-and-exam-pattern-3051460</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 06:00:06 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "SYLLABUS_IDENTIFICATION": {
+    "EXAM_NAME": "GPRB Head Constable Driver Mechanic Exam",
+    "RECRUITMENT_NAME": "Head Constable Driver Mechanic Recruitment",
+    "CONDUCTING_BODY": "Gujarat Police Recruitment Board (GPRB)",
+    "EXAM_TYPE": "Recruitment",
+    "CATEGORY": "Police",
+    "ACADEMIC_YEAR": "2026",
+    "CLASS_OR_LEVEL": "Head Constable"
+  },
+  "SYLLABUS_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "",
+    "SYLLABUS_VERSION": "",
+    "OFFICIAL_SYLLABUS_LINK": ""
+  },
+  "EXAM_PATTERN_OVERVIEW": {
+    "TOTAL_MARKS": 100,
+    "TOTAL_QUESTIONS": 100,
+    "DURATION": "2 hours",
+    "MEDIUM": "English, Gujarati, Hindi",
+    "MODE": "Offline",
+    "NEGATIVE_MARKING": "No",
+    "SECTIONS_COUNT": 7
+  },
+  "SUBJECTS": [
+    {
+      "SUBJECT_NAME": "General Knowledge",
+      "TOPICS": [
+        {
+          "TOPIC_NAME": "General Knowledge",
+          "SUB_TOPICS": [],
+          "MARKS_WEIGHTAGE": "25",
+          "NUMBER_OF_QUESTIONS": 25,
+          "DIFFICULTY_LEVEL": ""
+        }
+      ],
+      "TOTAL_MARKS": 25,
+      "TOTAL_QUESTIONS": 25,
+      "IMPORTANT_BOOKS": [],
+      "NOTES": ""
+    },
+    {
+      "SUBJECT_NAME": "English",
+      "TOPICS": [
+        {
+          "TOPIC_NAME": "English",
+          "SUB_TOPICS": [],
+          "MARKS_WEIGHTAGE": "10",
+          "NUMBER_OF_QUESTIONS": 10,
+          "DIFFICULTY_LEVEL": ""
+        }
+      ],
+      "TOTAL_MARKS": 10,
+      "TOTAL_QUESTIONS": 10,
+      "IMPORTANT_BOOKS": [],
+      "NOTES": ""
+    },
+    {
+      "SUBJECT_NAME": "Gujarati",
+      "TOPICS": [
+        {
+          "TOPIC_NAME": "Gujarati",
+          "SUB_TOPICS": [],
+          "MARKS_WEIGHTAGE": "10",
+          "NUMBER_OF_QUESTIONS": 10,
+          "DIFFICULTY_LEVEL": ""
+        }
+      ],
+      "TOTAL_MARKS": 10,
+      "TOTAL_QUESTIONS": 10,
+      "IMPORTANT_BOOKS": [],
+      "NOTES": ""
+    },
+    {
+      "SUBJECT_NAME": "Mathematics",
+      "TOPICS": [
+        {
+          "TOPIC_NAME": "Mathematics",
+          "SUB_TOPICS": [],
+          "MARKS_WEIGHTAGE": "10",
+          "NUMBER_OF_QUESTIONS": 10,
+          "DIFFICULTY_LEVEL": ""
+        }
+      ],
+      "TOTAL_MARKS": 10,
+      "TOTAL_QUESTIONS": 10,
+      "IMPORTANT_BOOKS": [],
+      "NOTES": ""
+    },
+    {
+      "SUBJECT_NAME": "Reasoning",
+      "TOPICS": [
+        {
+          "TOPIC_NAME": "Reasoning",
+          "SUB_TOPICS": [],
+          "MARKS_WEIGHTAGE": "10",
+          "NUMBER_OF_QUESTIONS": 10,
+          "DIFFICULTY_LEVEL": ""
+        }
+      ],
+      "TOTAL_MARKS": 10,
+      "TOTAL_QUESTIONS": 10,
+      "IMPORTANT_BOOKS": [],
+      "NOTES": ""
+    },
+    {
+      "SUBJECT_NAME": "Computer Knowledge",
+      "TOPICS": [
+        {
+          "TOPIC_NAME": "Computer Knowledge",
+          "SUB_TOPICS": [],
+          "MARKS_WEIGHTAGE": "10",
+          "NUMBER_OF_QUESTIONS": 10,
+          "DIFFICULTY_LEVEL": ""
+        }
+      ],
+      "TOTAL_MARKS": 10,
+      "TOTAL_QUESTIONS": 10,
+      "IMPORTANT_BOOKS": [],
+      "NOTES": ""
+    },
+    {
+      "SUBJECT_NAME": "Driver Mechanic Knowledge",
+      "TOPICS": [
+        {
+          "TOPIC_NAME": "Driver Mechanic Knowledge",
+          "SUB_TOPICS": [],
+          "MARKS_WEIGHTAGE": "25",
+          "NUMBER_OF_QUESTIONS": 25,
+          "DIFFICULTY_LEVEL": ""
+        }
+      ],
+      "TOTAL_MARKS": 25,
+      "TOTAL_QUESTIONS": 25,
+      "IMPORTANT_BOOKS": [],
+      "NOTES": ""
+    }
+  ],
+  "SECTIONAL_DETAILS": [
+    {
+      "SECTION_NAME": "Written Examination",
+      "SUBJECTS_INCLUDED": [
+        "General Knowledge",
+        "English",
+        "Gujarati",
+        "Mathematics",
+        "Reasoning",
+        "Computer Knowledge",
+        "Driver Mechanic Knowledge"
+      ],
+      "TOTAL_MARKS": 100,
+      "TOTAL_QUESTIONS": 100
+    },
+    {
+      "SECTION_NAME": "Physical Efficiency Test (PET)",
+      "SUBJECTS_INCLUDED": [],
+      "TOTAL_MARKS": 0,
+      "TOTAL_QUESTIONS": 0
+    },
+    {
+      "SECTION_NAME": "Driving Test",
+      "SUBJECTS_INCLUDED": [],
+      "TOTAL_MARKS": 0,
+      "TOTAL_QUESTIONS": 0
+    }
+  ],
+  "RECOMMENDED_RESOURCES": {
+    "BOOKS": [],
+    "ONLINE_RESOURCES": [],
+    "PREVIOUS_YEAR_PAPERS_LINK": ""
+  },
+  "PREPARATION_TIPS": {
+    "STRATEGY": "Focus on General Knowledge and Driver Mechanic Knowledge sections as they carry higher weightage. Practice previous year papers.",
+    "IMPORTANT_TOPICS": [
+      "Current Affairs",
+      "Traffic Rules",
+      "Vehicle Mechanics"
+    ],
+    "TIME_MANAGEMENT_TIPS": "Allocate time proportionally to each section based on marks."
+  },
+  "IMPORTANT_DATES": {
+    "SYLLABUS_RELEASE_DATE": "",
+    "LAST_UPDATED": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "SYLLABUS_PDF": "",
+    "OFFICIAL_WEBSITE": ""
+  },
+  "ADDITIONAL_INFO": {
+    "FREQUENTLY_ASKED_QUESTIONS": [],
+    "LATEST_CHANGES": "",
+    "CONTACT_HELPLINE": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>UKPSC Lecturer Admit Card 2026 - Download Here</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/ukpsc-lecturer-admit-card-2026-3051459</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 05:59:08 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "UKPSC Lecturer Exam",
+    "RECRUITMENT_NAME": "UKPSC Lecturer Recruitment 2026",
+    "POST_NAME": "Lecturer",
+    "CONDUCTING_BODY": "Uttarakhand Public Service Commission (UKPSC)",
+    "EXAM_TYPE": "State Level Recruitment",
+    "CATEGORY": "Teaching"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": false,
+    "RELEASE_DATE": "To be announced",
+    "DIRECT_DOWNLOAD_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "To be announced",
+    "EXAM_TIME": "",
+    "EXAM_SHIFT": "",
+    "EXAM_DURATION": "",
+    "EXAM_MODE": "",
+    "EXAM_CENTER_CITY": "",
+    "EXAM_CENTER_NAME": "",
+    "FULL_SCHEDULE": []
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [
+      "Visit official UKPSC website",
+      "Click on 'Admit Card' section",
+      "Select 'Lecturer Admit Card 2026'",
+      "Enter Registration Number and Date of Birth",
+      "Download and print admit card"
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth"],
+    "ALTERNATE_METHOD": ""
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": [],
+    "EXAM_DAY_GUIDELINES": ["Reach exam center on time", "Carry a valid photo ID"],
+    "DOCUMENTS_TO_CARRY": ["Admit Card", "Photo ID proof"],
+    "PROHIBITED_ITEMS": ["Electronic gadgets", "Calculator", "Mobile phones"],
+    "COVID_SPECIFIC": ""
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "To be announced",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "Exam date",
+    "EXAM_DATE_LIST": [],
+    "RESULT_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://psc.uk.gov.in/",
+    "DIRECT_DOWNLOAD": "",
+    "OFFICIAL_WEBSITE": "https://psc.uk.gov.in/",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "Contact UKPSC helpline for any discrepancies",
+    "REPRINT_OPTION": "Available on official website",
+    "CONTACT_DETAILS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>District Court Rayagada Junior Clerk/Copyist Recruitment 2026 - Apply Offline</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/district-court-rayagada-junior-clerk-copyist-recruitment-2026-apply-offline-3051458</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 05:54:52 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Junior Clerk/Copyist",
+    "JOB_TYPE": "Sarkari Naukri",
+    "JOB_CATEGORY": "Court Staff",
+    "DEPARTMENT": "District Court",
+    "MINISTRY": "Law and Justice",
+    "RECRUITING_AGENCY": "District Court, Rayagada",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [],
+    "JOB_LOCATION": "Rayagada, Odisha",
+    "GROUP": "C"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Offline",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>District Judge Dhenkanal Recruitment 2026 - Apply Offline for 20 Junior Typist, Steno and More Posts</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/district-judge-dhenkanal-recruitment-2026-apply-offline-for-20-junior-typist-steno-and-more-posts-3051456</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 05:53:10 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Junior Typist, Steno and More Posts",
+    "JOB_TYPE": "सरकारी नौकरी",
+    "JOB_CATEGORY": "गैर-तकनीकी",
+    "DEPARTMENT": "District and Sessions Judge, Dhenkanal",
+    "MINISTRY": "Law and Justice",
+    "RECRUITING_AGENCY": "District and Sessions Judge Office, Dhenkanal",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 20,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Junior Typist",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": "अराजपत्रित"
+      },
+      {
+        "POST_NAME": "Steno",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": "अराजपत्रित"
+      },
+      {
+        "POST_NAME": "Other Posts",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": "अराजपत्रित"
+      }
+    ],
+    "JOB_LOCATION": "Dhenkanal, Odisha",
+    "GROUP": "C"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 18,
+      "MAXIMUM_AGE": 32,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "ऑफलाइन",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": null,
+      "INTERVIEW": null,
+      "SKILL_TEST": null,
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Angul District Court Recruitment 2026 - Apply Offline for 18 Salaried Amin, Steno and More Posts</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/angul-district-court-recruitment-2026-apply-offline-for-18-salaried-amin-steno-and-more-posts-3051453</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 05:50:43 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Salaried Amin, Steno and More Posts",
+    "JOB_TYPE": "Government",
+    "JOB_CATEGORY": "Group C",
+    "DEPARTMENT": "District Court",
+    "MINISTRY": "Law and Justice",
+    "RECRUITING_AGENCY": "Angul District Court",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 18,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Salaried Amin",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      },
+      {
+        "POST_NAME": "Steno",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      },
+      {
+        "POST_NAME": "Others",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "Angul, Odisha",
+    "GROUP": "C"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Offline",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Andhra University Result 2026 Out - Direct Link to Download B.Tech 7th Semester Revaluation Results at andhrauniversity.edu.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/andhra-university-result-2026-out-direct-link-to-download-btech-7th-semester-revaluation-results-3051450</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 05:50:14 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "B.Tech 7th Semester Revaluation",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Andhra University",
+    "EXAM_TYPE": "University Exam",
+    "CATEGORY": "Result"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026",
+    "RESULT_TYPE": "Revaluation Result",
+    "DIRECT_RESULT_LINK": "https://andhrauniversity.edu.in/result",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website andhrauniversity.edu.in",
+      "Click on the result link for B.Tech 7th Semester Revaluation",
+      "Enter roll number and other required details",
+      "Submit and view/download the result"
+    ],
+    "REQUIRED_DETAILS": ["Roll Number", "Date of Birth"],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://andhrauniversity.edu.in/result/scorecard",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "https://andhrauniversity.edu.in/result",
+    "OFFICIAL_WEBSITE": "https://andhrauniversity.edu.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "Candidates applied for revaluation can check their revised marks.",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>Dr MGR Medical University Result 2026 Out - Check B.Pharm 4th &amp; 7th Semester Results Online at tnmgrmuexam.ac.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/dr-mgr-medical-university-result-2026-out-check-bpharm-4th-7th-semester-results-online-3051448</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 05:42:30 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "B.Pharm 4th &amp; 7th Semester",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Dr MGR Medical University",
+    "EXAM_TYPE": "University Semester Exam",
+    "CATEGORY": "Academic Exam"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "",
+    "RESULT_TYPE": "Semester Result",
+    "DIRECT_RESULT_LINK": "https://tnmgrmuexam.ac.in",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit official website tnmgrmuexam.ac.in",
+      "Click on 'Results' tab",
+      "Select B.Pharm 4th &amp; 7th Semester result link",
+      "Enter registration number and other details",
+      "Submit to view result"
+    ],
+    "REQUIRED_DETAILS": ["Registration Number"],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "https://tnmgrmuexam.ac.in",
+    "OFFICIAL_WEBSITE": "https://tnmgrmuexam.ac.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
   }
 }</t>
   </si>
@@ -49229,6 +54868,1156 @@
         <v>1367</v>
       </c>
     </row>
+    <row r="342">
+      <c r="A342" t="s">
+        <v>7</v>
+      </c>
+      <c r="B342" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C342" t="s">
+        <v>1369</v>
+      </c>
+      <c r="D342" t="s">
+        <v>1370</v>
+      </c>
+      <c r="E342" t="s">
+        <v>24</v>
+      </c>
+      <c r="F342" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G342" t="s">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="s">
+        <v>7</v>
+      </c>
+      <c r="B343" t="s">
+        <v>1372</v>
+      </c>
+      <c r="C343" t="s">
+        <v>1373</v>
+      </c>
+      <c r="D343" t="s">
+        <v>1374</v>
+      </c>
+      <c r="E343" t="s">
+        <v>29</v>
+      </c>
+      <c r="F343" t="s">
+        <v>1372</v>
+      </c>
+      <c r="G343" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="s">
+        <v>7</v>
+      </c>
+      <c r="B344" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C344" t="s">
+        <v>1377</v>
+      </c>
+      <c r="D344" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E344" t="s">
+        <v>11</v>
+      </c>
+      <c r="F344" t="s">
+        <v>1376</v>
+      </c>
+      <c r="G344" t="s">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="s">
+        <v>52</v>
+      </c>
+      <c r="B345" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C345" t="s">
+        <v>1381</v>
+      </c>
+      <c r="D345" t="s">
+        <v>1382</v>
+      </c>
+      <c r="E345" t="s">
+        <v>24</v>
+      </c>
+      <c r="F345" t="s">
+        <v>1380</v>
+      </c>
+      <c r="G345" t="s">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="s">
+        <v>52</v>
+      </c>
+      <c r="B346" t="s">
+        <v>1384</v>
+      </c>
+      <c r="C346" t="s">
+        <v>1385</v>
+      </c>
+      <c r="D346" t="s">
+        <v>1386</v>
+      </c>
+      <c r="E346" t="s">
+        <v>11</v>
+      </c>
+      <c r="F346" t="s">
+        <v>1384</v>
+      </c>
+      <c r="G346" t="s">
+        <v>1387</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="s">
+        <v>52</v>
+      </c>
+      <c r="B347" t="s">
+        <v>1388</v>
+      </c>
+      <c r="C347" t="s">
+        <v>1389</v>
+      </c>
+      <c r="D347" t="s">
+        <v>1390</v>
+      </c>
+      <c r="E347" t="s">
+        <v>38</v>
+      </c>
+      <c r="F347" t="s">
+        <v>1388</v>
+      </c>
+      <c r="G347" t="s">
+        <v>1391</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="s">
+        <v>52</v>
+      </c>
+      <c r="B348" t="s">
+        <v>1392</v>
+      </c>
+      <c r="C348" t="s">
+        <v>1393</v>
+      </c>
+      <c r="D348" t="s">
+        <v>1394</v>
+      </c>
+      <c r="E348" t="s">
+        <v>11</v>
+      </c>
+      <c r="F348" t="s">
+        <v>1392</v>
+      </c>
+      <c r="G348" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="s">
+        <v>52</v>
+      </c>
+      <c r="B349" t="s">
+        <v>1396</v>
+      </c>
+      <c r="C349" t="s">
+        <v>1397</v>
+      </c>
+      <c r="D349" t="s">
+        <v>1398</v>
+      </c>
+      <c r="E349" t="s">
+        <v>11</v>
+      </c>
+      <c r="F349" t="s">
+        <v>1396</v>
+      </c>
+      <c r="G349" t="s">
+        <v>1399</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="s">
+        <v>52</v>
+      </c>
+      <c r="B350" t="s">
+        <v>1400</v>
+      </c>
+      <c r="C350" t="s">
+        <v>1401</v>
+      </c>
+      <c r="D350" t="s">
+        <v>1402</v>
+      </c>
+      <c r="E350" t="s">
+        <v>38</v>
+      </c>
+      <c r="F350" t="s">
+        <v>1400</v>
+      </c>
+      <c r="G350" t="s">
+        <v>1403</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="s">
+        <v>52</v>
+      </c>
+      <c r="B351" t="s">
+        <v>1404</v>
+      </c>
+      <c r="C351" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D351" t="s">
+        <v>1406</v>
+      </c>
+      <c r="E351" t="s">
+        <v>11</v>
+      </c>
+      <c r="F351" t="s">
+        <v>1404</v>
+      </c>
+      <c r="G351" t="s">
+        <v>1407</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="s">
+        <v>52</v>
+      </c>
+      <c r="B352" t="s">
+        <v>1408</v>
+      </c>
+      <c r="C352" t="s">
+        <v>1409</v>
+      </c>
+      <c r="D352" t="s">
+        <v>1410</v>
+      </c>
+      <c r="E352" t="s">
+        <v>29</v>
+      </c>
+      <c r="F352" t="s">
+        <v>1408</v>
+      </c>
+      <c r="G352" t="s">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="s">
+        <v>52</v>
+      </c>
+      <c r="B353" t="s">
+        <v>999</v>
+      </c>
+      <c r="C353" t="s">
+        <v>1412</v>
+      </c>
+      <c r="D353" t="s">
+        <v>1413</v>
+      </c>
+      <c r="E353" t="s">
+        <v>11</v>
+      </c>
+      <c r="F353" t="s">
+        <v>999</v>
+      </c>
+      <c r="G353" t="s">
+        <v>1414</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="s">
+        <v>52</v>
+      </c>
+      <c r="B354" t="s">
+        <v>1415</v>
+      </c>
+      <c r="C354" t="s">
+        <v>1416</v>
+      </c>
+      <c r="D354" t="s">
+        <v>1417</v>
+      </c>
+      <c r="E354" t="s">
+        <v>393</v>
+      </c>
+      <c r="F354" t="s">
+        <v>1415</v>
+      </c>
+      <c r="G354" t="s">
+        <v>1418</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="s">
+        <v>52</v>
+      </c>
+      <c r="B355" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C355" t="s">
+        <v>1420</v>
+      </c>
+      <c r="D355" t="s">
+        <v>1421</v>
+      </c>
+      <c r="E355" t="s">
+        <v>11</v>
+      </c>
+      <c r="F355" t="s">
+        <v>1419</v>
+      </c>
+      <c r="G355" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="s">
+        <v>52</v>
+      </c>
+      <c r="B356" t="s">
+        <v>1423</v>
+      </c>
+      <c r="C356" t="s">
+        <v>1424</v>
+      </c>
+      <c r="D356" t="s">
+        <v>1425</v>
+      </c>
+      <c r="E356" t="s">
+        <v>11</v>
+      </c>
+      <c r="F356" t="s">
+        <v>1423</v>
+      </c>
+      <c r="G356" t="s">
+        <v>1426</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="s">
+        <v>52</v>
+      </c>
+      <c r="B357" t="s">
+        <v>1427</v>
+      </c>
+      <c r="C357" t="s">
+        <v>1428</v>
+      </c>
+      <c r="D357" t="s">
+        <v>1429</v>
+      </c>
+      <c r="E357" t="s">
+        <v>29</v>
+      </c>
+      <c r="F357" t="s">
+        <v>1427</v>
+      </c>
+      <c r="G357" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="s">
+        <v>52</v>
+      </c>
+      <c r="B358" t="s">
+        <v>1431</v>
+      </c>
+      <c r="C358" t="s">
+        <v>1432</v>
+      </c>
+      <c r="D358" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E358" t="s">
+        <v>29</v>
+      </c>
+      <c r="F358" t="s">
+        <v>1431</v>
+      </c>
+      <c r="G358" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="s">
+        <v>52</v>
+      </c>
+      <c r="B359" t="s">
+        <v>1435</v>
+      </c>
+      <c r="C359" t="s">
+        <v>1436</v>
+      </c>
+      <c r="D359" t="s">
+        <v>1437</v>
+      </c>
+      <c r="E359" t="s">
+        <v>393</v>
+      </c>
+      <c r="F359" t="s">
+        <v>1435</v>
+      </c>
+      <c r="G359" t="s">
+        <v>1438</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="s">
+        <v>52</v>
+      </c>
+      <c r="B360" t="s">
+        <v>1439</v>
+      </c>
+      <c r="C360" t="s">
+        <v>1440</v>
+      </c>
+      <c r="D360" t="s">
+        <v>1441</v>
+      </c>
+      <c r="E360" t="s">
+        <v>11</v>
+      </c>
+      <c r="F360" t="s">
+        <v>1439</v>
+      </c>
+      <c r="G360" t="s">
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="s">
+        <v>52</v>
+      </c>
+      <c r="B361" t="s">
+        <v>1443</v>
+      </c>
+      <c r="C361" t="s">
+        <v>1444</v>
+      </c>
+      <c r="D361" t="s">
+        <v>1445</v>
+      </c>
+      <c r="E361" t="s">
+        <v>38</v>
+      </c>
+      <c r="F361" t="s">
+        <v>1443</v>
+      </c>
+      <c r="G361" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="s">
+        <v>52</v>
+      </c>
+      <c r="B362" t="s">
+        <v>1447</v>
+      </c>
+      <c r="C362" t="s">
+        <v>1448</v>
+      </c>
+      <c r="D362" t="s">
+        <v>1449</v>
+      </c>
+      <c r="E362" t="s">
+        <v>29</v>
+      </c>
+      <c r="F362" t="s">
+        <v>1447</v>
+      </c>
+      <c r="G362" t="s">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="s">
+        <v>52</v>
+      </c>
+      <c r="B363" t="s">
+        <v>1451</v>
+      </c>
+      <c r="C363" t="s">
+        <v>1452</v>
+      </c>
+      <c r="D363" t="s">
+        <v>1453</v>
+      </c>
+      <c r="E363" t="s">
+        <v>11</v>
+      </c>
+      <c r="F363" t="s">
+        <v>1451</v>
+      </c>
+      <c r="G363" t="s">
+        <v>1454</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="s">
+        <v>52</v>
+      </c>
+      <c r="B364" t="s">
+        <v>1455</v>
+      </c>
+      <c r="C364" t="s">
+        <v>1456</v>
+      </c>
+      <c r="D364" t="s">
+        <v>1457</v>
+      </c>
+      <c r="E364" t="s">
+        <v>29</v>
+      </c>
+      <c r="F364" t="s">
+        <v>1455</v>
+      </c>
+      <c r="G364" t="s">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="s">
+        <v>52</v>
+      </c>
+      <c r="B365" t="s">
+        <v>1459</v>
+      </c>
+      <c r="C365" t="s">
+        <v>1460</v>
+      </c>
+      <c r="D365" t="s">
+        <v>1461</v>
+      </c>
+      <c r="E365" t="s">
+        <v>11</v>
+      </c>
+      <c r="F365" t="s">
+        <v>1459</v>
+      </c>
+      <c r="G365" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="s">
+        <v>52</v>
+      </c>
+      <c r="B366" t="s">
+        <v>1463</v>
+      </c>
+      <c r="C366" t="s">
+        <v>1464</v>
+      </c>
+      <c r="D366" t="s">
+        <v>1465</v>
+      </c>
+      <c r="E366" t="s">
+        <v>29</v>
+      </c>
+      <c r="F366" t="s">
+        <v>1463</v>
+      </c>
+      <c r="G366" t="s">
+        <v>1466</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="s">
+        <v>52</v>
+      </c>
+      <c r="B367" t="s">
+        <v>1467</v>
+      </c>
+      <c r="C367" t="s">
+        <v>1468</v>
+      </c>
+      <c r="D367" t="s">
+        <v>1469</v>
+      </c>
+      <c r="E367" t="s">
+        <v>393</v>
+      </c>
+      <c r="F367" t="s">
+        <v>1467</v>
+      </c>
+      <c r="G367" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="s">
+        <v>52</v>
+      </c>
+      <c r="B368" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C368" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D368" t="s">
+        <v>1473</v>
+      </c>
+      <c r="E368" t="s">
+        <v>29</v>
+      </c>
+      <c r="F368" t="s">
+        <v>1471</v>
+      </c>
+      <c r="G368" t="s">
+        <v>1474</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="s">
+        <v>52</v>
+      </c>
+      <c r="B369" t="s">
+        <v>1475</v>
+      </c>
+      <c r="C369" t="s">
+        <v>1476</v>
+      </c>
+      <c r="D369" t="s">
+        <v>1477</v>
+      </c>
+      <c r="E369" t="s">
+        <v>11</v>
+      </c>
+      <c r="F369" t="s">
+        <v>1475</v>
+      </c>
+      <c r="G369" t="s">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="s">
+        <v>52</v>
+      </c>
+      <c r="B370" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C370" t="s">
+        <v>1480</v>
+      </c>
+      <c r="D370" t="s">
+        <v>1481</v>
+      </c>
+      <c r="E370" t="s">
+        <v>29</v>
+      </c>
+      <c r="F370" t="s">
+        <v>1479</v>
+      </c>
+      <c r="G370" t="s">
+        <v>1482</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="s">
+        <v>52</v>
+      </c>
+      <c r="B371" t="s">
+        <v>1483</v>
+      </c>
+      <c r="C371" t="s">
+        <v>1484</v>
+      </c>
+      <c r="D371" t="s">
+        <v>1485</v>
+      </c>
+      <c r="E371" t="s">
+        <v>29</v>
+      </c>
+      <c r="F371" t="s">
+        <v>1483</v>
+      </c>
+      <c r="G371" t="s">
+        <v>1486</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="s">
+        <v>52</v>
+      </c>
+      <c r="B372" t="s">
+        <v>1487</v>
+      </c>
+      <c r="C372" t="s">
+        <v>1488</v>
+      </c>
+      <c r="D372" t="s">
+        <v>1489</v>
+      </c>
+      <c r="E372" t="s">
+        <v>29</v>
+      </c>
+      <c r="F372" t="s">
+        <v>1487</v>
+      </c>
+      <c r="G372" t="s">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="s">
+        <v>52</v>
+      </c>
+      <c r="B373" t="s">
+        <v>1491</v>
+      </c>
+      <c r="C373" t="s">
+        <v>1492</v>
+      </c>
+      <c r="D373" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E373" t="s">
+        <v>29</v>
+      </c>
+      <c r="F373" t="s">
+        <v>1491</v>
+      </c>
+      <c r="G373" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="s">
+        <v>52</v>
+      </c>
+      <c r="B374" t="s">
+        <v>1495</v>
+      </c>
+      <c r="C374" t="s">
+        <v>1496</v>
+      </c>
+      <c r="D374" t="s">
+        <v>1497</v>
+      </c>
+      <c r="E374" t="s">
+        <v>11</v>
+      </c>
+      <c r="F374" t="s">
+        <v>1495</v>
+      </c>
+      <c r="G374" t="s">
+        <v>1498</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="s">
+        <v>52</v>
+      </c>
+      <c r="B375" t="s">
+        <v>1499</v>
+      </c>
+      <c r="C375" t="s">
+        <v>1500</v>
+      </c>
+      <c r="D375" t="s">
+        <v>1501</v>
+      </c>
+      <c r="E375" t="s">
+        <v>29</v>
+      </c>
+      <c r="F375" t="s">
+        <v>1499</v>
+      </c>
+      <c r="G375" t="s">
+        <v>1502</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="s">
+        <v>52</v>
+      </c>
+      <c r="B376" t="s">
+        <v>1503</v>
+      </c>
+      <c r="C376" t="s">
+        <v>1504</v>
+      </c>
+      <c r="D376" t="s">
+        <v>1505</v>
+      </c>
+      <c r="E376" t="s">
+        <v>29</v>
+      </c>
+      <c r="F376" t="s">
+        <v>1503</v>
+      </c>
+      <c r="G376" t="s">
+        <v>1506</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="s">
+        <v>52</v>
+      </c>
+      <c r="B377" t="s">
+        <v>1507</v>
+      </c>
+      <c r="C377" t="s">
+        <v>1508</v>
+      </c>
+      <c r="D377" t="s">
+        <v>1509</v>
+      </c>
+      <c r="E377" t="s">
+        <v>11</v>
+      </c>
+      <c r="F377" t="s">
+        <v>1507</v>
+      </c>
+      <c r="G377" t="s">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="s">
+        <v>52</v>
+      </c>
+      <c r="B378" t="s">
+        <v>1511</v>
+      </c>
+      <c r="C378" t="s">
+        <v>1512</v>
+      </c>
+      <c r="D378" t="s">
+        <v>1513</v>
+      </c>
+      <c r="E378" t="s">
+        <v>741</v>
+      </c>
+      <c r="F378" t="s">
+        <v>1511</v>
+      </c>
+      <c r="G378" t="s">
+        <v>1514</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="s">
+        <v>52</v>
+      </c>
+      <c r="B379" t="s">
+        <v>1515</v>
+      </c>
+      <c r="C379" t="s">
+        <v>1516</v>
+      </c>
+      <c r="D379" t="s">
+        <v>1517</v>
+      </c>
+      <c r="E379" t="s">
+        <v>29</v>
+      </c>
+      <c r="F379" t="s">
+        <v>1515</v>
+      </c>
+      <c r="G379" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="s">
+        <v>52</v>
+      </c>
+      <c r="B380" t="s">
+        <v>1519</v>
+      </c>
+      <c r="C380" t="s">
+        <v>1520</v>
+      </c>
+      <c r="D380" t="s">
+        <v>1521</v>
+      </c>
+      <c r="E380" t="s">
+        <v>11</v>
+      </c>
+      <c r="F380" t="s">
+        <v>1519</v>
+      </c>
+      <c r="G380" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="s">
+        <v>52</v>
+      </c>
+      <c r="B381" t="s">
+        <v>1523</v>
+      </c>
+      <c r="C381" t="s">
+        <v>1524</v>
+      </c>
+      <c r="D381" t="s">
+        <v>1525</v>
+      </c>
+      <c r="E381" t="s">
+        <v>29</v>
+      </c>
+      <c r="F381" t="s">
+        <v>1523</v>
+      </c>
+      <c r="G381" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="s">
+        <v>52</v>
+      </c>
+      <c r="B382" t="s">
+        <v>1527</v>
+      </c>
+      <c r="C382" t="s">
+        <v>1528</v>
+      </c>
+      <c r="D382" t="s">
+        <v>1529</v>
+      </c>
+      <c r="E382" t="s">
+        <v>11</v>
+      </c>
+      <c r="F382" t="s">
+        <v>1527</v>
+      </c>
+      <c r="G382" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="s">
+        <v>52</v>
+      </c>
+      <c r="B383" t="s">
+        <v>1531</v>
+      </c>
+      <c r="C383" t="s">
+        <v>1532</v>
+      </c>
+      <c r="D383" t="s">
+        <v>1533</v>
+      </c>
+      <c r="E383" t="s">
+        <v>11</v>
+      </c>
+      <c r="F383" t="s">
+        <v>1531</v>
+      </c>
+      <c r="G383" t="s">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="s">
+        <v>52</v>
+      </c>
+      <c r="B384" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C384" t="s">
+        <v>1536</v>
+      </c>
+      <c r="D384" t="s">
+        <v>1537</v>
+      </c>
+      <c r="E384" t="s">
+        <v>11</v>
+      </c>
+      <c r="F384" t="s">
+        <v>1535</v>
+      </c>
+      <c r="G384" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="s">
+        <v>52</v>
+      </c>
+      <c r="B385" t="s">
+        <v>1539</v>
+      </c>
+      <c r="C385" t="s">
+        <v>1540</v>
+      </c>
+      <c r="D385" t="s">
+        <v>1541</v>
+      </c>
+      <c r="E385" t="s">
+        <v>393</v>
+      </c>
+      <c r="F385" t="s">
+        <v>1539</v>
+      </c>
+      <c r="G385" t="s">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="s">
+        <v>52</v>
+      </c>
+      <c r="B386" t="s">
+        <v>1543</v>
+      </c>
+      <c r="C386" t="s">
+        <v>1544</v>
+      </c>
+      <c r="D386" t="s">
+        <v>1545</v>
+      </c>
+      <c r="E386" t="s">
+        <v>38</v>
+      </c>
+      <c r="F386" t="s">
+        <v>1543</v>
+      </c>
+      <c r="G386" t="s">
+        <v>1546</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="s">
+        <v>52</v>
+      </c>
+      <c r="B387" t="s">
+        <v>1547</v>
+      </c>
+      <c r="C387" t="s">
+        <v>1548</v>
+      </c>
+      <c r="D387" t="s">
+        <v>1549</v>
+      </c>
+      <c r="E387" t="s">
+        <v>11</v>
+      </c>
+      <c r="F387" t="s">
+        <v>1547</v>
+      </c>
+      <c r="G387" t="s">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="s">
+        <v>52</v>
+      </c>
+      <c r="B388" t="s">
+        <v>1551</v>
+      </c>
+      <c r="C388" t="s">
+        <v>1552</v>
+      </c>
+      <c r="D388" t="s">
+        <v>1553</v>
+      </c>
+      <c r="E388" t="s">
+        <v>11</v>
+      </c>
+      <c r="F388" t="s">
+        <v>1551</v>
+      </c>
+      <c r="G388" t="s">
+        <v>1554</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="s">
+        <v>52</v>
+      </c>
+      <c r="B389" t="s">
+        <v>1555</v>
+      </c>
+      <c r="C389" t="s">
+        <v>1556</v>
+      </c>
+      <c r="D389" t="s">
+        <v>1557</v>
+      </c>
+      <c r="E389" t="s">
+        <v>11</v>
+      </c>
+      <c r="F389" t="s">
+        <v>1555</v>
+      </c>
+      <c r="G389" t="s">
+        <v>1558</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="s">
+        <v>52</v>
+      </c>
+      <c r="B390" t="s">
+        <v>1559</v>
+      </c>
+      <c r="C390" t="s">
+        <v>1560</v>
+      </c>
+      <c r="D390" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E390" t="s">
+        <v>29</v>
+      </c>
+      <c r="F390" t="s">
+        <v>1559</v>
+      </c>
+      <c r="G390" t="s">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="s">
+        <v>52</v>
+      </c>
+      <c r="B391" t="s">
+        <v>1563</v>
+      </c>
+      <c r="C391" t="s">
+        <v>1564</v>
+      </c>
+      <c r="D391" t="s">
+        <v>1565</v>
+      </c>
+      <c r="E391" t="s">
+        <v>29</v>
+      </c>
+      <c r="F391" t="s">
+        <v>1563</v>
+      </c>
+      <c r="G391" t="s">
+        <v>1566</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/data/articles.xlsx
+++ b/data/articles.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1567" uniqueCount="1567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1770" uniqueCount="1770">
   <si>
     <t>Competitor</t>
   </si>
@@ -46717,6 +46717,7201 @@
     "REVALUATION_PROCESS": "",
     "CONTACT_DETAILS": "",
     "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>BSNL Senior Executive Trainee Exam Date 2026 – Out</t>
+  </si>
+  <si>
+    <t>https://sarkariresult.com.cm/bsnl-senior-executive-trainee-2026/</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 10:43:09 +0000</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Senior Executive Trainee",
+    "JOB_TYPE": "Regular",
+    "JOB_CATEGORY": "Technical",
+    "DEPARTMENT": "Telecommunications",
+    "MINISTRY": "Ministry of Communications",
+    "RECRUITING_AGENCY": "BSNL",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [],
+    "JOB_LOCATION": "All India",
+    "GROUP": "A"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {},
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {},
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {},
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {},
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {}
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "2026",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://sarkariresult.com.cm",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/anna-university-project-assistant-recruitment-2026-apply-offline-3051609</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 12:57:52 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Project Assistant",
+    "JOB_TYPE": "Contractual",
+    "JOB_CATEGORY": "Technical",
+    "DEPARTMENT": "Project related department",
+    "MINISTRY": "",
+    "RECRUITING_AGENCY": "Anna University",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Project Assistant",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": "Technical"
+      }
+    ],
+    "JOB_LOCATION": "Chennai, Tamil Nadu",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": null,
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Offline",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": null,
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": null
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.annauniv.edu",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Arogyakeralam Recruitment 2026 - Apply Online for Ophthalmic Assistant, Audiologist cum Speech therapist and More Posts</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/arogyakeralam-recruitment-2026-apply-online-for-ophthalmic-assistant-senior-treatment-supervisor-and-more-posts-3051607</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 12:56:40 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Ophthalmic Assistant, Audiologist cum Speech Therapist and More Posts",
+    "JOB_TYPE": "Government",
+    "JOB_CATEGORY": "Health",
+    "DEPARTMENT": "Arogyakeralam",
+    "MINISTRY": "",
+    "RECRUITING_AGENCY": "Arogyakeralam",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Ophthalmic Assistant",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      },
+      {
+        "POST_NAME": "Audiologist cum Speech Therapist",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "Kerala",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "https://www.arogyakeralam.gov.in",
+    "OFFICIAL_WEBSITE": "https://www.arogyakeralam.gov.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Bank of Baroda Apprentice Previous Year Question Paper: Download PDF Here</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/bank-of-baroda-apprentice-previous-year-question-paper-download-pdf-here-3051605</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 12:53:53 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "PAPER_IDENTIFICATION": {
+    "EXAM_NAME": "Bank of Baroda Apprentice Exam",
+    "RECRUITMENT_NAME": "Bank of Baroda Apprentice Recruitment",
+    "POST_NAME": "Apprentice",
+    "CONDUCTING_BODY": "Bank of Baroda",
+    "EXAM_TYPE": "Recruitment",
+    "CATEGORY": "Banking",
+    "PAPER_YEAR": "",
+    "PAPER_SHIFT": "",
+    "PAPER_SET": "",
+    "PAPER_LANGUAGE": "",
+    "PAPER_SUBJECT": "",
+    "PAPER_CODE": "",
+    "PAPER_TYPE": "Previous Year Question Paper"
+  },
+  "PAPER_STATUS": {
+    "RELEASED": false,
+    "RELEASE_DATE": "",
+    "AVAILABILITY": "Downloadable via link",
+    "DIRECT_DOWNLOAD_LINK": "",
+    "STATUS_CHECK_LINK": "https://www.freejobalert.com/articles/bank-of-baroda-apprentice-previous-year-question-paper-download-pdf-here-3051605"
+  },
+  "PAPER_DETAILS": {
+    "TOTAL_MARKS": 0,
+    "TOTAL_QUESTIONS": 0,
+    "DURATION": "",
+    "MODE": "",
+    "NEGATIVE_MARKING": "",
+    "DIFFICULTY_LEVEL": "",
+    "SOLVED": false,
+    "ANSWER_KEY_AVAILABLE": false,
+    "ANSWER_KEY_LINK": "",
+    "SOLUTION_LINK": "",
+    "OFFICIAL_OR_MEMORY_BASED": ""
+  },
+  "SUBJECT_WISE_DETAILS": [],
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": ["Visit the article URL", "Click on the download link provided"],
+    "REQUIRED_DETAILS": [],
+    "ALTERNATE_METHOD": ""
+  },
+  "FILE_INFORMATION": {
+    "FILE_FORMAT": "PDF",
+    "FILE_SIZE": "",
+    "NUMBER_OF_PAGES": 0
+  },
+  "IMPORTANT_DATES": {
+    "EXAM_DATE": "",
+    "PAPER_RELEASE_DATE": "",
+    "ANSWER_KEY_RELEASE_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_DOWNLOAD": "",
+    "OFFICIAL_WEBSITE": "https://www.bankofbaroda.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PREPARATION_TIPS": "",
+    "IMPORTANT_TOPICS": [],
+    "COMMON_MISTAKES": "",
+    "CONTACT_DETAILS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>ICAR-IISWC Young Professional-I Recruitment 2026 - Walkin</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/icar-iiswc-young-professional-i-yp-1-recruitment-2026-walkin-3051604</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 12:52:44 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Young Professional-I",
+    "JOB_TYPE": "Young Professional",
+    "JOB_CATEGORY": "Research/Project",
+    "DEPARTMENT": "ICAR-Indian Institute of Soil and Water Conservation",
+    "MINISTRY": "Ministry of Agriculture and Farmers Welfare",
+    "RECRUITING_AGENCY": "ICAR-Indian Institute of Soil and Water Conservation (IISWC)",
+    "ADVT_NO": "Not available",
+    "TOTAL_VACANCIES": 1,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Young Professional-I",
+        "VACANCIES": 1,
+        "CATEGORY": "Not available",
+        "PAY_LEVEL": "Not available",
+        "CLASSIFICATION": "Contractual"
+      }
+    ],
+    "JOB_LOCATION": "Dehradun, Uttarakhand",
+    "GROUP": "Not applicable"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "Not available",
+    "PAY_SCALE": "₹25,000 per month",
+    "MINIMUM_SALARY": 25000,
+    "MAXIMUM_SALARY": 25000,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Graduate in Agriculture/Agricultural Engineering/Soil Science/Computer Application/Life Sciences or equivalent",
+    "EDUCATION_DETAILS": [
+      "Graduate in Agriculture",
+      "Graduate in Agricultural Engineering",
+      "Graduate in Soil Science",
+      "Graduate in Computer Application",
+      "Graduate in Life Sciences or equivalent"
+    ],
+    "MINIMUM_PERCENTAGE": "60%",
+    "EXPERIENCE_REQUIRED": "Preference to candidates with experience in research projects",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 21,
+      "MAXIMUM_AGE": 45,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "10 years",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": "Date of interview"
+    },
+    "PHYSICAL_STANDARDS": {},
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Walk-in",
+    "APPLICATION_START_DATE": "2026-01-01",
+    "APPLICATION_LAST_DATE": "2026-01-15",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": "No fee"
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "Visit the official IISWC website for notification",
+      "Prepare application form and self-attested documents",
+      "Appear for walk-in interview at the given venue"
+    ],
+    "REQUIRED_DOCUMENTS": [
+      "Application form",
+      "Educational certificates",
+      "Age proof",
+      "Experience certificates (if any)",
+      "Category certificate (if applicable)",
+      "Passport size photographs"
+    ],
+    "PHOTO_SPECIFICATIONS": "Not specified",
+    "SIGNATURE_SPECIFICATIONS": "Not specified"
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [
+      "Walk-in Interview"
+    ],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": null,
+      "INTERVIEW": {
+        "TOTAL_MARKS": 100,
+        "DURATION": "Not specified"
+      },
+      "SKILL_TEST": null,
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {}
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "2026-01-01",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "2026-01-15",
+    "FINAL_RESULT_DATE": "2026-01-20",
+    "JOINING_DATE": "2026-02-01"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "https://www.freejobalert.com/wp-content/uploads/2026/01/ICAR-IISWC-Young-Professional-I-Walkin.pdf",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.iiswc.org",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "As per ICAR norms",
+    "CONTACT_HELPLINE": "0135-2751234",
+    "IMP_INSTRUCTIONS": [
+      "Candidates must bring all original documents for verification",
+      "No TA/DA will be paid for attending interview"
+    ],
+    "OFFICIAL_LANGUAGE": "Hindi/English",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>IIM Guwahati Junior Assistant Recruitment 2026 - Apply Online</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/iim-guwahati-junior-assistant-recruitment-2026-apply-online-3051599</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 12:47:50 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Junior Assistant",
+    "JOB_TYPE": "Regular",
+    "JOB_CATEGORY": "Non-Technical",
+    "DEPARTMENT": "Administration",
+    "MINISTRY": "Ministry of Education",
+    "RECRUITING_AGENCY": "IIM Guwahati",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Junior Assistant",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "Guwahati, Assam",
+    "GROUP": "C"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "Pay Level 3",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 21700,
+    "MAXIMUM_SALARY": 69100,
+    "ALLOWANCES": ["Dearness Allowance", "House Rent Allowance", "Transport Allowance"],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Graduation from a recognized university with computer skills",
+    "EDUCATION_DETAILS": ["Graduation"],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 21,
+      "MAXIMUM_AGE": 30,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "10 years",
+        "EX_SERVICEMEN": "As per norms",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "2026-01-01",
+    "APPLICATION_LAST_DATE": "2026-01-31",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 500,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": "Online"
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "1. Visit the official website of IIM Guwahati.",
+      "2. Click on the recruitment notification for Junior Assistant.",
+      "3. Register with a valid email ID and phone number.",
+      "4. Fill the application form with all required details.",
+      "5. Upload scanned copies of photograph and signature.",
+      "6. Pay the application fee online.",
+      "7. Submit the form and take a printout for future reference."
+    ],
+    "REQUIRED_DOCUMENTS": ["Photograph", "Signature", "Educational certificates", "Caste certificate (if applicable)", "ID proof"],
+    "PHOTO_SPECIFICATIONS": "Recent passport size color photo (max 50 KB, JPEG format)",
+    "SIGNATURE_SPECIFICATIONS": "Signature in black ink on white paper (max 20 KB, JPEG format)"
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Written Test", "Skill Test", "Interview"],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": null,
+      "INTERVIEW": {
+        "TOTAL_MARKS": 100,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "Computer proficiency test",
+        "TOTAL_MARKS": 100,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": ["General Knowledge", "English", "Quantitative Aptitude", "Reasoning", "Computer Skills"],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "2025-12-15",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "https://www.freejobalert.com/articles/iim-guwahati-junior-assistant-recruitment-2026-apply-online-3051599",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "2 years",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "As per Government of India norms",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "English",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>DLSA Kamrup Driver Result 2026 OUT (Direct Link) - Download Scorecard @kamrup.dcourts.gov.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/dlsa-kamrup-driver-result-2026-3051538</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 12:42:52 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Driver",
+    "JOB_TYPE": "Government",
+    "JOB_CATEGORY": "Technical",
+    "DEPARTMENT": "District Legal Services Authority (DLSA), Kamrup",
+    "MINISTRY": "Law and Justice",
+    "RECRUITING_AGENCY": "District Legal Services Authority (DLSA), Kamrup",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Driver",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "Kamrup, Assam",
+    "GROUP": "C"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://kamrup.dcourts.gov.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "https://www.freejobalert.com/articles/dlsa-kamrup-driver-result-2026-3051538",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>HPSLSA Driver-cum-Office Assistant Recruitment 2026 - Apply Online for 11 Posts</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/hpslsa-driver-cum-office-assistant-recruitment-2026-apply-online-for-11-posts-3051597</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 12:41:27 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Driver-cum-Office Assistant",
+    "JOB_TYPE": "सरकारी नौकरी",
+    "JOB_CATEGORY": "गैर-तकनीकी",
+    "DEPARTMENT": "Himachal Pradesh State Legal Services Authority",
+    "MINISTRY": "Law &amp; Justice, Himachal Pradesh",
+    "RECRUITING_AGENCY": "Himachal Pradesh State Legal Services Authority (HPSLSA)",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 11,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Driver-cum-Office Assistant",
+        "VACANCIES": 11,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "Himachal Pradesh",
+    "GROUP": "C"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "₹19,900 - ₹63,200",
+    "MINIMUM_SALARY": 19900,
+    "MAXIMUM_SALARY": 63200,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "10th pass + valid driving license",
+    "EDUCATION_DETAILS": [
+      "Matriculation (10th) from a recognized board",
+      "Valid driving license for light and heavy vehicles"
+    ],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "2 years driving experience",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 18,
+      "MAXIMUM_AGE": 45,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "10 years",
+        "EX_SERVICEMEN": "3 years",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": "01-01-2026"
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "2026-01-15",
+    "APPLICATION_LAST_DATE": "2026-02-14",
+    "LAST_DATE_FOR_FEE": "2026-02-14",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 100,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": "Online"
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "Visit the official website hpslsa.nic.in",
+      "Click on the recruitment notification",
+      "Fill the online application form",
+      "Upload required documents",
+      "Pay application fee",
+      "Submit the form and take printout"
+    ],
+    "REQUIRED_DOCUMENTS": [
+      "10th mark sheet and certificate",
+      "Valid driving license",
+      "Experience certificate",
+      "Photo and signature",
+      "Caste certificate (if applicable)"
+    ],
+    "PHOTO_SPECIFICATIONS": "Passport size, white background, JPEG, max 100KB",
+    "SIGNATURE_SPECIFICATIONS": "Black ink on white paper, JPEG, max 50KB"
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [
+      "Written Test",
+      "Driving Test",
+      "Document Verification"
+    ],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 100,
+        "DURATION": "2 hours",
+        "SUBJECTS": [
+          "General Knowledge",
+          "Hindi",
+          "Driving rules and regulations"
+        ],
+        "NEGATIVE_MARKING": "1/4 mark per wrong answer"
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "Driving Test",
+        "TOTAL_MARKS": 50,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [
+      "General Knowledge: Himachal Pradesh, National/International events",
+      "Hindi grammar and comprehension",
+      "Traffic rules and driving safety"
+    ],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "2026-01-10",
+    "EXAM_DATE": "2026-03-15",
+    "ADMIT_CARD_DATE": "2026-03-01",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "https://hpslsa.nic.in/advt-2026.pdf",
+    "APPLY_ONLINE_LINK": "https://hpslsa.nic.in/apply",
+    "OFFICIAL_WEBSITE": "https://hpslsa.nic.in",
+    "ADMIT_CARD_LINK": "https://hpslsa.nic.in/admitcard",
+    "RESULT_LINK": "https://hpslsa.nic.in/result",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "2 years",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "Promotion to higher grades as per departmental rules",
+    "TRANSFER_POLICY": "Within Himachal Pradesh",
+    "RESERVATION_DETAILS": "As per Himachal Government norms",
+    "CONTACT_HELPLINE": "0177-2801234",
+    "IMP_INSTRUCTIONS": [
+      "Apply only online, no offline applications",
+      "Keep a copy of submitted application for future reference"
+    ],
+    "OFFICIAL_LANGUAGE": "Hindi and English",
+    "DOMICILE_REQUIREMENTS": "Himachal Pradesh domicile preferred"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Tezpur University Recruitment 2026 - Apply Online for Field Assistant, Junior Research Fellow Posts</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/tezpur-university-recruitment-2026-apply-online-for-field-assistant-junior-research-fellow-posts-3051595</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 12:34:13 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Field Assistant, Junior Research Fellow",
+    "JOB_TYPE": "Contractual",
+    "JOB_CATEGORY": "Research",
+    "DEPARTMENT": "Not specified",
+    "MINISTRY": "Ministry of Education",
+    "RECRUITING_AGENCY": "Tezpur University",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Field Assistant",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      },
+      {
+        "POST_NAME": "Junior Research Fellow",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "Tezpur, Assam",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "As per norms",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "For Field Assistant: 10th pass; For JRF: Master's degree in relevant discipline",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "Desirable for JRF",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online/Offline",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Interview"],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": null,
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": null,
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.tezu.ernet.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>MANIT Bhopal Research Assistant Recruitment 2026 - Apply Offline</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/manit-bhopal-research-assistant-recruitment-2026-apply-offline-3051593</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 12:33:40 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Research Assistant",
+    "JOB_TYPE": "Research",
+    "JOB_CATEGORY": "Group C",
+    "DEPARTMENT": "Maulana Azad National Institute of Technology (MANIT)",
+    "MINISTRY": "Ministry of Education",
+    "RECRUITING_AGENCY": "MANIT Bhopal",
+    "ADVT_NO": "MANIT/RA/2026",
+    "TOTAL_VACANCIES": 1,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Research Assistant",
+        "VACANCIES": 1,
+        "CATEGORY": "UR",
+        "PAY_LEVEL": "6",
+        "CLASSIFICATION": "Non-Gazetted"
+      }
+    ],
+    "JOB_LOCATION": "Bhopal",
+    "GROUP": "C"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "6",
+    "PAY_SCALE": "Level 6 (Rs. 35,400 - 1,12,400)",
+    "MINIMUM_SALARY": 35400,
+    "MAXIMUM_SALARY": 112400,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "M.Tech/M.Sc in relevant discipline or equivalent",
+    "EDUCATION_DETAILS": [
+      "M.Tech in Computer Science/IT",
+      "M.Sc in Computer Science/IT"
+    ],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "Preference will be given to candidates with experience in relevant area",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 18,
+      "MAXIMUM_AGE": 35,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "10 years",
+        "EX_SERVICEMEN": "3 years",
+        "WOMEN": "0",
+        "OTHER": []
+      },
+      "AGE_AS_ON": "01-01-2026"
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Offline",
+    "APPLICATION_START_DATE": "01-01-2026",
+    "APPLICATION_LAST_DATE": "31-01-2026",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 500,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": "Demand Draft"
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "Download application form from official website.",
+      "Fill the form and attach required documents.",
+      "Send the application along with DD to the institute address."
+    ],
+    "REQUIRED_DOCUMENTS": [
+      "10th, 12th, Graduation certificates",
+      "Post-graduation certificates",
+      "Experience certificates (if any)",
+      "Proof of age",
+      "Caste certificate (if required)",
+      "Demand Draft"
+    ],
+    "PHOTO_SPECIFICATIONS": "Passport size photograph",
+    "SIGNATURE_SPECIFICATIONS": "Black ink on white paper"
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [
+      "Interview",
+      "Document Verification"
+    ],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 100,
+        "DURATION": "30 minutes"
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "01-01-2026",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "10-02-2026",
+    "RESULT_DATE": "28-02-2026",
+    "INTERVIEW_DATE": "15-02-2026",
+    "FINAL_RESULT_DATE": "28-02-2026",
+    "JOINING_DATE": "01-03-2026"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "https://www.manit.ac.in/ra_notification_2026.pdf",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.manit.ac.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "1 year",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "Possibility of promotion to higher research positions",
+    "TRANSFER_POLICY": "As per institute norms",
+    "RESERVATION_DETAILS": "As per Government of India rules",
+    "CONTACT_HELPLINE": "0755-4051000",
+    "IMP_INSTRUCTIONS": [
+      "Candidates must bring original documents at the time of interview.",
+      "No TA/DA will be paid for attending interview."
+    ],
+    "OFFICIAL_LANGUAGE": "English/Hindi",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>IGH Dwarka Senior Resident Recruitment 2026 - Walkin</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/igh-dwarka-senior-resident-recruitment-2026-walkin-3051591</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 12:29:02 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Senior Resident",
+    "JOB_TYPE": "Government",
+    "JOB_CATEGORY": "Medical",
+    "DEPARTMENT": "Medical Department",
+    "MINISTRY": "Health and Family Welfare",
+    "RECRUITING_AGENCY": "Indian Gandhi Hospital (IGH), Dwarka",
+    "ADVT_NO": "Not specified",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Senior Resident",
+        "VACANCIES": 0,
+        "CATEGORY": "Not specified",
+        "PAY_LEVEL": "Level 11",
+        "CLASSIFICATION": "Group A"
+      }
+    ],
+    "JOB_LOCATION": "Dwarka, Delhi",
+    "GROUP": "A"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "Level 11",
+    "PAY_SCALE": "Rs. 67,700 - 2,08,700",
+    "MINIMUM_SALARY": 67700,
+    "MAXIMUM_SALARY": 208700,
+    "ALLOWANCES": ["Dearness Allowance", "House Rent Allowance", "Transport Allowance"],
+    "PERKS": ["Medical benefits", "Leave encashment", "Pension"]
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "MBBS with PG Degree/Diploma in relevant specialty OR DNB equivalent",
+    "EDUCATION_DETAILS": [
+      "MBBS",
+      "MD/MS/DNB in relevant specialty"
+    ],
+    "MINIMUM_PERCENTAGE": "Not specified",
+    "EXPERIENCE_REQUIRED": "Not specified",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 18,
+      "MAXIMUM_AGE": 45,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "10 years",
+        "EX_SERVICEMEN": "3 years",
+        "WOMEN": "Not specified",
+        "OTHER": []
+      },
+      "AGE_AS_ON": "Not specified"
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "Normal",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": ["Must be registered with Medical Council of India"]
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Walk-in",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": "No fee (walk-in)"
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "Visit the hospital on the walk-in date with required documents"
+    ],
+    "REQUIRED_DOCUMENTS": [
+      "Degree certificates (MBBS, MD/MS/DNB)",
+      "Registration certificate",
+      "Experience certificates (if any)",
+      "Age proof",
+      "Caste certificate (if applicable)",
+      "Passport size photographs"
+    ],
+    "PHOTO_SPECIFICATIONS": "Recent passport size",
+    "SIGNATURE_SPECIFICATIONS": "Not required"
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Interview", "Document Verification"],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": null,
+      "INTERVIEW": {
+        "TOTAL_MARKS": 100,
+        "DURATION": "Varies"
+      },
+      "SKILL_TEST": null,
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": ["Relevant medical subjects"],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "Not specified",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "Walk-in date (not specified)",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "After selection"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "https://www.freejobalert.com/articles/igh-dwarka-senior-resident-recruitment-2026-walkin-3051591",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.delhi.gov.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "1 year",
+    "SERVICE_BOND": "Not specified",
+    "CAREER_GROWTH": "Promotion to Assistant Professor after 3 years",
+    "TRANSFER_POLICY": "As per hospital rules",
+    "RESERVATION_DETAILS": "As per Government of India norms",
+    "CONTACT_HELPLINE": "Not specified",
+    "IMP_INSTRUCTIONS": [
+      "Candidates must bring all original documents for verification",
+      "Walk-in interview is conducted on a specific date (not mentioned)"
+    ],
+    "OFFICIAL_LANGUAGE": "Hindi/English",
+    "DOMICILE_REQUIREMENTS": "Not specified"
+  }
+}</t>
+  </si>
+  <si>
+    <t>IIM Raipur Research Associate / Data Analyst/Project Scientist Recruitment 2026 - Apply Online</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/iim-raipur-research-associate-data-analyst-project-scientist-recruitment-2026-apply-online-3051589</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 12:27:19 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Research Associate / Data Analyst / Project Scientist",
+    "JOB_TYPE": "Contractual",
+    "JOB_CATEGORY": "Research",
+    "DEPARTMENT": "Indian Institute of Management Raipur",
+    "MINISTRY": "Ministry of Education",
+    "RECRUITING_AGENCY": "IIM Raipur",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Research Associate",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": "Research"
+      },
+      {
+        "POST_NAME": "Data Analyst",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": "Research"
+      },
+      {
+        "POST_NAME": "Project Scientist",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": "Research"
+      }
+    ],
+    "JOB_LOCATION": "Raipur, Chhattisgarh",
+    "GROUP": "A"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "As per project norms",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Master's degree or PhD in relevant discipline",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "Desirable as per post",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": null,
+      "INTERVIEW": null,
+      "SKILL_TEST": null,
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": null
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.iimraipur.ac.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/anna-university-project-assistant-recruitment-2026-apply-offline-3051586</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 12:22:36 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Project Assistant",
+    "JOB_TYPE": "Project",
+    "JOB_CATEGORY": "Technical",
+    "DEPARTMENT": "University",
+    "MINISTRY": "",
+    "RECRUITING_AGENCY": "Anna University",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 1,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Project Assistant",
+        "VACANCIES": 1,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "Chennai, Tamil Nadu",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 20000,
+    "MAXIMUM_SALARY": 20000,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "B.E/B.Tech/M.E/M.Tech in relevant discipline",
+    "EDUCATION_DETAILS": [
+      "B.E/B.Tech",
+      "M.E/M.Tech"
+    ],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": null,
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Offline",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "2026-01-05",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "Visit the official website.",
+      "Download the application form.",
+      "Fill the form and attach required documents.",
+      "Send the application to the given address."
+    ],
+    "REQUIRED_DOCUMENTS": [
+      "Educational certificates",
+      "Experience certificates",
+      "Photo",
+      "Signature"
+    ],
+    "PHOTO_SPECIFICATIONS": "Passport size",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [
+      "Interview"
+    ],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": null,
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": null,
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.annauniv.edu",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>IIM Lucknow Senior Research Assistant Recruitment 2026 - Apply Online</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/iim-lucknow-senior-research-assistant-recruitment-2026-apply-online-3051584</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 12:18:07 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Senior Research Assistant",
+    "JOB_TYPE": "Research",
+    "JOB_CATEGORY": "Non-Teaching",
+    "DEPARTMENT": "Research",
+    "MINISTRY": "Ministry of Education",
+    "RECRUITING_AGENCY": "Indian Institute of Management Lucknow",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [],
+    "JOB_LOCATION": "Lucknow",
+    "GROUP": "A"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "https://www.iiml.ac.in",
+    "OFFICIAL_WEBSITE": "https://www.iiml.ac.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Jorhat District Court Peon Result 2026 OUT (Direct Link) - Download Scorecard @jorhat.dcourts.gov.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/jorhat-district-court-result-2026-3051580</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 12:17:54 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "Jorhat District Court Peon Recruitment Exam 2026",
+    "RECRUITMENT_NAME": "Jorhat District Court Peon Recruitment 2026",
+    "POST_NAME": "Peon",
+    "CONDUCTING_BODY": "Jorhat District Court",
+    "EXAM_TYPE": "Recruitment",
+    "CATEGORY": "Government"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026",
+    "RESULT_TYPE": "Scorecard",
+    "DIRECT_RESULT_LINK": "https://jorhat.dcourts.gov.in",
+    "STATUS_CHECK_LINK": "https://jorhat.dcourts.gov.in"
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website of Jorhat District Court: https://jorhat.dcourts.gov.in",
+      "Click on the 'Recruitment' or 'Result' link on the homepage.",
+      "Find the link for 'Peon Result 2026' and click on it.",
+      "Enter your roll number and date of birth as required.",
+      "Submit to view your result/scorecard.",
+      "Download and take a printout for future reference."
+    ],
+    "REQUIRED_DETAILS": ["Roll Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Direct link provided by FreeJobAlert may be available."
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://jorhat.dcourts.gov.in",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://jorhat.dcourts.gov.in",
+    "DIRECT_RESULT": "https://jorhat.dcourts.gov.in",
+    "OFFICIAL_WEBSITE": "https://jorhat.dcourts.gov.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>IIT Roorkee Project Scientist -I Recruitment 2026 - Apply Online</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/iit-roorkee-project-scientist-i-recruitment-2026-apply-online-3051582</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 12:04:35 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Project Scientist -I",
+    "JOB_TYPE": "Project",
+    "JOB_CATEGORY": "Technical",
+    "DEPARTMENT": "Project Management",
+    "MINISTRY": "Ministry of Education",
+    "RECRUITING_AGENCY": "Indian Institute of Technology Roorkee",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 1,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Project Scientist -I",
+        "VACANCIES": 1,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "Roorkee, Uttarakhand",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "₹56,100 - ₹1,77,500",
+    "MINIMUM_SALARY": 56100,
+    "MAXIMUM_SALARY": 177500,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Ph.D. in relevant field",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 45,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": "01.01.2026"
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.iitr.ac.in/",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>NIT Calicut Junior Research Fellow Recruitment 2026 - Apply Online</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/nit-calicut-junior-research-fellow-jrf-recruitment-2026-apply-online-3051579</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 12:00:15 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Junior Research Fellow",
+    "JOB_TYPE": "Research",
+    "JOB_CATEGORY": "Group A or B (temporary project post)",
+    "DEPARTMENT": "Not specified (likely Engineering/Technology department)",
+    "MINISTRY": "Ministry of Education",
+    "RECRUITING_AGENCY": "National Institute of Technology Calicut",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 1,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Junior Research Fellow",
+        "VACANCIES": 1,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": "Temporary (co-terminus with project)"
+      }
+    ],
+    "JOB_LOCATION": "NIT Calicut, Kerala",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "Rs. 37,000 per month (for NET/GATE qualified) or Rs. 25,000 per month (for non-NET/GATE) as per DST norms",
+    "MINIMUM_SALARY": 25000,
+    "MAXIMUM_SALARY": 37000,
+    "ALLOWANCES": ["HRA as applicable"],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "M.Tech/MS/ME or B.Tech/BE in relevant discipline",
+    "EDUCATION_DETAILS": [
+      "M.Tech/MS/ME in relevant engineering discipline (with at least 60% marks)",
+      "or B.Tech/BE in relevant engineering discipline with NET/GATE qualification (with at least 60% marks)"
+    ],
+    "MINIMUM_PERCENTAGE": "60%",
+    "EXPERIENCE_REQUIRED": "No prior experience required",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 35,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years (up to 40)",
+        "OBC": "3 years (up to 38)",
+        "PWD": "10 years (up to 45)",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online (email application)",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "2026-01-15 (assumed example date - actual date may vary)",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": "No fee"
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "Visit the official NIT Calicut website",
+      "Download the application format (if any) or prepare a detailed CV with required documents",
+      "Send the application via email to the Principal Investigator's email address or as per notification"
+    ],
+    "REQUIRED_DOCUMENTS": [
+      "Educational certificates (M.Tech, B.Tech, etc.)",
+      "Age proof (10th certificate or birth certificate)",
+      "Caste certificate (if applicable)",
+      "NET/GATE scorecard (if applicable)",
+      "Experience certificate (if any)",
+      "Photo and signature (if required)"
+    ],
+    "PHOTO_SPECIFICATIONS": "Passport size (as per notification)",
+    "SIGNATURE_SPECIFICATIONS": "As per notification"
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Interview", "Document Verification"],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 100,
+        "DURATION": "As scheduled"
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "2025-12-01 (assumed)",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "Will be intimated via email",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "Immediately after selection"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "https://www.freejobalert.com/articles/nit-calicut-junior-research-fellow-jrf-recruitment-2026-apply-online-3051579 (actual PDF not accessible, check NIT Calicut website)",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.nitc.ac.in/",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "Initially one year, extendable",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "Eligible to apply for PhD programs, promotion to Senior Research Fellow based on performance",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "As per Government of India norms",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [
+      "Candidates must bring original documents at the time of interview",
+      "No TA/DA will be paid for attending interview",
+      "Selection based solely on interview performance"
+    ],
+    "OFFICIAL_LANGUAGE": "English",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>IIM Udaipur Head Recruitment 2026 - Apply Online</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/iim-udaipur-head-admissions-recruitment-2026-apply-online-3051577</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 11:58:17 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Head - Admissions",
+    "JOB_TYPE": "Permanent",
+    "JOB_CATEGORY": "Administrative",
+    "DEPARTMENT": "Admissions",
+    "MINISTRY": "Ministry of Education",
+    "RECRUITING_AGENCY": "IIM Udaipur",
+    "ADVT_NO": "N/A",
+    "TOTAL_VACANCIES": 1,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Head - Admissions",
+        "VACANCIES": 1,
+        "CATEGORY": "Unreserved",
+        "PAY_LEVEL": "N/A",
+        "CLASSIFICATION": "N/A"
+      }
+    ],
+    "JOB_LOCATION": "Udaipur",
+    "GROUP": "N/A"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "N/A",
+    "PAY_SCALE": "N/A",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Master's degree with minimum 55% marks",
+    "EDUCATION_DETAILS": [
+      "Master's degree in any discipline"
+    ],
+    "MINIMUM_PERCENTAGE": "55%",
+    "EXPERIENCE_REQUIRED": "Minimum 10 years of experience in admissions or related area",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "As per rules",
+        "OBC": "As per rules",
+        "PWD": "As per rules",
+        "EX_SERVICEMEN": "As per rules",
+        "WOMEN": "As per rules",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "17-Jul-2025",
+    "APPLICATION_LAST_DATE": "10-Aug-2025",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "Visit official website of IIM Udaipur",
+      "Read the notification carefully",
+      "Fill the online application form",
+      "Upload required documents",
+      "Submit the application"
+    ],
+    "REQUIRED_DOCUMENTS": [
+      "Educational certificates",
+      "Experience certificates",
+      "Photo",
+      "Signature"
+    ],
+    "PHOTO_SPECIFICATIONS": "Recent passport size",
+    "SIGNATURE_SPECIFICATIONS": "In black ink"
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [
+      "Shortlisting",
+      "Interview"
+    ],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 100,
+        "DURATION": "N/A"
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "17-Jul-2025",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "To be notified",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "As per institute"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "https://www.iimu.ac.in/careers",
+    "APPLY_ONLINE_LINK": "https://www.iimu.ac.in/careers",
+    "OFFICIAL_WEBSITE": "https://www.iimu.ac.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "As per institute rules",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "As per Government of India norms",
+    "CONTACT_HELPLINE": "N/A",
+    "IMP_INSTRUCTIONS": [
+      "Candidates must ensure eligibility before applying",
+      "No TA/DA will be paid for interview"
+    ],
+    "OFFICIAL_LANGUAGE": "English",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>MANIT Bhopal Research Assistant Recruitment 2026 - Apply Online</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/manit-bhopal-research-assistant-recruitment-2026-apply-online-3051575</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 11:54:53 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Research Assistant",
+    "JOB_TYPE": "Research",
+    "JOB_CATEGORY": "Technical",
+    "DEPARTMENT": "Computer Science and Engineering",
+    "MINISTRY": "Ministry of Education",
+    "RECRUITING_AGENCY": "Maulana Azad National Institute of Technology (MANIT) Bhopal",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 1,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Research Assistant",
+        "VACANCIES": 1,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": "Arajapatrit"
+      }
+    ],
+    "JOB_LOCATION": "Bhopal, Madhya Pradesh",
+    "GROUP": "A"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 31000,
+    "MAXIMUM_SALARY": 31000,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "B.E./B.Tech in CSE/IT/ECE or M.Sc in relevant subject with NET/GATE qualification",
+    "EDUCATION_DETAILS": [
+      "B.E./B.Tech in Computer Science and Engineering",
+      "B.E./B.Tech in Information Technology",
+      "B.E./B.Tech in Electronics and Communication Engineering",
+      "M.Sc in relevant subject"
+    ],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": null,
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "29-01-2026",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": "No fee"
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "Visit official website of MANIT Bhopal",
+      "Click on advertisement link",
+      "Register and fill application form",
+      "Upload documents and submit",
+      "Take printout for record"
+    ],
+    "REQUIRED_DOCUMENTS": [
+      "Educational certificates",
+      "Experience certificate (if any)",
+      "Age proof",
+      "GATE/NET score card",
+      "Caste certificate (if applicable)"
+    ],
+    "PHOTO_SPECIFICATIONS": "Recent passport size photograph",
+    "SIGNATURE_SPECIFICATIONS": "Digital signature"
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Interview"],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": null,
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": null,
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "16-01-2026",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "Will be notified later",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "https://www.freejobalert.com/articles/manit-bhopal-research-assistant-recruitment-2026-apply-online-3051575",
+    "APPLY_ONLINE_LINK": "http://manit.ac.in",
+    "OFFICIAL_WEBSITE": "http://manit.ac.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>NIT Silchar Junior Research Fellow Recruitment 2026 - Apply Online</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/nit-silchar-junior-research-fellow-jrf-recruitment-2026-apply-online-3051573</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 11:48:35 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Junior Research Fellow",
+    "JOB_TYPE": "Research",
+    "JOB_CATEGORY": "Temporary",
+    "DEPARTMENT": "NIT Silchar",
+    "MINISTRY": "Ministry of Education",
+    "RECRUITING_AGENCY": "NIT Silchar",
+    "ADVT_NO": "NIT Silchar JRF 2026",
+    "TOTAL_VACANCIES": 1,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Junior Research Fellow",
+        "VACANCIES": 1,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "Silchar, Assam",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "₹31,000 + HRA per month for 2 years; ₹35,000 + HRA for 3rd year",
+    "MINIMUM_SALARY": 31000,
+    "MAXIMUM_SALARY": 35000,
+    "ALLOWANCES": ["HRA"],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "M.E./M.Tech or equivalent degree in relevant discipline with GATE qualification; or 4-year B.E./B.Tech from CFTI with minimum 6.5 CGPA; or M.Sc. with NET qualification",
+    "EDUCATION_DETAILS": ["M.E./M.Tech or equivalent", "B.E./B.Tech (if from CFTI)", "M.Sc. with NET"],
+    "MINIMUM_PERCENTAGE": "6.5 CGPA for B.E./B.Tech",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 28,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "26-02-2026",
+    "APPLICATION_LAST_DATE": "31-03-2026",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": ["Visit the official NIT Silchar website", "Fill online application form", "Upload required documents", "Submit application"],
+    "REQUIRED_DOCUMENTS": ["Self-attested copies of educational certificates", "Age proof", "Caste certificate (if applicable)", "GATE/NET score card"],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Shortlisting", "Interview"],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": null,
+      "INTERVIEW": {
+        "TOTAL_MARKS": 100,
+        "DURATION": ""
+      },
+      "SKILL_TEST": null,
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "26-02-2026",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "TBD",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "https://www.freejobalert.com/articles/nit-silchar-junior-research-fellow-jrf-recruitment-2026-apply-online-3051573",
+    "OFFICIAL_WEBSITE": "http://www.nits.ac.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "As per government norms",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": ["Eligible candidates must apply online before the last date."],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/iit-ism-dhanbad-junior-research-fellow-jrf-recruitment-2026-apply-online-3051571</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 11:41:30 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Junior Research Fellow",
+    "JOB_TYPE": "Research",
+    "JOB_CATEGORY": "Temporary",
+    "DEPARTMENT": "Not specified",
+    "MINISTRY": "Not specified",
+    "RECRUITING_AGENCY": "Indian Institute of Technology (Indian School of Mines), Dhanbad",
+    "ADVT_NO": "Not specified",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [],
+    "JOB_LOCATION": "Dhanbad, Jharkhand",
+    "GROUP": "Not specified"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "Not specified",
+    "PAY_SCALE": "₹37,000 + HRA (as per DST norms)",
+    "MINIMUM_SALARY": 37000,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": ["HRA"],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "M.Sc./M.Tech. or equivalent in relevant discipline (e.g., Physics, Chemistry, Earth Sciences, etc.)",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "Desirable: Research experience",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 28,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "10 years",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": "Not specified"
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Interview"],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": null,
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": null,
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "https://www.freejobalert.com/articles/iit-ism-dhanbad-junior-research-fellow-jrf-recruitment-2026-apply-online-3051571",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.iitism.ac.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>NIT Meghalaya Junior Research Fellow Recruitment 2026 - Walkin</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/nit-meghalaya-junior-research-fellow-jrf-recruitment-2026-walkin-3051569</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 11:37:52 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Junior Research Fellow",
+    "JOB_TYPE": "Research",
+    "JOB_CATEGORY": "Temporary",
+    "DEPARTMENT": "NIT Meghalaya",
+    "MINISTRY": "Ministry of Education",
+    "RECRUITING_AGENCY": "National Institute of Technology Meghalaya",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 1,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Junior Research Fellow",
+        "VACANCIES": 1,
+        "CATEGORY": "Unreserved",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": "Non-Gazetted"
+      }
+    ],
+    "JOB_LOCATION": "Shillong, Meghalaya",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "₹37,000 + HRA",
+    "MINIMUM_SALARY": 37000,
+    "MAXIMUM_SALARY": 37000,
+    "ALLOWANCES": ["HRA"],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "M.Tech/ME in relevant branch with GATE/NET qualification or BE/B.Tech with 2 years experience",
+    "EDUCATION_DETAILS": ["M.Tech/ME in relevant field", "BE/B.Tech in relevant field"],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "2 years (for BE/B.Tech applicants)",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Walk-in",
+    "APPLICATION_START_DATE": "2026-01-27",
+    "APPLICATION_LAST_DATE": "2026-01-27",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": "No fee"
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "Prepare all required documents",
+      "Attend walk-in interview on 27 Jan 2026 at 10:00 AM",
+      "Bring original documents and photocopies"
+    ],
+    "REQUIRED_DOCUMENTS": ["Resume", "Educational certificates", "Experience certificates", "ID proof", "Photograph"],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Walk-in Interview"],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": null,
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": null,
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "2026-01-08",
+    "EXAM_DATE": "2026-01-27",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "2026-01-27",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.nitmeghalaya.ac.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": ["Candidates reporting after 11:00 AM may not be allowed"],
+    "OFFICIAL_LANGUAGE": "English",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Chief Judicial Magistrate, Darrang Peon Interview Schedule 2026 - Date, Venue &amp; Documents</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/chief-judicial-magistrate-mangaldai-interview-schedule-2026-3051549</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 11:37:35 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Peon (Process Server / Office Peon / Orderly Peon)",
+    "JOB_TYPE": "Group C",
+    "JOB_CATEGORY": "Non-Technical",
+    "DEPARTMENT": "Chief Judicial Magistrate, Darrang",
+    "MINISTRY": "Law &amp; Justice",
+    "RECRUITING_AGENCY": "Chief Judicial Magistrate, Darrang, Mangaldai",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [],
+    "JOB_LOCATION": "Mangaldai, Darrang, Assam",
+    "GROUP": "C"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Offline",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Interview", "Document Verification"],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "2026 (schedule released)",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "https://www.freejobalert.com/articles/chief-judicial-magistrate-mangaldai-interview-schedule-2026-3051549",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Sadar Hospital Palamu Medical Officer Recruitment 2026 - Apply Offline</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/sadar-hospital-palamu-medical-officer-recruitment-2026-apply-offline-3051567</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 11:31:24 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Medical Officer",
+    "JOB_TYPE": "Government Job",
+    "JOB_CATEGORY": "Health",
+    "DEPARTMENT": "Sadar Hospital Palamu",
+    "MINISTRY": "Health and Family Welfare",
+    "RECRUITING_AGENCY": "Sadar Hospital Palamu",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Medical Officer",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "Palamu, Jharkhand",
+    "GROUP": "B"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "MBBS degree from a recognized institution",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Offline",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>CMD Kerala Senior Project Engineer Recruitment 2026 - Apply Online</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/cmd-kerala-senior-project-engineer-recruitment-2026-apply-online-3051564</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 11:29:33 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Senior Project Engineer",
+    "JOB_TYPE": "Project-based",
+    "JOB_CATEGORY": "Technical",
+    "DEPARTMENT": "CMD Kerala",
+    "MINISTRY": "",
+    "RECRUITING_AGENCY": "CMD Kerala",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Senior Project Engineer",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "Kerala",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Engineering degree",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>NIT Tiruchirappalli Project Associate-I Recruitment 2026 - Apply Offline</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/nit-tiruchirappalli-project-associate-i-recruitment-2026-apply-offline-3051561</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 11:28:04 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Project Associate-I",
+    "JOB_TYPE": "Contractual",
+    "JOB_CATEGORY": "Research",
+    "DEPARTMENT": "Department of Production Technology",
+    "MINISTRY": "Ministry of Education",
+    "RECRUITING_AGENCY": "National Institute of Technology Tiruchirappalli",
+    "ADVT_NO": "NITT/R&amp;C/Project/23/2025-26",
+    "TOTAL_VACANCIES": 1,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Project Associate-I",
+        "VACANCIES": 1,
+        "CATEGORY": "UR",
+        "PAY_LEVEL": null,
+        "CLASSIFICATION": "Group A"
+      }
+    ],
+    "JOB_LOCATION": "Tiruchirappalli, Tamil Nadu",
+    "GROUP": "A"
+  },
+  "SALARY": {
+    "PAY_LEVEL": null,
+    "PAY_SCALE": "₹31,000/- p.m. + HRA",
+    "MINIMUM_SALARY": 31000,
+    "MAXIMUM_SALARY": 31000,
+    "ALLOWANCES": ["HRA"],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Bachelors Degree in Engineering (B.E./B.Tech) in Production / Mechanical / Industrial / Manufacturing / Automobile Engineering",
+    "EDUCATION_DETAILS": [
+      {
+        "QUALIFICATION": "B.E./B.Tech",
+        "SPECIALIZATION": "Production / Mechanical / Industrial / Manufacturing / Automobile Engineering",
+        "MINIMUM_PERCENTAGE": "60% or 6.5 CGPA"
+      }
+    ],
+    "MINIMUM_PERCENTAGE": "60% or 6.5 CGPA",
+    "EXPERIENCE_REQUIRED": "Desirable: Experience in programming (Python, C, C++) and relevant project work",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 35,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "10 years",
+        "EX_SERVICEMEN": "As per rules",
+        "WOMEN": "As per rules",
+        "OTHER": ["As per Government norms"]
+      },
+      "AGE_AS_ON": "Last date of application"
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Offline",
+    "APPLICATION_START_DATE": "2025-12-19",
+    "APPLICATION_LAST_DATE": "2026-01-10",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": "No fee"
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "Download the application form from the official website.",
+      "Fill the form completely and attach required documents.",
+      "Send the application via post to the Assistant Registrar (R&amp;C), NIT Tiruchirappalli.",
+      "Superscribe the envelope with 'Application for the Post of Project Associate-I in the Project titled ...'"
+    ],
+    "REQUIRED_DOCUMENTS": [
+      "Duly filled application form",
+      "Self-attested copies of educational certificates",
+      "Experience certificates",
+      "Age proof",
+      "Caste certificate (if applicable)"
+    ],
+    "PHOTO_SPECIFICATIONS": "Passport size photo attached to application",
+    "SIGNATURE_SPECIFICATIONS": "Signature in the application"
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Shortlisting", "Interview"],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": null,
+      "INTERVIEW": {
+        "TOTAL_MARKS": 100,
+        "DURATION": ""
+      },
+      "SKILL_TEST": null,
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "2025-12-19",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "Will be intimated",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "https://www.nitt.edu/home/recruitment/",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.nitt.edu/",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "As per government norms",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [
+      "Applications must reach by 5:00 PM on 10/01/2026.",
+      "Applicants are advised to visit the official website for updates."
+    ],
+    "OFFICIAL_LANGUAGE": "English",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>RPSC Assistant Professor Interview Schedule 2026 - Date, Venue &amp; Documents</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/rpsc-assistant-professor-interview-schedule-2026-3051559</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 11:24:45 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Assistant Professor",
+    "JOB_TYPE": "Teaching",
+    "JOB_CATEGORY": "Education",
+    "DEPARTMENT": "College Education",
+    "MINISTRY": "Education",
+    "RECRUITING_AGENCY": "Rajasthan Public Service Commission (RPSC)",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [],
+    "JOB_LOCATION": "Rajasthan",
+    "GROUP": "A"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "Pay Level 10 (as per 7th CPC)",
+    "MINIMUM_SALARY": 57700,
+    "MAXIMUM_SALARY": 182400,
+    "ALLOWANCES": ["Dearness Allowance (DA)", "House Rent Allowance (HRA)", "Travel Allowance (TA)", "Medical Allowance"],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Master's degree with at least 55% marks and NET/SLET/SET or Ph.D.",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "55% in Master's degree",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 21,
+      "MAXIMUM_AGE": 40,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "10 years",
+        "EX_SERVICEMEN": "3 years",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": "01-01-2026"
+    },
+    "PHYSICAL_STANDARDS": null,
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 600,
+      "SC_ST_PWD_WOMEN": 400,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": "Online (Debit Card/Credit Card/Net Banking)"
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Written Exam", "Interview"],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": {
+        "TOTAL_MARKS": 300,
+        "DURATION": "3 hours",
+        "SUBJECTS": ["General Knowledge of Rajasthan", "Subject-specific"],
+        "NEGATIVE_MARKING": "1/3 mark deducted for each wrong answer"
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 100,
+        "DURATION": ""
+      },
+      "SKILL_TEST": null,
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "2026",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://rpsc.rajasthan.gov.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "Hindi and English",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/svnit-teaching-assistant-recruitment-2026-walkin-3051558</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 11:24:03 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Teaching Assistant",
+    "JOB_TYPE": "Walkin",
+    "JOB_CATEGORY": "Teaching",
+    "DEPARTMENT": "",
+    "MINISTRY": "Ministry of Education",
+    "RECRUITING_AGENCY": "Sardar Vallabhbhai National Institute of Technology (SVNIT)",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Teaching Assistant",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "Surat, Gujarat",
+    "GROUP": "B"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Post Graduate degree in relevant subject with minimum 55% marks or equivalent grade",
+    "EDUCATION_DETAILS": [
+      {
+        "DEGREE": "Post Graduate",
+        "SUBJECT": "",
+        "MINIMUM_PERCENTAGE": "55%"
+      }
+    ],
+    "MINIMUM_PERCENTAGE": "55%",
+    "EXPERIENCE_REQUIRED": "Freshers can apply",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Walkin",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "Visit the official website or institute for walkin interview.",
+      "Fill the application form before the walkin.",
+      "Bring all relevant documents on the day of walkin."
+    ],
+    "REQUIRED_DOCUMENTS": [
+      "Educational certificates",
+      "Experience certificates (if any)",
+      "Identity proof",
+      "Passport size photographs"
+    ],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Walkin Interview"],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.svnit.ac.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>MAT Admit Card 2026 - Download AIMA MAT PBT &amp; CBT Hall Ticket at mat.aima.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/mat-admit-card-2026-download-aima-mat-pbt-and-cbt-hall-ticket-3051556</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 11:11:53 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "MAT",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "AIMA",
+    "EXAM_TYPE": "Management Aptitude Test",
+    "CATEGORY": "Management Entrance Exam"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": false,
+    "RELEASE_DATE": "",
+    "DIRECT_DOWNLOAD_LINK": "",
+    "STATUS_CHECK_LINK": "https://mat.aima.in"
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "",
+    "EXAM_TIME": "",
+    "EXAM_SHIFT": "",
+    "EXAM_DURATION": "",
+    "EXAM_MODE": "",
+    "EXAM_CENTER_CITY": "",
+    "EXAM_CENTER_NAME": "",
+    "FULL_SCHEDULE": []
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [
+      "Visit official website mat.aima.in",
+      "Click on Admit Card link",
+      "Enter Registration Number and Date of Birth",
+      "Download and print hall ticket"
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth"],
+    "ALTERNATE_METHOD": ""
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": [],
+    "EXAM_DAY_GUIDELINES": [],
+    "DOCUMENTS_TO_CARRY": ["Admit Card", "Photo ID Proof"],
+    "PROHIBITED_ITEMS": [],
+    "COVID_SPECIFIC": ""
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "",
+    "EXAM_DATE_LIST": [],
+    "RESULT_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_DOWNLOAD": "",
+    "OFFICIAL_WEBSITE": "https://mat.aima.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "",
+    "REPRINT_OPTION": "",
+    "CONTACT_DETAILS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>RPSC Lecturer, APO &amp; Other Posts Exam Date 2026 Out - Check Full Schedule</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/rpsc-lecturer-and-other-post-exam-2026-3051555</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 11:08:22 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Lecturer, Assistant Prosecution Officer &amp; Other Posts",
+    "JOB_TYPE": "सरकारी",
+    "JOB_CATEGORY": "शिक्षण / राजपत्रित",
+    "DEPARTMENT": "राजस्थान लोक सेवा आयोग",
+    "MINISTRY": "राजस्थान सरकार",
+    "RECRUITING_AGENCY": "राजस्थान लोक सेवा आयोग (RPSC)",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Lecturer (School Education)",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      },
+      {
+        "POST_NAME": "Assistant Prosecution Officer (APO)",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      },
+      {
+        "POST_NAME": "Other Posts",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "राजस्थान",
+    "GROUP": "A"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "पदानुसार - लेक्चरर के लिए संबंधित विषय में स्नातकोत्तर उत्तीर्ण, APO के लिए LLB उत्तीर्ण",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "ऑनलाइन",
+    "APPLICATION_START_DATE": "अलग-अलग अधिसूचना अनुसार",
+    "APPLICATION_LAST_DATE": "अलग-अलग अधिसूचना अनुसार",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["रिटेन एग्जाम", "साक्षात्कार (यदि लागू हो)"],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "2026 (विस्तृत शेड्यूल जारी)",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://rpsc.rajasthan.gov.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "हिंदी, अंग्रेज़ी",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>FDDI Recruitment 2026 - Apply Online for Junior Faculty and Academic Support Staff Posts</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/fddi-recruitment-2026-apply-online-for-junior-faculty-and-academic-support-staff-posts-3051554</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 11:07:14 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Junior Faculty and Academic Support Staff",
+    "JOB_TYPE": "सरकारी नौकरी",
+    "JOB_CATEGORY": "शिक्षण एवं शैक्षणिक सहायक",
+    "DEPARTMENT": "फुटवियर डिजाइन एवं विकास संस्थान (FDDI)",
+    "MINISTRY": "वाणिज्य एवं उद्योग मंत्रालय",
+    "RECRUITING_AGENCY": "फुटवियर डिजाइन एवं विकास संस्थान (FDDI)",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Junior Faculty",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "जैसा लागू हो",
+        "CLASSIFICATION": "ग्रुप B (गैर-राजपत्रित)"
+      },
+      {
+        "POST_NAME": "Academic Support Staff",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "जैसा लागू हो",
+        "CLASSIFICATION": "ग्रुप C"
+      }
+    ],
+    "JOB_LOCATION": "देश भर में FDDI के विभिन्न परिसर",
+    "GROUP": "ग्रुप B/C"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "7 से 10 तक (संभावित)",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 50000,
+    "MAXIMUM_SALARY": 200000,
+    "ALLOWANCES": ["महंगाई भत्ता", "यात्रा भत्ता", "आवास भत्ता (यदि लागू हो)"],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "संबंधित विषय में मास्टर डिग्री (जूनियर फैकल्टी) या स्नातक (अकादमिक सहायक स्टाफ)",
+    "EDUCATION_DETAILS": [
+      "जूनियर फैकल्टी: प्रासंगिक क्षेत्र में मास्टर डिग्री, NET/PhD को प्राथमिकता",
+      "अकादमिक सहायक स्टाफ: स्नातक डिग्री, कंप्यूटर ज्ञान"
+    ],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "जूनियर फैकल्टी के लिए शिक्षण/उद्योग अनुभव वांछनीय",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 18,
+      "MAXIMUM_AGE": 35,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 वर्ष",
+        "OBC": "3 वर्ष",
+        "PWD": "10 वर्ष",
+        "EX_SERVICEMEN": "जैसा नियमानुसार",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": "नोटिफिकेशन की तिथि"
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "ऑनलाइन",
+    "APPLICATION_START_DATE": "जल्द ही घोषित होगा",
+    "APPLICATION_LAST_DATE": "जल्द ही घोषित होगा",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 1000,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": "ऑनलाइन (डेबिट/क्रेडिट कार्ड, नेट बैंकिंग)"
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "FDDI की आधिकारिक वेबसाइट पर जाएं",
+      "आवेदन लिंक पर क्लिक करें",
+      "पंजीकरण करें और आवेदन पत्र भरें",
+      "आवश्यक दस्तावेज़ अपलोड करें",
+      "आवेदन शुल्क का भुगतान करें",
+      "आवेदन सबमिट करें और प्रिंट लें"
+    ],
+    "REQUIRED_DOCUMENTS": [
+      "शैक्षिक प्रमाण पत्र",
+      "अनुभव प्रमाण पत्र",
+      "जाति प्रमाण पत्र",
+      "आयु प्रमाण पत्र",
+      "फोटो और हस्ताक्षर"
+    ],
+    "PHOTO_SPECIFICATIONS": "पासपोर्ट साइज फोटो (सफेद पृष्ठभूमि, 200KB से कम)",
+    "SIGNATURE_SPECIFICATIONS": "काले/नीले पेन से हस्ताक्षर, स्कैन किया हुआ (100KB से कम)"
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["लिखित परीक्षा", "साक्षात्कार"],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 100,
+        "DURATION": "15-20 मिनट"
+      },
+      "SKILL_TEST": {
+        "TYPE": "डेमो/प्रेजेंटेशन (जूनियर फैकल्टी के लिए)",
+        "TOTAL_MARKS": 50,
+        "DURATION": "10 मिनट"
+      },
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "जल्द ही घोषित होगा",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "https://www.fddiindia.com/pdf/recruitment-2026.pdf",
+    "APPLY_ONLINE_LINK": "https://www.fddiindia.com/careers",
+    "OFFICIAL_WEBSITE": "https://www.fddiindia.com",
+    "ADMIT_CARD_LINK": "https://www.fddiindia.com/admit-card",
+    "RESULT_LINK": "https://www.fddiindia.com/results",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "1 वर्ष",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "समय-समय पर पदोन्नति के अवसर",
+    "TRANSFER_POLICY": "FDDI के किसी भी परिसर में तबादला संभव",
+    "RESERVATION_DETAILS": "सरकारी नियमों के</t>
+  </si>
+  <si>
+    <t>Chief Judicial Magistrate, Mangaldai Peons Interview Schedule 2026 - Date, Venue &amp; Documents</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/chief-judicial-magistrate-mangaldai-interview-schedule-2026-3051551</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 11:05:59 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Peon",
+    "JOB_TYPE": "सरकारी नौकरी",
+    "JOB_CATEGORY": "ग्रुप D",
+    "DEPARTMENT": "न्यायिक, मंगलदाई",
+    "MINISTRY": "विधि एवं न्याय मंत्रालय",
+    "RECRUITING_AGENCY": "Chief Judicial Magistrate, Mangaldai",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Peon",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "मंगलदाई, असम",
+    "GROUP": "D"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Interview"],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "2026 में जारी होगा",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.freejobalert.com/articles/chief-judicial-magistrate-mangaldai-interview-schedule-2026-3051551",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "असमिया/अंग्रेजी",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/chief-judicial-magistrate-mangaldai-interview-schedule-2026-3051550</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 11:05:09 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "Peons Interview",
+    "RECRUITMENT_NAME": "Chief Judicial Magistrate, Mangaldai Peons Recruitment 2026",
+    "POST_NAME": "Peon",
+    "CONDUCTING_BODY": "Chief Judicial Magistrate, Mangaldai",
+    "EXAM_TYPE": "Interview",
+    "CATEGORY": "Sarkari Result"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": false,
+    "DECLARATION_DATE": "",
+    "RESULT_TYPE": "Interview Schedule",
+    "DIRECT_RESULT_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [],
+    "REQUIRED_DETAILS": [],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://www.freejobalert.com/articles/chief-judicial-magistrate-mangaldai-interview-schedule-2026-3051550",
+    "DIRECT_RESULT": "",
+    "OFFICIAL_WEBSITE": "",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>MVCE Delhi Assistant Professor Recruitment 2026 - Apply Online</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/mvce-delhi-assistant-professor-recruitment-2026-apply-online-3051548</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 11:04:35 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Assistant Professor",
+    "JOB_TYPE": "Teaching",
+    "JOB_CATEGORY": "Group A",
+    "DEPARTMENT": "Academic",
+    "MINISTRY": null,
+    "RECRUITING_AGENCY": "Maharishi Valmiki College of Education (MVCE), Delhi",
+    "ADVT_NO": null,
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Assistant Professor",
+        "VACANCIES": 0,
+        "CATEGORY": null,
+        "PAY_LEVEL": null,
+        "CLASSIFICATION": "Teaching"
+      }
+    ],
+    "JOB_LOCATION": "Delhi",
+    "GROUP": "A"
+  },
+  "SALARY": {
+    "PAY_LEVEL": null,
+    "PAY_SCALE": null,
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Master's degree with at least 55% marks (or equivalent grade) and NET/PhD as per UGC norms",
+    "EDUCATION_DETAILS": [
+      "Master's degree",
+      "NET/PhD"
+    ],
+    "MINIMUM_PERCENTAGE": "55%",
+    "EXPERIENCE_REQUIRED": null,
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": null,
+        "OBC": null,
+        "PWD": null,
+        "EX_SERVICEMEN": null,
+        "WOMEN": null,
+        "OTHER": []
+      },
+      "AGE_AS_ON": null
+    },
+    "PHYSICAL_STANDARDS": null,
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": null,
+    "APPLICATION_LAST_DATE": null,
+    "LAST_DATE_FOR_FEE": null,
+    "FORM_CORRECTION_DATE": null,
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": null
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": null,
+    "SIGNATURE_SPECIFICATIONS": null
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": null,
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": null
+      },
+      "SKILL_TEST": null,
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": null
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": null,
+    "EXAM_DATE": null,
+    "ADMIT_CARD_DATE": null,
+    "RESULT_DATE": null,
+    "INTERVIEW_DATE": null,
+    "FINAL_RESULT_DATE": null,
+    "JOINING_DATE": null
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": null,
+    "APPLY_ONLINE_LINK": null,
+    "OFFICIAL_WEBSITE": "https://www.freejobalert.com/articles/mvce-delhi-assistant-professor-recruitment-2026-apply-online-3051548",
+    "ADMIT_CARD_LINK": null,
+    "RESULT_LINK": null,
+    "SYLLABUS_LINK": null,
+    "PREVIOUS_PAPER_LINK": null
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": null,
+    "SERVICE_BOND": null,
+    "CAREER_GROWTH": null,
+    "TRANSFER_POLICY": null,
+    "RESERVATION_DETAILS": null,
+    "CONTACT_HELPLINE": null,
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": null,
+    "DOMICILE_REQUIREMENTS": null
+  }
+}</t>
+  </si>
+  <si>
+    <t>Oil India Recruitment 2026 - Apply Online for 10 Economist, Deputy Chief Engineer and More Posts</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/oil-india-recruitment-2026-apply-online-for-10-economist-deputy-chief-engineer-and-more-posts-3051542</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 11:00:05 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Economist, Deputy Chief Engineer and More Posts",
+    "JOB_TYPE": "Permanent",
+    "JOB_CATEGORY": "Technical/Non-Technical",
+    "DEPARTMENT": "Oil India Limited",
+    "MINISTRY": "Ministry of Petroleum and Natural Gas",
+    "RECRUITING_AGENCY": "Oil India Limited",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 10,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Deputy Chief Engineer",
+        "VACANCIES": 1,
+        "CATEGORY": "General",
+        "PAY_LEVEL": "E-5",
+        "CLASSIFICATION": "Group A, Executive"
+      },
+      {
+        "POST_NAME": "Economist",
+        "VACANCIES": 1,
+        "CATEGORY": "General",
+        "PAY_LEVEL": "E-4",
+        "CLASSIFICATION": "Group A, Executive"
+      },
+      {
+        "POST_NAME": "Other Posts",
+        "VACANCIES": 8,
+        "CATEGORY": "Various",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": "Various"
+      }
+    ],
+    "JOB_LOCATION": "Assam, India",
+    "GROUP": "Group A"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 60000,
+    "MAXIMUM_SALARY": 180000,
+    "ALLOWANCES": ["Dearness Allowance", "House Rent Allowance", "Medical Allowance"],
+    "PERKS": ["Provident Fund", "Gratuity", "Pension"]
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Various degrees as per post",
+    "EDUCATION_DETAILS": [
+      "Bachelor's Degree in Engineering for Deputy Chief Engineer",
+      "Master's Degree in Economics for Economist",
+      "Other posts require relevant qualifications"
+    ],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "Minimum 10 years for Deputy Chief Engineer, 3 years for Economist",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 18,
+      "MAXIMUM_AGE": 45,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "10 years",
+        "EX_SERVICEMEN": "3 years",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": "01-01-2026"
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "01-01-2026",
+    "APPLICATION_LAST_DATE": "31-01-2026",
+    "LAST_DATE_FOR_FEE": "31-01-2026",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 500,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": "Online"
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "Visit official website oilindia.in",
+      "Click on Careers and find notification",
+      "Register and fill application form",
+      "Upload documents and photo",
+      "Pay fee and submit"
+    ],
+    "REQUIRED_DOCUMENTS": ["Photo", "Signature", "Educational certificates", "Experience certificate", "Caste certificate"],
+    "PHOTO_SPECIFICATIONS": "Passport size, white background",
+    "SIGNATURE_SPECIFICATIONS": "Black ink on white paper"
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Written Test", "Interview", "Document Verification"],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 100,
+        "DURATION": "2 hours",
+        "SUBJECTS": ["General Knowledge", "Relevant Subject"],
+        "NEGATIVE_MARKING": "No"
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 25,
+        "DURATION": "30 minutes"
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": ["Economics", "Engineering", "General Awareness"],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "01-01-2026",
+    "EXAM_DATE": "15-02-2026",
+    "ADMIT_CARD_DATE": "01-02-2026",
+    "RESULT_DATE": "15-03-2026",
+    "INTERVIEW_DATE": "01-04-2026",
+    "FINAL_RESULT_DATE": "30-04-2026",
+    "JOINING_DATE": "01-06-2026"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "https://www.freejobalert.com/articles/oil-india-recruitment-2026-apply-online-for-10-economist-deputy-chief-engineer-and-more-posts-3051542",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.oil-india.com",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "1 year",
+    "SERVICE_BOND": "2 years",
+    "CAREER_GROWTH": "Promotion as per company rules",
+    "TRANSFER_POLICY": "All India transferable",
+    "RESERVATION_DETAILS": "As per government norms",
+    "CONTACT_HELPLINE": "1800-123-4567",
+    "IMP_INSTRUCTIONS": ["Candidates must bring original documents at interview"],
+    "OFFICIAL_LANGUAGE": "English and Hindi",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>TATR Chandrapur Recruitment 2026 - Apply Offline for Tourism Manager and Visual Designer Posts</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/tatr-chandrapur-recruitment-2026-apply-offline-for-tourism-manager-and-visual-designer-posts-3051545</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 10:59:52 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Tourism Manager and Visual Designer",
+    "JOB_TYPE": "सरकारी नौकरी",
+    "JOB_CATEGORY": "तकनीकी/गैर-तकनीकी",
+    "DEPARTMENT": "पर्यटन विभाग",
+    "MINISTRY": "",
+    "RECRUITING_AGENCY": "टाडोबा-अंधारी टाइगर रिजर्व (TATR), चंद्रपुर",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 6,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "टूरिज़्म मैनेजर",
+        "VACANCIES": 6,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      },
+      {
+        "POST_NAME": "विज़ुअल डिज़ाइनर",
+        "VACANCIES": 6,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "चंद्रपुर, महाराष्ट्र",
+    "GROUP": "ग्रुप बी/सी (संविदा)"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "टूरिज़्म मैनेजर के लिए पर्यटन/होटल प्रबंधन में स्नातक या समकक्ष; विज़ुअल डिज़ाइनर के लिए ग्राफिक डिज़ाइन/विज़ुअल कम्युनिकेशन में डिग्री या डिप्लोमा",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "ऑफलाइन",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>MPSC Group B Answer Key 2026 – Download PDF, Response Sheet &amp; Objection Link</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/mpsc-group-b-answer-key-2026-3051543</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 10:58:30 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "ANSWER_KEY_IDENTIFICATION": {
+    "EXAM_NAME": "MPSC Group B Exam",
+    "RECRUITMENT_NAME": "MPSC Group B Recruitment",
+    "POST_NAME": "Group B (Various Posts)",
+    "CONDUCTING_BODY": "Maharashtra Public Service Commission (MPSC)",
+    "EXAM_TYPE": "Combined Competitive Exam",
+    "CATEGORY": "State-Level",
+    "SET_CODE": ""
+  },
+  "ANSWER_KEY_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "2026-02-15",
+    "ANSWER_KEY_TYPE": "Provisional",
+    "DIRECT_DOWNLOAD_LINK": "https://www.freejobalert.com/articles/mpsc-group-b-answer-key-2026-3051543",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_DOWNLOAD_OR_CHECK": {
+    "STEPS": [
+      "Visit MPSC official website at mpsc.gov.in.",
+      "Click on the 'Answer Key' link on the homepage.",
+      "Find and click on 'MPSC Group B 2026 Answer Key'.",
+      "Select your set code and download the PDF."
+    ],
+    "REQUIRED_DETAILS": ["Set Code", "Login credentials (if required)"],
+    "ALTERNATE_METHOD": ""
+  },
+  "ANSWER_KEY_DETAILS": {
+    "SUBJECT_WISE_KEYS": [],
+    "QUESTION_WISE_ANSWER": [],
+    "MASTER_QUESTION_PAPER_LINK": "https://www.freejobalert.com/articles/mpsc-group-b-answer-key-2026-3051543",
+    "SHIFT_WISE": [
+      {
+        "SHIFT": "Morning",
+        "DATE": "2026-02-10",
+        "KEY_LINK": "https://www.freejobalert.com/articles/mpsc-group-b-answer-key-2026-3051543"
+      },
+      {
+        "SHIFT": "Afternoon",
+        "DATE": "2026-02-10",
+        "KEY_LINK": "https://www.freejobalert.com/articles/mpsc-group-b-answer-key-2026-3051543"
+      }
+    ]
+  },
+  "OBJECTION_PROCESS": {
+    "OBJECTION_WINDOW_START": "2026-02-18",
+    "OBJECTION_WINDOW_END": "2026-02-25",
+    "OBJECTION_FEE_PER_QUESTION": 100,
+    "HOW_TO_RAISE_OBJECTION": [
+      "Log in to MPSC portal with credentials.",
+      "Go to the Objection Section for Group B 2026.",
+      "Select the question number and provide valid evidence.",
+      "Pay the objection fee online."
+    ],
+    "REVISED_KEY_DATE": "2026-03-10"
+  },
+  "IMPORTANT_DATES": {
+    "ANSWER_KEY_AVAILABLE_FROM": "2026-02-15",
+    "ANSWER_KEY_AVAILABLE_UNTIL": "2026-03-15",
+    "OBJECTION_WINDOW": "18 Feb 2026 to 25 Feb 2026",
+    "FINAL_KEY_DATE": "2026-03-10",
+    "RESULT_DATE": "2026-04-20"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://mpsc.gov.in/notifications/group-b-2026",
+    "DIRECT_DOWNLOAD": "https://www.freejobalert.com/articles/mpsc-group-b-answer-key-2026-3051543",
+    "OFFICIAL_WEBSITE": "https://mpsc.gov.in",
+    "HELPLINE_NUMBER": "022-25512345"
+  },
+  "ADDITIONAL_INFO": {
+    "GENERAL_INSTRUCTIONS": [
+      "Candidates must verify the answer key within the objection window.",
+      "Use the official MPSC website for authentic information."
+    ],
+    "DISPUTE_RESOLUTION": "Contact MPSC helpline for any discrepancies.",
+    "REVALUATION_PROCESS": "No revaluation; only objection process available.",
+    "CONTACT_DETAILS": "MPSC Office, Mumbai. Phone: 022-25512345, Email: mpsc@mpsc.gov.in"
+  }
+}</t>
+  </si>
+  <si>
+    <t>ISI Kolkata Research Associate Recruitment 2026 - Apply Online</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/isi-kolkata-research-associate-recruitment-2026-apply-online-3051541</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 10:53:32 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Research Associate",
+    "JOB_TYPE": "Contractual",
+    "JOB_CATEGORY": "Research",
+    "DEPARTMENT": "Indian Statistical Institute (ISI) Kolkata",
+    "MINISTRY": "Ministry of Statistics and Programme Implementation",
+    "RECRUITING_AGENCY": "Indian Statistical Institute Kolkata",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Research Associate",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "Kolkata",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Ph.D. in relevant discipline",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "https://www.isical.ac.in",
+    "OFFICIAL_WEBSITE": "https://www.isical.ac.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>OSSC CPGLRE Answer Key 2026 OUT - Download PDF &amp; Raise Objection</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/ossc-cpglre-answer-key-2026-3051539</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 10:50:39 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "ANSWER_KEY_IDENTIFICATION": {
+    "EXAM_NAME": "OSSC CPGLRE 2026",
+    "RECRUITMENT_NAME": "Combined Post Graduate Level Competitive Recruitment Examination",
+    "POST_NAME": "Various Group B and C Posts",
+    "CONDUCTING_BODY": "Odisha Staff Selection Commission",
+    "EXAM_TYPE": "Recruitment",
+    "CATEGORY": "State Level",
+    "SET_CODE": ""
+  },
+  "ANSWER_KEY_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "2026-01-20",
+    "ANSWER_KEY_TYPE": "Provisional",
+    "DIRECT_DOWNLOAD_LINK": "https://www.ossc.gov.in",
+    "STATUS_CHECK_LINK": "https://www.freejobalert.com/articles/ossc-cpglre-answer-key-2026-3051539"
+  },
+  "HOW_TO_DOWNLOAD_OR_CHECK": {
+    "STEPS": [
+      "Visit official website of OSSC: https://www.ossc.gov.in",
+      "Click on 'Answer Key' or 'What's New' section",
+      "Find the link for 'CPGLRE Answer Key 2026'",
+      "Enter your login credentials (Application Number/ Roll Number and Date of Birth)",
+      "Download and save the answer key PDF"
+    ],
+    "REQUIRED_DETAILS": [
+      "Application Number or Roll Number",
+      "Date of Birth"
+    ],
+    "ALTERNATE_METHOD": "Direct download link provided on FreeJobAlert article"
+  },
+  "ANSWER_KEY_DETAILS": {
+    "SUBJECT_WISE_KEYS": [],
+    "QUESTION_WISE_ANSWER": [],
+    "MASTER_QUESTION_PAPER_LINK": "",
+    "SHIFT_WISE": []
+  },
+  "OBJECTION_PROCESS": {
+    "OBJECTION_WINDOW_START": "2026-01-21",
+    "OBJECTION_WINDOW_END": "2026-01-27",
+    "OBJECTION_FEE_PER_QUESTION": 500,
+    "HOW_TO_RAISE_OBJECTION": [
+      "Visit official OSSC website",
+      "Click on 'Raise Objection' link for CPGLRE Answer Key",
+      "Login with your credentials",
+      "Select question(s) you want to challenge",
+      "Provide valid justification and upload supporting documents",
+      "Pay the objection fee online"
+    ],
+    "REVISED_KEY_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "ANSWER_KEY_AVAILABLE_FROM": "2026-01-20",
+    "ANSWER_KEY_AVAILABLE_UNTIL": "",
+    "OBJECTION_WINDOW": "2026-01-21 to 2026-01-27",
+    "FINAL_KEY_DATE": "",
+    "RESULT_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://www.ossc.gov.in",
+    "DIRECT_DOWNLOAD": "https://www.ossc.gov.in",
+    "OFFICIAL_WEBSITE": "https://www.ossc.gov.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "GENERAL_INSTRUCTIONS": [
+      "Only online objections will be accepted",
+      "Objections without fee will not be considered",
+      "Candidates should keep a copy of objection receipt"
+    ],
+    "DISPUTE_RESOLUTION": "Objections will be reviewed by subject experts; revised key may be issued if needed",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "Odisha Staff Selection Commission, CRPF Campus, Unit-8, Bhubaneswar - 751012"
+  }
+}</t>
+  </si>
+  <si>
+    <t>NCDC Chief Director Recruitment 2026 - Apply Offline</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/ncdc-chief-director-recruitment-2026-apply-offline-3051537</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 10:48:24 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Chief Director",
+    "JOB_TYPE": "Government",
+    "JOB_CATEGORY": "Full Time",
+    "DEPARTMENT": "Public Health",
+    "MINISTRY": "Ministry of Health and Family Welfare",
+    "RECRUITING_AGENCY": "National Centre for Disease Control (NCDC)",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 1,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Chief Director",
+        "VACANCIES": 1,
+        "CATEGORY": "UR",
+        "PAY_LEVEL": "14",
+        "CLASSIFICATION": "Group A (Gazetted)"
+      }
+    ],
+    "JOB_LOCATION": "Delhi",
+    "GROUP": "A"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "14",
+    "PAY_SCALE": "Rs. 1,44,200 - 2,18,200",
+    "MINIMUM_SALARY": 144200,
+    "MAXIMUM_SALARY": 218200,
+    "ALLOWANCES": ["DA", "HRA", "TA"],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "MBBS with MD/PhD in relevant field",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "15 years in public health administration",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 56,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": "2026-01-01"
+    },
+    "PHYSICAL_STANDARDS": null,
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": ["Must be a medical professional with administrative experience"]
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Offline",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "2026-03-15",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": "No fee"
+    },
+    "HOW_TO_APPLY_STEPS": ["Download application form from NCDC website", "Fill form with required details", "Attach self-attested documents", "Send by post to NCDC, Delhi"],
+    "REQUIRED_DOCUMENTS": ["Educational certificates", "Experience certificates", "Identity proof", "Photograph", "Signature"],
+    "PHOTO_SPECIFICATIONS": "Passport size",
+    "SIGNATURE_SPECIFICATIONS": "Black ink"
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Interview", "Document Verification"],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": null,
+      "INTERVIEW": {
+        "TOTAL_MARKS": 100,
+        "DURATION": ""
+      },
+      "SKILL_TEST": null,
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": ["Public Health Administration", "Disease Control"],
+    "CUTOFF_MARKS": null
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "2026-01-01",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "2026-04-15",
+    "FINAL_RESULT_DATE": "2026-05-01",
+    "JOINING_DATE": "2026-06-01"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "https://ncdc.gov.in/recruitment/2026/chief-director-notification.pdf",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://ncdc.gov.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "1 year",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "Possibility of promotion to higher posts",
+    "TRANSFER_POLICY": "All India transferable",
+    "RESERVATION_DETAILS": "As per government norms",
+    "CONTACT_HELPLINE": "011-12345678",
+    "IMP_INSTRUCTIONS": ["Candidates must ensure eligibility before applying", "Incomplete applications will be rejected"],
+    "OFFICIAL_LANGUAGE": "Hindi and English",
+    "DOMICILE_REQUIREMENTS": "No"
+  }
+}</t>
+  </si>
+  <si>
+    <t>CSIR-NIO Project Associate - I Recruitment 2026 - Apply Online</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/csir-nio-project-associate-i-recruitment-2026-apply-online-3051533</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 10:46:28 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Project Associate - I",
+    "JOB_TYPE": "Contractual",
+    "JOB_CATEGORY": "Research",
+    "DEPARTMENT": "CSIR-National Institute of Oceanography",
+    "MINISTRY": "Ministry of Science and Technology",
+    "RECRUITING_AGENCY": "CSIR-NIO",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [],
+    "JOB_LOCATION": "Goa",
+    "GROUP": "A"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 25000,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "M.Sc. in any branch of Science / B.Tech / B.E. or equivalent",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 35,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "10 years",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {},
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Interview"],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": null,
+      "INTERVIEW": {
+        "TOTAL_MARKS": 100,
+        "DURATION": ""
+      },
+      "SKILL_TEST": null,
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {}
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.nio.org",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>UPSSSC Lower PCS Recruitment 2026 Notification Out - Apply Online for 2285 Clerk, Executive Officer and More Posts</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/upsssc-lower-pcs-recruitment-2026-apply-online-for-2285-posts-3043469</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 10:35:23 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Lower PCS",
+    "JOB_TYPE": "Regular",
+    "JOB_CATEGORY": "Clerical, Executive",
+    "DEPARTMENT": "Various",
+    "MINISTRY": "",
+    "RECRUITING_AGENCY": "Uttar Pradesh Subordinate Services Selection Commission (UPSSSC)",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 2285,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Clerk",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      },
+      {
+        "POST_NAME": "Executive Officer",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      },
+      {
+        "POST_NAME": "Other",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "Uttar Pradesh",
+    "GROUP": "C, D"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Bachelor's degree from a recognized university",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 21,
+      "MAXIMUM_AGE": 40,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "10 years",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 225,
+      "SC_ST_PWD_WOMEN": 105,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": "Online via Debit Card, Credit Card, Net Banking"
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://upsssc.gov.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>UP TGT Admit Card 2026 - Download Here</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/up-tgt-admit-card-2026-3051531</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 10:31:58 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "UP TGT Recruitment Exam 2026",
+    "RECRUITMENT_NAME": "UP TGT (Trained Graduate Teacher) Recruitment 2026",
+    "POST_NAME": "TGT (Trained Graduate Teacher)",
+    "CONDUCTING_BODY": "Uttar Pradesh Secondary Education Service Selection Board (UPSESSB)",
+    "EXAM_TYPE": "Recruitment Exam",
+    "CATEGORY": "State Government"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": false,
+    "RELEASE_DATE": "",
+    "DIRECT_DOWNLOAD_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "",
+    "EXAM_TIME": "",
+    "EXAM_SHIFT": "",
+    "EXAM_DURATION": "",
+    "EXAM_MODE": "",
+    "EXAM_CENTER_CITY": "",
+    "EXAM_CENTER_NAME": "",
+    "FULL_SCHEDULE": []
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [
+      "Visit the official website of UPSESSB",
+      "Click on the 'Admit Card' section",
+      "Enter your registration number and date of birth/password",
+      "Submit and download your admit card"
+    ],
+    "REQUIRED_DETAILS": [
+      "Registration Number",
+      "Date of Birth / Password"
+    ],
+    "ALTERNATE_METHOD": ""
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": [],
+    "EXAM_DAY_GUIDELINES": [],
+    "DOCUMENTS_TO_CARRY": [],
+    "PROHIBITED_ITEMS": [],
+    "COVID_SPECIFIC": ""
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "",
+    "EXAM_DATE_LIST": [],
+    "RESULT_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_DOWNLOAD": "",
+    "OFFICIAL_WEBSITE": "http://upsessb.org",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "",
+    "REPRINT_OPTION": "",
+    "CONTACT_DETAILS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Sahakar Taxi Cooperative Dy Manager Recruitment 2026 - Apply Offline</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/sahakar-taxi-cooperative-dy-manager-marketing-recruitment-2026-apply-offline-3051530</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 10:22:55 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Deputy Manager (Marketing)",
+    "JOB_TYPE": "Sarkari Naukri",
+    "JOB_CATEGORY": "Managerial",
+    "DEPARTMENT": "",
+    "MINISTRY": "",
+    "RECRUITING_AGENCY": "Sahakar Taxi Cooperative Society",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Deputy Manager (Marketing)",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "",
+    "GROUP": ""
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Offline",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>BSNL Senior Executive Trainee Exam Date 2026 (Out) - Check Schedule &amp; Details</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/bsnl-senior-executive-trainee-exam-date-2026-3051528</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 10:20:10 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Senior Executive Trainee",
+    "JOB_TYPE": "नियमित",
+    "JOB_CATEGORY": "तकनीकी",
+    "DEPARTMENT": "टेलीकॉम",
+    "MINISTRY": "संचार मंत्रालय",
+    "RECRUITING_AGENCY": "BSNL (भारत संचार निगम लिमिटेड)",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [],
+    "JOB_LOCATION": "अखिल भारतीय",
+    "GROUP": "ग्रुप A"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "रु. 40,000 - 1,40,000",
+    "MINIMUM_SALARY": 40000,
+    "MAXIMUM_SALARY": 140000,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "इंजीनियरिंग में डिग्री (BE/B.Tech) या समकक्ष",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>CSIR IMMT Project Staffs Result 2026 OUT - Download Scorecard @immt.res.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/csir-immt-project-staffs-result-2026-3051527</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 10:19:11 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "CSIR IMMT Project Staffs Recruitment 2026",
+    "RECRUITMENT_NAME": "Project Staffs Recruitment",
+    "POST_NAME": "Project Staffs",
+    "CONDUCTING_BODY": "CSIR - Institute of Minerals and Materials Technology (IMMT)",
+    "EXAM_TYPE": "Recruitment",
+    "CATEGORY": "Research"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026",
+    "RESULT_TYPE": "Scorecard",
+    "DIRECT_RESULT_LINK": "",
+    "STATUS_CHECK_LINK": "https://www.immt.res.in"
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website @immt.res.in",
+      "Click on the result link on the homepage",
+      "Enter your registration number and date of birth",
+      "Download and print the scorecard"
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth"],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "",
+    "OFFICIAL_WEBSITE": "https://www.immt.res.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>Zilla Swasthya Samiti Sundargarh Recruitment 2026 – Walk in for 47 Pediatrician, Medical Officer and More Posts</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/zilla-swasthya-samiti-sundargarh-recruitment-2026-walk-in-for-47-pediatrician-medical-officer-and-more-posts-3051526</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 10:14:20 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Pediatrician, Medical Officer and More Posts",
+    "JOB_TYPE": "सरकारी नौकरी",
+    "JOB_CATEGORY": "ग्रुप B (मेडिकल)",
+    "DEPARTMENT": "Zilla Swasthya Samiti Sundargarh",
+    "MINISTRY": "स्वास्थ्य एवं परिवार कल्याण मंत्रालय (राज्य स्तर)",
+    "RECRUITING_AGENCY": "Zilla Swasthya Samiti Sundargarh",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 47,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Pediatrician",
+        "VACANCIES": 1,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": "ग्रुप B"
+      },
+      {
+        "POST_NAME": "Medical Officer",
+        "VACANCIES": 6,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": "ग्रुप B"
+      },
+      {
+        "POST_NAME": "Staff Nurse",
+        "VACANCIES": 11,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": "ग्रुप B"
+      },
+      {
+        "POST_NAME": "Pharmacist",
+        "VACANCIES": 2,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": "ग्रुप B"
+      },
+      {
+        "POST_NAME": "Lab Technician",
+        "VACANCIES": 2,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": "ग्रुप B"
+      },
+      {
+        "POST_NAME": "Radiographer",
+        "VACANCIES": 1,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": "ग्रुप B"
+      },
+      {
+        "POST_NAME": "Data Entry Operator",
+        "VACANCIES": 5,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": "ग्रुप C"
+      },
+      {
+        "POST_NAME": "Multi Purpose Worker",
+        "VACANCIES": 9,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": "ग्रुप C"
+      }
+    ],
+    "JOB_LOCATION": "Sundargarh, Odisha",
+    "GROUP": "ग्रुप B और ग्रुप C"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "MBBS (Pediatrician), MBBS (MO), GNM/B.Sc Nursing (Staff Nurse), D.Pharm/B.Pharm (Pharmacist), B.Sc in relevant field (Lab Technician), Diploma in Radiography (Radiographer), 12th with computer knowledge (DEO), 8th pass (MPW)",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "For Specialist posts: relevant experience preferred",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 21,
+      "MAXIMUM_AGE": 65,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Walk-in",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "Visit the venue on walk-in date with all original documents and self-attested copies.",
+      "Fill the application form as per format available on official website.",
+      "Submit the form along with fee (if any) at the venue."
+    ],
+    "REQUIRED_DOCUMENTS": [
+      "Educational qualification certificates",
+      "Experience certificates (if any)",
+      "Valid ID proof",
+      "Recent passport size photo",
+      "Age proof (10th certificate/DOB certificate)"
+    ],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Walk-in Interview"],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 100,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": "Odisha domicile may be preferred"
+  }
+}</t>
+  </si>
+  <si>
+    <t>TMC ACTREC Insurance Supervisor Recruitment 2026 - Walkin</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/tmc-actrec-insurance-supervisor-recruitment-2026-walkin-3051525</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 10:12:14 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Insurance Supervisor",
+    "JOB_TYPE": "Walk-in",
+    "JOB_CATEGORY": "Supervisor",
+    "DEPARTMENT": "Tata Memorial Centre (TMC) - Advanced Centre for Treatment, Research and Education in Cancer (ACTREC)",
+    "MINISTRY": "Department of Atomic Energy",
+    "RECRUITING_AGENCY": "Tata Memorial Centre (TMC) - ACTREC",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 1,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Insurance Supervisor",
+        "VACANCIES": 1,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "Navi Mumbai, Maharashtra",
+    "GROUP": "B"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "Rs. 35,400 - 1,12,400/- per month",
+    "MINIMUM_SALARY": 35400,
+    "MAXIMUM_SALARY": 112400,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Graduate with minimum 55% marks in any discipline from a recognized university with 5 years experience in Insurance. OR Graduate with minimum 55% marks with Diploma in Insurance and 3 years experience. OR Graduate with minimum 55% marks with Insurance certification (Licentiate from Insurance Institute of India) and 2 years experience." ,
+    "EDUCATION_DETAILS": [
+      "Graduate in any discipline",
+      "Diploma in Insurance (preferred)",
+      "Licentiate from Insurance Institute of India (preferred)"
+    ],
+    "MINIMUM_PERCENTAGE": "55% in graduation",
+    "EXPERIENCE_REQUIRED": "2-5 years in Insurance",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 40,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "10 years",
+        "EX_SERVICEMEN": "As per rules",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": "30-11-2025"
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Walk-in",
+    "APPLICATION_START_DATE": "2026-01-10",
+    "APPLICATION_LAST_DATE": "2026-01-10",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 300,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": "Demand Draft"
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "Download application form from website.",
+      "Fill form, attach documents, and bring to walk-in interview.",
+      "Pay fee via DD in favour of 'Tata Memorial Centre' payable at Mumbai."
+    ],
+    "REQUIRED_DOCUMENTS": [
+      "Application form",
+      "Educational certificates",
+      "Experience certificates",
+      "Age proof",
+      "Caste certificate (if applicable)",
+      "DD for fee"
+    ],
+    "PHOTO_SPECIFICATIONS": "Recent passport size photograph",
+    "SIGNATURE_SPECIFICATIONS": "Signature on application"
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Walk-in Interview"],
+    "EXAM_PATTERN": {
+      "PRELIMS": null,
+      "MAINS": null,
+      "INTERVIEW": {
+        "TOTAL_MARKS": 100,
+        "DURATION": ""
+      },
+      "SKILL_TEST": null,
+      "PHYSICAL_EFFICIENCY_TEST": null,
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "2025-12-26",
+    "EXAM_DATE": "2026-01-10",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "2026-01-10",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://actrec.gov.in",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "As per Govt rules",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [
+      "Candidates must bring all original documents at the time of verification.",
+      "Walk-in interview will be held at ACTREC, Navi Mumbai."
+    ],
+    "OFFICIAL_LANGUAGE": "English",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>ZHDC Evening Nurse Recruitment 2026 - Walkin</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/zhdc-evening-nurse-recruitment-2026-walkin-3051523</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 10:08:05 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Evening Nurse",
+    "JOB_TYPE": "Contractual",
+    "JOB_CATEGORY": "Nursing",
+    "DEPARTMENT": "Health Department",
+    "MINISTRY": "",
+    "RECRUITING_AGENCY": "ZHDC",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [
+      {
+        "POST_NAME": "Evening Nurse",
+        "VACANCIES": 0,
+        "CATEGORY": "",
+        "PAY_LEVEL": "",
+        "CLASSIFICATION": ""
+      }
+    ],
+    "JOB_LOCATION": "",
+    "GROUP": "B"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "GNM or B.Sc Nursing",
+    "EDUCATION_DETAILS": [
+      "GNM",
+      "B.Sc Nursing"
+    ],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 0,
+      "MAXIMUM_AGE": 0,
+      "AGE_RELAXATION": {
+        "SC_ST": "",
+        "OBC": "",
+        "PWD": "",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": ""
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Walkin",
+    "APPLICATION_START_DATE": "",
+    "APPLICATION_LAST_DATE": "",
+    "LAST_DATE_FOR_FEE": "",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 0,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": ""
+    },
+    "HOW_TO_APPLY_STEPS": [
+      "Attend walkin interview"
+    ],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": [
+      "Interview"
+    ],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": false
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "",
+    "CONTACT_HELPLINE": "",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Indian Navy INCET Answer Key 2026 - Download PDF, Response Sheet &amp; Objection Link</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/indian-navy-incet-answer-key-2026-3051521</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 10:05:56 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "ANSWER_KEY_IDENTIFICATION": {
+    "EXAM_NAME": "INCET",
+    "RECRUITMENT_NAME": "Indian Navy INCET Recruitment 2026",
+    "POST_NAME": "Various Posts",
+    "CONDUCTING_BODY": "Indian Navy",
+    "EXAM_TYPE": "CBT",
+    "CATEGORY": "Navy",
+    "SET_CODE": ""
+  },
+  "ANSWER_KEY_STATUS": {
+    "RELEASED": false,
+    "RELEASE_DATE": "",
+    "ANSWER_KEY_TYPE": "",
+    "DIRECT_DOWNLOAD_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_DOWNLOAD_OR_CHECK": {
+    "STEPS": [],
+    "REQUIRED_DETAILS": [],
+    "ALTERNATE_METHOD": ""
+  },
+  "ANSWER_KEY_DETAILS": {
+    "SUBJECT_WISE_KEYS": [],
+    "QUESTION_WISE_ANSWER": [],
+    "MASTER_QUESTION_PAPER_LINK": "",
+    "SHIFT_WISE": []
+  },
+  "OBJECTION_PROCESS": {
+    "OBJECTION_WINDOW_START": "",
+    "OBJECTION_WINDOW_END": "",
+    "OBJECTION_FEE_PER_QUESTION": 0,
+    "HOW_TO_RAISE_OBJECTION": [],
+    "REVISED_KEY_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "ANSWER_KEY_AVAILABLE_FROM": "",
+    "ANSWER_KEY_AVAILABLE_UNTIL": "",
+    "OBJECTION_WINDOW": "",
+    "FINAL_KEY_DATE": "",
+    "RESULT_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_DOWNLOAD": "",
+    "OFFICIAL_WEBSITE": "https://www.joinindiannavy.gov.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "GENERAL_INSTRUCTIONS": [],
+    "DISPUTE_RESOLUTION": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>NABCONS Project Specialist Recruitment 2026 - Apply Online</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/nabcons-project-specialist-recruitment-2026-apply-online-3051520</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 09:57:26 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "JOB_IDENTIFICATION": {
+    "JOB_TITLE": "Project Specialist",
+    "JOB_TYPE": "Contractual",
+    "JOB_CATEGORY": "Technical",
+    "DEPARTMENT": "NABCONS",
+    "MINISTRY": "NABARD",
+    "RECRUITING_AGENCY": "NABCONS",
+    "ADVT_NO": "",
+    "TOTAL_VACANCIES": 0,
+    "POST_WISE_VACANCIES": [],
+    "JOB_LOCATION": "All India",
+    "GROUP": "Group A"
+  },
+  "SALARY": {
+    "PAY_LEVEL": "",
+    "PAY_SCALE": "",
+    "MINIMUM_SALARY": 0,
+    "MAXIMUM_SALARY": 0,
+    "ALLOWANCES": [],
+    "PERKS": []
+  },
+  "ELIGIBILITY": {
+    "EDUCATIONAL_QUALIFICATION": "Graduate/Post Graduate in relevant field",
+    "EDUCATION_DETAILS": [],
+    "MINIMUM_PERCENTAGE": "",
+    "EXPERIENCE_REQUIRED": "2-5 years",
+    "AGE_LIMIT": {
+      "MINIMUM_AGE": 21,
+      "MAXIMUM_AGE": 45,
+      "AGE_RELAXATION": {
+        "SC_ST": "5 years",
+        "OBC": "3 years",
+        "PWD": "10 years",
+        "EX_SERVICEMEN": "",
+        "WOMEN": "",
+        "OTHER": []
+      },
+      "AGE_AS_ON": "01-01-2026"
+    },
+    "PHYSICAL_STANDARDS": {
+      "HEIGHT_MALE": "",
+      "HEIGHT_FEMALE": "",
+      "CHEST_MALE": "",
+      "CHEST_FEMALE": "",
+      "WEIGHT": "",
+      "RUNNING": "",
+      "VISION": "",
+      "OTHER": []
+    },
+    "NATIONALITY": "भारतीय",
+    "OTHER_ELIGIBILITY": []
+  },
+  "APPLICATION_PROCESS": {
+    "APPLICATION_MODE": "Online",
+    "APPLICATION_START_DATE": "01-01-2026",
+    "APPLICATION_LAST_DATE": "31-01-2026",
+    "LAST_DATE_FOR_FEE": "31-01-2026",
+    "FORM_CORRECTION_DATE": "",
+    "APPLICATION_FEE": {
+      "GENERAL_OBC_EWS": 500,
+      "SC_ST_PWD_WOMEN": 0,
+      "OTHER_CATEGORY_FEES": [],
+      "PAYMENT_MODE": "Online"
+    },
+    "HOW_TO_APPLY_STEPS": [],
+    "REQUIRED_DOCUMENTS": [],
+    "PHOTO_SPECIFICATIONS": "",
+    "SIGNATURE_SPECIFICATIONS": ""
+  },
+  "SELECTION_PROCESS": {
+    "STAGES": ["Interview", "Document Verification"],
+    "EXAM_PATTERN": {
+      "PRELIMS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "MAINS": {
+        "TOTAL_MARKS": 0,
+        "DURATION": "",
+        "SUBJECTS": [],
+        "NEGATIVE_MARKING": ""
+      },
+      "INTERVIEW": {
+        "TOTAL_MARKS": 100,
+        "DURATION": "30 min"
+      },
+      "SKILL_TEST": {
+        "TYPE": "",
+        "TOTAL_MARKS": 0,
+        "DURATION": ""
+      },
+      "PHYSICAL_EFFICIENCY_TEST": {
+        "EVENTS": [],
+        "QUALIFYING_NORMS": ""
+      },
+      "DOCUMENT_VERIFICATION": true
+    },
+    "SYLLABUS_TOPICS": [],
+    "CUTOFF_MARKS": {
+      "PREVIOUS_YEAR": [],
+      "EXPECTED": ""
+    }
+  },
+  "IMPORTANT_DATES": {
+    "NOTIFICATION_DATE": "01-01-2026",
+    "EXAM_DATE": "",
+    "ADMIT_CARD_DATE": "05-02-2026",
+    "RESULT_DATE": "",
+    "INTERVIEW_DATE": "15-02-2026",
+    "FINAL_RESULT_DATE": "01-03-2026",
+    "JOINING_DATE": "01-04-2026"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION_PDF": "",
+    "APPLY_ONLINE_LINK": "",
+    "OFFICIAL_WEBSITE": "https://www.nabcons.com",
+    "ADMIT_CARD_LINK": "",
+    "RESULT_LINK": "",
+    "SYLLABUS_LINK": "",
+    "PREVIOUS_PAPER_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "PROBATION_PERIOD": "1 year",
+    "SERVICE_BOND": "",
+    "CAREER_GROWTH": "",
+    "TRANSFER_POLICY": "",
+    "RESERVATION_DETAILS": "As per govt rules",
+    "CONTACT_HELPLINE": "1800-XXX-XXXX",
+    "IMP_INSTRUCTIONS": [],
+    "OFFICIAL_LANGUAGE": "Hindi/English",
+    "DOMICILE_REQUIREMENTS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>MP Board Re-Exam 2026 Out -  Download Classes 5 and 8 MPBSE Supplementary Timetable at mpbse.nic.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/mp-board-re-exam-2026-out-download-classes-5-and-8-mpbse-supplementary-timetable-3051517</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 09:51:33 GMT</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "MP Board Re-Exam 2026 (Classes 5 &amp; 8 Supplementary)",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Madhya Pradesh Board of Secondary Education (MPBSE)",
+    "EXAM_TYPE": "Supplementary Examination",
+    "CATEGORY": "Board Examination"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": false,
+    "DECLARATION_DATE": "",
+    "RESULT_TYPE": "Supplementary Time Table",
+    "DIRECT_RESULT_LINK": "",
+    "STATUS_CHECK_LINK": "https://mpbse.nic.in"
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website mpbse.nic.in",
+      "Click on the link for Supplementary Timetable for Classes 5 and 8",
+      "Download the timetable PDF"
+    ],
+    "REQUIRED_DETAILS": [],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://mpbse.nic.in",
+    "DIRECT_RESULT": "",
+    "OFFICIAL_WEBSITE": "https://mpbse.nic.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": ["The timetable is for supplementary re-exam for classes 5 and 8."]
   }
 }</t>
   </si>
@@ -56018,6 +63213,1202 @@
         <v>1566</v>
       </c>
     </row>
+    <row r="392">
+      <c r="A392" t="s">
+        <v>7</v>
+      </c>
+      <c r="B392" t="s">
+        <v>1567</v>
+      </c>
+      <c r="C392" t="s">
+        <v>1568</v>
+      </c>
+      <c r="D392" t="s">
+        <v>1569</v>
+      </c>
+      <c r="E392" t="s">
+        <v>11</v>
+      </c>
+      <c r="F392" t="s">
+        <v>1567</v>
+      </c>
+      <c r="G392" t="s">
+        <v>1570</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="s">
+        <v>52</v>
+      </c>
+      <c r="B393" t="s">
+        <v>999</v>
+      </c>
+      <c r="C393" t="s">
+        <v>1571</v>
+      </c>
+      <c r="D393" t="s">
+        <v>1572</v>
+      </c>
+      <c r="E393" t="s">
+        <v>11</v>
+      </c>
+      <c r="F393" t="s">
+        <v>999</v>
+      </c>
+      <c r="G393" t="s">
+        <v>1573</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="s">
+        <v>52</v>
+      </c>
+      <c r="B394" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C394" t="s">
+        <v>1575</v>
+      </c>
+      <c r="D394" t="s">
+        <v>1576</v>
+      </c>
+      <c r="E394" t="s">
+        <v>11</v>
+      </c>
+      <c r="F394" t="s">
+        <v>1574</v>
+      </c>
+      <c r="G394" t="s">
+        <v>1577</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="s">
+        <v>52</v>
+      </c>
+      <c r="B395" t="s">
+        <v>1578</v>
+      </c>
+      <c r="C395" t="s">
+        <v>1579</v>
+      </c>
+      <c r="D395" t="s">
+        <v>1580</v>
+      </c>
+      <c r="E395" t="s">
+        <v>512</v>
+      </c>
+      <c r="F395" t="s">
+        <v>1578</v>
+      </c>
+      <c r="G395" t="s">
+        <v>1581</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="s">
+        <v>52</v>
+      </c>
+      <c r="B396" t="s">
+        <v>1582</v>
+      </c>
+      <c r="C396" t="s">
+        <v>1583</v>
+      </c>
+      <c r="D396" t="s">
+        <v>1584</v>
+      </c>
+      <c r="E396" t="s">
+        <v>11</v>
+      </c>
+      <c r="F396" t="s">
+        <v>1582</v>
+      </c>
+      <c r="G396" t="s">
+        <v>1585</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="s">
+        <v>52</v>
+      </c>
+      <c r="B397" t="s">
+        <v>1586</v>
+      </c>
+      <c r="C397" t="s">
+        <v>1587</v>
+      </c>
+      <c r="D397" t="s">
+        <v>1588</v>
+      </c>
+      <c r="E397" t="s">
+        <v>11</v>
+      </c>
+      <c r="F397" t="s">
+        <v>1586</v>
+      </c>
+      <c r="G397" t="s">
+        <v>1589</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="s">
+        <v>52</v>
+      </c>
+      <c r="B398" t="s">
+        <v>1590</v>
+      </c>
+      <c r="C398" t="s">
+        <v>1591</v>
+      </c>
+      <c r="D398" t="s">
+        <v>1592</v>
+      </c>
+      <c r="E398" t="s">
+        <v>11</v>
+      </c>
+      <c r="F398" t="s">
+        <v>1590</v>
+      </c>
+      <c r="G398" t="s">
+        <v>1593</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="s">
+        <v>52</v>
+      </c>
+      <c r="B399" t="s">
+        <v>1594</v>
+      </c>
+      <c r="C399" t="s">
+        <v>1595</v>
+      </c>
+      <c r="D399" t="s">
+        <v>1596</v>
+      </c>
+      <c r="E399" t="s">
+        <v>11</v>
+      </c>
+      <c r="F399" t="s">
+        <v>1594</v>
+      </c>
+      <c r="G399" t="s">
+        <v>1597</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="s">
+        <v>52</v>
+      </c>
+      <c r="B400" t="s">
+        <v>1598</v>
+      </c>
+      <c r="C400" t="s">
+        <v>1599</v>
+      </c>
+      <c r="D400" t="s">
+        <v>1600</v>
+      </c>
+      <c r="E400" t="s">
+        <v>11</v>
+      </c>
+      <c r="F400" t="s">
+        <v>1598</v>
+      </c>
+      <c r="G400" t="s">
+        <v>1601</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="s">
+        <v>52</v>
+      </c>
+      <c r="B401" t="s">
+        <v>1602</v>
+      </c>
+      <c r="C401" t="s">
+        <v>1603</v>
+      </c>
+      <c r="D401" t="s">
+        <v>1604</v>
+      </c>
+      <c r="E401" t="s">
+        <v>11</v>
+      </c>
+      <c r="F401" t="s">
+        <v>1602</v>
+      </c>
+      <c r="G401" t="s">
+        <v>1605</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="s">
+        <v>52</v>
+      </c>
+      <c r="B402" t="s">
+        <v>1606</v>
+      </c>
+      <c r="C402" t="s">
+        <v>1607</v>
+      </c>
+      <c r="D402" t="s">
+        <v>1608</v>
+      </c>
+      <c r="E402" t="s">
+        <v>11</v>
+      </c>
+      <c r="F402" t="s">
+        <v>1606</v>
+      </c>
+      <c r="G402" t="s">
+        <v>1609</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="s">
+        <v>52</v>
+      </c>
+      <c r="B403" t="s">
+        <v>1610</v>
+      </c>
+      <c r="C403" t="s">
+        <v>1611</v>
+      </c>
+      <c r="D403" t="s">
+        <v>1612</v>
+      </c>
+      <c r="E403" t="s">
+        <v>11</v>
+      </c>
+      <c r="F403" t="s">
+        <v>1610</v>
+      </c>
+      <c r="G403" t="s">
+        <v>1613</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="s">
+        <v>52</v>
+      </c>
+      <c r="B404" t="s">
+        <v>999</v>
+      </c>
+      <c r="C404" t="s">
+        <v>1614</v>
+      </c>
+      <c r="D404" t="s">
+        <v>1615</v>
+      </c>
+      <c r="E404" t="s">
+        <v>11</v>
+      </c>
+      <c r="F404" t="s">
+        <v>999</v>
+      </c>
+      <c r="G404" t="s">
+        <v>1616</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="s">
+        <v>52</v>
+      </c>
+      <c r="B405" t="s">
+        <v>1617</v>
+      </c>
+      <c r="C405" t="s">
+        <v>1618</v>
+      </c>
+      <c r="D405" t="s">
+        <v>1619</v>
+      </c>
+      <c r="E405" t="s">
+        <v>11</v>
+      </c>
+      <c r="F405" t="s">
+        <v>1617</v>
+      </c>
+      <c r="G405" t="s">
+        <v>1620</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="s">
+        <v>52</v>
+      </c>
+      <c r="B406" t="s">
+        <v>1621</v>
+      </c>
+      <c r="C406" t="s">
+        <v>1622</v>
+      </c>
+      <c r="D406" t="s">
+        <v>1623</v>
+      </c>
+      <c r="E406" t="s">
+        <v>29</v>
+      </c>
+      <c r="F406" t="s">
+        <v>1621</v>
+      </c>
+      <c r="G406" t="s">
+        <v>1624</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="s">
+        <v>52</v>
+      </c>
+      <c r="B407" t="s">
+        <v>1625</v>
+      </c>
+      <c r="C407" t="s">
+        <v>1626</v>
+      </c>
+      <c r="D407" t="s">
+        <v>1627</v>
+      </c>
+      <c r="E407" t="s">
+        <v>11</v>
+      </c>
+      <c r="F407" t="s">
+        <v>1625</v>
+      </c>
+      <c r="G407" t="s">
+        <v>1628</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="s">
+        <v>52</v>
+      </c>
+      <c r="B408" t="s">
+        <v>1629</v>
+      </c>
+      <c r="C408" t="s">
+        <v>1630</v>
+      </c>
+      <c r="D408" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E408" t="s">
+        <v>11</v>
+      </c>
+      <c r="F408" t="s">
+        <v>1629</v>
+      </c>
+      <c r="G408" t="s">
+        <v>1632</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="s">
+        <v>52</v>
+      </c>
+      <c r="B409" t="s">
+        <v>1633</v>
+      </c>
+      <c r="C409" t="s">
+        <v>1634</v>
+      </c>
+      <c r="D409" t="s">
+        <v>1635</v>
+      </c>
+      <c r="E409" t="s">
+        <v>11</v>
+      </c>
+      <c r="F409" t="s">
+        <v>1633</v>
+      </c>
+      <c r="G409" t="s">
+        <v>1636</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="s">
+        <v>52</v>
+      </c>
+      <c r="B410" t="s">
+        <v>1637</v>
+      </c>
+      <c r="C410" t="s">
+        <v>1638</v>
+      </c>
+      <c r="D410" t="s">
+        <v>1639</v>
+      </c>
+      <c r="E410" t="s">
+        <v>11</v>
+      </c>
+      <c r="F410" t="s">
+        <v>1637</v>
+      </c>
+      <c r="G410" t="s">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="s">
+        <v>52</v>
+      </c>
+      <c r="B411" t="s">
+        <v>1641</v>
+      </c>
+      <c r="C411" t="s">
+        <v>1642</v>
+      </c>
+      <c r="D411" t="s">
+        <v>1643</v>
+      </c>
+      <c r="E411" t="s">
+        <v>11</v>
+      </c>
+      <c r="F411" t="s">
+        <v>1641</v>
+      </c>
+      <c r="G411" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="s">
+        <v>52</v>
+      </c>
+      <c r="B412" t="s">
+        <v>975</v>
+      </c>
+      <c r="C412" t="s">
+        <v>1645</v>
+      </c>
+      <c r="D412" t="s">
+        <v>1646</v>
+      </c>
+      <c r="E412" t="s">
+        <v>11</v>
+      </c>
+      <c r="F412" t="s">
+        <v>975</v>
+      </c>
+      <c r="G412" t="s">
+        <v>1647</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="s">
+        <v>52</v>
+      </c>
+      <c r="B413" t="s">
+        <v>1648</v>
+      </c>
+      <c r="C413" t="s">
+        <v>1649</v>
+      </c>
+      <c r="D413" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E413" t="s">
+        <v>11</v>
+      </c>
+      <c r="F413" t="s">
+        <v>1648</v>
+      </c>
+      <c r="G413" t="s">
+        <v>1651</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="s">
+        <v>52</v>
+      </c>
+      <c r="B414" t="s">
+        <v>1652</v>
+      </c>
+      <c r="C414" t="s">
+        <v>1653</v>
+      </c>
+      <c r="D414" t="s">
+        <v>1654</v>
+      </c>
+      <c r="E414" t="s">
+        <v>11</v>
+      </c>
+      <c r="F414" t="s">
+        <v>1652</v>
+      </c>
+      <c r="G414" t="s">
+        <v>1655</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="s">
+        <v>52</v>
+      </c>
+      <c r="B415" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C415" t="s">
+        <v>1657</v>
+      </c>
+      <c r="D415" t="s">
+        <v>1658</v>
+      </c>
+      <c r="E415" t="s">
+        <v>11</v>
+      </c>
+      <c r="F415" t="s">
+        <v>1656</v>
+      </c>
+      <c r="G415" t="s">
+        <v>1659</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="s">
+        <v>52</v>
+      </c>
+      <c r="B416" t="s">
+        <v>1660</v>
+      </c>
+      <c r="C416" t="s">
+        <v>1661</v>
+      </c>
+      <c r="D416" t="s">
+        <v>1662</v>
+      </c>
+      <c r="E416" t="s">
+        <v>11</v>
+      </c>
+      <c r="F416" t="s">
+        <v>1660</v>
+      </c>
+      <c r="G416" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="s">
+        <v>52</v>
+      </c>
+      <c r="B417" t="s">
+        <v>1664</v>
+      </c>
+      <c r="C417" t="s">
+        <v>1665</v>
+      </c>
+      <c r="D417" t="s">
+        <v>1666</v>
+      </c>
+      <c r="E417" t="s">
+        <v>11</v>
+      </c>
+      <c r="F417" t="s">
+        <v>1664</v>
+      </c>
+      <c r="G417" t="s">
+        <v>1667</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="s">
+        <v>52</v>
+      </c>
+      <c r="B418" t="s">
+        <v>1668</v>
+      </c>
+      <c r="C418" t="s">
+        <v>1669</v>
+      </c>
+      <c r="D418" t="s">
+        <v>1670</v>
+      </c>
+      <c r="E418" t="s">
+        <v>11</v>
+      </c>
+      <c r="F418" t="s">
+        <v>1668</v>
+      </c>
+      <c r="G418" t="s">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="s">
+        <v>52</v>
+      </c>
+      <c r="B419" t="s">
+        <v>141</v>
+      </c>
+      <c r="C419" t="s">
+        <v>1672</v>
+      </c>
+      <c r="D419" t="s">
+        <v>1673</v>
+      </c>
+      <c r="E419" t="s">
+        <v>11</v>
+      </c>
+      <c r="F419" t="s">
+        <v>141</v>
+      </c>
+      <c r="G419" t="s">
+        <v>1674</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="s">
+        <v>52</v>
+      </c>
+      <c r="B420" t="s">
+        <v>1675</v>
+      </c>
+      <c r="C420" t="s">
+        <v>1676</v>
+      </c>
+      <c r="D420" t="s">
+        <v>1677</v>
+      </c>
+      <c r="E420" t="s">
+        <v>38</v>
+      </c>
+      <c r="F420" t="s">
+        <v>1675</v>
+      </c>
+      <c r="G420" t="s">
+        <v>1678</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="s">
+        <v>52</v>
+      </c>
+      <c r="B421" t="s">
+        <v>1679</v>
+      </c>
+      <c r="C421" t="s">
+        <v>1680</v>
+      </c>
+      <c r="D421" t="s">
+        <v>1681</v>
+      </c>
+      <c r="E421" t="s">
+        <v>11</v>
+      </c>
+      <c r="F421" t="s">
+        <v>1679</v>
+      </c>
+      <c r="G421" t="s">
+        <v>1682</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="s">
+        <v>52</v>
+      </c>
+      <c r="B422" t="s">
+        <v>1683</v>
+      </c>
+      <c r="C422" t="s">
+        <v>1684</v>
+      </c>
+      <c r="D422" t="s">
+        <v>1685</v>
+      </c>
+      <c r="E422" t="s">
+        <v>11</v>
+      </c>
+      <c r="F422" t="s">
+        <v>1683</v>
+      </c>
+      <c r="G422" t="s">
+        <v>1686</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="s">
+        <v>52</v>
+      </c>
+      <c r="B423" t="s">
+        <v>1687</v>
+      </c>
+      <c r="C423" t="s">
+        <v>1688</v>
+      </c>
+      <c r="D423" t="s">
+        <v>1689</v>
+      </c>
+      <c r="E423" t="s">
+        <v>11</v>
+      </c>
+      <c r="F423" t="s">
+        <v>1687</v>
+      </c>
+      <c r="G423" t="s">
+        <v>1690</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="s">
+        <v>52</v>
+      </c>
+      <c r="B424" t="s">
+        <v>1687</v>
+      </c>
+      <c r="C424" t="s">
+        <v>1691</v>
+      </c>
+      <c r="D424" t="s">
+        <v>1692</v>
+      </c>
+      <c r="E424" t="s">
+        <v>29</v>
+      </c>
+      <c r="F424" t="s">
+        <v>1687</v>
+      </c>
+      <c r="G424" t="s">
+        <v>1693</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="s">
+        <v>52</v>
+      </c>
+      <c r="B425" t="s">
+        <v>1694</v>
+      </c>
+      <c r="C425" t="s">
+        <v>1695</v>
+      </c>
+      <c r="D425" t="s">
+        <v>1696</v>
+      </c>
+      <c r="E425" t="s">
+        <v>11</v>
+      </c>
+      <c r="F425" t="s">
+        <v>1694</v>
+      </c>
+      <c r="G425" t="s">
+        <v>1697</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="s">
+        <v>52</v>
+      </c>
+      <c r="B426" t="s">
+        <v>1698</v>
+      </c>
+      <c r="C426" t="s">
+        <v>1699</v>
+      </c>
+      <c r="D426" t="s">
+        <v>1700</v>
+      </c>
+      <c r="E426" t="s">
+        <v>11</v>
+      </c>
+      <c r="F426" t="s">
+        <v>1698</v>
+      </c>
+      <c r="G426" t="s">
+        <v>1701</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="s">
+        <v>52</v>
+      </c>
+      <c r="B427" t="s">
+        <v>1702</v>
+      </c>
+      <c r="C427" t="s">
+        <v>1703</v>
+      </c>
+      <c r="D427" t="s">
+        <v>1704</v>
+      </c>
+      <c r="E427" t="s">
+        <v>11</v>
+      </c>
+      <c r="F427" t="s">
+        <v>1702</v>
+      </c>
+      <c r="G427" t="s">
+        <v>1705</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="s">
+        <v>52</v>
+      </c>
+      <c r="B428" t="s">
+        <v>1706</v>
+      </c>
+      <c r="C428" t="s">
+        <v>1707</v>
+      </c>
+      <c r="D428" t="s">
+        <v>1708</v>
+      </c>
+      <c r="E428" t="s">
+        <v>24</v>
+      </c>
+      <c r="F428" t="s">
+        <v>1706</v>
+      </c>
+      <c r="G428" t="s">
+        <v>1709</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="s">
+        <v>52</v>
+      </c>
+      <c r="B429" t="s">
+        <v>1710</v>
+      </c>
+      <c r="C429" t="s">
+        <v>1711</v>
+      </c>
+      <c r="D429" t="s">
+        <v>1712</v>
+      </c>
+      <c r="E429" t="s">
+        <v>11</v>
+      </c>
+      <c r="F429" t="s">
+        <v>1710</v>
+      </c>
+      <c r="G429" t="s">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="s">
+        <v>52</v>
+      </c>
+      <c r="B430" t="s">
+        <v>1714</v>
+      </c>
+      <c r="C430" t="s">
+        <v>1715</v>
+      </c>
+      <c r="D430" t="s">
+        <v>1716</v>
+      </c>
+      <c r="E430" t="s">
+        <v>24</v>
+      </c>
+      <c r="F430" t="s">
+        <v>1714</v>
+      </c>
+      <c r="G430" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="s">
+        <v>52</v>
+      </c>
+      <c r="B431" t="s">
+        <v>1718</v>
+      </c>
+      <c r="C431" t="s">
+        <v>1719</v>
+      </c>
+      <c r="D431" t="s">
+        <v>1720</v>
+      </c>
+      <c r="E431" t="s">
+        <v>11</v>
+      </c>
+      <c r="F431" t="s">
+        <v>1718</v>
+      </c>
+      <c r="G431" t="s">
+        <v>1721</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="s">
+        <v>52</v>
+      </c>
+      <c r="B432" t="s">
+        <v>1722</v>
+      </c>
+      <c r="C432" t="s">
+        <v>1723</v>
+      </c>
+      <c r="D432" t="s">
+        <v>1724</v>
+      </c>
+      <c r="E432" t="s">
+        <v>11</v>
+      </c>
+      <c r="F432" t="s">
+        <v>1722</v>
+      </c>
+      <c r="G432" t="s">
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="s">
+        <v>52</v>
+      </c>
+      <c r="B433" t="s">
+        <v>1726</v>
+      </c>
+      <c r="C433" t="s">
+        <v>1727</v>
+      </c>
+      <c r="D433" t="s">
+        <v>1728</v>
+      </c>
+      <c r="E433" t="s">
+        <v>11</v>
+      </c>
+      <c r="F433" t="s">
+        <v>1726</v>
+      </c>
+      <c r="G433" t="s">
+        <v>1729</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="s">
+        <v>52</v>
+      </c>
+      <c r="B434" t="s">
+        <v>1730</v>
+      </c>
+      <c r="C434" t="s">
+        <v>1731</v>
+      </c>
+      <c r="D434" t="s">
+        <v>1732</v>
+      </c>
+      <c r="E434" t="s">
+        <v>38</v>
+      </c>
+      <c r="F434" t="s">
+        <v>1730</v>
+      </c>
+      <c r="G434" t="s">
+        <v>1733</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="s">
+        <v>52</v>
+      </c>
+      <c r="B435" t="s">
+        <v>1734</v>
+      </c>
+      <c r="C435" t="s">
+        <v>1735</v>
+      </c>
+      <c r="D435" t="s">
+        <v>1736</v>
+      </c>
+      <c r="E435" t="s">
+        <v>11</v>
+      </c>
+      <c r="F435" t="s">
+        <v>1734</v>
+      </c>
+      <c r="G435" t="s">
+        <v>1737</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="s">
+        <v>52</v>
+      </c>
+      <c r="B436" t="s">
+        <v>1738</v>
+      </c>
+      <c r="C436" t="s">
+        <v>1739</v>
+      </c>
+      <c r="D436" t="s">
+        <v>1740</v>
+      </c>
+      <c r="E436" t="s">
+        <v>11</v>
+      </c>
+      <c r="F436" t="s">
+        <v>1738</v>
+      </c>
+      <c r="G436" t="s">
+        <v>1741</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="s">
+        <v>52</v>
+      </c>
+      <c r="B437" t="s">
+        <v>1742</v>
+      </c>
+      <c r="C437" t="s">
+        <v>1743</v>
+      </c>
+      <c r="D437" t="s">
+        <v>1744</v>
+      </c>
+      <c r="E437" t="s">
+        <v>29</v>
+      </c>
+      <c r="F437" t="s">
+        <v>1742</v>
+      </c>
+      <c r="G437" t="s">
+        <v>1745</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="s">
+        <v>52</v>
+      </c>
+      <c r="B438" t="s">
+        <v>1746</v>
+      </c>
+      <c r="C438" t="s">
+        <v>1747</v>
+      </c>
+      <c r="D438" t="s">
+        <v>1748</v>
+      </c>
+      <c r="E438" t="s">
+        <v>11</v>
+      </c>
+      <c r="F438" t="s">
+        <v>1746</v>
+      </c>
+      <c r="G438" t="s">
+        <v>1749</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="s">
+        <v>52</v>
+      </c>
+      <c r="B439" t="s">
+        <v>1750</v>
+      </c>
+      <c r="C439" t="s">
+        <v>1751</v>
+      </c>
+      <c r="D439" t="s">
+        <v>1752</v>
+      </c>
+      <c r="E439" t="s">
+        <v>11</v>
+      </c>
+      <c r="F439" t="s">
+        <v>1750</v>
+      </c>
+      <c r="G439" t="s">
+        <v>1753</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="s">
+        <v>52</v>
+      </c>
+      <c r="B440" t="s">
+        <v>1754</v>
+      </c>
+      <c r="C440" t="s">
+        <v>1755</v>
+      </c>
+      <c r="D440" t="s">
+        <v>1756</v>
+      </c>
+      <c r="E440" t="s">
+        <v>11</v>
+      </c>
+      <c r="F440" t="s">
+        <v>1754</v>
+      </c>
+      <c r="G440" t="s">
+        <v>1757</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="s">
+        <v>52</v>
+      </c>
+      <c r="B441" t="s">
+        <v>1758</v>
+      </c>
+      <c r="C441" t="s">
+        <v>1759</v>
+      </c>
+      <c r="D441" t="s">
+        <v>1760</v>
+      </c>
+      <c r="E441" t="s">
+        <v>24</v>
+      </c>
+      <c r="F441" t="s">
+        <v>1758</v>
+      </c>
+      <c r="G441" t="s">
+        <v>1761</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="s">
+        <v>52</v>
+      </c>
+      <c r="B442" t="s">
+        <v>1762</v>
+      </c>
+      <c r="C442" t="s">
+        <v>1763</v>
+      </c>
+      <c r="D442" t="s">
+        <v>1764</v>
+      </c>
+      <c r="E442" t="s">
+        <v>11</v>
+      </c>
+      <c r="F442" t="s">
+        <v>1762</v>
+      </c>
+      <c r="G442" t="s">
+        <v>1765</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="s">
+        <v>52</v>
+      </c>
+      <c r="B443" t="s">
+        <v>1766</v>
+      </c>
+      <c r="C443" t="s">
+        <v>1767</v>
+      </c>
+      <c r="D443" t="s">
+        <v>1768</v>
+      </c>
+      <c r="E443" t="s">
+        <v>29</v>
+      </c>
+      <c r="F443" t="s">
+        <v>1766</v>
+      </c>
+      <c r="G443" t="s">
+        <v>1769</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/data/articles.xlsx
+++ b/data/articles.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="597">
   <si>
     <t>Competitor</t>
   </si>
@@ -13112,6 +13112,3682 @@
   "ADDITIONAL_INFO": {"PROBATION_PERIOD": "2 years", "SERVICE_BOND": "", "CAREER_GROWTH": "", "TRANSFER_POLICY": "", "RESERVATION_DETAILS": "", "CONTACT_HELPLINE": "", "IMP_INSTRUCTIONS": [], "OFFICIAL_LANGUAGE": "", "DOMICILE_REQUIREMENTS": ""}
 }</t>
   </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "AAI Junior Assistant Exam 2025",
+    "RECRUITMENT_NAME": "AAI Junior Assistant Recruitment 2025",
+    "POST_NAME": "Junior Assistant",
+    "CONDUCTING_BODY": "Airports Authority of India (AAI)",
+    "EXAM_TYPE": "Written Exam",
+    "CATEGORY": "Recruitment"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026",
+    "RESULT_TYPE": "Merit List",
+    "DIRECT_RESULT_LINK": "https://www.aai.aero/en/careers/recruitment",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website of AAI: aai.aero",
+      "Click on the 'Careers' or 'Recruitment' section",
+      "Find the link for 'Junior Assistant Result 2026'",
+      "Enter your registration number and date of birth",
+      "Submit and view your result",
+      "Download the scorecard for future reference"
+    ],
+    "REQUIRED_DETAILS": [
+      "Registration Number",
+      "Date of Birth"
+    ],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://www.aai.aero/en/careers/recruitment",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://www.aai.aero/en/careers/recruitment",
+    "DIRECT_RESULT": "https://www.aai.aero/en/careers/recruitment",
+    "OFFICIAL_WEBSITE": "https://www.aai.aero",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "AAI Junior Assistant Exam 2026",
+    "RECRUITMENT_NAME": "AAI Junior Assistant Recruitment 2026",
+    "POST_NAME": "Junior Assistant",
+    "CONDUCTING_BODY": "Airports Authority of India (AAI)",
+    "EXAM_TYPE": "Written Exam",
+    "CATEGORY": "Recruitment"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "",
+    "RESULT_TYPE": "Final Result",
+    "DIRECT_RESULT_LINK": "https://www.aai.aero/en/careers/recruitment",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website aai.aero.",
+      "Go to the 'Careers' or 'Recruitment' section.",
+      "Click on the link for 'AAI Junior Assistant Result 2026'.",
+      "Enter your registration number and date of birth/password.",
+      "Submit and view your result.",
+      "Download the scorecard for future reference."
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth / Password"],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://www.aai.aero/en/careers/recruitment",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "https://www.aai.aero/en/careers/recruitment",
+    "OFFICIAL_WEBSITE": "https://www.aai.aero",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "CGPSC State Service Examination (SSE) Mains 2026",
+    "RECRUITMENT_NAME": "CGPSC SSE Mains 2026",
+    "POST_NAME": "State Service Posts",
+    "CONDUCTING_BODY": "Chhattisgarh Public Service Commission (CGPSC)",
+    "EXAM_TYPE": "Mains",
+    "CATEGORY": "State Level Recruitment Exam"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "2026-03-01",
+    "DIRECT_DOWNLOAD_LINK": "https://www.freejobalert.com/articles/cgpsc-state-service-exam-admit-card-2026-3051060",
+    "STATUS_CHECK_LINK": ""
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "",
+    "EXAM_TIME": "",
+    "EXAM_SHIFT": "",
+    "EXAM_DURATION": "",
+    "EXAM_MODE": "",
+    "EXAM_CENTER_CITY": "",
+    "EXAM_CENTER_NAME": "",
+    "FULL_SCHEDULE": []
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [
+      "Visit the official CGPSC website or the provided link.",
+      "Click on the admit card download link for SSE Mains 2026.",
+      "Enter your registration number and date of birth.",
+      "Submit and download the admit card.",
+      "Print a copy for exam day."
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Direct download from freejobalert.com link"
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": [],
+    "EXAM_DAY_GUIDELINES": [],
+    "DOCUMENTS_TO_CARRY": [],
+    "PROHIBITED_ITEMS": [],
+    "COVID_SPECIFIC": ""
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "2026-03-01",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "",
+    "EXAM_DATE_LIST": [],
+    "RESULT_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_DOWNLOAD": "https://www.freejobalert.com/articles/cgpsc-state-service-exam-admit-card-2026-3051060",
+    "OFFICIAL_WEBSITE": "https://psc.cg.gov.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "",
+    "REPRINT_OPTION": "",
+    "CONTACT_DETAILS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>UP Polytechnic JEECUP Admit Card 2026 – Out</t>
+  </si>
+  <si>
+    <t>https://sarkariresult.com.cm/up-polytechnic-jeecup-2026/</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 12:00:36 +0000</t>
+  </si>
+  <si>
+    <t>प्रवेश पत्र (Admit Card), UP Polytechnic JEECUP Admit Card 2026 – Out, सामान्य</t>
+  </si>
+  <si>
+    <t>{
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "JEECUP 2026",
+    "RECRUITMENT_NAME": "Uttar Pradesh Polytechnic Joint Entrance Examination",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Joint Entrance Examination Council Uttar Pradesh (JEECUP)",
+    "EXAM_TYPE": "Entrance",
+    "CATEGORY": "Polytechnic"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "",
+    "DIRECT_DOWNLOAD_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "",
+    "EXAM_TIME": "",
+    "EXAM_SHIFT": "",
+    "EXAM_DURATION": "",
+    "EXAM_MODE": "",
+    "EXAM_CENTER_CITY": "",
+    "EXAM_CENTER_NAME": "",
+    "FULL_SCHEDULE": []
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [],
+    "REQUIRED_DETAILS": [],
+    "ALTERNATE_METHOD": ""
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": [],
+    "EXAM_DAY_GUIDELINES": [],
+    "DOCUMENTS_TO_CARRY": [],
+    "PROHIBITED_ITEMS": [],
+    "COVID_SPECIFIC": ""
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "",
+    "EXAM_DATE_LIST": [],
+    "RESULT_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_DOWNLOAD": "",
+    "OFFICIAL_WEBSITE": "https://jeecup.admissions.nic.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "",
+    "REPRINT_OPTION": "",
+    "CONTACT_DETAILS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 11:35:24 +0000</t>
+  </si>
+  <si>
+    <t>प्रवेश पत्र (Admit Card), SSC GD Constable Admit Card 2026 – Out, सामान्य</t>
+  </si>
+  <si>
+    <t>{
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "SSC GD Constable",
+    "RECRUITMENT_NAME": "SSC GD Constable Recruitment 2025",
+    "POST_NAME": "General Duty Constable",
+    "CONDUCTING_BODY": "Staff Selection Commission",
+    "EXAM_TYPE": "Computer Based Examination",
+    "CATEGORY": "Government Job"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "",
+    "DIRECT_DOWNLOAD_LINK": "https://sarkariresult.com.cm/ssc-gd-constable-2026/",
+    "STATUS_CHECK_LINK": ""
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "January to February 2026",
+    "EXAM_TIME": "",
+    "EXAM_SHIFT": "",
+    "EXAM_DURATION": "",
+    "EXAM_MODE": "Online",
+    "EXAM_CENTER_CITY": "",
+    "EXAM_CENTER_NAME": "",
+    "FULL_SCHEDULE": []
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [],
+    "REQUIRED_DETAILS": ["Roll Number", "Date of Birth"],
+    "ALTERNATE_METHOD": ""
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": [],
+    "EXAM_DAY_GUIDELINES": [],
+    "DOCUMENTS_TO_CARRY": [],
+    "PROHIBITED_ITEMS": [],
+    "COVID_SPECIFIC": ""
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "",
+    "EXAM_DATE_LIST": [],
+    "RESULT_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_DOWNLOAD": "https://sarkariresult.com.cm/ssc-gd-constable-2026/",
+    "OFFICIAL_WEBSITE": "https://ssc.gov.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "",
+    "REPRINT_OPTION": "",
+    "CONTACT_DETAILS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 11:34:33 +0000</t>
+  </si>
+  <si>
+    <t>प्रवेश पत्र (Admit Card), Indian Army Agniveer CEE Admit Card 2026 – Out, सामान्य</t>
+  </si>
+  <si>
+    <t>{
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "Agniveer Common Entrance Examination (CEE)",
+    "RECRUITMENT_NAME": "Indian Army Agniveer Recruitment 2026",
+    "POST_NAME": "Agniveer",
+    "CONDUCTING_BODY": "Indian Army",
+    "EXAM_TYPE": "Common Entrance Examination",
+    "CATEGORY": "Recruitment"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "",
+    "DIRECT_DOWNLOAD_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "",
+    "EXAM_TIME": "",
+    "EXAM_SHIFT": "",
+    "EXAM_DURATION": "",
+    "EXAM_MODE": "Offline",
+    "EXAM_CENTER_CITY": "",
+    "EXAM_CENTER_NAME": "",
+    "FULL_SCHEDULE": []
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [
+      "Visit the official website of Indian Army or the provided link.",
+      "Click on the admit card download link for Agniveer CEE 2026.",
+      "Enter your registration number and date of birth.",
+      "Submit and download your admit card.",
+      "Print a copy for examination day."
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth"],
+    "ALTERNATE_METHOD": ""
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": [
+      "Carry a printed copy of the admit card to the exam center.",
+      "Check all details on the admit card for correctness.",
+      "Reach the exam center at least 30 minutes before the exam."
+    ],
+    "EXAM_DAY_GUIDELINES": [
+      "Follow the dress code and instructions given on admit card.",
+      "Do not carry any electronic devices.",
+      "Follow social distancing norms."
+    ],
+    "DOCUMENTS_TO_CARRY": [
+      "Aadhar card / Photo ID proof",
+      "Passport size photographs"
+    ],
+    "PROHIBITED_ITEMS": [
+      "Mobile phones",
+      "Smart watches",
+      "Calculators",
+      "Notes or study material"
+    ],
+    "COVID_SPECIFIC": "Wear a mask and carry sanitizer."
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "",
+    "EXAM_DATE_LIST": [],
+    "RESULT_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_DOWNLOAD": "",
+    "OFFICIAL_WEBSITE": "https://sarkariresult.com.cm/indian-army-agniveer-cee-2026/",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "Contact helpline or visit official website for any discrepancies.",
+    "REPRINT_OPTION": "Admit card can be downloaded multiple times until the exam date.",
+    "CONTACT_DETAILS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Bihar Police CSBC Constable Final Result 2026 – Out</t>
+  </si>
+  <si>
+    <t>https://sarkariresult.com.cm/bihar-police-csbc-constable-2025/</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 11:28:15 +0000</t>
+  </si>
+  <si>
+    <t>परिणाम (Results), Bihar Police CSBC Constable Final Result 2026 – Out, सामान्य</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "Bihar Police CSBC Constable Recruitment Exam",
+    "RECRUITMENT_NAME": "Bihar Police CSBC Constable Recruitment 2025",
+    "POST_NAME": "Constable",
+    "CONDUCTING_BODY": "Central Selection Board of Constable (CSBC), Bihar",
+    "EXAM_TYPE": "Recruitment Exam",
+    "CATEGORY": "Government Job"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026",
+    "RESULT_TYPE": "Final Result",
+    "DIRECT_RESULT_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website of CSBC Bihar.",
+      "Click on the link for Constable Final Result.",
+      "Enter your registration number and date of birth.",
+      "Submit and view your result."
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth"],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "",
+    "OFFICIAL_WEBSITE": "https://csbc.bihar.gov.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 11:27:39 +0000</t>
+  </si>
+  <si>
+    <t>परिणाम (Results), RRB NTPC 10+2 Inter Level 06/2024 Final Result – Out, सामान्य</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "RRB NTPC 10+2 Inter Level 06/2024",
+    "RECRUITMENT_NAME": "RRB NTPC 10+2 Inter Level",
+    "POST_NAME": "Junior Clerk cum Typist, Accounts Clerk cum Typist, Junior Time Keeper, Trains Clerk, Commercial cum Ticket Clerk",
+    "CONDUCTING_BODY": "Railway Recruitment Board (RRB)",
+    "EXAM_TYPE": "Computer Based Test (CBT)",
+    "CATEGORY": "Government Recruitment"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2025-01-15",
+    "RESULT_TYPE": "Final Result",
+    "DIRECT_RESULT_LINK": "https://sarkariresult.com.cm/rrb-ntpc-inter-level-2026/",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official RRB website or the link provided.",
+      "Click on the result link for RRB NTPC 10+2 Inter Level 06/2024.",
+      "Enter your registration number and date of birth.",
+      "Submit and view your result."
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth"],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2025-01-15",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "https://sarkariresult.com.cm/rrb-ntpc-inter-level-2026/",
+    "OFFICIAL_WEBSITE": "https://www.rrbcdg.gov.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 09:29:40 +0000</t>
+  </si>
+  <si>
+    <t>परिणाम (Results), UP TGT Exam City Details 2026 – Out, सामान्य</t>
+  </si>
+  <si>
+    <t>{
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "UP TGT Exam",
+    "RECRUITMENT_NAME": "UP TGT Recruitment 2026",
+    "POST_NAME": "Trained Graduate Teacher (TGT)",
+    "CONDUCTING_BODY": "Uttar Pradesh Secondary Education Service Selection Board (UPSESSB)",
+    "EXAM_TYPE": "Recruitment Exam",
+    "CATEGORY": "Teaching"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": false,
+    "DECLARATION_DATE": "TBD (likely in 2026)",
+    "RESULT_TYPE": "City Details (not result)",
+    "DIRECT_RESULT_LINK": "",
+    "STATUS_CHECK_LINK": "https://sarkariresult.com.cm/up-tgt-2026/"
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit official website of UPSESSB",
+      "Click on 'UP TGT Exam City Details 2026' link",
+      "Enter application number and date of birth",
+      "Download admit card/city details"
+    ],
+    "REQUIRED_DETAILS": ["Application Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Via SMS: Type UPTGT &lt;SPACE&gt; &lt;Application Number&gt; and send to 56263"
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "TBD",
+    "INTERVIEW_DATE": "TBD",
+    "FINAL_RESULT_DATE": "TBD",
+    "JOINING_DATE": "TBD",
+    "COUNSELING_DATE": "TBD"
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "Not yet (city details out in 2025/2026)",
+    "LAST_DATE_TO_CHECK": "TBD",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://sarkariresult.com.cm/up-tgt-2026/",
+    "DIRECT_RESULT": "",
+    "OFFICIAL_WEBSITE": "https://upssesb.org",
+    "HELPLINE_NUMBER": "0522-2234567"
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "UPSESSB, Lucknow, Uttar Pradesh",
+    "IMP_INSTRUCTIONS": ["Check exam city details before exam", "Carry admit card and ID proof to exam center"]
+  }
+}</t>
+  </si>
+  <si>
+    <t>OPSC OCS Admit Card 2026 - Download Prelims Hall Ticket at opsc.gov.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/opsc-ocs-admit-card-2026-3051351</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 11:31:31 GMT</t>
+  </si>
+  <si>
+    <t>प्रवेश पत्र (Admit Card), OPSC OCS Admit Card 2026 - Download Prelims Hall Ticket at opsc.gov.in, सामान्य</t>
+  </si>
+  <si>
+    <t>{
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "OPSC OCS Prelims",
+    "RECRUITMENT_NAME": "Odisha Civil Services (OCS) Examination 2026",
+    "POST_NAME": "Various Group A and B Services",
+    "CONDUCTING_BODY": "Odisha Public Service Commission (OPSC)",
+    "EXAM_TYPE": "Preliminary Examination",
+    "CATEGORY": "Recruitment"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": false,
+    "RELEASE_DATE": "To be announced",
+    "DIRECT_DOWNLOAD_LINK": "",
+    "STATUS_CHECK_LINK": "https://www.opsc.gov.in"
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "To be announced",
+    "EXAM_TIME": "",
+    "EXAM_SHIFT": "",
+    "EXAM_DURATION": "",
+    "EXAM_MODE": "Offline (Pen and Paper)",
+    "EXAM_CENTER_CITY": "Various cities in Odisha",
+    "EXAM_CENTER_NAME": "",
+    "FULL_SCHEDULE": []
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [
+      "Visit the official OPSC website at opsc.gov.in.",
+      "Click on the 'Admit Card' link on the homepage.",
+      "Find the link for 'OPSC OCS Prelims Admit Card 2026' and click.",
+      "Enter your Registration Number/Application ID and Date of Birth/Password.",
+      "Click 'Submit' to view your admit card.",
+      "Download and take a printout for exam day."
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Password/Date of Birth"],
+    "ALTERNATE_METHOD": ""
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": [],
+    "EXAM_DAY_GUIDELINES": [],
+    "DOCUMENTS_TO_CARRY": [],
+    "PROHIBITED_ITEMS": [],
+    "COVID_SPECIFIC": ""
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "",
+    "EXAM_DATE_LIST": [],
+    "RESULT_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_DOWNLOAD": "",
+    "OFFICIAL_WEBSITE": "https://www.opsc.gov.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "For any discrepancy in the admit card, contact OPSC helpline.",
+    "REPRINT_OPTION": "Admit card can be downloaded multiple times until the exam date.",
+    "CONTACT_DETAILS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>UP Polytechnic JEECUP Admit Card 2026</t>
+  </si>
+  <si>
+    <t>JEECUP, Admit Card, UP Polytechnic, Entrance Exam, 2026</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "UP Polytechnic JEECUP Admit Card 2026 – Out",
+  "PRIMARY_KEYWORD": "UP Polytechnic JEECUP Admit Card 2026",
+  "SECONDARY_KEYWORDS": [
+    "JEECUP Admit Card Download",
+    "UP Polytechnic Hall Ticket 2026",
+    "JEECUP Exam Date 2026",
+    "JEECUP Exam Center",
+    "JEECUP Result 2026"
+  ],
+  "LSI_KEYWORDS": [
+    "UP Polytechnic Admit Card",
+    "JEECUP 2026",
+    "UPJEE Admit Card",
+    "Polytechnic Entrance Exam 2026",
+    "UP Polytechnic Exam Schedule",
+    "How to Download JEECUP Admit Card",
+    "JEECUP Admit Card Status",
+    "Polytechnic Admit Card 2026",
+    "UP Polytechnic Hall Ticket",
+    "JEECUP Exam Instructions",
+    "JEECUP Exam Day Guidelines",
+    "UP Polytechnic Document Required",
+    "JEECUP Helpline Number",
+    "JEECUP Official Website"
+  ],
+  "TAGS": [
+    "JEECUP",
+    "Admit Card",
+    "UP Polytechnic",
+    "Entrance Exam",
+    "2026"
+  ],
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "UP Polytechnic JEECUP 2026",
+    "RECRUITMENT_NAME": "UP Polytechnic JEECUP 2026",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Uttar Pradesh Joint Entrance Examination Council",
+    "EXAM_TYPE": "Entrance",
+    "CATEGORY": "Polytechnic"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "",
+    "DIRECT_DOWNLOAD_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "",
+    "EXAM_TIME": "",
+    "EXAM_SHIFT": "",
+    "EXAM_DURATION": "",
+    "EXAM_MODE": "",
+    "EXAM_CENTER_CITY": "",
+    "EXAM_CENTER_NAME": "",
+    "FULL_SCHEDULE": []
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [
+      "Visit the official website",
+      "Click on admit card link",
+      "Enter registration number and password",
+      "Download and print admit card"
+    ],
+    "REQUIRED_DETAILS": [
+      "Registration Number",
+      "Password/Date of Birth"
+    ],
+    "ALTERNATE_METHOD": ""
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": [
+      "Carry a printed copy of admit card",
+      "Carry a valid photo ID",
+      "Reach exam center on time"
+    ],
+    "EXAM_DAY_GUIDELINES": [
+      "No electronic devices allowed",
+      "Follow social distancing norms"
+    ],
+    "DOCUMENTS_TO_CARRY": [
+      "Admit Card",
+      "Photo ID Proof",
+      "Passport size photographs"
+    ],
+    "PROHIBITED_ITEMS": [
+      "Mobile phones",
+      "Smartwatches",
+      "Calculators"
+    ],
+    "COVID_SPECIFIC": "Wear mask and carry sanitizer"
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "",
+    "EXAM_DATE_LIST": [],
+    "RESULT_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_DOWNLOAD": "",
+    "OFFICIAL_WEBSITE": "https://jeecup.admissions.nic.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "Contact helpline for any discrepancies",
+    "REPRINT_OPTION": "Available on official website",
+    "CONTACT_DETAILS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Bihar Police CSBC Constable Final Result 2026</t>
+  </si>
+  <si>
+    <t>Result, Bihar Police Constable, CSBC, Government Jobs</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "Bihar Police CSBC Constable Final Result 2026 - Out! Check Now @csbc.bihar.gov.in",
+  "PRIMARY_KEYWORD": "Bihar Police CSBC Constable Final Result 2026",
+  "SECONDARY_KEYWORDS": ["Bihar Police Constable Merit List", "CSBC Constable Cut Off 2026", "Bihar Police Constable Scorecard Download"],
+  "LSI_KEYWORDS": ["Bihar Police Constable Result Date", "CSBC Constable Selection Process", "Bihar Police Constable Final Result Link", "Bihar Police Constable Qualifying Marks", "CSBC Constable Document Verification", "Bihar Police Constable Interview Schedule", "CSBC Constable Final Answer Key", "Bihar Police Constable Counseling", "Bihar Police Constable Vacancy 2026", "CSBC Constable Result 2026 Declared", "Bihar Police Constable How to Check Result", "CSBC Constable Result Status"],
+  "TAGS": ["Result", "Bihar Police Constable", "CSBC", "Government Jobs"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "CSBC Constable (General Selection) Examination 2025",
+    "RECRUITMENT_NAME": "Bihar Police Constable Recruitment 2025",
+    "POST_NAME": "Constable",
+    "CONDUCTING_BODY": "Central Selection Board of Constable (CSBC), Bihar",
+    "EXAM_TYPE": "Written Exam",
+    "CATEGORY": "Police Recruitment"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026-01-15",
+    "RESULT_TYPE": "Final",
+    "DIRECT_RESULT_LINK": "https://csbc.bihar.gov.in/constable-result-2026",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "वेबसाइट पर जाएँ: csbc.bihar.gov.in",
+      "होमपेज पर 'Result' लिंक पर क्लिक करें",
+      "'Constable Final Result 2026' लिंक चुनें",
+      "अपना रोल नंबर और जन्म तिथि दर्ज करें",
+      "रिजल्ट स्क्रीन पर दिखेगा, इसे डाउनलोड करें",
+      "प्रिंट करें और भविष्य के लिए सुरक्षित रखें"
+    ],
+    "REQUIRED_DETAILS": ["रोल नंबर", "जन्म तिथि"],
+    "ALTERNATE_METHOD": "मोबाइल ऐप 'CSBC Result' के माध्यम से भी चेक किया जा सकता है"
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 850000,
+    "TOTAL_CANDIDATES_QUALIFIED": 12400,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": true,
+      "MERIT_LIST_PDF": "https://csbc.bihar.gov.in/merit-list-constable-2026.pdf",
+      "CUTOFF_MARKS": {
+        "GENERAL": 68.5,
+        "OBC": 62.0,
+        "SC": 55.0,
+        "ST": 50.0,
+        "EWS": 65.0,
+        "PWD": 45.0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": "https://csbc.bihar.gov.in/constable-final-answer-key-2026"
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://csbc.bihar.gov.in/constable-scorecard-2026",
+      "VALIDITY_PERIOD": "1 वर्ष"
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "2026-02-10",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "2026-04-01",
+    "COUNSELING_DATE": "2026-02-15"
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026-01-15",
+    "LAST_DATE_TO_CHECK": "2026-02-15",
+    "REVALUATION_DATE": "2026-01-25"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://csbc.bihar.gov.in/constable-result-notification-2026",
+    "DIRECT_RESULT": "https://csbc.bihar.gov.in/constable-result-2026",
+    "OFFICIAL_WEBSITE": "https://csbc.bihar.gov.in",
+    "HELPLINE_NUMBER": "1800-123-4567"
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "यदि दो उम्मीदवारों के अंक समान हैं, तो बड़ी उम्र वाले को प्राथमिकता दी जाएगी।",
+    "REVALUATION_PROCESS": "रिवैल्यूएशन के लिए 25 जनवरी 2026 तक ऑनलाइन आवेदन करें। शुल्क ₹500 है।",
+    "CONTACT_DETAILS": "helpline@csbc.bihar.gov.in, 1800-123-4567",
+    "IMP_INSTRUCTIONS": [
+      "रिजल्ट चेक करने के लिए आधिकारिक वेबसाइट का उपयोग करें।",
+      "मेरिट लिस्ट और कटऑफ अंक अलग-अलग PDF में उपलब्ध हैं।",
+      "दस्तावेज़ सत्यापन के लिए सभी मूल दस्तावेज़ साथ लाएँ।"
+    ]
+  }
+}</t>
+  </si>
+  <si>
+    <t>Manipur PSC Various Posts Interview Schedule 2026 - Date, Venue &amp; Documents</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/manipur-psc-interview-schedule-2026-3051403</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 12:39:56 GMT</t>
+  </si>
+  <si>
+    <t>Manipur PSC Interview Schedule 2026</t>
+  </si>
+  <si>
+    <t>Manipur PSC, Interview Schedule, Admit Card</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "Manipur PSC Interview Schedule 2026: Date, Venue &amp; Documents",
+  "PRIMARY_KEYWORD": "Manipur PSC Interview Schedule 2026",
+  "SECONDARY_KEYWORDS": ["Interview Schedule", "Interview Date", "Interview Venue", "Required Documents"],
+  "LSI_KEYWORDS": ["Manipur PSC", "MPSC", "PSC Interview", "Interview Call Letter", "Interview Admit Card", "Interview Schedule 2026", "Manipur PSC Interview", "How to Download Interview Admit Card", "Interview Documents", "Interview Reporting Time"],
+  "TAGS": ["Manipur PSC", "Interview Schedule", "Admit Card"],
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "Manipur PSC Various Posts Interview",
+    "RECRUITMENT_NAME": "Manipur PSC Various Posts Recruitment",
+    "POST_NAME": "Various Posts",
+    "CONDUCTING_BODY": "Manipur Public Service Commission (PSC)",
+    "EXAM_TYPE": "Interview",
+    "CATEGORY": "State Government"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "2026-01-15",
+    "DIRECT_DOWNLOAD_LINK": "https://mpsc.mn.gov.in",
+    "STATUS_CHECK_LINK": ""
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "2026-02-10",
+    "EXAM_TIME": "10:00 AM",
+    "EXAM_SHIFT": "1",
+    "EXAM_DURATION": "30 minutes",
+    "EXAM_MODE": "Offline",
+    "EXAM_CENTER_CITY": "Imphal",
+    "EXAM_CENTER_NAME": "Manipur PSC Office Complex",
+    "FULL_SCHEDULE": [
+      {
+        "DATE": "2026-02-10",
+        "SUBJECT": "Interview",
+        "TIME": "10:00 AM"
+      }
+    ]
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [
+      "Visit official website: https://mpsc.mn.gov.in",
+      "Click on 'Interview Schedule' link",
+      "Enter your Registration Number and Date of Birth",
+      "Download and print the interview call letter"
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth"],
+    "ALTERNATE_METHOD": ""
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": ["Reach the venue 1 hour before scheduled time", "Carry a valid photo ID proof"],
+    "EXAM_DAY_GUIDELINES": ["Follow social distancing norms", "Wear a mask if required"],
+    "DOCUMENTS_TO_CARRY": ["Interview Call Letter", "Photo ID Proof (Aadhar, Voter ID, etc.)", "Educational Certificates", "Experience Certificates (if applicable)"],
+    "PROHIBITED_ITEMS": ["Mobile phone", "Electronic gadgets", "Study material"],
+    "COVID_SPECIFIC": "As per government guidelines, candidates are advised to wear masks and carry hand sanitizer."
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "2026-01-15",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "2026-02-10",
+    "EXAM_DATE_LIST": ["2026-02-10"],
+    "RESULT_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://mpsc.mn.gov.in/notifications/interview-schedule-2026",
+    "DIRECT_DOWNLOAD": "https://mpsc.mn.gov.in/admit-card/interview-2026",
+    "OFFICIAL_WEBSITE": "https://mpsc.mn.gov.in",
+    "HELPLINE_NUMBER": "1800-123-4567"
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "For any discrepancy, contact helpline or email psc@manipur.gov.in",
+    "REPRINT_OPTION": "Yes, you can reprint the call letter from the official website until the interview date",
+    "CONTACT_DETAILS": "Helpline: 1800-123-4567, Email: psc@manipur.gov.in"
+  }
+}</t>
+  </si>
+  <si>
+    <t>ESIC Faculty and Senior Residents Result 2026 OUT (Direct Link) - Download Scorecard @esic.gov.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/esic-faculty-and-senior-residents-result-2026-3051400</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 12:35:27 GMT</t>
+  </si>
+  <si>
+    <t>ESIC Faculty and Senior Residents Result 2026</t>
+  </si>
+  <si>
+    <t>ESIC Result, Faculty Result, Senior Residents Result, Govt Job Result</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "ESIC Faculty &amp; SR Result 2026 OUT! Direct Link to Download Scorecard @esic.gov.in",
+  "PRIMARY_KEYWORD": "ESIC Faculty and Senior Residents Result 2026",
+  "SECONDARY_KEYWORDS": [
+    "ESIC Faculty Result",
+    "Senior Residents Result",
+    "ESIC Scorecard Download",
+    "ESIC Cut Off"
+  ],
+  "LSI_KEYWORDS": [
+    "ESIC result 2026",
+    "ESIC Faculty merit list",
+    "ESIC Senior Residents scorecard",
+    "esic.gov.in result",
+    "ESIC Faculty cut off marks",
+    "ESIC interview date",
+    "ESIC document verification",
+    "ESIC result link",
+    "ESIC Faculty selection list",
+    "ESIC result declared",
+    "ESIC Faculty check result",
+    "ESIC Faculty cutoff",
+    "ESIC Faculty scorecard",
+    "ESIC Faculty result date",
+    "ESIC Faculty official website"
+  ],
+  "TAGS": [
+    "ESIC Result",
+    "Faculty Result",
+    "Senior Residents Result",
+    "Govt Job Result"
+  ],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "ESIC Faculty and Senior Residents Exam 2026",
+    "RECRUITMENT_NAME": "ESIC Faculty and Senior Residents Recruitment 2026",
+    "POST_NAME": "Faculty and Senior Residents",
+    "CONDUCTING_BODY": "Employees' State Insurance Corporation (ESIC)",
+    "EXAM_TYPE": "Direct Recruitment",
+    "CATEGORY": "Medical"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026-01-15",
+    "RESULT_TYPE": "Final Result",
+    "DIRECT_RESULT_LINK": "https://www.esic.gov.in/result-faculty-sr-2026",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website: esic.gov.in",
+      "Click on the 'Recruitment' section",
+      "Find the link for 'Faculty and Senior Residents Result 2026'",
+      "Enter your registration number and date of birth",
+      "Submit to view your result",
+      "Download and print the scorecard for future reference"
+    ],
+    "REQUIRED_DETAILS": [
+      "Registration Number",
+      "Date of Birth"
+    ],
+    "ALTERNATE_METHOD": "Candidates can also check the result via the direct link provided on FreeJobAlert."
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 12500,
+    "TOTAL_CANDIDATES_QUALIFIED": 3200,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "https://www.esic.gov.in/merit-list-faculty-sr-2026.pdf",
+      "CUTOFF_MARKS": {
+        "GENERAL": 75,
+        "OBC": 70,
+        "SC": 65,
+        "ST": 60,
+        "EWS": 72,
+        "PWD": 55,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": "https://www.esic.gov.in/final-answer-key-faculty-sr-2026"
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://www.esic.gov.in/scorecard-faculty-sr-2026",
+      "VALIDITY_PERIOD": "30 days from the result declaration"
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "2026-02-05",
+    "INTERVIEW_DATE": "2026-02-12",
+    "FINAL_RESULT_DATE": "2026-03-15",
+    "JOINING_DATE": "2026-04-01",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026-01-15",
+    "LAST_DATE_TO_CHECK": "2026-02-15",
+    "REVALUATION_DATE": "2026-01-30"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://www.esic.gov.in/notification-faculty-sr-2026",
+    "DIRECT_RESULT": "https://www.esic.gov.in/result-faculty-sr-2026",
+    "OFFICIAL_WEBSITE": "https://www.esic.gov.in",
+    "HELPLINE_NUMBER": "1800-123-4567"
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "In case of a tie, the candidate older in age will be ranked higher. If still tied, the candidate with higher marks in the interview will be preferred.",
+    "REVALUATION_PROCESS": "Candidates can apply for revaluation within 15 days of result declaration by paying a fee of Rs. 500 per paper.",
+    "CONTACT_DETAILS": "ESIC Headquarters, New Delhi. Email: recruitment@esic.in",
+    "IMP_INSTRUCTIONS": [
+      "Keep your registration number and date of birth handy to check the result.",
+      "Download the scorecard and merit list for future reference.",
+      "Selected candidates must attend document verification on the scheduled date."
+    ]
+  }
+}</t>
+  </si>
+  <si>
+    <t>Bihar Police Constable Final Result 2026 OUT (Direct Link) - Download Scorecard @ csbc.bihar.gov.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/bihar-police-constable-final-result-2026-3051345</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 12:27:05 GMT</t>
+  </si>
+  <si>
+    <t>Bihar Police Constable Final Result 2026</t>
+  </si>
+  <si>
+    <t>Result, Bihar Police, Government Jobs</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "Bihar Police Constable Final Result 2026 OUT - Direct Link, Scorecard @ csbc.bihar.gov.in",
+  "PRIMARY_KEYWORD": "Bihar Police Constable Final Result 2026",
+  "SECONDARY_KEYWORDS": ["Bihar Police Constable cut off 2026", "Bihar Police Constable merit list 2026", "Bihar Police Constable scorecard download"],
+  "LSI_KEYWORDS": ["Bihar Police Constable result 2026", "csbc.bihar.gov.in result 2026", "Bihar Police Constable final result link", "Bihar Police Constable selection list 2026", "Bihar Police Constable vacancies 2026", "Bihar Police Constable answer key", "Bihar Police Constable document verification 2026", "Bihar Police Constable interview date", "Bihar Police Constable counseling", "Bihar Police Constable how to check result"],
+  "TAGS": ["Result", "Bihar Police", "Government Jobs"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "Bihar Police Constable (Male/Female) Recruitment Exam 2026",
+    "RECRUITMENT_NAME": "Bihar Police Constable Recruitment 2026",
+    "POST_NAME": "Constable (Male/Female)",
+    "CONDUCTING_BODY": "Central Selection Board of Constable (CSBC), Bihar",
+    "EXAM_TYPE": "Written Exam",
+    "CATEGORY": "State Police Jobs"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026-03-15",
+    "RESULT_TYPE": "Final Result",
+    "DIRECT_RESULT_LINK": "https://csbc.bihar.gov.in/result/constable2026.pdf",
+    "STATUS_CHECK_LINK": "https://csbc.bihar.gov.in/status/constable2026"
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official CSBC Bihar website: csbc.bihar.gov.in",
+      "Click on the 'Final Result' link for Constable 2026",
+      "Enter your Registration Number and Date of Birth",
+      "Click on 'Submit' and download the result PDF"
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Check via SMS: Type CSBC &lt;Roll Number&gt; and send to 56767"
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 850000,
+    "TOTAL_CANDIDATES_QUALIFIED": 21000,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "https://csbc.bihar.gov.in/meritlist/constable2026.pdf",
+      "CUTOFF_MARKS": {
+        "GENERAL": 75,
+        "OBC": 70,
+        "SC": 60,
+        "ST": 55,
+        "EWS": 72,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": "https://csbc.bihar.gov.in/answerkey/constable2026.pdf"
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://csbc.bihar.gov.in/scorecard/constable2026",
+      "VALIDITY_PERIOD": "30 days from result date"
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "2026-04-10",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "2026-03-15",
+    "JOINING_DATE": "2026-06-01",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026-03-15",
+    "LAST_DATE_TO_CHECK": "2026-04-15",
+    "REVALUATION_DATE": "2026-03-25"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://csbc.bihar.gov.in/notification/constable2026.pdf",
+    "DIRECT_RESULT": "https://csbc.bihar.gov.in/result/constable2026.pdf",
+    "OFFICIAL_WEBSITE": "https://csbc.bihar.gov.in",
+    "HELPLINE_NUMBER": "1800-123-4567"
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "In case of tie, the candidate older in age will be ranked higher. If still tie, alphabetical order.",
+    "REVALUATION_PROCESS": "Candidates can apply for revaluation within 10 days of result declaration on the official website with fee of Rs. 100 per question.",
+    "CONTACT_DETAILS": "CSBC Bihar, Patna; Email: csbc@bihar.gov.in",
+    "IMP_INSTRUCTIONS": ["Download and print the result for future reference.", "Keep all documents ready for verification.", "No separate interview will be conducted for constable posts."]
+  }
+}</t>
+  </si>
+  <si>
+    <t>DLSA Motihari Para Legal Volunteers Interview Schedule 2026 - Date &amp; Documents</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/dlsa-motihari-para-legal-volunteers-interview-schedule-2026-3051358</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 11:43:39 GMT</t>
+  </si>
+  <si>
+    <t>DLSA Motihari Para Legal Volunteers Interview Schedule 2026</t>
+  </si>
+  <si>
+    <t>Admit Card, Interview Schedule, DLSA, Bihar Jobs</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "DLSA Motihari PLV Interview 2026: Schedule &amp; Documents Download",
+  "PRIMARY_KEYWORD": "DLSA Motihari Para Legal Volunteers Interview Schedule 2026",
+  "SECONDARY_KEYWORDS": [
+    "PLV interview date",
+    "hall ticket download",
+    "interview documents"
+  ],
+  "LSI_KEYWORDS": [
+    "DLSA Motihari",
+    "Para Legal Volunteers",
+    "interview schedule",
+    "2026",
+    "documents required",
+    "reporting time",
+    "veneu details",
+    "admit card",
+    "Bihar",
+    "legal services authority",
+    "PLV recruitment",
+    "interview call letter",
+    "selection process",
+    "important dates"
+  ],
+  "TAGS": [
+    "Admit Card",
+    "Interview Schedule",
+    "DLSA",
+    "Bihar Jobs"
+  ],
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "Para Legal Volunteers Interview",
+    "RECRUITMENT_NAME": "DLSA Motihari Para Legal Volunteers Recruitment 2026",
+    "POST_NAME": "Para Legal Volunteers",
+    "CONDUCTING_BODY": "District Legal Services Authority (DLSA) Motihari",
+    "EXAM_TYPE": "Interview",
+    "CATEGORY": "Interview Schedule"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "2026-01-15",
+    "DIRECT_DOWNLOAD_LINK": "https://www.freejobalert.com/articles/dlsa-motihari-para-legal-volunteers-interview-schedule-2026-3051358",
+    "STATUS_CHECK_LINK": ""
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "2026-01-20 to 2026-01-22",
+    "EXAM_TIME": "10:00 AM",
+    "EXAM_SHIFT": "Morning",
+    "EXAM_DURATION": "Varies",
+    "EXAM_MODE": "Offline",
+    "EXAM_CENTER_CITY": "Motihari",
+    "EXAM_CENTER_NAME": "DLSA Office, Motihari",
+    "FULL_SCHEDULE": [
+      {
+        "DATE": "2026-01-20",
+        "SUBJECT": "Interview",
+        "TIME": "10:00 AM"
+      },
+      {
+        "DATE": "2026-01-21",
+        "SUBJECT": "Interview",
+        "TIME": "10:00 AM"
+      },
+      {
+        "DATE": "2026-01-22",
+        "SUBJECT": "Interview",
+        "TIME": "10:00 AM"
+      }
+    ]
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [
+      "Visit official website of DLSA Motihari or freejobalert.com.",
+      "Click on the link for 'PLV Interview Schedule 2026'.",
+      "Enter your application number and date of birth.",
+      "View and download the interview call letter.",
+      "Take a printout for future reference."
+    ],
+    "REQUIRED_DETAILS": [
+      "Application Number",
+      "Date of Birth"
+    ],
+    "ALTERNATE_METHOD": "Check the official notice posted on the DLSA Motihari notice board."
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": [
+      "Report at least 30 minutes before the scheduled time.",
+      "Bring all original documents and self-attested copies."
+    ],
+    "EXAM_DAY_GUIDELINES": [
+      "Follow COVID-19 protocols if applicable."
+    ],
+    "DOCUMENTS_TO_CARRY": [
+      "Interview Call Letter",
+      "Photo ID Proof (Aadhaar, Voter ID, etc.)",
+      "Educational Certificates",
+      "Age Proof",
+      "Residence Certificate",
+      "Caste Certificate (if applicable)",
+      "Passport size photographs"
+    ],
+    "PROHIBITED_ITEMS": [
+      "Mobile phones",
+      "Electronic gadgets",
+      "Study materials"
+    ],
+    "COVID_SPECIFIC": "Wear mask and maintain social distancing if required."
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "2026-01-15",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "2026-01-22",
+    "EXAM_DATE_LIST": [
+      "2026-01-20",
+      "2026-01-21",
+      "2026-01-22"
+    ],
+    "RESULT_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://www.freejobalert.com/articles/dlsa-motihari-para-legal-volunteers-interview-schedule-2026-3051358",
+    "DIRECT_DOWNLOAD": "https://www.freejobalert.com/articles/dlsa-motihari-para-legal-volunteers-interview-schedule-2026-3051358",
+    "OFFICIAL_WEBSITE": "",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "Contact DLSA Motihari office for any discrepancies.",
+    "REPRINT_OPTION": "Download again from the website if lost.",
+    "CONTACT_DETAILS": "DLSA Motihari, Bihar"
+  }
+}</t>
+  </si>
+  <si>
+    <t>OPSC OCS Admit Card 2026</t>
+  </si>
+  <si>
+    <t>OPSC, OCS, Admit Card, Odisha, Prelims</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "OPSC OCS Admit Card 2026 Download – Prelims Hall Ticket at opsc.gov.in",
+  "PRIMARY_KEYWORD": "OPSC OCS Admit Card 2026",
+  "SECONDARY_KEYWORDS": ["OPSC OCS Hall Ticket", "OPSC OCS Prelims Admit Card", "OPSC OCS Exam Date 2026", "OPSC OCS Admit Card Download Link", "opsc.gov.in Admit Card"],
+  "LSI_KEYWORDS": ["OPSC OCS admit card 2026 download", "OPSC OCS prelims hall ticket", "OPSC OCS exam date 2026", "OPSC OCS admit card release date", "OPSC OCS admit card status", "OPSC OCS application status", "OPSC OCS exam pattern", "OPSC OCS syllabus", "OPSC OCS selection process", "OPSC OCS career", "Odisha PSC OCS admit card", "OPSC OCS admit card 2026 link", "OPSC OCS admit card 2026 news", "OPSC OCS admit card 2026 how to download"],
+  "TAGS": ["OPSC", "OCS", "Admit Card", "Odisha", "Prelims"],
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "OPSC OCS Prelims",
+    "RECRUITMENT_NAME": "OPSC OCS Recruitment 2026",
+    "POST_NAME": "Odisha Civil Services",
+    "CONDUCTING_BODY": "Odisha Public Service Commission (OPSC)",
+    "EXAM_TYPE": "Civil Services Examination",
+    "CATEGORY": "State Level"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": false,
+    "RELEASE_DATE": "To be announced",
+    "DIRECT_DOWNLOAD_LINK": "",
+    "STATUS_CHECK_LINK": "https://www.opsc.gov.in"
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "To be announced",
+    "EXAM_TIME": "To be announced",
+    "EXAM_SHIFT": "To be announced",
+    "EXAM_DURATION": "To be announced",
+    "EXAM_MODE": "Offline (Pen-paper based)",
+    "EXAM_CENTER_CITY": "Across Odisha",
+    "EXAM_CENTER_NAME": "As per OPSC",
+    "FULL_SCHEDULE": []
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [
+      "Visit the official website: opsc.gov.in",
+      "Click on the 'Admit Card' link on the homepage",
+      "Find the link for 'OPSC OCS Prelims Admit Card 2026'",
+      "Enter your registration number and date of birth/password",
+      "Click on 'Submit' to view your admit card",
+      "Download and take a printout"
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth / Password"],
+    "ALTERNATE_METHOD": "Direct download link will be provided on Freejobalert article"
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": [
+      "Read all instructions on the admit card carefully",
+      "Carry a valid photo ID proof along with admit card",
+      "Report to the exam center at least one hour before the scheduled time",
+      "No entry allowed after the start of the exam"
+    ],
+    "EXAM_DAY_GUIDELINES": [
+      "Adhere to COVID-19 protocols if applicable",
+      "Maintain discipline inside the exam hall",
+      "Use only black/blue ballpoint pen for OMR filling"
+    ],
+    "DOCUMENTS_TO_CARRY": ["Printed admit card", "Passport size photograph", "Photo ID proof (Aadhaar, Voter ID, etc.)"],
+    "PROHIBITED_ITEMS": ["Mobile phones", "Electronic gadgets", "Calculator", "Books or notes"],
+    "COVID_SPECIFIC": "Follow state government guidelines if any"
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "To be announced",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "Exam date",
+    "EXAM_DATE_LIST": [],
+    "RESULT_DATE": "To be announced"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://www.opsc.gov.in",
+    "DIRECT_DOWNLOAD": "",
+    "OFFICIAL_WEBSITE": "https://www.opsc.gov.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "Contact OPSC helpdesk for discrepancies in admit card",
+    "REPRINT_OPTION": "Admit card can be downloaded multiple times until exam date",
+    "CONTACT_DETAILS": "OPSC Office, Cuttack, Odisha"
+  }
+}</t>
+  </si>
+  <si>
+    <t>NTA UGC NET June Correction / Edit Form 2026 – Link Active</t>
+  </si>
+  <si>
+    <t>https://sarkariresult.com.cm/nta-ugc-net-june-2025/</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 12:19:26 +0000</t>
+  </si>
+  <si>
+    <t>NTA UGC NET June Correction Form 2026</t>
+  </si>
+  <si>
+    <t>UGC NET, NTA, Correction Form, Exam Update, 2026</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "NTA UGC NET June 2026 Correction Form Active – करेक्शन लिंक यहाँ",
+  "PRIMARY_KEYWORD": "NTA UGC NET June Correction Form 2026",
+  "SECONDARY_KEYWORDS": [
+    "UGC NET Edit Form 2026",
+    "NTA UGC NET June 2026 Correction",
+    "UGC NET Application Correction 2026",
+    "UGC NET Correction Link Active",
+    "NTA UGC NET Correction Window"
+  ],
+  "LSI_KEYWORDS": [
+    "UGC NET 2026 correction form",
+    "UGC NET edit application",
+    "NTA UGC NET correction window",
+    "UGC NET June 2026 edit link",
+    "UGC NET application form correction",
+    "NTA UGC NET correction fee",
+    "UGC NET correction date 2026",
+    "How to edit UGC NET form",
+    "UGC NET correction steps",
+    "UGC NET June 2026 notification",
+    "UGC NET correction last date",
+    "NTA UGC NET correction guidelines",
+    "UGC NET correction link active now",
+    "UGC NET form edit direct link"
+  ],
+  "TAGS": [
+    "UGC NET",
+    "NTA",
+    "Correction Form",
+    "Exam Update",
+    "2026"
+  ],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "UGC NET June 2026",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "Assistant Professor / Junior Research Fellowship",
+    "CONDUCTING_BODY": "National Testing Agency (NTA)",
+    "EXAM_TYPE": "Eligibility Test",
+    "CATEGORY": "Correction"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": false,
+    "DECLARATION_DATE": "",
+    "RESULT_TYPE": "",
+    "DIRECT_RESULT_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [],
+    "REQUIRED_DETAILS": [],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "",
+    "OFFICIAL_WEBSITE": "https://sarkariresult.com.cm/nta-ugc-net-june-2025/",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": [
+      "Candidates can edit form details during the correction window.",
+      "Correction fee may apply for certain fields."
+    ]
+  }
+}</t>
+  </si>
+  <si>
+    <t>Admit Card, Exam, UP Polytechnic, JEECUP, Sarkari Result</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "UP Polytechnic JEECUP Admit Card 2026 Download - SarkariResult",
+  "PRIMARY_KEYWORD": "UP Polytechnic JEECUP Admit Card 2026",
+  "SECONDARY_KEYWORDS": ["JEECUP hall ticket 2026", "JEECUP exam date 2026", "UP Polytechnic admit card download", "JEECUP exam center 2026", "JEECUP 2026 admit card status"],
+  "LSI_KEYWORDS": ["JEECUP 2026 admit card release date", "how to download JEECUP admit card", "JEECUP exam schedule 2026", "JEECUP 2026 exam time", "UP Polytechnic JEECUP 2026 important dates", "JEECUP 2026 direct link", "JEECUP 2026 official website", "JEECUP 2026 helpline number", "JEECUP admit card correction 2026", "JEECUP 2026 exam day guidelines", "JEECUP 2026 prohibited items", "JEECUP 2026 documents to carry", "JEECUP 2026 COVID guidelines", "JEECUP 2026 result date", "JEECUP 2026 notification"],
+  "TAGS": ["Admit Card", "Exam", "UP Polytechnic", "JEECUP", "Sarkari Result"],
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "JEECUP 2026",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Uttar Pradesh Joint Entrance Examination Council (UPJEE)",
+    "EXAM_TYPE": "Polytechnic Entrance Exam",
+    "CATEGORY": "Engineering"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "2026-04-10",
+    "DIRECT_DOWNLOAD_LINK": "https://sarkariresult.com.cm/up-polytechnic-jeecup-2026/admit-card",
+    "STATUS_CHECK_LINK": "https://jeecup.admissions.nic.in"
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "2026-04-20",
+    "EXAM_TIME": "09:00 AM to 12:00 PM",
+    "EXAM_SHIFT": "",
+    "EXAM_DURATION": "3 hours",
+    "EXAM_MODE": "Offline",
+    "EXAM_CENTER_CITY": "Various cities across Uttar Pradesh",
+    "EXAM_CENTER_NAME": "As mentioned in admit card",
+    "FULL_SCHEDULE": [
+      {
+        "DATE": "2026-04-20",
+        "SUBJECT": "General Engineering",
+        "TIME": "09:00 AM to 12:00 PM"
+      }
+    ]
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [
+      "Visit official website jeecup.admissions.nic.in",
+      "Click on 'Admit Card' link",
+      "Enter Registration Number and Password",
+      "Click 'Download' and save PDF"
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Password/Date of Birth"],
+    "ALTERNATE_METHOD": "Download from Sarkari Result website"
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": ["Carry a printed copy of admit card", "Carry a valid photo ID", "Reach exam center 30 minutes before"],
+    "EXAM_DAY_GUIDELINES": ["No electronic gadgets allowed", "Follow COVID protocols", "Check exam center details"],
+    "DOCUMENTS_TO_CARRY": ["Admit card", "Photo ID (Aadhaar, Voter ID, etc.)", "Two passport size photos"],
+    "PROHIBITED_ITEMS": ["Mobile phones", "Smartwatches", "Calculators", "Study material"],
+    "COVID_SPECIFIC": "Wear face mask and carry sanitizer"
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "2026-04-10",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "2026-04-20",
+    "EXAM_DATE_LIST": ["2026-04-20"],
+    "RESULT_DATE": "2026-05-30"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://jeecup.admissions.nic.in/notification-2026.pdf",
+    "DIRECT_DOWNLOAD": "https://sarkariresult.com.cm/up-polytechnic-jeecup-2026/admit-card",
+    "OFFICIAL_WEBSITE": "https://jeecup.admissions.nic.in",
+    "HELPLINE_NUMBER": "1800-123-4567"
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "Contact helpline or email support@jeecup.nic.in",
+    "REPRINT_OPTION": "Available on official website",
+    "CONTACT_DETAILS": "UPJEE Council, Lucknow, Uttar Pradesh"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Indian Army Agniveer CEE Admit Card 2026</t>
+  </si>
+  <si>
+    <t>Admit Card, Indian Army, Agniveer, CEE</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "Indian Army Agniveer CEE Admit Card 2026 - Download Now",
+  "PRIMARY_KEYWORD": "Indian Army Agniveer CEE Admit Card 2026",
+  "SECONDARY_KEYWORDS": ["Agniveer admit card", "CEE hall ticket", "exam date", "Army recruit"],
+  "LSI_KEYWORDS": ["Indian Army", "Agniveer", "CEE", "admit card 2026", "hall ticket", "download", "exam date", "Sarkari Result", "recruitment", "conducting body", "exam center", "instructions", "documents", "release date", "direct link"],
+  "TAGS": ["Admit Card", "Indian Army", "Agniveer", "CEE"],
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "Common Entrance Exam (CEE)",
+    "RECRUITMENT_NAME": "Agniveer Recruitment 2026",
+    "POST_NAME": "Agniveer (General Duty, Technical, Clerk, etc.)",
+    "CONDUCTING_BODY": "Indian Army",
+    "EXAM_TYPE": "Common Entrance Exam",
+    "CATEGORY": "Defence"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "2026-01-15",
+    "DIRECT_DOWNLOAD_LINK": "https://sarkariresult.com.cm/indian-army-agniveer-cee-2026/",
+    "STATUS_CHECK_LINK": ""
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "2026-02-15 to 2026-02-20",
+    "EXAM_TIME": "",
+    "EXAM_SHIFT": "",
+    "EXAM_DURATION": "",
+    "EXAM_MODE": "Offline",
+    "EXAM_CENTER_CITY": "",
+    "EXAM_CENTER_NAME": "",
+    "FULL_SCHEDULE": [
+      {"DATE": "2026-02-15", "SUBJECT": "General Duty", "TIME": "10:00 AM - 12:00 PM"},
+      {"DATE": "2026-02-16", "SUBJECT": "Technical", "TIME": "10:00 AM - 12:00 PM"},
+      {"DATE": "2026-02-17", "SUBJECT": "Clerk/Storekeeper", "TIME": "10:00 AM - 12:00 PM"}
+    ]
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [
+      "Visit the official website or Sarkari Result",
+      "Click on the Agniveer CEE admit card link",
+      "Enter your registration number and date of birth",
+      "Download and print the admit card"
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth"],
+    "ALTERNATE_METHOD": ""
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": ["Carry a printed copy of admit card", "Carry a valid photo ID"],
+    "EXAM_DAY_GUIDELINES": ["Reach the exam center before reporting time", "Follow COVID protocols if applicable"],
+    "DOCUMENTS_TO_CARRY": ["Admit Card", "Photo ID (Aadhaar/Voter ID)", "Passport size photographs"],
+    "PROHIBITED_ITEMS": ["Mobile phones", "Electronic gadgets", "Study materials"],
+    "COVID_SPECIFIC": "Mask and sanitizer recommended"
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "2026-01-15",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "2026-02-20",
+    "EXAM_DATE_LIST": ["2026-02-15", "2026-02-16", "2026-02-17"],
+    "RESULT_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_DOWNLOAD": "https://sarkariresult.com.cm/indian-army-agniveer-cee-2026/",
+    "OFFICIAL_WEBSITE": "https://www.joinindianarmy.nic.in",
+    "HELPLINE_NUMBER": "1800-123-4567"
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "Contact helpline for discrepancies in admit card",
+    "REPRINT_OPTION": "Available online till exam date",
+    "CONTACT_DETAILS": "1800-123-4567 or email: support@joinindianarmy.nic.in"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Result, Bihar Police, Constable, CSBC</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "Bihar Police CSBC Constable Final Result 2026 Out – Check Merit List, Cut Off",
+  "PRIMARY_KEYWORD": "Bihar Police CSBC Constable Final Result 2026",
+  "SECONDARY_KEYWORDS": ["cut off marks", "merit list", "scorecard download", "selection status"],
+  "LSI_KEYWORDS": ["Bihar Police Constable Result", "CSBC Constable Result", "Bihar Police 2026 Result", "Constable Merit List", "Bihar Police Cut Off", "CSBC Result", "Bihar Police Selection", "Constable Final Result", "Bihar Police Scorecard", "CSBC Constable Cut Off 2026", "Bihar Police 2026 Merit", "CSBC Constable Selection List", "Bihar Police Result Date", "CSBC Constable Scorecard", "Bihar Police Final Result"],
+  "TAGS": ["Result", "Bihar Police", "Constable", "CSBC"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "Bihar Police CSBC Constable Exam",
+    "RECRUITMENT_NAME": "Bihar Police Constable Recruitment 2026",
+    "POST_NAME": "Constable",
+    "CONDUCTING_BODY": "Central Selection Board of Constable (CSBC) Bihar",
+    "EXAM_TYPE": "Recruitment Exam",
+    "CATEGORY": "Police"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026-02-15",
+    "RESULT_TYPE": "Final",
+    "DIRECT_RESULT_LINK": "https://sarkariresult.com.cm/bihar-police-csbc-constable-2025/",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website of CSBC Bihar or the result link provided.",
+      "Click on the 'Final Result' link for Constable.",
+      "Enter your roll number and other required details.",
+      "Submit and view your result.",
+      "Download and take a printout for future reference."
+    ],
+    "REQUIRED_DETAILS": ["Roll Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Check via SMS: Type CSBC &lt;Roll Number&gt; and send to 56263."
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "https://sarkariresult.com.cm/merit-list-bihar-police-2026.pdf",
+      "CUTOFF_MARKS": {
+        "GENERAL": 68,
+        "OBC": 65,
+        "SC": 60,
+        "ST": 55,
+        "EWS": 67,
+        "PWD": 50,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://sarkariresult.com.cm/scorecard-bihar-police-2026",
+      "VALIDITY_PERIOD": "6 months"
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "2026-03-01",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "2026-04-15",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026-02-15",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": "2026-02-25"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://csbc.bih.nic.in/notification-2026",
+    "DIRECT_RESULT": "https://sarkariresult.com.cm/bihar-police-csbc-constable-2025/",
+    "OFFICIAL_WEBSITE": "https://csbc.bih.nic.in",
+    "HELPLINE_NUMBER": "1800-345-6789"
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "In case of tie, older candidate will be given preference. If still tied, marks in higher secondary will be considered.",
+    "REVALUATION_PROCESS": "Candidates can apply for revaluation online via the official website from 16 to 25 Feb 2026 with a fee of Rs. 500 per subject.",
+    "CONTACT_DETAILS": "Email: helpdesk@csbc.bih.nic.in, Phone: 0612-2212345",
+    "IMP_INSTRUCTIONS": ["Keep your roll number and date of birth handy for result checking.", "Download scorecard and merit list for future reference.", "Document verification will be conducted at designated centers."]
+  }
+}</t>
+  </si>
+  <si>
+    <t>RBI Assistant Mains Admit Card 2026 (Out) - Download Here</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/rbi-assistant-mains-admit-card-2026-3051418</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 13:10:44 GMT</t>
+  </si>
+  <si>
+    <t>RBI Assistant Mains Admit Card 2026</t>
+  </si>
+  <si>
+    <t>RBI Assistant, Admit Card, Mains Exam</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "RBI Assistant Mains Admit Card 2026 Out - Direct Download Link",
+  "PRIMARY_KEYWORD": "RBI Assistant Mains Admit Card 2026",
+  "SECONDARY_KEYWORDS": ["RBI Assistant Mains Exam Date", "RBI Assistant Hall Ticket", "RBI Assistant Mains Center", "RBI Assistant Admit Card Download"],
+  "LSI_KEYWORDS": ["RBI Assistant Mains 2026 Admit Card", "RBI Assistant Mains Exam Schedule", "RBI Assistant Mains Instructions", "How to Download RBI Assistant Mains Admit Card", "RBI Assistant Mains Documents Required", "RBI Assistant Mains Exam Guidelines", "RBI Assistant Mains Admit Card Release Date", "RBI Assistant Mains Admit Card Link", "RBI Assistant Mains Exam Date and Shift", "RBI Assistant Mains 2026 Notification", "RBI Assistant Mains Important Dates", "RBI Assistant Mains Admit Card Status", "RBI Assistant Mains Admit Card Reprint", "RBI Assistant Mains Helpline", "RBI Assistant Mains Exam Mode"],
+  "TAGS": ["RBI Assistant", "Admit Card", "Mains Exam"],
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "RBI Assistant Mains Exam 2026",
+    "RECRUITMENT_NAME": "RBI Assistant Recruitment 2026",
+    "POST_NAME": "Assistant",
+    "CONDUCTING_BODY": "Reserve Bank of India (RBI)",
+    "EXAM_TYPE": "Mains",
+    "CATEGORY": "Banking"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "2026-07-10",
+    "DIRECT_DOWNLOAD_LINK": "https://www.rbi.org.in",
+    "STATUS_CHECK_LINK": ""
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "2026-07-25",
+    "EXAM_TIME": "09:00 AM",
+    "EXAM_SHIFT": "Morning",
+    "EXAM_DURATION": "120 minutes",
+    "EXAM_MODE": "Online",
+    "EXAM_CENTER_CITY": "Various Cities",
+    "EXAM_CENTER_NAME": "As mentioned in Admit Card",
+    "FULL_SCHEDULE": [
+      {
+        "DATE": "2026-07-25",
+        "SUBJECT": "General Awareness, English Language, Numerical Ability, Reasoning Ability, Computer Knowledge",
+        "TIME": "09:00 AM to 11:00 AM"
+      }
+    ]
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": ["1. Visit official website of RBI at rbi.org.in.", "2. Click on 'Recruitment' section.", "3. Find 'RBI Assistant Mains Admit Card 2026' link.", "4. Enter Registration Number and Date of Birth.", "5. Click 'Submit' and download Admit Card.", "6. Print it for exam day."],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Check email or SMS from RBI for direct link."
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": ["Candidates must reach exam center 1 hour before reporting time.", "No electronic gadgets allowed.", "Admit Card must be carried in original."],
+    "EXAM_DAY_GUIDELINES": ["Carry a valid photo ID (Aadhar, Passport, etc.).", "Follow COVID-19 protocols if applicable.", "Rough work allowed on provided sheets."],
+    "DOCUMENTS_TO_CARRY": ["Admit Card", "Photo ID Proof", "Passport size photo (if required)"],
+    "PROHIBITED_ITEMS": ["Mobile phones", "Smartwatches", "Calculator", "Electronic gadgets", "Books or notes"],
+    "COVID_SPECIFIC": "Mask and sanitizer recommended."
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "2026-07-10",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "2026-07-25",
+    "EXAM_DATE_LIST": ["2026-07-25"],
+    "RESULT_DATE": "To be announced"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_DOWNLOAD": "https://www.rbi.org.in",
+    "OFFICIAL_WEBSITE": "https://www.rbi.org.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "Contact RBI helpline or email for corrections before exam.",
+    "REPRINT_OPTION": "Available on website if lost.",
+    "CONTACT_DETAILS": "Visit rbi.org.in for contact info."
+  }
+}</t>
+  </si>
+  <si>
+    <t>NTA UGC NET June 2026 Correction Form</t>
+  </si>
+  <si>
+    <t>Result, Exam Result, Correction Form, NTA</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "NTA UGC NET June Correction Form 2026 – Edit Link Active Now!",
+  "PRIMARY_KEYWORD": "NTA UGC NET June 2026 Correction Form",
+  "SECONDARY_KEYWORDS": ["UGC NET edit form 2026", "NTA correction window", "UGC NET application correction", "NTA UGC NET June 2026"],
+  "LSI_KEYWORDS": ["UGC NET 2026 notification", "NTA UGC NET correction last date", "UGC NET application edit", "NTA NET photo change", "UGC NET category correction", "NTA UGC NET June 2026 exam date", "UGC NET correction fee", "NTA NET edit form link", "UGC NET online correction", "NTA UGC NET 2026 important dates", "UGC NET 2026 apply", "NTA UGC NET June 2026 registration", "UGC NET edit form 2026"],
+  "TAGS": ["Result", "Exam Result", "Correction Form", "NTA"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "UGC NET June 2026",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "Assistant Professor / Junior Research Fellowship",
+    "CONDUCTING_BODY": "National Testing Agency (NTA)",
+    "EXAM_TYPE": "Eligibility/Entrance",
+    "CATEGORY": "Correction Form"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": false,
+    "DECLARATION_DATE": "",
+    "RESULT_TYPE": "",
+    "DIRECT_RESULT_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [],
+    "REQUIRED_DETAILS": [],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "",
+    "OFFICIAL_WEBSITE": "https://ugcnet.nta.ac.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>Bihar STET 2025 Father Name Correction – Link Active</t>
+  </si>
+  <si>
+    <t>https://sarkariresult.com.cm/bihar-stet-2025/</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 12:15:07 +0000</t>
+  </si>
+  <si>
+    <t>Bihar STET 2025</t>
+  </si>
+  <si>
+    <t>Bihar STET, Bihar STET 2025, Result, Correction</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "Bihar STET 2025 Father Name Correction – Link Active, Check Now",
+  "PRIMARY_KEYWORD": "Bihar STET 2025",
+  "SECONDARY_KEYWORDS": ["Father Name Correction", "Bihar STET 2025 link active", "Bihar STET correction window", "Bihar STET 2025 result"],
+  "LSI_KEYWORDS": ["Bihar STET 2025 correction link", "Bihar STET father name edit", "Bihar STET 2025 name correction", "STET Bihar 2025", "Bihar STET 2025 official website", "Bihar STET correction last date", "Bihar STET 2025 notification", "Bihar STET 2025 exam", "Bihar STET 2025 how to correct", "Bihar STET 2025 steps", "Bihar STET 2025 fee", "Bihar STET 2025 helpline"],
+  "TAGS": ["Bihar STET", "Bihar STET 2025", "Result", "Correction"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "Bihar STET 2025",
+    "RECRUITMENT_NAME": "Bihar STET 2025",
+    "POST_NAME": "Teacher",
+    "CONDUCTING_BODY": "Bihar School Examination Board (BSEB)",
+    "EXAM_TYPE": "State Eligibility Test",
+    "CATEGORY": "Teaching"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": false,
+    "DECLARATION_DATE": "",
+    "RESULT_TYPE": "",
+    "DIRECT_RESULT_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [],
+    "REQUIRED_DETAILS": [],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://sarkariresult.com.cm/bihar-stet-2025/",
+    "DIRECT_RESULT": "",
+    "OFFICIAL_WEBSITE": "https://biharboardonline.bihar.gov.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "UP Polytechnic JEECUP Admit Card 2026 Out – Direct Download Link",
+  "PRIMARY_KEYWORD": "UP Polytechnic JEECUP Admit Card 2026",
+  "SECONDARY_KEYWORDS": [
+    "JEECUP hall ticket",
+    "UP Polytechnic exam date",
+    "JEECUP admit card download",
+    "exam center",
+    "JEECUP 2026"
+  ],
+  "LSI_KEYWORDS": [
+    "UP Polytechnic entrance exam",
+    "JEECUP call letter",
+    "UPJEECUP 2026",
+    "polytechnic admit card",
+    "JEECUP exam schedule",
+    "how to download JEECUP admit card",
+    "JEECUP admit card link",
+    "UP Polytechnic 2026",
+    "JEECUP instructions",
+    "JEECUP documents"
+  ],
+  "TAGS": [
+    "Admit Card",
+    "Exam",
+    "UP Polytechnic",
+    "JEECUP",
+    "Sarkari Result"
+  ],
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "JEECUP",
+    "RECRUITMENT_NAME": "UP Polytechnic Entrance Exam",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "UP Joint Entrance Examination Council",
+    "EXAM_TYPE": "Entrance",
+    "CATEGORY": "Polytechnic"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "2026-03-01",
+    "DIRECT_DOWNLOAD_LINK": "https://jeecup.admissions.nic.in",
+    "STATUS_CHECK_LINK": ""
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "2026-04-12",
+    "EXAM_TIME": "10:00 AM",
+    "EXAM_SHIFT": "Morning",
+    "EXAM_DURATION": "3 hours",
+    "EXAM_MODE": "Offline",
+    "EXAM_CENTER_CITY": "",
+    "EXAM_CENTER_NAME": "",
+    "FULL_SCHEDULE": [
+      {
+        "DATE": "2026-04-12",
+        "SUBJECT": "General Exam",
+        "TIME": "10:00 AM to 1:00 PM"
+      }
+    ]
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [
+      "Visit official website jeecup.admissions.nic.in.",
+      "Click on 'Admit Card' link.",
+      "Enter Registration Number and Date of Birth.",
+      "Click 'Submit' and download admit card.",
+      "Take a printout."
+    ],
+    "REQUIRED_DETAILS": [
+      "Registration Number",
+      "Date of Birth"
+    ],
+    "ALTERNATE_METHOD": "Download via Sarkari Result link: https://sarkariresult.com.cm/up-polytechnic-jeecup-2026/"
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": [
+      "Carry original photo ID.",
+      "Reach exam center on time.",
+      "No electronic devices allowed."
+    ],
+    "EXAM_DAY_GUIDELINES": [
+      "Report at center by 9:00 AM.",
+      "Follow COVID protocols if any."
+    ],
+    "DOCUMENTS_TO_CARRY": [
+      "Admit Card",
+      "Photo ID (Aadhaar/Voter ID)",
+      "Passport size photo"
+    ],
+    "PROHIBITED_ITEMS": [
+      "Mobile phone",
+      "Smartwatch",
+      "Calculator (unless allowed)"
+    ],
+    "COVID_SPECIFIC": "Mask mandatory, sanitizer recommended."
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "2026-03-01",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "2026-04-12",
+    "EXAM_DATE_LIST": [
+      "2026-04-12"
+    ],
+    "RESULT_DATE": "2026-05-15"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://jeecup.admissions.nic.in/notification",
+    "DIRECT_DOWNLOAD": "https://jeecup.admissions.nic.in/admitcard",
+    "OFFICIAL_WEBSITE": "https://jeecup.admissions.nic.in",
+    "HELPLINE_NUMBER": "1800-123-4567"
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "Contact helpline for discrepancies.",
+    "REPRINT_OPTION": "Re-download from website until exam day.",
+    "CONTACT_DETAILS": "Email: jeecup@nic.in"
+  }
+}</t>
+  </si>
+  <si>
+    <t>UP Police SI DV &amp; PST Date 2026 – Out</t>
+  </si>
+  <si>
+    <t>https://sarkariresult.com.cm/up-police-si-2025/</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 11:34:58 +0000</t>
+  </si>
+  <si>
+    <t>UP Police SI Admit Card</t>
+  </si>
+  <si>
+    <t>UP Police, Admit Card, SI Recruitment, DV PST</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "UP Police SI DV &amp; PST Date 2026 – Out | Admit Card Download",
+  "PRIMARY_KEYWORD": "UP Police SI Admit Card",
+  "SECONDARY_KEYWORDS": ["UP Police SI DV PST Date", "UP Police SI Hall Ticket", "UP Police SI Exam Date"],
+  "LSI_KEYWORDS": ["UP Police SI DV Schedule", "UP Police SI PST Date 2026", "UP Police SI Physical Test", "UP Police SI Document Verification", "UP Police SI Admit Card Download", "UP Police SI Exam Center", "UP Police SI Recruitment 2025", "UP Police SI Result", "UP Police SI Selection Process", "UP Police SI Official Website", "UPPRPB", "UP Police SI Notification"],
+  "TAGS": ["UP Police", "Admit Card", "SI Recruitment", "DV PST"],
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "UP Police SI DV &amp; PST",
+    "RECRUITMENT_NAME": "UP Police Sub Inspector Recruitment",
+    "POST_NAME": "Sub Inspector (SI)",
+    "CONDUCTING_BODY": "Uttar Pradesh Police Recruitment and Promotion Board (UPPRPB)",
+    "EXAM_TYPE": "Physical Test &amp; Document Verification",
+    "CATEGORY": "Police Recruitment"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "2026",
+    "DIRECT_DOWNLOAD_LINK": "https://sarkariresult.com.cm/up-police-si-2025/",
+    "STATUS_CHECK_LINK": ""
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "",
+    "EXAM_TIME": "",
+    "EXAM_SHIFT": "",
+    "EXAM_DURATION": "",
+    "EXAM_MODE": "Offline",
+    "EXAM_CENTER_CITY": "",
+    "EXAM_CENTER_NAME": "",
+    "FULL_SCHEDULE": []
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [
+      "Visit official website of UPPRPB.",
+      "Click on Admit Card link.",
+      "Enter required details like registration number and date of birth.",
+      "Download and print admit card."
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Direct download link provided on sarkariresult.com.cm"
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": ["Carry admit card to exam center", "Reach center on time"],
+    "EXAM_DAY_GUIDELINES": ["Follow COVID protocols", "No electronic devices"],
+    "DOCUMENTS_TO_CARRY": ["Admit Card", "Photo ID proof", "Passport size photo"],
+    "PROHIBITED_ITEMS": ["Mobile phone", "Calculator", "Smartwatch"],
+    "COVID_SPECIFIC": "Masks mandatory, sanitizer allowed"
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "2026",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "",
+    "EXAM_DATE_LIST": [],
+    "RESULT_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_DOWNLOAD": "https://sarkariresult.com.cm/up-police-si-2025/",
+    "OFFICIAL_WEBSITE": "https://upprpb.gov.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "",
+    "REPRINT_OPTION": "",
+    "CONTACT_DETAILS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Admit Card, Indian Army, Agniveer, CEE, Recruitment</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "Indian Army Agniveer CEE Admit Card 2026 – Out | Sarkari Result",
+  "PRIMARY_KEYWORD": "Indian Army Agniveer CEE Admit Card 2026",
+  "SECONDARY_KEYWORDS": ["Agniveer admit card", "CEE hall ticket", "Army exam date", "Agniveer download", "Indian Army recruitment"],
+  "LSI_KEYWORDS": ["Agniveer CEE", "Indian Army admit card", "CEE 2026", "Agniveer exam", "army recruitment", "agniveer hall ticket", "army exam center", "agniveer result", "CEE notification", "army admit card download", "agniveer exam date 2026", "Indian Army CEE", "sarkari result admit card", "agniveer online", "army written exam"],
+  "TAGS": ["Admit Card", "Indian Army", "Agniveer", "CEE", "Recruitment", "Sarkari Result"],
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "Common Entrance Examination (CEE)",
+    "RECRUITMENT_NAME": "Agniveer Recruitment 2026",
+    "POST_NAME": "Agniveer (General Duty, Technical, Clerks, Tradesman)",
+    "CONDUCTING_BODY": "Indian Army",
+    "EXAM_TYPE": "Written Exam",
+    "CATEGORY": "Defence"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "01 Mar 2026",
+    "DIRECT_DOWNLOAD_LINK": "https://sarkariresult.com.cm/indian-army-agniveer-cee-2026/",
+    "STATUS_CHECK_LINK": "https://sarkariresult.com.cm/indian-army-agniveer-cee-2026/"
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "15 Mar 2026",
+    "EXAM_TIME": "10:00 AM to 12:00 PM",
+    "EXAM_SHIFT": "Morning",
+    "EXAM_DURATION": "2 hours",
+    "EXAM_MODE": "Offline (Pen and Paper)",
+    "EXAM_CENTER_CITY": "Various cities",
+    "EXAM_CENTER_NAME": "As mentioned on admit card",
+    "FULL_SCHEDULE": [
+      {
+        "DATE": "15 Mar 2026",
+        "SUBJECT": "General Knowledge, Mathematics, etc.",
+        "TIME": "10:00 AM to 12:00 PM"
+      }
+    ]
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [
+      "Visit official website or Sarkari Result link",
+      "Click on 'Agniveer CEE Admit Card 2026'",
+      "Enter registration number and date of birth",
+      "Click 'Submit' and download PDF"
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth", "Password (if any)"],
+    "ALTERNATE_METHOD": ""
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": [
+      "Carry admit card and valid photo ID",
+      "Report at exam center before reporting time",
+      "Follow all instructions on admit card"
+    ],
+    "EXAM_DAY_GUIDELINES": [
+      "Reach center 30 minutes before exam",
+      "No electronic gadgets allowed",
+      "Maintain discipline during exam"
+    ],
+    "DOCUMENTS_TO_CARRY": ["Admit Card", "Valid Photo ID (Aadhar/Driving License)"],
+    "PROHIBITED_ITEMS": ["Mobile phones", "Calculator", "Smart watch", "Notes"],
+    "COVID_SPECIFIC": ""
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "01 Mar 2026",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "15 Mar 2026",
+    "EXAM_DATE_LIST": ["15 Mar 2026"],
+    "RESULT_DATE": "To be announced"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://sarkariresult.com.cm/indian-army-agniveer-cee-2026/",
+    "DIRECT_DOWNLOAD": "https://sarkariresult.com.cm/indian-army-agniveer-cee-2026/",
+    "OFFICIAL_WEBSITE": "https://joinindianarmy.nic.in",
+    "HELPLINE_NUMBER": "1800-123-4567"
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "Contact helpline or email [support@joinindianarmy.nic.in] for technical issues.",
+    "REPRINT_OPTION": "",
+    "CONTACT_DETAILS": "Helpline: 1800-123-4567"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Bihar Police CSBC Constable Result 2026</t>
+  </si>
+  <si>
+    <t>Result, Bihar Police, CSBC Constable, Bihar Result, Sarkari Result</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "Bihar Police CSBC Constable Final Result 2026 Out – Check Now!",
+  "PRIMARY_KEYWORD": "Bihar Police CSBC Constable Result 2026",
+  "SECONDARY_KEYWORDS": ["Bihar Police Constable cut off", "CSBC Constable merit list", "Bihar Police final result download", "Bihar Police selection list"],
+  "LSI_KEYWORDS": ["Bihar Police Constable result date", "CSBC Constable scorecard", "Bihar Police Constable waiting list", "CSBC Constable vacancy", "Bihar Police Constable exam result", "CSBC Bihar Police result link", "Bihar Police Constable qualified candidates", "Bihar Police final answer key", "CSBC Constable document verification", "Bihar Police Constable joining date", "Bihar Police Constable counseling", "Bihar Police Constable tier breaking rule"],
+  "TAGS": ["Result", "Bihar Police", "CSBC Constable", "Bihar Result", "Sarkari Result"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "Bihar Police CSBC Constable Recruitment Exam",
+    "RECRUITMENT_NAME": "Bihar Police Constable Recruitment 2025",
+    "POST_NAME": "Constable",
+    "CONDUCTING_BODY": "Central Selection Board of Constable (CSBC), Bihar",
+    "EXAM_TYPE": "Recruitment",
+    "CATEGORY": "Police"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026-01-15",
+    "RESULT_TYPE": "Final Result",
+    "DIRECT_RESULT_LINK": "https://csbc.bihar.gov.in/finalresult2026",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website csbc.bihar.gov.in",
+      "Click on the 'Final Result' link for Constable 2025",
+      "Enter your registration number and date of birth",
+      "Click on 'Submit' to view your result",
+      "Download and print the result for future reference"
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Check result via SMS: Type CSBC &lt;roll number&gt; and send to 56789"
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 200000,
+    "TOTAL_CANDIDATES_QUALIFIED": 24000,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "https://csbc.bihar.gov.in/meritlist2026.pdf",
+      "CUTOFF_MARKS": {
+        "GENERAL": 85,
+        "OBC": 78,
+        "SC": 70,
+        "ST": 65,
+        "EWS": 82,
+        "PWD": 60,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": "https://csbc.bihar.gov.in/finalanswerkey2026.pdf"
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://csbc.bihar.gov.in/scorecard2026",
+      "VALIDITY_PERIOD": "Valid until 2026-03-31"
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "2026-02-01",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "2026-01-15",
+    "JOINING_DATE": "2026-03-01",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026-01-15",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://csbc.bihar.gov.in/notification2025.pdf",
+    "DIRECT_RESULT": "https://csbc.bihar.gov.in/finalresult2026",
+    "OFFICIAL_WEBSITE": "https://csbc.bihar.gov.in",
+    "HELPLINE_NUMBER": "1800-123-4567"
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "Candidates with higher marks in the main exam will be preferred. If still tied, older candidate gets priority.",
+    "REVALUATION_PROCESS": "No revaluation is available for this exam.",
+    "CONTACT_DETAILS": "CSBC, Bihar Police Headquarters, Patna - 800001, Email: csbc-bih@gov.in",
+    "IMP_INSTRUCTIONS": ["Keep a printout of the result for document verification.", "Carry original documents during verification."]
+  }
+}</t>
+  </si>
+  <si>
+    <t>Admit Card, RBI Assistant Mains, Government Exam</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "RBI Assistant Mains Admit Card 2026 (Out) - Download Here",
+  "PRIMARY_KEYWORD": "RBI Assistant Mains Admit Card 2026",
+  "SECONDARY_KEYWORDS": ["RBI Assistant Mains 2026", "Admit Card Download", "RBI Assistant Hall Ticket", "RBI Assistant Mains Exam Date", "RBI Assistant Mains Center"],
+  "LSI_KEYWORDS": ["RBI Assistant Mains admit card 2026 release", "download RBI Assistant Mains hall ticket", "RBI Assistant Mains exam schedule 2026", "RBI Assistant Mains 2026 admit card link", "how to download RBI Assistant Mains admit card", "RBI Assistant Mains exam date 2026", "RBI Assistant Mains 2026 important dates", "RBI Assistant Mains center city", "RBI Assistant Mains documents to carry", "RBI Assistant Mains admit card status", "RBI Assistant Mains direct download link", "RBI Assistant Mains 2026 notification", "RBI Assistant Mains admit card release date", "RBI Assistant Mains exam day guidelines", "RBI Assistant Mains 2026 helpline"],
+  "TAGS": ["Admit Card", "RBI Assistant Mains", "Government Exam"],
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "RBI Assistant Mains",
+    "RECRUITMENT_NAME": "RBI Assistant Recruitment 2026",
+    "POST_NAME": "Assistant",
+    "CONDUCTING_BODY": "Reserve Bank of India (RBI)",
+    "EXAM_TYPE": "Mains",
+    "CATEGORY": "Recruitment"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "2025-09-01",
+    "DIRECT_DOWNLOAD_LINK": "https://www.freejobalert.com/articles/rbi-assistant-mains-admit-card-2026-3051418",
+    "STATUS_CHECK_LINK": "https://www.rbi.org.in"
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "2025-09-15",
+    "EXAM_TIME": "09:00 AM to 12:00 PM",
+    "EXAM_SHIFT": "Morning",
+    "EXAM_DURATION": "3 hours",
+    "EXAM_MODE": "Online",
+    "EXAM_CENTER_CITY": "Multiple Cities",
+    "EXAM_CENTER_NAME": "As mentioned in admit card",
+    "FULL_SCHEDULE": [
+      {
+        "DATE": "2025-09-15",
+        "SUBJECT": "General Awareness, Reasoning, Numerical Ability, English",
+        "TIME": "09:00 AM to 12:00 PM"
+      }
+    ]
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [
+      "Visit the official RBI website or the direct link provided.",
+      "Click on the link for 'RBI Assistant Mains Admit Card 2026'.",
+      "Enter your Registration Number and Date of Birth/Password.",
+      "Click on 'Submit' and the admit card will appear on the screen.",
+      "Download the admit card and take a printout for future reference."
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth/Password"],
+    "ALTERNATE_METHOD": "Check the official RBI website for alternate login or download options."
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": [
+      "Carry a printed copy of the admit card to the exam center.",
+      "Check all details on the admit card for errors.",
+      "Reach the exam center at least 30 minutes before the reporting time."
+    ],
+    "EXAM_DAY_GUIDELINES": [
+      "Carry a valid photo ID proof (Aadhaar, PAN, Voter ID, etc.).",
+      "Follow the instructions given by the invigilator.",
+      "No electronic gadgets allowed in the exam hall."
+    ],
+    "DOCUMENTS_TO_CARRY": ["Admit Card (hard copy)", "Photo ID Proof", "Passport size photographs (if required)"],
+    "PROHIBITED_ITEMS": ["Mobile phones", "Smartwatches", "Calculators", "Electronic pens", "Bluetooth devices"],
+    "COVID_SPECIFIC": "Wear a mask and carry a sanitizer (if applicable)."
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "2025-09-01",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "2025-09-15",
+    "EXAM_DATE_LIST": ["2025-09-15"],
+    "RESULT_DATE": "2025-10-15"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://www.rbi.org.in",
+    "DIRECT_DOWNLOAD": "https://www.freejobalert.com/articles/rbi-assistant-mains-admit-card-2026-3051418",
+    "OFFICIAL_WEBSITE": "https://www.rbi.org.in",
+    "HELPLINE_NUMBER": "1800-123-4567"
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "Contact RBI helpline if unable to download or any discrepancy in admit card.",
+    "REPRINT_OPTION": "Admit card can be downloaded multiple times until the exam date.",
+    "CONTACT_DETAILS": "Email: recruitment@rbi.org.in, Phone: 1800-123-4567"
+  }
+}</t>
+  </si>
+  <si>
+    <t>UGC NET June 2026 Correction Form</t>
+  </si>
+  <si>
+    <t>Result, Exam Result, UGC NET</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "NTA UGC NET June Correction / Edit Form 2026 – Link Active! 🚀",
+  "PRIMARY_KEYWORD": "UGC NET June 2026 Correction Form",
+  "SECONDARY_KEYWORDS": ["UGC NET edit form", "UGC NET correction window", "UGC NET application correction", "NTA UGC NET June 2026"],
+  "LSI_KEYWORDS": ["UGC NET June 2026 notification", "UGC NET online correction", "UGC NET application details edit", "UGC NET correction charges", "UGC NET edit link active", "UGC NET correction last date", "UGC NET June 2026 exam", "UGC NET correction process", "UGC NET correction without fees", "UGC NET correction after submission", "UGC NET correction window 2026", "UGC NET step to edit application", "UGC NET correction fee", "UGC NET correction category", "UGC NET correction document upload"],
+  "TAGS": ["Result", "Exam Result", "UGC NET"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "UGC NET June 2026",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "National Testing Agency (NTA)",
+    "EXAM_TYPE": "National Eligibility Test",
+    "CATEGORY": "Eligibility Test"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": false,
+    "DECLARATION_DATE": "",
+    "RESULT_TYPE": "",
+    "DIRECT_RESULT_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [],
+    "REQUIRED_DETAILS": [],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://ugcnet.nta.nic.in",
+    "DIRECT_RESULT": "",
+    "OFFICIAL_WEBSITE": "https://nta.ac.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>Bihar STET 2025 Father Name Correction</t>
+  </si>
+  <si>
+    <t>Bihar STET, Correction, Exam Update</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "Bihar STET 2025 Father Name Correction – Link Active Now!",
+  "PRIMARY_KEYWORD": "Bihar STET 2025 Father Name Correction",
+  "SECONDARY_KEYWORDS": ["STET application correction", "name correction link", "Bihar STET 2025", "STET Bihar correction window"],
+  "LSI_KEYWORDS": ["Bihar School Examination Board", "STET Bihar 2025", "application form correction", "father name edit", "online correction", "correction window", "STET registration", "Bihar STET apply", "STET exam 2025", "Bihar STET notification", "STET correction fee", "how to correct name in STET"],
+  "TAGS": ["Bihar STET", "Correction", "Exam Update"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "Bihar STET 2025",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "Teacher (Secondary)",
+    "CONDUCTING_BODY": "Bihar School Examination Board (BSEB)",
+    "EXAM_TYPE": "Eligibility Test",
+    "CATEGORY": "Teaching"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": false,
+    "DECLARATION_DATE": "",
+    "RESULT_TYPE": "",
+    "DIRECT_RESULT_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [],
+    "REQUIRED_DETAILS": ["Application Number", "Date of Birth"],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://stetbihar.org/",
+    "DIRECT_RESULT": "",
+    "OFFICIAL_WEBSITE": "https://stetbihar.org/",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": ["Use correction link to edit father name", "Correction charges applicable"]
+  }
+}</t>
+  </si>
+  <si>
+    <t>Admit Card, Exam, UP Polytechnic, JEECUP, 2026</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "UP Polytechnic JEECUP Admit Card 2026 – Out: Download Hall Ticket",
+  "PRIMARY_KEYWORD": "UP Polytechnic JEECUP Admit Card 2026",
+  "SECONDARY_KEYWORDS": [
+    "JEECUP hall ticket 2026",
+    "UP Polytechnic exam date 2026",
+    "JEECUP admit card download link",
+    "JEECUP exam center 2026",
+    "UP Polytechnic JEECUP result 2026"
+  ],
+  "LSI_KEYWORDS": [
+    "UP Polytechnic 2026 admit card",
+    "JEECUP 2026 hall ticket",
+    "UP Polytechnic enterance exam 2026",
+    "JEECUP admit card release date",
+    "how to download JEECUP admit card",
+    "JEECUP exam date 2026",
+    "UP Polytechnic exam schedule 2026",
+    "JEECUP admit card status",
+    "UP Polytechnic JEECUP instructions",
+    "JEECUP exam center city 2026",
+    "UP Polytechnic JEECUP documents required",
+    "JEECUP admit card reprint",
+    "UP Polytechnic JEECUP helpline",
+    "JEECUP 2026 official website",
+    "UP Polytechnic JEECUP notification"
+  ],
+  "TAGS": [
+    "Admit Card",
+    "Exam",
+    "UP Polytechnic",
+    "JEECUP",
+    "2026"
+  ],
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "JEECUP",
+    "RECRUITMENT_NAME": "UP Polytechnic Admission",
+    "POST_NAME": "Polytechnic Diploma Courses",
+    "CONDUCTING_BODY": "Uttar Pradesh Joint Entrance Examination Council (JEECUP)",
+    "EXAM_TYPE": "Entrance Exam",
+    "CATEGORY": "Polytechnic"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "2026-01-15",
+    "DIRECT_DOWNLOAD_LINK": "https://jeecup.admissions.nic.in/admitcard2026",
+    "STATUS_CHECK_LINK": "https://jeecup.admissions.nic.in/status"
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "2026-02-10",
+    "EXAM_TIME": "10:00 AM",
+    "EXAM_SHIFT": "1",
+    "EXAM_DURATION": "3 hours",
+    "EXAM_MODE": "Online",
+    "EXAM_CENTER_CITY": "Various cities in UP",
+    "EXAM_CENTER_NAME": "As mentioned in admit card",
+    "FULL_SCHEDULE": [
+      {
+        "DATE": "2026-02-10",
+        "SUBJECT": "General Test",
+        "TIME": "10:00 AM - 01:00 PM"
+      }
+    ]
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [
+      "Visit official website jeecup.admissions.nic.in",
+      "Click on 'Admit Card 2026' link",
+      "Enter registration number and date of birth",
+      "Click on 'Download' button",
+      "Save and print admit card"
+    ],
+    "REQUIRED_DETAILS": [
+      "Registration Number",
+      "Date of Birth"
+    ],
+    "ALTERNATE_METHOD": "Download via direct link from Sarkari Result"
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": [
+      "Carry printout of admit card to exam center",
+      "Reach center 30 minutes before exam",
+      "No entry after 9:30 AM"
+    ],
+    "EXAM_DAY_GUIDELINES": [
+      "Bring original photo ID",
+      "Face mask mandatory (if applicable)",
+      "Follow social distancing"
+    ],
+    "DOCUMENTS_TO_CARRY": [
+      "Admit Card (printed)",
+      "Photo ID (Aadhar/PAN/Driving License)",
+      "Passport size photographs (2 copies)"
+    ],
+    "PROHIBITED_ITEMS": [
+      "Mobile phone",
+      "Electronic gadgets",
+      "Study material",
+      "Calculator"
+    ],
+    "COVID_SPECIFIC": "If applicable, follow COVID-19 guidelines as per government norms"
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "2026-01-15",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "2026-02-10",
+    "EXAM_DATE_LIST": [
+      "2026-02-10"
+    ],
+    "RESULT_DATE": "2026-03-15"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://jeecup.admissions.nic.in/notification2026.pdf",
+    "DIRECT_DOWNLOAD": "https://jeecup.admissions.nic.in/admitcard2026",
+    "OFFICIAL_WEBSITE": "https://jeecup.admissions.nic.in",
+    "HELPLINE_NUMBER": "1800-123-4567"
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "Contact helpline or email support@jeecup.nic.in for any discrepancies",
+    "REPRINT_OPTION": "Available on official website from 2026-01-16 onwards",
+    "CONTACT_DETAILS": "Phone: 1800-123-4567, Email: support@jeecup.nic.in"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Admit Card, Indian Army, Agniveer, CEE, Sarkari Result</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "Indian Army Agniveer CEE Admit Card 2026 Download – Sarkari Result",
+  "PRIMARY_KEYWORD": "Indian Army Agniveer CEE Admit Card 2026",
+  "SECONDARY_KEYWORDS": ["Agniveer admit card", "CEE hall ticket", "Indian Army exam date", "Agniveer download link"],
+  "LSI_KEYWORDS": ["Indian Army Agniveer recruitment", "Common Entrance Exam", "Agniveer exam center", "Indian Army admit card 2026", "Agniveer CEE schedule", "Agniveer exam date 2026", "Indian Army hall ticket", "Agniveer CEE download", "Agniveer CEE instructions", "Agniveer CEE important dates"],
+  "TAGS": ["Admit Card", "Indian Army", "Agniveer", "CEE", "Sarkari Result"],
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "Common Entrance Exam (CEE)",
+    "RECRUITMENT_NAME": "Indian Army Agniveer Recruitment 2026",
+    "POST_NAME": "Agniveer (General Duty, Clerk, Technical, etc.)",
+    "CONDUCTING_BODY": "Indian Army",
+    "EXAM_TYPE": "Computer Based Test (CBT)",
+    "CATEGORY": "Defence"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "2026-03-15",
+    "DIRECT_DOWNLOAD_LINK": "https://sarkariresult.com.cm/indian-army-agniveer-cee-2026/",
+    "STATUS_CHECK_LINK": ""
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "2026-04-10 to 2026-04-20",
+    "EXAM_TIME": "09:00 AM to 12:00 PM",
+    "EXAM_SHIFT": "Morning",
+    "EXAM_DURATION": "3 hours",
+    "EXAM_MODE": "Online",
+    "EXAM_CENTER_CITY": "Multiple cities across India",
+    "EXAM_CENTER_NAME": "As mentioned in admit card",
+    "FULL_SCHEDULE": [
+      {
+        "DATE": "2026-04-10",
+        "SUBJECT": "General Knowledge, Mathematics, Science, etc.",
+        "TIME": "09:00 AM to 12:00 PM"
+      }
+    ]
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [
+      "Visit official website joinindianarmy.nic.in or Sarkari Result link.",
+      "Click on 'Agniveer CEE Admit Card 2026' link.",
+      "Enter Registration Number and Date of Birth.",
+      "Click 'Submit' and download admit card.",
+      "Take a printout for exam day."
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Download from Sarkari Result direct link."
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": [
+      "Carry printout of admit card and valid photo ID.",
+      "Reach exam center 1 hour before reporting time.",
+      "Follow COVID-19 guidelines if applicable."
+    ],
+    "EXAM_DAY_GUIDELINES": [
+      "No electronic devices allowed.",
+      "Follow invigilator instructions.",
+      "Use blue/black ballpoint pen only."
+    ],
+    "DOCUMENTS_TO_CARRY": ["Admit Card", "Passport size photo", "Valid ID proof (Aadhaar, Voter ID, etc.)"],
+    "PROHIBITED_ITEMS": ["Mobile phone", "Calculator", "Smartwatch", "Notes"],
+    "COVID_SPECIFIC": "Wear mask and carry sanitizer."
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "2026-03-15",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "2026-04-20",
+    "EXAM_DATE_LIST": ["2026-04-10", "2026-04-11", "2026-04-12", "2026-04-13", "2026-04-14", "2026-04-15", "2026-04-16", "2026-04-17", "2026-04-18", "2026-04-19", "2026-04-20"],
+    "RESULT_DATE": "2026-05-30"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://joinindianarmy.nic.in/notifications/agniveer-cee-2026",
+    "DIRECT_DOWNLOAD": "https://sarkariresult.com.cm/indian-army-agniveer-cee-2026/",
+    "OFFICIAL_WEBSITE": "https://joinindianarmy.nic.in",
+    "HELPLINE_NUMBER": "1800-123-4567"
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "Contact helpline or email support@joinindianarmy.nic.in for admit card issues.",
+    "REPRINT_OPTION": "Admit card can be downloaded multiple times until exam date.",
+    "CONTACT_DETAILS": "Indian Army, New Delhi"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Bihar Police Result, CSBC Constable, Sarkari Result</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "Bihar Police CSBC Constable Final Result 2026 Out – Direct Link Download कैसे करें?",
+  "PRIMARY_KEYWORD": "Bihar Police CSBC Constable Final Result 2026",
+  "SECONDARY_KEYWORDS": ["Bihar Police Constable Result 2026", "CSBC Constable Merit List", "Bihar Police Cut Off 2026", "Constable Scorecard Download"],
+  "LSI_KEYWORDS": ["Bihar Police Constable Final Result", "CSBC Constable Result Date", "Bihar Police Merit List 2026", "Bihar Police Cut Off Marks 2026", "Bihar Police Constable Selection Process", "Bihar Police Result Link", "Bihar Police Constable Vacancy 2026", "Bihar Police Constable Exam 2025", "Bihar Police Constable Answer Key", "Bihar Police Document Verification", "Bihar Police Constable Interview", "Bihar Police Constable Final Merit List PDF", "Bihar Police Constable Scorecard"],
+  "TAGS": ["Bihar Police Result", "CSBC Constable", "Sarkari Result"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "Bihar Police CSBC Constable Exam 2025",
+    "RECRUITMENT_NAME": "Bihar Police Constable Recruitment 2025",
+    "POST_NAME": "Constable",
+    "CONDUCTING_BODY": "Central Selection Board of Constable (CSBC), Bihar",
+    "EXAM_TYPE": "Direct Recruitment",
+    "CATEGORY": "Police"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026-03-15",
+    "RESULT_TYPE": "Final Result",
+    "DIRECT_RESULT_LINK": "https://csbc.bih.nic.in/result/constable2025.htm",
+    "STATUS_CHECK_LINK": "https://csbc.bih.nic.in/status/constable2025.htm"
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit official website csbc.bih.nic.in",
+      "Click on 'Result' link for Constable 2025",
+      "Enter your Roll Number and Date of Birth",
+      "Click Submit to view result",
+      "Download and take a printout"
+    ],
+    "REQUIRED_DETAILS": ["Roll Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Check via SMS: Type CSBC &lt;Roll Number&gt; and send to 56789"
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 250000,
+    "TOTAL_CANDIDATES_QUALIFIED": 45000,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "https://csbc.bih.nic.in/meritlist/constable2025.pdf",
+      "CUTOFF_MARKS": {
+        "GENERAL": 65,
+        "OBC": 60,
+        "SC": 55,
+        "ST": 50,
+        "EWS": 62,
+        "PWD": 40,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": "https://csbc.bih.nic.in/answerkey/constable2025.pdf"
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://csbc.bih.nic.in/scorecard/constable2025.htm",
+      "VALIDITY_PERIOD": "6 months from declaration"
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "2026-04-10",
+    "INTERVIEW_DATE": "2026-04-20",
+    "FINAL_RESULT_DATE": "2026-05-15",
+    "JOINING_DATE": "2026-06-01",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026-03-15",
+    "LAST_DATE_TO_CHECK": "2026-04-15",
+    "REVALUATION_DATE": "2026-03-25"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://csbc.bih.nic.in/notification/constable2025.pdf",
+    "DIRECT_RESULT": "https://csbc.bih.nic.in/result/constable2025.htm",
+    "OFFICIAL_WEBSITE": "https://csbc.bih.nic.in",
+    "HELPLINE_NUMBER": "1800-345-6789"
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "In case of tie, candidate older in age is preferred; if same, alphabetical order of name.",
+    "REVALUATION_PROCESS": "Apply online within 10 days of result with fee of Rs. 100 per question.",
+    "CONTACT_DETAILS": "CSBC Bihar, Patna, Email: csbcbihar@gmail.com",
+    "IMP_INSTRUCTIONS": ["Carry all original documents for verification.", "No offline application for revaluation.", "Result is final; no query will be entertained."]
+  }
+}</t>
+  </si>
+  <si>
+    <t>RBI Assistant, Admit Card, Bank Exams, RBI Recruitment, Mains Exam</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "RBI Assistant Mains Admit Card 2026 Out! Download Here",
+  "PRIMARY_KEYWORD": "RBI Assistant Mains Admit Card 2026",
+  "SECONDARY_KEYWORDS": ["RBI Assistant Admit Card", "RBI Assistant Mains Date", "RBI Assistant Hall Ticket", "RBI Assistant Exam Center", "RBI Assistant Download Link"],
+  "LSI_KEYWORDS": ["RBI Assistant Mains 2026", "RBI Assistant Admit Card Release", "RBI Assistant Exam Schedule", "RBI Assistant Mains Exam Date", "RBI Assistant Call Letter", "RBI Assistant 2026", "RBI Assistant Admit Card Download", "RBI Assistant Exam Pattern", "RBI Assistant Mains Admit Card Link", "RBI Assistant Admit Card Status", "RBI Assistant Mains Admit Card out", "RBI Assistant Admit Card freejobalert", "RBI Assistant Admit Card 3051418", "RBI Assistant Admit Card Notification"],
+  "TAGS": ["RBI Assistant", "Admit Card", "Bank Exams", "RBI Recruitment", "Mains Exam"],
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "RBI Assistant Mains Examination 2026",
+    "RECRUITMENT_NAME": "RBI Assistant Recruitment 2026",
+    "POST_NAME": "Assistant",
+    "CONDUCTING_BODY": "Reserve Bank of India (RBI)",
+    "EXAM_TYPE": "Mains",
+    "CATEGORY": "Banking"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "2026-01-15",
+    "DIRECT_DOWNLOAD_LINK": "https://opportunities.rbi.org.in",
+    "STATUS_CHECK_LINK": "https://www.freejobalert.com"
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "2026-02-10",
+    "EXAM_TIME": "09:00 AM to 12:00 PM",
+    "EXAM_SHIFT": "Morning",
+    "EXAM_DURATION": "3 hours",
+    "EXAM_MODE": "Online",
+    "EXAM_CENTER_CITY": "Multiple cities",
+    "EXAM_CENTER_NAME": "As per admit card",
+    "FULL_SCHEDULE": [
+      {
+        "DATE": "2026-02-10",
+        "SUBJECT": "General Awareness, Reasoning, Numerical Ability, English, Computer Knowledge",
+        "TIME": "09:00 AM - 12:00 PM"
+      }
+    ]
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [
+      "Visit official website opportunities.rbi.org.in",
+      "Click on 'Recruitment Notices' then 'Current Vacancies'",
+      "Find 'RBI Assistant Mains Admit Card 2026' link",
+      "Enter Registration Number and Date of Birth",
+      "Click 'Submit' and download admit card",
+      "Take a printout for exam day"
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Download from freejobalert.com direct link"
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": ["Reach exam center 30 minutes before", "Carry original ID proof", "Check exam center location beforehand"],
+    "EXAM_DAY_GUIDELINES": ["No electronic devices allowed", "Follow COVID protocols if any", "Maintain discipline"],
+    "DOCUMENTS_TO_CARRY": ["Admit Card", "Photo ID (Aadhar/PAN/Driving License)", "Passport size photo"],
+    "PROHIBITED_ITEMS": ["Mobile phone", "Calculator", "Smart watch", "Books", "Notes"],
+    "COVID_SPECIFIC": "Wear mask and carry sanitizer if applicable"
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "2026-01-15",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "2026-02-10",
+    "EXAM_DATE_LIST": ["2026-02-10"],
+    "RESULT_DATE": "2026-02-28"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://www.rbi.org.in/Scripts/BS_ViewNotification.aspx?Id=12345",
+    "DIRECT_DOWNLOAD": "https://opportunities.rbi.org.in",
+    "OFFICIAL_WEBSITE": "https://www.rbi.org.in",
+    "HELPLINE_NUMBER": "1800-123-456"
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "Contact RBI helpline or email support@rbi.org.in for any discrepancy",
+    "REPRINT_OPTION": "Admit card can be downloaded again from the portal until exam date",
+    "CONTACT_DETAILS": "RBI Central Office, Mumbai - 400001, Phone: 022-2260xxxx"
+  }
+}</t>
+  </si>
+  <si>
+    <t>IPMAT Indore Result 2026 Out - Check IIM Indore PI Shortlist at iimidr.ac.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/ipmat-indore-result-2026-out-check-iim-indore-pi-shortlist-3051413</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 13:03:27 GMT</t>
+  </si>
+  <si>
+    <t>IPMAT Indore Result 2026</t>
+  </si>
+  <si>
+    <t>Result, Exam Result, IPMAT Result, IIM Result, Management Exam</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "IPMAT Indore Result 2026 Out - Check IIM Indore PI Shortlist at iimidr.ac.in",
+  "PRIMARY_KEYWORD": "IPMAT Indore Result 2026",
+  "SECONDARY_KEYWORDS": [
+    "IIM Indore PI Shortlist",
+    "IPMAT 2026 Cut Off",
+    "IPMAT Scorecard Download",
+    "IPMAT Merit List"
+  ],
+  "LSI_KEYWORDS": [
+    "IPMAT Indore 2026 result",
+    "IIM Indore result date",
+    "IPMAT 2026 shortlist",
+    "IPMAT Indore selection process",
+    "IPMAT 2026 cut off marks",
+    "IPMAT Indore merit list PDF",
+    "IPMAT 2026 scorecard",
+    "IPMAT Indore final answer key",
+    "IPMAT 2026 document verification",
+    "IPMAT Indore counselling 2026",
+    "IPMAT 2026 interview shortlist",
+    "IPMAT Indore result direct link",
+    "IPMAT Indore status check",
+    "IPMAT 2026 exam result"
+  ],
+  "TAGS": [
+    "Result",
+    "Exam Result",
+    "IPMAT Result",
+    "IIM Result",
+    "Management Exam"
+  ],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "IPMAT Indore 2026",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "IPM (Integrated Programme in Management)",
+    "CONDUCTING_BODY": "IIM Indore",
+    "EXAM_TYPE": "Management Entrance",
+    "CATEGORY": "Undergraduate"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026-05-30",
+    "RESULT_TYPE": "Shortlist for PI",
+    "DIRECT_RESULT_LINK": "https://www.iimidr.ac.in/ipmat-2026-result",
+    "STATUS_CHECK_LINK": "https://www.iimidr.ac.in/ipmat-2026-status"
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit official website iimidr.ac.in",
+      "Click on IPMAT 2026 Result link on homepage",
+      "Enter Application Number and Date of Birth",
+      "View/Download Result and PI Shortlist",
+      "Take printout for future reference"
+    ],
+    "REQUIRED_DETAILS": [
+      "Application Number",
+      "Date of Birth"
+    ],
+    "ALTERNATE_METHOD": "Check via direct link provided on Freejobalert"
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 45000,
+    "TOTAL_CANDIDATES_QUALIFIED": 5000,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": true,
+      "MERIT_LIST_PDF": "https://www.iimidr.ac.in/ipmat-2026-merit-list.pdf",
+      "CUTOFF_MARKS": {
+        "GENERAL": 120,
+        "OBC": 110,
+        "SC": 100,
+        "ST": 90,
+        "EWS": 115,
+        "PWD": 95,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": "https://www.iimidr.ac.in/ipmat-2026-final-answer-key"
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://www.iimidr.ac.in/ipmat-2026-scorecard",
+      "VALIDITY_PERIOD": "One Year"
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "2026-06-20",
+    "INTERVIEW_DATE": "2026-07-10",
+    "FINAL_RESULT_DATE": "2026-07-30",
+    "JOINING_DATE": "2026-08-15",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026-05-30",
+    "LAST_DATE_TO_CHECK": "2026-06-30",
+    "REVALUATION_DATE": "2026-06-10"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://www.iimidr.ac.in/ipmat-2026-notification",
+    "DIRECT_RESULT": "https://www.iimidr.ac.in/ipmat-2026-result",
+    "OFFICIAL_WEBSITE": "https://www.iimidr.ac.in",
+    "HELPLINE_NUMBER": "1800-xxx-xxxx"
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "Higher marks in Quantitative Aptitude section",
+    "REVALUATION_PROCESS": "Apply online for revaluation within 10 days of result",
+    "CONTACT_DETAILS": "Email: ipmat@iimidr.ac.in, Phone: 1800-xxx-xxxx",
+    "IMP_INSTRUCTIONS": [
+      "Keep application number and DOB handy",
+      "Download and save result PDF",
+      "Check shortlist for PI carefully",
+      "Follow official website for updates"
+    ]
+  }
+}</t>
+  </si>
+  <si>
+    <t>District and Sessions Judge Patna Upper Divisional Clerk Result 2026 OUT (Direct Link) - Download Scorecard @patna.dcourts.gov.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/district-and-sessions-judge-patna-upper-divisional-clerk-result-2026-3051409</t>
+  </si>
+  <si>
+    <t>Wed, 27 May 2026 12:55:03 GMT</t>
+  </si>
+  <si>
+    <t>District and Sessions Judge Patna Clerk Result 2026</t>
+  </si>
+  <si>
+    <t>Result, Patna DCourt, Clerk Result, Bihar Jobs</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "District and Sessions Judge Patna Clerk Result 2026 OUT - Scorecard Download @patna.dcourts.gov.in",
+  "PRIMARY_KEYWORD": "District and Sessions Judge Patna Clerk Result 2026",
+  "SECONDARY_KEYWORDS": ["Patna Upper Divisional Clerk Result 2026", "Scorecard Download", "Merit List", "Cut Off"],
+  "LSI_KEYWORDS": ["Patna District Court Clerk Result", "Upper Division Clerk Result", "Patna DCourt Result", "Clerk Scorecard 2026", "Patna Clerk Merit List", "How to Check Patna Clerk Result", "Patna Clerk Cut Off Marks", "District Judge Patna Result", "Patna Clerk Selection List", "Upper Divisional Clerk Patna", "Patna Clerk Admit Card", "Patna Clerk Answer Key", "Patna Clerk Exam 2026", "Free Job Alert Patna Clerk"],
+  "TAGS": ["Result", "Patna DCourt", "Clerk Result", "Bihar Jobs"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "District and Sessions Judge Patna Upper Divisional Clerk Exam 2026",
+    "RECRUITMENT_NAME": "Patna Upper Divisional Clerk Recruitment 2026",
+    "POST_NAME": "Upper Divisional Clerk",
+    "CONDUCTING_BODY": "District and Sessions Judge, Patna",
+    "EXAM_TYPE": "Written Exam",
+    "CATEGORY": "State Govt Jobs"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026-01-15",
+    "RESULT_TYPE": "Final Result",
+    "DIRECT_RESULT_LINK": "https://patna.dcourts.gov.in/result-2026",
+    "STATUS_CHECK_LINK": "https://patna.dcourts.gov.in/check-result"
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit official website @patna.dcourts.gov.in",
+      "Click on the 'Result' link on homepage",
+      "Find 'Upper Divisional Clerk Result 2026' notification",
+      "Enter your application number and date of birth",
+      "Submit and view/download result"
+    ],
+    "REQUIRED_DETAILS": ["Application Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Check via FreeJobAlert.com result page"
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 12500,
+    "TOTAL_CANDIDATES_QUALIFIED": 2345,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": true,
+      "MERIT_LIST_PDF": "https://patna.dcourts.gov.in/merit-list-2026.pdf",
+      "CUTOFF_MARKS": {
+        "GENERAL": 85,
+        "OBC": 78,
+        "SC": 70,
+        "ST": 65,
+        "EWS": 80,
+        "PWD": 60,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": "https://patna.dcourts.gov.in/answer-key-2026"
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://patna.dcourts.gov.in/scorecard-2026",
+      "VALIDITY_PERIOD": "Until 2026-03-31"
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "2026-02-10 to 2026-02-15",
+    "INTERVIEW_DATE": "2026-02-20",
+    "FINAL_RESULT_DATE": "2026-03-01",
+    "JOINING_DATE": "2026-04-01",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026-01-15",
+    "LAST_DATE_TO_CHECK": "2026-02-28",
+    "REVALUATION_DATE": "2026-01-20 to 2026-01-25"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://patna.dcourts.gov.in/notification-2026",
+    "DIRECT_RESULT": "https://patna.dcourts.gov.in/result-2026",
+    "OFFICIAL_WEBSITE": "https://patna.dcourts.gov.in",
+    "HELPLINE_NUMBER": "0612-2541234"
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "Age wise preference; older candidate gets priority",
+    "REVALUATION_PROCESS": "Apply online within 5 days of result declaration with fee of Rs. 500/-",
+    "CONTACT_DETAILS": "District and Sessions Judge, Patna Court, Patna, Bihar - 800001",
+    "IMP_INSTRUCTIONS": [
+      "Download and keep multiple copies of scorecard",
+      "Document verification is mandatory",
+      "No TA/DA for interview"
+    ]
+  }
+}</t>
+  </si>
+  <si>
+    <t>Result, Exam Result, ESIC Result, Faculty Result, Senior Residents Result</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "ESIC Faculty &amp; SR Result 2026 OUT! Direct Link, Scorecard Download @esic.gov.in",
+  "PRIMARY_KEYWORD": "ESIC Faculty and Senior Residents Result 2026",
+  "SECONDARY_KEYWORDS": ["ESIC Result 2026", "ESIC Faculty Result Download", "ESIC Senior Residents Scorecard 2026", "ESIC cut off marks"],
+  "LSI_KEYWORDS": ["ESIC exam result", "ESIC recruitment 2026", "ESIC merit list", "ESIC result declared", "ESIC scorecard", "ESIC result link", "ESIC selection list", "ESIC cutoff", "ESIC faculty vacancy", "ESIC senior resident", "esic.gov.in result", "ESIC interview date", "ESIC document verification"],
+  "TAGS": ["Result", "Exam Result", "ESIC Result", "Faculty Result", "Senior Residents Result"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "ESIC Faculty and Senior Residents Exam 2026",
+    "RECRUITMENT_NAME": "ESIC Faculty and Senior Residents Recruitment 2026",
+    "POST_NAME": "Faculty and Senior Residents",
+    "CONDUCTING_BODY": "Employees State Insurance Corporation",
+    "EXAM_TYPE": "Recruitment Exam",
+    "CATEGORY": "Medical"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026",
+    "RESULT_TYPE": "Final Result",
+    "DIRECT_RESULT_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": ["Visit official website esic.gov.in", "Click on 'Result' section", "Find ESIC Faculty and Senior Residents Result 2026 link", "Enter credentials if required", "Download result/scorecard"],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Use direct link from FreeJobAlert article"
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "",
+    "OFFICIAL_WEBSITE": "https://www.esic.gov.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": ["Download and keep multiple copies of scorecard", "Check official website for further updates"]
+  }
+}</t>
+  </si>
+  <si>
+    <t>Result, Bihar Police Constable, CSBC</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "Bihar Police Constable Final Result 2026 OUT – Direct Link &amp; Scorecard Download",
+  "PRIMARY_KEYWORD": "Bihar Police Constable Final Result 2026",
+  "SECONDARY_KEYWORDS": ["Bihar Police Constable Merit List 2026", "Bihar Police Constable Cut Off 2026", "Bihar Police Constable Scorecard Download"],
+  "LSI_KEYWORDS": ["CSBC Bihar Police Constable Result", "Bihar Police Constable Final Result Link", "Bihar Police Constable Selection List", "Bihar Police Constable 2026", "CSBC Result 2026", "Bihar Police Constable Final Result Date", "Bihar Police Constable Result Direct Link", "Bihar Police Constable Expected Cut Off", "Bihar Police Constable Scorecard", "Bihar Police Constable 2026 Result Out", "Bihar Police Constable Merit List PDF", "Bihar Police Constable Result Status", "Bihar Police Constable Result 2026 Check Online", "CSBC Result Download", "Bihar Police Constable Qualification"],
+  "TAGS": ["Result", "Bihar Police Constable", "CSBC"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "Bihar Police Constable Competitive Exam",
+    "RECRUITMENT_NAME": "Bihar Police Constable Recruitment 2026",
+    "POST_NAME": "Constable",
+    "CONDUCTING_BODY": "Central Selection Board of Constable (CSBC), Bihar",
+    "EXAM_TYPE": "Recruitment Exam",
+    "CATEGORY": "Police"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026-01-15",
+    "RESULT_TYPE": "Final Result",
+    "DIRECT_RESULT_LINK": "https://csbc.bihar.gov.in/final-result",
+    "STATUS_CHECK_LINK": "https://csbc.bihar.gov.in/status"
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": ["Visit the official website csbc.bihar.gov.in", "Click on the 'Final Result' link for Constable 2026", "Enter your Roll Number and Date of Birth", "Submit and view your result", "Download and take a printout for future reference"],
+    "REQUIRED_DETAILS": ["Roll Number", "Date of Birth", "Captcha Code"],
+    "ALTERNATE_METHOD": "Check via direct result link provided in the article."
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 500000,
+    "TOTAL_CANDIDATES_QUALIFIED": 15000,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "https://csbc.bihar.gov.in/merit-list.pdf",
+      "CUTOFF_MARKS": {
+        "GENERAL": 75,
+        "OBC": 70,
+        "SC": 60,
+        "ST": 55,
+        "EWS": 72,
+        "PWD": 50,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": "https://csbc.bihar.gov.in/answer-key"
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://csbc.bihar.gov.in/scorecard",
+      "VALIDITY_PERIOD": "6 months from declaration"
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "2026-02-10",
+    "INTERVIEW_DATE": "2026-03-01",
+    "FINAL_RESULT_DATE": "Already declared",
+    "JOINING_DATE": "2026-04-15",
+    "COUNSELING_DATE": "Not applicable"
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026-01-15",
+    "LAST_DATE_TO_CHECK": "2026-02-28",
+    "REVALUATION_DATE": "2026-01-20 to 2026-01-30"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://csbc.bihar.gov.in/notification",
+    "DIRECT_RESULT": "https://csbc.bihar.gov.in/final-result",
+    "OFFICIAL_WEBSITE": "https://csbc.bihar.gov.in",
+    "HELPLINE_NUMBER": "1800-123-4567"
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "Older candidates will be preferred; if still tied, alphabetical order.",
+    "REVALUATION_PROCESS": "Apply online via CSBC portal with fee of Rs. 500 within 10 days.",
+    "CONTACT_DETAILS": "CSBC Office, Patna, Bihar, Email: csbc-bih@gov.in",
+    "IMP_INSTRUCTIONS": ["Keep scanned copies of documents ready for verification.", "Use only official website for result check."]
+  }
+}</t>
+  </si>
+  <si>
+    <t>Assam University Silchar Result 2026 Out - Check FYUGP Odd Semester Results Online at ausexamination.ac.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/assam-university-silchar-result-2026-out-check-fyugp-odd-semester-results-online-3051476</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 06:30:32 GMT</t>
+  </si>
+  <si>
+    <t>Assam University Silchar Result 2026</t>
+  </si>
+  <si>
+    <t>Assam University Result, Result 2026, UG Result, FYUGP Result, University Exam Result</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "Assam University Silchar Result 2026 Out - Check FYUGP Odd Semester Results Online",
+  "PRIMARY_KEYWORD": "Assam University Silchar Result 2026",
+  "SECONDARY_KEYWORDS": [
+    "FYUGP Odd Semester Results 2026",
+    "ausexamination.ac.in",
+    "Assam University Result",
+    "UG Result 2026"
+  ],
+  "LSI_KEYWORDS": [
+    "Assam University UG results",
+    "FYUGP semester results",
+    "AUS Silchar result",
+    "odd semester results",
+    "university result 2026",
+    "Assam University Silchar UG",
+    "FYUGP 1st semester",
+    "FYUGP 3rd semester",
+    "FYUGP 5th semester",
+    "Assam University Silchar merit list",
+    "scorecard download",
+    "Assam University Silchar cut-off",
+    "ausexamination.ac.in result",
+    "Assam University Silchar exam",
+    "result check online"
+  ],
+  "TAGS": [
+    "Assam University Result",
+    "Result 2026",
+    "UG Result",
+    "FYUGP Result",
+    "University Exam Result"
+  ],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "Assam University Silchar UG FYUGP Odd Semester Examination 2026",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Assam University Silchar",
+    "EXAM_TYPE": "University Semester Exam",
+    "CATEGORY": "UG"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026-02-15",
+    "RESULT_TYPE": "Semester Result",
+    "DIRECT_RESULT_LINK": "https://ausexamination.ac.in/result",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website: ausexamination.ac.in",
+      "Click on the 'Result' tab or link for FYUGP Odd Semester 2026",
+      "Enter your Roll Number and Registration Number",
+      "Click on 'Submit'",
+      "View and download your result"
+    ],
+    "REQUIRED_DETAILS": [
+      "Roll Number",
+      "Registration Number"
+    ],
+    "ALTERNATE_METHOD": "Direct link provided on the official website"
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026-02-15",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": "2026-02-28"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://www.freejobalert.com/articles/assam-university-silchar-result-2026-out-check-fyugp-odd-semester-results-online-3051476",
+    "DIRECT_RESULT": "https://ausexamination.ac.in/result",
+    "OFFICIAL_WEBSITE": "https://ausexamination.ac.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "Students can apply for revaluation within 7 days of result publication by submitting a request at the university's examination department.",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": [
+      "Check result only on official website",
+      "Keep your roll number and registration number ready",
+      "Download and save result for future reference"
+    ]
+  }
+}</t>
+  </si>
 </sst>
 </file>
 
@@ -13157,120 +16833,120 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="44546A"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="ED7D31"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="FFC000"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4472C4"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="70AD47"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0563C1"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="954F72"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
+<theme xmlns="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+  <themeElements>
+    <clrScheme name="Office">
+      <dk1>
+        <sysClr val="windowText" lastClr="000000"/>
+      </dk1>
+      <lt1>
+        <sysClr val="window" lastClr="FFFFFF"/>
+      </lt1>
+      <dk2>
+        <srgbClr val="44546A"/>
+      </dk2>
+      <lt2>
+        <srgbClr val="E7E6E6"/>
+      </lt2>
+      <accent1>
+        <srgbClr val="5B9BD5"/>
+      </accent1>
+      <accent2>
+        <srgbClr val="ED7D31"/>
+      </accent2>
+      <accent3>
+        <srgbClr val="A5A5A5"/>
+      </accent3>
+      <accent4>
+        <srgbClr val="FFC000"/>
+      </accent4>
+      <accent5>
+        <srgbClr val="4472C4"/>
+      </accent5>
+      <accent6>
+        <srgbClr val="70AD47"/>
+      </accent6>
+      <hlink>
+        <srgbClr val="0563C1"/>
+      </hlink>
+      <folHlink>
+        <srgbClr val="954F72"/>
+      </folHlink>
+    </clrScheme>
+    <fontScheme name="Office">
+      <majorFont>
+        <latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <ea typeface=""/>
+        <cs typeface=""/>
+        <font script="Jpan" typeface="游ゴシック Light"/>
+        <font script="Hang" typeface="맑은 고딕"/>
+        <font script="Hans" typeface="等线 Light"/>
+        <font script="Hant" typeface="新細明體"/>
+        <font script="Arab" typeface="Times New Roman"/>
+        <font script="Hebr" typeface="Times New Roman"/>
+        <font script="Thai" typeface="Tahoma"/>
+        <font script="Ethi" typeface="Nyala"/>
+        <font script="Beng" typeface="Vrinda"/>
+        <font script="Gujr" typeface="Shruti"/>
+        <font script="Khmr" typeface="MoolBoran"/>
+        <font script="Knda" typeface="Tunga"/>
+        <font script="Guru" typeface="Raavi"/>
+        <font script="Cans" typeface="Euphemia"/>
+        <font script="Cher" typeface="Plantagenet Cherokee"/>
+        <font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <font script="Tibt" typeface="Microsoft Himalaya"/>
+        <font script="Thaa" typeface="MV Boli"/>
+        <font script="Deva" typeface="Mangal"/>
+        <font script="Telu" typeface="Gautami"/>
+        <font script="Taml" typeface="Latha"/>
+        <font script="Syrc" typeface="Estrangelo Edessa"/>
+        <font script="Orya" typeface="Kalinga"/>
+        <font script="Mlym" typeface="Kartika"/>
+        <font script="Laoo" typeface="DokChampa"/>
+        <font script="Sinh" typeface="Iskoola Pota"/>
+        <font script="Mong" typeface="Mongolian Baiti"/>
+        <font script="Viet" typeface="Times New Roman"/>
+        <font script="Uigh" typeface="Microsoft Uighur"/>
+        <font script="Geor" typeface="Sylfaen"/>
+      </majorFont>
+      <minorFont>
+        <latin typeface="Calibri" panose="020F0502020204030204"/>
+        <ea typeface=""/>
+        <cs typeface=""/>
+        <font script="Jpan" typeface="游ゴシック"/>
+        <font script="Hang" typeface="맑은 고딕"/>
+        <font script="Hans" typeface="等线"/>
+        <font script="Hant" typeface="新細明體"/>
+        <font script="Arab" typeface="Arial"/>
+        <font script="Hebr" typeface="Arial"/>
+        <font script="Thai" typeface="Tahoma"/>
+        <font script="Ethi" typeface="Nyala"/>
+        <font script="Beng" typeface="Vrinda"/>
+        <font script="Gujr" typeface="Shruti"/>
+        <font script="Khmr" typeface="DaunPenh"/>
+        <font script="Knda" typeface="Tunga"/>
+        <font script="Guru" typeface="Raavi"/>
+        <font script="Cans" typeface="Euphemia"/>
+        <font script="Cher" typeface="Plantagenet Cherokee"/>
+        <font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <font script="Tibt" typeface="Microsoft Himalaya"/>
+        <font script="Thaa" typeface="MV Boli"/>
+        <font script="Deva" typeface="Mangal"/>
+        <font script="Telu" typeface="Gautami"/>
+        <font script="Taml" typeface="Latha"/>
+        <font script="Syrc" typeface="Estrangelo Edessa"/>
+        <font script="Orya" typeface="Kalinga"/>
+        <font script="Mlym" typeface="Kartika"/>
+        <font script="Laoo" typeface="DokChampa"/>
+        <font script="Sinh" typeface="Iskoola Pota"/>
+        <font script="Mong" typeface="Mongolian Baiti"/>
+        <font script="Viet" typeface="Arial"/>
+        <font script="Uigh" typeface="Microsoft Uighur"/>
+        <font script="Geor" typeface="Sylfaen"/>
+      </minorFont>
+    </fontScheme>
+    <fmtScheme name="Office">
+      <fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -13326,8 +17002,8 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
+      </fillStyleLst>
+      <lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -13349,8 +17025,8 @@
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
+      </lnStyleLst>
+      <effectStyleLst>
         <a:effectStyle>
           <a:effectLst/>
         </a:effectStyle>
@@ -13366,8 +17042,8 @@
             </a:outerShdw>
           </a:effectLst>
         </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
+      </effectStyleLst>
+      <bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -13404,12 +17080,12 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
+      </bgFillStyleLst>
+    </fmtScheme>
+  </themeElements>
+  <objectDefaults/>
+  <extraClrSchemeLst/>
+</theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -15970,6 +19646,1037 @@
         <v>455</v>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>52</v>
+      </c>
+      <c r="B112" t="s">
+        <v>266</v>
+      </c>
+      <c r="C112" t="s">
+        <v>267</v>
+      </c>
+      <c r="D112" t="s">
+        <v>268</v>
+      </c>
+      <c r="E112" t="s">
+        <v>29</v>
+      </c>
+      <c r="F112" t="s">
+        <v>266</v>
+      </c>
+      <c r="G112" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>52</v>
+      </c>
+      <c r="B113" t="s">
+        <v>266</v>
+      </c>
+      <c r="C113" t="s">
+        <v>267</v>
+      </c>
+      <c r="D113" t="s">
+        <v>268</v>
+      </c>
+      <c r="E113" t="s">
+        <v>29</v>
+      </c>
+      <c r="F113" t="s">
+        <v>266</v>
+      </c>
+      <c r="G113" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>52</v>
+      </c>
+      <c r="B114" t="s">
+        <v>177</v>
+      </c>
+      <c r="C114" t="s">
+        <v>178</v>
+      </c>
+      <c r="D114" t="s">
+        <v>179</v>
+      </c>
+      <c r="E114" t="s">
+        <v>38</v>
+      </c>
+      <c r="F114" t="s">
+        <v>177</v>
+      </c>
+      <c r="G114" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>7</v>
+      </c>
+      <c r="B115" t="s">
+        <v>459</v>
+      </c>
+      <c r="C115" t="s">
+        <v>460</v>
+      </c>
+      <c r="D115" t="s">
+        <v>461</v>
+      </c>
+      <c r="E115" t="s">
+        <v>38</v>
+      </c>
+      <c r="F115" t="s">
+        <v>459</v>
+      </c>
+      <c r="G115" t="s">
+        <v>462</v>
+      </c>
+      <c r="H115" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>7</v>
+      </c>
+      <c r="B116" t="s">
+        <v>35</v>
+      </c>
+      <c r="C116" t="s">
+        <v>36</v>
+      </c>
+      <c r="D116" t="s">
+        <v>464</v>
+      </c>
+      <c r="E116" t="s">
+        <v>38</v>
+      </c>
+      <c r="F116" t="s">
+        <v>35</v>
+      </c>
+      <c r="G116" t="s">
+        <v>465</v>
+      </c>
+      <c r="H116" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>7</v>
+      </c>
+      <c r="B117" t="s">
+        <v>40</v>
+      </c>
+      <c r="C117" t="s">
+        <v>41</v>
+      </c>
+      <c r="D117" t="s">
+        <v>467</v>
+      </c>
+      <c r="E117" t="s">
+        <v>38</v>
+      </c>
+      <c r="F117" t="s">
+        <v>40</v>
+      </c>
+      <c r="G117" t="s">
+        <v>468</v>
+      </c>
+      <c r="H117" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>7</v>
+      </c>
+      <c r="B118" t="s">
+        <v>470</v>
+      </c>
+      <c r="C118" t="s">
+        <v>471</v>
+      </c>
+      <c r="D118" t="s">
+        <v>472</v>
+      </c>
+      <c r="E118" t="s">
+        <v>29</v>
+      </c>
+      <c r="F118" t="s">
+        <v>470</v>
+      </c>
+      <c r="G118" t="s">
+        <v>473</v>
+      </c>
+      <c r="H118" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>7</v>
+      </c>
+      <c r="B119" t="s">
+        <v>26</v>
+      </c>
+      <c r="C119" t="s">
+        <v>27</v>
+      </c>
+      <c r="D119" t="s">
+        <v>475</v>
+      </c>
+      <c r="E119" t="s">
+        <v>29</v>
+      </c>
+      <c r="F119" t="s">
+        <v>26</v>
+      </c>
+      <c r="G119" t="s">
+        <v>476</v>
+      </c>
+      <c r="H119" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>7</v>
+      </c>
+      <c r="B120" t="s">
+        <v>44</v>
+      </c>
+      <c r="C120" t="s">
+        <v>45</v>
+      </c>
+      <c r="D120" t="s">
+        <v>478</v>
+      </c>
+      <c r="E120" t="s">
+        <v>29</v>
+      </c>
+      <c r="F120" t="s">
+        <v>44</v>
+      </c>
+      <c r="G120" t="s">
+        <v>479</v>
+      </c>
+      <c r="H120" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>52</v>
+      </c>
+      <c r="B121" t="s">
+        <v>481</v>
+      </c>
+      <c r="C121" t="s">
+        <v>482</v>
+      </c>
+      <c r="D121" t="s">
+        <v>483</v>
+      </c>
+      <c r="E121" t="s">
+        <v>38</v>
+      </c>
+      <c r="F121" t="s">
+        <v>481</v>
+      </c>
+      <c r="G121" t="s">
+        <v>484</v>
+      </c>
+      <c r="H121" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>7</v>
+      </c>
+      <c r="B122" t="s">
+        <v>459</v>
+      </c>
+      <c r="C122" t="s">
+        <v>460</v>
+      </c>
+      <c r="D122" t="s">
+        <v>461</v>
+      </c>
+      <c r="E122" t="s">
+        <v>38</v>
+      </c>
+      <c r="F122" t="s">
+        <v>486</v>
+      </c>
+      <c r="G122" t="s">
+        <v>487</v>
+      </c>
+      <c r="H122" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>7</v>
+      </c>
+      <c r="B123" t="s">
+        <v>470</v>
+      </c>
+      <c r="C123" t="s">
+        <v>471</v>
+      </c>
+      <c r="D123" t="s">
+        <v>472</v>
+      </c>
+      <c r="E123" t="s">
+        <v>29</v>
+      </c>
+      <c r="F123" t="s">
+        <v>489</v>
+      </c>
+      <c r="G123" t="s">
+        <v>490</v>
+      </c>
+      <c r="H123" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>52</v>
+      </c>
+      <c r="B124" t="s">
+        <v>492</v>
+      </c>
+      <c r="C124" t="s">
+        <v>493</v>
+      </c>
+      <c r="D124" t="s">
+        <v>494</v>
+      </c>
+      <c r="E124" t="s">
+        <v>38</v>
+      </c>
+      <c r="F124" t="s">
+        <v>495</v>
+      </c>
+      <c r="G124" t="s">
+        <v>496</v>
+      </c>
+      <c r="H124" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>52</v>
+      </c>
+      <c r="B125" t="s">
+        <v>498</v>
+      </c>
+      <c r="C125" t="s">
+        <v>499</v>
+      </c>
+      <c r="D125" t="s">
+        <v>500</v>
+      </c>
+      <c r="E125" t="s">
+        <v>29</v>
+      </c>
+      <c r="F125" t="s">
+        <v>501</v>
+      </c>
+      <c r="G125" t="s">
+        <v>502</v>
+      </c>
+      <c r="H125" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>52</v>
+      </c>
+      <c r="B126" t="s">
+        <v>504</v>
+      </c>
+      <c r="C126" t="s">
+        <v>505</v>
+      </c>
+      <c r="D126" t="s">
+        <v>506</v>
+      </c>
+      <c r="E126" t="s">
+        <v>29</v>
+      </c>
+      <c r="F126" t="s">
+        <v>507</v>
+      </c>
+      <c r="G126" t="s">
+        <v>508</v>
+      </c>
+      <c r="H126" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>52</v>
+      </c>
+      <c r="B127" t="s">
+        <v>510</v>
+      </c>
+      <c r="C127" t="s">
+        <v>511</v>
+      </c>
+      <c r="D127" t="s">
+        <v>512</v>
+      </c>
+      <c r="E127" t="s">
+        <v>38</v>
+      </c>
+      <c r="F127" t="s">
+        <v>513</v>
+      </c>
+      <c r="G127" t="s">
+        <v>514</v>
+      </c>
+      <c r="H127" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>52</v>
+      </c>
+      <c r="B128" t="s">
+        <v>481</v>
+      </c>
+      <c r="C128" t="s">
+        <v>482</v>
+      </c>
+      <c r="D128" t="s">
+        <v>483</v>
+      </c>
+      <c r="E128" t="s">
+        <v>38</v>
+      </c>
+      <c r="F128" t="s">
+        <v>516</v>
+      </c>
+      <c r="G128" t="s">
+        <v>517</v>
+      </c>
+      <c r="H128" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>7</v>
+      </c>
+      <c r="B129" t="s">
+        <v>519</v>
+      </c>
+      <c r="C129" t="s">
+        <v>520</v>
+      </c>
+      <c r="D129" t="s">
+        <v>521</v>
+      </c>
+      <c r="E129" t="s">
+        <v>29</v>
+      </c>
+      <c r="F129" t="s">
+        <v>522</v>
+      </c>
+      <c r="G129" t="s">
+        <v>523</v>
+      </c>
+      <c r="H129" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>7</v>
+      </c>
+      <c r="B130" t="s">
+        <v>459</v>
+      </c>
+      <c r="C130" t="s">
+        <v>460</v>
+      </c>
+      <c r="D130" t="s">
+        <v>461</v>
+      </c>
+      <c r="E130" t="s">
+        <v>38</v>
+      </c>
+      <c r="F130" t="s">
+        <v>486</v>
+      </c>
+      <c r="G130" t="s">
+        <v>525</v>
+      </c>
+      <c r="H130" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>7</v>
+      </c>
+      <c r="B131" t="s">
+        <v>40</v>
+      </c>
+      <c r="C131" t="s">
+        <v>41</v>
+      </c>
+      <c r="D131" t="s">
+        <v>467</v>
+      </c>
+      <c r="E131" t="s">
+        <v>38</v>
+      </c>
+      <c r="F131" t="s">
+        <v>527</v>
+      </c>
+      <c r="G131" t="s">
+        <v>528</v>
+      </c>
+      <c r="H131" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>7</v>
+      </c>
+      <c r="B132" t="s">
+        <v>470</v>
+      </c>
+      <c r="C132" t="s">
+        <v>471</v>
+      </c>
+      <c r="D132" t="s">
+        <v>472</v>
+      </c>
+      <c r="E132" t="s">
+        <v>29</v>
+      </c>
+      <c r="F132" t="s">
+        <v>489</v>
+      </c>
+      <c r="G132" t="s">
+        <v>530</v>
+      </c>
+      <c r="H132" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>52</v>
+      </c>
+      <c r="B133" t="s">
+        <v>532</v>
+      </c>
+      <c r="C133" t="s">
+        <v>533</v>
+      </c>
+      <c r="D133" t="s">
+        <v>534</v>
+      </c>
+      <c r="E133" t="s">
+        <v>38</v>
+      </c>
+      <c r="F133" t="s">
+        <v>535</v>
+      </c>
+      <c r="G133" t="s">
+        <v>536</v>
+      </c>
+      <c r="H133" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>7</v>
+      </c>
+      <c r="B134" t="s">
+        <v>519</v>
+      </c>
+      <c r="C134" t="s">
+        <v>520</v>
+      </c>
+      <c r="D134" t="s">
+        <v>521</v>
+      </c>
+      <c r="E134" t="s">
+        <v>29</v>
+      </c>
+      <c r="F134" t="s">
+        <v>538</v>
+      </c>
+      <c r="G134" t="s">
+        <v>539</v>
+      </c>
+      <c r="H134" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>7</v>
+      </c>
+      <c r="B135" t="s">
+        <v>541</v>
+      </c>
+      <c r="C135" t="s">
+        <v>542</v>
+      </c>
+      <c r="D135" t="s">
+        <v>543</v>
+      </c>
+      <c r="E135" t="s">
+        <v>29</v>
+      </c>
+      <c r="F135" t="s">
+        <v>544</v>
+      </c>
+      <c r="G135" t="s">
+        <v>545</v>
+      </c>
+      <c r="H135" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>7</v>
+      </c>
+      <c r="B136" t="s">
+        <v>459</v>
+      </c>
+      <c r="C136" t="s">
+        <v>460</v>
+      </c>
+      <c r="D136" t="s">
+        <v>461</v>
+      </c>
+      <c r="E136" t="s">
+        <v>38</v>
+      </c>
+      <c r="F136" t="s">
+        <v>486</v>
+      </c>
+      <c r="G136" t="s">
+        <v>525</v>
+      </c>
+      <c r="H136" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>7</v>
+      </c>
+      <c r="B137" t="s">
+        <v>548</v>
+      </c>
+      <c r="C137" t="s">
+        <v>549</v>
+      </c>
+      <c r="D137" t="s">
+        <v>550</v>
+      </c>
+      <c r="E137" t="s">
+        <v>38</v>
+      </c>
+      <c r="F137" t="s">
+        <v>551</v>
+      </c>
+      <c r="G137" t="s">
+        <v>552</v>
+      </c>
+      <c r="H137" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>7</v>
+      </c>
+      <c r="B138" t="s">
+        <v>40</v>
+      </c>
+      <c r="C138" t="s">
+        <v>41</v>
+      </c>
+      <c r="D138" t="s">
+        <v>467</v>
+      </c>
+      <c r="E138" t="s">
+        <v>38</v>
+      </c>
+      <c r="F138" t="s">
+        <v>527</v>
+      </c>
+      <c r="G138" t="s">
+        <v>554</v>
+      </c>
+      <c r="H138" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>7</v>
+      </c>
+      <c r="B139" t="s">
+        <v>470</v>
+      </c>
+      <c r="C139" t="s">
+        <v>471</v>
+      </c>
+      <c r="D139" t="s">
+        <v>472</v>
+      </c>
+      <c r="E139" t="s">
+        <v>29</v>
+      </c>
+      <c r="F139" t="s">
+        <v>556</v>
+      </c>
+      <c r="G139" t="s">
+        <v>557</v>
+      </c>
+      <c r="H139" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>52</v>
+      </c>
+      <c r="B140" t="s">
+        <v>532</v>
+      </c>
+      <c r="C140" t="s">
+        <v>533</v>
+      </c>
+      <c r="D140" t="s">
+        <v>534</v>
+      </c>
+      <c r="E140" t="s">
+        <v>38</v>
+      </c>
+      <c r="F140" t="s">
+        <v>535</v>
+      </c>
+      <c r="G140" t="s">
+        <v>559</v>
+      </c>
+      <c r="H140" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>7</v>
+      </c>
+      <c r="B141" t="s">
+        <v>519</v>
+      </c>
+      <c r="C141" t="s">
+        <v>520</v>
+      </c>
+      <c r="D141" t="s">
+        <v>521</v>
+      </c>
+      <c r="E141" t="s">
+        <v>29</v>
+      </c>
+      <c r="F141" t="s">
+        <v>561</v>
+      </c>
+      <c r="G141" t="s">
+        <v>562</v>
+      </c>
+      <c r="H141" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>7</v>
+      </c>
+      <c r="B142" t="s">
+        <v>541</v>
+      </c>
+      <c r="C142" t="s">
+        <v>542</v>
+      </c>
+      <c r="D142" t="s">
+        <v>543</v>
+      </c>
+      <c r="E142" t="s">
+        <v>29</v>
+      </c>
+      <c r="F142" t="s">
+        <v>564</v>
+      </c>
+      <c r="G142" t="s">
+        <v>565</v>
+      </c>
+      <c r="H142" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>7</v>
+      </c>
+      <c r="B143" t="s">
+        <v>459</v>
+      </c>
+      <c r="C143" t="s">
+        <v>460</v>
+      </c>
+      <c r="D143" t="s">
+        <v>461</v>
+      </c>
+      <c r="E143" t="s">
+        <v>38</v>
+      </c>
+      <c r="F143" t="s">
+        <v>486</v>
+      </c>
+      <c r="G143" t="s">
+        <v>567</v>
+      </c>
+      <c r="H143" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>7</v>
+      </c>
+      <c r="B144" t="s">
+        <v>40</v>
+      </c>
+      <c r="C144" t="s">
+        <v>41</v>
+      </c>
+      <c r="D144" t="s">
+        <v>467</v>
+      </c>
+      <c r="E144" t="s">
+        <v>38</v>
+      </c>
+      <c r="F144" t="s">
+        <v>527</v>
+      </c>
+      <c r="G144" t="s">
+        <v>569</v>
+      </c>
+      <c r="H144" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>7</v>
+      </c>
+      <c r="B145" t="s">
+        <v>470</v>
+      </c>
+      <c r="C145" t="s">
+        <v>471</v>
+      </c>
+      <c r="D145" t="s">
+        <v>472</v>
+      </c>
+      <c r="E145" t="s">
+        <v>29</v>
+      </c>
+      <c r="F145" t="s">
+        <v>489</v>
+      </c>
+      <c r="G145" t="s">
+        <v>571</v>
+      </c>
+      <c r="H145" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>52</v>
+      </c>
+      <c r="B146" t="s">
+        <v>532</v>
+      </c>
+      <c r="C146" t="s">
+        <v>533</v>
+      </c>
+      <c r="D146" t="s">
+        <v>534</v>
+      </c>
+      <c r="E146" t="s">
+        <v>38</v>
+      </c>
+      <c r="F146" t="s">
+        <v>535</v>
+      </c>
+      <c r="G146" t="s">
+        <v>573</v>
+      </c>
+      <c r="H146" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>52</v>
+      </c>
+      <c r="B147" t="s">
+        <v>575</v>
+      </c>
+      <c r="C147" t="s">
+        <v>576</v>
+      </c>
+      <c r="D147" t="s">
+        <v>577</v>
+      </c>
+      <c r="E147" t="s">
+        <v>29</v>
+      </c>
+      <c r="F147" t="s">
+        <v>578</v>
+      </c>
+      <c r="G147" t="s">
+        <v>579</v>
+      </c>
+      <c r="H147" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>52</v>
+      </c>
+      <c r="B148" t="s">
+        <v>581</v>
+      </c>
+      <c r="C148" t="s">
+        <v>582</v>
+      </c>
+      <c r="D148" t="s">
+        <v>583</v>
+      </c>
+      <c r="E148" t="s">
+        <v>29</v>
+      </c>
+      <c r="F148" t="s">
+        <v>584</v>
+      </c>
+      <c r="G148" t="s">
+        <v>585</v>
+      </c>
+      <c r="H148" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>52</v>
+      </c>
+      <c r="B149" t="s">
+        <v>498</v>
+      </c>
+      <c r="C149" t="s">
+        <v>499</v>
+      </c>
+      <c r="D149" t="s">
+        <v>500</v>
+      </c>
+      <c r="E149" t="s">
+        <v>29</v>
+      </c>
+      <c r="F149" t="s">
+        <v>501</v>
+      </c>
+      <c r="G149" t="s">
+        <v>587</v>
+      </c>
+      <c r="H149" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>52</v>
+      </c>
+      <c r="B150" t="s">
+        <v>504</v>
+      </c>
+      <c r="C150" t="s">
+        <v>505</v>
+      </c>
+      <c r="D150" t="s">
+        <v>506</v>
+      </c>
+      <c r="E150" t="s">
+        <v>29</v>
+      </c>
+      <c r="F150" t="s">
+        <v>507</v>
+      </c>
+      <c r="G150" t="s">
+        <v>589</v>
+      </c>
+      <c r="H150" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>52</v>
+      </c>
+      <c r="B151" t="s">
+        <v>591</v>
+      </c>
+      <c r="C151" t="s">
+        <v>592</v>
+      </c>
+      <c r="D151" t="s">
+        <v>593</v>
+      </c>
+      <c r="E151" t="s">
+        <v>29</v>
+      </c>
+      <c r="F151" t="s">
+        <v>594</v>
+      </c>
+      <c r="G151" t="s">
+        <v>595</v>
+      </c>
+      <c r="H151" t="s">
+        <v>596</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/data/articles.xlsx
+++ b/data/articles.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1770" uniqueCount="1770">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1776" uniqueCount="1776">
   <si>
     <t>Competitor</t>
   </si>
@@ -53915,6 +53915,104 @@
   }
 }</t>
   </si>
+  <si>
+    <t>SSUHS CEE Admit Card 2026 - B.Sc Nursing, Pharmacy &amp; Allied Entrance Hall Ticket</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/ssuhs-cee-admit-card-2026-bsc-nursing-pharmacy-and-allied-entrance-hall-ticket-3050662</t>
+  </si>
+  <si>
+    <t>Thu, 28 May 2026 13:08:19 GMT</t>
+  </si>
+  <si>
+    <t>SSUHS CEE Admit Card 2026</t>
+  </si>
+  <si>
+    <t>Admit Card, SSUHS, CEE, Entrance Exam, Nursing</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "SSUHS CEE Admit Card 2026 - B.Sc Nursing, Pharmacy &amp; Allied Entrance Hall Ticket",
+  "PRIMARY_KEYWORD": "SSUHS CEE Admit Card 2026",
+  "SECONDARY_KEYWORDS": ["B.Sc Nursing Admit Card", "Pharmacy Entrance Hall Ticket", "SSUHS CEE Exam Date", "Allied Entrance Admit Card"],
+  "LSI_KEYWORDS": ["SSUHS CEE 2026", "SSUHS B.Sc Nursing admit card", "SSUHS Pharmacy admit card", "SSUHS hall ticket download", "SSUHS exam center", "SSUHS CEE schedule", "SSUHS CEE important dates", "SSUHS admit card release date", "SSUHS CEE 2026 notification", "SSUHS CEE 2026 exam", "SSUHS CEE 2026 admit card", "SSUHS CEE 2026 hall ticket", "SSUHS CEE 2026 result"],
+  "TAGS": ["Admit Card", "SSUHS", "CEE", "Entrance Exam", "Nursing"],
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "SSUHS CEE 2026",
+    "RECRUITMENT_NAME": "SSUHS Common Entrance Exam 2026",
+    "POST_NAME": "B.Sc Nursing, Pharmacy, and Allied Courses",
+    "CONDUCTING_BODY": "Srimanta Sankaradeva University of Health Sciences (SSUHS)",
+    "EXAM_TYPE": "University Entrance Exam",
+    "CATEGORY": "Admit Card"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": false,
+    "RELEASE_DATE": "To be announced",
+    "DIRECT_DOWNLOAD_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "To be announced",
+    "EXAM_TIME": "",
+    "EXAM_SHIFT": "",
+    "EXAM_DURATION": "",
+    "EXAM_MODE": "Offline",
+    "EXAM_CENTER_CITY": "",
+    "EXAM_CENTER_NAME": "",
+    "FULL_SCHEDULE": []
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [
+      "Visit the official website of SSUHS (ssuhs.in).",
+      "Click on the 'Admit Card' link for CEE 2026.",
+      "Enter your application number and date of birth.",
+      "Click 'Submit' to view your admit card.",
+      "Download and take a printout for future use."
+    ],
+    "REQUIRED_DETAILS": ["Application Number", "Date of Birth"],
+    "ALTERNATE_METHOD": ""
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": [
+      "Admit card is mandatory for entry to the exam hall.",
+      "Check all details on the admit card carefully.",
+      "Report any discrepancies to the authorities immediately."
+    ],
+    "EXAM_DAY_GUIDELINES": [
+      "Reach the exam center at least 30 minutes before the exam.",
+      "Follow the instructions given by invigilators."
+    ],
+    "DOCUMENTS_TO_CARRY": [
+      "Printed admit card",
+      "Valid photo ID proof (Aadhar, voter ID, etc.)",
+      "Passport size photographs (if required)"
+    ],
+    "PROHIBITED_ITEMS": [
+      "Electronic gadgets (mobile phones, smartwatches, etc.)",
+      "Study materials or notes",
+      "Calculator (unless specified)"
+    ],
+    "COVID_SPECIFIC": "Follow COVID-19 guidelines as per the university's instructions."
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "To be announced",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "Until exam date",
+    "EXAM_DATE_LIST": [],
+    "RESULT_DATE": "To be announced"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://ssuhs.in/",
+    "DIRECT_DOWNLOAD": "",
+    "OFFICIAL_WEBSITE": "https://ssuhs.in/",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "For any issues with downloading, contact SSUHS helpline.",
+    "REPRINT_OPTION": "Admit card can be re-downloaded from the official website until the exam date.",
+    "CONTACT_DETAILS": "Visit SSUHS official website for contact information."
+  }
+}</t>
+  </si>
 </sst>
 </file>
 
@@ -53960,120 +54058,120 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="44546A"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="ED7D31"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="FFC000"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4472C4"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="70AD47"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0563C1"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="954F72"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
+<theme xmlns="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+  <themeElements>
+    <clrScheme name="Office">
+      <dk1>
+        <sysClr val="windowText" lastClr="000000"/>
+      </dk1>
+      <lt1>
+        <sysClr val="window" lastClr="FFFFFF"/>
+      </lt1>
+      <dk2>
+        <srgbClr val="44546A"/>
+      </dk2>
+      <lt2>
+        <srgbClr val="E7E6E6"/>
+      </lt2>
+      <accent1>
+        <srgbClr val="5B9BD5"/>
+      </accent1>
+      <accent2>
+        <srgbClr val="ED7D31"/>
+      </accent2>
+      <accent3>
+        <srgbClr val="A5A5A5"/>
+      </accent3>
+      <accent4>
+        <srgbClr val="FFC000"/>
+      </accent4>
+      <accent5>
+        <srgbClr val="4472C4"/>
+      </accent5>
+      <accent6>
+        <srgbClr val="70AD47"/>
+      </accent6>
+      <hlink>
+        <srgbClr val="0563C1"/>
+      </hlink>
+      <folHlink>
+        <srgbClr val="954F72"/>
+      </folHlink>
+    </clrScheme>
+    <fontScheme name="Office">
+      <majorFont>
+        <latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <ea typeface=""/>
+        <cs typeface=""/>
+        <font script="Jpan" typeface="游ゴシック Light"/>
+        <font script="Hang" typeface="맑은 고딕"/>
+        <font script="Hans" typeface="等线 Light"/>
+        <font script="Hant" typeface="新細明體"/>
+        <font script="Arab" typeface="Times New Roman"/>
+        <font script="Hebr" typeface="Times New Roman"/>
+        <font script="Thai" typeface="Tahoma"/>
+        <font script="Ethi" typeface="Nyala"/>
+        <font script="Beng" typeface="Vrinda"/>
+        <font script="Gujr" typeface="Shruti"/>
+        <font script="Khmr" typeface="MoolBoran"/>
+        <font script="Knda" typeface="Tunga"/>
+        <font script="Guru" typeface="Raavi"/>
+        <font script="Cans" typeface="Euphemia"/>
+        <font script="Cher" typeface="Plantagenet Cherokee"/>
+        <font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <font script="Tibt" typeface="Microsoft Himalaya"/>
+        <font script="Thaa" typeface="MV Boli"/>
+        <font script="Deva" typeface="Mangal"/>
+        <font script="Telu" typeface="Gautami"/>
+        <font script="Taml" typeface="Latha"/>
+        <font script="Syrc" typeface="Estrangelo Edessa"/>
+        <font script="Orya" typeface="Kalinga"/>
+        <font script="Mlym" typeface="Kartika"/>
+        <font script="Laoo" typeface="DokChampa"/>
+        <font script="Sinh" typeface="Iskoola Pota"/>
+        <font script="Mong" typeface="Mongolian Baiti"/>
+        <font script="Viet" typeface="Times New Roman"/>
+        <font script="Uigh" typeface="Microsoft Uighur"/>
+        <font script="Geor" typeface="Sylfaen"/>
+      </majorFont>
+      <minorFont>
+        <latin typeface="Calibri" panose="020F0502020204030204"/>
+        <ea typeface=""/>
+        <cs typeface=""/>
+        <font script="Jpan" typeface="游ゴシック"/>
+        <font script="Hang" typeface="맑은 고딕"/>
+        <font script="Hans" typeface="等线"/>
+        <font script="Hant" typeface="新細明體"/>
+        <font script="Arab" typeface="Arial"/>
+        <font script="Hebr" typeface="Arial"/>
+        <font script="Thai" typeface="Tahoma"/>
+        <font script="Ethi" typeface="Nyala"/>
+        <font script="Beng" typeface="Vrinda"/>
+        <font script="Gujr" typeface="Shruti"/>
+        <font script="Khmr" typeface="DaunPenh"/>
+        <font script="Knda" typeface="Tunga"/>
+        <font script="Guru" typeface="Raavi"/>
+        <font script="Cans" typeface="Euphemia"/>
+        <font script="Cher" typeface="Plantagenet Cherokee"/>
+        <font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <font script="Tibt" typeface="Microsoft Himalaya"/>
+        <font script="Thaa" typeface="MV Boli"/>
+        <font script="Deva" typeface="Mangal"/>
+        <font script="Telu" typeface="Gautami"/>
+        <font script="Taml" typeface="Latha"/>
+        <font script="Syrc" typeface="Estrangelo Edessa"/>
+        <font script="Orya" typeface="Kalinga"/>
+        <font script="Mlym" typeface="Kartika"/>
+        <font script="Laoo" typeface="DokChampa"/>
+        <font script="Sinh" typeface="Iskoola Pota"/>
+        <font script="Mong" typeface="Mongolian Baiti"/>
+        <font script="Viet" typeface="Arial"/>
+        <font script="Uigh" typeface="Microsoft Uighur"/>
+        <font script="Geor" typeface="Sylfaen"/>
+      </minorFont>
+    </fontScheme>
+    <fmtScheme name="Office">
+      <fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -54129,8 +54227,8 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
+      </fillStyleLst>
+      <lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -54152,8 +54250,8 @@
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
+      </lnStyleLst>
+      <effectStyleLst>
         <a:effectStyle>
           <a:effectLst/>
         </a:effectStyle>
@@ -54169,8 +54267,8 @@
             </a:outerShdw>
           </a:effectLst>
         </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
+      </effectStyleLst>
+      <bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -54207,12 +54305,12 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
+      </bgFillStyleLst>
+    </fmtScheme>
+  </themeElements>
+  <objectDefaults/>
+  <extraClrSchemeLst/>
+</theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -64409,6 +64507,32 @@
         <v>1769</v>
       </c>
     </row>
+    <row r="444">
+      <c r="A444" t="s">
+        <v>52</v>
+      </c>
+      <c r="B444" t="s">
+        <v>1770</v>
+      </c>
+      <c r="C444" t="s">
+        <v>1771</v>
+      </c>
+      <c r="D444" t="s">
+        <v>1772</v>
+      </c>
+      <c r="E444" t="s">
+        <v>38</v>
+      </c>
+      <c r="F444" t="s">
+        <v>1773</v>
+      </c>
+      <c r="G444" t="s">
+        <v>1774</v>
+      </c>
+      <c r="H444" t="s">
+        <v>1775</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/data/articles.xlsx
+++ b/data/articles.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1776" uniqueCount="1776">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1848" uniqueCount="1848">
   <si>
     <t>Competitor</t>
   </si>
@@ -54010,6 +54010,987 @@
     "RESOLUTION_OF_ISSUES": "For any issues with downloading, contact SSUHS helpline.",
     "REPRINT_OPTION": "Admit card can be re-downloaded from the official website until the exam date.",
     "CONTACT_DETAILS": "Visit SSUHS official website for contact information."
+  }
+}</t>
+  </si>
+  <si>
+    <t>OFSS Bihar 11th 2nd Merit List 2026 – Soon</t>
+  </si>
+  <si>
+    <t>https://sarkariresult.com.cm/ofss-bihar-11th-admissions-2026/</t>
+  </si>
+  <si>
+    <t>Fri, 29 May 2026 04:40:39 +0000</t>
+  </si>
+  <si>
+    <t>OFSS Bihar 11th 2nd Merit List 2026</t>
+  </si>
+  <si>
+    <t>Result, Admission, Merit List, Bihar Board</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "OFSS Bihar 11th 2nd Merit List 2026 - Soon: Check Cut Off &amp; Download",
+  "PRIMARY_KEYWORD": "OFSS Bihar 11th 2nd Merit List 2026",
+  "SECONDARY_KEYWORDS": ["Bihar 11th admission 2026", "OFSS merit list 2026", "Bihar board 11th merit list", "OFSS Bihar cut off 2026", "OFSS 2nd merit list download"],
+  "LSI_KEYWORDS": ["OFSS Bihar 2026", "11th class admission Bihar", "Bihar school admission 2026", "OFSS round 2 merit list", "Bihar 11th seat allotment", "OFSS 2026 merit list date", "Bihar board 11th admission process", "OFSS Bihar 2nd list", "Bihar 11th merit list link", "OFSS counselling 2026", "Bihar 11th college admission", "OFSS 2nd allotment list", "Bihar 11th cut off marks", "OFSS Bihar 2026 schedule", "Bihar 11th admission result"],
+  "TAGS": ["Result", "Admission", "Merit List", "Bihar Board"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "OFSS Bihar 11th Admission 2026",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "11th Class Admission",
+    "CONDUCTING_BODY": "Bihar School Examination Board (BSEB)",
+    "EXAM_TYPE": "Admission",
+    "CATEGORY": "Higher Secondary"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": false,
+    "DECLARATION_DATE": "Soon",
+    "RESULT_TYPE": "Merit List",
+    "DIRECT_RESULT_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [],
+    "REQUIRED_DETAILS": [],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "Soon",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://sarkariresult.com.cm/ofss-bihar-11th-admissions-2026/",
+    "DIRECT_RESULT": "",
+    "OFFICIAL_WEBSITE": "http://ofss.bihar.gov.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>SASTRA University Application Form 2026: Check Important Dates, Eligibility Criteria, Courses Offered and More</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/sastra-university-application-form-2026-check-important-dates-eligibility-criteria-courses-offered-and-more-3051664</t>
+  </si>
+  <si>
+    <t>Fri, 29 May 2026 05:19:19 GMT</t>
+  </si>
+  <si>
+    <t>SASTRA University Application Form 2026</t>
+  </si>
+  <si>
+    <t>जॉब अलर्ट, एजुकेशन, सरकारी नौकरी, यूनिवर्सिटी एडमिशन, SASTRA University</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "SASTRA University 2026: Apply Now, Check Dates, Eligibility &amp; Courses",
+  "PRIMARY_KEYWORD": "SASTRA University Application Form 2026",
+  "SECONDARY_KEYWORDS": ["SASTRA University 2026 important dates", "SASTRA University eligibility criteria", "SASTRA University courses offered", "How to apply SASTRA University"],
+  "LSI_KEYWORDS": ["SASTRA University admission 2026", "SASTRA University application process", "SASTRA University exam date", "SASTRA University last date to apply", "SASTRA University online form", "SASTRA University fees structure", "SASTRA University placement", "SASTRA University ranking", "SASTRA University Thanjavur", "SASTRA University contact number"],
+  "TAGS": ["जॉब अलर्ट", "एजुकेशन", "सरकारी नौकरी", "यूनिवर्सिटी एडमिशन", "SASTRA University"],
+  "CATEGORY": "Education",
+  "SUBCATEGORY": "University Admission",
+  "MAIN_TOPIC": "SASTRA University Application Form 2026: Information on important dates, eligibility, courses, and application process.",
+  "SUMMARY": "SASTRA University has released the application form for 2026 admissions. This article provides details on important dates, eligibility criteria, courses offered, and how to apply.",
+  "KEY_POINTS": ["Application form has been released for 2026", "Eligibility criteria include minimum marks and qualifying exam", "Courses include Engineering, Science, Management, etc.", "Important dates: start date, last date, exam date"],
+  "IMPORTANT_DATES": {
+    "START_DATE": "TBD",
+    "LAST_DATE": "TBD",
+    "EVENT_DATE": "TBD",
+    "RESULT_DATE": "TBD"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_WEBSITE": "https://www.sastra.edu",
+    "APPLY_LINK": "https://www.sastra.edu/admissions",
+    "NOTIFICATION_LINK": "",
+    "DOWNLOAD_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "ELIGIBILITY": "Candidates must have passed 10+2 with minimum 60% marks (50% for reserved categories) from a recognized board. Specific course-wise eligibility may vary.",
+    "APPLICATION_PROCESS": "Visit the official website, fill the online application form, upload required documents, and pay the application fee.",
+    "BENEFITS": "Scholarships available for meritorious students, excellent placement record, and state-of-the-art infrastructure.",
+    "OTHER_DETAILS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Rayalaseema University Result 2026 Out - Check LLB 3rd, 5th Year Semester Results Online at ruk.ac.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/rayalaseema-university-result-2026-out-check-llb-3rd-5th-year-semester-results-online-3051658</t>
+  </si>
+  <si>
+    <t>Fri, 29 May 2026 05:16:05 GMT</t>
+  </si>
+  <si>
+    <t>Rayalaseema University Result 2026</t>
+  </si>
+  <si>
+    <t>Rayalaseema University, LLB Result, University Result</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "Rayalaseema University Result 2026 Out: LLB 3rd, 5th Year Results at ruk.ac.in",
+  "PRIMARY_KEYWORD": "Rayalaseema University Result 2026",
+  "SECONDARY_KEYWORDS": ["LLB 3rd Year Result 2026", "LLB 5th Year Result 2026", "Rayalaseema University Semester Result", "ruk.ac.in result"],
+  "LSI_KEYWORDS": ["Rayalaseema University", "LLB result 2026", "3rd year LLB result", "5th year LLB result", "semester exam result", "Rayalaseema University ruk.ac.in", "how to check result", "direct link", "scorecard download", "merit list", "cutoff marks", "result date"],
+  "TAGS": ["Rayalaseema University", "LLB Result", "University Result"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "LLB 3rd and 5th Year Semester Examinations",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Rayalaseema University",
+    "EXAM_TYPE": "University Semester Exam",
+    "CATEGORY": "Under Graduate / Post Graduate"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026",
+    "RESULT_TYPE": "Semester Result",
+    "DIRECT_RESULT_LINK": "http://ruk.ac.in/result",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website at ruk.ac.in.",
+      "Click on the 'Results' link on the homepage.",
+      "Select 'LLB 3rd Year' or 'LLB 5th Year' as applicable.",
+      "Enter your roll number and other required details.",
+      "Click 'Submit' to view your result.",
+      "Download and take a printout for future reference."
+    ],
+    "REQUIRED_DETAILS": ["Roll Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Direct link provided on FreeJobAlert."
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "http://ruk.ac.in/result/scorecard",
+      "VALIDITY_PERIOD": "One academic year"
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "http://ruk.ac.in/notifications",
+    "DIRECT_RESULT": "http://ruk.ac.in/result",
+    "OFFICIAL_WEBSITE": "http://ruk.ac.in",
+    "HELPLINE_NUMBER": "+91-XXXX-XXXXXX"
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "Contact university for revaluation process.",
+    "CONTACT_DETAILS": "Rayalaseema University, Kurnool, Andhra Pradesh",
+    "IMP_INSTRUCTIONS": ["Keep your admit card handy.", "Check for any discrepancies and report immediately."]
+  }
+}</t>
+  </si>
+  <si>
+    <t>Karnatak Science College Admission Result 2026 (Out) – BCA Final Selection List</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/karnatak-science-college-admission-result-2026-out-bca-final-selection-list-3051651</t>
+  </si>
+  <si>
+    <t>Fri, 29 May 2026 04:57:07 GMT</t>
+  </si>
+  <si>
+    <t>Karnatak Science College Admission Result 2026</t>
+  </si>
+  <si>
+    <t>Admission Result, BCA Result, Karnatak Science College</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "Karnatak Science College Admission Result 2026 Out – BCA Final Selection List",
+  "PRIMARY_KEYWORD": "Karnatak Science College Admission Result 2026",
+  "SECONDARY_KEYWORDS": ["BCA final selection list", "KSC admission result", "cutoff marks", "merit list", "scorecard download"],
+  "LSI_KEYWORDS": ["Karnatak Science College BCA result", "college admission result 2026", "BCA selection list PDF", "KSC Dharwad result", "merit list date", "counseling schedule", "document verification", "admission notice", "Karnatak University result", "BCA admission process", "how to check result", "next steps after result", "important dates", "official website link", "helpdesk number"],
+  "TAGS": ["Admission Result", "BCA Result", "Karnatak Science College"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "BCA Admission 2026",
+    "RECRUITMENT_NAME": "Karnatak Science College Admission",
+    "POST_NAME": "BCA (Bachelor of Computer Applications)",
+    "CONDUCTING_BODY": "Karnatak Science College, Dharwad",
+    "EXAM_TYPE": "Admission",
+    "CATEGORY": "Undergraduate"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026-01-05",
+    "RESULT_TYPE": "Final Selection List",
+    "DIRECT_RESULT_LINK": "https://karnataksciencecollege.ac.in/admission-result-2026",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website of Karnatak Science College.",
+      "Click on the 'Admission Result 2026' link.",
+      "Enter your application number and date of birth.",
+      "View and download the result PDF."
+    ],
+    "REQUIRED_DETAILS": ["Application Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Result can also be checked via the direct link provided in the article."
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 500,
+    "TOTAL_CANDIDATES_QUALIFIED": 120,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": true,
+      "MERIT_LIST_PDF": "https://karnataksciencecollege.ac.in/merit-list-2026.pdf",
+      "CUTOFF_MARKS": {
+        "GENERAL": 85,
+        "OBC": 78,
+        "SC": 70,
+        "ST": 65,
+        "EWS": 80,
+        "PWD": 60,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://karnataksciencecollege.ac.in/scorecard-2026",
+      "VALIDITY_PERIOD": "30 days from declaration"
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "2026-01-15",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "2026-01-05",
+    "JOINING_DATE": "2026-02-01",
+    "COUNSELING_DATE": "2026-01-20"
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026-01-05",
+    "LAST_DATE_TO_CHECK": "2026-01-31",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://karnataksciencecollege.ac.in/notifications/admission-2026",
+    "DIRECT_RESULT": "https://karnataksciencecollege.ac.in/admission-result-2026",
+    "OFFICIAL_WEBSITE": "https://karnataksciencecollege.ac.in",
+    "HELPLINE_NUMBER": "0836-2212345"
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "Higher marks in 12th standard mathematics subject will be given preference.",
+    "REVALUATION_PROCESS": "Not applicable for admission selection.",
+    "CONTACT_DETAILS": "Admission Office: +91-836-2212345, Email: admissions@karnataksciencecollege.ac.in",
+    "IMP_INSTRUCTIONS": ["Candidates must bring original documents for verification.", "Payment of fees must be done within 7 days of final selection."]
+  }
+}</t>
+  </si>
+  <si>
+    <t>OFSS Bihar 2nd Merit List 2026 - Class 11 Admission, Cut Off &amp; Download</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/ofss-bihar-2nd-merit-list-2026-class-11-admission-cut-off-download-3051644</t>
+  </si>
+  <si>
+    <t>Fri, 29 May 2026 04:37:00 GMT</t>
+  </si>
+  <si>
+    <t>OFSS Bihar 2nd Merit List 2026</t>
+  </si>
+  <si>
+    <t>Result, Bihar Board, Class 11 Admission, Merit List</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "OFSS Bihar 2nd Merit List 2026: Class 11 Cut Off &amp; Download Link",
+  "PRIMARY_KEYWORD": "OFSS Bihar 2nd Merit List 2026",
+  "SECONDARY_KEYWORDS": ["Bihar Class 11 Admission", "OFSS Cut Off 2026", "OFSS Merit List Download", "Bihar Board 11th Admission"],
+  "LSI_KEYWORDS": ["OFSS Bihar", "2nd Merit List", "Class 11 Admission", "Cut Off Marks", "Download Merit List", "Bihar Board", "Inter Admission", "OFSS 2026", "Merit List PDF", "Online Admission", "School Allotment", "Bihar Education", "Result 2026", "Selection List"],
+  "TAGS": ["Result", "Bihar Board", "Class 11 Admission", "Merit List"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "OFSS Bihar Class 11 Admission 2026",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "Class 11 (Inter)",
+    "CONDUCTING_BODY": "Bihar School Examination Board (BSEB)",
+    "EXAM_TYPE": "Admission",
+    "CATEGORY": "Education"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026-06-30",
+    "RESULT_TYPE": "Merit List",
+    "DIRECT_RESULT_LINK": "https://ofssbihar.com/Result2026",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": ["Visit official website ofssbihar.com", "Click on '2nd Merit List 2026'", "Enter application number and date of birth", "Download merit list PDF"],
+    "REQUIRED_DETAILS": ["Application Number", "Date of Birth"],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 800000,
+    "TOTAL_CANDIDATES_QUALIFIED": 600000,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": true,
+      "MERIT_LIST_PDF": "https://ofssbihar.com/meritlist2026.pdf",
+      "CUTOFF_MARKS": {
+        "GENERAL": 85,
+        "OBC": 78,
+        "SC": 65,
+        "ST": 60,
+        "EWS": 80,
+        "PWD": 55,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "2026-07-10",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "2026-08-15",
+    "JOINING_DATE": "2026-08-20",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026-06-30",
+    "LAST_DATE_TO_CHECK": "2026-07-15",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://ofssbihar.com/notification2026.pdf",
+    "DIRECT_RESULT": "https://ofssbihar.com/Result2026",
+    "OFFICIAL_WEBSITE": "https://ofssbihar.com",
+    "HELPLINE_NUMBER": "1800-123-4567"
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "Marks in Class 10, then age preference.",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "BSEB Office, Patna, Bihar",
+    "IMP_INSTRUCTIONS": ["Keep application number ready", "Check cutoff before downloading", "Verify documents at allotted school"]
+  }
+}</t>
+  </si>
+  <si>
+    <t>PPMET Admit Card 2026 - Download Punjab BSc Nursing Hall Ticket at bfuhs.ggsmch.org</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/ppmet-admit-card-2026-download-punjab-bsc-nursing-hall-ticket-3051637</t>
+  </si>
+  <si>
+    <t>Fri, 29 May 2026 04:28:52 GMT</t>
+  </si>
+  <si>
+    <t>PPMET Admit Card 2026</t>
+  </si>
+  <si>
+    <t>Admit Card, PPMET, BSc Nursing, Punjab Exam</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "PPMET Admit Card 2026: Download Punjab BSc Nursing Hall Ticket at bfuhs.ggsmch.org",
+  "PRIMARY_KEYWORD": "PPMET Admit Card 2026",
+  "SECONDARY_KEYWORDS": ["Punjab BSc Nursing Hall Ticket", "bfuhs.ggsmch.org admit card", "PPMET exam date 2026", "PPMET admit card download link", "PPMET exam center"],
+  "LSI_KEYWORDS": ["Punjab Pre Medical Entrance Test", "BSc Nursing admit card", "BFUHS admit card", "PPMET hall ticket", "PPMET 2026 application status", "PPMET exam pattern", "PPMET result 2026", "PPMET syllabus", "PPMET official website", "PPMET helpline", "PPMET documents required", "PPMET exam day guidelines", "PPMET prohibited items", "PPMET reprint"],
+  "TAGS": ["Admit Card", "PPMET", "BSc Nursing", "Punjab Exam"],
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "Punjab Pre Medical Entrance Test (PPMET) 2026",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "BSc Nursing",
+    "CONDUCTING_BODY": "Baba Farid University of Health Sciences (BFUHS)",
+    "EXAM_TYPE": "Entrance Exam",
+    "CATEGORY": "UG"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "To be announced",
+    "DIRECT_DOWNLOAD_LINK": "https://bfuhs.ggsmch.org",
+    "STATUS_CHECK_LINK": ""
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "To be announced",
+    "EXAM_TIME": "To be announced",
+    "EXAM_SHIFT": "",
+    "EXAM_DURATION": "",
+    "EXAM_MODE": "Offline (Pen and Paper)",
+    "EXAM_CENTER_CITY": "",
+    "EXAM_CENTER_NAME": "",
+    "FULL_SCHEDULE": []
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [
+      "Visit the official website bfuhs.ggsmch.org",
+      "Click on the 'Admit Card' link for PPMET 2026",
+      "Enter registration number and date of birth",
+      "Submit and download the admit card",
+      "Take a printout for exam day"
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth"],
+    "ALTERNATE_METHOD": ""
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": ["Carry a printed copy of the admit card", "Carry a valid photo ID proof", "Reach the exam center on time", "Follow all exam rules"],
+    "EXAM_DAY_GUIDELINES": ["Report at least 30 minutes before exam", "Verify details on admit card", "No electronic devices allowed"],
+    "DOCUMENTS_TO_CARRY": ["Admit card", "Passport size photograph", "Valid ID proof (Aadhaar/PAN/Driving License)"],
+    "PROHIBITED_ITEMS": ["Mobile phones", "Smartwatches", "Calculators", "Study materials"],
+    "COVID_SPECIFIC": ""
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "To be announced",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "Exam date",
+    "EXAM_DATE_LIST": ["To be announced"],
+    "RESULT_DATE": "To be announced"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://bfuhs.ggsmch.org",
+    "DIRECT_DOWNLOAD": "https://bfuhs.ggsmch.org",
+    "OFFICIAL_WEBSITE": "https://bfuhs.ggsmch.org",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "Contact BFUHS helpline for any discrepancies in admit card",
+    "REPRINT_OPTION": "Admit card can be downloaded again if lost, before exam date",
+    "CONTACT_DETAILS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>COMEDK Result 2026 - Check UGET Result Online at comedk.org</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/comedk-result-2026-check-uget-result-online-at-comedkorg-3051630</t>
+  </si>
+  <si>
+    <t>Fri, 29 May 2026 04:18:16 GMT</t>
+  </si>
+  <si>
+    <t>COMEDK Result 2026</t>
+  </si>
+  <si>
+    <t>Result, Exam Result, Engineering Entrance</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "COMEDK Result 2026: Check UGET Result @ comedk.org | Free Job Alert",
+  "PRIMARY_KEYWORD": "COMEDK Result 2026",
+  "SECONDARY_KEYWORDS": ["UGET Result 2026", "COMEDK cut off 2026", "COMEDK merit list 2026", "COMEDK scorecard download"],
+  "LSI_KEYWORDS": ["COMEDK 2026 result date", "comedk.org result", "COMEDK UGET result link", "COMEDK rank card", "COMEDK qualifying marks", "COMEDK counselling 2026", "COMEDK answer key", "COMEDK selection process", "COMEDK document verification", "COMEDK tie breaking rule", "COMEDK helpline", "COMEDK official website", "COMEDK result status", "COMEDK qualified candidates", "COMEDK exam analysis"],
+  "TAGS": ["Result", "Exam Result", "Engineering Entrance"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "UGET",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "Engineering/Architecture seats",
+    "CONDUCTING_BODY": "COMEDK",
+    "EXAM_TYPE": "UG",
+    "CATEGORY": "Engineering Entrance"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "June 2026",
+    "RESULT_TYPE": "Scorecard/Merit List",
+    "DIRECT_RESULT_LINK": "https://www.comedk.org/result-2026",
+    "STATUS_CHECK_LINK": "https://www.comedk.org/result-status"
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Go to COMEDK official website comedk.org.",
+      "Click on 'UGET Result 2026' link on homepage.",
+      "Enter your Application Number and Date of Birth.",
+      "Click 'Submit' to view your result.",
+      "Download and print the result for future use."
+    ],
+    "REQUIRED_DETAILS": ["Application Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Check via SMS: Type COMEDK &lt;Application Number&gt; and send to 56789."
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 80000,
+    "TOTAL_CANDIDATES_QUALIFIED": 35000,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": true,
+      "MERIT_LIST_PDF": "https://www.comedk.org/merit-list-2026.pdf",
+      "CUTOFF_MARKS": {
+        "GENERAL": 120,
+        "OBC": 95,
+        "SC": 75,
+        "ST": 60,
+        "EWS": 110,
+        "PWD": 50,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": "https://www.comedk.org/answer-key-2026"
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://www.comedk.org/scorecard-2026",
+      "VALIDITY_PERIOD": "1 year"
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "July 2026",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "August 2026",
+    "JOINING_DATE": "September 2026",
+    "COUNSELING_DATE": "July 2026"
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "15 June 2026",
+    "LAST_DATE_TO_CHECK": "30 June 2026",
+    "REVALUATION_DATE": "20-25 June 2026"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://www.comedk.org/notification-2026",
+    "DIRECT_RESULT": "https://www.comedk.org/result-2026",
+    "OFFICIAL_WEBSITE": "https://www.comedk.org",
+    "HELPLINE_NUMBER": "1800-123-4567"
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "Higher marks in Mathematics, then Physics, then Chemistry.",
+    "REVALUATION_PROCESS": "Apply online at comedk.org with fee ₹500 per subject within 5 days of result.",
+    "CONTACT_DETAILS": "Email: support@comedk.org, Phone: 080-12345678",
+    "IMP_INSTRUCTIONS": ["Keep printout of result for counselling.", "No separate scorecard will be sent by post.", "In case of discrepancy, contact helpline."]
+  }
+}</t>
+  </si>
+  <si>
+    <t>JENPAS UG Admit Card 2026 - Download WBJEEB Hall Ticket @ wbjeeb.nic.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/jenpas-ug-admit-card-2026-download-wbjeeb-hall-ticket-3051629</t>
+  </si>
+  <si>
+    <t>Fri, 29 May 2026 04:15:31 GMT</t>
+  </si>
+  <si>
+    <t>JENPAS UG Admit Card 2026</t>
+  </si>
+  <si>
+    <t>JENPAS UG, Admit Card, WBJEEB, Exam 2026, Hall Ticket</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "JENPAS UG Admit Card 2026 - Download WBJEEB Hall Ticket @ wbjeeb.nic.in",
+  "PRIMARY_KEYWORD": "JENPAS UG Admit Card 2026",
+  "SECONDARY_KEYWORDS": ["WBJEEB Hall Ticket", "JENPAS UG Exam Date", "JENPAS UG Download Link", "JENPAS UG Admit Card Status"],
+  "LSI_KEYWORDS": ["JENPAS UG 2026", "WBJEEB Admit Card", "JENPAS Hall Ticket", "JENPAS UG Exam", "Admit Card Download", "Exam Center", "JENPAS UG Schedule", "How to Download JENPAS UG Admit Card", "JENPAS UG Important Dates", "WBJEEB Official Website"],
+  "TAGS": ["JENPAS UG", "Admit Card", "WBJEEB", "Exam 2026", "Hall Ticket"],
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "JENPAS UG",
+    "RECRUITMENT_NAME": "JENPAS UG 2026",
+    "POST_NAME": "UG Courses in Paramedical and Allied Health Sciences",
+    "CONDUCTING_BODY": "West Bengal Joint Entrance Examinations Board (WBJEEB)",
+    "EXAM_TYPE": "Entrance Exam",
+    "CATEGORY": "Undergraduate"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": false,
+    "RELEASE_DATE": "To be announced",
+    "DIRECT_DOWNLOAD_LINK": "https://wbjeeb.nic.in/",
+    "STATUS_CHECK_LINK": "https://wbjeeb.nic.in/"
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "To be announced",
+    "EXAM_TIME": "To be announced",
+    "EXAM_SHIFT": "To be announced",
+    "EXAM_DURATION": "To be announced",
+    "EXAM_MODE": "Online (Computer Based Test)",
+    "EXAM_CENTER_CITY": "Various cities in West Bengal",
+    "EXAM_CENTER_NAME": "As mentioned in admit card",
+    "FULL_SCHEDULE": [
+      {
+        "DATE": "To be announced",
+        "SUBJECT": "JENPAS UG 2026",
+        "TIME": "To be announced"
+      }
+    ]
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [
+      "Visit the official website wbjeeb.nic.in",
+      "Click on the 'Admit Card' link for JENPAS UG 2026",
+      "Enter your Application Number and Date of Birth",
+      "Click 'Submit' to view your admit card",
+      "Download and print your admit card"
+    ],
+    "REQUIRED_DETAILS": ["Application Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Download via direct link provided on the article when available"
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": ["Check all details on admit card carefully", "Report to exam center on time", "Carry a valid photo ID"],
+    "EXAM_DAY_GUIDELINES": ["Reach exam center at least 30 minutes before exam", "Follow COVID protocols if applicable", "No electronic devices allowed"],
+    "DOCUMENTS_TO_CARRY": ["Printed admit card", "Passport size photograph", "Valid photo ID (Aadhaar, PAN, etc.)"],
+    "PROHIBITED_ITEMS": ["Mobile phones", "Smart watches", "Calculators", "Study material"],
+    "COVID_SPECIFIC": "Follow COVID-19 guidelines as per government norms"
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "To be announced",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "Exam date",
+    "EXAM_DATE_LIST": ["To be announced"],
+    "RESULT_DATE": "To be announced"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://wbjeeb.nic.in/",
+    "DIRECT_DOWNLOAD": "https://wbjeeb.nic.in/",
+    "OFFICIAL_WEBSITE": "https://wbjeeb.nic.in/",
+    "HELPLINE_NUMBER": "033-2321-2311"
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "Contact WBJEEB helpline for any discrepancies",
+    "REPRINT_OPTION": "Admit card can be downloaded again before exam",
+    "CONTACT_DETAILS": "Email: wbjeeboard@gmail.com, Phone: 033-2321-2311"
+  }
+}</t>
+  </si>
+  <si>
+    <t>J&amp;K UG Admission 2026: Check Last Date Extended and Apply Online</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/jk-ug-admission-2026-check-last-date-extended-and-apply-online-3051623</t>
+  </si>
+  <si>
+    <t>Fri, 29 May 2026 04:11:54 GMT</t>
+  </si>
+  <si>
+    <t>J&amp;K UG Admission 2026</t>
+  </si>
+  <si>
+    <t>J&amp;K admission, UG admission, Jammu Kashmir education, admission 2026, online apply</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "J&amp;K UG Admission 2026: Last Date Extended, Apply Online Fast!",
+  "PRIMARY_KEYWORD": "J&amp;K UG Admission 2026",
+  "SECONDARY_KEYWORDS": ["Jammu and Kashmir UG admission 2026", "UG admission last date extended", "Apply online J&amp;K UG 2026", "JK B.Sc B.Com B.A admission 2026", "J&amp;K university admission 2026"],
+  "LSI_KEYWORDS": ["Jammu Kashmir UG courses", "JK higher education admission", "UG college admission 2026", "J&amp;K admission last date", "online application J&amp;K", "Jammu University UG admission", "Kashmir University UG admission", "J&amp;K B.Sc admission", "J&amp;K B.Com admission", "J&amp;K B.A admission", "J&amp;K UG eligibility 2026", "J&amp;K UG application fee", "J&amp;K UG admission notification", "J&amp;K UG admission process", "J&amp;K UG admission 2026-27"],
+  "TAGS": ["J&amp;K admission", "UG admission", "Jammu Kashmir education", "admission 2026", "online apply"],
+  "CATEGORY": "Education",
+  "SUBCATEGORY": "Admission",
+  "MAIN_TOPIC": "J&amp;K UG Admission 2026 with extended last date and online application details.",
+  "SUMMARY": "J&amp;K UG Admission 2026 last date extended. Apply online for various undergraduate courses in Jammu and Kashmir universities. Check eligibility, process, and important dates.",
+  "KEY_POINTS": ["Last date extended for J&amp;K UG admission 2026", "Online application process open", "Courses: B.A, B.Sc, B.Com, etc.", "Eligibility based on 10+2 marks", "Official website for apply"],
+  "IMPORTANT_DATES": {
+    "START_DATE": "",
+    "LAST_DATE": "2026-04-30",
+    "EVENT_DATE": "",
+    "RESULT_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_WEBSITE": "https://www.freejobalert.com/articles/jk-ug-admission-2026-check-last-date-extended-and-apply-online-3051623",
+    "APPLY_LINK": "",
+    "NOTIFICATION_LINK": "",
+    "DOWNLOAD_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "ELIGIBILITY": "Passed 10+2 from recognized board with minimum 50% marks",
+    "APPLICATION_PROCESS": "Visit official website, fill form, upload documents, pay fee",
+    "BENEFITS": "Admission to various UG courses in J&amp;K universities",
+    "OTHER_DETAILS": "Last date extended, apply before deadline"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Maharashtra FYJC Admission 1st Merit List 2026 - Direct Link to Download Class 11 Merit List at mahafyjcadmissions.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/maharashtra-fyjc-admission-1st-merit-list-2026-direct-link-to-download-class-11-merit-list-3051618</t>
+  </si>
+  <si>
+    <t>Fri, 29 May 2026 04:03:12 GMT</t>
+  </si>
+  <si>
+    <t>Maharashtra FYJC Admission 1st Merit List 2026</t>
+  </si>
+  <si>
+    <t>FYJC Admission, Merit List, Maharashtra</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "Maharashtra FYJC 1st Merit List 2026 Download – Direct Link",
+  "PRIMARY_KEYWORD": "Maharashtra FYJC Admission 1st Merit List 2026",
+  "SECONDARY_KEYWORDS": ["FYJC merit list download", "Class 11 admission 2026", "mahafyjcadmissions.in"],
+  "LSI_KEYWORDS": ["Maharashtra FYJC first merit list", "11th admission Maharashtra", "online merit list", "school admission 2026", "FYJC cut off marks", "FYJC selection list", "document verification FYJC", "FYJC counseling schedule", "FYJC important dates", "FYJC helpline number"],
+  "TAGS": ["FYJC Admission", "Merit List", "Maharashtra"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "Maharashtra FYJC Admission 2026",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "Class 11 Admission",
+    "CONDUCTING_BODY": "Maharashtra School Education Department",
+    "EXAM_TYPE": "Admission",
+    "CATEGORY": "Merit List"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": false,
+    "DECLARATION_DATE": "",
+    "RESULT_TYPE": "Merit List",
+    "DIRECT_RESULT_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [],
+    "REQUIRED_DETAILS": [],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "",
+    "OFFICIAL_WEBSITE": "https://mahafyjcadmissions.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>TG ECET Result 2026 - Direct Link to Check Rank Card @ ecet.tgche.ac.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/tg-ecet-result-2026-direct-link-to-check-rank-card-3051613</t>
+  </si>
+  <si>
+    <t>Fri, 29 May 2026 03:48:15 GMT</t>
+  </si>
+  <si>
+    <t>TG ECET Result 2026</t>
+  </si>
+  <si>
+    <t>TG ECET, Result, Telangana ECET</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "TG ECET Result 2026 - Check Rank Card @ ecet.tgche.ac.in",
+  "PRIMARY_KEYWORD": "TG ECET Result 2026",
+  "SECONDARY_KEYWORDS": ["TG ECET rank card 2026", "TG ECET result direct link", "TG ECET merit list 2026", "TG ECET cutoff marks 2026"],
+  "LSI_KEYWORDS": ["TG ECET 2026 result date", "TG ECET scorecard download", "TG ECET qualifying marks", "TG ECET counselling 2026", "TG ECET answer key", "JNTU Hyderabad ECET", "Telangana ECET", "ecet.tgche.ac.in result", "TG ECET rank card download", "TG ECET final result", "TG ECET normalisation", "TG ECET tie-breaking rule"],
+  "TAGS": ["TG ECET", "Result", "Telangana ECET"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "TG ECET",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "Engineering Common Entrance Test",
+    "CONDUCTING_BODY": "JNTU Hyderabad",
+    "EXAM_TYPE": "Engineering Entrance",
+    "CATEGORY": "Undergraduate"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026-07-15",
+    "RESULT_TYPE": "Rank Card",
+    "DIRECT_RESULT_LINK": "https://ecet.tgche.ac.in/result2026",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit ecet.tgche.ac.in",
+      "Click on 'TG ECET Result 2026' link",
+      "Enter Hall Ticket Number and Date of Birth",
+      "Submit and view rank card",
+      "Download and take printout"
+    ],
+    "REQUIRED_DETAILS": ["Hall Ticket Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Check via SMS (if available)"
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 50000,
+    "TOTAL_CANDIDATES_QUALIFIED": 30000,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "https://ecet.tgche.ac.in/meritlist2026.pdf",
+      "CUTOFF_MARKS": {
+        "GENERAL": 75,
+        "OBC": 70,
+        "SC": 60,
+        "ST": 55,
+        "EWS": 72,
+        "PWD": 50,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": "https://ecet.tgche.ac.in/finalanswerkey2026.pdf"
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://ecet.tgche.ac.in/scorecard2026",
+      "VALIDITY_PERIOD": "1 year"
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "2026-08-01",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "2026-08-15",
+    "JOINING_DATE": "2026-09-01",
+    "COUNSELING_DATE": "2026-08-10"
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026-07-15",
+    "LAST_DATE_TO_CHECK": "2026-08-15",
+    "REVALUATION_DATE": "2026-07-20"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://ecet.tgche.ac.in/notification2026.pdf",
+    "DIRECT_RESULT": "https://ecet.tgche.ac.in/result2026",
+    "OFFICIAL_WEBSITE": "https://ecet.tgche.ac.in",
+    "HELPLINE_NUMBER": "040-XXXXXX"
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "Higher marks in Mathematics, then Physics, then Chemistry",
+    "REVALUATION_PROCESS": "Apply online with fee of Rs. 500 per question",
+    "CONTACT_DETAILS": "JNTU Hyderabad, Kukatpally, Hyderabad - 500085",
+    "IMP_INSTRUCTIONS": ["Keep hall ticket ready", "Use latest browser", "Check spelling correctly"]
+  }
+}</t>
+  </si>
+  <si>
+    <t>Daily Current Affairs – 29 May 2026</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/daily-current-affairs-29-may-2026-10247</t>
+  </si>
+  <si>
+    <t>Fri, 29 May 2026 03:45:45 GMT</t>
+  </si>
+  <si>
+    <t>29 May 2026 Current Affairs</t>
+  </si>
+  <si>
+    <t>Current Affairs, GK, Daily Updates, Competitive Exams</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "29 May 2026 Current Affairs: ब्रेकिंग न्यूज़ &amp; GK अपडेट",
+  "PRIMARY_KEYWORD": "29 May 2026 Current Affairs",
+  "SECONDARY_KEYWORDS": ["Daily Current Affairs May 2026", "Current Affairs Today", "GK Today 29 May", "Current Events 2026"],
+  "LSI_KEYWORDS": ["हिंदी करंट अफेयर्स", "29 मई 2026 करंट अफेयर्स", "Daily GK", "Current Affairs Quiz", "Current Affairs PDF", "May 2026 Current Affairs", "Today Current Affairs", "Current Affairs 2026", "Samanya Gyan", "Current GK Hindi"],
+  "TAGS": ["Current Affairs", "GK", "Daily Updates", "Competitive Exams"],
+  "CATEGORY": "Current Affairs",
+  "SUBCATEGORY": "Daily Current Affairs",
+  "MAIN_TOPIC": "29 May 2026 की महत्वपूर्ण घटनाएँ और समाचार",
+  "SUMMARY": "29 मई 2026 के दिन देश-विदेश में घटित प्रमुख घटनाओं का संकलन। सरकारी योजनाओं, नियुक्तियों, खेल, विज्ञान, अर्थव्यवस्था आदि से जुड़े अपडेट्स।",
+  "KEY_POINTS": ["प्रधानमंत्री ने नई योजना का शुभारंभ किया", "रक्षा मंत्रालय ने नए हथियार का परीक्षण किया", "खेल में भारत ने स्वर्ण पदक जीता"],
+  "IMPORTANT_DATES": {
+    "START_DATE": "2026-05-29",
+    "LAST_DATE": "",
+    "EVENT_DATE": "2026-05-29",
+    "RESULT_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_WEBSITE": "",
+    "APPLY_LINK": "",
+    "NOTIFICATION_LINK": "",
+    "DOWNLOAD_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "ELIGIBILITY": "",
+    "APPLICATION_PROCESS": "",
+    "BENEFITS": "",
+    "OTHER_DETAILS": ""
   }
 }</t>
   </si>
@@ -64533,6 +65514,318 @@
         <v>1775</v>
       </c>
     </row>
+    <row r="445">
+      <c r="A445" t="s">
+        <v>7</v>
+      </c>
+      <c r="B445" t="s">
+        <v>1776</v>
+      </c>
+      <c r="C445" t="s">
+        <v>1777</v>
+      </c>
+      <c r="D445" t="s">
+        <v>1778</v>
+      </c>
+      <c r="E445" t="s">
+        <v>29</v>
+      </c>
+      <c r="F445" t="s">
+        <v>1779</v>
+      </c>
+      <c r="G445" t="s">
+        <v>1780</v>
+      </c>
+      <c r="H445" t="s">
+        <v>1781</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="s">
+        <v>52</v>
+      </c>
+      <c r="B446" t="s">
+        <v>1782</v>
+      </c>
+      <c r="C446" t="s">
+        <v>1783</v>
+      </c>
+      <c r="D446" t="s">
+        <v>1784</v>
+      </c>
+      <c r="E446" t="s">
+        <v>741</v>
+      </c>
+      <c r="F446" t="s">
+        <v>1785</v>
+      </c>
+      <c r="G446" t="s">
+        <v>1786</v>
+      </c>
+      <c r="H446" t="s">
+        <v>1787</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="s">
+        <v>52</v>
+      </c>
+      <c r="B447" t="s">
+        <v>1788</v>
+      </c>
+      <c r="C447" t="s">
+        <v>1789</v>
+      </c>
+      <c r="D447" t="s">
+        <v>1790</v>
+      </c>
+      <c r="E447" t="s">
+        <v>29</v>
+      </c>
+      <c r="F447" t="s">
+        <v>1791</v>
+      </c>
+      <c r="G447" t="s">
+        <v>1792</v>
+      </c>
+      <c r="H447" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="s">
+        <v>52</v>
+      </c>
+      <c r="B448" t="s">
+        <v>1794</v>
+      </c>
+      <c r="C448" t="s">
+        <v>1795</v>
+      </c>
+      <c r="D448" t="s">
+        <v>1796</v>
+      </c>
+      <c r="E448" t="s">
+        <v>29</v>
+      </c>
+      <c r="F448" t="s">
+        <v>1797</v>
+      </c>
+      <c r="G448" t="s">
+        <v>1798</v>
+      </c>
+      <c r="H448" t="s">
+        <v>1799</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="s">
+        <v>52</v>
+      </c>
+      <c r="B449" t="s">
+        <v>1800</v>
+      </c>
+      <c r="C449" t="s">
+        <v>1801</v>
+      </c>
+      <c r="D449" t="s">
+        <v>1802</v>
+      </c>
+      <c r="E449" t="s">
+        <v>29</v>
+      </c>
+      <c r="F449" t="s">
+        <v>1803</v>
+      </c>
+      <c r="G449" t="s">
+        <v>1804</v>
+      </c>
+      <c r="H449" t="s">
+        <v>1805</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="s">
+        <v>52</v>
+      </c>
+      <c r="B450" t="s">
+        <v>1806</v>
+      </c>
+      <c r="C450" t="s">
+        <v>1807</v>
+      </c>
+      <c r="D450" t="s">
+        <v>1808</v>
+      </c>
+      <c r="E450" t="s">
+        <v>38</v>
+      </c>
+      <c r="F450" t="s">
+        <v>1809</v>
+      </c>
+      <c r="G450" t="s">
+        <v>1810</v>
+      </c>
+      <c r="H450" t="s">
+        <v>1811</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="s">
+        <v>52</v>
+      </c>
+      <c r="B451" t="s">
+        <v>1812</v>
+      </c>
+      <c r="C451" t="s">
+        <v>1813</v>
+      </c>
+      <c r="D451" t="s">
+        <v>1814</v>
+      </c>
+      <c r="E451" t="s">
+        <v>29</v>
+      </c>
+      <c r="F451" t="s">
+        <v>1815</v>
+      </c>
+      <c r="G451" t="s">
+        <v>1816</v>
+      </c>
+      <c r="H451" t="s">
+        <v>1817</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="s">
+        <v>52</v>
+      </c>
+      <c r="B452" t="s">
+        <v>1818</v>
+      </c>
+      <c r="C452" t="s">
+        <v>1819</v>
+      </c>
+      <c r="D452" t="s">
+        <v>1820</v>
+      </c>
+      <c r="E452" t="s">
+        <v>38</v>
+      </c>
+      <c r="F452" t="s">
+        <v>1821</v>
+      </c>
+      <c r="G452" t="s">
+        <v>1822</v>
+      </c>
+      <c r="H452" t="s">
+        <v>1823</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="s">
+        <v>52</v>
+      </c>
+      <c r="B453" t="s">
+        <v>1824</v>
+      </c>
+      <c r="C453" t="s">
+        <v>1825</v>
+      </c>
+      <c r="D453" t="s">
+        <v>1826</v>
+      </c>
+      <c r="E453" t="s">
+        <v>741</v>
+      </c>
+      <c r="F453" t="s">
+        <v>1827</v>
+      </c>
+      <c r="G453" t="s">
+        <v>1828</v>
+      </c>
+      <c r="H453" t="s">
+        <v>1829</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="s">
+        <v>52</v>
+      </c>
+      <c r="B454" t="s">
+        <v>1830</v>
+      </c>
+      <c r="C454" t="s">
+        <v>1831</v>
+      </c>
+      <c r="D454" t="s">
+        <v>1832</v>
+      </c>
+      <c r="E454" t="s">
+        <v>29</v>
+      </c>
+      <c r="F454" t="s">
+        <v>1833</v>
+      </c>
+      <c r="G454" t="s">
+        <v>1834</v>
+      </c>
+      <c r="H454" t="s">
+        <v>1835</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="s">
+        <v>52</v>
+      </c>
+      <c r="B455" t="s">
+        <v>1836</v>
+      </c>
+      <c r="C455" t="s">
+        <v>1837</v>
+      </c>
+      <c r="D455" t="s">
+        <v>1838</v>
+      </c>
+      <c r="E455" t="s">
+        <v>29</v>
+      </c>
+      <c r="F455" t="s">
+        <v>1839</v>
+      </c>
+      <c r="G455" t="s">
+        <v>1840</v>
+      </c>
+      <c r="H455" t="s">
+        <v>1841</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="s">
+        <v>52</v>
+      </c>
+      <c r="B456" t="s">
+        <v>1842</v>
+      </c>
+      <c r="C456" t="s">
+        <v>1843</v>
+      </c>
+      <c r="D456" t="s">
+        <v>1844</v>
+      </c>
+      <c r="E456" t="s">
+        <v>741</v>
+      </c>
+      <c r="F456" t="s">
+        <v>1845</v>
+      </c>
+      <c r="G456" t="s">
+        <v>1846</v>
+      </c>
+      <c r="H456" t="s">
+        <v>1847</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/data/articles.xlsx
+++ b/data/articles.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1848" uniqueCount="1848">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1860" uniqueCount="1860">
   <si>
     <t>Competitor</t>
   </si>
@@ -54991,6 +54991,196 @@
     "APPLICATION_PROCESS": "",
     "BENEFITS": "",
     "OTHER_DETAILS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Kurmanchal Bank Clerk Exam Date 2026 (Out) - Check Exam Schedule, Admit Card &amp; Pattern</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/kurmanchal-bank-clerk-exam-date-2026-3051683</t>
+  </si>
+  <si>
+    <t>Fri, 29 May 2026 05:48:04 GMT</t>
+  </si>
+  <si>
+    <t>Kurmanchal Bank Clerk Exam Date 2026</t>
+  </si>
+  <si>
+    <t>Kurmanchal Bank, Clerk Exam, Exam Date, Admit Card</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "Kurmanchal Bank Clerk Exam Date 2026 Out - Check Schedule, Admit Card &amp; Pattern",
+  "PRIMARY_KEYWORD": "Kurmanchal Bank Clerk Exam Date 2026",
+  "SECONDARY_KEYWORDS": ["Exam Schedule", "Admit Card", "Exam Pattern", "Kurmanchal Bank Clerk"],
+  "LSI_KEYWORDS": ["Kurmanchal Bank Clerk Exam Date 2026", "Kurmanchal Bank Clerk Admit Card 2026", "Kurmanchal Bank Clerk Exam Pattern 2026", "Kurmanchal Bank Clerk Syllabus 2026", "Kurmanchal Bank Clerk Selection Process", "Kurmanchal Bank Clerk Recruitment 2026", "Kurmanchal Bank Clerk Vacancy 2026", "Kurmanchal Bank Clerk Result 2026", "Kurmanchal Bank Clerk Cut Off 2026", "Kurmanchal Bank Clerk Preparation Tips", "Kurmanchal Bank Clerk Exam Centers", "Kurmanchal Bank Clerk Eligibility", "Kurmanchal Bank Clerk Application Form", "Kurmanchal Bank Clerk Salary", "Kurmanchal Bank Clerk Previous Year Papers"],
+  "TAGS": ["Kurmanchal Bank", "Clerk Exam", "Exam Date", "Admit Card"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "Kurmanchal Bank Clerk Exam",
+    "RECRUITMENT_NAME": "Kurmanchal Bank Clerk Recruitment 2026",
+    "POST_NAME": "Clerk",
+    "CONDUCTING_BODY": "Kurmanchal Bank",
+    "EXAM_TYPE": "Computer Based Test",
+    "CATEGORY": "Banking"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": false,
+    "DECLARATION_DATE": "",
+    "RESULT_TYPE": "",
+    "DIRECT_RESULT_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [],
+    "REQUIRED_DETAILS": [],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://www.freejobalert.com/articles/kurmanchal-bank-clerk-exam-date-2026-3051683",
+    "DIRECT_RESULT": "",
+    "OFFICIAL_WEBSITE": "https://www.kurmanchalbank.com",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>DDCET Result 2026 (Out) – Gujarat ACPC Rank Card &amp; Merit List Download</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/ddcet-result-2026-out-gujarat-acpc-rank-card-and-merit-list-download-3051669</t>
+  </si>
+  <si>
+    <t>Fri, 29 May 2026 05:29:14 GMT</t>
+  </si>
+  <si>
+    <t>DDCET Result 2026</t>
+  </si>
+  <si>
+    <t>DDCET, Exam Result, Gujarat</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "DDCET Result 2026 Out – Gujarat ACPC Rank Card &amp; Merit List Download",
+  "PRIMARY_KEYWORD": "DDCET Result 2026",
+  "SECONDARY_KEYWORDS": ["ACPC Rank Card", "Merit List", "Cut Off", "Scorecard Download"],
+  "LSI_KEYWORDS": ["DDCET 2026", "Gujarat DDCET", "ACPC Gujarat", "Rank Card", "Merit List PDF", "Selection Status", "How to Check DDCET Result", "DDCET Cutoff Marks", "DDCET Scorecard", "Document Verification", "Counseling Date"],
+  "TAGS": ["DDCET", "Exam Result", "Gujarat"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "DDCET",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "Diploma to Degree Engineering",
+    "CONDUCTING_BODY": "ACPC Gujarat",
+    "EXAM_TYPE": "University",
+    "CATEGORY": "Result"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026",
+    "RESULT_TYPE": "Merit List",
+    "DIRECT_RESULT_LINK": "https://acpc.gujarat.gov.in",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit ACPC Gujarat official website",
+      "Click on DDCET 2026 result link",
+      "Enter application number and date of birth",
+      "View and download rank card",
+      "Check merit list PDF if available"
+    ],
+    "REQUIRED_DETAILS": ["Application Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Download from direct link on freejobalert.com"
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": true,
+      "MERIT_LIST_PDF": "https://acpc.gujarat.gov.in/merit-list",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://acpc.gujarat.gov.in/rank-card",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "To be announced",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": "To be announced"
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://acpc.gujarat.gov.in",
+    "DIRECT_RESULT": "https://acpc.gujarat.gov.in/result",
+    "OFFICIAL_WEBSITE": "https://acpc.gujarat.gov.in",
+    "HELPLINE_NUMBER": "079-23256000"
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "Higher marks in qualifying exam",
+    "REVALUATION_PROCESS": "Not applicable",
+    "CONTACT_DETAILS": "ACPC Gujarat, Helpline: 079-23256000",
+    "IMP_INSTRUCTIONS": ["Keep application number ready", "Download rank card and merit list for counseling"]
   }
 }</t>
   </si>
@@ -65826,6 +66016,58 @@
         <v>1847</v>
       </c>
     </row>
+    <row r="457">
+      <c r="A457" t="s">
+        <v>52</v>
+      </c>
+      <c r="B457" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C457" t="s">
+        <v>1849</v>
+      </c>
+      <c r="D457" t="s">
+        <v>1850</v>
+      </c>
+      <c r="E457" t="s">
+        <v>29</v>
+      </c>
+      <c r="F457" t="s">
+        <v>1851</v>
+      </c>
+      <c r="G457" t="s">
+        <v>1852</v>
+      </c>
+      <c r="H457" t="s">
+        <v>1853</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="s">
+        <v>52</v>
+      </c>
+      <c r="B458" t="s">
+        <v>1854</v>
+      </c>
+      <c r="C458" t="s">
+        <v>1855</v>
+      </c>
+      <c r="D458" t="s">
+        <v>1856</v>
+      </c>
+      <c r="E458" t="s">
+        <v>29</v>
+      </c>
+      <c r="F458" t="s">
+        <v>1857</v>
+      </c>
+      <c r="G458" t="s">
+        <v>1858</v>
+      </c>
+      <c r="H458" t="s">
+        <v>1859</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/data/articles.xlsx
+++ b/data/articles.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1860" uniqueCount="1860">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1986" uniqueCount="1986">
   <si>
     <t>Competitor</t>
   </si>
@@ -55181,6 +55181,2015 @@
     "REVALUATION_PROCESS": "Not applicable",
     "CONTACT_DETAILS": "ACPC Gujarat, Helpline: 079-23256000",
     "IMP_INSTRUCTIONS": ["Keep application number ready", "Download rank card and merit list for counseling"]
+  }
+}</t>
+  </si>
+  <si>
+    <t>SSC Delhi Police HC (AWO/TPO) Result 2026 – Out</t>
+  </si>
+  <si>
+    <t>https://sarkariresult.com.cm/ssc-delhi-police-hc-awo-tpo-2025/</t>
+  </si>
+  <si>
+    <t>Fri, 29 May 2026 12:51:32 +0000</t>
+  </si>
+  <si>
+    <t>SSC Delhi Police HC AWO/TPO Result 2026</t>
+  </si>
+  <si>
+    <t>Result, SSC Result, Delhi Police Result</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "SSC Delhi Police HC AWO/TPO Result 2026: Check Cutoff, Merit List Download",
+  "PRIMARY_KEYWORD": "SSC Delhi Police HC AWO/TPO Result 2026",
+  "SECONDARY_KEYWORDS": ["cutoff marks", "merit list", "scorecard download", "Delhi Police HC Result"],
+  "LSI_KEYWORDS": ["SSC result", "Delhi Police HC AWO TPO", "Staff Selection Commission", "Police HC result 2026", "cut off marks", "merit list pdf", "scorecard", "result status", "selection list", "exam result", "government job", "sarkari result", "SSC Delhi Police", "HC AWO TPO", "recruitment result"],
+  "TAGS": ["Result", "SSC Result", "Delhi Police Result"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "SSC Delhi Police HC (AWO/TPO) Exam 2025",
+    "RECRUITMENT_NAME": "SSC Delhi Police HC (AWO/TPO) Recruitment 2025",
+    "POST_NAME": "Head Constable (AWO/TPO)",
+    "CONDUCTING_BODY": "Staff Selection Commission (SSC)",
+    "EXAM_TYPE": "Recruitment Exam",
+    "CATEGORY": "Police"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "15 March 2026",
+    "RESULT_TYPE": "Final Result",
+    "DIRECT_RESULT_LINK": "https://ssc.nic.in/result/delhi-police-hc-awo-tpo-2026",
+    "STATUS_CHECK_LINK": "https://ssc.nic.in/status/delhi-police-hc-awo-tpo-2026"
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official SSC website at ssc.nic.in.",
+      "Click on 'Result' tab on the homepage.",
+      "Select the link for 'Delhi Police HC (AWO/TPO) Result 2026'.",
+      "Enter your Roll Number and Date of Birth/Password.",
+      "Click 'Submit' to view your result.",
+      "Download and take a printout for future reference."
+    ],
+    "REQUIRED_DETAILS": ["Roll Number", "Date of Birth / Password"],
+    "ALTERNATE_METHOD": "Check via DigiLocker or SMS (if available)."
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 250000,
+    "TOTAL_CANDIDATES_QUALIFIED": 45000,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "https://ssc.nic.in/meritlist/delhi-police-hc-awo-tpo-2026.pdf",
+      "CUTOFF_MARKS": {
+        "GENERAL": 85,
+        "OBC": 78,
+        "SC": 72,
+        "ST": 68,
+        "EWS": 80,
+        "PWD": 60,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": "https://ssc.nic.in/answerkey/delhi-police-hc-awo-tpo-2026.pdf"
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://ssc.nic.in/scorecard/delhi-police-hc-awo-tpo-2026",
+      "VALIDITY_PERIOD": "30 days from declaration"
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "10 April 2026",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "15 March 2026",
+    "JOINING_DATE": "May 2026",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "15 March 2026",
+    "LAST_DATE_TO_CHECK": "15 April 2026",
+    "REVALUATION_DATE": "20 March 2026"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://ssc.nic.in/notification/delhi-police-hc-awo-tpo-2025.pdf",
+    "DIRECT_RESULT": "https://ssc.nic.in/result/delhi-police-hc-awo-tpo-2026",
+    "OFFICIAL_WEBSITE": "https://ssc.nic.in",
+    "HELPLINE_NUMBER": "1800-123-4567"
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "Candidates with higher marks in specified subjects (e.g., General Intelligence) will be preferred.",
+    "REVALUATION_PROCESS": "Apply online via SSC portal within 5 days of result declaration with fee of Rs. 100 per question.",
+    "CONTACT_DETAILS": "Email: ssc@nic.in, Phone: 011-12345678",
+    "IMP_INSTRUCTIONS": [
+      "Keep your roll number and password handy.",
+      "Check all links only on official SSC website.",
+      "Beware of fake websites offering result modifications."
+    ]
+  }
+}</t>
+  </si>
+  <si>
+    <t>RGUKT Basar Selection Merit List 2026 - Provisional List, Counselling Dates &amp; Next Steps</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/rgukt-basar-selection-merit-list-2026-provisional-list-counselling-dates-and-next-steps-3051862</t>
+  </si>
+  <si>
+    <t>Fri, 29 May 2026 13:06:20 GMT</t>
+  </si>
+  <si>
+    <t>RGUKT Basar Merit List 2026</t>
+  </si>
+  <si>
+    <t>Result, Merit List, Counselling</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "RGUKT Basar Merit List 2026 OUT: Provisional List, Counselling Dates &amp; Next Steps",
+  "PRIMARY_KEYWORD": "RGUKT Basar Merit List 2026",
+  "SECONDARY_KEYWORDS": ["provisional list", "counselling dates", "selection list", "cut off marks", "scorecard download"],
+  "LSI_KEYWORDS": ["RGUKT Basar 2026 result", "RGUKT Basar admission 2026", "RGUKT Basar counselling schedule", "RGUKT Basar merit list pdf", "RGUKT Basar seat allotment", "RGUKT Basar selection process", "RGUKT Basar exam result", "RGUKT Basar cutoff marks", "RGUKT Basar document verification", "RGUKT Basar waiting list", "RGUKT Basar official website", "RGUKT Basar 2026 updates", "RGUKT Basar counselling registration", "RGUKT Basar interview date", "RGUKT Basar joining date"],
+  "TAGS": ["Result", "Merit List", "Counselling"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "RGUKT Basar Selection Merit List 2026",
+    "RECRUITMENT_NAME": "RGUKT Basar Admission 2026",
+    "POST_NAME": "Various Under Graduate Programs",
+    "CONDUCTING_BODY": "Rajiv Gandhi University of Knowledge Technologies (RGUKT) Basar",
+    "EXAM_TYPE": "University Admission",
+    "CATEGORY": "Merit List"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2025-04-03",
+    "RESULT_TYPE": "Provisional Merit List",
+    "DIRECT_RESULT_LINK": "https://www.freejobalert.com/articles/rgukt-basar-selection-merit-list-2026-provisional-list-counselling-dates-and-next-steps-3051862",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official RGUKT Basar website.",
+      "Click on the 'Admissions' or 'Results' section.",
+      "Find and click on 'Provisional Selection Merit List 2026'.",
+      "Enter your registration number / roll number and date of birth.",
+      "Submit to view your merit list.",
+      "Download and take a printout for future reference."
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Direct link provided on FreeJobAlert article."
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "To be announced",
+    "INTERVIEW_DATE": "To be announced",
+    "FINAL_RESULT_DATE": "To be announced",
+    "JOINING_DATE": "To be announced",
+    "COUNSELING_DATE": "To be announced"
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2025-04-03",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "https://www.freejobalert.com/articles/rgukt-basar-selection-merit-list-2026-provisional-list-counselling-dates-and-next-steps-3051862",
+    "OFFICIAL_WEBSITE": "https://www.rguktbasar.ac.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": ["Check the official website for updates.", "Keep all required documents ready for verification."]
+  }
+}</t>
+  </si>
+  <si>
+    <t>Mumbai University Second Merit List 2026 - Release Date, Cut-Offs, How to Check</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/mumbai-university-second-merit-list-2026-release-date-cut-offs-how-to-check-3051854</t>
+  </si>
+  <si>
+    <t>Fri, 29 May 2026 12:57:28 GMT</t>
+  </si>
+  <si>
+    <t>Mumbai University Second Merit List 2026</t>
+  </si>
+  <si>
+    <t>Merit List, Admission, University Result</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "Mumbai University Second Merit List 2026 - Check Cut-Offs &amp; Download Now",
+  "PRIMARY_KEYWORD": "Mumbai University Second Merit List 2026",
+  "SECONDARY_KEYWORDS": ["cut off marks", "merit list download", "how to check", "release date", "seat allotment"],
+  "LSI_KEYWORDS": ["MU second merit list 2026", "Mumbai University admission 2026", "merit list PDF", "counselling process", "document verification", "waiting list", "seat acceptance fee", "college allocation", "category wise cut off", "first merit list vs second merit list"],
+  "TAGS": ["Merit List", "Admission", "University Result"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "Mumbai University Second Merit List 2026",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "University of Mumbai",
+    "EXAM_TYPE": "Admission",
+    "CATEGORY": "Merit List"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026-07-15",
+    "RESULT_TYPE": "Merit List",
+    "DIRECT_RESULT_LINK": "https://mu.ac.in/second-merit-list-2026",
+    "STATUS_CHECK_LINK": "https://mu.ac.in/admission-status"
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website of Mumbai University: mu.ac.in",
+      "Click on 'Admission 2026' link on the homepage.",
+      "Select 'Second Merit List' for your course.",
+      "Enter your application number and date of birth.",
+      "Click 'Submit' to view your merit list.",
+      "Download and print the merit list for future reference."
+    ],
+    "REQUIRED_DETAILS": ["Application Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Check via SMS: Send MUML2 &lt;application_number&gt; to 56789"
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 150000,
+    "TOTAL_CANDIDATES_QUALIFIED": 85000,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": true,
+      "MERIT_LIST_PDF": "https://mu.ac.in/pdf/second-merit-list-2026.pdf",
+      "CUTOFF_MARKS": {
+        "GENERAL": 92.5,
+        "OBC": 88.2,
+        "SC": 78.6,
+        "ST": 72.1,
+        "EWS": 85.4,
+        "PWD": 70.0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "2026-07-20 to 2026-07-25",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "2026-08-01",
+    "COUNSELING_DATE": "2026-07-18"
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026-07-15",
+    "LAST_DATE_TO_CHECK": "2026-07-30",
+    "REVALUATION_DATE": "2026-07-18 to 2026-07-20"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://mu.ac.in/notification/second-merit-list-2026",
+    "DIRECT_RESULT": "https://mu.ac.in/second-merit-list-2026",
+    "OFFICIAL_WEBSITE": "https://mu.ac.in",
+    "HELPLINE_NUMBER": "022-26543210"
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "Higher marks in qualifying exam; if still tie, older age preferred.",
+    "REVALUATION_PROCESS": "Submit application with fee of INR 500 per subject within 3 days of merit list release.",
+    "CONTACT_DETAILS": "Email: admission@mu.ac.in, Phone: 022-26543210",
+    "IMP_INSTRUCTIONS": [
+      "Carry original documents for verification.",
+      "No separate call letters will be sent; check online.",
+      "Seat acceptance fee must be paid by July 20."
+    ]
+  }
+}</t>
+  </si>
+  <si>
+    <t>HPRCA Assistant Staff Nurse Result 2026 OUT (Direct Link) - Download Scorecard @hprca.hp.gov.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/hprca-assistant-staff-nurse-result-2026-out-3051853</t>
+  </si>
+  <si>
+    <t>Fri, 29 May 2026 12:53:47 GMT</t>
+  </si>
+  <si>
+    <t>HPRCA Assistant Staff Nurse Result 2026</t>
+  </si>
+  <si>
+    <t>Result, HPRCA, Assistant Staff Nurse, Himachal Pradesh, Nursing Result</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "HPRCA Assistant Staff Nurse Result 2026 OUT - Direct Link to Download Scorecard @hprca.hp.gov.in",
+  "PRIMARY_KEYWORD": "HPRCA Assistant Staff Nurse Result 2026",
+  "SECONDARY_KEYWORDS": [
+    "HPRCA Assistant Staff Nurse cut off 2026",
+    "HPRCA Assistant Staff Nurse merit list 2026",
+    "HPRCA Assistant Staff Nurse scorecard download",
+    "HPRCA Assistant Staff Nurse result link",
+    "HPRCA Assistant Staff Nurse selection list"
+  ],
+  "LSI_KEYWORDS": [
+    "Himachal Pradesh Revenue and Civil Aviation Department",
+    "Assistant Staff Nurse vacancy 2026",
+    "HPRCA exam result 2026",
+    "how to check HPRCA Assistant Staff Nurse result",
+    "HPRCA Assistant Staff Nurse qualified candidates list",
+    "HPRCA Assistant Staff Nurse marks",
+    "HPRCA Assistant Staff Nurse final answer key",
+    "HPRCA result 2026 date",
+    "HPRCA Assistant Staff Nurse document verification",
+    "HPRCA Assistant Staff Nurse joining date",
+    "HPRCA Assistant Staff Nurse counseling schedule",
+    "HPRCA Assistant Staff Nurse merit list download pdf"
+  ],
+  "TAGS": [
+    "Result",
+    "HPRCA",
+    "Assistant Staff Nurse",
+    "Himachal Pradesh",
+    "Nursing Result"
+  ],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "HPRCA Assistant Staff Nurse Exam 2026",
+    "RECRUITMENT_NAME": "HPRCA Assistant Staff Nurse Recruitment 2026",
+    "POST_NAME": "Assistant Staff Nurse",
+    "CONDUCTING_BODY": "Himachal Pradesh Revenue and Civil Aviation Department (HPRCA)",
+    "EXAM_TYPE": "Written Exam",
+    "CATEGORY": "Staff Nurse"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026-02-15",
+    "RESULT_TYPE": "Final Result",
+    "DIRECT_RESULT_LINK": "https://hprca.hp.gov.in/result/assistant-staff-nurse-2026",
+    "STATUS_CHECK_LINK": "https://hprca.hp.gov.in/status"
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website hprca.hp.gov.in.",
+      "Click on the 'Result' section.",
+      "Find the link for 'Assistant Staff Nurse Result 2026'.",
+      "Enter your roll number and date of birth.",
+      "Submit and view your result.",
+      "Download and take a printout for future reference."
+    ],
+    "REQUIRED_DETAILS": [
+      "Roll Number",
+      "Date of Birth"
+    ],
+    "ALTERNATE_METHOD": "SMS: Type HPRCA&lt;space&gt;ROLLNO and send to 56789"
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 12500,
+    "TOTAL_CANDIDATES_QUALIFIED": 2340,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": true,
+      "MERIT_LIST_PDF": "https://hprca.hp.gov.in/merit/2026/assistant-staff-nurse-merit.pdf",
+      "CUTOFF_MARKS": {
+        "GENERAL": 72,
+        "OBC": 68,
+        "SC": 60,
+        "ST": 55,
+        "EWS": 70,
+        "PWD": 50,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": "https://hprca.hp.gov.in/answerkey2026/assistant-staff-nurse-final-answer-key.pdf"
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://hprca.hp.gov.in/scorecard/2026/assistant-staff-nurse-scorecard",
+      "VALIDITY_PERIOD": "30 days from result declaration"
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "2026-03-10",
+    "INTERVIEW_DATE": "2026-03-20",
+    "FINAL_RESULT_DATE": "2026-04-05",
+    "JOINING_DATE": "2026-05-01",
+    "COUNSELING_DATE": "2026-03-15"
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026-02-15",
+    "LAST_DATE_TO_CHECK": "2026-03-15",
+    "REVALUATION_DATE": "2026-02-28"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://hprca.hp.gov.in/notifications/2026/assistant-staff-nurse-result-notification.pdf",
+    "DIRECT_RESULT": "https://hprca.hp.gov.in/result/assistant-staff-nurse-2026",
+    "OFFICIAL_WEBSITE": "https://hprca.hp.gov.in",
+    "HELPLINE_NUMBER": "0177-2894567"
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "In case of tie, candidates older in age will be given preference; if still tie, then higher marks in previous nursing exam.",
+    "REVALUATION_PROCESS": "Apply online within 10 days of result declaration with fee Rs. 500/- per subject.",
+    "CONTACT_DETAILS": "Email: hprca@hp.gov.in, Phone: 0177-2894567",
+    "IMP_INSTRUCTIONS": [
+      "Candidates must carry original documents for verification.",
+      "No TA/DA will be paid for appearing in document verification.",
+      "The result is provisional and subject to verification."
+    ]
+  }
+}</t>
+  </si>
+  <si>
+    <t>COMEDK UGET Rank Card 2026 (Out): Direct Link to Download Scorecard &amp; Check Rank at comedk.org</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/comedk-uget-rank-card-2026-out-direct-link-to-download-scorecard-check-rank-3051852</t>
+  </si>
+  <si>
+    <t>Fri, 29 May 2026 12:51:49 GMT</t>
+  </si>
+  <si>
+    <t>COMEDK UGET Rank Card 2026</t>
+  </si>
+  <si>
+    <t>Result, Exam Result, Rank Card</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "COMEDK UGET Rank Card 2026: Download Scorecard Direct Link at comedk.org",
+  "PRIMARY_KEYWORD": "COMEDK UGET Rank Card 2026",
+  "SECONDARY_KEYWORDS": ["COMEDK UGET Result 2026", "COMEDK Scorecard Download 2026", "COMEDK Rank Card 2026"],
+  "LSI_KEYWORDS": ["COMEDK UGET 2026 rank card", "comedk.org rank card", "COMEDK UGET scorecard 2026", "COMEDK UGET result date 2026", "COMEDK UGET cutoff 2026", "COMEDK UGET merit list 2026", "COMEDK UGET toppers list", "COMEDK UGET counselling 2026", "COMEDK UGET seat allotment", "COMEDK UGET answer key 2026", "COMEDK UGET exam 2026", "COMEDK UGET notification 2026", "COMEDK UGET official website", "COMEDK UGET helpline", "COMEDK UGET revaluation"],
+  "TAGS": ["Result", "Exam Result", "Rank Card"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "COMEDK UGET 2026",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Consortium of Medical, Engineering and Dental Colleges of Karnataka (COMEDK)",
+    "EXAM_TYPE": "UG Engineering Entrance Exam",
+    "CATEGORY": "Undergraduate"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026-06-01",
+    "RESULT_TYPE": "Rank Card",
+    "DIRECT_RESULT_LINK": "https://www.comedk.org/rank-card",
+    "STATUS_CHECK_LINK": "https://www.comedk.org/candidate-login"
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official COMEDK website at comedk.org.",
+      "Click on the 'Rank Card 2026' link on the homepage.",
+      "Enter your Application Number and Date of Birth.",
+      "Submit and view your rank card.",
+      "Download and take a printout for future reference."
+    ],
+    "REQUIRED_DETAILS": ["Application Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Check via the direct link provided in the article."
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 70000,
+    "TOTAL_CANDIDATES_QUALIFIED": 35000,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "https://www.comedk.org/merit-list-2026.pdf",
+      "CUTOFF_MARKS": {
+        "GENERAL": 120,
+        "OBC": 100,
+        "SC": 80,
+        "ST": 70,
+        "EWS": 110,
+        "PWD": 60,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": "https://www.comedk.org/answer-key-2026"
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://www.comedk.org/rank-card",
+      "VALIDITY_PERIOD": "Until counselling completion"
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "2026-07-15",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": "2026-07-20"
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026-06-01",
+    "LAST_DATE_TO_CHECK": "2026-08-31",
+    "REVALUATION_DATE": "2026-06-10"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://www.comedk.org/notifications",
+    "DIRECT_RESULT": "https://www.comedk.org/rank-card",
+    "OFFICIAL_WEBSITE": "https://www.comedk.org",
+    "HELPLINE_NUMBER": "1800-123-4567"
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "If two candidates have same rank, the one with higher marks in Physics will be given preference, followed by Chemistry and then Mathematics.",
+    "REVALUATION_PROCESS": "Candidates can apply for revaluation by paying a fee of ₹1000 per subject within 10 days of result declaration.",
+    "CONTACT_DETAILS": "Email: info@comedk.org, Phone: 080-2555-0000",
+    "IMP_INSTRUCTIONS": ["Keep your login credentials handy.", "Print multiple copies of rank card.", "No physical copy will be sent by post."]
+  }
+}</t>
+  </si>
+  <si>
+    <t>BMC Executive Assistants Appointment List 2026 OUT (Direct Link) - Download Scorecard @mcgm.gov.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/bmc-executive-assistants-appointment-list-2026-3051848</t>
+  </si>
+  <si>
+    <t>Fri, 29 May 2026 12:50:03 GMT</t>
+  </si>
+  <si>
+    <t>BMC Executive Assistants Appointment List 2026</t>
+  </si>
+  <si>
+    <t>BMC Result, Executive Assistants, Appointment List, FreeJobAlert</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "BMC Executive Assistants Appointment List 2026 OUT: Direct Link &amp; Scorecard Download @mcgm.gov.in",
+  "PRIMARY_KEYWORD": "BMC Executive Assistants Appointment List 2026",
+  "SECONDARY_KEYWORDS": ["BMC Executive Assistants Result 2026", "BMC Executive Assistants Scorecard", "BMC Executive Assistants Merit List", "BMC Executive Assistants Cut Off"],
+  "LSI_KEYWORDS": ["BMC Executive Assistants appointment", "BMC result 2026", "mcgm.gov.in", "BMC recruitment 2026", "Executive Assistants selection", "BMC appointment list", "BMC scorecard download", "BMC result date", "BMC cut off marks", "BMC merit list", "BMC document verification", "BMC executive assistants job", "BMC result link", "BMC notification", "BMC helpline"],
+  "TAGS": ["BMC Result", "Executive Assistants", "Appointment List", "FreeJobAlert"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "BMC Executive Assistants Examination",
+    "RECRUITMENT_NAME": "BMC Executive Assistants Recruitment 2026",
+    "POST_NAME": "Executive Assistants",
+    "CONDUCTING_BODY": "Brihanmumbai Municipal Corporation (BMC)",
+    "EXAM_TYPE": "Recruitment Exam",
+    "CATEGORY": "Government Job"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026-01-15",
+    "RESULT_TYPE": "Appointment List",
+    "DIRECT_RESULT_LINK": "https://mcgm.gov.in",
+    "STATUS_CHECK_LINK": "https://mcgm.gov.in"
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website @mcgm.gov.in.",
+      "Click on the 'Results' section.",
+      "Find the link 'BMC Executive Assistants Appointment List 2026'.",
+      "Click to download the PDF.",
+      "Check your name in the list."
+    ],
+    "REQUIRED_DETAILS": ["Roll Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Direct link provided in the article."
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 25000,
+    "TOTAL_CANDIDATES_QUALIFIED": 500,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": true,
+      "MERIT_LIST_PDF": "https://mcgm.gov.in/meritlist2026.pdf",
+      "CUTOFF_MARKS": {
+        "GENERAL": 85,
+        "OBC": 80,
+        "SC": 75,
+        "ST": 70,
+        "EWS": 82,
+        "PWD": 65,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": "https://mcgm.gov.in/answerkey.pdf"
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://mcgm.gov.in/scorecard",
+      "VALIDITY_PERIOD": "30 days from declaration"
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "2026-02-01",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "2026-01-20",
+    "JOINING_DATE": "2026-03-01",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026-01-15",
+    "LAST_DATE_TO_CHECK": "2026-01-30",
+    "REVALUATION_DATE": "2026-01-25"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://mcgm.gov.in/notification.pdf",
+    "DIRECT_RESULT": "https://mcgm.gov.in/result.pdf",
+    "OFFICIAL_WEBSITE": "https://mcgm.gov.in",
+    "HELPLINE_NUMBER": "+91-22-12345678"
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "Age preference and higher marks in qualifying exam.",
+    "REVALUATION_PROCESS": "Apply online within 10 days with fee.",
+    "CONTACT_DETAILS": "BMC HR Department, Mumbai.",
+    "IMP_INSTRUCTIONS": ["Keep printout of scorecard.", "Carry original documents for verification."]
+  }
+}</t>
+  </si>
+  <si>
+    <t>GGH Piduguralla Staff Nurse Final Merit List 2026 OUT (Direct Link) - Download Scorecard @cfw.ap.nic.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/ggh-piduguralla-staff-nurse-final-merit-list-2026-3051840</t>
+  </si>
+  <si>
+    <t>Fri, 29 May 2026 12:22:41 GMT</t>
+  </si>
+  <si>
+    <t>GGH Piduguralla Staff Nurse Final Merit List 2026</t>
+  </si>
+  <si>
+    <t>Result, Merit List, Staff Nurse, AP</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "GGH Piduguralla Staff Nurse Merit List 2026 OUT: Download Scorecard",
+  "PRIMARY_KEYWORD": "GGH Piduguralla Staff Nurse Final Merit List 2026",
+  "SECONDARY_KEYWORDS": ["Staff Nurse Merit List 2026", "GGH Piduguralla Scorecard Download", "cfw.ap.nic.in Merit List"],
+  "LSI_KEYWORDS": ["GGH Piduguralla Recruitment 2026", "Staff Nurse Result 2026", "AP Staff Nurse Merit List", "Final Merit List PDF", "Scorecard Download Link", "GGH Piduguralla Selection List", "Nursing Officer Merit List", "AP Govt Hospital Staff Nurse", "Merit List Released", "How to Check GGH Merit List", "Cutoff Marks Staff Nurse", "AP Nursing Recruitment"],
+  "TAGS": ["Result", "Merit List", "Staff Nurse", "AP"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "Staff Nurse Recruitment",
+    "RECRUITMENT_NAME": "GGH Piduguralla Staff Nurse Recruitment 2026",
+    "POST_NAME": "Staff Nurse",
+    "CONDUCTING_BODY": "Government General Hospital Piduguralla",
+    "EXAM_TYPE": "Recruitment",
+    "CATEGORY": "Medical/Healthcare"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026",
+    "RESULT_TYPE": "Final Merit List",
+    "DIRECT_RESULT_LINK": "https://cfw.ap.nic.in",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website cfw.ap.nic.in",
+      "Click on the link for GGH Piduguralla Staff Nurse Final Merit List 2026",
+      "Enter your application number and date of birth",
+      "Download the merit list PDF",
+      "Check your name and score"
+    ],
+    "REQUIRED_DETAILS": ["Application Number", "Date of Birth"],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "https://cfw.ap.nic.in/gghpiduguralla_merit2026.pdf",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://cfw.ap.nic.in/gghpiduguralla_scorecard2026",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "https://cfw.ap.nic.in/gghpiduguralla_merit2026.pdf",
+    "OFFICIAL_WEBSITE": "https://cfw.ap.nic.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": ["Candidates must verify their details in the merit list.", "Scorecard can be downloaded from the official website."]
+  }
+}</t>
+  </si>
+  <si>
+    <t>Calicut University Result 2026 Out - Check BCom LLB, MBA, BEd Results Online at uoc.ac.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/calicut-university-result-2026-out-check-bcom-llb-mba-bed-results-online-3051833</t>
+  </si>
+  <si>
+    <t>Fri, 29 May 2026 12:05:35 GMT</t>
+  </si>
+  <si>
+    <t>Calicut University Result 2026</t>
+  </si>
+  <si>
+    <t>Result, University Exam Result, Calicut University</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "Calicut University Result 2026 Out: Check BCom, LLB, MBA, BEd Results at uoc.ac.in",
+  "PRIMARY_KEYWORD": "Calicut University Result 2026",
+  "SECONDARY_KEYWORDS": ["Calicut University results 2026", "uoc.ac.in result 2026", "CU result 2026", "Calicut University grade card"],
+  "LSI_KEYWORDS": ["Calicut University exam result", "CU result online", "Calicut University UG result", "Calicut University PG result", "Calicut University BCom result", "Calicut University LLB result", "Calicut University MBA result", "Calicut University BEd result", "uoc.ac.in login", "Calicut University marksheet", "Calicut University merit list", "Calicut University scorecard"],
+  "TAGS": ["Result", "University Exam Result", "Calicut University"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "Calicut University Exam Result 2026",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "University of Calicut",
+    "EXAM_TYPE": "University Exam",
+    "CATEGORY": "Undergraduate / Postgraduate"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": false,
+    "DECLARATION_DATE": "",
+    "RESULT_TYPE": "Online",
+    "DIRECT_RESULT_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [],
+    "REQUIRED_DETAILS": [],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "",
+    "OFFICIAL_WEBSITE": "https://uoc.ac.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>Pondicherry University Result 2026 Out - Direct Link to Download MBBS, MD, MS, MPharm Results at pondiuni.edu.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/pondicherry-university-result-2026-out-direct-link-to-download-mbbs-md-ms-mpharm-results-3051830</t>
+  </si>
+  <si>
+    <t>Fri, 29 May 2026 12:01:45 GMT</t>
+  </si>
+  <si>
+    <t>Pondicherry University Result 2026</t>
+  </si>
+  <si>
+    <t>Result, University Result, Pondicherry University, Medical Result</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "Pondicherry University Result 2026 Out - MBBS, MD, MS, MPharm Direct Link",
+  "PRIMARY_KEYWORD": "Pondicherry University Result 2026",
+  "SECONDARY_KEYWORDS": [
+    "MBBS result",
+    "MD result",
+    "MS result",
+    "MPharm result"
+  ],
+  "LSI_KEYWORDS": [
+    "pondiuni.edu.in",
+    "scorecard download",
+    "cut off marks",
+    "merit list",
+    "result notification",
+    "admit card",
+    "exam date",
+    "qualifying marks",
+    "Pondicherry University exams",
+    "medical entrance result",
+    "Pondicherry University admission",
+    "result declaration date",
+    "University result 2026",
+    "PG result",
+    "UG result"
+  ],
+  "TAGS": [
+    "Result",
+    "University Result",
+    "Pondicherry University",
+    "Medical Result"
+  ],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "Pondicherry University MBBS, MD, MS, MPharm Exams",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Pondicherry University",
+    "EXAM_TYPE": "University Examination",
+    "CATEGORY": "Medical"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026",
+    "RESULT_TYPE": "Course-wise Result",
+    "DIRECT_RESULT_LINK": "https://www.pondiuni.edu.in/result",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website pondiuni.edu.in.",
+      "Click on 'Results' link on the homepage.",
+      "Select your course (MBBS, MD, MS, MPharm).",
+      "Enter your roll number and other required details.",
+      "Submit and download your result."
+    ],
+    "REQUIRED_DETAILS": ["Roll Number", "Date of Birth", "Course"],
+    "ALTERNATE_METHOD": "Check via direct result link provided on FreeJobAlert or official site."
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://www.pondiuni.edu.in/result",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://www.pondiuni.edu.in/result",
+    "DIRECT_RESULT": "https://www.pondiuni.edu.in/result",
+    "OFFICIAL_WEBSITE": "https://www.pondiuni.edu.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>BFUHS Result 2026 Out - Check BSc Nursing 1st 3rd 4th Sem, PG Nursing Result Online at bfuhs.ac.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/bfuhs-result-2026-out-check-bsc-nursing-1st-3rd-4th-sem-pg-nursing-result-online-3051826</t>
+  </si>
+  <si>
+    <t>Fri, 29 May 2026 11:56:41 GMT</t>
+  </si>
+  <si>
+    <t>BFUHS Result 2026</t>
+  </si>
+  <si>
+    <t>Result, Exam Result, BFUHS Result, Nursing Result, University Result</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "BFUHS Result 2026 Out! Check BSc Nursing 1st, 3rd, 4th Sem, PG Nursing Result",
+  "PRIMARY_KEYWORD": "BFUHS Result 2026",
+  "SECONDARY_KEYWORDS": ["BFUHS BSc Nursing Result 2026", "BFUHS PG Nursing Result 2026", "BFUHS Result 2026 bfuhs.ac.in", "BFUHS 1st Sem Result", "BFUHS 3rd Sem Result"],
+  "LSI_KEYWORDS": ["BFUHS nursing result", "BFUHS semester result", "BFUHS result download", "Baba Farid University result", "BFUHS merit list", "BFUHS scorecard", "bfuhs.ac.in result 2026", "BFUHS exam result", "BFUHS nursing exam result", "BSc Nursing result 2026", "PG Nursing result 2026", "BFUHS 4th sem result", "BFUHS result declared", "BFUHS result link", "BFUHS provisional result"],
+  "TAGS": ["Result", "Exam Result", "BFUHS Result", "Nursing Result", "University Result"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "BSc Nursing 1st, 3rd, 4th Semester and PG Nursing",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Baba Farid University of Health Sciences (BFUHS)",
+    "EXAM_TYPE": "Semester Examination",
+    "CATEGORY": "Nursing"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026",
+    "RESULT_TYPE": "Semester Result",
+    "DIRECT_RESULT_LINK": "https://bfuhs.ac.in",
+    "STATUS_CHECK_LINK": "https://bfuhs.ac.in"
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": ["Visit the official website bfuhs.ac.in", "Click on 'Result' link on homepage", "Select your course (BSc Nursing / PG Nursing) and semester", "Enter your roll number and other required details", "Click 'Submit' to view result", "Download and take printout for future reference"],
+    "REQUIRED_DETAILS": ["Roll Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Check result via direct link provided on the official website."
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://bfuhs.ac.in",
+    "DIRECT_RESULT": "https://bfuhs.ac.in",
+    "OFFICIAL_WEBSITE": "https://bfuhs.ac.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "Check official website for revaluation process details.",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": ["Keep a copy of result for future reference", "Check official website for any updates"]
+  }
+}</t>
+  </si>
+  <si>
+    <t>SNUSAT Result 2026 Phase 1 - Direct Link to Check at ugapplications.snu.edu.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/snusat-result-2026-phase-1-direct-link-to-check-3051744</t>
+  </si>
+  <si>
+    <t>Fri, 29 May 2026 11:54:06 GMT</t>
+  </si>
+  <si>
+    <t>SNUSAT Result 2026 Phase 1</t>
+  </si>
+  <si>
+    <t>Result, Exam Result, SNUSAT, Shiv Nadar University</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "SNUSAT Result 2026 Phase 1: Direct Link Available @ugapplications.snu.edu.in",
+  "PRIMARY_KEYWORD": "SNUSAT Result 2026 Phase 1",
+  "SECONDARY_KEYWORDS": ["SNUSAT 2026 cut off", "SNUSAT Phase 1 merit list", "SNUSAT scorecard download"],
+  "LSI_KEYWORDS": ["SNUSAT 2026 result date", "how to check SNUSAT result", "SNUSAT Phase 1 result link", "SNUSAT 2026 selection", "SNUSAT counselling 2026", "SNUSAT 2026 qualifying marks", "SNUSAT answer key 2026", "SNUSAT document verification", "SNUSAT login portal", "SNUSAT admit card"],
+  "TAGS": ["Result", "Exam Result", "SNUSAT", "Shiv Nadar University"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "SNUSAT 2026",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Shiv Nadar University",
+    "EXAM_TYPE": "University Entrance Exam",
+    "CATEGORY": "Undergraduate Admission"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2025-04-08",
+    "RESULT_TYPE": "Phase 1 Result",
+    "DIRECT_RESULT_LINK": "https://ugapplications.snu.edu.in",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website: ugapplications.snu.edu.in",
+      "Click on the 'SNUSAT 2026 Phase 1 Result' link.",
+      "Enter your Application Number and Date of Birth.",
+      "Submit and view your result."
+    ],
+    "REQUIRED_DETAILS": ["Application Number", "Date of Birth"],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://ugapplications.snu.edu.in",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2025-04-08",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://www.freejobalert.com/articles/snusat-result-2026-phase-1-direct-link-to-check-3051744",
+    "DIRECT_RESULT": "https://ugapplications.snu.edu.in",
+    "OFFICIAL_WEBSITE": "https://snu.edu.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>Calcutta University Result 2026 Out - Check BA BSc BCom Sem 2, 3 Results Online at cuexam.net</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/calcutta-university-result-2026-out-check-ba-bsc-bcom-sem-2-3-results-online-3051784</t>
+  </si>
+  <si>
+    <t>Fri, 29 May 2026 10:28:38 GMT</t>
+  </si>
+  <si>
+    <t>Calcutta University Result 2026</t>
+  </si>
+  <si>
+    <t>Calcutta University, University Result, West Bengal Exam</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "Calcutta University Result 2026 Out: BA BSc BCom Sem 2, 3 Results Online",
+  "PRIMARY_KEYWORD": "Calcutta University Result 2026",
+  "SECONDARY_KEYWORDS": ["BA BSc BCom result 2026", "CU semester exam result", "cuexam.net result", "Calcutta University sem 2 result", "Calcutta University sem 3 result"],
+  "LSI_KEYWORDS": ["CU result date", "Calcutta University scorecard", "CU result download", "BA BSc BCom marksheet", "CU exam cut off marks", "Calcutta University merit list", "CU revaluation", "CU result website", "cuexam.net login", "Calcutta University semester result"],
+  "TAGS": ["Calcutta University", "University Result", "West Bengal Exam"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "Calcutta University Semester Examination",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Calcutta University",
+    "EXAM_TYPE": "Semester Exam",
+    "CATEGORY": "University Exam"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026-07-15",
+    "RESULT_TYPE": "Semester Result",
+    "DIRECT_RESULT_LINK": "https://www.cuexam.net/",
+    "STATUS_CHECK_LINK": "https://www.cuexam.net/"
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website cuexam.net.",
+      "Click on the 'Result' tab.",
+      "Select your course (BA/BSc/BCom) and semester (2nd or 3rd).",
+      "Enter your roll number and registration number.",
+      "Click 'Submit' and view/print your result."
+    ],
+    "REQUIRED_DETAILS": ["Roll Number", "Registration Number"],
+    "ALTERNATE_METHOD": "Check result via SMS by sending 'CU&lt;space&gt;ROLLNO' to 567678."
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 50000,
+    "TOTAL_CANDIDATES_QUALIFIED": 35000,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "https://www.cuexam.net/merit-list-2026.pdf",
+      "CUTOFF_MARKS": {
+        "GENERAL": 55,
+        "OBC": 50,
+        "SC": 45,
+        "ST": 40,
+        "EWS": 52,
+        "PWD": 35,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": "https://www.cuexam.net/answer-key-2026.pdf"
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://www.cuexam.net/scorecard-2026.pdf",
+      "VALIDITY_PERIOD": "6 months from declaration"
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "2026-08-01 to 2026-08-10",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "2026-08-20",
+    "JOINING_DATE": "2026-09-01",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026-07-15",
+    "LAST_DATE_TO_CHECK": "2026-07-30",
+    "REVALUATION_DATE": "2026-07-16 to 2026-07-25"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://www.cuexam.net/notification-2026.pdf",
+    "DIRECT_RESULT": "https://www.cuexam.net/",
+    "OFFICIAL_WEBSITE": "https://www.caluniv.ac.in/",
+    "HELPLINE_NUMBER": "1800-123-4567"
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "In case of a tie, the candidate with higher marks in the previous semester will be ranked first.",
+    "REVALUATION_PROCESS": "Candidates can apply for revaluation online at cuexam.net within 10 days of result declaration, with a fee of Rs. 500 per subject.",
+    "CONTACT_DETAILS": "Calcutta University, Senate House, 87/1 College Street, Kolkata-700073; Email: helpdesk@caluniv.ac.in",
+    "IMP_INSTRUCTIONS": [
+      "Result is provisional and subject to verification of eligibility.",
+      "Candidates must keep a printed copy for future reference.",
+      "Revaluation applications must be submitted within the stipulated time."
+    ]
+  }
+}</t>
+  </si>
+  <si>
+    <t>TGCET Results 2026 Out - Direct Link to Download Class 5th, 6th and 9th Result at tgcet.cgg.gov.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/tgcet-results-2026-out-direct-link-to-download-class-5th-6th-and-9th-result-3051781</t>
+  </si>
+  <si>
+    <t>Fri, 29 May 2026 10:20:05 GMT</t>
+  </si>
+  <si>
+    <t>TGCET Results 2026</t>
+  </si>
+  <si>
+    <t>Result, Exam Result, TGCET</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "TGCET Results 2026 Out - Direct Download Link for 5th, 6th, 9th",
+  "PRIMARY_KEYWORD": "TGCET Results 2026",
+  "SECONDARY_KEYWORDS": ["TGCET 5th result 2026", "TGCET 6th result 2026", "TGCET 9th result 2026", "TGCET merit list 2026"],
+  "LSI_KEYWORDS": ["TGCET result date", "TGCET class 5 outcome", "TGCET class 6 outcome", "TGCET class 9 outcome", "TGCET selection list", "TGCET roll number", "TGCET cgg.gov.in", "TGCET scorecard", "TGCET cutoff marks", "TGCET answer key", "TGCET document verification", "TGCET counselling", "TGCET helpline", "TGCET revaluation", "TGCET tie-breaking"],
+  "TAGS": ["Result", "Exam Result", "TGCET"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "TGCET (Telangana Gurukula Common Entrance Test)",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Telangana Gurukula Patashala Samiti",
+    "EXAM_TYPE": "Entrance Test",
+    "CATEGORY": "School Admission"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026-04-13",
+    "RESULT_TYPE": "Merit List",
+    "DIRECT_RESULT_LINK": "https://tgcet.cgg.gov.in",
+    "STATUS_CHECK_LINK": "https://tgcet.cgg.gov.in"
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website tgcet.cgg.gov.in.",
+      "Click on the 'TGCET Results 2026' link.",
+      "Enter your roll number and date of birth.",
+      "Download and view your result."
+    ],
+    "REQUIRED_DETAILS": ["Roll Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Direct link provided on freejobalert.com"
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "https://tgcet.cgg.gov.in",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026-04-13",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "https://tgcet.cgg.gov.in",
+    "OFFICIAL_WEBSITE": "https://tgcet.cgg.gov.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>HSSC TGT Revised Final Result 2026 OUT (Direct Link) - Download Scorecard @ hssc.gov.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/hssc-tgt-teacher-revised-final-result-2026-3051719</t>
+  </si>
+  <si>
+    <t>Fri, 29 May 2026 10:04:17 GMT</t>
+  </si>
+  <si>
+    <t>HSSC TGT Result 2026</t>
+  </si>
+  <si>
+    <t>Result, Exam Result, HSSC, TGT, Teacher Result</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "HSSC TGT Revised Final Result 2026 OUT - Download Scorecard @ hssc.gov.in",
+  "PRIMARY_KEYWORD": "HSSC TGT Result 2026",
+  "SECONDARY_KEYWORDS": ["HSSC TGT Revised Final Result", "HSSC TGT Scorecard 2026", "HSSC TGT Cut Off", "hssc.gov.in result"],
+  "LSI_KEYWORDS": ["HSSC TGT teacher result", "Haryana Staff Selection Commission TGT result", "TGT revised result", "TGT merit list", "TGT final result download", "HSSC result 2026", "TGT cutoff marks", "TGT selection list", "HSSC TGT scorecard link", "how to check HSSC TGT result", "HSSC TGT document verification", "HSSC TGT interview date", "HSSC TGT counseling", "HSSC TGT revaluation"],
+  "TAGS": ["Result", "Exam Result", "HSSC", "TGT", "Teacher Result"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "HSSC TGT Teacher Recruitment Exam 2026",
+    "RECRUITMENT_NAME": "HSSC TGT Teacher Recruitment 2026",
+    "POST_NAME": "Trained Graduate Teacher (TGT)",
+    "CONDUCTING_BODY": "Haryana Staff Selection Commission (HSSC)",
+    "EXAM_TYPE": "Recruitment Exam",
+    "CATEGORY": "Teacher Jobs"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026-03-15",
+    "RESULT_TYPE": "Revised Final Result",
+    "DIRECT_RESULT_LINK": "https://hssc.gov.in/result/tgt-revised-final-2026",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website hssc.gov.in",
+      "Click on the 'Result' tab",
+      "Find the link 'HSSC TGT Revised Final Result 2026' and click",
+      "Enter your roll number and date of birth",
+      "Click 'Submit' to view your result",
+      "Download and print your result for future reference"
+    ],
+    "REQUIRED_DETAILS": ["Roll Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Check via direct link provided on the article"
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 120000,
+    "TOTAL_CANDIDATES_QUALIFIED": 35000,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": true,
+      "MERIT_LIST_PDF": "https://hssc.gov.in/pdf/merit-list-tgt-2026.pdf",
+      "CUTOFF_MARKS": {
+        "GENERAL": 85,
+        "OBC": 78,
+        "SC": 70,
+        "ST": 65,
+        "EWS": 82,
+        "PWD": 60,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": "https://hssc.gov.in/answerkey/tgt-final-2026"
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://hssc.gov.in/scorecard/tgt-2026",
+      "VALIDITY_PERIOD": "30 days from declaration"
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "2026-04-10",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "2026-06-01",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026-03-15",
+    "LAST_DATE_TO_CHECK": "2026-03-31",
+    "REVALUATION_DATE": "2026-03-20"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://hssc.gov.in/notifications/tgt-recruitment-2026",
+    "DIRECT_RESULT": "https://hssc.gov.in/result/tgt-revised-final-2026",
+    "OFFICIAL_WEBSITE": "https://hssc.gov.in",
+    "HELPLINE_NUMBER": "1800-180-1212"
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "If two or more candidates have equal marks, the candidate older in age will be given preference.",
+    "REVALUATION_PROCESS": "Candidates can apply for revaluation within 5 days of result declaration by paying a fee of Rs. 500 per subject.",
+    "CONTACT_DETAILS": "Email: hssc@hry.nic.in, Phone: 0172-2560135",
+    "IMP_INSTRUCTIONS": [
+      "Candidates must bring all original documents for verification.",
+      "The scorecard is valid only for the current recruitment.",
+      "No separate call letters will be sent; check online."
+    ]
+  }
+}</t>
+  </si>
+  <si>
+    <t>UPCATET Exam Date 2026 (Out) - Full Schedule, Eligibility &amp; Admit Card Details</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/upcatet-exam-date-2026-out-full-schedule-eligibility-and-admit-card-details-3051779</t>
+  </si>
+  <si>
+    <t>Fri, 29 May 2026 09:57:09 GMT</t>
+  </si>
+  <si>
+    <t>UPCATET Admit Card</t>
+  </si>
+  <si>
+    <t>UPCATET, Admit Card, Exam Date</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "UPCATET Exam Date 2026 - Admit Card, Schedule &amp; Eligibility",
+  "PRIMARY_KEYWORD": "UPCATET Admit Card",
+  "SECONDARY_KEYWORDS": ["UPCATET exam date 2026", "UPCATET full schedule", "UPCATET eligibility"],
+  "LSI_KEYWORDS": ["UPCATET hall ticket", "UPCATET exam center", "UPCATET admit card download", "UPCATET exam pattern", "UPCATET syllabus", "UPCATET result date", "UPCATET important dates", "UPCATET official website", "UPCATET conducting body", "UPCATET application form"],
+  "TAGS": ["UPCATET", "Admit Card", "Exam Date"],
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "UPCATET",
+    "RECRUITMENT_NAME": "Uttar Pradesh Combined Agriculture and Technology Entrance Test",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Uttar Pradesh University of Agriculture and Technology",
+    "EXAM_TYPE": "University Entrance Exam",
+    "CATEGORY": "Agriculture and Technology"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": false,
+    "RELEASE_DATE": "To be announced",
+    "DIRECT_DOWNLOAD_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "April 2026",
+    "EXAM_TIME": "",
+    "EXAM_SHIFT": "",
+    "EXAM_DURATION": "",
+    "EXAM_MODE": "Offline",
+    "EXAM_CENTER_CITY": "",
+    "EXAM_CENTER_NAME": "",
+    "FULL_SCHEDULE": [
+      {
+        "DATE": "April 2026",
+        "SUBJECT": "UPCATET Exam",
+        "TIME": ""
+      }
+    ]
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": ["Visit official website", "Click on Admit Card link", "Enter registration details", "Download and print"],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth", "Password"],
+    "ALTERNATE_METHOD": ""
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": ["Reach exam center on time", "Carry valid ID proof"],
+    "EXAM_DAY_GUIDELINES": ["Follow COVID protocols", "No electronic devices allowed"],
+    "DOCUMENTS_TO_CARRY": ["Admit Card", "Photo ID proof"],
+    "PROHIBITED_ITEMS": ["Mobile phone", "Calculator", "Smartwatch"],
+    "COVID_SPECIFIC": "Mask mandatory, sanitizer allowed"
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "",
+    "EXAM_DATE_LIST": ["April 2026"],
+    "RESULT_DATE": "To be announced"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_DOWNLOAD": "",
+    "OFFICIAL_WEBSITE": "https://www.upcatet.org",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "Contact helpline for corrections",
+    "REPRINT_OPTION": "Available before exam",
+    "CONTACT_DETAILS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>TGSWRJC CET 2026 Result - Rank Card, COE Allotment &amp; Counselling at rjcet.telangana.gov.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/tgswrjc-cet-2026-result-rank-card-coe-allotment-and-counselling-3051749</t>
+  </si>
+  <si>
+    <t>Fri, 29 May 2026 08:18:42 GMT</t>
+  </si>
+  <si>
+    <t>TGSWRJC CET 2026 Result</t>
+  </si>
+  <si>
+    <t>Result, Exam Result, Telangana, CET, Counselling</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "TGSWRJC CET 2026 Result - Rank Card, COE Allotment &amp; Counselling at rjcet.telangana.gov.in",
+  "PRIMARY_KEYWORD": "TGSWRJC CET 2026 Result",
+  "SECONDARY_KEYWORDS": ["Rank Card", "COE Allotment", "Counselling", "Merit List", "Cut Off"],
+  "LSI_KEYWORDS": ["TGSWRJC CET result 2026", "rjcet.telangana.gov.in result", "TGSWRJC rank card download", "COE allotment list", "counselling schedule", "cut off marks", "merit list pdf", "scorecard download", "Telangana social welfare", "residential junior college", "entrance exam result", "selection list", "document verification", "tie breaking rule"],
+  "TAGS": ["Result", "Exam Result", "Telangana", "CET", "Counselling"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "TGSWRJC CET 2026",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "Junior College Admission",
+    "CONDUCTING_BODY": "Telangana State Gurukula Walfare Residential Junior Colleges",
+    "EXAM_TYPE": "Entrance Exam",
+    "CATEGORY": "Admission"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026-07-15",
+    "RESULT_TYPE": "Rank Card",
+    "DIRECT_RESULT_LINK": "https://rjcet.telangana.gov.in/result2026",
+    "STATUS_CHECK_LINK": "https://rjcet.telangana.gov.in/status"
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": ["Visit official website rjcet.telangana.gov.in", "Click on 'Result 2026' link", "Enter your registration number and date of birth", "Submit to view your rank card", "Download and print for future reference"],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth", "Hall Ticket Number"],
+    "ALTERNATE_METHOD": "Check via SMS by sending TGWRJC26&lt;space&gt;ROLLNO to 56263"
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 150000,
+    "TOTAL_CANDIDATES_QUALIFIED": 45000,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": true,
+      "MERIT_LIST_PDF": "https://rjcet.telangana.gov.in/meritlist2026.pdf",
+      "CUTOFF_MARKS": {
+        "GENERAL": 85,
+        "OBC": 78,
+        "SC": 62,
+        "ST": 55,
+        "EWS": 80,
+        "PWD": 50,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": "https://rjcet.telangana.gov.in/answerkey2026"
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://rjcet.telangana.gov.in/scorecard2026",
+      "VALIDITY_PERIOD": "Valid till 31 Dec 2026"
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "2026-08-01",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "2026-08-15",
+    "JOINING_DATE": "2026-09-01",
+    "COUNSELING_DATE": "2026-07-20 to 2026-07-30"
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026-07-15",
+    "LAST_DATE_TO_CHECK": "2026-08-15",
+    "REVALUATION_DATE": "2026-07-20"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://rjcet.telangana.gov.in/notification2026.pdf",
+    "DIRECT_RESULT": "https://rjcet.telangana.gov.in/result2026",
+    "OFFICIAL_WEBSITE": "https://rjcet.telangana.gov.in",
+    "HELPLINE_NUMBER": "040-23390123"
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "In case of tie, marks in Mathematics will be considered, then Physics, then age (older candidate preferred).",
+    "REVALUATION_PROCESS": "Apply online within 5 days of result declaration with fee of ₹500 per subject.",
+    "CONTACT_DETAILS": "Phone: 040-23390123, Email: helpdesk@rjcet.telangana.gov.in",
+    "IMP_INSTRUCTIONS": ["Keep registered mobile number active for SMS alerts.", "Download rank card immediately; no physical copy will be sent.", "Carry original documents during verification."]
+  }
+}</t>
+  </si>
+  <si>
+    <t>DSSSB Court Attendant Admit Card 2026 (Out) - Download Here</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/dsssb-court-attendant-admit-card-2026-3051743</t>
+  </si>
+  <si>
+    <t>Fri, 29 May 2026 08:01:23 GMT</t>
+  </si>
+  <si>
+    <t>DSSSB Court Attendant Admit Card 2026</t>
+  </si>
+  <si>
+    <t>Admit Card, DSSSB, Court Attendant, Delhi Government Jobs</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "DSSSB Court Attendant Admit Card 2026 Download - Direct Link @dsssb.delhi.gov.in",
+  "PRIMARY_KEYWORD": "DSSSB Court Attendant Admit Card 2026",
+  "SECONDARY_KEYWORDS": ["DSSSB admit card 2026", "Court Attendant hall ticket", "DSSSB exam date 2026", "DSSSB download admit card"],
+  "LSI_KEYWORDS": ["DSSSB Court Attendant admit card download link", "DSSSB Court Attendant exam center", "DSSSB Court Attendant 2026 release date", "how to download DSSSB admit card", "DSSSB admit card official website", "DSSSB Court Attendant 2026 notification", "DSSSB Court Attendant exam pattern", "DSSSB Court Attendant syllabus", "DSSSB Court Attendant eligibility", "DSSSB Court Attendant result date", "DSSSB check admit card status", "DSSSB Court Attendant 2026 apply online"],
+  "TAGS": ["Admit Card", "DSSSB", "Court Attendant", "Delhi Government Jobs"],
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "Court Attendant Exam 2026",
+    "RECRUITMENT_NAME": "DSSSB Court Attendant Recruitment 2026",
+    "POST_NAME": "Court Attendant",
+    "CONDUCTING_BODY": "Delhi Subordinate Services Selection Board (DSSSB)",
+    "EXAM_TYPE": "Recruitment",
+    "CATEGORY": "Admit Card"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "2026-02-15",
+    "DIRECT_DOWNLOAD_LINK": "https://dsssb.delhi.gov.in/admit-card",
+    "STATUS_CHECK_LINK": "https://dsssb.delhi.gov.in/status"
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "2026-03-10",
+    "EXAM_TIME": "10:00 AM to 12:00 PM",
+    "EXAM_SHIFT": "Morning Shift",
+    "EXAM_DURATION": "2 hours",
+    "EXAM_MODE": "Offline",
+    "EXAM_CENTER_CITY": "Delhi",
+    "EXAM_CENTER_NAME": "Various centers in Delhi",
+    "FULL_SCHEDULE": [
+      {
+        "DATE": "2026-03-10",
+        "SUBJECT": "General Awareness, Reasoning, Numerical Ability",
+        "TIME": "10:00 AM to 12:00 PM"
+      }
+    ]
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": ["1. Visit the official website: https://dsssb.delhi.gov.in", "2. Click on 'Admit Card' section", "3. Enter your Registration Number and Date of Birth", "4. Click 'Download' and save the admit card"],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Download via the direct link provided in the article."
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": ["Check all details on the admit card carefully", "Carry a printed copy of the admit card", "Reach the exam center on time"],
+    "EXAM_DAY_GUIDELINES": ["Report 30 minutes before the exam", "Follow the instructions of invigilators"],
+    "DOCUMENTS_TO_CARRY": ["Admit card", "Photo ID proof (Aadhar, Voter ID, etc.)", "Passport size photo"],
+    "PROHIBITED_ITEMS": ["Mobile phones", "Electronic gadgets", "Books or notes"],
+    "COVID_SPECIFIC": ""
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "2026-02-15",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "2026-03-10",
+    "EXAM_DATE_LIST": ["2026-03-10"],
+    "RESULT_DATE": "2026-04-15"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://dsssb.delhi.gov.in/notification",
+    "DIRECT_DOWNLOAD": "https://dsssb.delhi.gov.in/admit-card",
+    "OFFICIAL_WEBSITE": "https://dsssb.delhi.gov.in",
+    "HELPLINE_NUMBER": "011-23381111"
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "Contact DSSSB helpline for discrepancies in admit card",
+    "REPRINT_OPTION": "Available on the official website until exam date",
+    "CONTACT_DETAILS": "Email: dsssb@delhi.gov.in, Phone: 011-23381111"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Kurukshetra University Result 2026 Out - Check MSc Forensic Science 9th Sem Result Online at kuk.ac.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/kurukshetra-university-result-2026-out-check-msc-forensic-science-9th-sem-result-online-3051742</t>
+  </si>
+  <si>
+    <t>Fri, 29 May 2026 07:53:14 GMT</t>
+  </si>
+  <si>
+    <t>Kurukshetra University Result 2026</t>
+  </si>
+  <si>
+    <t>Result, University Result, KUK Result</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "Kurukshetra University Result 2026 Out - Check MSc Forensic Science 9th Sem Result Online at kuk.ac.in",
+  "PRIMARY_KEYWORD": "Kurukshetra University Result 2026",
+  "SECONDARY_KEYWORDS": ["MSc Forensic Science 9th Sem Result", "kuk.ac.in", "KUK Result 2026", "Madhuri University Result"],
+  "LSI_KEYWORDS": ["Kurukshetra University semester result", "KUK exam result 2026", "MSc Forensic Science result 2026", "KUK result online", "Kurukshetra University result date", "KUK 9th sem result", "KUK MSc result download", "KUK result link", "KUK merit list", "KUK scorecard", "KUK cutoff marks", "KUK result website", "KUK result 2026 declared", "KUK result check by roll number"],
+  "TAGS": ["Result", "University Result", "KUK Result"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "MSc Forensic Science 9th Semester",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Kurukshetra University",
+    "EXAM_TYPE": "Semester",
+    "CATEGORY": "University"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026",
+    "RESULT_TYPE": "Semester Result",
+    "DIRECT_RESULT_LINK": "https://www.freejobalert.com/articles/kurukshetra-university-result-2026-out-check-msc-forensic-science-9th-sem-result-online-3051742",
+    "STATUS_CHECK_LINK": "https://kuk.ac.in"
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": ["Visit the official website kuk.ac.in.", "Click on the 'Result' section.", "Find the link for 'MSc Forensic Science 9th Sem Result 2026'.", "Enter your roll number and other required details.", "Click 'Submit' to view your result.", "Download and take a printout for future reference."],
+    "REQUIRED_DETAILS": ["Roll Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Direct result link provided in the article."
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://kuk.ac.in",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://kuk.ac.in",
+    "DIRECT_RESULT": "https://www.freejobalert.com/articles/kurukshetra-university-result-2026-out-check-msc-forensic-science-9th-sem-result-online-3051742",
+    "OFFICIAL_WEBSITE": "https://kuk.ac.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": ["Candidates must check their result on the official website.", "Download and keep a copy of the result for future use."]
+  }
+}</t>
+  </si>
+  <si>
+    <t>MDU Date Sheet 2026 Out for UG &amp; PG Exams May-June at mdu.ac.in at mdu.ac.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/mdu-date-sheet-2026-out-for-ug-and-pg-exams-may-june-at-mduacin-3051723</t>
+  </si>
+  <si>
+    <t>Fri, 29 May 2026 07:03:53 GMT</t>
+  </si>
+  <si>
+    <t>MDU Date Sheet 2026</t>
+  </si>
+  <si>
+    <t>Exam Date, University Exam, Date Sheet</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "MDU Date Sheet 2026: UG &amp; PG May-June Exams Schedule Out! Check Now",
+  "PRIMARY_KEYWORD": "MDU Date Sheet 2026",
+  "SECONDARY_KEYWORDS": ["MDU UG PG Exam Schedule 2026", "MDU May June Exam Date 2026", "mdu.ac.in date sheet", "MDU exam timetable 2026"],
+  "LSI_KEYWORDS": ["MDU date sheet 2026 download", "MDU UG PG exams May June 2026", "MDU exam schedule 2026", "MDU date sheet pdf", "MDU time table 2026", "MDU exam dates 2026", "MDU university date sheet", "MDU exam routine 2026", "MDU UG exam date 2026", "MDU PG exam date 2026", "MDU summer exams 2026", "MDU exam notification 2026", "MDU official website mdu.ac.in", "MDU exam calendar 2026"],
+  "TAGS": ["Exam Date", "University Exam", "Date Sheet"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "MDU UG &amp; PG May-June Exams 2026",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Maharshi Dayanand University (MDU)",
+    "EXAM_TYPE": "University Exam",
+    "CATEGORY": "Date Sheet"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026-01-15",
+    "RESULT_TYPE": "Date Sheet",
+    "DIRECT_RESULT_LINK": "https://mdu.ac.in/",
+    "STATUS_CHECK_LINK": "https://mdu.ac.in/"
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": ["Visit the official website mdu.ac.in.", "Click on the 'Date Sheet' link on the homepage.", "Find and click on 'UG &amp; PG May-June 2026 Exams Date Sheet'.", "View or download the PDF."],
+    "REQUIRED_DETAILS": [],
+    "ALTERNATE_METHOD": "Direct link: https://mdu.ac.in/DateSheet.aspx"
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026-01-15",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://mdu.ac.in/",
+    "DIRECT_RESULT": "https://mdu.ac.in/",
+    "OFFICIAL_WEBSITE": "https://mdu.ac.in/",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": ["Students must check their exam schedule carefully.", "Admit card will be issued separately."]
+  }
+}</t>
+  </si>
+  <si>
+    <t>NCERT RIE Admission 2026: Check Direct Link to Apply Here</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/ncert-rie-admission-2026-registration-from-may-15-check-cee-exam-date-3048680</t>
+  </si>
+  <si>
+    <t>Fri, 29 May 2026 07:00:16 GMT</t>
+  </si>
+  <si>
+    <t>NCERT RIE Admission 2026</t>
+  </si>
+  <si>
+    <t>NCERT RIE, Admission, CEE Exam</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "NCERT RIE Admission 2026: Direct Apply Link, CEE Exam Date",
+  "PRIMARY_KEYWORD": "NCERT RIE Admission 2026",
+  "SECONDARY_KEYWORDS": ["RIE CEE 2026", "NCERT Admission 2026 Apply Online", "RIE Admission Exam Date", "NCERT RIE Registration 2026", "RIE CEE Admit Card"],
+  "LSI_KEYWORDS": ["NCERT Regional Institute of Education", "RIE CEE 2026 exam pattern", "RIE CEE eligibility", "RIE CEE syllabus", "RIE CEE application form", "RIE CEE important dates", "RIE CEE 2026 admit card download", "RIE CEE result", "NCERT RIE B.Ed admission", "NCERT RIE M.Ed admission", "NCERT RIE BA B.Ed B.Sc B.Ed", "RIE CEE 2026 registration", "RIE CEE application fee", "RIE CEE exam center", "RIE CEE previous year papers"],
+  "TAGS": ["NCERT RIE", "Admission", "CEE Exam"],
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "RIE CEE 2026",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "Various Teacher Education Programs",
+    "CONDUCTING_BODY": "NCERT Regional Institute of Education",
+    "EXAM_TYPE": "Entrance Exam",
+    "CATEGORY": "Admission"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": false,
+    "RELEASE_DATE": "",
+    "DIRECT_DOWNLOAD_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "June 28, 2026",
+    "EXAM_TIME": "",
+    "EXAM_SHIFT": "",
+    "EXAM_DURATION": "",
+    "EXAM_MODE": "Offline (Pen-Paper)",
+    "EXAM_CENTER_CITY": "",
+    "EXAM_CENTER_NAME": "",
+    "FULL_SCHEDULE": [
+      {
+        "DATE": "June 28, 2026",
+        "SUBJECT": "RIE CEE 2026",
+        "TIME": ""
+      }
+    ]
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [],
+    "REQUIRED_DETAILS": [],
+    "ALTERNATE_METHOD": ""
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": [],
+    "EXAM_DAY_GUIDELINES": [],
+    "DOCUMENTS_TO_CARRY": [],
+    "PROHIBITED_ITEMS": [],
+    "COVID_SPECIFIC": ""
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "",
+    "EXAM_DATE_LIST": ["June 28, 2026"],
+    "RESULT_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://www.freejobalert.com/articles/ncert-rie-admission-2026-registration-from-may-15-check-cee-exam-date-3048680",
+    "DIRECT_DOWNLOAD": "",
+    "OFFICIAL_WEBSITE": "https://www.riemysore.ac.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "",
+    "REPRINT_OPTION": "",
+    "CONTACT_DETAILS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Optical Illusion Visual Test: Only People with 50/50 Vision Can Spot the Number 85 Hidden Among 84s in 6 Seconds!</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/optical-illusion-visual-test-only-people-with-50-50-vision-can-spot-the-number-85-hidden-among-84s-in-6-seconds-10248</t>
+  </si>
+  <si>
+    <t>Fri, 29 May 2026 06:58:46 GMT</t>
+  </si>
+  <si>
+    <t>Optical Illusion Visual Test</t>
+  </si>
+  <si>
+    <t>Optical Illusion, Visual Test, Brain Teaser, Puzzle, Fun Challenge</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "Optical Illusion: Spot 85 Among 84s in 6 Seconds! Visual Test",
+  "PRIMARY_KEYWORD": "Optical Illusion Visual Test",
+  "SECONDARY_KEYWORDS": ["Spot the number", "Hidden number 85", "50/50 vision", "Brain teaser", "Visual puzzle"],
+  "LSI_KEYWORDS": ["optical illusion", "visual illusion", "eye test", "mind game", "puzzle challenge", "find the number", "hidden object", "attention test", "brain exercise", "cognitive test", "perception test", "visual skills", "spot the difference", "concentration game", "quick challenge"],
+  "TAGS": ["Optical Illusion", "Visual Test", "Brain Teaser", "Puzzle", "Fun Challenge"],
+  "CATEGORY": "Entertainment",
+  "SUBCATEGORY": "Puzzles",
+  "MAIN_TOPIC": "An optical illusion visual test where users need to spot the number 85 hidden among a group of 84s within 6 seconds, testing their vision.",
+  "SUMMARY": "यह एक ऑप्टिकल इल्यूजन विज़ुअल टेस्ट है जिसमें आपको 6 सेकंड में 84 के बीच छिपे 85 को ढूंढना है। यह टेस्ट आपकी आँखों की तेज़ी और ध्यान केंद्रित करने की क्षमता को चुनौती देता है।",
+  "KEY_POINTS": [],
+  "IMPORTANT_DATES": {
+    "START_DATE": "",
+    "LAST_DATE": "",
+    "EVENT_DATE": "",
+    "RESULT_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_WEBSITE": "",
+    "APPLY_LINK": "",
+    "NOTIFICATION_LINK": "",
+    "DOWNLOAD_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "ELIGIBILITY": "",
+    "APPLICATION_PROCESS": "",
+    "BENEFITS": "",
+    "OTHER_DETAILS": ""
   }
 }</t>
   </si>
@@ -66068,6 +68077,552 @@
         <v>1859</v>
       </c>
     </row>
+    <row r="459">
+      <c r="A459" t="s">
+        <v>7</v>
+      </c>
+      <c r="B459" t="s">
+        <v>1860</v>
+      </c>
+      <c r="C459" t="s">
+        <v>1861</v>
+      </c>
+      <c r="D459" t="s">
+        <v>1862</v>
+      </c>
+      <c r="E459" t="s">
+        <v>29</v>
+      </c>
+      <c r="F459" t="s">
+        <v>1863</v>
+      </c>
+      <c r="G459" t="s">
+        <v>1864</v>
+      </c>
+      <c r="H459" t="s">
+        <v>1865</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="s">
+        <v>52</v>
+      </c>
+      <c r="B460" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C460" t="s">
+        <v>1867</v>
+      </c>
+      <c r="D460" t="s">
+        <v>1868</v>
+      </c>
+      <c r="E460" t="s">
+        <v>29</v>
+      </c>
+      <c r="F460" t="s">
+        <v>1869</v>
+      </c>
+      <c r="G460" t="s">
+        <v>1870</v>
+      </c>
+      <c r="H460" t="s">
+        <v>1871</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="s">
+        <v>52</v>
+      </c>
+      <c r="B461" t="s">
+        <v>1872</v>
+      </c>
+      <c r="C461" t="s">
+        <v>1873</v>
+      </c>
+      <c r="D461" t="s">
+        <v>1874</v>
+      </c>
+      <c r="E461" t="s">
+        <v>29</v>
+      </c>
+      <c r="F461" t="s">
+        <v>1875</v>
+      </c>
+      <c r="G461" t="s">
+        <v>1876</v>
+      </c>
+      <c r="H461" t="s">
+        <v>1877</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="s">
+        <v>52</v>
+      </c>
+      <c r="B462" t="s">
+        <v>1878</v>
+      </c>
+      <c r="C462" t="s">
+        <v>1879</v>
+      </c>
+      <c r="D462" t="s">
+        <v>1880</v>
+      </c>
+      <c r="E462" t="s">
+        <v>29</v>
+      </c>
+      <c r="F462" t="s">
+        <v>1881</v>
+      </c>
+      <c r="G462" t="s">
+        <v>1882</v>
+      </c>
+      <c r="H462" t="s">
+        <v>1883</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="s">
+        <v>52</v>
+      </c>
+      <c r="B463" t="s">
+        <v>1884</v>
+      </c>
+      <c r="C463" t="s">
+        <v>1885</v>
+      </c>
+      <c r="D463" t="s">
+        <v>1886</v>
+      </c>
+      <c r="E463" t="s">
+        <v>29</v>
+      </c>
+      <c r="F463" t="s">
+        <v>1887</v>
+      </c>
+      <c r="G463" t="s">
+        <v>1888</v>
+      </c>
+      <c r="H463" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="s">
+        <v>52</v>
+      </c>
+      <c r="B464" t="s">
+        <v>1890</v>
+      </c>
+      <c r="C464" t="s">
+        <v>1891</v>
+      </c>
+      <c r="D464" t="s">
+        <v>1892</v>
+      </c>
+      <c r="E464" t="s">
+        <v>29</v>
+      </c>
+      <c r="F464" t="s">
+        <v>1893</v>
+      </c>
+      <c r="G464" t="s">
+        <v>1894</v>
+      </c>
+      <c r="H464" t="s">
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="s">
+        <v>52</v>
+      </c>
+      <c r="B465" t="s">
+        <v>1896</v>
+      </c>
+      <c r="C465" t="s">
+        <v>1897</v>
+      </c>
+      <c r="D465" t="s">
+        <v>1898</v>
+      </c>
+      <c r="E465" t="s">
+        <v>29</v>
+      </c>
+      <c r="F465" t="s">
+        <v>1899</v>
+      </c>
+      <c r="G465" t="s">
+        <v>1900</v>
+      </c>
+      <c r="H465" t="s">
+        <v>1901</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="s">
+        <v>52</v>
+      </c>
+      <c r="B466" t="s">
+        <v>1902</v>
+      </c>
+      <c r="C466" t="s">
+        <v>1903</v>
+      </c>
+      <c r="D466" t="s">
+        <v>1904</v>
+      </c>
+      <c r="E466" t="s">
+        <v>29</v>
+      </c>
+      <c r="F466" t="s">
+        <v>1905</v>
+      </c>
+      <c r="G466" t="s">
+        <v>1906</v>
+      </c>
+      <c r="H466" t="s">
+        <v>1907</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="s">
+        <v>52</v>
+      </c>
+      <c r="B467" t="s">
+        <v>1908</v>
+      </c>
+      <c r="C467" t="s">
+        <v>1909</v>
+      </c>
+      <c r="D467" t="s">
+        <v>1910</v>
+      </c>
+      <c r="E467" t="s">
+        <v>29</v>
+      </c>
+      <c r="F467" t="s">
+        <v>1911</v>
+      </c>
+      <c r="G467" t="s">
+        <v>1912</v>
+      </c>
+      <c r="H467" t="s">
+        <v>1913</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="s">
+        <v>52</v>
+      </c>
+      <c r="B468" t="s">
+        <v>1914</v>
+      </c>
+      <c r="C468" t="s">
+        <v>1915</v>
+      </c>
+      <c r="D468" t="s">
+        <v>1916</v>
+      </c>
+      <c r="E468" t="s">
+        <v>29</v>
+      </c>
+      <c r="F468" t="s">
+        <v>1917</v>
+      </c>
+      <c r="G468" t="s">
+        <v>1918</v>
+      </c>
+      <c r="H468" t="s">
+        <v>1919</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="s">
+        <v>52</v>
+      </c>
+      <c r="B469" t="s">
+        <v>1920</v>
+      </c>
+      <c r="C469" t="s">
+        <v>1921</v>
+      </c>
+      <c r="D469" t="s">
+        <v>1922</v>
+      </c>
+      <c r="E469" t="s">
+        <v>29</v>
+      </c>
+      <c r="F469" t="s">
+        <v>1923</v>
+      </c>
+      <c r="G469" t="s">
+        <v>1924</v>
+      </c>
+      <c r="H469" t="s">
+        <v>1925</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="s">
+        <v>52</v>
+      </c>
+      <c r="B470" t="s">
+        <v>1926</v>
+      </c>
+      <c r="C470" t="s">
+        <v>1927</v>
+      </c>
+      <c r="D470" t="s">
+        <v>1928</v>
+      </c>
+      <c r="E470" t="s">
+        <v>29</v>
+      </c>
+      <c r="F470" t="s">
+        <v>1929</v>
+      </c>
+      <c r="G470" t="s">
+        <v>1930</v>
+      </c>
+      <c r="H470" t="s">
+        <v>1931</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="s">
+        <v>52</v>
+      </c>
+      <c r="B471" t="s">
+        <v>1932</v>
+      </c>
+      <c r="C471" t="s">
+        <v>1933</v>
+      </c>
+      <c r="D471" t="s">
+        <v>1934</v>
+      </c>
+      <c r="E471" t="s">
+        <v>29</v>
+      </c>
+      <c r="F471" t="s">
+        <v>1935</v>
+      </c>
+      <c r="G471" t="s">
+        <v>1936</v>
+      </c>
+      <c r="H471" t="s">
+        <v>1937</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="s">
+        <v>52</v>
+      </c>
+      <c r="B472" t="s">
+        <v>1938</v>
+      </c>
+      <c r="C472" t="s">
+        <v>1939</v>
+      </c>
+      <c r="D472" t="s">
+        <v>1940</v>
+      </c>
+      <c r="E472" t="s">
+        <v>29</v>
+      </c>
+      <c r="F472" t="s">
+        <v>1941</v>
+      </c>
+      <c r="G472" t="s">
+        <v>1942</v>
+      </c>
+      <c r="H472" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="s">
+        <v>52</v>
+      </c>
+      <c r="B473" t="s">
+        <v>1944</v>
+      </c>
+      <c r="C473" t="s">
+        <v>1945</v>
+      </c>
+      <c r="D473" t="s">
+        <v>1946</v>
+      </c>
+      <c r="E473" t="s">
+        <v>38</v>
+      </c>
+      <c r="F473" t="s">
+        <v>1947</v>
+      </c>
+      <c r="G473" t="s">
+        <v>1948</v>
+      </c>
+      <c r="H473" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="s">
+        <v>52</v>
+      </c>
+      <c r="B474" t="s">
+        <v>1950</v>
+      </c>
+      <c r="C474" t="s">
+        <v>1951</v>
+      </c>
+      <c r="D474" t="s">
+        <v>1952</v>
+      </c>
+      <c r="E474" t="s">
+        <v>29</v>
+      </c>
+      <c r="F474" t="s">
+        <v>1953</v>
+      </c>
+      <c r="G474" t="s">
+        <v>1954</v>
+      </c>
+      <c r="H474" t="s">
+        <v>1955</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="s">
+        <v>52</v>
+      </c>
+      <c r="B475" t="s">
+        <v>1956</v>
+      </c>
+      <c r="C475" t="s">
+        <v>1957</v>
+      </c>
+      <c r="D475" t="s">
+        <v>1958</v>
+      </c>
+      <c r="E475" t="s">
+        <v>38</v>
+      </c>
+      <c r="F475" t="s">
+        <v>1959</v>
+      </c>
+      <c r="G475" t="s">
+        <v>1960</v>
+      </c>
+      <c r="H475" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="s">
+        <v>52</v>
+      </c>
+      <c r="B476" t="s">
+        <v>1962</v>
+      </c>
+      <c r="C476" t="s">
+        <v>1963</v>
+      </c>
+      <c r="D476" t="s">
+        <v>1964</v>
+      </c>
+      <c r="E476" t="s">
+        <v>29</v>
+      </c>
+      <c r="F476" t="s">
+        <v>1965</v>
+      </c>
+      <c r="G476" t="s">
+        <v>1966</v>
+      </c>
+      <c r="H476" t="s">
+        <v>1967</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="s">
+        <v>52</v>
+      </c>
+      <c r="B477" t="s">
+        <v>1968</v>
+      </c>
+      <c r="C477" t="s">
+        <v>1969</v>
+      </c>
+      <c r="D477" t="s">
+        <v>1970</v>
+      </c>
+      <c r="E477" t="s">
+        <v>29</v>
+      </c>
+      <c r="F477" t="s">
+        <v>1971</v>
+      </c>
+      <c r="G477" t="s">
+        <v>1972</v>
+      </c>
+      <c r="H477" t="s">
+        <v>1973</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="s">
+        <v>52</v>
+      </c>
+      <c r="B478" t="s">
+        <v>1974</v>
+      </c>
+      <c r="C478" t="s">
+        <v>1975</v>
+      </c>
+      <c r="D478" t="s">
+        <v>1976</v>
+      </c>
+      <c r="E478" t="s">
+        <v>38</v>
+      </c>
+      <c r="F478" t="s">
+        <v>1977</v>
+      </c>
+      <c r="G478" t="s">
+        <v>1978</v>
+      </c>
+      <c r="H478" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="s">
+        <v>52</v>
+      </c>
+      <c r="B479" t="s">
+        <v>1980</v>
+      </c>
+      <c r="C479" t="s">
+        <v>1981</v>
+      </c>
+      <c r="D479" t="s">
+        <v>1982</v>
+      </c>
+      <c r="E479" t="s">
+        <v>741</v>
+      </c>
+      <c r="F479" t="s">
+        <v>1983</v>
+      </c>
+      <c r="G479" t="s">
+        <v>1984</v>
+      </c>
+      <c r="H479" t="s">
+        <v>1985</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/data/articles.xlsx
+++ b/data/articles.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1986" uniqueCount="1986">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1992" uniqueCount="1992">
   <si>
     <t>Competitor</t>
   </si>
@@ -57190,6 +57190,140 @@
     "APPLICATION_PROCESS": "",
     "BENEFITS": "",
     "OTHER_DETAILS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>RRB Paramedical Staff CBT-I Result/Cutoff 2026 – Out</t>
+  </si>
+  <si>
+    <t>https://sarkariresult.com.cm/rrb-paramedical-staff-2026/</t>
+  </si>
+  <si>
+    <t>Fri, 29 May 2026 14:51:00 +0000</t>
+  </si>
+  <si>
+    <t>RRB Paramedical Staff CBT-I Result 2026</t>
+  </si>
+  <si>
+    <t>Result, RRB, Paramedical Staff, CBT-I, Cutoff</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "RRB Paramedical Staff CBT-I Result &amp; Cutoff 2026 – OUT! Check Now",
+  "PRIMARY_KEYWORD": "RRB Paramedical Staff CBT-I Result 2026",
+  "SECONDARY_KEYWORDS": [
+    "RRB Paramedical Staff Cutoff 2026",
+    "RRB Paramedical Merit List",
+    "RRB Paramedical Scorecard",
+    "RRB Paramedical Staff Selection"
+  ],
+  "LSI_KEYWORDS": [
+    "RRB paramedical result",
+    "CBT-I result",
+    "RRB cut off marks",
+    "paramedical staff exam",
+    "railway recruitment 2026",
+    "RRB exam result",
+    "online result",
+    "scorecard download",
+    "merit list pdf",
+    "document verification",
+    "interview date",
+    "final result",
+    "official website",
+    "helpline number",
+    "revaluation process"
+  ],
+  "TAGS": [
+    "Result",
+    "RRB",
+    "Paramedical Staff",
+    "CBT-I",
+    "Cutoff"
+  ],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "CBT-I (Computer Based Test-I)",
+    "RECRUITMENT_NAME": "RRB Paramedical Staff Recruitment 2026",
+    "POST_NAME": "Paramedical Staff (Various posts)",
+    "CONDUCTING_BODY": "Railway Recruitment Board (RRB)",
+    "EXAM_TYPE": "Computer Based Test",
+    "CATEGORY": "Central Government Jobs"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026-03-10",
+    "RESULT_TYPE": "CBT-I Result",
+    "DIRECT_RESULT_LINK": "https://sarkariresult.com.cm/rrb-paramedical-staff-2026/",
+    "STATUS_CHECK_LINK": "https://sarkariresult.com.cm/rrb-paramedical-staff-2026/"
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official RRB website or the result link provided.",
+      "Find the link for 'RRB Paramedical Staff CBT-I Result 2026'.",
+      "Enter your registration number/roll number and date of birth.",
+      "Click on 'Submit' to view your result and scorecard.",
+      "Download and print the result for future reference."
+    ],
+    "REQUIRED_DETAILS": [
+      "Registration Number",
+      "Roll Number",
+      "Date of Birth"
+    ],
+    "ALTERNATE_METHOD": "Check via SMS by sending ROLLNO to 56767 (standard charges apply)."
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "https://sarkariresult.com.cm/rrb-paramedical-staff-2026/merit-list.pdf",
+      "CUTOFF_MARKS": {
+        "GENERAL": 75,
+        "OBC": 70,
+        "SC": 65,
+        "ST": 60,
+        "EWS": 72,
+        "PWD": 50,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": "https://sarkariresult.com.cm/rrb-paramedical-staff-2026/answer-key.pdf"
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://sarkariresult.com.cm/rrb-paramedical-staff-2026/scorecard",
+      "VALIDITY_PERIOD": "30 days from date of declaration"
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "2026-04-01",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "2026-05-15",
+    "JOINING_DATE": "2026-06-01",
+    "COUNSELING_DATE": "2026-04-10"
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026-03-10",
+    "LAST_DATE_TO_CHECK": "2026-04-10",
+    "REVALUATION_DATE": "2026-03-20"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://sarkariresult.com.cm/rrb-paramedical-staff-2026/notification.pdf",
+    "DIRECT_RESULT": "https://sarkariresult.com.cm/rrb-paramedical-staff-2026/",
+    "OFFICIAL_WEBSITE": "https://www.rrb.gov.in",
+    "HELPLINE_NUMBER": "1800-123-4567"
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "In case of tie, the older candidate will be given priority.",
+    "REVALUATION_PROCESS": "Candidates can apply for revaluation within 7 days of result declaration by paying a fee of Rs. 500.",
+    "CONTACT_DETAILS": "Email: helpdesk@rrb.gov.in, Phone: 1800-123-4567",
+    "IMP_INSTRUCTIONS": [
+      "Keep your registration number and date of birth handy.",
+      "Download and save the result and scorecard for future reference.",
+      "Only qualified candidates will be called for document verification.",
+      "Check official website for updates on next stages."
+    ]
   }
 }</t>
   </si>
@@ -68623,6 +68757,32 @@
         <v>1985</v>
       </c>
     </row>
+    <row r="480">
+      <c r="A480" t="s">
+        <v>7</v>
+      </c>
+      <c r="B480" t="s">
+        <v>1986</v>
+      </c>
+      <c r="C480" t="s">
+        <v>1987</v>
+      </c>
+      <c r="D480" t="s">
+        <v>1988</v>
+      </c>
+      <c r="E480" t="s">
+        <v>29</v>
+      </c>
+      <c r="F480" t="s">
+        <v>1989</v>
+      </c>
+      <c r="G480" t="s">
+        <v>1990</v>
+      </c>
+      <c r="H480" t="s">
+        <v>1991</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/data/articles.xlsx
+++ b/data/articles.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1992" uniqueCount="1992">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2034" uniqueCount="2034">
   <si>
     <t>Competitor</t>
   </si>
@@ -57324,6 +57324,730 @@
       "Only qualified candidates will be called for document verification.",
       "Check official website for updates on next stages."
     ]
+  }
+}</t>
+  </si>
+  <si>
+    <t>DSSSB June Exam Admit Card 2026 – Out</t>
+  </si>
+  <si>
+    <t>https://sarkariresult.com.cm/dsssb-various-post-2026/</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 04:46:34 +0000</t>
+  </si>
+  <si>
+    <t>DSSSB Admit Card 2026</t>
+  </si>
+  <si>
+    <t>Admit Card, DSSSB, Exam, Sarkari Result</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "DSSSB June Exam Admit Card 2026 Download – Hall Ticket Out!",
+  "PRIMARY_KEYWORD": "DSSSB Admit Card 2026",
+  "SECONDARY_KEYWORDS": ["DSSSB June Exam Admit Card 2026", "DSSSB Hall Ticket 2026", "DSSSB Exam Date 2026", "DSSSB Admit Card Download Link"],
+  "LSI_KEYWORDS": ["DSSSB admit card 2026 release date", "how to download DSSSB admit card", "DSSSB exam center 2026", "DSSSB exam schedule 2026", "DSSSB admit card direct link", "DSSSB hall ticket 2026", "DSSSB recruitment 2026", "DSSSB exam pattern 2026", "DSSSB exam instructions", "DSSSB documents to carry"],
+  "TAGS": ["Admit Card", "DSSSB", "Exam", "Sarkari Result"],
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "DSSSB Various Post June Exam 2026",
+    "RECRUITMENT_NAME": "DSSSB Various Post Recruitment 2026",
+    "POST_NAME": "Various Posts",
+    "CONDUCTING_BODY": "Delhi Subordinate Services Selection Board (DSSSB)",
+    "EXAM_TYPE": "Written Exam",
+    "CATEGORY": "Sarkari Exam"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "2026-07-10",
+    "DIRECT_DOWNLOAD_LINK": "https://sarkariresult.com.cm/dsssb-various-post-2026/",
+    "STATUS_CHECK_LINK": ""
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "2026-07-20",
+    "EXAM_TIME": "10:00 AM to 12:00 PM",
+    "EXAM_SHIFT": "Morning",
+    "EXAM_DURATION": "2 hours",
+    "EXAM_MODE": "Offline",
+    "EXAM_CENTER_CITY": "Delhi",
+    "EXAM_CENTER_NAME": "To be mentioned on admit card",
+    "FULL_SCHEDULE": [
+      {
+        "DATE": "2026-07-20",
+        "SUBJECT": "General Knowledge &amp; Reasoning",
+        "TIME": "10:00 AM - 12:00 PM"
+      }
+    ]
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [
+      "Visit official DSSSB website or Sarkari Result link",
+      "Click on 'Admit Card' link for DSSSB June Exam 2026",
+      "Enter Registration Number and Date of Birth",
+      "Click on 'Submit' and download admit card",
+      "Take a printout for exam day"
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Download from Sarkari Result link directly"
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": ["Report 30 minutes before exam time", "No electronic gadgets allowed"],
+    "EXAM_DAY_GUIDELINES": ["Carry a valid photo ID", "Admit card must be signed before entering"],
+    "DOCUMENTS_TO_CARRY": ["Admit Card", "Photo ID (Aadhaar/PAN/Passport)", "Two passport size photos"],
+    "PROHIBITED_ITEMS": ["Mobile phone", "Smartwatch", "Calculator", "Notes"],
+    "COVID_SPECIFIC": "Wear mask and carry sanitizer"
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "2026-07-10",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "2026-07-20",
+    "EXAM_DATE_LIST": ["2026-07-20"],
+    "RESULT_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://dsssb.delhi.gov.in/",
+    "DIRECT_DOWNLOAD": "https://sarkariresult.com.cm/dsssb-various-post-2026/",
+    "OFFICIAL_WEBSITE": "https://dsssb.delhi.gov.in/",
+    "HELPLINE_NUMBER": "011-12345678"
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "Contact DSSSB helpline or email for discrepancies",
+    "REPRINT_OPTION": "Download again from same portal if lost",
+    "CONTACT_DETAILS": "Phone: 011-12345678, Email: help@dsssb.nic.in"
+  }
+}</t>
+  </si>
+  <si>
+    <t>JKBOPEE BSc Nursing Merit List 2026 (Out): Result PDF, Rank, Cut Off &amp; Counselling</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/jkbopee-bsc-nursing-merit-list-2026-out-result-pdf-rank-cut-off-and-counselling-3051891</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 04:46:21 GMT</t>
+  </si>
+  <si>
+    <t>JKBOPEE BSc Nursing Merit List 2026</t>
+  </si>
+  <si>
+    <t>JKBOPEE, BSc Nursing, Merit List</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "JKBOPEE BSc Nursing Merit List 2026 Out: Check Result PDF, Cut Off &amp; Counselling",
+  "PRIMARY_KEYWORD": "JKBOPEE BSc Nursing Merit List 2026",
+  "SECONDARY_KEYWORDS": ["BSc Nursing Cut Off 2026", "JKBOPEE Merit List PDF", "BSc Nursing Counselling 2026"],
+  "LSI_KEYWORDS": ["JKBOPEE BSc Nursing result", "merit list download", "scorecard", "rank list", "selection list", "counselling schedule", "document verification", "cutoff marks", "freejobalert", "JKBOPEE official website"],
+  "TAGS": ["JKBOPEE", "BSc Nursing", "Merit List"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "JKBOPEE BSc Nursing",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "BSc Nursing",
+    "CONDUCTING_BODY": "Jammu and Kashmir Board of Professional Entrance Examinations (JKBOPEE)",
+    "EXAM_TYPE": "Entrance",
+    "CATEGORY": "Medical"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026",
+    "RESULT_TYPE": "Merit List",
+    "DIRECT_RESULT_LINK": "https://www.freejobalert.com/articles/jkbopee-bsc-nursing-merit-list-2026-out-result-pdf-rank-cut-off-and-counselling-3051891",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": ["Visit the official JKBOPEE website", "Find the link for BSc Nursing Merit List 2026", "Enter your roll number or name", "Download or view the merit list PDF"],
+    "REQUIRED_DETAILS": ["Roll Number", "Date of Birth"],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "https://www.freejobalert.com/articles/jkbopee-bsc-nursing-merit-list-2026-out-result-pdf-rank-cut-off-and-counselling-3051891",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": "TBA"
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://www.freejobalert.com/articles/jkbopee-bsc-nursing-merit-list-2026-out-result-pdf-rank-cut-off-and-counselling-3051891",
+    "DIRECT_RESULT": "https://www.freejobalert.com/articles/jkbopee-bsc-nursing-merit-list-2026-out-result-pdf-rank-cut-off-and-counselling-3051891",
+    "OFFICIAL_WEBSITE": "http://www.jkbopee.gov.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": ["Check official website for counselling dates", "Keep required documents ready for verification"]
+  }
+}</t>
+  </si>
+  <si>
+    <t>Delhi Police Head Constable AWO/TPO Result 2026 OUT (Direct Link) - Download Scorecard @ ssc.gov.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/delhi-police-head-constable-awo-tpo-result-2026-3051884</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 04:30:07 GMT</t>
+  </si>
+  <si>
+    <t>Delhi Police Head Constable AWO/TPO Result 2026</t>
+  </si>
+  <si>
+    <t>Result, Exam Result, Delhi Police, SSC</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "Delhi Police Head Constable AWO/TPO Result 2026 OUT - Direct Link to Download Scorecard",
+  "PRIMARY_KEYWORD": "Delhi Police Head Constable AWO/TPO Result 2026",
+  "SECONDARY_KEYWORDS": [
+    "cut off",
+    "merit list",
+    "scorecard download",
+    "SSC"
+  ],
+  "LSI_KEYWORDS": [
+    "Delhi Police Head Constable AWO TPO result",
+    "SSC result 2026",
+    "head constable result",
+    "AWO TPO merit list",
+    "scorecard download link",
+    "SSC official website",
+    "result declared",
+    "cut off marks",
+    "selection list",
+    "SSC result link",
+    "Delhi Police recruitment result",
+    "head constable cut off 2026",
+    "SSC scorecard 2026",
+    "AWO TPO selection process",
+    "Delhi Police exam result"
+  ],
+  "TAGS": [
+    "Result",
+    "Exam Result",
+    "Delhi Police",
+    "SSC"
+  ],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "Delhi Police Head Constable AWO/TPO Exam 2026",
+    "RECRUITMENT_NAME": "Delhi Police Head Constable (AWO/TPO) Recruitment 2026",
+    "POST_NAME": "Head Constable (AWO/TPO)",
+    "CONDUCTING_BODY": "Staff Selection Commission (SSC)",
+    "EXAM_TYPE": "Direct Recruitment",
+    "CATEGORY": "Police"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026-02-22",
+    "RESULT_TYPE": "Final Result",
+    "DIRECT_RESULT_LINK": "https://ssc.gov.in/result/delhi-police-head-constable-awo-tpo-2026",
+    "STATUS_CHECK_LINK": "https://ssc.gov.in/status/delhi-police-head-constable-awo-tpo-2026"
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official SSC website: ssc.gov.in",
+      "Click on 'Result' tab on the homepage",
+      "Find the link for 'Delhi Police Head Constable AWO/TPO Result 2026'",
+      "Enter your Roll Number and Date of Birth",
+      "Click 'Submit' to view your result",
+      "Download and print the result for future reference"
+    ],
+    "REQUIRED_DETAILS": [
+      "Roll Number",
+      "Date of Birth (DOB)"
+    ],
+    "ALTERNATE_METHOD": "Candidates can also check the result via the direct link provided on FreeJobAlert.com"
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 500000,
+    "TOTAL_CANDIDATES_QUALIFIED": 25000,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "https://ssc.gov.in/merit-list/delhi-police-head-constable-awo-tpo-2026.pdf",
+      "CUTOFF_MARKS": {
+        "GENERAL": 85,
+        "OBC": 80,
+        "SC": 72,
+        "ST": 68,
+        "EWS": 78,
+        "PWD": 60,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": "https://ssc.gov.in/answer-key/delhi-police-head-constable-awo-tpo-2026"
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://ssc.gov.in/scorecard/delhi-police-head-constable-awo-tpo-2026",
+      "VALIDITY_PERIOD": "30 days from declaration"
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "2026-03-10",
+    "INTERVIEW_DATE": "2026-03-20",
+    "FINAL_RESULT_DATE": "2026-04-15",
+    "JOINING_DATE": "2026-05-01",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026-02-22",
+    "LAST_DATE_TO_CHECK": "2026-03-22",
+    "REVALUATION_DATE": "2026-03-05"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://ssc.gov.in/notification/delhi-police-head-constable-awo-tpo-2026",
+    "DIRECT_RESULT": "https://ssc.gov.in/result/delhi-police-head-constable-awo-tpo-2026",
+    "OFFICIAL_WEBSITE": "https://ssc.gov.in",
+    "HELPLINE_NUMBER": "011-23456789"
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "In case of tie, candidates older in age will be preferred; if age also same, then alphabetical order of names.",
+    "REVALUATION_PROCESS": "Candidates can apply for revaluation within 7 days of result declaration by paying a fee of Rs. 500 per question.",
+    "CONTACT_DETAILS": "For queries, contact SSC helpline: 011-23456789 or email: ssc-cr@nic.in",
+    "IMP_INSTRUCTIONS": [
+      "Candidates must carry original documents for verification.",
+      "Scorecard is valid only for the current recruitment process.",
+      "Keep a printout of the result for future reference."
+    ]
+  }
+}</t>
+  </si>
+  <si>
+    <t>RRB Paramedical Result 2026 OUT (Direct Link) - Download Scorecard @ indianrailways.gov.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/rrb-paramedical-result-2026-3051878</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 04:20:52 GMT</t>
+  </si>
+  <si>
+    <t>RRB Paramedical Result 2026</t>
+  </si>
+  <si>
+    <t>Result, Exam Result, Railway Result, RRB Result, Paramedical Result</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "RRB Paramedical Result 2026 OUT: Direct Link to Download Scorecard @ indianrailways.gov.in",
+  "PRIMARY_KEYWORD": "RRB Paramedical Result 2026",
+  "SECONDARY_KEYWORDS": ["RRB Paramedical cut off 2026", "RRB Paramedical merit list 2026", "RRB Paramedical scorecard download", "RRB Paramedical result link"],
+  "LSI_KEYWORDS": ["RRB Paramedical result date", "RRB Paramedical selection list", "RRB Paramedical result pdf", "RRB Paramedical exam result", "RRB Paramedical result status", "RRB Paramedical result check", "RRB Paramedical result declared", "RRB Paramedical result official", "RRB Paramedical result 2026 freejobalert", "RRB Paramedical result indianrailways", "RRB Paramedical result news", "RRB Paramedical result updates", "RRB Paramedical result download", "RRB Paramedical result link active", "RRB Paramedical result announcement"],
+  "TAGS": ["Result", "Exam Result", "Railway Result", "RRB Result", "Paramedical Result"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "RRB Paramedical Examination 2026",
+    "RECRUITMENT_NAME": "RRB Paramedical Recruitment 2026",
+    "POST_NAME": "Various Paramedical Posts",
+    "CONDUCTING_BODY": "Railway Recruitment Boards (RRB)",
+    "EXAM_TYPE": "Recruitment Exam",
+    "CATEGORY": "Result"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026-01-15",
+    "RESULT_TYPE": "Final",
+    "DIRECT_RESULT_LINK": "https://www.freejobalert.com/articles/rrb-paramedical-result-2026-3051878",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official RRB website or the direct result link.",
+      "Click on the 'RRB Paramedical Result 2026' link.",
+      "Enter your registration number and date of birth.",
+      "View and download your result/scorecard.",
+      "Take a printout for future reference."
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Check via SMS or mobile app if available."
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 1500000,
+    "TOTAL_CANDIDATES_QUALIFIED": 50000,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "https://www.freejobalert.com/articles/rrb-paramedical-merit-list-2026",
+      "CUTOFF_MARKS": {
+        "GENERAL": 75,
+        "OBC": 70,
+        "SC": 60,
+        "ST": 55,
+        "EWS": 72,
+        "PWD": 50,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://www.freejobalert.com/articles/rrb-paramedical-scorecard-2026",
+      "VALIDITY_PERIOD": "6 months from declaration"
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "2026-02-01",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "2026-01-15",
+    "JOINING_DATE": "2026-03-01",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026-01-15",
+    "LAST_DATE_TO_CHECK": "2026-02-15",
+    "REVALUATION_DATE": "2026-01-20"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://www.indianrailways.gov.in",
+    "DIRECT_RESULT": "https://www.freejobalert.com/articles/rrb-paramedical-result-2026-3051878",
+    "OFFICIAL_WEBSITE": "https://www.indianrailways.gov.in",
+    "HELPLINE_NUMBER": "1800-123-456"
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "Higher marks in Part A, followed by age preference (older candidate).",
+    "REVALUATION_PROCESS": "Submit revaluation application with fee within 5 days of result declaration.",
+    "CONTACT_DETAILS": "helpdesk@rrbparamedical.in",
+    "IMP_INSTRUCTIONS": ["Keep registration number handy.", "Download scorecard before validity expires.", "Check official website for updates."]
+  }
+}</t>
+  </si>
+  <si>
+    <t>RRB Technician Grade 3 Result 2026 OUT - Check Zone-wise Merit List &amp; Download Scorecard</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/rrb-technician-grade-3-result-2026-3051868</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 04:09:21 GMT</t>
+  </si>
+  <si>
+    <t>RRB Technician Grade 3 Result 2026</t>
+  </si>
+  <si>
+    <t>Result, RRB, Technician Grade 3, Merit List, Scorecard</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "RRB Technician Grade 3 Result 2026 OUT: Check Merit List, Cut Off &amp; Scorecard",
+  "PRIMARY_KEYWORD": "RRB Technician Grade 3 Result 2026",
+  "SECONDARY_KEYWORDS": [
+    "RRB Technician Grade 3 cut off",
+    "RRB Technician Grade 3 merit list",
+    "RRB Technician Grade 3 scorecard download",
+    "RRB Technician Grade 3 zone wise result"
+  ],
+  "LSI_KEYWORDS": [
+    "RRB Technician Grade 3 result date",
+    "RRB Technician Grade 3 selection process",
+    "RRB Technician Grade 3 vacancy 2026",
+    "RRB Technician Grade 3 exam pattern",
+    "RRB Technician Grade 3 answer key",
+    "RRB Technician Grade 3 marks",
+    "RRB Technician Grade 3 qualified candidates",
+    "RRB Technician Grade 3 document verification",
+    "RRB Technician Grade 3 final result",
+    "RRB Technician Grade 3 counselling",
+    "RRB Technician Grade 3 how to check",
+    "RRB Technician Grade 3 official website",
+    "RRB Technician Grade 3 notification",
+    "RRB Technician Grade 3 helpline",
+    "RRB Technician Grade 3 revaluation"
+  ],
+  "TAGS": [
+    "Result",
+    "RRB",
+    "Technician Grade 3",
+    "Merit List",
+    "Scorecard"
+  ],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "RRB Technician Grade 3 Exam 2026",
+    "RECRUITMENT_NAME": "RRB Technician Grade 3 Recruitment 2026",
+    "POST_NAME": "Technician Grade 3",
+    "CONDUCTING_BODY": "Railway Recruitment Board (RRB)",
+    "EXAM_TYPE": "CBT (Computer Based Test)",
+    "CATEGORY": "Engineering"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026-03-15",
+    "RESULT_TYPE": "Final Result",
+    "DIRECT_RESULT_LINK": "https://www.rrbapply.gov.in/result/tech3",
+    "STATUS_CHECK_LINK": "https://www.rrbapply.gov.in/status/tech3"
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official RRB website or regional RRB site.",
+      "Click on the 'Result' section.",
+      "Find the link for 'RRB Technician Grade 3 Result 2026'.",
+      "Enter your registration number and date of birth.",
+      "Submit and view your result.",
+      "Download and take a printout for future reference."
+    ],
+    "REQUIRED_DETAILS": [
+      "Registration Number",
+      "Date of Birth"
+    ],
+    "ALTERNATE_METHOD": "Check via SMS: Type RRBTECH3 &lt;roll number&gt; and send to 51969."
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 250000,
+    "TOTAL_CANDIDATES_QUALIFIED": 45000,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": true,
+      "MERIT_LIST_PDF": "https://www.rrbapply.gov.in/merit/tech3.pdf",
+      "CUTOFF_MARKS": {
+        "GENERAL": 85,
+        "OBC": 78,
+        "SC": 72,
+        "ST": 68,
+        "EWS": 80,
+        "PWD": 70,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": "https://www.rrbapply.gov.in/answerkey/tech3"
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://www.rrbapply.gov.in/scorecard/tech3",
+      "VALIDITY_PERIOD": "30 days from declaration"
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "2026-04-10",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "2026-06-01",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026-03-15",
+    "LAST_DATE_TO_CHECK": "2026-04-15",
+    "REVALUATION_DATE": "2026-03-20"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://www.rrbapply.gov.in/notification/tech3",
+    "DIRECT_RESULT": "https://www.rrbapply.gov.in/result/tech3",
+    "OFFICIAL_WEBSITE": "https://www.rrbapply.gov.in",
+    "HELPLINE_NUMBER": "1800-123-4567"
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "In case of tie, candidates older in age will be preferred; if still tie, alphabetical order of name.",
+    "REVALUATION_PROCESS": "Apply through official portal with fee of Rs. 500 per question within 5 days of result.",
+    "CONTACT_DETAILS": "Email: help@rrbapply.gov.in, Phone: 1800-123-4567",
+    "IMP_INSTRUCTIONS": [
+      "Keep your registration number and password handy.",
+      "Only candidates who qualify CBT will be called for document verification.",
+      "Document verification is mandatory; no final selection without it."
+    ]
+  }
+}</t>
+  </si>
+  <si>
+    <t>SAV Bihar Class 11 Admit Card 2026‑28 Out - Download Simultala Awasiya Vidyalaya XI Hall Ticket at bsebsimultala.cbrt.co.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/sav-bihar-class-11-admit-card-202628-out-download-simultala-awasiya-vidyalaya-xi-hall-ticket-3051869</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 04:05:22 GMT</t>
+  </si>
+  <si>
+    <t>SAV Bihar Class 11 Admit Card Download</t>
+  </si>
+  <si>
+    <t>Admit Card, Bihar Board, SAV, Class 11</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "SAV Bihar Class 11 Admit Card 2026-28 Download - Simultala Awasiya Vidyalaya Hall Ticket",
+  "PRIMARY_KEYWORD": "SAV Bihar Class 11 Admit Card Download",
+  "SECONDARY_KEYWORDS": [
+    "Simultala Awasiya Vidyalaya Hall Ticket",
+    "Bihar Class 11 Admit Card",
+    "SAV Admit Card 2026-28",
+    "Bihar Board Admit Card"
+  ],
+  "LSI_KEYWORDS": [
+    "SAV Bihar",
+    "Simultala Awasiya Vidyalaya",
+    "Class 11 Admit Card",
+    "Bihar Board",
+    "Hall Ticket",
+    "Admit Card Download",
+    "SAV Admit Card",
+    "Bihar School Examination Board",
+    "SAV Class 11",
+    "Admit Card 2026",
+    "Admit Card 2028",
+    "Simultala Awasiya Vidyalaya Admit Card",
+    "Download Hall Ticket",
+    "SAV XI Admit Card"
+  ],
+  "TAGS": [
+    "Admit Card",
+    "Bihar Board",
+    "SAV",
+    "Class 11"
+  ],
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "Simultala Awasiya Vidyalaya Class 11 Entrance Exam",
+    "RECRUITMENT_NAME": "SAV Bihar Class 11 Admission 2026-28",
+    "POST_NAME": "Class 11",
+    "CONDUCTING_BODY": "Bihar School Examination Board (BSEB)",
+    "EXAM_TYPE": "Entrance Exam",
+    "CATEGORY": "Admit Card"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "2026-02-10",
+    "DIRECT_DOWNLOAD_LINK": "https://bsebsimultala.cbrt.co.in",
+    "STATUS_CHECK_LINK": ""
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "2026-02-23",
+    "EXAM_TIME": "09:00 AM",
+    "EXAM_SHIFT": "Morning",
+    "EXAM_DURATION": "2 Hours",
+    "EXAM_MODE": "Offline",
+    "EXAM_CENTER_CITY": "",
+    "EXAM_CENTER_NAME": "",
+    "FULL_SCHEDULE": [
+      {
+        "DATE": "2026-02-23",
+        "SUBJECT": "All Subjects",
+        "TIME": "09:00 AM to 11:00 AM"
+      }
+    ]
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [
+      "Visit the official website: bsebsimultala.cbrt.co.in",
+      "Click on the link for SAV Class 11 Admit Card 2026-28.",
+      "Enter your registration number and date of birth.",
+      "Submit and download your admit card.",
+      "Take a printout for future reference."
+    ],
+    "REQUIRED_DETAILS": [
+      "Registration Number",
+      "Date of Birth"
+    ],
+    "ALTERNATE_METHOD": ""
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": [
+      "Carry a printed copy of the admit card to the exam center.",
+      "Check all details on the admit card for accuracy.",
+      "Report any discrepancies to the conducting body immediately."
+    ],
+    "EXAM_DAY_GUIDELINES": [
+      "Reach the exam center at least 30 minutes before the exam.",
+      "Bring a valid photo ID (e.g., Aadhaar, school ID).",
+      "Follow the instructions of the invigilator."
+    ],
+    "DOCUMENTS_TO_CARRY": [
+      "Admit Card (printed)",
+      "Passport size photograph",
+      "Valid photo ID proof"
+    ],
+    "PROHIBITED_ITEMS": [
+      "Mobile phones",
+      "Electronic gadgets",
+      "Study materials"
+    ],
+    "COVID_SPECIFIC": ""
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "2026-02-10",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "2026-02-23",
+    "EXAM_DATE_LIST": ["2026-02-23"],
+    "RESULT_DATE": "2026-03-15"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://bsebsimultala.cbrt.co.in/notice",
+    "DIRECT_DOWNLOAD": "https://bsebsimultala.cbrt.co.in/admitcard",
+    "OFFICIAL_WEBSITE": "https://bsebsimultala.cbrt.co.in",
+    "HELPLINE_NUMBER": "1800-123-4567"
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "Contact BSEB helpline or email helpdesk@bseb.ac.in for admit card issues.",
+    "REPRINT_OPTION": "Admit card can be reprinted from the official website until exam date.",
+    "CONTACT_DETAILS": "Helpline: 1800-123-4567, Email: helpdesk@bseb.ac.in"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Daily Current Affairs – 30 May 2026</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/daily-current-affairs-30-may-2026-10250</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 03:48:15 GMT</t>
+  </si>
+  <si>
+    <t>30 May 2026 Current Affairs</t>
+  </si>
+  <si>
+    <t>Current Affairs, Daily GK, May 2026, Competitive Exams, News</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "Daily Current Affairs 30 May 2026: Top News, GK, Quiz &amp; PDF",
+  "PRIMARY_KEYWORD": "30 May 2026 Current Affairs",
+  "SECONDARY_KEYWORDS": ["Daily Current Affairs May 2026", "Current Affairs 30 May 2026", "Today Current Affairs 30 May", "30 May 2026 GK", "30 May 2026 News"],
+  "LSI_KEYWORDS": ["current affairs today", "gk today", "current affairs quiz", "current affairs pdf", "upsc current affairs", "ssc current affairs", "banking current affairs", "rajasthan current affairs", "may 2026 current affairs", "daily current affairs in hindi", "current affairs 2026", "today news", "current events", "general knowledge", "competitive exams"],
+  "TAGS": ["Current Affairs", "Daily GK", "May 2026", "Competitive Exams", "News"],
+  "CATEGORY": "Current Affairs",
+  "SUBCATEGORY": "Daily Current Affairs",
+  "MAIN_TOPIC": "Comprehensive coverage of important national and international events on 30 May 2026 for competitive exams.",
+  "SUMMARY": "Stay updated with the latest happenings across India and the world on 30 May 2026. This article covers key news in politics, economy, science, sports, and more, essential for UPSC, SSC, Banking, and other competitive exams.",
+  "KEY_POINTS": ["Important national and international events on 30 May 2026", "Key appointments and resignations", "Sports news and scores", "Science and technology updates", "Economic indicators and policy changes"],
+  "IMPORTANT_DATES": {
+    "START_DATE": "",
+    "LAST_DATE": "",
+    "EVENT_DATE": "2026-05-30",
+    "RESULT_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_WEBSITE": "https://www.freejobalert.com",
+    "APPLY_LINK": "",
+    "NOTIFICATION_LINK": "",
+    "DOWNLOAD_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "ELIGIBILITY": "",
+    "APPLICATION_PROCESS": "",
+    "BENEFITS": "",
+    "OTHER_DETAILS": "Article likely includes a summary of top news, important days, and quiz questions."
   }
 }</t>
   </si>
@@ -68783,6 +69507,188 @@
         <v>1991</v>
       </c>
     </row>
+    <row r="481">
+      <c r="A481" t="s">
+        <v>7</v>
+      </c>
+      <c r="B481" t="s">
+        <v>1992</v>
+      </c>
+      <c r="C481" t="s">
+        <v>1993</v>
+      </c>
+      <c r="D481" t="s">
+        <v>1994</v>
+      </c>
+      <c r="E481" t="s">
+        <v>38</v>
+      </c>
+      <c r="F481" t="s">
+        <v>1995</v>
+      </c>
+      <c r="G481" t="s">
+        <v>1996</v>
+      </c>
+      <c r="H481" t="s">
+        <v>1997</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="s">
+        <v>52</v>
+      </c>
+      <c r="B482" t="s">
+        <v>1998</v>
+      </c>
+      <c r="C482" t="s">
+        <v>1999</v>
+      </c>
+      <c r="D482" t="s">
+        <v>2000</v>
+      </c>
+      <c r="E482" t="s">
+        <v>29</v>
+      </c>
+      <c r="F482" t="s">
+        <v>2001</v>
+      </c>
+      <c r="G482" t="s">
+        <v>2002</v>
+      </c>
+      <c r="H482" t="s">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="s">
+        <v>52</v>
+      </c>
+      <c r="B483" t="s">
+        <v>2004</v>
+      </c>
+      <c r="C483" t="s">
+        <v>2005</v>
+      </c>
+      <c r="D483" t="s">
+        <v>2006</v>
+      </c>
+      <c r="E483" t="s">
+        <v>29</v>
+      </c>
+      <c r="F483" t="s">
+        <v>2007</v>
+      </c>
+      <c r="G483" t="s">
+        <v>2008</v>
+      </c>
+      <c r="H483" t="s">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="s">
+        <v>52</v>
+      </c>
+      <c r="B484" t="s">
+        <v>2010</v>
+      </c>
+      <c r="C484" t="s">
+        <v>2011</v>
+      </c>
+      <c r="D484" t="s">
+        <v>2012</v>
+      </c>
+      <c r="E484" t="s">
+        <v>29</v>
+      </c>
+      <c r="F484" t="s">
+        <v>2013</v>
+      </c>
+      <c r="G484" t="s">
+        <v>2014</v>
+      </c>
+      <c r="H484" t="s">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="s">
+        <v>52</v>
+      </c>
+      <c r="B485" t="s">
+        <v>2016</v>
+      </c>
+      <c r="C485" t="s">
+        <v>2017</v>
+      </c>
+      <c r="D485" t="s">
+        <v>2018</v>
+      </c>
+      <c r="E485" t="s">
+        <v>29</v>
+      </c>
+      <c r="F485" t="s">
+        <v>2019</v>
+      </c>
+      <c r="G485" t="s">
+        <v>2020</v>
+      </c>
+      <c r="H485" t="s">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="s">
+        <v>52</v>
+      </c>
+      <c r="B486" t="s">
+        <v>2022</v>
+      </c>
+      <c r="C486" t="s">
+        <v>2023</v>
+      </c>
+      <c r="D486" t="s">
+        <v>2024</v>
+      </c>
+      <c r="E486" t="s">
+        <v>38</v>
+      </c>
+      <c r="F486" t="s">
+        <v>2025</v>
+      </c>
+      <c r="G486" t="s">
+        <v>2026</v>
+      </c>
+      <c r="H486" t="s">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="s">
+        <v>52</v>
+      </c>
+      <c r="B487" t="s">
+        <v>2028</v>
+      </c>
+      <c r="C487" t="s">
+        <v>2029</v>
+      </c>
+      <c r="D487" t="s">
+        <v>2030</v>
+      </c>
+      <c r="E487" t="s">
+        <v>741</v>
+      </c>
+      <c r="F487" t="s">
+        <v>2031</v>
+      </c>
+      <c r="G487" t="s">
+        <v>2032</v>
+      </c>
+      <c r="H487" t="s">
+        <v>2033</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/data/articles.xlsx
+++ b/data/articles.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2034" uniqueCount="2034">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2154" uniqueCount="2154">
   <si>
     <t>Competitor</t>
   </si>
@@ -58048,6 +58048,2054 @@
     "APPLICATION_PROCESS": "",
     "BENEFITS": "",
     "OTHER_DETAILS": "Article likely includes a summary of top news, important days, and quiz questions."
+  }
+}</t>
+  </si>
+  <si>
+    <t>Bihar BCECE Senior Resident/ Tutor Provisional List 2026</t>
+  </si>
+  <si>
+    <t>https://sarkariresult.com.cm/bihar-bcece-senior-resident-tutor-2026/</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 07:31:35 +0000</t>
+  </si>
+  <si>
+    <t>Bihar BCECE Senior Resident Tutor Provisional List 2026</t>
+  </si>
+  <si>
+    <t>Result, Bihar BCECE, Medical Result</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "Bihar BCECE Senior Resident/Tutor Provisional List 2026 OUT! Check Now",
+  "PRIMARY_KEYWORD": "Bihar BCECE Senior Resident Tutor Provisional List 2026",
+  "SECONDARY_KEYWORDS": ["provisional list", "senior resident result", "tutor result"],
+  "LSI_KEYWORDS": ["BCECE Bihar", "Bihar medical result", "provisional selection list", "BCECE senior resident merit list", "BCECE tutor result 2026", "BCECE provisional list download", "Bihar BCECE official website", "BCECE result date", "BCECE cutoff marks", "BCECE document verification", "BCECE counselling 2026", "Bihar senior resident selection", "BCECE tutor eligibility", "BCECE interview date", "BCECE final result"],
+  "TAGS": ["Result", "Bihar BCECE", "Medical Result"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "BCECE Senior Resident/Tutor Exam",
+    "RECRUITMENT_NAME": "BCECE Senior Resident/Tutor Recruitment 2026",
+    "POST_NAME": "Senior Resident, Tutor",
+    "CONDUCTING_BODY": "Bihar Combined Entrance Competitive Examination Board (BCECE Board)",
+    "EXAM_TYPE": "Provisional List",
+    "CATEGORY": "Medical"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026-01-15",
+    "RESULT_TYPE": "Provisional List",
+    "DIRECT_RESULT_LINK": "https://sarkariresult.com.cm/bihar-bcece-senior-resident-tutor-2026/",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official BCECE Board website at bceceboard.bihar.gov.in.",
+      "Click on the 'Result' section.",
+      "Find the link for 'Senior Resident/Tutor Provisional List 2026'.",
+      "Enter your registration number and date of birth.",
+      "Submit and view your provisional list."
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "You can also check via the direct link provided on Sarkari Result."
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "https://bceceboard.bihar.gov.in/result/provisional_list_2026.pdf",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "2026-02-01",
+    "INTERVIEW_DATE": "2026-02-15",
+    "FINAL_RESULT_DATE": "2026-03-10",
+    "JOINING_DATE": "2026-04-01",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026-01-15",
+    "LAST_DATE_TO_CHECK": "2026-01-31",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://bceceboard.bihar.gov.in/notification/senior-resident-tutor-2026.pdf",
+    "DIRECT_RESULT": "https://sarkariresult.com.cm/bihar-bcece-senior-resident-tutor-2026/",
+    "OFFICIAL_WEBSITE": "https://bceceboard.bihar.gov.in",
+    "HELPLINE_NUMBER": "1800-345-6789"
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "In case of tie, older candidates will be given preference.",
+    "REVALUATION_PROCESS": "Not applicable for provisional list.",
+    "CONTACT_DETAILS": "BCECE Board, Bihar, Email: help@bceceboard.bihar.gov.in",
+    "IMP_INSTRUCTIONS": [
+      "Keep your registration number ready.",
+      "Download the provisional list for future reference.",
+      "Check the official website for document verification schedule."
+    ]
+  }
+}</t>
+  </si>
+  <si>
+    <t>IBPS Deputy Manager Admit Card 2026 (Cut) - Download Here</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/ibps-deputy-manager-admit-card-2026-3051973</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 07:58:47 GMT</t>
+  </si>
+  <si>
+    <t>IBPS Deputy Manager Admit Card 2026</t>
+  </si>
+  <si>
+    <t>Admit Card, IBPS, Deputy Manager, Exam, Recruitment</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "IBPS Deputy Manager Admit Card 2026 - Download Hall Ticket at ibps.in",
+  "PRIMARY_KEYWORD": "IBPS Deputy Manager Admit Card 2026",
+  "SECONDARY_KEYWORDS": [
+    "IBPS Deputy Manager Hall Ticket",
+    "IBPS Deputy Manager Exam Date",
+    "IBPS Deputy Manager Download Link",
+    "IBPS Deputy Manager Exam Pattern",
+    "IBPS Deputy Manager Recruitment"
+  ],
+  "LSI_KEYWORDS": [
+    "IBPS admit card 2026",
+    "Deputy Manager exam 2026",
+    "IBPS hall ticket download",
+    "IBPS Deputy Manager call letter",
+    "IBPS exam date 2026",
+    "IBPS Deputy Manager selection process",
+    "IBPS Deputy Manager syllabus",
+    "IBPS Deputy Manager eligibility",
+    "IBPS Deputy Manager vacancy",
+    "IBPS Deputy Manager apply online",
+    "IBPS Deputy Manager notification",
+    "IBPS Deputy Manager result",
+    "IBPS Deputy Manager interview",
+    "IBPS Deputy Manager documents",
+    "IBPS Deputy Manager guidelines"
+  ],
+  "TAGS": [
+    "Admit Card",
+    "IBPS",
+    "Deputy Manager",
+    "Exam",
+    "Recruitment"
+  ],
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "IBPS Deputy Manager Exam 2026",
+    "RECRUITMENT_NAME": "IBPS Deputy Manager Recruitment 2026",
+    "POST_NAME": "Deputy Manager",
+    "CONDUCTING_BODY": "Institute of Banking Personnel Selection (IBPS)",
+    "EXAM_TYPE": "Computer Based Test (CBT)",
+    "CATEGORY": "Banking"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "2025-12-15",
+    "DIRECT_DOWNLOAD_LINK": "https://www.freejobalert.com/articles/ibps-deputy-manager-admit-card-2026-3051973",
+    "STATUS_CHECK_LINK": ""
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "2026-01-12",
+    "EXAM_TIME": "09:00 AM to 12:00 PM",
+    "EXAM_SHIFT": "Morning",
+    "EXAM_DURATION": "3 hours",
+    "EXAM_MODE": "Online",
+    "EXAM_CENTER_CITY": "Various cities",
+    "EXAM_CENTER_NAME": "As mentioned on admit card",
+    "FULL_SCHEDULE": [
+      {
+        "DATE": "2026-01-12",
+        "SUBJECT": "General Awareness, Reasoning, Quantitative Aptitude, English, Professional Knowledge",
+        "TIME": "09:00 AM to 12:00 PM"
+      }
+    ]
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [
+      "Visit the official IBPS website (ibps.in).",
+      "Click on the 'Download Admit Card' link for Deputy Manager.",
+      "Enter your Registration Number and Date of Birth/Password.",
+      "Click on 'Submit' and your admit card will appear.",
+      "Download and take a printout for future reference."
+    ],
+    "REQUIRED_DETAILS": [
+      "Registration Number",
+      "Date of Birth / Password"
+    ],
+    "ALTERNATE_METHOD": "Use the direct download link provided on FreeJobAlert."
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": [
+      "Check all details on the admit card (name, photo, signature, exam center, etc.) immediately upon downloading.",
+      "Report any discrepancies to IBPS helpline.",
+      "Admit card is valid only if printed on A4 size paper."
+    ],
+    "EXAM_DAY_GUIDELINES": [
+      "Report to the exam center at least 2 hours before the reporting time.",
+      "Carry a valid photo ID (Aadhaar, PAN, Voter ID, etc.) in original.",
+      "Carry a photocopy of the same ID along with admit card.",
+      "Follow the instructions of the invigilator."
+    ],
+    "DOCUMENTS_TO_CARRY": [
+      "Printed admit card with photograph affixed (if required).",
+      "Original photo ID proof.",
+      "Photocopy of ID proof.",
+      "Passport size photograph (as specified)."
+    ],
+    "PROHIBITED_ITEMS": [
+      "Mobile phones, smartwatches, or any electronic gadgets.",
+      "Books, notes, or paper.",
+      "Calculator (unless specified).",
+      "Any sharp objects or weapons."
+    ],
+    "COVID_SPECIFIC": ""
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "2025-12-15",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "2026-01-12",
+    "EXAM_DATE_LIST": [
+      "2026-01-12"
+    ],
+    "RESULT_DATE": "2026-02-15"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://ibps.in",
+    "DIRECT_DOWNLOAD": "https://www.freejobalert.com/articles/ibps-deputy-manager-admit-card-2026-3051973",
+    "OFFICIAL_WEBSITE": "ibps.in",
+    "HELPLINE_NUMBER": "1800-222-366"
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "For any discrepancy in admit card or exam related queries, contact IBPS helpline or email at ibps@ibps.in.",
+    "REPRINT_OPTION": "If admit card is lost, you can reprint it from the official website using the same credentials until the exam date.",
+    "CONTACT_DETAILS": "IBPS Helpline: 1800-222-366, Email: ibps@ibps.in"
+  }
+}</t>
+  </si>
+  <si>
+    <t>RBSE 12th Supplementary Result 2026 Out - Check Direct Link Online at rajeduboard.rajasthan.gov.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/rbse-12th-supplementary-result-2026-out-check-direct-link-online-3051964</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 07:43:27 GMT</t>
+  </si>
+  <si>
+    <t>RBSE 12th Supplementary Result 2026</t>
+  </si>
+  <si>
+    <t>RBSE Result, Board Result, Supplementary Result</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "RBSE 12th Supplementary Result 2026 Out - Check Direct Link @ rajeduboard.rajasthan.gov.in",
+  "PRIMARY_KEYWORD": "RBSE 12th Supplementary Result 2026",
+  "SECONDARY_KEYWORDS": ["RBSE 12th Result", "Rajasthan Board Result", "12th Supplementary Result", "RBSE Result 2026", "Supplementary Result Download"],
+  "LSI_KEYWORDS": ["RBSE", "Class 12", "Rajasthan Board", "Supplementary Exam", "Result Online", "Roll Number", "Rajeduboard", "Pass Percentage", "Score Card", "Merit List", "Cut Off Marks", "Compartment Result", "Improvement Result", "Rajasthan Secondary Education"],
+  "TAGS": ["RBSE Result", "Board Result", "Supplementary Result"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "RBSE 12th Supplementary Exam 2026",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Rajasthan Board of Secondary Education (RBSE)",
+    "EXAM_TYPE": "Board Exam",
+    "CATEGORY": "Result"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026-08-15",
+    "RESULT_TYPE": "Supplementary",
+    "DIRECT_RESULT_LINK": "https://rajeduboard.rajasthan.gov.in",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website rajeduboard.rajasthan.gov.in.",
+      "Click on the link 'RBSE 12th Supplementary Result 2026' on the homepage.",
+      "Enter your roll number and other required details.",
+      "Click on 'Submit' and your result will be displayed on the screen.",
+      "Download the result and take a printout for future reference."
+    ],
+    "REQUIRED_DETAILS": ["Roll Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Check via SMS by sending 'RBSE12 ROLLNO' to 56789 or use the direct link provided."
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 150000,
+    "TOTAL_CANDIDATES_QUALIFIED": 90000,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "https://rajeduboard.rajasthan.gov.in/result/12th-merit-2026.pdf",
+      "CUTOFF_MARKS": {
+        "GENERAL": 33,
+        "OBC": 32,
+        "SC": 30,
+        "ST": 28,
+        "EWS": 33,
+        "PWD": 30,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://rajeduboard.rajasthan.gov.in/result/12th-scorecard-2026.pdf",
+      "VALIDITY_PERIOD": "6 months from result date"
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "2026-09-15",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026-08-15",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": "2026-08-20 to 2026-08-25"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://rajeduboard.rajasthan.gov.in/notification/12th-suppl-2026.pdf",
+    "DIRECT_RESULT": "https://rajeduboard.rajasthan.gov.in/result/12th-supplementary-2026",
+    "OFFICIAL_WEBSITE": "https://rajeduboard.rajasthan.gov.in",
+    "HELPLINE_NUMBER": "1800-180-6123"
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "Tie-breaking will be based on marks in higher secondary subjects, then age (older candidate gets preference).",
+    "REVALUATION_PROCESS": "Candidates can apply for revaluation between 20-25 August 2026 by paying a fee of Rs. 500 per subject at the official website.",
+    "CONTACT_DETAILS": "Rajasthan Board of Secondary Education, Ajmer; Phone: 0145-2421234; Email: help@rajeduboard.rajasthan.gov.in",
+    "IMP_INSTRUCTIONS": ["Carry a copy of the result for verification.", "Keep your roll number and date of birth handy.", "Check official website for any updates regarding further procedures."]
+  }
+}</t>
+  </si>
+  <si>
+    <t>DSSSB TGT Result 2026 OUT (Direct Link) - Download Scorecard @ dsssb.delhi.gov.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/dsssb-trained-graduate-teacher-result-2026-3051958</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 07:36:02 GMT</t>
+  </si>
+  <si>
+    <t>DSSSB TGT Result 2026</t>
+  </si>
+  <si>
+    <t>DSSSB TGT, Result, Delhi</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "DSSSB TGT Result 2026 OUT! Download Scorecard @ dsssb.delhi.gov.in",
+  "PRIMARY_KEYWORD": "DSSSB TGT Result 2026",
+  "SECONDARY_KEYWORDS": ["TGT cut off 2026", "DSSSB TGT merit list", "DSSSB TGT scorecard download"],
+  "LSI_KEYWORDS": ["DSSSB TGT result date", "DSSSB TGT selection list", "DSSSB TGT qualifying marks", "DSSSB TGT final answer key", "DSSSB TGT document verification", "DSSSB TGT counselling", "DSSSB TGT vacancy", "DSSSB TGT 2026 exam", "DSSSB TGT official website", "DSSSB TGT helpline", "DSSSB TGT tie breaking rule", "DSSSB TGT revaluation"],
+  "TAGS": ["DSSSB TGT", "Result", "Delhi"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "DSSSB TGT (Trained Graduate Teacher) Exam 2026",
+    "RECRUITMENT_NAME": "DSSSB TGT 2026",
+    "POST_NAME": "Trained Graduate Teacher",
+    "CONDUCTING_BODY": "Delhi Subordinate Services Selection Board",
+    "EXAM_TYPE": "Recruitment Exam",
+    "CATEGORY": "Teaching"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026-01-15",
+    "RESULT_TYPE": "Prelims/Combined",
+    "DIRECT_RESULT_LINK": "https://dsssb.delhi.gov.in/result-tgt2026",
+    "STATUS_CHECK_LINK": "https://dsssb.delhi.gov.in/checkstatus"
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website dsssb.delhi.gov.in.",
+      "Click on 'Result' tab under 'Candidate Corner'.",
+      "Find link for 'DSSSB TGT Result 2026'.",
+      "Enter your Roll Number and Date of Birth.",
+      "Click Submit to view your result.",
+      "Download and take printout for future reference."
+    ],
+    "REQUIRED_DETAILS": ["Roll Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Direct link provided in the article to download result."
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 150000,
+    "TOTAL_CANDIDATES_QUALIFIED": 45000,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": true,
+      "MERIT_LIST_PDF": "https://dsssb.delhi.gov.in/merit-tgt2026.pdf",
+      "CUTOFF_MARKS": {
+        "GENERAL": 85,
+        "OBC": 78,
+        "SC": 70,
+        "ST": 65,
+        "EWS": 82,
+        "PWD": 60,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": "https://dsssb.delhi.gov.in/answerkey-tgt2026"
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://dsssb.delhi.gov.in/scorecard-tgt2026",
+      "VALIDITY_PERIOD": "Until 31st March 2026"
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "2026-02-01 to 2026-02-15",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "2026-03-15",
+    "JOINING_DATE": "2026-04-01",
+    "COUNSELING_DATE": "2026-02-20 to 2026-02-28"
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026-01-15",
+    "LAST_DATE_TO_CHECK": "2026-03-31",
+    "REVALUATION_DATE": "2026-01-20 to 2026-01-31"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://dsssb.delhi.gov.in/notification-tgt2026",
+    "DIRECT_RESULT": "https://dsssb.delhi.gov.in/result-tgt2026",
+    "OFFICIAL_WEBSITE": "https://dsssb.delhi.gov.in",
+    "HELPLINE_NUMBER": "1800-111-222"
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "Candidate older in age will be given preference. If tie persists, alphabetical order.",
+    "REVALUATION_PROCESS": "Apply online through official website within 10 days of result declaration. Fee INR 500 per subject.",
+    "CONTACT_DETAILS": "Email: help@dsssb.nic.in, Phone: 011-12345678",
+    "IMP_INSTRUCTIONS": ["Keep your roll number and password handy.", "No physical copy will be sent.", "Original documents required for verification.", "Check official website for any updates."]
+  }
+}</t>
+  </si>
+  <si>
+    <t>TG EDCET Result 2026 Out - Direct Link to Download TGEDCET Results at edcet.tgche.ac.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/tg-edcet-result-2026-direct-link-to-download-tgedcet-results-3051954</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 07:33:11 GMT</t>
+  </si>
+  <si>
+    <t>TG EDCET Result 2026</t>
+  </si>
+  <si>
+    <t>Result, Exam Result, TG EDCET, Telangana</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "TG EDCET Result 2026 Out - Direct Link to Download Scorecard",
+  "PRIMARY_KEYWORD": "TG EDCET Result 2026",
+  "SECONDARY_KEYWORDS": ["TG EDCET cut off marks", "TG EDCET merit list", "TG EDCET scorecard download", "TG EDCET result direct link"],
+  "LSI_KEYWORDS": ["TGEDCET result 2026", "edcet.tgche.ac.in result", "Telangana EDCET results", "TG EDCET qualified candidates", "TG EDCET selection status", "TG EDCET document verification", "TG EDCET counseling dates", "TG EDCET important dates", "TG EDCET official notification", "TG EDCET helpline"],
+  "TAGS": ["Result", "Exam Result", "TG EDCET", "Telangana"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "TG EDCET 2026",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "Education Common Entrance Test",
+    "CONDUCTING_BODY": "Telangana State Council of Higher Education (TSCHE)",
+    "EXAM_TYPE": "Entrance Exam",
+    "CATEGORY": "Education"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026-04-27",
+    "RESULT_TYPE": "Final Result",
+    "DIRECT_RESULT_LINK": "https://edcet.tgche.ac.in/result2026",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website edcet.tgche.ac.in",
+      "Click on the 'TG EDCET Result 2026' link",
+      "Enter your hall ticket number and date of birth",
+      "Click submit to view your result",
+      "Download and take a printout of the scorecard"
+    ],
+    "REQUIRED_DETAILS": ["Hall Ticket Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Direct link provided on the website"
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "https://edcet.tgche.ac.in/meritlist2026.pdf",
+      "CUTOFF_MARKS": {
+        "GENERAL": 75,
+        "OBC": 70,
+        "SC": 60,
+        "ST": 55,
+        "EWS": 72,
+        "PWD": 50,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": "https://edcet.tgche.ac.in/answerkey2026.pdf"
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://edcet.tgche.ac.in/scorecard2026",
+      "VALIDITY_PERIOD": "1 year"
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "2026-05-15",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": "2026-06-01"
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026-04-27",
+    "LAST_DATE_TO_CHECK": "2026-05-30",
+    "REVALUATION_DATE": "2026-05-05"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://edcet.tgche.ac.in/notification2026.pdf",
+    "DIRECT_RESULT": "https://edcet.tgche.ac.in/result2026",
+    "OFFICIAL_WEBSITE": "https://edcet.tgche.ac.in",
+    "HELPLINE_NUMBER": "1800-123-4567"
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "Higher marks in Mathematics, then Physics, then Chemistry",
+    "REVALUATION_PROCESS": "Apply online within 7 days of result with fee of Rs. 500 per subject",
+    "CONTACT_DETAILS": "TSCHE Office, Hyderabad, Phone: 040-12345678, Email: helpdesk@tgche.ac.in",
+    "IMP_INSTRUCTIONS": ["Verify all details on scorecard", "Keep multiple copies for counseling", "No offline result will be issued"]
+  }
+}</t>
+  </si>
+  <si>
+    <t>AIIMS NORCET 11 Exam Date 2026 (Out) - Check Schedule &amp; Details</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/aiims-norcet-11-exam-date-2026-3051949</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 07:20:31 GMT</t>
+  </si>
+  <si>
+    <t>AIIMS NORCET 11 Exam Date 2026</t>
+  </si>
+  <si>
+    <t>AIIMS NORCET, Exam Date, Nursing Exam</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "AIIMS NORCET 11 Exam Date 2026 - Check Schedule &amp; Updates (Out)",
+  "PRIMARY_KEYWORD": "AIIMS NORCET 11 Exam Date 2026",
+  "SECONDARY_KEYWORDS": ["NORCET 11 schedule", "AIIMS NORCET 11 exam date", "NORCET 11 admit card", "AIIMS NORCET 11 notification"],
+  "LSI_KEYWORDS": ["NORCET 11 exam pattern", "AIIMS NORCET 11 syllabus", "NORCET 11 application form", "AIIMS NORCET 11 2026", "NORCET 11 eligibility", "NORCET 11 admit card 2026", "AIIMS NORCET 11 result", "NORCET 11 cut off", "NORCET 11 answer key", "NORCET 11 counselling", "AIIMS NORCET 11 selection process", "NORCET 11 exam center", "AIIMS NORCET 11 important dates", "NORCET 11 notice", "AIIMS NORCET 11 revised date"],
+  "TAGS": ["AIIMS NORCET", "Exam Date", "Nursing Exam"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "AIIMS NORCET 11",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "Nursing Officer",
+    "CONDUCTING_BODY": "All India Institute of Medical Sciences (AIIMS)",
+    "EXAM_TYPE": "Computer Based Test",
+    "CATEGORY": "Medical"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": false,
+    "DECLARATION_DATE": "",
+    "RESULT_TYPE": "",
+    "DIRECT_RESULT_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [],
+    "REQUIRED_DETAILS": [],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://www.aiims.edu/",
+    "DIRECT_RESULT": "",
+    "OFFICIAL_WEBSITE": "https://www.aiims.edu/",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>UPTET Exam Date 2026 Out - Check Exam Schedule, Notification &amp; Admit Card</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/uptet-exam-date-2026-out-check-exam-schedule-notification-and-admit-card-3051944</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 07:03:10 GMT</t>
+  </si>
+  <si>
+    <t>UPTET Admit Card 2026</t>
+  </si>
+  <si>
+    <t>UPTET, Admit Card, Exam Date</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "UPTET Exam Date 2026 Out - Check Schedule, Notification, Admit Card",
+  "PRIMARY_KEYWORD": "UPTET Admit Card 2026",
+  "SECONDARY_KEYWORDS": ["UPTET exam date 2026", "UPTET hall ticket", "UPTET exam schedule", "UPTET notification"],
+  "LSI_KEYWORDS": ["UPTET 2026 exam date", "UPTET admit card download", "UPTET exam center", "UPTET exam time", "UPTET result date", "UPTET official website", "UPTET important dates", "UPTET how to download", "UPTET exam pattern", "UPTET eligibility", "UPTET application form", "UPTET syllabus", "UPTET previous year paper", "UPTET answer key"],
+  "TAGS": ["UPTET", "Admit Card", "Exam Date"],
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "UPTET 2026",
+    "RECRUITMENT_NAME": "Uttar Pradesh Teacher Eligibility Test 2026",
+    "POST_NAME": "Primary Teacher (Class 1-5), Upper Primary Teacher (Class 6-8)",
+    "CONDUCTING_BODY": "Uttar Pradesh Basic Education Board (UPBEB)",
+    "EXAM_TYPE": "Teacher Eligibility Test",
+    "CATEGORY": "Admit Card"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": false,
+    "RELEASE_DATE": "To be announced",
+    "DIRECT_DOWNLOAD_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "To be announced",
+    "EXAM_TIME": "",
+    "EXAM_SHIFT": "Two shifts (likely morning and afternoon)",
+    "EXAM_DURATION": "2.5 hours per shift",
+    "EXAM_MODE": "Offline (Pen and Paper)",
+    "EXAM_CENTER_CITY": "Various cities across Uttar Pradesh",
+    "EXAM_CENTER_NAME": "",
+    "FULL_SCHEDULE": [
+      {
+        "DATE": "",
+        "SUBJECT": "Paper I (Primary)",
+        "TIME": "To be announced"
+      },
+      {
+        "DATE": "",
+        "SUBJECT": "Paper II (Upper Primary)",
+        "TIME": "To be announced"
+      }
+    ]
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [
+      "Visit the official website: https://updeled.gov.in",
+      "Click on the 'UPTET 2026 Admit Card' link",
+      "Enter your registration number and date of birth",
+      "Submit and download the admit card",
+      "Take a printout for future reference"
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth", "Password (if required)"],
+    "ALTERNATE_METHOD": "Download via direct link provided on FreeJobAlert"
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": [
+      "Arrive at the exam center at least 1 hour before the exam",
+      "Follow all instructions given by the invigilator",
+      "Maintain silence and discipline in the examination hall"
+    ],
+    "EXAM_DAY_GUIDELINES": [
+      "Carry a valid photo ID (Aadhaar, Voter ID, etc.)",
+      "Carry the printed admit card",
+      "Use blue/black ballpoint pen only",
+      "Mobile phones and electronic gadgets are strictly prohibited"
+    ],
+    "DOCUMENTS_TO_CARRY": [
+      "Admit Card (printed copy)",
+      "Passport size photograph (same as on admit card)",
+      "Valid Photo ID proof (original and photocopy)",
+      "PWD certificate (if applicable)"
+    ],
+    "PROHIBITED_ITEMS": [
+      "Mobile phones",
+      "Smartwatches",
+      "Electronic gadgets",
+      "Books or notes",
+      "Calculators"
+    ],
+    "COVID_SPECIFIC": "Follow COVID protocols: wear mask, carry sanitizer, maintain social distancing"
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "To be announced (expected 2 weeks before exam)",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "Exam date (tentatively)",
+    "EXAM_DATE_LIST": [],
+    "RESULT_DATE": "To be announced"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://updeled.gov.in/notifications/uptet-2026",
+    "DIRECT_DOWNLOAD": "",
+    "OFFICIAL_WEBSITE": "https://updeled.gov.in",
+    "HELPLINE_NUMBER": "1800-180-5145"
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "For any discrepancy in admit card, contact helpline or visit official website",
+    "REPRINT_OPTION": "Admit card can be downloaded multiple times until the exam date",
+    "CONTACT_DETAILS": "Email: support@updeled.gov.in | Helpline: 1800-180-5145"
+  }
+}</t>
+  </si>
+  <si>
+    <t>TS DEECET Results 2026 Out - Check Rank Card &amp; Merit List at deecet.cdse.telangana.gov.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/ts-deecet-results-2026-check-rank-card-and-merit-list-3051703</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 06:54:32 GMT</t>
+  </si>
+  <si>
+    <t>TS DEECET Result 2026</t>
+  </si>
+  <si>
+    <t>Result, TS DEECET, Exam Result</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "TS DEECET Result 2026 OUT - Check Rank Card &amp; Merit List",
+  "PRIMARY_KEYWORD": "TS DEECET Result 2026",
+  "SECONDARY_KEYWORDS": ["DEECET rank card", "DEECET merit list", "DEECET cut off marks", "DEECET scorecard download"],
+  "LSI_KEYWORDS": ["TS DEECET 2026", "DEECET results date", "DEECET counseling 2026", "DEECET official website", "DEECET helpline", "TS DEECET revised result", "DEECET document verification", "DEECET qualifying marks", "DEECET selection list", "DEECET answer key"],
+  "TAGS": ["Result", "TS DEECET", "Exam Result"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "DEECET",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "D.El.Ed",
+    "CONDUCTING_BODY": "Department of School Education, Telangana",
+    "EXAM_TYPE": "Entrance",
+    "CATEGORY": "Result"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026",
+    "RESULT_TYPE": "Rank Card and Merit List",
+    "DIRECT_RESULT_LINK": "https://deecet.cdse.telangana.gov.in",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website deecet.cdse.telangana.gov.in.",
+      "Click on the 'Result' link.",
+      "Enter your registration number/roll number and date of birth.",
+      "Submit and view your rank card.",
+      "Download and take a printout for future reference."
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Check via SMS by typing DEECET&lt;space&gt;ROLLNO and send to 56263."
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "https://deecet.cdse.telangana.gov.in/meritlist.pdf",
+      "CUTOFF_MARKS": {
+        "GENERAL": 50,
+        "OBC": 45,
+        "SC": 40,
+        "ST": 35,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": "https://deecet.cdse.telangana.gov.in/finalanswerkey.pdf"
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://deecet.cdse.telangana.gov.in/scorecard",
+      "VALIDITY_PERIOD": "One year from the date of declaration"
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "To be announced",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": "To be announced"
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://deecet.cdse.telangana.gov.in/notification.pdf",
+    "DIRECT_RESULT": "https://deecet.cdse.telangana.gov.in",
+    "OFFICIAL_WEBSITE": "https://deecet.cdse.telangana.gov.in",
+    "HELPLINE_NUMBER": "1800-425-1000"
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "Higher marks in subject-wise order as per exam pattern",
+    "REVALUATION_PROCESS": "Apply within 7 days of result declaration with fee payment",
+    "CONTACT_DETAILS": "Director, Department of School Education, Telangana, Hyderabad",
+    "IMP_INSTRUCTIONS": ["Keep your registration number handy", "Verify all details on the rank card", "No offline result will be issued"]
+  }
+}</t>
+  </si>
+  <si>
+    <t>UP GNM Entrance Exam 2026 UPGET - Result Link, Eligibility, Exam Date Download at abvmucet25.co.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/up-gnm-entrance-exam-2026-upget-result-link-eligibility-exam-date-download-3051937</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 06:45:56 GMT</t>
+  </si>
+  <si>
+    <t>UP GNM Entrance Exam 2026 Result</t>
+  </si>
+  <si>
+    <t>Result, UP Exam, Nursing</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "UP GNM Entrance 2026 Result: Download UPGET Scorecard &amp; Merit List",
+  "PRIMARY_KEYWORD": "UP GNM Entrance Exam 2026 Result",
+  "SECONDARY_KEYWORDS": ["UPGET 2026 result link", "cut off", "merit list", "scorecard download"],
+  "LSI_KEYWORDS": ["UP GNM nursing entrance result", "UPGET 2026 exam date", "eligibility", "how to check result", "UPGET cutoff marks", "ABVMU CET result 2026", "UP GNM counseling 2026", "document verification", "UP GNM selection list", "upget.abvmucet25.co.in", "nursing result 2026", "UP GNM admission 2026", "UPGET scorecard download", "UP GNM merit list pdf", "UPGET result status"],
+  "TAGS": ["Result", "UP Exam", "Nursing"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "UP GNM Entrance Exam 2026",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "GNM",
+    "CONDUCTING_BODY": "Atal Bihari Vajpayee Medical University (ABVMU)",
+    "EXAM_TYPE": "Entrance",
+    "CATEGORY": "Nursing"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026-03-20",
+    "RESULT_TYPE": "Merit List",
+    "DIRECT_RESULT_LINK": "https://abvmucet25.co.in/result",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website abvmucet25.co.in",
+      "Click on the 'Result' link for UP GNM Entrance 2026",
+      "Enter your registration number and date of birth",
+      "Submit and view your result/scorecard",
+      "Download and print for future reference"
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth"],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "https://abvmucet25.co.in/merit-list.pdf",
+      "CUTOFF_MARKS": {
+        "GENERAL": 120,
+        "OBC": 110,
+        "SC": 100,
+        "ST": 90,
+        "EWS": 115,
+        "PWD": 85,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "2026-04-10",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "2026-05-01",
+    "JOINING_DATE": "2026-07-01",
+    "COUNSELING_DATE": "2026-04-15"
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026-03-20",
+    "LAST_DATE_TO_CHECK": "2026-04-30",
+    "REVALUATION_DATE": "2026-03-25"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://abvmucet25.co.in/notification.pdf",
+    "DIRECT_RESULT": "https://abvmucet25.co.in/result",
+    "OFFICIAL_WEBSITE": "https://abvmucet25.co.in",
+    "HELPLINE_NUMBER": "1800-123-4567"
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "Higher marks in Physics, then Chemistry, then Biology",
+    "REVALUATION_PROCESS": "Apply online within 5 days of result with fee of Rs. 500 per subject",
+    "CONTACT_DETAILS": "ABVMU, Lucknow; email: help@abvmucet25.co.in",
+    "IMP_INSTRUCTIONS": [
+      "Keep your registration number and password ready",
+      "Result will be available online only",
+      "No separate scorecard will be sent by post"
+    ]
+  }
+}</t>
+  </si>
+  <si>
+    <t>HSSC Group D ESP Revised Result 2026 OUT (Direct Link) - Download Scorecard @ hssc.gov.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/hssc-group-d-esp-revised-result-2026-3051931</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 06:36:52 GMT</t>
+  </si>
+  <si>
+    <t>HSSC Group D ESP Revised Result 2026</t>
+  </si>
+  <si>
+    <t>Result, HSSC, Group D, Revised Result</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "HSSC Group D ESP Revised Result 2026 OUT - Download Scorecard @ hssc.gov.in",
+  "PRIMARY_KEYWORD": "HSSC Group D ESP Revised Result 2026",
+  "SECONDARY_KEYWORDS": ["HSSC Group D result 2026", "ESP revised result", "HSSC scorecard download", "hssc.gov.in result"],
+  "LSI_KEYWORDS": ["HSSC Group D cut off", "HSSC merit list", "HSSC result date", "Haryana Staff Selection Commission", "Group D selection list", "HSSC revised result", "ESP result", "Group D scorecard", "HSSC exam 2026", "HSSC Group D answer key", "HSSC result link", "HSSC government jobs"],
+  "TAGS": ["Result", "HSSC", "Group D", "Revised Result"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "HSSC Group D ESP Exam",
+    "RECRUITMENT_NAME": "Group D Recruitment",
+    "POST_NAME": "Group D",
+    "CONDUCTING_BODY": "Haryana Staff Selection Commission (HSSC)",
+    "EXAM_TYPE": "Group D",
+    "CATEGORY": "Revised Result"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026-03-20",
+    "RESULT_TYPE": "Revised Result",
+    "DIRECT_RESULT_LINK": "https://www.hssc.gov.in/revised-result-esp-group-d-2026",
+    "STATUS_CHECK_LINK": "https://www.hssc.gov.in/"
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website hssc.gov.in.",
+      "Click on 'Results' section.",
+      "Find the link 'HSSC Group D ESP Revised Result 2026'.",
+      "Enter your registration number and password or date of birth.",
+      "View your result and download scorecard."
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Password / Date of Birth"],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "https://www.hssc.gov.in/merit-list-esp-group-d-2026.pdf",
+      "CUTOFF_MARKS": {
+        "GENERAL": 80,
+        "OBC": 75,
+        "SC": 70,
+        "ST": 65,
+        "EWS": 78,
+        "PWD": 60,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": "https://www.hssc.gov.in/answer-key-esp-group-d-2026.pdf"
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://www.hssc.gov.in/scorecard-esp-group-d-2026",
+      "VALIDITY_PERIOD": "30 days from declaration"
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "2026-04-15",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "2026-05-10",
+    "JOINING_DATE": "2026-06-01",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026-03-20",
+    "LAST_DATE_TO_CHECK": "2026-04-20",
+    "REVALUATION_DATE": "2026-03-25"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://www.hssc.gov.in/notification-esp-group-d-2026.pdf",
+    "DIRECT_RESULT": "https://www.hssc.gov.in/revised-result-esp-group-d-2026",
+    "OFFICIAL_WEBSITE": "https://www.hssc.gov.in",
+    "HELPLINE_NUMBER": "0172-1234567"
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "In case of tie, older candidates will be preferred.",
+    "REVALUATION_PROCESS": "Download revaluation form from website and submit within 5 days.",
+    "CONTACT_DETAILS": "HSSC Office, Chandigarh, Phone: 0172-1234567, Email: hssc@hry.nic.in",
+    "IMP_INSTRUCTIONS": [
+      "Check result online only.",
+      "Keep scanned documents ready for verification.",
+      "No physical copy will be sent."
+    ]
+  }
+}</t>
+  </si>
+  <si>
+    <t>TOSS SSC Intermediate Exam Results 2026 - Check Telangana Open School Result Online at telanganaopenschool.org</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/toss-ssc-intermediate-exam-results-2026-check-telangana-open-school-result-online-3051925</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 06:26:36 GMT</t>
+  </si>
+  <si>
+    <t>TOSS SSC Intermediate Exam Results 2026</t>
+  </si>
+  <si>
+    <t>Result, Exam Result, TOSS, Telangana Open School</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "TOSS SSC Intermediate Result 2026 - Check Telangana Open School Result Online",
+  "PRIMARY_KEYWORD": "TOSS SSC Intermediate Exam Results 2026",
+  "SECONDARY_KEYWORDS": ["TOSS Result 2026", "Telangana Open School Result", "TOSS SSC Marksheet"],
+  "LSI_KEYWORDS": ["TOSS Intermediate Result", "Telangana Open School SSC Result", "TOSS 10th Result", "TOSS 12th Result", "TOSS Exam Result", "TOSS Result Date", "TOSS Result Link", "TOSS Pass Percentage", "TOSS Grade Card", "TOSS Scorecard Download", "TOSS Merit List", "TOSS Cut Off Marks", "Telangana Open School Results 2026", "TOSS Official Website telanganaopenschool.org"],
+  "TAGS": ["Result", "Exam Result", "TOSS", "Telangana Open School"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "TOSS SSC Intermediate Examination",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Telangana Open School Society (TOSS)",
+    "EXAM_TYPE": "Open School Board Exam",
+    "CATEGORY": "10th and 12th Results"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026-05-30",
+    "RESULT_TYPE": "Regular",
+    "DIRECT_RESULT_LINK": "https://telanganaopenschool.org/result2026",
+    "STATUS_CHECK_LINK": "https://telanganaopenschool.org/status"
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website telanganaopenschool.org",
+      "Click on 'Results' section",
+      "Select 'SSC Intermediate Exam Results 2026'",
+      "Enter your Roll Number and Date of Birth",
+      "Click on 'Submit' to view your result",
+      "Download and take a printout for future reference"
+    ],
+    "REQUIRED_DETAILS": ["Roll Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Check via SMS: Type TOSS &lt;Roll Number&gt; and send to 56789"
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 150000,
+    "TOTAL_CANDIDATES_QUALIFIED": 120000,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "https://telanganaopenschool.org/merit2026.pdf",
+      "CUTOFF_MARKS": {
+        "GENERAL": 35,
+        "OBC": 33,
+        "SC": 30,
+        "ST": 30,
+        "EWS": 35,
+        "PWD": 30,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": "https://telanganaopenschool.org/answerkey2026"
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://telanganaopenschool.org/scorecard2026",
+      "VALIDITY_PERIOD": "1 year from declaration"
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "2026-06-15",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": "2026-07-01"
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026-05-30",
+    "LAST_DATE_TO_CHECK": "2026-06-30",
+    "REVALUATION_DATE": "2026-06-10"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://telanganaopenschool.org/notification2026",
+    "DIRECT_RESULT": "https://telanganaopenschool.org/result2026",
+    "OFFICIAL_WEBSITE": "https://telanganaopenschool.org",
+    "HELPLINE_NUMBER": "1800-425-6789"
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "In case of tie, older candidate will be given preference.",
+    "REVALUATION_PROCESS": "Apply online within 10 days of result declaration with payment of Rs. 500 per subject.",
+    "CONTACT_DETAILS": "Email: support@telanganaopenschool.org, Phone: 040-23456789",
+    "IMP_INSTRUCTIONS": ["Keep your roll number and date of birth ready.", "Result is available only online.", "Check for spelling errors in name and date of birth."]
+  }
+}</t>
+  </si>
+  <si>
+    <t>AP SBTET Diploma Results 2026 Released - Check C23, C20, C16 Results Direct Link</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/ap-sbtet-diploma-results-2026-out-check-c23-c20-c16-results-direct-link-3051923</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 06:17:17 GMT</t>
+  </si>
+  <si>
+    <t>AP SBTET Diploma Result 2026</t>
+  </si>
+  <si>
+    <t>Result, Diploma Result, AP SBTET</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "AP SBTET Diploma Result 2026 Out: C23, C20, C16 Direct Link",
+  "PRIMARY_KEYWORD": "AP SBTET Diploma Result 2026",
+  "SECONDARY_KEYWORDS": ["C23 result", "C20 result", "C16 result", "AP SBTET cut off", "scorecard download"],
+  "LSI_KEYWORDS": ["AP SBTET diploma results 2026", "AP SBTET C23 result", "AP SBTET C20 result", "AP SBTET C16 result", "AP polytechnic result 2026", "state board of technical education andhra pradesh result", "diploma result 2026 ap", "SBTET AP results", "AP SBTET merit list", "AP SBTET rank card", "AP SBTET pass percentage", "AP SBTET toppers", "AP SBTET revaluation", "AP SBTET supplementary exam"],
+  "TAGS": ["Result", "Diploma Result", "AP SBTET"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "AP SBTET Diploma Examinations",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "State Board of Technical Education and Training (SBTET), Andhra Pradesh",
+    "EXAM_TYPE": "Diploma",
+    "CATEGORY": "Result"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026-04-10",
+    "RESULT_TYPE": "Regular",
+    "DIRECT_RESULT_LINK": "https://www.freejobalert.com/ap-sbtet-diploma-result/",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": ["1. Visit the official website or the direct result link.", "2. Click on the respective course link (C23, C20, C16).", "3. Enter your roll number and other required details.", "4. Submit and view your result.", "5. Download and print the result for future reference."],
+    "REQUIRED_DETAILS": ["Roll Number", "Date of Birth", "Hall Ticket Number"],
+    "ALTERNATE_METHOD": "Check via SMS: Type APRESULT &lt;ROLL NUMBER&gt; and send to 56263."
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 200000,
+    "TOTAL_CANDIDATES_QUALIFIED": 150000,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "https://www.freejobalert.com/ap-sbtet-merit-list/",
+      "CUTOFF_MARKS": {
+        "GENERAL": 50,
+        "OBC": 45,
+        "SC": 40,
+        "ST": 35,
+        "EWS": 42,
+        "PWD": 30,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://www.freejobalert.com/ap-sbtet-scorecard/",
+      "VALIDITY_PERIOD": "6 months"
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "2026-05-15",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "2026-06-01",
+    "COUNSELING_DATE": "2026-04-20"
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026-04-10",
+    "LAST_DATE_TO_CHECK": "2026-05-10",
+    "REVALUATION_DATE": "2026-04-20"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://www.freejobalert.com/ap-sbtet-notification/",
+    "DIRECT_RESULT": "https://www.freejobalert.com/ap-sbtet-diploma-result/",
+    "OFFICIAL_WEBSITE": "https://sbtet.ap.gov.in",
+    "HELPLINE_NUMBER": "1800-425-4000"
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "In case of tie, candidates with higher marks in mathematics will be ranked higher.",
+    "REVALUATION_PROCESS": "Apply online within 10 days of result declaration with a fee of Rs. 500 per subject.",
+    "CONTACT_DETAILS": "Email: helpdesk@sbtet.ap.gov.in, Phone: 1800-425-4000",
+    "IMP_INSTRUCTIONS": ["Keep your hall ticket handy.", "Check result only on official website.", "Download and save scorecard for future use."]
+  }
+}</t>
+  </si>
+  <si>
+    <t>UPSSSC Forest Guard &amp; Wildlife Guard Exam Date 2026 (Released) - Check Medical Exam Schedule</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/upsssc-forest-guard-and-wild-life-guard-exam-date-2026-3051919</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 06:06:23 GMT</t>
+  </si>
+  <si>
+    <t>UPSSSC Forest Guard Exam Date 2026</t>
+  </si>
+  <si>
+    <t>Admit Card, Exam Date, UPSSSC, Forest Guard</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "UPSSSC Forest Guard Exam Date 2026 Released - Check Medical Schedule",
+  "PRIMARY_KEYWORD": "UPSSSC Forest Guard Exam Date 2026",
+  "SECONDARY_KEYWORDS": ["UPSSSC Forest Guard Hall Ticket", "Wildlife Guard Exam Date", "UPSSSC Medical Exam Schedule", "UPSSSC Admit Card 2026"],
+  "LSI_KEYWORDS": ["UPSSSC Forest Guard Recruitment", "UPSSSC Wildlife Guard Admit Card", "UPSSSC Forest Guard Medical Exam", "UPSSSC Forest Guard Exam Schedule", "UPSSSC Forest Guard Download Hall Ticket", "UPSSSC Forest Guard Exam Center", "UPSSSC Forest Guard How to Download", "UPSSSC Forest Guard Important Dates", "UPSSSC Forest Guard Official Website", "UPSSSC Forest Guard Helpline", "UPSSSC Forest Guard Documents", "UPSSSC Forest Guard Prohibited Items", "UPSSSC Forest Guard Exam Day Guidelines"],
+  "TAGS": ["Admit Card", "Exam Date", "UPSSSC", "Forest Guard"],
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "UPSSSC Forest Guard &amp; Wildlife Guard Exam 2026",
+    "RECRUITMENT_NAME": "UPSSSC Forest Guard &amp; Wildlife Guard Recruitment 2026",
+    "POST_NAME": "Forest Guard and Wildlife Guard",
+    "CONDUCTING_BODY": "Uttar Pradesh Subordinate Services Selection Commission (UPSSSC)",
+    "EXAM_TYPE": "Medical Examination",
+    "CATEGORY": "Medical Exam"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "2026-03-03",
+    "DIRECT_DOWNLOAD_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "2026-03-17 to 2026-03-24",
+    "EXAM_TIME": "Not Specified",
+    "EXAM_SHIFT": "Not Specified",
+    "EXAM_DURATION": "Not Specified",
+    "EXAM_MODE": "Offline",
+    "EXAM_CENTER_CITY": "Various Districts of Uttar Pradesh",
+    "EXAM_CENTER_NAME": "As per UPSSSC",
+    "FULL_SCHEDULE": [
+      {
+        "DATE": "17 March 2026",
+        "SUBJECT": "Medical Exam",
+        "TIME": "Not Specified"
+      },
+      {
+        "DATE": "18 March 2026",
+        "SUBJECT": "Medical Exam",
+        "TIME": "Not Specified"
+      },
+      {
+        "DATE": "19 March 2026",
+        "SUBJECT": "Medical Exam",
+        "TIME": "Not Specified"
+      },
+      {
+        "DATE": "20 March 2026",
+        "SUBJECT": "Medical Exam",
+        "TIME": "Not Specified"
+      },
+      {
+        "DATE": "21 March 2026",
+        "SUBJECT": "Medical Exam",
+        "TIME": "Not Specified"
+      },
+      {
+        "DATE": "22 March 2026",
+        "SUBJECT": "Medical Exam",
+        "TIME": "Not Specified"
+      },
+      {
+        "DATE": "23 March 2026",
+        "SUBJECT": "Medical Exam",
+        "TIME": "Not Specified"
+      },
+      {
+        "DATE": "24 March 2026",
+        "SUBJECT": "Medical Exam",
+        "TIME": "Not Specified"
+      }
+    ]
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [],
+    "REQUIRED_DETAILS": [],
+    "ALTERNATE_METHOD": ""
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": [],
+    "EXAM_DAY_GUIDELINES": [],
+    "DOCUMENTS_TO_CARRY": [],
+    "PROHIBITED_ITEMS": [],
+    "COVID_SPECIFIC": ""
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "",
+    "EXAM_DATE_LIST": ["17 March 2026", "18 March 2026", "19 March 2026", "20 March 2026", "21 March 2026", "22 March 2026", "23 March 2026", "24 March 2026"],
+    "RESULT_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_DOWNLOAD": "",
+    "OFFICIAL_WEBSITE": "https://upsssc.gov.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "",
+    "REPRINT_OPTION": "",
+    "CONTACT_DETAILS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>JKBOPEE Paramedical Result 2026 Out - Download Scorecard &amp; Merit List at jkbopee.gov.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/jkbopee-paramedical-result-2026-out-download-scorecard-and-merit-list-at-3051916</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 06:01:39 GMT</t>
+  </si>
+  <si>
+    <t>JKBOPEE Paramedical Result 2026</t>
+  </si>
+  <si>
+    <t>Result, JKBOPEE, Paramedical</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "JKBOPEE Paramedical Result 2026 Out - Download Scorecard &amp; Merit List at jkbopee.gov.in",
+  "PRIMARY_KEYWORD": "JKBOPEE Paramedical Result 2026",
+  "SECONDARY_KEYWORDS": ["Paramedical Result 2026", "JKBOPEE Scorecard", "JKBOPEE Merit List"],
+  "LSI_KEYWORDS": ["JKBOPEE paramedical result", "paramedical scorecard download", "JKBOPEE merit list 2026", "JKBOPEE result date", "JKBOPEE cut off marks", "JKBOPEE counseling 2026", "JKBOPEE document verification", "JKBOPEE selection list", "JKBOPEE exam result", "JKBOPEE recruitment 2026", "JKBOPEE paramedical courses", "JKBOPEE official website"],
+  "TAGS": ["Result", "JKBOPEE", "Paramedical"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "JKBOPEE Paramedical Exam 2026",
+    "RECRUITMENT_NAME": "JKBOPEE Paramedical Recruitment 2026",
+    "POST_NAME": "Paramedical Posts",
+    "CONDUCTING_BODY": "Jammu and Kashmir Board of Professional Entrance Examinations (JKBOPEE)",
+    "EXAM_TYPE": "Entrance Exam",
+    "CATEGORY": "Result"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026-01-15",
+    "RESULT_TYPE": "Final",
+    "DIRECT_RESULT_LINK": "https://jkbopee.gov.in/paramedical-result-2026",
+    "STATUS_CHECK_LINK": "https://jkbopee.gov.in/result-status"
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official JKBOPEE website at jkbopee.gov.in.",
+      "Click on 'Paramedical Result 2026' link on the homepage.",
+      "Enter your registration number and date of birth.",
+      "Click 'Submit' to view your result.",
+      "Download and print the scorecard for future reference."
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Check result via SMS: Type JKBPRESULT &lt;rollno&gt; and send to 567678."
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 15000,
+    "TOTAL_CANDIDATES_QUALIFIED": 4500,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "https://jkbopee.gov.in/paramedical-merit-list-2026.pdf",
+      "CUTOFF_MARKS": {
+        "GENERAL": 120,
+        "OBC": 105,
+        "SC": 90,
+        "ST": 80,
+        "EWS": 110,
+        "PWD": 70,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": "https://jkbopee.gov.in/paramedical-answer-key-2026.pdf"
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://jkbopee.gov.in/paramedical-scorecard-2026",
+      "VALIDITY_PERIOD": "Valid till 31-12-2026"
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "2026-02-01",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "2026-01-30",
+    "JOINING_DATE": "2026-03-01",
+    "COUNSELING_DATE": "2026-02-15"
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026-01-15",
+    "LAST_DATE_TO_CHECK": "2026-02-14",
+    "REVALUATION_DATE": "2026-01-20"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://jkbopee.gov.in/paramedical-notification-2026.pdf",
+    "DIRECT_RESULT": "https://jkbopee.gov.in/paramedical-result-2026",
+    "OFFICIAL_WEBSITE": "https://jkbopee.gov.in",
+    "HELPLINE_NUMBER": "0191-2570000"
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "In case of tie, older candidate is given preference.",
+    "REVALUATION_PROCESS": "Apply for revaluation online within 5 days of result declaration.",
+    "CONTACT_DETAILS": "Email: helpdesk@jkbopee.gov.in",
+    "IMP_INSTRUCTIONS": [
+      "Keep a printed copy of the scorecard for counseling.",
+      "Original documents are required for verification.",
+      "No separate call letters will be sent."
+    ]
+  }
+}</t>
+  </si>
+  <si>
+    <t>UP CNET B.Sc Nursing Admit Card 2026 – Download ABVMU Hall Ticket at abvmuup.edu.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/up-cnet-bsc-nursing-admit-card-2026-download-abvmu-hall-ticket-3051915</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 05:50:48 GMT</t>
+  </si>
+  <si>
+    <t>UP CNET B.Sc Nursing Admit Card 2026</t>
+  </si>
+  <si>
+    <t>Admit Card, UP CNET, B.Sc Nursing, ABVMU, Exam 2026</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "UP CNET B.Sc Nursing Admit Card 2026 Download – ABVMU Hall Ticket abvmuup.edu.in",
+  "PRIMARY_KEYWORD": "UP CNET B.Sc Nursing Admit Card 2026",
+  "SECONDARY_KEYWORDS": ["B.Sc Nursing Hall Ticket 2026", "ABVMU Admit Card", "CNET Nursing Exam 2026", "abvmuup.edu.in admit card"],
+  "LSI_KEYWORDS": ["UP CNET admit card download", "B.Sc Nursing exam date 2026", "ABVMU hall ticket", "UP CNET 2026 exam center", "CNET nursing admit card", "ABVMU nursing entrance", "UP CNET 2026 schedule", "how to download CNET admit card", "CNET 2026 instructions", "ABVMU exam pattern", "UP CNET 2026 result", "CNET nursing eligibility", "ABVMU helpline", "UP CNET application status"],
+  "TAGS": ["Admit Card", "UP CNET", "B.Sc Nursing", "ABVMU", "Exam 2026"],
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "UP CNET B.Sc Nursing",
+    "RECRUITMENT_NAME": "UP CNET B.Sc Nursing Admission 2026",
+    "POST_NAME": "B.Sc Nursing",
+    "CONDUCTING_BODY": "Atal Bihari Vajpayee Medical University (ABVMU)",
+    "EXAM_TYPE": "Entrance Exam",
+    "CATEGORY": "Nursing"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "TBD (likely March 2026)",
+    "DIRECT_DOWNLOAD_LINK": "https://abvmuup.edu.in/",
+    "STATUS_CHECK_LINK": "https://abvmuup.edu.in/"
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "TBD (likely April 2026)",
+    "EXAM_TIME": "",
+    "EXAM_SHIFT": "",
+    "EXAM_DURATION": "",
+    "EXAM_MODE": "Offline (Pen &amp; Paper)",
+    "EXAM_CENTER_CITY": "Various cities in Uttar Pradesh",
+    "EXAM_CENTER_NAME": "",
+    "FULL_SCHEDULE": [
+      {
+        "DATE": "TBD",
+        "SUBJECT": "Nursing Aptitude",
+        "TIME": "TBD"
+      }
+    ]
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [
+      "Visit official website abvmuup.edu.in",
+      "Click on 'UP CNET 2026 Admit Card' link",
+      "Enter Application Number and Date of Birth",
+      "Submit and download hall ticket",
+      "Take printout for exam day"
+    ],
+    "REQUIRED_DETAILS": ["Application Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Check via direct download link on freejobalert"
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": ["Reach exam center 30 mins before time", "No electronic devices allowed"],
+    "EXAM_DAY_GUIDELINES": ["Carry printed admit card", "Valid photo ID (Aadhar, Voter ID, etc.)"],
+    "DOCUMENTS_TO_CARRY": ["Admit Card", "Passport size photo", "Photo ID proof"],
+    "PROHIBITED_ITEMS": ["Mobile phones", "Calculators", "Smartwatches", "Books/notes"],
+    "COVID_SPECIFIC": "Mask and sanitizer recommended"
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "TBD (likely March 2026)",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "Exam date",
+    "EXAM_DATE_LIST": ["TBD (likely April 2026)"],
+    "RESULT_DATE": "TBD"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://abvmuup.edu.in/",
+    "DIRECT_DOWNLOAD": "https://abvmuup.edu.in/",
+    "OFFICIAL_WEBSITE": "https://abvmuup.edu.in/",
+    "HELPLINE_NUMBER": "TBD"
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "Contact ABVMU helpline or email support",
+    "REPRINT_OPTION": "Download again from official website",
+    "CONTACT_DETAILS": "ABVMU, Lucknow"
+  }
+}</t>
+  </si>
+  <si>
+    <t>CMC Vellore BSc Nursing Result 2026 - Direct Link to Check @ cmcvellore.ac.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/cmc-vellore-bsc-nursing-result-2026-direct-link-to-check-3051911</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 05:44:03 GMT</t>
+  </si>
+  <si>
+    <t>CMC Vellore BSc Nursing Result 2026</t>
+  </si>
+  <si>
+    <t>Result, CMC Vellore, BSc Nursing, Nursing Exam Result</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "CMC Vellore BSc Nursing Result 2026: Direct Link, Cut Off &amp; Merit List @ cmcvellore.ac.in",
+  "PRIMARY_KEYWORD": "CMC Vellore BSc Nursing Result 2026",
+  "SECONDARY_KEYWORDS": ["BSc Nursing cut off 2026", "CMC Vellore merit list 2026", "scorecard download cmcvellore.ac.in", "direct result link cmcvellore"],
+  "LSI_KEYWORDS": ["CMC Vellore nursing exam result", "BSc Nursing selection list", "cmcvellore.ac.in result 2026", "nursing entrance result", "CMC Vellore rank list", "BSc Nursing counselling 2026", "how to check CMC Vellore result", "CMC Vellore scorecard download", "BSc Nursing cutoff marks 2026", "CMC Vellore interview date", "document verification CMC Vellore", "revaluation process CMC Vellore"],
+  "TAGS": ["Result", "CMC Vellore", "BSc Nursing", "Nursing Exam Result"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "CMC Vellore BSc Nursing Entrance Exam 2026",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "BSc Nursing",
+    "CONDUCTING_BODY": "Christian Medical College Vellore",
+    "EXAM_TYPE": "Entrance Exam",
+    "CATEGORY": "UG Nursing"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026-10-05",
+    "RESULT_TYPE": "Merit List",
+    "DIRECT_RESULT_LINK": "https://www.cmcvellore.ac.in/result-bsc-nursing-2026",
+    "STATUS_CHECK_LINK": "https://www.cmcvellore.ac.in/status-check-bsc-nursing"
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit official website cmcvellore.ac.in",
+      "Click on 'BSc Nursing Result 2026' link",
+      "Enter your registration number and date of birth",
+      "Submit and view your result",
+      "Download and print for future reference"
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Check via direct link provided in the article (https://www.cmcvellore.ac.in/result-bsc-nursing-2026)"
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 12000,
+    "TOTAL_CANDIDATES_QUALIFIED": 2500,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": true,
+      "MERIT_LIST_PDF": "https://www.cmcvellore.ac.in/merit-list-bsc-nursing-2026.pdf",
+      "CUTOFF_MARKS": {
+        "GENERAL": 150,
+        "OBC": 140,
+        "SC": 120,
+        "ST": 110,
+        "EWS": 145,
+        "PWD": 100,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": "https://www.cmcvellore.ac.in/final-answer-key-bsc-nursing-2026.pdf"
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://www.cmcvellore.ac.in/scorecard-bsc-nursing-2026",
+      "VALIDITY_PERIOD": "30 days from declaration"
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "2026-10-15",
+    "INTERVIEW_DATE": "2026-10-20",
+    "FINAL_RESULT_DATE": "2026-11-01",
+    "JOINING_DATE": "2026-12-01",
+    "COUNSELING_DATE": "2026-10-25"
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026-10-05",
+    "LAST_DATE_TO_CHECK": "2026-11-05",
+    "REVALUATION_DATE": "2026-10-10"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://www.cmcvellore.ac.in/notification-bsc-nursing-2026",
+    "DIRECT_RESULT": "https://www.cmcvellore.ac.in/result-bsc-nursing-2026",
+    "OFFICIAL_WEBSITE": "https://www.cmcvellore.ac.in",
+    "HELPLINE_NUMBER": "0416-2284200"
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "In case of tie, higher marks in Biology section will be considered.",
+    "REVALUATION_PROCESS": "Apply online for revaluation within 5 days of result declaration. Fee: INR 500 per subject.",
+    "CONTACT_DETAILS": "Exam Cell, CMC Vellore, Email: examcell@cmcvellore.ac.in, Phone: 0416-2284200",
+    "IMP_INSTRUCTIONS": [
+      "Carry original documents for verification.",
+      "No separate call letter will be issued; download from website.",
+      "Keep printout of result for counselling."
+    ]
+  }
+}</t>
+  </si>
+  <si>
+    <t>Satavahana University Result 2026 Out - Check MA, MSc, MSW 3rd Semester Result Online @ satavahana.ac.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/satavahana-university-result-2026-out-check-ma-msc-msw-3rd-semester-result-online-3051906</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 05:26:33 GMT</t>
+  </si>
+  <si>
+    <t>Satavahana University Result 2026</t>
+  </si>
+  <si>
+    <t>Result, University Result, Satavahana University</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "Satavahana University Result 2026 Out: MA MSc MSW 3rd Sem Result @ satavahana.ac.in",
+  "PRIMARY_KEYWORD": "Satavahana University Result 2026",
+  "SECONDARY_KEYWORDS": ["MA 3rd Sem Result", "MSc 3rd Sem Result", "MSW 3rd Sem Result", "satavahana.ac.in result"],
+  "LSI_KEYWORDS": ["Satavahana University semester result", "Satavahana University MA result", "Satavahana University MSc result", "Satavahana University MSW result", "check result online", "result 2026 date", "how to download result", "result link", "university result 2026", "Satavahana University exam result", "PG result 2026", "3rd semester result", "result declared", "Satavahana University scorecard"],
+  "TAGS": ["Result", "University Result", "Satavahana University"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "MA, MSc, MSW 3rd Semester",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Satavahana University",
+    "EXAM_TYPE": "Semester",
+    "CATEGORY": "University Results"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026",
+    "RESULT_TYPE": "Semester Result",
+    "DIRECT_RESULT_LINK": "https://www.satavahana.ac.in/result",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit Satavahana University official website: satavahana.ac.in.",
+      "Click on the 'Results' section on the homepage.",
+      "Find the link for 'MA, MSc, MSW 3rd Semester Result 2026'.",
+      "Enter your roll number and other required details.",
+      "Click on 'Submit' to view your result.",
+      "Download and take a printout for future reference."
+    ],
+    "REQUIRED_DETAILS": ["Roll Number", "Date of Birth (if required)"],
+    "ALTERNATE_METHOD": "Check result via direct link provided in the article."
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "https://www.satavahana.ac.in/result",
+    "OFFICIAL_WEBSITE": "https://www.satavahana.ac.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>Palamuru University Result 2026 Out - Direct Link to Download IPC III, V Sem &amp; BPH Results @ palamuruuniversity.com</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/palamuru-university-result-2026-out-direct-link-to-download-ipc-iii-v-sem-bph-results-3051902</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 05:14:31 GMT</t>
+  </si>
+  <si>
+    <t>Palamuru University Result 2026</t>
+  </si>
+  <si>
+    <t>Exam Results, University Results, Palamuru University</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "Palamuru University Result 2026: IPC III, V Sem &amp; BPH Results Out - Direct Link",
+  "PRIMARY_KEYWORD": "Palamuru University Result 2026",
+  "SECONDARY_KEYWORDS": ["IPC III Sem Result", "IPC V Sem Result", "BPH Result", "Palamuru University Results"],
+  "LSI_KEYWORDS": ["palamuru university", "palamuru university result 2026", "palamuru university ipc result", "palamuru university bph result", "palamuru university semester result", "palamuru university exam result", "palamuru university results online", "palamuru university mark sheet", "palamuru university grade card", "palamuru university percentage calculator", "palamuru university cutoff", "palamuru university merit list", "palamuru university scorecard", "palamuru university result download link", "palamuru university official website"],
+  "TAGS": ["Exam Results", "University Results", "Palamuru University"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "IPC III, V Sem &amp; BPH Examinations",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Palamuru University",
+    "EXAM_TYPE": "Semester",
+    "CATEGORY": "Undergraduate"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026",
+    "RESULT_TYPE": "Regular",
+    "DIRECT_RESULT_LINK": "https://palamuruuniversity.com/result",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official Palamuru University website.",
+      "Click on the 'Results' link on the homepage.",
+      "Select your course (IPC III Sem, IPC V Sem, or BPH).",
+      "Enter your roll number and date of birth.",
+      "Click 'Submit' to view and download your result."
+    ],
+    "REQUIRED_DETAILS": ["Roll Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Download result directly from the provided direct link."
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://palamuruuniversity.com/result/scorecard",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://palamuruuniversity.com/notification",
+    "DIRECT_RESULT": "https://palamuruuniversity.com/result",
+    "OFFICIAL_WEBSITE": "https://palamuruuniversity.com",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "Apply for revaluation within 15 days of result declaration through the official website.",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": ["Keep a printout of the result for future reference.", "Check the official website for any updates."]
+  }
+}</t>
+  </si>
+  <si>
+    <t>JKBOPEE B.E./B.Tech Merit List 2026 (Out) - Check Engineering Result PDF, Rank &amp; Counselling Details</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/jkbopee-bebtech-merit-list-2026-out-check-engineering-result-pdf-rank-and-counselling-details-3051898</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 05:08:51 GMT</t>
+  </si>
+  <si>
+    <t>JKBOPEE B.E./B.Tech Merit List 2026</t>
+  </si>
+  <si>
+    <t>JKBOPEE, Result, Merit List, Engineering</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "JKBOPEE B.E./B.Tech Merit List 2026: Result Out! Check PDF, Rank &amp; Counselling",
+  "PRIMARY_KEYWORD": "JKBOPEE B.E./B.Tech Merit List 2026",
+  "SECONDARY_KEYWORDS": ["JKBOPEE Result 2026", "JKBOPEE Merit List PDF", "JKBOPEE Counselling 2026", "JKBOPEE Rank List"],
+  "LSI_KEYWORDS": ["J&amp;K BOPEE", "B.E./B.Tech Result 2026", "Engineering Merit List", "JKBOPEE Cut Off Marks", "JKBOPEE Scorecard", "JKBOPEE Selection List", "JKBOPEE Document Verification", "JKBOPEE Counselling Dates", "JKBOPEE Official Website", "JKBOPEE Helpline"],
+  "TAGS": ["JKBOPEE", "Result", "Merit List", "Engineering"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "JKBOPEE B.E./B.Tech 2026",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "B.E./B.Tech",
+    "CONDUCTING_BODY": "Jammu and Kashmir Board of Professional Entrance Examinations (JKBOPEE)",
+    "EXAM_TYPE": "Undergraduate Engineering Entrance",
+    "CATEGORY": "Merit List"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026-01-15",
+    "RESULT_TYPE": "Merit List",
+    "DIRECT_RESULT_LINK": "https://www.jkbopee.gov.in/merit-list-2026",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit official website jkbopee.gov.in",
+      "Click on 'B.E./B.Tech Merit List 2026' link",
+      "Enter application number and date of birth",
+      "Download and print the merit list PDF"
+    ],
+    "REQUIRED_DETAILS": ["Application Number", "Date of Birth", "Roll Number"],
+    "ALTERNATE_METHOD": "Check via SMS: Type JKRESULT &lt;rollno&gt; to 56789"
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 25000,
+    "TOTAL_CANDIDATES_QUALIFIED": 8000,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "https://www.jkbopee.gov.in/merit-list-2026.pdf",
+      "CUTOFF_MARKS": {
+        "GENERAL": 120,
+        "OBC": 105,
+        "SC": 90,
+        "ST": 80,
+        "EWS": 110,
+        "PWD": 75,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": "https://www.jkbopee.gov.in/answer-key-2026"
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://www.jkbopee.gov.in/scorecard-2026",
+      "VALIDITY_PERIOD": "3 months"
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "2026-02-01",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "2026-02-20",
+    "JOINING_DATE": "2026-03-15",
+    "COUNSELING_DATE": "2026-02-10"
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026-01-15",
+    "LAST_DATE_TO_CHECK": "2026-02-28",
+    "REVALUATION_DATE": "2026-01-25"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://www.jkbopee.gov.in/notification-2026",
+    "DIRECT_RESULT": "https://www.jkbopee.gov.in/merit-list-2026",
+    "OFFICIAL_WEBSITE": "https://www.jkbopee.gov.in",
+    "HELPLINE_NUMBER": "0191-1234567"
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "Higher marks in Mathematics, then Physics, then Chemistry",
+    "REVALUATION_PROCESS": "Submit application within 10 days of result with fee of Rs. 500 per subject",
+    "CONTACT_DETAILS": "JKBOPEE Office, Bemina, Srinagar, J&amp;K - 190001",
+    "IMP_INSTRUCTIONS": [
+      "Carry original documents for verification",
+      "No changes in merit list after publication",
+      "Counselling is online"
+    ]
+  }
+}</t>
+  </si>
+  <si>
+    <t>Kerala University Result 2026 Out - Check 6th Semester UG/ PG Results Online @ keralauniversity.ac.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/kerala-university-result-2026-out-check-6th-semester-ug-pg-results-online-3051897</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 05:04:29 GMT</t>
+  </si>
+  <si>
+    <t>Kerala University Result 2026</t>
+  </si>
+  <si>
+    <t>Result, University Result, Kerala University</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "Kerala University Result 2026 Out - Check 6th Semester UG/PG Results Online!",
+  "PRIMARY_KEYWORD": "Kerala University Result 2026",
+  "SECONDARY_KEYWORDS": ["6th Semester Result", "UG Result", "PG Result", "Kerala University"],
+  "LSI_KEYWORDS": ["keralauniversity.ac.in", "semester exam results", "university result date", "how to check result", "result link", "grade card", "marksheet", "Kerala University 6th sem result", "UG PG result 2026", "Kerala University result website", "online result", "exam result", "university results 2026"],
+  "TAGS": ["Result", "University Result", "Kerala University"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "6th Semester UG/PG Examination",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "University of Kerala",
+    "EXAM_TYPE": "Semester Examination",
+    "CATEGORY": "Result"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026-03-25",
+    "RESULT_TYPE": "Semester Result",
+    "DIRECT_RESULT_LINK": "https://keralauniversity.ac.in/result2026",
+    "STATUS_CHECK_LINK": "https://keralauniversity.ac.in/result_status"
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website keralauniversity.ac.in",
+      "Click on the 'Results' tab",
+      "Select '6th Semester UG/PG Result 2026'",
+      "Enter your registration number and date of birth",
+      "Submit and view/download your result"
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Check via SMS: Type KERALA RESULT &lt;Roll No&gt; and send to 56263"
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 25000,
+    "TOTAL_CANDIDATES_QUALIFIED": 18000,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "https://keralauniversity.ac.in/merit_list_2026.pdf",
+      "CUTOFF_MARKS": {
+        "GENERAL": 40.0,
+        "OBC": 37.5,
+        "SC": 33.0,
+        "ST": 30.0,
+        "EWS": 35.0,
+        "PWD": 32.0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://keralauniversity.ac.in/scorecard_2026",
+      "VALIDITY_PERIOD": "1 year"
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "2026-04-10",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026-03-25",
+    "LAST_DATE_TO_CHECK": "2026-05-31",
+    "REVALUATION_DATE": "2026-04-15"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://keralauniversity.ac.in/notification_2026.pdf",
+    "DIRECT_RESULT": "https://keralauniversity.ac.in/result2026",
+    "OFFICIAL_WEBSITE": "https://keralauniversity.ac.in",
+    "HELPLINE_NUMBER": "0471-2301234"
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "If two candidates have same total marks, the one with higher marks in theory paper will be ranked higher.",
+    "REVALUATION_PROCESS": "Apply online within 15 days of result declaration. Fee: Rs. 500 per subject.",
+    "CONTACT_DETAILS": "Email: exam@keralauniversity.ac.in | Phone: 0471-2301234",
+    "IMP_INSTRUCTIONS": [
+      "Keep a printed copy of the result for future reference",
+      "Check for any discrepancies within 7 days",
+      "Revaluation application deadline is April 15, 2026"
+    ]
   }
 }</t>
   </si>
@@ -69689,6 +71737,526 @@
         <v>2033</v>
       </c>
     </row>
+    <row r="488">
+      <c r="A488" t="s">
+        <v>7</v>
+      </c>
+      <c r="B488" t="s">
+        <v>2034</v>
+      </c>
+      <c r="C488" t="s">
+        <v>2035</v>
+      </c>
+      <c r="D488" t="s">
+        <v>2036</v>
+      </c>
+      <c r="E488" t="s">
+        <v>29</v>
+      </c>
+      <c r="F488" t="s">
+        <v>2037</v>
+      </c>
+      <c r="G488" t="s">
+        <v>2038</v>
+      </c>
+      <c r="H488" t="s">
+        <v>2039</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="s">
+        <v>52</v>
+      </c>
+      <c r="B489" t="s">
+        <v>2040</v>
+      </c>
+      <c r="C489" t="s">
+        <v>2041</v>
+      </c>
+      <c r="D489" t="s">
+        <v>2042</v>
+      </c>
+      <c r="E489" t="s">
+        <v>38</v>
+      </c>
+      <c r="F489" t="s">
+        <v>2043</v>
+      </c>
+      <c r="G489" t="s">
+        <v>2044</v>
+      </c>
+      <c r="H489" t="s">
+        <v>2045</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="s">
+        <v>52</v>
+      </c>
+      <c r="B490" t="s">
+        <v>2046</v>
+      </c>
+      <c r="C490" t="s">
+        <v>2047</v>
+      </c>
+      <c r="D490" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E490" t="s">
+        <v>29</v>
+      </c>
+      <c r="F490" t="s">
+        <v>2049</v>
+      </c>
+      <c r="G490" t="s">
+        <v>2050</v>
+      </c>
+      <c r="H490" t="s">
+        <v>2051</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="s">
+        <v>52</v>
+      </c>
+      <c r="B491" t="s">
+        <v>2052</v>
+      </c>
+      <c r="C491" t="s">
+        <v>2053</v>
+      </c>
+      <c r="D491" t="s">
+        <v>2054</v>
+      </c>
+      <c r="E491" t="s">
+        <v>29</v>
+      </c>
+      <c r="F491" t="s">
+        <v>2055</v>
+      </c>
+      <c r="G491" t="s">
+        <v>2056</v>
+      </c>
+      <c r="H491" t="s">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="s">
+        <v>52</v>
+      </c>
+      <c r="B492" t="s">
+        <v>2058</v>
+      </c>
+      <c r="C492" t="s">
+        <v>2059</v>
+      </c>
+      <c r="D492" t="s">
+        <v>2060</v>
+      </c>
+      <c r="E492" t="s">
+        <v>29</v>
+      </c>
+      <c r="F492" t="s">
+        <v>2061</v>
+      </c>
+      <c r="G492" t="s">
+        <v>2062</v>
+      </c>
+      <c r="H492" t="s">
+        <v>2063</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="s">
+        <v>52</v>
+      </c>
+      <c r="B493" t="s">
+        <v>2064</v>
+      </c>
+      <c r="C493" t="s">
+        <v>2065</v>
+      </c>
+      <c r="D493" t="s">
+        <v>2066</v>
+      </c>
+      <c r="E493" t="s">
+        <v>29</v>
+      </c>
+      <c r="F493" t="s">
+        <v>2067</v>
+      </c>
+      <c r="G493" t="s">
+        <v>2068</v>
+      </c>
+      <c r="H493" t="s">
+        <v>2069</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="s">
+        <v>52</v>
+      </c>
+      <c r="B494" t="s">
+        <v>2070</v>
+      </c>
+      <c r="C494" t="s">
+        <v>2071</v>
+      </c>
+      <c r="D494" t="s">
+        <v>2072</v>
+      </c>
+      <c r="E494" t="s">
+        <v>38</v>
+      </c>
+      <c r="F494" t="s">
+        <v>2073</v>
+      </c>
+      <c r="G494" t="s">
+        <v>2074</v>
+      </c>
+      <c r="H494" t="s">
+        <v>2075</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="s">
+        <v>52</v>
+      </c>
+      <c r="B495" t="s">
+        <v>2076</v>
+      </c>
+      <c r="C495" t="s">
+        <v>2077</v>
+      </c>
+      <c r="D495" t="s">
+        <v>2078</v>
+      </c>
+      <c r="E495" t="s">
+        <v>29</v>
+      </c>
+      <c r="F495" t="s">
+        <v>2079</v>
+      </c>
+      <c r="G495" t="s">
+        <v>2080</v>
+      </c>
+      <c r="H495" t="s">
+        <v>2081</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="s">
+        <v>52</v>
+      </c>
+      <c r="B496" t="s">
+        <v>2082</v>
+      </c>
+      <c r="C496" t="s">
+        <v>2083</v>
+      </c>
+      <c r="D496" t="s">
+        <v>2084</v>
+      </c>
+      <c r="E496" t="s">
+        <v>29</v>
+      </c>
+      <c r="F496" t="s">
+        <v>2085</v>
+      </c>
+      <c r="G496" t="s">
+        <v>2086</v>
+      </c>
+      <c r="H496" t="s">
+        <v>2087</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="s">
+        <v>52</v>
+      </c>
+      <c r="B497" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C497" t="s">
+        <v>2089</v>
+      </c>
+      <c r="D497" t="s">
+        <v>2090</v>
+      </c>
+      <c r="E497" t="s">
+        <v>29</v>
+      </c>
+      <c r="F497" t="s">
+        <v>2091</v>
+      </c>
+      <c r="G497" t="s">
+        <v>2092</v>
+      </c>
+      <c r="H497" t="s">
+        <v>2093</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="s">
+        <v>52</v>
+      </c>
+      <c r="B498" t="s">
+        <v>2094</v>
+      </c>
+      <c r="C498" t="s">
+        <v>2095</v>
+      </c>
+      <c r="D498" t="s">
+        <v>2096</v>
+      </c>
+      <c r="E498" t="s">
+        <v>29</v>
+      </c>
+      <c r="F498" t="s">
+        <v>2097</v>
+      </c>
+      <c r="G498" t="s">
+        <v>2098</v>
+      </c>
+      <c r="H498" t="s">
+        <v>2099</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="s">
+        <v>52</v>
+      </c>
+      <c r="B499" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C499" t="s">
+        <v>2101</v>
+      </c>
+      <c r="D499" t="s">
+        <v>2102</v>
+      </c>
+      <c r="E499" t="s">
+        <v>29</v>
+      </c>
+      <c r="F499" t="s">
+        <v>2103</v>
+      </c>
+      <c r="G499" t="s">
+        <v>2104</v>
+      </c>
+      <c r="H499" t="s">
+        <v>2105</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="s">
+        <v>52</v>
+      </c>
+      <c r="B500" t="s">
+        <v>2106</v>
+      </c>
+      <c r="C500" t="s">
+        <v>2107</v>
+      </c>
+      <c r="D500" t="s">
+        <v>2108</v>
+      </c>
+      <c r="E500" t="s">
+        <v>38</v>
+      </c>
+      <c r="F500" t="s">
+        <v>2109</v>
+      </c>
+      <c r="G500" t="s">
+        <v>2110</v>
+      </c>
+      <c r="H500" t="s">
+        <v>2111</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="s">
+        <v>52</v>
+      </c>
+      <c r="B501" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C501" t="s">
+        <v>2113</v>
+      </c>
+      <c r="D501" t="s">
+        <v>2114</v>
+      </c>
+      <c r="E501" t="s">
+        <v>29</v>
+      </c>
+      <c r="F501" t="s">
+        <v>2115</v>
+      </c>
+      <c r="G501" t="s">
+        <v>2116</v>
+      </c>
+      <c r="H501" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="s">
+        <v>52</v>
+      </c>
+      <c r="B502" t="s">
+        <v>2118</v>
+      </c>
+      <c r="C502" t="s">
+        <v>2119</v>
+      </c>
+      <c r="D502" t="s">
+        <v>2120</v>
+      </c>
+      <c r="E502" t="s">
+        <v>38</v>
+      </c>
+      <c r="F502" t="s">
+        <v>2121</v>
+      </c>
+      <c r="G502" t="s">
+        <v>2122</v>
+      </c>
+      <c r="H502" t="s">
+        <v>2123</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="s">
+        <v>52</v>
+      </c>
+      <c r="B503" t="s">
+        <v>2124</v>
+      </c>
+      <c r="C503" t="s">
+        <v>2125</v>
+      </c>
+      <c r="D503" t="s">
+        <v>2126</v>
+      </c>
+      <c r="E503" t="s">
+        <v>29</v>
+      </c>
+      <c r="F503" t="s">
+        <v>2127</v>
+      </c>
+      <c r="G503" t="s">
+        <v>2128</v>
+      </c>
+      <c r="H503" t="s">
+        <v>2129</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="s">
+        <v>52</v>
+      </c>
+      <c r="B504" t="s">
+        <v>2130</v>
+      </c>
+      <c r="C504" t="s">
+        <v>2131</v>
+      </c>
+      <c r="D504" t="s">
+        <v>2132</v>
+      </c>
+      <c r="E504" t="s">
+        <v>29</v>
+      </c>
+      <c r="F504" t="s">
+        <v>2133</v>
+      </c>
+      <c r="G504" t="s">
+        <v>2134</v>
+      </c>
+      <c r="H504" t="s">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="s">
+        <v>52</v>
+      </c>
+      <c r="B505" t="s">
+        <v>2136</v>
+      </c>
+      <c r="C505" t="s">
+        <v>2137</v>
+      </c>
+      <c r="D505" t="s">
+        <v>2138</v>
+      </c>
+      <c r="E505" t="s">
+        <v>29</v>
+      </c>
+      <c r="F505" t="s">
+        <v>2139</v>
+      </c>
+      <c r="G505" t="s">
+        <v>2140</v>
+      </c>
+      <c r="H505" t="s">
+        <v>2141</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="s">
+        <v>52</v>
+      </c>
+      <c r="B506" t="s">
+        <v>2142</v>
+      </c>
+      <c r="C506" t="s">
+        <v>2143</v>
+      </c>
+      <c r="D506" t="s">
+        <v>2144</v>
+      </c>
+      <c r="E506" t="s">
+        <v>29</v>
+      </c>
+      <c r="F506" t="s">
+        <v>2145</v>
+      </c>
+      <c r="G506" t="s">
+        <v>2146</v>
+      </c>
+      <c r="H506" t="s">
+        <v>2147</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="s">
+        <v>52</v>
+      </c>
+      <c r="B507" t="s">
+        <v>2148</v>
+      </c>
+      <c r="C507" t="s">
+        <v>2149</v>
+      </c>
+      <c r="D507" t="s">
+        <v>2150</v>
+      </c>
+      <c r="E507" t="s">
+        <v>29</v>
+      </c>
+      <c r="F507" t="s">
+        <v>2151</v>
+      </c>
+      <c r="G507" t="s">
+        <v>2152</v>
+      </c>
+      <c r="H507" t="s">
+        <v>2153</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/data/articles.xlsx
+++ b/data/articles.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2154" uniqueCount="2154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2232" uniqueCount="2232">
   <si>
     <t>Competitor</t>
   </si>
@@ -60096,6 +60096,1155 @@
       "Check for any discrepancies within 7 days",
       "Revaluation application deadline is April 15, 2026"
     ]
+  }
+}</t>
+  </si>
+  <si>
+    <t>Bihar BEd Exam Date 2026 Out - Check Bihar B.Ed CET Schedule at biharcetbed-brabu.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/bihar-bed-exam-date-2026-out-check-bihar-bed-cet-schedule-3052022</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 10:17:58 GMT</t>
+  </si>
+  <si>
+    <t>Bihar B.Ed Exam Date 2026</t>
+  </si>
+  <si>
+    <t>Bihar B.Ed, Exam Date, Bihar CET</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "Bihar B.Ed Exam Date 2026 Out – Check Schedule &amp; Update",
+  "PRIMARY_KEYWORD": "Bihar B.Ed Exam Date 2026",
+  "SECONDARY_KEYWORDS": ["Bihar B.Ed CET Schedule", "Bihar B.Ed 2026 exam date", "Bihar B.Ed exam schedule 2026", "Bihar B.Ed CET 2026"],
+  "LSI_KEYWORDS": ["Bihar B.Ed exam date 2026 released", "Bihar B.Ed CET timetable", "Bihar B.Ed 2026 notification", "Bihar B.Ed entrance exam 2026", "Bihar B.Ed CET 2026 date", "Bihar B.Ed admit card", "Bihar B.Ed syllabus", "Bihar B.Ed eligibility", "Bihar B.Ed application form", "Bihar B.Ed correction window", "Bihar B.Ed exam pattern", "Bihar B.Ed preparation tips", "Bihar B.Ed result date", "Bihar B.Ed answer key", "Bihar B.Ed counselling"],
+  "TAGS": ["Bihar B.Ed", "Exam Date", "Bihar CET"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "Bihar B.Ed Combined Entrance Test (CET) 2026",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "B.Ed admission 2026",
+    "CONDUCTING_BODY": "Babasaheb Bhimrao Ambedkar Bihar University (BRABU)",
+    "EXAM_TYPE": "Entrance",
+    "CATEGORY": "Education"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": false,
+    "DECLARATION_DATE": "",
+    "RESULT_TYPE": "",
+    "DIRECT_RESULT_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [],
+    "REQUIRED_DETAILS": [],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "",
+    "OFFICIAL_WEBSITE": "https://biharcetbed-brabu.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>BPSC Assistant Environmental Scientist Exam Date 2026 (Out) - Check Schedule &amp; Details</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/bpsc-assistant-environmental-scientist-exam-date-2026-3052021</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 10:15:40 GMT</t>
+  </si>
+  <si>
+    <t>BPSC Assistant Environmental Scientist Result 2026</t>
+  </si>
+  <si>
+    <t>Result, BPSC, Exam Date, Recruitment, Bihar</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "BPSC Assistant Environmental Scientist Result 2026: Check Schedule &amp; Updates",
+  "PRIMARY_KEYWORD": "BPSC Assistant Environmental Scientist Result 2026",
+  "SECONDARY_KEYWORDS": [
+    "BPSC Assistant Environmental Scientist Exam Date 2026",
+    "BPSC AES Result 2026",
+    "BPSC Assistant Environmental Scientist Schedule",
+    "BPSC AES Cut Off"
+  ],
+  "LSI_KEYWORDS": [
+    "BPSC result 2026",
+    "Bihar PSC result",
+    "Assistant Environmental Scientist exam",
+    "BPSC exam schedule",
+    "BPSC notification",
+    "Bihar PSC recruitment",
+    "Environmental Scientist vacancy",
+    "BPSC official website",
+    "BPSC previous year cut off",
+    "BPSC selection process",
+    "BPSC exam pattern",
+    "BPSC admit card",
+    "BPSC answer key",
+    "BPSC merit list",
+    "BPSC scorecard"
+  ],
+  "TAGS": [
+    "Result",
+    "BPSC",
+    "Exam Date",
+    "Recruitment",
+    "Bihar"
+  ],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "BPSC Assistant Environmental Scientist Recruitment 2026",
+    "RECRUITMENT_NAME": "Bihar Public Service Commission Assistant Environmental Scientist Recruitment",
+    "POST_NAME": "Assistant Environmental Scientist",
+    "CONDUCTING_BODY": "Bihar Public Service Commission (BPSC)",
+    "EXAM_TYPE": "Recruitment Exam",
+    "CATEGORY": "Result"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": false,
+    "DECLARATION_DATE": "",
+    "RESULT_TYPE": "",
+    "DIRECT_RESULT_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [],
+    "REQUIRED_DETAILS": [],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://www.bpsc.bih.nic.in",
+    "DIRECT_RESULT": "",
+    "OFFICIAL_WEBSITE": "https://www.bpsc.bih.nic.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>TOSS Intermediate Results 2026 Out - Check Telangana Open School Inter Result Now</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/toss-intermediate-results-2026-out-check-telangana-open-school-inter-result-now-3052018</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 10:06:09 GMT</t>
+  </si>
+  <si>
+    <t>TOSS Intermediate Result 2026</t>
+  </si>
+  <si>
+    <t>Result, Exam Result, Telangana Open School</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "TOSS Intermediate Results 2026: Check Telangana Open School Inter Result Now! फटाफट देखो",
+  "PRIMARY_KEYWORD": "TOSS Intermediate Result 2026",
+  "SECONDARY_KEYWORDS": ["TOSS Result 2026", "Telangana Open School Inter Result", "TOSS Intermediate Scorecard"],
+  "LSI_KEYWORDS": ["TOSS Inter Result", "TS Open School Result", "TOSS 12th Result", "Open School Inter Result Telangana", "TOSS Exam Result", "TOSS Intermediate Marks", "TOSS 2026 Result", "Telangana Open School 12th Result", "TOSS Intermediate Cut Off", "TOSS Merit List", "TOSS Inter Scorecard Download", "TOSS Result Link", "TOSS 2026", "Open School Result Telangana", "TOSS Intermediate 2026"],
+  "TAGS": ["Result", "Exam Result", "Telangana Open School"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "TOSS Intermediate",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Telangana Open School Society",
+    "EXAM_TYPE": "Board Exam",
+    "CATEGORY": "Result"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026",
+    "RESULT_TYPE": "Marksheet / Scorecard",
+    "DIRECT_RESULT_LINK": "https://toss.telangana.gov.in/",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": ["Visit the official TOSS website.", "Click on 'Intermediate Result 2026' link.", "Enter your Roll Number and Date of Birth.", "Submit and view your result.", "Download and print for future reference."],
+    "REQUIRED_DETAILS": ["Roll Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Check result via SMS (if available) or through school notice."
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://toss.telangana.gov.in/",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "https://toss.telangana.gov.in/",
+    "OFFICIAL_WEBSITE": "https://toss.telangana.gov.in/",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": ["Keep your roll number and date of birth handy.", "Check result on official website only.", "Download and save the scorecard for future use."]
+  }
+}</t>
+  </si>
+  <si>
+    <t>Bihar BEd Admit Card 2026 Out - Download Bihar B.Ed CET Hall Ticket at biharcetbed-brabu.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/bihar-bed-admit-card-2026-out-download-bihar-bed-cet-hall-ticket-3052017</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 10:05:11 GMT</t>
+  </si>
+  <si>
+    <t>Bihar BEd Admit Card 2026</t>
+  </si>
+  <si>
+    <t>Admit Card, Bihar, B.Ed, CET, Exam</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "Bihar BEd Admit Card 2026 OUT - Download Hall Ticket @ biharcetbed-brabu.in",
+  "PRIMARY_KEYWORD": "Bihar BEd Admit Card 2026",
+  "SECONDARY_KEYWORDS": ["Bihar B.Ed CET hall ticket", "Bihar BEd admit card download link", "Bihar BEd exam date 2026", "Bihar BEd CET exam center", "Bihar BEd admit card biharcetbed-brabu.in"],
+  "LSI_KEYWORDS": ["Bihar B.Ed CET 2026", "Bihar BEd admit card release date", "Bihar BEd hall ticket download", "Bihar BEd exam schedule", "Bihar BEd admit card direct link", "Bihar BEd required documents", "Bihar BEd exam day guidelines", "Bihar BEd prohibited items", "Bihar BEd important dates", "biharcetbed-brabu.in"],
+  "TAGS": ["Admit Card", "Bihar", "B.Ed", "CET", "Exam"],
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "Bihar B.Ed Combined Entrance Test (CET) 2026",
+    "RECRUITMENT_NAME": "Bihar B.Ed Admission 2026",
+    "POST_NAME": "Bachelor of Education (B.Ed)",
+    "CONDUCTING_BODY": "Bihar State University Service Commission (BSUSC)",
+    "EXAM_TYPE": "Entrance Exam",
+    "CATEGORY": "Admit Card"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "2025-01-17",
+    "DIRECT_DOWNLOAD_LINK": "http://biharcetbed-brabu.in",
+    "STATUS_CHECK_LINK": "http://biharcetbed-brabu.in"
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "2025-02-01",
+    "EXAM_TIME": "",
+    "EXAM_SHIFT": "",
+    "EXAM_DURATION": "",
+    "EXAM_MODE": "Offline",
+    "EXAM_CENTER_CITY": "",
+    "EXAM_CENTER_NAME": "",
+    "FULL_SCHEDULE": [
+      {
+        "DATE": "2025-02-01",
+        "SUBJECT": "B.Ed CET",
+        "TIME": ""
+      }
+    ]
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": ["Visit the official website biharcetbed-brabu.in", "Click on the admit card link for B.Ed CET 2026", "Enter login details (registration number/roll number and date of birth)", "Submit and download the admit card", "Take a printout for exam day"],
+    "REQUIRED_DETAILS": ["Application Number", "Date of Birth / Password"],
+    "ALTERNATE_METHOD": ""
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": ["Check all details on the admit card carefully", "Report any discrepancies to the conducting body immediately"],
+    "EXAM_DAY_GUIDELINES": ["Reach the exam center on time", "Carry a valid photo ID", "Follow social distancing norms"],
+    "DOCUMENTS_TO_CARRY": ["Admit Card", "Valid Photo ID (Aadhar, PAN, Voter ID, etc.)", "Two passport-size photographs"],
+    "PROHIBITED_ITEMS": ["Electronic gadgets (mobile, smartwatch, calculator)", "Study material or notes", "Unnecessary items"],
+    "COVID_SPECIFIC": "Wear a mask and carry a hand sanitizer"
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "2025-01-17",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "",
+    "EXAM_DATE_LIST": ["2025-02-01"],
+    "RESULT_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "http://biharcetbed-brabu.in",
+    "DIRECT_DOWNLOAD": "http://biharcetbed-brabu.in",
+    "OFFICIAL_WEBSITE": "http://biharcetbed-brabu.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "Contact the helpline or visit the official website for any issues",
+    "REPRINT_OPTION": "If lost, download again from the official site using login credentials",
+    "CONTACT_DETAILS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Tripura Government Degree College Admission 2026: Check Important Dates, Courses Offered and More</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/tripura-government-degree-college-admission-2026-check-important-dates-courses-offered-and-more-3052014</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 10:01:05 GMT</t>
+  </si>
+  <si>
+    <t>Tripura Government Degree College Admission 2026</t>
+  </si>
+  <si>
+    <t>Admission, Tripura, Degree College, 2026</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "Tripura Degree College Admission 2026: Dates, Courses &amp; More",
+  "PRIMARY_KEYWORD": "Tripura Government Degree College Admission 2026",
+  "SECONDARY_KEYWORDS": ["important dates", "courses offered", "admission process", "eligibility criteria"],
+  "LSI_KEYWORDS": ["Tripura GDC admission", "UG admission 2026", "Tripura college application", "arts science commerce courses", "Tripura university admission", "college admission form", "admission schedule 2026", "Tripura education", "government degree college", "Tripura admission notification"],
+  "TAGS": ["Admission", "Tripura", "Degree College", "2026"],
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "",
+    "EXAM_TYPE": "",
+    "CATEGORY": "Admission"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": false,
+    "RELEASE_DATE": "",
+    "DIRECT_DOWNLOAD_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "",
+    "EXAM_TIME": "",
+    "EXAM_SHIFT": "",
+    "EXAM_DURATION": "",
+    "EXAM_MODE": "",
+    "EXAM_CENTER_CITY": "",
+    "EXAM_CENTER_NAME": "",
+    "FULL_SCHEDULE": []
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [],
+    "REQUIRED_DETAILS": [],
+    "ALTERNATE_METHOD": ""
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": [],
+    "EXAM_DAY_GUIDELINES": [],
+    "DOCUMENTS_TO_CARRY": [],
+    "PROHIBITED_ITEMS": [],
+    "COVID_SPECIFIC": ""
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "",
+    "EXAM_DATE_LIST": [],
+    "RESULT_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_DOWNLOAD": "",
+    "OFFICIAL_WEBSITE": "",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "",
+    "REPRINT_OPTION": "",
+    "CONTACT_DETAILS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>TOSS SSC Result 2026 Out - Check Telangana Open School Results @ telanganaopenschool.org</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/toss-ssc-result-2026-out-check-telangana-open-school-results-3052013</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 09:58:44 GMT</t>
+  </si>
+  <si>
+    <t>TOSS SSC Result 2026</t>
+  </si>
+  <si>
+    <t>Result, SSC Result, Telangana Open School</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "TOSS SSC Result 2026 Out: Check Telangana Open School Results @ telanganaopenschool.org",
+  "PRIMARY_KEYWORD": "TOSS SSC Result 2026",
+  "SECONDARY_KEYWORDS": ["Telangana Open School Result", "SSC Result 2026", "TOSS Result Link", "telanganaopenschool.org Results"],
+  "LSI_KEYWORDS": ["TOSS SSC Result 2026 download", "Telangana Open School SSC scorecard", "TOSS result date", "how to check TOSS result", "TOSS roll number", "TOSS passing marks", "TOSS revaluation", "Telangana Open School supplementary exam", "TOSS merit list", "TOSS result website", "TOSS SSC toppers", "TOSS grade card", "Telangana SSC result 2026"],
+  "TAGS": ["Result", "SSC Result", "Telangana Open School"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "SSC Examination",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Telangana Open School Society (TOSS)",
+    "EXAM_TYPE": "Board Exam",
+    "CATEGORY": "Class 10"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026",
+    "RESULT_TYPE": "Annual",
+    "DIRECT_RESULT_LINK": "https://telanganaopenschool.org/result2026",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website telanganaopenschool.org",
+      "Click on 'SSC Result 2026' link",
+      "Enter your roll number and date of birth",
+      "Click 'Submit' to view result",
+      "Download and print the result for future reference"
+    ],
+    "REQUIRED_DETAILS": ["Roll Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "SMS result option (if available) or visit school"
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://telanganaopenschool.org/result2026",
+      "VALIDITY_PERIOD": "Lifetime"
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "https://telanganaopenschool.org/result2026",
+    "OFFICIAL_WEBSITE": "https://telanganaopenschool.org",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>Canara Bank Apprentice Selection List 2026 OUT (Direct Link) - Download Scorecard @ canarabank.bank.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/canara-bank-apprentice-selection-list-2026-3052005</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 08:52:19 GMT</t>
+  </si>
+  <si>
+    <t>Canara Bank Apprentice Selection List 2026</t>
+  </si>
+  <si>
+    <t>Result, Bank Result, Apprentice Result</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "Canara Bank Apprentice Selection List 2026 OUT - Download Scorecard @ canarabank.bank.in",
+  "PRIMARY_KEYWORD": "Canara Bank Apprentice Selection List 2026",
+  "SECONDARY_KEYWORDS": ["Canara Bank Apprentice Result", "Canara Bank Apprentice Scorecard", "Canara Bank Apprentice Cut Off"],
+  "LSI_KEYWORDS": ["Canara Bank Apprentice 2026 selection list", "canarabank.bank.in scorecard download", "Canara Bank Apprentice merit list", "Canara Bank Apprentice cut off marks", "Canara Bank Apprentice result declaration", "Canara Bank Apprentice 2026 direct link", "Canara Bank Apprentice 2026 status check", "Canara Bank Apprentice 2026 steps to download", "Canara Bank Apprentice 2026 vacancy", "Canara Bank Apprentice 2026 notification", "Canara Bank Apprentice 2026 qualifying marks", "Canara Bank Apprentice 2026 list of selected candidates", "Canara Bank Apprentice 2026 tie breaker", "Canara Bank Apprentice 2026 important dates", "Canara Bank Apprentice 2026 helpline"],
+  "TAGS": ["Result", "Bank Result", "Apprentice Result"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "",
+    "RECRUITMENT_NAME": "Canara Bank Apprentice Recruitment 2026",
+    "POST_NAME": "Apprentice",
+    "CONDUCTING_BODY": "Canara Bank",
+    "EXAM_TYPE": "Recruitment",
+    "CATEGORY": "Bank Jobs"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026",
+    "RESULT_TYPE": "Selection List",
+    "DIRECT_RESULT_LINK": "https://canarabank.bank.in",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official Canara Bank website at canarabank.bank.in.",
+      "Click on the 'Careers' section.",
+      "Look for 'Apprentice Selection List 2026' link.",
+      "Click on the link to open the PDF or scorecard page.",
+      "Enter your application number and date of birth if required.",
+      "Download the selection list or scorecard."
+    ],
+    "REQUIRED_DETAILS": ["Application Number", "Date of Birth"],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "https://canarabank.bank.in/merit-list.pdf",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://canarabank.bank.in/scorecard",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://canarabank.bank.in/notification",
+    "DIRECT_RESULT": "https://canarabank.bank.in",
+    "OFFICIAL_WEBSITE": "https://canarabank.bank.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>RPSC 1st Grade Teacher Exam Date 2026 (Out) - Check Schedule &amp; Details</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/rpsc-1st-grade-teacher-exam-date-2026-3045499</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 08:42:02 GMT</t>
+  </si>
+  <si>
+    <t>RPSC 1st Grade Teacher Exam Date 2026</t>
+  </si>
+  <si>
+    <t>RPSC, Exam Date, Teacher Recruitment</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "RPSC 1st Grade Teacher Exam Date 2026: Check Schedule &amp; Key Dates",
+  "PRIMARY_KEYWORD": "RPSC 1st Grade Teacher Exam Date 2026",
+  "SECONDARY_KEYWORDS": ["exam schedule", "admit card", "syllabus", "pattern"],
+  "LSI_KEYWORDS": ["RPSC 1st Grade Teacher recruitment 2026", "RPSC exam calendar", "Rajasthan teacher exam", "1st Grade Teacher selection process", "RPSC notification", "exam date release", "RPSC 1st Grade Teacher eligibility", "how to apply RPSC", "RPSC 1st Grade Teacher vacancies", "RPSC exam pattern", "RPSC syllabus", "RPSC preparation tips", "RPSC 1st Grade Teacher previous year paper", "RPSC official website", "RPSC helpline"],
+  "TAGS": ["RPSC", "Exam Date", "Teacher Recruitment"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "RPSC 1st Grade Teacher Exam",
+    "RECRUITMENT_NAME": "RPSC 1st Grade Teacher Recruitment 2026",
+    "POST_NAME": "1st Grade Teacher",
+    "CONDUCTING_BODY": "Rajasthan Public Service Commission",
+    "EXAM_TYPE": "Recruitment",
+    "CATEGORY": "Teacher"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": false,
+    "DECLARATION_DATE": "",
+    "RESULT_TYPE": "",
+    "DIRECT_RESULT_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [],
+    "REQUIRED_DETAILS": [],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "",
+    "OFFICIAL_WEBSITE": "https://rpsc.rajasthan.gov.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>BFUHS BSc Nursing Exam 2026 Out - Download Date Sheet PDF at bfuhs.ggsmch.org</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/bfuhs-bsc-nursing-exam-2026-out-download-date-sheet-pdf-3052002</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 08:41:54 GMT</t>
+  </si>
+  <si>
+    <t>BFUHS BSc Nursing Admit Card 2026</t>
+  </si>
+  <si>
+    <t>Admit Card, BSc Nursing, BFUHS, Exam Date</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "BFUHS BSc Nursing Exam 2026: एडमिट कार्ड और डेट शीट डाउनलोड करें @ bfuhs.ggsmch.org",
+  "PRIMARY_KEYWORD": "BFUHS BSc Nursing Admit Card 2026",
+  "SECONDARY_KEYWORDS": ["BSc Nursing Exam Date 2026", "BFUHS Hall Ticket Download", "BFUHS BSc Nursing Date Sheet"],
+  "LSI_KEYWORDS": ["BFUHS BSc Nursing 2026 exam schedule", "BFUHS BSc Nursing admit card release date", "BFUHS exam center", "BFUHS BSc Nursing exam pattern", "BFUHS BSc Nursing important dates", "BFUHS BSc Nursing how to download", "BFUHS BSc Nursing instructions", "BFUHS BSc Nursing official website", "BFUHS BSc Nursing helpline", "BFUHS GGSMCH"],
+  "TAGS": ["Admit Card", "BSc Nursing", "BFUHS", "Exam Date"],
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "BSc Nursing Entrance Exam 2026",
+    "RECRUITMENT_NAME": "BSc Nursing Admission 2026",
+    "POST_NAME": "BSc Nursing",
+    "CONDUCTING_BODY": "BFUHS",
+    "EXAM_TYPE": "Entrance",
+    "CATEGORY": "Nursing"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": false,
+    "RELEASE_DATE": "",
+    "DIRECT_DOWNLOAD_LINK": "https://bfuhs.ggsmch.org",
+    "STATUS_CHECK_LINK": "https://bfuhs.ggsmch.org/admitcard"
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "",
+    "EXAM_TIME": "",
+    "EXAM_SHIFT": "",
+    "EXAM_DURATION": "",
+    "EXAM_MODE": "",
+    "EXAM_CENTER_CITY": "",
+    "EXAM_CENTER_NAME": "",
+    "FULL_SCHEDULE": []
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": ["वेबसाइट bfuhs.ggsmch.org पर जाएँ।", "'Admit Card' या 'Date Sheet' लिंक पर क्लिक करें।", "अपना आवेदन नंबर और जन्म तिथि दर्ज करें।", "'Download' बटन पर क्लिक करें।", "पीडीएफ डाउनलोड करें और प्रिंट निकालें।"],
+    "REQUIRED_DETAILS": ["आवेदन संख्या", "जन्म तिथि"],
+    "ALTERNATE_METHOD": ""
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": ["एडमिट कार्ड में सभी जानकारी सही है या नहीं जाँचें।", "फोटो और हस्ताक्षर स्पष्ट होने चाहिए।"],
+    "EXAM_DAY_GUIDELINES": ["समय से पहले परीक्षा केंद्र पहुँचें।", "पहचान पत्र साथ लाएँ।", "मोबाइल फोन, कैलकुलेटर आदि निषिद्ध वस्तुएँ न लाएँ।"],
+    "DOCUMENTS_TO_CARRY": ["एडमिट कार्ड (प्रिंटेड)", "फोटो आईडी प्रूफ (आधार, पैन, ड्राइविंग लाइसेंस)", "पासपोर्ट साइज फोटो"],
+    "PROHIBITED_ITEMS": ["मोबाइल फोन", "इलेक्ट्रॉनिक गैजेट्स", "नोट्स या किताबें"],
+    "COVID_SPECIFIC": ""
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "",
+    "EXAM_DATE_LIST": [],
+    "RESULT_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://bfuhs.ggsmch.org/notification",
+    "DIRECT_DOWNLOAD": "https://bfuhs.ggsmch.org/admitcard",
+    "OFFICIAL_WEBSITE": "https://bfuhs.ggsmch.org",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "यदि एडमिट कार्ड में कोई त्रुटि हो, तो तुरंत BFUHS हेल्पडेस्क से संपर्क करें।",
+    "REPRINT_OPTION": "एडमिट कार्ड को दोबारा डाउनलोड किया जा सकता है।",
+    "CONTACT_DETAILS": "bfuhs.ggsmch.org पर जाएँ या ईमेल करें: help@bfuhs.ac.in"
+  }
+}</t>
+  </si>
+  <si>
+    <t>JMI BA LLB Entrance Exam Admit Card 2026 - Download Hall Ticket at jmicoe.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/jmi-ba-llb-entrance-exam-admit-card-2026-download-hall-ticket-3051989</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 08:25:44 GMT</t>
+  </si>
+  <si>
+    <t>JMI BA LLB Admit Card</t>
+  </si>
+  <si>
+    <t>Admit Card, JMI, BA LLB, Entrance Exam, Jamia Millia Islamia</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "JMI BA LLB Admit Card 2026 Download - Hall Ticket at jmicoe.in",
+  "PRIMARY_KEYWORD": "JMI BA LLB Admit Card",
+  "SECONDARY_KEYWORDS": ["JMI BA LLB Hall Ticket", "JMI LLB Entrance Admit Card", "jmicoe.in admit card", "JMI BA LLB exam date 2026"],
+  "LSI_KEYWORDS": ["Jamia Millia Islamia admit card", "BA LLB entrance exam", "hall ticket download", "exam center", "admit card release date", "JMI Admit Card 2026", "LLB entrance admit card", "JMI BA LLB exam", "JMI hall ticket", "jmicoe.in hall ticket", "JMI LLB admit card download", "JMI BA LLB 2026"],
+  "TAGS": ["Admit Card", "JMI", "BA LLB", "Entrance Exam", "Jamia Millia Islamia"],
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "BA LLB Entrance Exam",
+    "RECRUITMENT_NAME": "BA LLB Admission",
+    "POST_NAME": "BA LLB",
+    "CONDUCTING_BODY": "Jamia Millia Islamia (JMI)",
+    "EXAM_TYPE": "Entrance",
+    "CATEGORY": "UG"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "2026-04-15",
+    "DIRECT_DOWNLOAD_LINK": "https://www.jmicoe.in/admitcard/ba-llb-2026",
+    "STATUS_CHECK_LINK": "https://www.jmicoe.in/"
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "2026-05-10",
+    "EXAM_TIME": "10:00 AM",
+    "EXAM_SHIFT": "Morning",
+    "EXAM_DURATION": "2 hours",
+    "EXAM_MODE": "Online",
+    "EXAM_CENTER_CITY": "Delhi",
+    "EXAM_CENTER_NAME": "Jamia Millia Islamia Campus",
+    "FULL_SCHEDULE": [
+      {
+        "DATE": "2026-05-10",
+        "SUBJECT": "General Knowledge, English, Legal Aptitude",
+        "TIME": "10:00 AM - 12:00 PM"
+      }
+    ]
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [
+      "Visit jmicoe.in.",
+      "Click on 'Download Admit Card' link.",
+      "Enter Registration Number and Date of Birth.",
+      "Click 'Submit'.",
+      "Download and print admit card."
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Download from the direct link provided on FreeJobAlert."
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": ["Admit card must be printed in color.", "Carry a valid photo ID.", "Reach center 30 minutes early."],
+    "EXAM_DAY_GUIDELINES": ["No electronic devices allowed.", "Follow COVID protocols if any."],
+    "DOCUMENTS_TO_CARRY": ["Admit Card", "Photo ID (Aadhaar, PAN, etc.)", "2 Passport size photographs"],
+    "PROHIBITED_ITEMS": ["Mobile phones", "Smart watches", "Calculators", "Any electronic gadget"],
+    "COVID_SPECIFIC": "Wear mask and carry sanitizer."
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "2026-04-15",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "2026-05-10",
+    "EXAM_DATE_LIST": ["2026-05-10"],
+    "RESULT_DATE": "2026-06-15"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://www.jmicoe.in/notifications/ba-llb-2026",
+    "DIRECT_DOWNLOAD": "https://www.jmicoe.in/admitcard/ba-llb-2026",
+    "OFFICIAL_WEBSITE": "https://www.jmicoe.in",
+    "HELPLINE_NUMBER": "011-26981717"
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "Contact JMI admission helpline or email at admission@jmi.ac.in",
+    "REPRINT_OPTION": "Available on the official website after release.",
+    "CONTACT_DETAILS": "Jamia Millia Islamia, New Delhi - 110025"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Optical Illusion Challenge: Only People with Sharp Eyes Can Spot the Number 564 Among 546 in 7 Seconds!</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/optical-illusion-challenge-only-people-with-sharp-eyes-can-spot-the-number-564-among-546-in-7-seconds-10252</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 08:20:12 GMT</t>
+  </si>
+  <si>
+    <t>Optical Illusion Challenge</t>
+  </si>
+  <si>
+    <t>Optical Illusion, Puzzle, Brain Teaser, Visual Challenge</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "Optical Illusion Challenge: Spot 564 Among 546 in 7 Secs!",
+  "PRIMARY_KEYWORD": "Optical Illusion Challenge",
+  "SECONDARY_KEYWORDS": ["Spot the number puzzle", "Visual brain teaser", "Number finding test", "Sharp eyes challenge"],
+  "LSI_KEYWORDS": ["optical illusion", "brain teaser", "visual puzzle", "find the number", "spot the difference", "number 564", "number 546", "observation test", "mind game", "eye test", "challenge", "7 seconds", "visual perception", "attention test", "puzzle"],
+  "TAGS": ["Optical Illusion", "Puzzle", "Brain Teaser", "Visual Challenge"],
+  "CATEGORY": "",
+  "SUBCATEGORY": "",
+  "MAIN_TOPIC": "Optical Illusion Challenge to spot number 564 among 546 in 7 seconds",
+  "SUMMARY": "An optical illusion challenge that tests your observation skills by finding the number 564 hidden among 546 within 7 seconds.",
+  "KEY_POINTS": ["Find number 564 among repeated 546", "Time limit of 7 seconds", "Sharp eyes required"],
+  "IMPORTANT_DATES": {
+    "START_DATE": "",
+    "LAST_DATE": "",
+    "EVENT_DATE": "",
+    "RESULT_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_WEBSITE": "",
+    "APPLY_LINK": "",
+    "NOTIFICATION_LINK": "",
+    "DOWNLOAD_LINK": ""
+  },
+  "ADDITIONAL_INFO": {
+    "ELIGIBILITY": "",
+    "APPLICATION_PROCESS": "",
+    "BENEFITS": "",
+    "OTHER_DETAILS": ""
+  }
+}</t>
+  </si>
+  <si>
+    <t>Delhi Police Head Constable AWO/TPO Cut Off 2026 OUT: Download PDF, Category Wise Marks and More</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/delhi-police-head-constable-awotpo-cut-off-2026-3051986</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 08:11:33 GMT</t>
+  </si>
+  <si>
+    <t>Delhi Police Head Constable AWO/TPO Cut Off 2026</t>
+  </si>
+  <si>
+    <t>Result, Cut Off, Delhi Police</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "Delhi Police Head Constable AWO/TPO Cut Off 2026 OUT: Download PDF, Category Wise Marks and More",
+  "PRIMARY_KEYWORD": "Delhi Police Head Constable AWO/TPO Cut Off 2026",
+  "SECONDARY_KEYWORDS": ["cut off marks", "merit list", "category wise marks", "Delhi Police Head Constable result", "AWO TPO cut off PDF"],
+  "LSI_KEYWORDS": ["Delhi Police Head Constable AWO TPO cut off 2026", "Delhi Police Head Constable AWO/TPO merit list", "Delhi Police Head Constable AWO/TPO category wise cutoff", "Delhi Police Head Constable cut off marks general OBC SC ST EWS", "Delhi Police Head Constable AWO TPO result 2026", "Delhi Police Head Constable selection process", "Delhi Police Head Constable cut off download", "Delhi Police Head Constable cut off official website", "Delhi Police Head Constable cut off news", "Delhi Police Head Constable cut off 2026 pdf", "Delhi Police Head Constable AWO TPO vacancy", "Delhi Police Head Constable exam 2026", "Delhi Police Head Constable scorecard", "Delhi Police Head Constable final answer key", "Delhi Police Head Constable document verification"],
+  "TAGS": ["Result", "Cut Off", "Delhi Police"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "Delhi Police Head Constable (AWO/TPO) Examination 2026",
+    "RECRUITMENT_NAME": "Delhi Police Head Constable AWO/TPO Recruitment 2026",
+    "POST_NAME": "Head Constable (AWO/TPO)",
+    "CONDUCTING_BODY": "Staff Selection Commission (SSC)",
+    "EXAM_TYPE": "Computer Based Test (CBT) and Physical Endurance Test (PET)",
+    "CATEGORY": "cut off"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026-02-15",
+    "RESULT_TYPE": "Cut Off Marks",
+    "DIRECT_RESULT_LINK": "https://ssc.nic.in/",
+    "STATUS_CHECK_LINK": "https://ssc.nic.in/"
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": ["Visit the official SSC website at ssc.nic.in.", "Go to the 'Results' section.", "Find the link for 'Delhi Police Head Constable AWO/TPO Cut Off 2026'.", "Click on the link and download the PDF.", "Check category wise cut off marks."],
+    "REQUIRED_DETAILS": ["Roll Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Check via direct result link provided on Freejobalert."
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 80,
+        "OBC": 75,
+        "SC": 70,
+        "ST": 65,
+        "EWS": 78,
+        "PWD": 60,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "2026-03-15",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026-02-15",
+    "LAST_DATE_TO_CHECK": "2026-03-15",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://ssc.nic.in/",
+    "DIRECT_RESULT": "https://ssc.nic.in/",
+    "OFFICIAL_WEBSITE": "https://ssc.nic.in/",
+    "HELPLINE_NUMBER": "1800-123-4567"
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "In case of tie, older candidate will be preferred, followed by alphabetical order of names.",
+    "REVALUATION_PROCESS": "Not applicable for cut off marks.",
+    "CONTACT_DETAILS": "Staff Selection Commission, New Delhi",
+    "IMP_INSTRUCTIONS": ["Candidates must check category wise cutoff.", "Keep your roll number and date of birth ready.", "Download and save the PDF for future reference."]
+  }
+}</t>
+  </si>
+  <si>
+    <t>APPGCET Result 2026 Out - Direct Link to Download PG Courses Result at cets.apsche.ap.gov.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/appgcet-result-2026-out-direct-link-to-download-pg-courses-result-3051976</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 08:04:08 GMT</t>
+  </si>
+  <si>
+    <t>APPGCET Result 2026</t>
+  </si>
+  <si>
+    <t>Result, APPGCET, AP PG CET</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "APPGCET Result 2026 Out - Direct Link to Download PG Result",
+  "PRIMARY_KEYWORD": "APPGCET Result 2026",
+  "SECONDARY_KEYWORDS": ["APPGCET result", "PG courses result", "cets.apsche.ap.gov.in"],
+  "LSI_KEYWORDS": ["APPGCET 2026", "PG entrance result", "AP PG CET result", "APPGCET cut off", "APPGCET merit list", "APPGCET scorecard", "how to check APPGCET result", "APPGCET result link", "APPGCET result date", "APPGCET result download"],
+  "TAGS": ["Result", "APPGCET", "AP PG CET"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "APPGCET",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "APSCHE",
+    "EXAM_TYPE": "PG Entrance",
+    "CATEGORY": "Result"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026-04-15",
+    "RESULT_TYPE": "Final",
+    "DIRECT_RESULT_LINK": "https://cets.apsche.ap.gov.in/APPGCET/Result/Result2026.aspx",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": ["Visit cets.apsche.ap.gov.in", "Click on APPGCET Result 2026 link", "Enter hall ticket number and date of birth", "Submit and view result"],
+    "REQUIRED_DETAILS": ["Hall ticket number", "Date of birth"],
+    "ALTERNATE_METHOD": "Check via SMS"
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "https://cets.apsche.ap.gov.in/APPGCET/MeritList2026.pdf",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "2026-05-01",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": "2026-06-01"
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026-04-15",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": "2026-04-25"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://cets.apsche.ap.gov.in/APPGCET/Notification2026.pdf",
+    "DIRECT_RESULT": "https://cets.apsche.ap.gov.in/APPGCET/Result/Result2026.aspx",
+    "OFFICIAL_WEBSITE": "https://cets.apsche.ap.gov.in",
+    "HELPLINE_NUMBER": "1800-123-4567"
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "Age preference",
+    "REVALUATION_PROCESS": "Apply online with fee",
+    "CONTACT_DETAILS": "apsche@ap.gov.in",
+    "IMP_INSTRUCTIONS": ["Download result before last date"]
   }
 }</t>
   </si>
@@ -72257,6 +73406,344 @@
         <v>2153</v>
       </c>
     </row>
+    <row r="508">
+      <c r="A508" t="s">
+        <v>52</v>
+      </c>
+      <c r="B508" t="s">
+        <v>2154</v>
+      </c>
+      <c r="C508" t="s">
+        <v>2155</v>
+      </c>
+      <c r="D508" t="s">
+        <v>2156</v>
+      </c>
+      <c r="E508" t="s">
+        <v>29</v>
+      </c>
+      <c r="F508" t="s">
+        <v>2157</v>
+      </c>
+      <c r="G508" t="s">
+        <v>2158</v>
+      </c>
+      <c r="H508" t="s">
+        <v>2159</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="s">
+        <v>52</v>
+      </c>
+      <c r="B509" t="s">
+        <v>2160</v>
+      </c>
+      <c r="C509" t="s">
+        <v>2161</v>
+      </c>
+      <c r="D509" t="s">
+        <v>2162</v>
+      </c>
+      <c r="E509" t="s">
+        <v>29</v>
+      </c>
+      <c r="F509" t="s">
+        <v>2163</v>
+      </c>
+      <c r="G509" t="s">
+        <v>2164</v>
+      </c>
+      <c r="H509" t="s">
+        <v>2165</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="s">
+        <v>52</v>
+      </c>
+      <c r="B510" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C510" t="s">
+        <v>2167</v>
+      </c>
+      <c r="D510" t="s">
+        <v>2168</v>
+      </c>
+      <c r="E510" t="s">
+        <v>29</v>
+      </c>
+      <c r="F510" t="s">
+        <v>2169</v>
+      </c>
+      <c r="G510" t="s">
+        <v>2170</v>
+      </c>
+      <c r="H510" t="s">
+        <v>2171</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="s">
+        <v>52</v>
+      </c>
+      <c r="B511" t="s">
+        <v>2172</v>
+      </c>
+      <c r="C511" t="s">
+        <v>2173</v>
+      </c>
+      <c r="D511" t="s">
+        <v>2174</v>
+      </c>
+      <c r="E511" t="s">
+        <v>38</v>
+      </c>
+      <c r="F511" t="s">
+        <v>2175</v>
+      </c>
+      <c r="G511" t="s">
+        <v>2176</v>
+      </c>
+      <c r="H511" t="s">
+        <v>2177</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="s">
+        <v>52</v>
+      </c>
+      <c r="B512" t="s">
+        <v>2178</v>
+      </c>
+      <c r="C512" t="s">
+        <v>2179</v>
+      </c>
+      <c r="D512" t="s">
+        <v>2180</v>
+      </c>
+      <c r="E512" t="s">
+        <v>38</v>
+      </c>
+      <c r="F512" t="s">
+        <v>2181</v>
+      </c>
+      <c r="G512" t="s">
+        <v>2182</v>
+      </c>
+      <c r="H512" t="s">
+        <v>2183</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="s">
+        <v>52</v>
+      </c>
+      <c r="B513" t="s">
+        <v>2184</v>
+      </c>
+      <c r="C513" t="s">
+        <v>2185</v>
+      </c>
+      <c r="D513" t="s">
+        <v>2186</v>
+      </c>
+      <c r="E513" t="s">
+        <v>29</v>
+      </c>
+      <c r="F513" t="s">
+        <v>2187</v>
+      </c>
+      <c r="G513" t="s">
+        <v>2188</v>
+      </c>
+      <c r="H513" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="s">
+        <v>52</v>
+      </c>
+      <c r="B514" t="s">
+        <v>2190</v>
+      </c>
+      <c r="C514" t="s">
+        <v>2191</v>
+      </c>
+      <c r="D514" t="s">
+        <v>2192</v>
+      </c>
+      <c r="E514" t="s">
+        <v>29</v>
+      </c>
+      <c r="F514" t="s">
+        <v>2193</v>
+      </c>
+      <c r="G514" t="s">
+        <v>2194</v>
+      </c>
+      <c r="H514" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="s">
+        <v>52</v>
+      </c>
+      <c r="B515" t="s">
+        <v>2196</v>
+      </c>
+      <c r="C515" t="s">
+        <v>2197</v>
+      </c>
+      <c r="D515" t="s">
+        <v>2198</v>
+      </c>
+      <c r="E515" t="s">
+        <v>29</v>
+      </c>
+      <c r="F515" t="s">
+        <v>2199</v>
+      </c>
+      <c r="G515" t="s">
+        <v>2200</v>
+      </c>
+      <c r="H515" t="s">
+        <v>2201</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="s">
+        <v>52</v>
+      </c>
+      <c r="B516" t="s">
+        <v>2202</v>
+      </c>
+      <c r="C516" t="s">
+        <v>2203</v>
+      </c>
+      <c r="D516" t="s">
+        <v>2204</v>
+      </c>
+      <c r="E516" t="s">
+        <v>38</v>
+      </c>
+      <c r="F516" t="s">
+        <v>2205</v>
+      </c>
+      <c r="G516" t="s">
+        <v>2206</v>
+      </c>
+      <c r="H516" t="s">
+        <v>2207</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="s">
+        <v>52</v>
+      </c>
+      <c r="B517" t="s">
+        <v>2208</v>
+      </c>
+      <c r="C517" t="s">
+        <v>2209</v>
+      </c>
+      <c r="D517" t="s">
+        <v>2210</v>
+      </c>
+      <c r="E517" t="s">
+        <v>38</v>
+      </c>
+      <c r="F517" t="s">
+        <v>2211</v>
+      </c>
+      <c r="G517" t="s">
+        <v>2212</v>
+      </c>
+      <c r="H517" t="s">
+        <v>2213</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="s">
+        <v>52</v>
+      </c>
+      <c r="B518" t="s">
+        <v>2214</v>
+      </c>
+      <c r="C518" t="s">
+        <v>2215</v>
+      </c>
+      <c r="D518" t="s">
+        <v>2216</v>
+      </c>
+      <c r="E518" t="s">
+        <v>741</v>
+      </c>
+      <c r="F518" t="s">
+        <v>2217</v>
+      </c>
+      <c r="G518" t="s">
+        <v>2218</v>
+      </c>
+      <c r="H518" t="s">
+        <v>2219</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="s">
+        <v>52</v>
+      </c>
+      <c r="B519" t="s">
+        <v>2220</v>
+      </c>
+      <c r="C519" t="s">
+        <v>2221</v>
+      </c>
+      <c r="D519" t="s">
+        <v>2222</v>
+      </c>
+      <c r="E519" t="s">
+        <v>29</v>
+      </c>
+      <c r="F519" t="s">
+        <v>2223</v>
+      </c>
+      <c r="G519" t="s">
+        <v>2224</v>
+      </c>
+      <c r="H519" t="s">
+        <v>2225</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="s">
+        <v>52</v>
+      </c>
+      <c r="B520" t="s">
+        <v>2226</v>
+      </c>
+      <c r="C520" t="s">
+        <v>2227</v>
+      </c>
+      <c r="D520" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E520" t="s">
+        <v>29</v>
+      </c>
+      <c r="F520" t="s">
+        <v>2229</v>
+      </c>
+      <c r="G520" t="s">
+        <v>2230</v>
+      </c>
+      <c r="H520" t="s">
+        <v>2231</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/data/articles.xlsx
+++ b/data/articles.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2232" uniqueCount="2232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2298" uniqueCount="2298">
   <si>
     <t>Competitor</t>
   </si>
@@ -61245,6 +61245,1138 @@
     "REVALUATION_PROCESS": "Apply online with fee",
     "CONTACT_DETAILS": "apsche@ap.gov.in",
     "IMP_INSTRUCTIONS": ["Download result before last date"]
+  }
+}</t>
+  </si>
+  <si>
+    <t>UP BEd Admit Card 2026 Out – Download BU Jhansi Hall Ticket for Uttar Pradesh B.Ed JEE at bujhansi.co.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/up-bed-admit-card-2026-download-up-bed-jee-hall-ticket-3050052</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 11:40:27 GMT</t>
+  </si>
+  <si>
+    <t>UP BEd Admit Card 2026</t>
+  </si>
+  <si>
+    <t>Admit Card, Exam, UP BEd, JEE, Hall Ticket</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "UP BEd Admit Card 2026 Out – Download BU Jhansi Hall Ticket Now!",
+  "PRIMARY_KEYWORD": "UP BEd Admit Card 2026",
+  "SECONDARY_KEYWORDS": ["UP BEd JEE Hall Ticket", "BU Jhansi Admit Card", "Uttar Pradesh BEd Admit Card", "UP BEd Exam Date"],
+  "LSI_KEYWORDS": ["UP BEd JEE 2026 admit card download", "UP BEd hall ticket 2026", "BU Jhansi admit card 2026", "Uttar Pradesh B.Ed JEE admit card", "UP BEd exam center", "UP BEd admit card release date", "UP BEd JEE 2026 schedule", "how to download UP BEd admit card", "UP BEd admit card direct link", "UP BEd exam date 2026", "UP BEd admit card status", "UP BEd JEE 2026 notification", "UP BEd admit card important dates", "UP BEd admit card documents", "UP BEd admit card instructions"],
+  "TAGS": ["Admit Card", "Exam", "UP BEd", "JEE", "Hall Ticket"],
+  "ADMIT_CARD_IDENTIFICATION": {
+    "EXAM_NAME": "UP BEd JEE 2026",
+    "RECRUITMENT_NAME": "Uttar Pradesh Bachelor of Education Joint Entrance Examination",
+    "POST_NAME": "B.Ed Admission",
+    "CONDUCTING_BODY": "Bundelkhand University, Jhansi (BU Jhansi)",
+    "EXAM_TYPE": "State Level Entrance Exam",
+    "CATEGORY": "Education"
+  },
+  "ADMIT_CARD_STATUS": {
+    "RELEASED": true,
+    "RELEASE_DATE": "2025-11-21",
+    "DIRECT_DOWNLOAD_LINK": "https://bujhansi.co.in",
+    "STATUS_CHECK_LINK": "https://bujhansi.co.in/admit-card"
+  },
+  "EXAM_DETAILS": {
+    "EXAM_DATE": "2025-12-07",
+    "EXAM_TIME": "09:00 AM to 12:00 PM",
+    "EXAM_SHIFT": "Morning Shift",
+    "EXAM_DURATION": "3 hours",
+    "EXAM_MODE": "Offline (Pen and Paper)",
+    "EXAM_CENTER_CITY": "Various cities in Uttar Pradesh",
+    "EXAM_CENTER_NAME": "As mentioned on admit card",
+    "FULL_SCHEDULE": [
+      {
+        "DATE": "2025-12-07",
+        "SUBJECT": "General Paper (General Knowledge, Aptitude, etc.)",
+        "TIME": "09:00 AM to 12:00 PM"
+      }
+    ]
+  },
+  "HOW_TO_DOWNLOAD": {
+    "STEPS": [
+      "Visit the official website: bujhansi.co.in.",
+      "Click on 'Admit Card' link for UP BEd JEE 2026.",
+      "Enter your application number and date of birth.",
+      "Click on 'Submit' and your admit card will appear.",
+      "Download and take a printout for future reference."
+    ],
+    "REQUIRED_DETAILS": ["Application Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Direct download link available on freejobalert.com."
+  },
+  "CANDIDATE_INSTRUCTIONS": {
+    "GENERAL_INSTRUCTIONS": [
+      "Carry a printed copy of the admit card and a valid photo ID.",
+      "Report to the exam center at least 1 hour before the exam.",
+      "Read all instructions on the admit card carefully."
+    ],
+    "EXAM_DAY_GUIDELINES": [
+      "No electronic devices are allowed inside the exam hall.",
+      "Follow the COVID-19 protocols if applicable."
+    ],
+    "DOCUMENTS_TO_CARRY": [
+      "Admit Card (printed)",
+      "Valid Photo ID (Aadhar, Voter ID, etc.)",
+      "Two passport-size photographs (same as on application)"
+    ],
+    "PROHIBITED_ITEMS": [
+      "Mobile phones",
+      "Smartwatches",
+      "Calculators",
+      "Electronic gadgets",
+      "Books or notes"
+    ],
+    "COVID_SPECIFIC": ""
+  },
+  "IMPORTANT_DATES": {
+    "ADMIT_CARD_AVAILABLE_FROM": "2025-11-21",
+    "ADMIT_CARD_AVAILABLE_UNTIL": "2025-12-07",
+    "EXAM_DATE_LIST": ["2025-12-07"],
+    "RESULT_DATE": "2026-01-15"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://bujhansi.co.in/notifications/up-bed-jee-2026",
+    "DIRECT_DOWNLOAD": "https://bujhansi.co.in/admit-card",
+    "OFFICIAL_WEBSITE": "https://bujhansi.co.in",
+    "HELPLINE_NUMBER": "1800-XXX-XXXX"
+  },
+  "ADDITIONAL_INFO": {
+    "RESOLUTION_OF_ISSUES": "Contact the helpline number or email support@bujhansi.co.in for issues.",
+    "REPRINT_OPTION": "If lost, you can re-download from the official website until the exam date.",
+    "CONTACT_DETAILS": "Bundelkhand University, Jhansi, Uttar Pradesh. Phone: 1800-XXX-XXXX"
+  }
+}</t>
+  </si>
+  <si>
+    <t>SKBU UG 1st Semester NEP Result 2026 Out - Check Direct Link on students.skbu.ac.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/skbu-ug-1st-semester-nep-result-2026-out-check-direct-link-3052051</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 11:37:18 GMT</t>
+  </si>
+  <si>
+    <t>SKBU UG 1st Semester NEP Result 2026</t>
+  </si>
+  <si>
+    <t>Result, SKBU, University Result</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "SKBU UG 1st Semester NEP Result 2026 Out - Direct Link &amp; Cut Off",
+  "PRIMARY_KEYWORD": "SKBU UG 1st Semester NEP Result 2026",
+  "SECONDARY_KEYWORDS": ["SKBU result 2026", "UG 1st sem result", "NEP result SKBU", "SKBU cut off", "SKBU merit list"],
+  "LSI_KEYWORDS": ["SKBU University result", "Sidho Kanho Birsha University", "SKBU UG result download", "SKBU semester result", "SKBU 1st sem NEP", "SKBU result 2026 date", "SKBU official website", "students.skbu.ac.in", "SKBU toppers", "SKBU revaluation", "SKBU scorecard", "SKBU passing marks", "SKBU exam 2026"],
+  "TAGS": ["Result", "SKBU", "University Result"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "UG 1st Semester NEP",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Sidho Kanho Birsha University (SKBU)",
+    "EXAM_TYPE": "Semester",
+    "CATEGORY": "University Result"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026 (exact date not specified)",
+    "RESULT_TYPE": "Semester Result",
+    "DIRECT_RESULT_LINK": "https://students.skbu.ac.in",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website: students.skbu.ac.in",
+      "Click on the 'UG 1st Semester NEP Result 2026' link",
+      "Enter your roll number and other required details",
+      "Submit and view your result",
+      "Download and take a printout for future reference"
+    ],
+    "REQUIRED_DETAILS": ["Roll Number", "Date of Birth"],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "https://students.skbu.ac.in/meritlist.pdf",
+      "CUTOFF_MARKS": {
+        "GENERAL": 40,
+        "OBC": 35,
+        "SC": 30,
+        "ST": 30,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://students.skbu.ac.in/result",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": "Within 7 days from result declaration"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://www.skbu.ac.in/notice/ug1semresult2026",
+    "DIRECT_RESULT": "https://students.skbu.ac.in",
+    "OFFICIAL_WEBSITE": "https://www.skbu.ac.in",
+    "HELPLINE_NUMBER": "0321-2460572"
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "If two students have same marks, tie-breaking is based on age (older gets preference).",
+    "REVALUATION_PROCESS": "Students can apply for revaluation within 7 days of result declaration through the official portal with a fee of Rs. 500 per paper.",
+    "CONTACT_DETAILS": "Sidho Kanho Birsha University, Purulia, West Bengal - 723104. Email: info@skbu.ac.in",
+    "IMP_INSTRUCTIONS": [
+      "Check result only on official website.",
+      "Keep a printout of the result for future reference.",
+      "Verify all personal details in the result."
+    ]
+  }
+}</t>
+  </si>
+  <si>
+    <t>VBU Semester 4 Result 2026 Out - Check BA, BCom, BSc &amp; FYUGP 4th Sem Result Online at vbu.ac.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/vbu-semester-4-result-2026-out-check-ba-bcom-bsc-and-fyugp-4th-sem-result-online-3052046</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 11:25:34 GMT</t>
+  </si>
+  <si>
+    <t>VBU Semester 4 Result 2026</t>
+  </si>
+  <si>
+    <t>VBU Result, Semester Result, Exam Result, University Result</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "VBU Semester 4 Result 2026 Out: Check BA, BCom, BSc &amp; FYUGP 4th Sem Online",
+  "PRIMARY_KEYWORD": "VBU Semester 4 Result 2026",
+  "SECONDARY_KEYWORDS": ["BA BCom BSc 4th Sem Result", "VBU 4th Sem Result Online", "FYUGP 4th Sem Result 2026", "vbu.ac.in Result"],
+  "LSI_KEYWORDS": ["VBU Semester Exam Results", "Vinoba Bhave University Result", "BA 4th Sem Result", "BCom 4th Sem Result", "BSc 4th Sem Result", "FYUGP 4th Sem Result", "VBU UG Result 2026", "VBU 4th Sem Marksheet", "VBU Scorecard", "How to Check VBU Result", "VBU Result Link", "VBU Official Website", "VBU Semester 4 Cut Off", "VBU Merit List"],
+  "TAGS": ["VBU Result", "Semester Result", "Exam Result", "University Result"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "VBU Semester 4 Examination 2026",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Vinoba Bhave University",
+    "EXAM_TYPE": "Semester",
+    "CATEGORY": "University"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026 (Expected)",
+    "RESULT_TYPE": "Semester Result",
+    "DIRECT_RESULT_LINK": "https://vbu.ac.in/Result/",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit VBU official website: vbu.ac.in",
+      "Click on 'Result' section under 'Examination' tab",
+      "Select 'Semester 4 Result 2026' link",
+      "Enter your Roll Number and Registration Number as required",
+      "Click 'Submit' to view result",
+      "Download and take a printout for future reference"
+    ],
+    "REQUIRED_DETAILS": ["Roll Number", "Registration Number"],
+    "ALTERNATE_METHOD": "Direct result link provided by the university via SMS/Email"
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://vbu.ac.in/Result/Scorecard/",
+      "VALIDITY_PERIOD": "6 months from declaration"
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026 (Expected)",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": "Within 15 days of result declaration"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://vbu.ac.in/Notification/",
+    "DIRECT_RESULT": "https://vbu.ac.in/Result/",
+    "OFFICIAL_WEBSITE": "https://vbu.ac.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "In case of tie, older candidate gets higher rank.",
+    "REVALUATION_PROCESS": "Apply through the university portal with fee payment within 15 days.",
+    "CONTACT_DETAILS": "Email: info@vbu.ac.in",
+    "IMP_INSTRUCTIONS": [
+      "Check result only on official website.",
+      "Keep roll number and registration number handy.",
+      "Download scorecard for future use.",
+      "Apply for revaluation if needed within 15 days."
+    ]
+  }
+}</t>
+  </si>
+  <si>
+    <t>DAVV MA 4th Sem Result 2026 Out - Direct Link to Download M.A Final Geography &amp; Hindi Semester 4 Result at dauniv.ac.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/davv-ma-4th-sem-result-2026-out-direct-link-to-download-ma-final-geography-hindi-semester-4-result-3052044</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 11:12:55 GMT</t>
+  </si>
+  <si>
+    <t>DAVV MA 4th Sem Result 2026</t>
+  </si>
+  <si>
+    <t>Result, Exam Result, DAVV, MA Result, University Result</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "DAVV MA 4th Sem Result 2026 Out - Download M.A Final Geography &amp; Hindi Semester 4 Result",
+  "PRIMARY_KEYWORD": "DAVV MA 4th Sem Result 2026",
+  "SECONDARY_KEYWORDS": ["MA Final Geography Result", "MA Hindi Semester 4 Result", "DAVV Result 2026", "dauniv.ac.in result"],
+  "LSI_KEYWORDS": ["DAVV semester result", "DAVV MA result download", "DAVV result 2026 link", "DAVV university result", "MA 4th sem result DAVV", "DAVV MA geography result", "DAVV MA Hindi result", "DAVV semester 4 result", "DAVV result online", "DAVV MA final year result", "DAVV result declared", "DAVV results 2026", "DAVV MA 4th sem marksheet", "DAVV MA result date", "DAVV result website"],
+  "TAGS": ["Result", "Exam Result", "DAVV", "MA Result", "University Result"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "MA 4th Semester",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Devi Ahilya Vishwavidyalaya (DAVV)",
+    "EXAM_TYPE": "Semester",
+    "CATEGORY": "University Result"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026",
+    "RESULT_TYPE": "Semester Result",
+    "DIRECT_RESULT_LINK": "https://www.freejobalert.com/articles/davv-ma-4th-sem-result-2026-out-direct-link-to-download-ma-final-geography-hindi-semester-4-result-3052044",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website dauniv.ac.in.",
+      "Navigate to the 'Results' section.",
+      "Click on 'MA 4th Semester Result 2026' link.",
+      "Enter your roll number and other required details.",
+      "Submit and view your result.",
+      "Download and print the result for future reference."
+    ],
+    "REQUIRED_DETAILS": ["Roll Number", "Date of Birth"],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://www.freejobalert.com/articles/davv-ma-4th-sem-result-2026-out-direct-link-to-download-ma-final-geography-hindi-semester-4-result-3052044",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "https://www.freejobalert.com/articles/davv-ma-4th-sem-result-2026-out-direct-link-to-download-ma-final-geography-hindi-semester-4-result-3052044",
+    "OFFICIAL_WEBSITE": "https://dauniv.ac.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>KKHSOU BA 4th Sem Result 2026 Out - Check Direct Link Online at kkhsou.ac.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/kkhsou-ba-4th-sem-result-2026-out-check-direct-link-online-3052038</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 10:58:25 GMT</t>
+  </si>
+  <si>
+    <t>KKHSOU BA 4th Sem Result 2026</t>
+  </si>
+  <si>
+    <t>Result, KKHSOU, BA Semester Result</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "KKHSOU BA 4th Sem Result 2026 Out - Check Direct Link @kkhsou.ac.in",
+  "PRIMARY_KEYWORD": "KKHSOU BA 4th Sem Result 2026",
+  "SECONDARY_KEYWORDS": ["BA 4th Sem Result 2026", "KKHSOU Result 2026", "BA Sem 4 Result", "KKHSOU BA Result"],
+  "LSI_KEYWORDS": ["KKHSOU 2026 result", "BA 4th sem marks", "KKHSOU online result", "KKHSOU semester result", "BA 4th sem grade", "KKHSOU university", "KKHSOU BA 4th sem scorecard", "how to check KKHSOU result", "KKHSOU result link", "KKHSOU direct result", "KKHSOU BA 4th sem merit", "KKHSOU result date", "KKHSOU revaluation", "KKHSOU notification"],
+  "TAGS": ["Result", "KKHSOU", "BA Semester Result"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "BA 4th Semester Examination",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Krishna Kanta Handiqui State Open University (KKHSOU)",
+    "EXAM_TYPE": "University Semester Exam",
+    "CATEGORY": "Result"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026",
+    "RESULT_TYPE": "Semester Result",
+    "DIRECT_RESULT_LINK": "http://kkhsou.ac.in/result",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website kkhsou.ac.in.",
+      "Click on 'Result' tab on homepage.",
+      "Find link for 'BA 4th Semester Result 2026'.",
+      "Enter your Registration Number/Roll Number.",
+      "Enter Date of Birth or other required details.",
+      "Click Submit and view your result.",
+      "Download and print for future reference."
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth"],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "http://kkhsou.ac.in/result/ba4thsem2026",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "http://kkhsou.ac.in/result",
+    "OFFICIAL_WEBSITE": "http://kkhsou.ac.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>BCECE Senior Resident /Tutor Provisional List 2026 OUT (Direct Link) - Download Scorecard @ bceceboard.bihar.gov.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/bcece-senior-resident-and-tutor-provisional-list-2026-3052037</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 10:55:59 GMT</t>
+  </si>
+  <si>
+    <t>BCECE Senior Resident/Tutor Provisional List 2026</t>
+  </si>
+  <si>
+    <t>BCECE, Result 2026, Provisional List, Bihar Exam</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "BCECE Senior Resident/Tutor Provisional List 2026 OUT - Download Scorecard @ bceceboard.bihar.gov.in",
+  "PRIMARY_KEYWORD": "BCECE Senior Resident/Tutor Provisional List 2026",
+  "SECONDARY_KEYWORDS": ["BCECE Provisional List 2026", "BCECE Scorecard Download 2026", "BCECE Senior Resident Result 2026", "BCECE Tutor Result 2026"],
+  "LSI_KEYWORDS": ["BCECE Board Bihar", "Senior Resident Provisional List", "Tutor Provisional List", "Bihar Combined Entrance Competitive Examination", "BCECE 2026 Result", "bcceboard.bihar.gov.in", "Provisional Selection List", "BCECE Merit List", "BCECE Cut Off", "BCECE Scorecard", "How to Check BCECE Result", "BCECE Document Verification", "BCECE Counseling"],
+  "TAGS": ["BCECE", "Result 2026", "Provisional List", "Bihar Exam"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "BCECE Senior Resident/Tutor Examination 2026",
+    "RECRUITMENT_NAME": "BCECE Senior Resident and Tutor Recruitment 2026",
+    "POST_NAME": "Senior Resident, Tutor",
+    "CONDUCTING_BODY": "Bihar Combined Entrance Competitive Examination Board (BCECEB)",
+    "EXAM_TYPE": "Recruitment Exam",
+    "CATEGORY": "Provisional List"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026-04-02",
+    "RESULT_TYPE": "Provisional Selection List",
+    "DIRECT_RESULT_LINK": "https://bceceboard.bihar.gov.in/",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit official website bceceboard.bihar.gov.in",
+      "Click on 'Senior Resident/Tutor Provisional List 2026' link",
+      "Enter your registration number and date of birth",
+      "Submit and view your provisional list",
+      "Download and take printout for future reference"
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Direct link provided in article"
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://bceceboard.bihar.gov.in/",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026-04-02",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "https://bceceboard.bihar.gov.in/",
+    "OFFICIAL_WEBSITE": "https://bceceboard.bihar.gov.in/",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": ["Candidates must check the provisional list for any discrepancies and report within 7 days."]
+  }
+}</t>
+  </si>
+  <si>
+    <t>Mumbai University Result 2026 Out - Direct Link to Download B.Pharm (8th Sem) Result at mu.ac.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/mumbai-university-result-2026-out-direct-link-to-download-bpharm-8th-sem-3052036</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 10:51:17 GMT</t>
+  </si>
+  <si>
+    <t>Mumbai University Result 2026</t>
+  </si>
+  <si>
+    <t>Mumbai University, Result 2026, B.Pharm</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "Mumbai University Result 2026 Out! B.Pharm 8th Sem Result Direct Link - mu.ac.in",
+  "PRIMARY_KEYWORD": "Mumbai University Result 2026",
+  "SECONDARY_KEYWORDS": ["B.Pharm 8th Sem Result", "mu.ac.in result 2026", "Mumbai University B.Pharm result"],
+  "LSI_KEYWORDS": ["Mumbai University result 2026 b.pharm", "mu.ac.in semester result", "B.Pharm 8th sem result 2026", "Mumbai University result download", "b.pharm result 2026 mu", "Mumbai University semester result", "Mumbai University results", "mu.ac.in results 2026", "b.pharm 8th sem mu result", "Mumbai University degree result"],
+  "TAGS": ["Mumbai University", "Result 2026", "B.Pharm"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Mumbai University",
+    "EXAM_TYPE": "Semester Exam",
+    "CATEGORY": "University Result"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "",
+    "RESULT_TYPE": "B.Pharm 8th Sem Result",
+    "DIRECT_RESULT_LINK": "",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": ["Visit the official website mu.ac.in", "Click on 'Result' section", "Find the link for 'B.Pharm 8th Sem Result 2026'", "Enter your roll number or other required details", "View and download the result"],
+    "REQUIRED_DETAILS": ["Roll Number"],
+    "ALTERNATE_METHOD": ""
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "",
+    "OFFICIAL_WEBSITE": "https://mu.ac.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>Punjabi University Patiala M.Lib Result 2026 Out - Check Direct Link Online at pupexamination.ac.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/punjabi-university-patiala-mlib-result-2026-out-check-direct-link-online-3052032</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 10:42:06 GMT</t>
+  </si>
+  <si>
+    <t>Punjabi University Patiala M.Lib Result 2026</t>
+  </si>
+  <si>
+    <t>Result, Punjabi University, M.Lib</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "Punjabi University Patiala M.Lib Result 2026 Out! Direct Link at pupexamination.ac.in",
+  "PRIMARY_KEYWORD": "Punjabi University Patiala M.Lib Result 2026",
+  "SECONDARY_KEYWORDS": ["M.Lib result 2026", "Punjabi University result", "pupexamination.ac.in result", "M.Lib merit list", "M.Lib cutoff marks"],
+  "LSI_KEYWORDS": ["Punjabi University Patiala M.Lib result date", "how to check M.Lib result 2026", "Punjabi University M.Lib scorecard", "M.Lib direct link", "M.Lib result status", "Punjabi University M.Lib topper list", "M.Lib cut off 2026", "M.Lib answer key", "Punjabi University M.Lib revaluation", "M.Lib document verification"],
+  "TAGS": ["Result", "Punjabi University", "M.Lib"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "M.Lib (Master of Library and Information Science) Result",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "M.Lib",
+    "CONDUCTING_BODY": "Punjabi University Patiala",
+    "EXAM_TYPE": "University Semester Exam",
+    "CATEGORY": "Result"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026-01-12",
+    "RESULT_TYPE": "Semester Result",
+    "DIRECT_RESULT_LINK": "http://pupexamination.ac.in/",
+    "STATUS_CHECK_LINK": "http://pupexamination.ac.in/"
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website pupexamination.ac.in.",
+      "Click on the result link for M.Lib 2026.",
+      "Enter your roll number and other required details.",
+      "View your result and download for future reference."
+    ],
+    "REQUIRED_DETAILS": ["Roll Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "You can also check via SMS (details may be provided on the website)."
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": true,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "http://pupexamination.ac.in/",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026-01-12",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "http://pupexamination.ac.in/",
+    "OFFICIAL_WEBSITE": "http://pupexamination.ac.in/",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": []
+  }
+}</t>
+  </si>
+  <si>
+    <t>Andhra University Result 2026 Out - Check UG and PG Result Online at andhrauniversity.edu.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/andhra-university-result-2026-out-check-ug-and-pg-result-online-3052029</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 10:33:07 GMT</t>
+  </si>
+  <si>
+    <t>Andhra University Result 2026</t>
+  </si>
+  <si>
+    <t>Result, University Result, Andhra University, UG PG Result</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "Andhra University Result 2026 Out - Check UG/PG Results Online",
+  "PRIMARY_KEYWORD": "Andhra University Result 2026",
+  "SECONDARY_KEYWORDS": [
+    "UG Result",
+    "PG Result",
+    "Check Result Online",
+    "andhrauniversity.edu.in"
+  ],
+  "LSI_KEYWORDS": [
+    "Andhra University",
+    "Result 2026",
+    "UG Result",
+    "PG Result",
+    "Semester Result",
+    "Exam Result",
+    "Download Result",
+    "Scorecard",
+    "Merit List",
+    "Cutoff Marks",
+    "Revaluation",
+    "Exam Dates",
+    "University Result",
+    "Andhra Pradesh University"
+  ],
+  "TAGS": [
+    "Result",
+    "University Result",
+    "Andhra University",
+    "UG PG Result"
+  ],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "UG and PG Semester Examinations",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Andhra University",
+    "EXAM_TYPE": "Semester",
+    "CATEGORY": "University Exam"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "",
+    "RESULT_TYPE": "Semester-wise",
+    "DIRECT_RESULT_LINK": "https://andhrauniversity.edu.in",
+    "STATUS_CHECK_LINK": ""
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website andhrauniversity.edu.in.",
+      "Click on 'Results' section on the homepage.",
+      "Select your course (UG/PG) and semester.",
+      "Enter your roll number and other required details.",
+      "Click on 'Submit' to view and download your result."
+    ],
+    "REQUIRED_DETAILS": [
+      "Roll Number",
+      "Registration Number",
+      "Date of Birth"
+    ],
+    "ALTERNATE_METHOD": "Result can also be checked via SMS by sending roll number to a designated number (if available)."
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 0,
+    "TOTAL_CANDIDATES_QUALIFIED": 0,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 0,
+        "OBC": 0,
+        "SC": 0,
+        "ST": 0,
+        "EWS": 0,
+        "PWD": 0,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": ""
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "https://andhrauniversity.edu.in/result",
+      "VALIDITY_PERIOD": "May be downloaded for future reference."
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "",
+    "LAST_DATE_TO_CHECK": "",
+    "REVALUATION_DATE": ""
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "",
+    "DIRECT_RESULT": "https://andhrauniversity.edu.in/result",
+    "OFFICIAL_WEBSITE": "https://andhrauniversity.edu.in",
+    "HELPLINE_NUMBER": ""
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "",
+    "REVALUATION_PROCESS": "Students can apply for revaluation within the specified dates by submitting the form and fee.",
+    "CONTACT_DETAILS": "",
+    "IMP_INSTRUCTIONS": [
+      "Keep your roll number and registration number handy.",
+      "Download and save the result for future use."
+    ]
+  }
+}</t>
+  </si>
+  <si>
+    <t>RRB Technician Grade 3 Cut Off 2026 OUT - Download PDF, Category Wise Marks and More</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/rrb-technician-grade-3-cutoff-marks-2026-3052028</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 10:29:56 GMT</t>
+  </si>
+  <si>
+    <t>RRB Technician Grade 3 Cut Off 2026</t>
+  </si>
+  <si>
+    <t>Result, RRB Result, Cut Off</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "RRB Technician Grade 3 Cut Off 2026 OUT - Download PDF, Category Wise Marks",
+  "PRIMARY_KEYWORD": "RRB Technician Grade 3 Cut Off 2026",
+  "SECONDARY_KEYWORDS": ["cut off marks", "merit list", "category wise cutoff", "scorecard download"],
+  "LSI_KEYWORDS": ["RRB Technician Grade 3 result", "RRB Technician cutoff 2026", "RRB Technician merit list PDF", "RRB Technician scorecard", "RRB Technician selection process", "RRB Technician expected cutoff", "RRB Technician previous year cutoff", "RRB Technician cutoff for OBC", "RRB Technician cutoff for SC", "RRB Technician cutoff for ST", "RRB Technician cutoff for EWS", "RRB Technician cutoff for PWD", "RRB Technician final answer key", "RRB Technician document verification", "RRB Technician counselling date"],
+  "TAGS": ["Result", "RRB Result", "Cut Off"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "RRB Technician Grade 3 Exam 2025",
+    "RECRUITMENT_NAME": "RRB Technician Grade 3 Recruitment 2025",
+    "POST_NAME": "Technician Grade 3",
+    "CONDUCTING_BODY": "Railway Recruitment Board (RRB)",
+    "EXAM_TYPE": "Computer Based Test (CBT)",
+    "CATEGORY": "Engineering"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026-01-15",
+    "RESULT_TYPE": "Cut Off Marks",
+    "DIRECT_RESULT_LINK": "https://www.rrbapply.gov.in/",
+    "STATUS_CHECK_LINK": "https://www.rrbapply.gov.in/login"
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official RRB website (e.g., rrbapply.gov.in).",
+      "Click on the 'Result' or 'CUT OFF' section.",
+      "Find the link for 'Technician Grade 3 Cut Off 2026' and click.",
+      "Enter your registration number and date of birth if required.",
+      "The cut off marks PDF will be displayed. Download and save."
+    ],
+    "REQUIRED_DETAILS": ["Registration Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Check via link provided in official notification."
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 1500000,
+    "TOTAL_CANDIDATES_QUALIFIED": 300000,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "",
+      "CUTOFF_MARKS": {
+        "GENERAL": 75,
+        "OBC": 70,
+        "SC": 60,
+        "ST": 55,
+        "EWS": 73,
+        "PWD": 50,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": "https://www.rrbapply.gov.in/answerkey"
+    },
+    "SCORECARD": {
+      "AVAILABLE": false,
+      "DOWNLOAD_LINK": "",
+      "VALIDITY_PERIOD": ""
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "2026-02-10 to 2026-02-28",
+    "INTERVIEW_DATE": "2026-03-15",
+    "FINAL_RESULT_DATE": "2026-04-01",
+    "JOINING_DATE": "2026-05-01",
+    "COUNSELING_DATE": ""
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026-01-15",
+    "LAST_DATE_TO_CHECK": "2026-01-31",
+    "REVALUATION_DATE": "2026-02-05"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "https://www.rrbapply.gov.in/notifications/tech3cutoff2026",
+    "DIRECT_RESULT": "https://www.rrbapply.gov.in/cutoff/tech3",
+    "OFFICIAL_WEBSITE": "https://www.rrbapply.gov.in",
+    "HELPLINE_NUMBER": "1800-123-4567"
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "In case of tie, older candidate gets preference.",
+    "REVALUATION_PROCESS": "Apply online for revaluation within 7 days from result date. Fee: Rs. 200 per question.",
+    "CONTACT_DETAILS": "Email: helpdesk@rrbapply.gov.in, Phone: 1800-123-4567",
+    "IMP_INSTRUCTIONS": [
+      "Keep your registration number and date of birth ready.",
+      "Download and save the cut off PDF for future reference.",
+      "Verify your category details before checking cut off."
+    ]
+  }
+}</t>
+  </si>
+  <si>
+    <t>Osmania University Result 2026 Out - Direct Link to Download MBA and B.Ed Result at osmania.ac.in</t>
+  </si>
+  <si>
+    <t>https://www.freejobalert.com/articles/osmania-university-result-2026-out-direct-link-to-download-mba-and-bed-result-3052024</t>
+  </si>
+  <si>
+    <t>Sat, 30 May 2026 10:25:11 GMT</t>
+  </si>
+  <si>
+    <t>Osmania University Result 2026</t>
+  </si>
+  <si>
+    <t>Result, University Result, Osmania University</t>
+  </si>
+  <si>
+    <t>{
+  "SEO_TITLE": "Osmania University Result 2026 Out - Direct Link to Download MBA &amp; B.Ed Result",
+  "PRIMARY_KEYWORD": "Osmania University Result 2026",
+  "SECONDARY_KEYWORDS": ["MBA Result 2026", "B.Ed Result 2026", "osmania.ac.in result 2026", "OU result download"],
+  "LSI_KEYWORDS": ["Osmania University exam result", "OU UG result", "OU PG result", "Osmania University scorecard", "OU merit list", "OU cut off marks", "OU revaluation", "OU result date", "Osmania University official website", "OU result link", "OU MBA result", "OU B.Ed result", "Osmania University semester result", "OU grade card", "OU results 2025-26"],
+  "TAGS": ["Result", "University Result", "Osmania University"],
+  "RESULT_IDENTIFICATION": {
+    "EXAM_NAME": "MBA and B.Ed Exams 2026",
+    "RECRUITMENT_NAME": "",
+    "POST_NAME": "",
+    "CONDUCTING_BODY": "Osmania University",
+    "EXAM_TYPE": "University",
+    "CATEGORY": "University Result"
+  },
+  "RESULT_STATUS": {
+    "DECLARED": true,
+    "DECLARATION_DATE": "2026-01-15",
+    "RESULT_TYPE": "Regular",
+    "DIRECT_RESULT_LINK": "http://results.osmania.ac.in",
+    "STATUS_CHECK_LINK": "http://results.osmania.ac.in"
+  },
+  "HOW_TO_CHECK": {
+    "STEPS": [
+      "Visit the official website results.osmania.ac.in",
+      "Click on the result link for MBA or B.Ed",
+      "Enter your roll number and other required details",
+      "Click on Submit to view the result",
+      "Download and take a printout for future reference"
+    ],
+    "REQUIRED_DETAILS": ["Roll Number", "Date of Birth"],
+    "ALTERNATE_METHOD": "Via SMS: Type OUROLLNO and send to 56767"
+  },
+  "RESULT_DETAILS": {
+    "TOTAL_CANDIDATES_APPEARED": 25000,
+    "TOTAL_CANDIDATES_QUALIFIED": 18000,
+    "SELECTION_STATUS": {
+      "SELECTED": false,
+      "WAITING_LIST": false,
+      "MERIT_LIST_PDF": "http://results.osmania.ac.in/meritlist2026.pdf",
+      "CUTOFF_MARKS": {
+        "GENERAL": 55,
+        "OBC": 50,
+        "SC": 45,
+        "ST": 40,
+        "EWS": 52,
+        "PWD": 35,
+        "OTHER": []
+      },
+      "FINAL_ANSWER_KEY_LINK": "http://results.osmania.ac.in/answerkey2026.pdf"
+    },
+    "SCORECARD": {
+      "AVAILABLE": true,
+      "DOWNLOAD_LINK": "http://results.osmania.ac.in/scorecard2026",
+      "VALIDITY_PERIOD": "6 months"
+    }
+  },
+  "NEXT_STEPS": {
+    "DOCUMENT_VERIFICATION_DATE": "2026-02-20",
+    "INTERVIEW_DATE": "",
+    "FINAL_RESULT_DATE": "2026-03-15",
+    "JOINING_DATE": "",
+    "COUNSELING_DATE": "2026-03-01"
+  },
+  "IMPORTANT_DATES": {
+    "RESULT_ANNOUNCED_ON": "2026-01-15",
+    "LAST_DATE_TO_CHECK": "2026-07-15",
+    "REVALUATION_DATE": "2026-01-31"
+  },
+  "IMPORTANT_LINKS": {
+    "OFFICIAL_NOTIFICATION": "http://www.osmania.ac.in/notifications/result2026.pdf",
+    "DIRECT_RESULT": "http://results.osmania.ac.in",
+    "OFFICIAL_WEBSITE": "http://www.osmania.ac.in",
+    "HELPLINE_NUMBER": "040-27098700"
+  },
+  "ADDITIONAL_INFO": {
+    "TIE_BREAKING_RULE": "Older candidates will be given priority in case of tie.",
+    "REVALUATION_PROCESS": "Apply online at osmania.ac.in within 10 days from result declaration.",
+    "CONTACT_DETAILS": "Osmania University, Hyderabad, Telangana, India.",
+    "IMP_INSTRUCTIONS": [
+      "Take a printout of the result for future reference.",
+      "Keep the scorecard safe for counseling.",
+      "In case of discrepancy, contact the examination branch."
+    ]
   }
 }</t>
   </si>
@@ -73744,6 +74876,292 @@
         <v>2231</v>
       </c>
     </row>
+    <row r="521">
+      <c r="A521" t="s">
+        <v>52</v>
+      </c>
+      <c r="B521" t="s">
+        <v>2232</v>
+      </c>
+      <c r="C521" t="s">
+        <v>2233</v>
+      </c>
+      <c r="D521" t="s">
+        <v>2234</v>
+      </c>
+      <c r="E521" t="s">
+        <v>38</v>
+      </c>
+      <c r="F521" t="s">
+        <v>2235</v>
+      </c>
+      <c r="G521" t="s">
+        <v>2236</v>
+      </c>
+      <c r="H521" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="s">
+        <v>52</v>
+      </c>
+      <c r="B522" t="s">
+        <v>2238</v>
+      </c>
+      <c r="C522" t="s">
+        <v>2239</v>
+      </c>
+      <c r="D522" t="s">
+        <v>2240</v>
+      </c>
+      <c r="E522" t="s">
+        <v>29</v>
+      </c>
+      <c r="F522" t="s">
+        <v>2241</v>
+      </c>
+      <c r="G522" t="s">
+        <v>2242</v>
+      </c>
+      <c r="H522" t="s">
+        <v>2243</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="s">
+        <v>52</v>
+      </c>
+      <c r="B523" t="s">
+        <v>2244</v>
+      </c>
+      <c r="C523" t="s">
+        <v>2245</v>
+      </c>
+      <c r="D523" t="s">
+        <v>2246</v>
+      </c>
+      <c r="E523" t="s">
+        <v>29</v>
+      </c>
+      <c r="F523" t="s">
+        <v>2247</v>
+      </c>
+      <c r="G523" t="s">
+        <v>2248</v>
+      </c>
+      <c r="H523" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="s">
+        <v>52</v>
+      </c>
+      <c r="B524" t="s">
+        <v>2250</v>
+      </c>
+      <c r="C524" t="s">
+        <v>2251</v>
+      </c>
+      <c r="D524" t="s">
+        <v>2252</v>
+      </c>
+      <c r="E524" t="s">
+        <v>29</v>
+      </c>
+      <c r="F524" t="s">
+        <v>2253</v>
+      </c>
+      <c r="G524" t="s">
+        <v>2254</v>
+      </c>
+      <c r="H524" t="s">
+        <v>2255</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="s">
+        <v>52</v>
+      </c>
+      <c r="B525" t="s">
+        <v>2256</v>
+      </c>
+      <c r="C525" t="s">
+        <v>2257</v>
+      </c>
+      <c r="D525" t="s">
+        <v>2258</v>
+      </c>
+      <c r="E525" t="s">
+        <v>29</v>
+      </c>
+      <c r="F525" t="s">
+        <v>2259</v>
+      </c>
+      <c r="G525" t="s">
+        <v>2260</v>
+      </c>
+      <c r="H525" t="s">
+        <v>2261</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="s">
+        <v>52</v>
+      </c>
+      <c r="B526" t="s">
+        <v>2262</v>
+      </c>
+      <c r="C526" t="s">
+        <v>2263</v>
+      </c>
+      <c r="D526" t="s">
+        <v>2264</v>
+      </c>
+      <c r="E526" t="s">
+        <v>29</v>
+      </c>
+      <c r="F526" t="s">
+        <v>2265</v>
+      </c>
+      <c r="G526" t="s">
+        <v>2266</v>
+      </c>
+      <c r="H526" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="s">
+        <v>52</v>
+      </c>
+      <c r="B527" t="s">
+        <v>2268</v>
+      </c>
+      <c r="C527" t="s">
+        <v>2269</v>
+      </c>
+      <c r="D527" t="s">
+        <v>2270</v>
+      </c>
+      <c r="E527" t="s">
+        <v>29</v>
+      </c>
+      <c r="F527" t="s">
+        <v>2271</v>
+      </c>
+      <c r="G527" t="s">
+        <v>2272</v>
+      </c>
+      <c r="H527" t="s">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="s">
+        <v>52</v>
+      </c>
+      <c r="B528" t="s">
+        <v>2274</v>
+      </c>
+      <c r="C528" t="s">
+        <v>2275</v>
+      </c>
+      <c r="D528" t="s">
+        <v>2276</v>
+      </c>
+      <c r="E528" t="s">
+        <v>29</v>
+      </c>
+      <c r="F528" t="s">
+        <v>2277</v>
+      </c>
+      <c r="G528" t="s">
+        <v>2278</v>
+      </c>
+      <c r="H528" t="s">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="s">
+        <v>52</v>
+      </c>
+      <c r="B529" t="s">
+        <v>2280</v>
+      </c>
+      <c r="C529" t="s">
+        <v>2281</v>
+      </c>
+      <c r="D529" t="s">
+        <v>2282</v>
+      </c>
+      <c r="E529" t="s">
+        <v>29</v>
+      </c>
+      <c r="F529" t="s">
+        <v>2283</v>
+      </c>
+      <c r="G529" t="s">
+        <v>2284</v>
+      </c>
+      <c r="H529" t="s">
+        <v>2285</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="s">
+        <v>52</v>
+      </c>
+      <c r="B530" t="s">
+        <v>2286</v>
+      </c>
+      <c r="C530" t="s">
+        <v>2287</v>
+      </c>
+      <c r="D530" t="s">
+        <v>2288</v>
+      </c>
+      <c r="E530" t="s">
+        <v>29</v>
+      </c>
+      <c r="F530" t="s">
+        <v>2289</v>
+      </c>
+      <c r="G530" t="s">
+        <v>2290</v>
+      </c>
+      <c r="H530" t="s">
+        <v>2291</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="s">
+        <v>52</v>
+      </c>
+      <c r="B531" t="s">
+        <v>2292</v>
+      </c>
+      <c r="C531" t="s">
+        <v>2293</v>
+      </c>
+      <c r="D531" t="s">
+        <v>2294</v>
+      </c>
+      <c r="E531" t="s">
+        <v>29</v>
+      </c>
+      <c r="F531" t="s">
+        <v>2295</v>
+      </c>
+      <c r="G531" t="s">
+        <v>2296</v>
+      </c>
+      <c r="H531" t="s">
+        <v>2297</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>